--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.02.20261</t>
-  </si>
-  <si>
-    <t>25.02.20262</t>
-  </si>
-  <si>
-    <t>25.02.20263</t>
-  </si>
-  <si>
-    <t>25.02.20264</t>
-  </si>
-  <si>
-    <t>25.02.20265</t>
-  </si>
-  <si>
-    <t>25.02.20266</t>
-  </si>
-  <si>
-    <t>25.02.20267</t>
-  </si>
-  <si>
-    <t>25.02.20268</t>
-  </si>
-  <si>
-    <t>25.02.20269</t>
-  </si>
-  <si>
-    <t>25.02.202610</t>
-  </si>
-  <si>
-    <t>25.02.202611</t>
-  </si>
-  <si>
-    <t>25.02.202612</t>
-  </si>
-  <si>
-    <t>25.02.202613</t>
-  </si>
-  <si>
-    <t>25.02.202614</t>
-  </si>
-  <si>
-    <t>25.02.202615</t>
-  </si>
-  <si>
-    <t>25.02.202616</t>
-  </si>
-  <si>
-    <t>25.02.202617</t>
-  </si>
-  <si>
-    <t>25.02.202618</t>
-  </si>
-  <si>
-    <t>25.02.202619</t>
-  </si>
-  <si>
-    <t>25.02.202620</t>
-  </si>
-  <si>
-    <t>25.02.202621</t>
-  </si>
-  <si>
-    <t>25.02.202622</t>
-  </si>
-  <si>
-    <t>25.02.202623</t>
-  </si>
-  <si>
-    <t>25.02.202624</t>
-  </si>
-  <si>
-    <t>25.02.202625</t>
-  </si>
-  <si>
-    <t>25.02.202626</t>
-  </si>
-  <si>
-    <t>25.02.202627</t>
-  </si>
-  <si>
-    <t>25.02.202628</t>
-  </si>
-  <si>
-    <t>25.02.202629</t>
-  </si>
-  <si>
-    <t>25.02.202630</t>
-  </si>
-  <si>
-    <t>25.02.202631</t>
-  </si>
-  <si>
-    <t>25.02.202632</t>
-  </si>
-  <si>
-    <t>25.02.202633</t>
-  </si>
-  <si>
-    <t>25.02.202634</t>
-  </si>
-  <si>
-    <t>25.02.202635</t>
-  </si>
-  <si>
-    <t>25.02.202636</t>
-  </si>
-  <si>
-    <t>25.02.202637</t>
-  </si>
-  <si>
-    <t>25.02.202638</t>
-  </si>
-  <si>
-    <t>25.02.202639</t>
-  </si>
-  <si>
-    <t>25.02.202640</t>
-  </si>
-  <si>
-    <t>25.02.202641</t>
-  </si>
-  <si>
-    <t>25.02.202642</t>
-  </si>
-  <si>
-    <t>25.02.202643</t>
-  </si>
-  <si>
-    <t>25.02.202644</t>
-  </si>
-  <si>
-    <t>25.02.202645</t>
-  </si>
-  <si>
-    <t>25.02.202646</t>
-  </si>
-  <si>
-    <t>25.02.202647</t>
-  </si>
-  <si>
-    <t>25.02.202648</t>
-  </si>
-  <si>
-    <t>25.02.202649</t>
-  </si>
-  <si>
-    <t>25.02.202650</t>
-  </si>
-  <si>
-    <t>25.02.202651</t>
-  </si>
-  <si>
-    <t>25.02.202652</t>
-  </si>
-  <si>
-    <t>25.02.202653</t>
-  </si>
-  <si>
-    <t>25.02.202654</t>
-  </si>
-  <si>
-    <t>25.02.202655</t>
-  </si>
-  <si>
-    <t>25.02.202656</t>
-  </si>
-  <si>
-    <t>25.02.202657</t>
-  </si>
-  <si>
-    <t>25.02.202658</t>
-  </si>
-  <si>
-    <t>25.02.202659</t>
-  </si>
-  <si>
-    <t>25.02.202660</t>
-  </si>
-  <si>
-    <t>25.02.202661</t>
-  </si>
-  <si>
-    <t>25.02.202662</t>
-  </si>
-  <si>
-    <t>25.02.202663</t>
-  </si>
-  <si>
-    <t>25.02.202664</t>
-  </si>
-  <si>
-    <t>25.02.202665</t>
-  </si>
-  <si>
-    <t>25.02.202666</t>
-  </si>
-  <si>
-    <t>25.02.202667</t>
-  </si>
-  <si>
-    <t>25.02.202668</t>
-  </si>
-  <si>
-    <t>25.02.202669</t>
-  </si>
-  <si>
-    <t>25.02.202670</t>
-  </si>
-  <si>
-    <t>25.02.202671</t>
-  </si>
-  <si>
-    <t>25.02.202672</t>
-  </si>
-  <si>
-    <t>25.02.202673</t>
-  </si>
-  <si>
-    <t>25.02.202674</t>
-  </si>
-  <si>
-    <t>25.02.202675</t>
-  </si>
-  <si>
-    <t>25.02.202676</t>
-  </si>
-  <si>
-    <t>25.02.202677</t>
-  </si>
-  <si>
-    <t>25.02.202678</t>
-  </si>
-  <si>
-    <t>25.02.202679</t>
-  </si>
-  <si>
-    <t>25.02.202680</t>
-  </si>
-  <si>
-    <t>25.02.202681</t>
-  </si>
-  <si>
-    <t>25.02.202682</t>
-  </si>
-  <si>
-    <t>25.02.202683</t>
-  </si>
-  <si>
-    <t>25.02.202684</t>
-  </si>
-  <si>
-    <t>25.02.202685</t>
-  </si>
-  <si>
-    <t>25.02.202686</t>
-  </si>
-  <si>
-    <t>25.02.202687</t>
-  </si>
-  <si>
-    <t>25.02.202688</t>
-  </si>
-  <si>
-    <t>25.02.202689</t>
-  </si>
-  <si>
-    <t>25.02.202690</t>
-  </si>
-  <si>
-    <t>25.02.202691</t>
-  </si>
-  <si>
-    <t>25.02.202692</t>
-  </si>
-  <si>
-    <t>25.02.202693</t>
-  </si>
-  <si>
-    <t>25.02.202694</t>
-  </si>
-  <si>
-    <t>25.02.202695</t>
-  </si>
-  <si>
-    <t>25.02.202696</t>
-  </si>
-  <si>
-    <t>26.02.20261</t>
-  </si>
-  <si>
-    <t>26.02.20262</t>
-  </si>
-  <si>
-    <t>26.02.20263</t>
-  </si>
-  <si>
-    <t>26.02.20264</t>
-  </si>
-  <si>
-    <t>26.02.20265</t>
-  </si>
-  <si>
-    <t>26.02.20266</t>
-  </si>
-  <si>
-    <t>26.02.20267</t>
-  </si>
-  <si>
-    <t>26.02.20268</t>
-  </si>
-  <si>
-    <t>26.02.20269</t>
-  </si>
-  <si>
-    <t>26.02.202610</t>
-  </si>
-  <si>
-    <t>26.02.202611</t>
-  </si>
-  <si>
-    <t>26.02.202612</t>
-  </si>
-  <si>
-    <t>26.02.202613</t>
-  </si>
-  <si>
-    <t>26.02.202614</t>
-  </si>
-  <si>
-    <t>26.02.202615</t>
-  </si>
-  <si>
-    <t>26.02.202616</t>
-  </si>
-  <si>
-    <t>26.02.202617</t>
-  </si>
-  <si>
-    <t>26.02.202618</t>
-  </si>
-  <si>
-    <t>26.02.202619</t>
-  </si>
-  <si>
-    <t>26.02.202620</t>
-  </si>
-  <si>
-    <t>26.02.202621</t>
-  </si>
-  <si>
-    <t>26.02.202622</t>
-  </si>
-  <si>
-    <t>26.02.202623</t>
-  </si>
-  <si>
-    <t>26.02.202624</t>
-  </si>
-  <si>
-    <t>26.02.202625</t>
-  </si>
-  <si>
-    <t>26.02.202626</t>
-  </si>
-  <si>
-    <t>26.02.202627</t>
-  </si>
-  <si>
-    <t>26.02.202628</t>
-  </si>
-  <si>
-    <t>26.02.202629</t>
-  </si>
-  <si>
-    <t>26.02.202630</t>
-  </si>
-  <si>
-    <t>26.02.202631</t>
-  </si>
-  <si>
-    <t>26.02.202632</t>
-  </si>
-  <si>
-    <t>26.02.202633</t>
-  </si>
-  <si>
-    <t>26.02.202634</t>
-  </si>
-  <si>
-    <t>26.02.202635</t>
-  </si>
-  <si>
-    <t>26.02.202636</t>
-  </si>
-  <si>
-    <t>26.02.202637</t>
-  </si>
-  <si>
-    <t>26.02.202638</t>
-  </si>
-  <si>
-    <t>26.02.202639</t>
-  </si>
-  <si>
-    <t>26.02.202640</t>
-  </si>
-  <si>
-    <t>26.02.202641</t>
-  </si>
-  <si>
-    <t>26.02.202642</t>
-  </si>
-  <si>
-    <t>26.02.202643</t>
-  </si>
-  <si>
-    <t>26.02.202644</t>
-  </si>
-  <si>
-    <t>26.02.202645</t>
-  </si>
-  <si>
-    <t>26.02.202646</t>
-  </si>
-  <si>
-    <t>26.02.202647</t>
-  </si>
-  <si>
-    <t>26.02.202648</t>
-  </si>
-  <si>
-    <t>26.02.202649</t>
-  </si>
-  <si>
-    <t>26.02.202650</t>
-  </si>
-  <si>
-    <t>26.02.202651</t>
-  </si>
-  <si>
-    <t>26.02.202652</t>
-  </si>
-  <si>
-    <t>26.02.202653</t>
-  </si>
-  <si>
-    <t>26.02.202654</t>
-  </si>
-  <si>
-    <t>26.02.202655</t>
-  </si>
-  <si>
-    <t>26.02.202656</t>
-  </si>
-  <si>
-    <t>26.02.202657</t>
-  </si>
-  <si>
-    <t>26.02.202658</t>
-  </si>
-  <si>
-    <t>26.02.202659</t>
-  </si>
-  <si>
-    <t>26.02.202660</t>
-  </si>
-  <si>
-    <t>26.02.202661</t>
-  </si>
-  <si>
-    <t>26.02.202662</t>
-  </si>
-  <si>
-    <t>26.02.202663</t>
-  </si>
-  <si>
-    <t>26.02.202664</t>
-  </si>
-  <si>
-    <t>26.02.202665</t>
-  </si>
-  <si>
-    <t>26.02.202666</t>
-  </si>
-  <si>
-    <t>26.02.202667</t>
-  </si>
-  <si>
-    <t>26.02.202668</t>
-  </si>
-  <si>
-    <t>26.02.202669</t>
-  </si>
-  <si>
-    <t>26.02.202670</t>
-  </si>
-  <si>
-    <t>26.02.202671</t>
-  </si>
-  <si>
-    <t>26.02.202672</t>
-  </si>
-  <si>
-    <t>26.02.202673</t>
-  </si>
-  <si>
-    <t>26.02.202674</t>
-  </si>
-  <si>
-    <t>26.02.202675</t>
-  </si>
-  <si>
-    <t>26.02.202676</t>
-  </si>
-  <si>
-    <t>26.02.202677</t>
-  </si>
-  <si>
-    <t>26.02.202678</t>
-  </si>
-  <si>
-    <t>26.02.202679</t>
-  </si>
-  <si>
-    <t>26.02.202680</t>
-  </si>
-  <si>
-    <t>26.02.202681</t>
-  </si>
-  <si>
-    <t>26.02.202682</t>
-  </si>
-  <si>
-    <t>26.02.202683</t>
-  </si>
-  <si>
-    <t>26.02.202684</t>
-  </si>
-  <si>
-    <t>26.02.202685</t>
-  </si>
-  <si>
-    <t>26.02.202686</t>
-  </si>
-  <si>
-    <t>26.02.202687</t>
-  </si>
-  <si>
-    <t>26.02.202688</t>
-  </si>
-  <si>
-    <t>26.02.202689</t>
-  </si>
-  <si>
-    <t>26.02.202690</t>
-  </si>
-  <si>
-    <t>26.02.202691</t>
-  </si>
-  <si>
-    <t>26.02.202692</t>
-  </si>
-  <si>
-    <t>26.02.202693</t>
-  </si>
-  <si>
-    <t>26.02.202694</t>
-  </si>
-  <si>
-    <t>26.02.202695</t>
-  </si>
-  <si>
-    <t>26.02.202696</t>
+    <t>12.03.20261</t>
+  </si>
+  <si>
+    <t>12.03.20262</t>
+  </si>
+  <si>
+    <t>12.03.20263</t>
+  </si>
+  <si>
+    <t>12.03.20264</t>
+  </si>
+  <si>
+    <t>12.03.20265</t>
+  </si>
+  <si>
+    <t>12.03.20266</t>
+  </si>
+  <si>
+    <t>12.03.20267</t>
+  </si>
+  <si>
+    <t>12.03.20268</t>
+  </si>
+  <si>
+    <t>12.03.20269</t>
+  </si>
+  <si>
+    <t>12.03.202610</t>
+  </si>
+  <si>
+    <t>12.03.202611</t>
+  </si>
+  <si>
+    <t>12.03.202612</t>
+  </si>
+  <si>
+    <t>12.03.202613</t>
+  </si>
+  <si>
+    <t>12.03.202614</t>
+  </si>
+  <si>
+    <t>12.03.202615</t>
+  </si>
+  <si>
+    <t>12.03.202616</t>
+  </si>
+  <si>
+    <t>12.03.202617</t>
+  </si>
+  <si>
+    <t>12.03.202618</t>
+  </si>
+  <si>
+    <t>12.03.202619</t>
+  </si>
+  <si>
+    <t>12.03.202620</t>
+  </si>
+  <si>
+    <t>12.03.202621</t>
+  </si>
+  <si>
+    <t>12.03.202622</t>
+  </si>
+  <si>
+    <t>12.03.202623</t>
+  </si>
+  <si>
+    <t>12.03.202624</t>
+  </si>
+  <si>
+    <t>12.03.202625</t>
+  </si>
+  <si>
+    <t>12.03.202626</t>
+  </si>
+  <si>
+    <t>12.03.202627</t>
+  </si>
+  <si>
+    <t>12.03.202628</t>
+  </si>
+  <si>
+    <t>12.03.202629</t>
+  </si>
+  <si>
+    <t>12.03.202630</t>
+  </si>
+  <si>
+    <t>12.03.202631</t>
+  </si>
+  <si>
+    <t>12.03.202632</t>
+  </si>
+  <si>
+    <t>12.03.202633</t>
+  </si>
+  <si>
+    <t>12.03.202634</t>
+  </si>
+  <si>
+    <t>12.03.202635</t>
+  </si>
+  <si>
+    <t>12.03.202636</t>
+  </si>
+  <si>
+    <t>12.03.202637</t>
+  </si>
+  <si>
+    <t>12.03.202638</t>
+  </si>
+  <si>
+    <t>12.03.202639</t>
+  </si>
+  <si>
+    <t>12.03.202640</t>
+  </si>
+  <si>
+    <t>12.03.202641</t>
+  </si>
+  <si>
+    <t>12.03.202642</t>
+  </si>
+  <si>
+    <t>12.03.202643</t>
+  </si>
+  <si>
+    <t>12.03.202644</t>
+  </si>
+  <si>
+    <t>12.03.202645</t>
+  </si>
+  <si>
+    <t>12.03.202646</t>
+  </si>
+  <si>
+    <t>12.03.202647</t>
+  </si>
+  <si>
+    <t>12.03.202648</t>
+  </si>
+  <si>
+    <t>12.03.202649</t>
+  </si>
+  <si>
+    <t>12.03.202650</t>
+  </si>
+  <si>
+    <t>12.03.202651</t>
+  </si>
+  <si>
+    <t>12.03.202652</t>
+  </si>
+  <si>
+    <t>12.03.202653</t>
+  </si>
+  <si>
+    <t>12.03.202654</t>
+  </si>
+  <si>
+    <t>12.03.202655</t>
+  </si>
+  <si>
+    <t>12.03.202656</t>
+  </si>
+  <si>
+    <t>12.03.202657</t>
+  </si>
+  <si>
+    <t>12.03.202658</t>
+  </si>
+  <si>
+    <t>12.03.202659</t>
+  </si>
+  <si>
+    <t>12.03.202660</t>
+  </si>
+  <si>
+    <t>12.03.202661</t>
+  </si>
+  <si>
+    <t>12.03.202662</t>
+  </si>
+  <si>
+    <t>12.03.202663</t>
+  </si>
+  <si>
+    <t>12.03.202664</t>
+  </si>
+  <si>
+    <t>12.03.202665</t>
+  </si>
+  <si>
+    <t>12.03.202666</t>
+  </si>
+  <si>
+    <t>12.03.202667</t>
+  </si>
+  <si>
+    <t>12.03.202668</t>
+  </si>
+  <si>
+    <t>12.03.202669</t>
+  </si>
+  <si>
+    <t>12.03.202670</t>
+  </si>
+  <si>
+    <t>12.03.202671</t>
+  </si>
+  <si>
+    <t>12.03.202672</t>
+  </si>
+  <si>
+    <t>12.03.202673</t>
+  </si>
+  <si>
+    <t>12.03.202674</t>
+  </si>
+  <si>
+    <t>12.03.202675</t>
+  </si>
+  <si>
+    <t>12.03.202676</t>
+  </si>
+  <si>
+    <t>12.03.202677</t>
+  </si>
+  <si>
+    <t>12.03.202678</t>
+  </si>
+  <si>
+    <t>12.03.202679</t>
+  </si>
+  <si>
+    <t>12.03.202680</t>
+  </si>
+  <si>
+    <t>12.03.202681</t>
+  </si>
+  <si>
+    <t>12.03.202682</t>
+  </si>
+  <si>
+    <t>12.03.202683</t>
+  </si>
+  <si>
+    <t>12.03.202684</t>
+  </si>
+  <si>
+    <t>12.03.202685</t>
+  </si>
+  <si>
+    <t>12.03.202686</t>
+  </si>
+  <si>
+    <t>12.03.202687</t>
+  </si>
+  <si>
+    <t>12.03.202688</t>
+  </si>
+  <si>
+    <t>12.03.202689</t>
+  </si>
+  <si>
+    <t>12.03.202690</t>
+  </si>
+  <si>
+    <t>12.03.202691</t>
+  </si>
+  <si>
+    <t>12.03.202692</t>
+  </si>
+  <si>
+    <t>12.03.202693</t>
+  </si>
+  <si>
+    <t>12.03.202694</t>
+  </si>
+  <si>
+    <t>12.03.202695</t>
+  </si>
+  <si>
+    <t>12.03.202696</t>
+  </si>
+  <si>
+    <t>13.03.20261</t>
+  </si>
+  <si>
+    <t>13.03.20262</t>
+  </si>
+  <si>
+    <t>13.03.20263</t>
+  </si>
+  <si>
+    <t>13.03.20264</t>
+  </si>
+  <si>
+    <t>13.03.20265</t>
+  </si>
+  <si>
+    <t>13.03.20266</t>
+  </si>
+  <si>
+    <t>13.03.20267</t>
+  </si>
+  <si>
+    <t>13.03.20268</t>
+  </si>
+  <si>
+    <t>13.03.20269</t>
+  </si>
+  <si>
+    <t>13.03.202610</t>
+  </si>
+  <si>
+    <t>13.03.202611</t>
+  </si>
+  <si>
+    <t>13.03.202612</t>
+  </si>
+  <si>
+    <t>13.03.202613</t>
+  </si>
+  <si>
+    <t>13.03.202614</t>
+  </si>
+  <si>
+    <t>13.03.202615</t>
+  </si>
+  <si>
+    <t>13.03.202616</t>
+  </si>
+  <si>
+    <t>13.03.202617</t>
+  </si>
+  <si>
+    <t>13.03.202618</t>
+  </si>
+  <si>
+    <t>13.03.202619</t>
+  </si>
+  <si>
+    <t>13.03.202620</t>
+  </si>
+  <si>
+    <t>13.03.202621</t>
+  </si>
+  <si>
+    <t>13.03.202622</t>
+  </si>
+  <si>
+    <t>13.03.202623</t>
+  </si>
+  <si>
+    <t>13.03.202624</t>
+  </si>
+  <si>
+    <t>13.03.202625</t>
+  </si>
+  <si>
+    <t>13.03.202626</t>
+  </si>
+  <si>
+    <t>13.03.202627</t>
+  </si>
+  <si>
+    <t>13.03.202628</t>
+  </si>
+  <si>
+    <t>13.03.202629</t>
+  </si>
+  <si>
+    <t>13.03.202630</t>
+  </si>
+  <si>
+    <t>13.03.202631</t>
+  </si>
+  <si>
+    <t>13.03.202632</t>
+  </si>
+  <si>
+    <t>13.03.202633</t>
+  </si>
+  <si>
+    <t>13.03.202634</t>
+  </si>
+  <si>
+    <t>13.03.202635</t>
+  </si>
+  <si>
+    <t>13.03.202636</t>
+  </si>
+  <si>
+    <t>13.03.202637</t>
+  </si>
+  <si>
+    <t>13.03.202638</t>
+  </si>
+  <si>
+    <t>13.03.202639</t>
+  </si>
+  <si>
+    <t>13.03.202640</t>
+  </si>
+  <si>
+    <t>13.03.202641</t>
+  </si>
+  <si>
+    <t>13.03.202642</t>
+  </si>
+  <si>
+    <t>13.03.202643</t>
+  </si>
+  <si>
+    <t>13.03.202644</t>
+  </si>
+  <si>
+    <t>13.03.202645</t>
+  </si>
+  <si>
+    <t>13.03.202646</t>
+  </si>
+  <si>
+    <t>13.03.202647</t>
+  </si>
+  <si>
+    <t>13.03.202648</t>
+  </si>
+  <si>
+    <t>13.03.202649</t>
+  </si>
+  <si>
+    <t>13.03.202650</t>
+  </si>
+  <si>
+    <t>13.03.202651</t>
+  </si>
+  <si>
+    <t>13.03.202652</t>
+  </si>
+  <si>
+    <t>13.03.202653</t>
+  </si>
+  <si>
+    <t>13.03.202654</t>
+  </si>
+  <si>
+    <t>13.03.202655</t>
+  </si>
+  <si>
+    <t>13.03.202656</t>
+  </si>
+  <si>
+    <t>13.03.202657</t>
+  </si>
+  <si>
+    <t>13.03.202658</t>
+  </si>
+  <si>
+    <t>13.03.202659</t>
+  </si>
+  <si>
+    <t>13.03.202660</t>
+  </si>
+  <si>
+    <t>13.03.202661</t>
+  </si>
+  <si>
+    <t>13.03.202662</t>
+  </si>
+  <si>
+    <t>13.03.202663</t>
+  </si>
+  <si>
+    <t>13.03.202664</t>
+  </si>
+  <si>
+    <t>13.03.202665</t>
+  </si>
+  <si>
+    <t>13.03.202666</t>
+  </si>
+  <si>
+    <t>13.03.202667</t>
+  </si>
+  <si>
+    <t>13.03.202668</t>
+  </si>
+  <si>
+    <t>13.03.202669</t>
+  </si>
+  <si>
+    <t>13.03.202670</t>
+  </si>
+  <si>
+    <t>13.03.202671</t>
+  </si>
+  <si>
+    <t>13.03.202672</t>
+  </si>
+  <si>
+    <t>13.03.202673</t>
+  </si>
+  <si>
+    <t>13.03.202674</t>
+  </si>
+  <si>
+    <t>13.03.202675</t>
+  </si>
+  <si>
+    <t>13.03.202676</t>
+  </si>
+  <si>
+    <t>13.03.202677</t>
+  </si>
+  <si>
+    <t>13.03.202678</t>
+  </si>
+  <si>
+    <t>13.03.202679</t>
+  </si>
+  <si>
+    <t>13.03.202680</t>
+  </si>
+  <si>
+    <t>13.03.202681</t>
+  </si>
+  <si>
+    <t>13.03.202682</t>
+  </si>
+  <si>
+    <t>13.03.202683</t>
+  </si>
+  <si>
+    <t>13.03.202684</t>
+  </si>
+  <si>
+    <t>13.03.202685</t>
+  </si>
+  <si>
+    <t>13.03.202686</t>
+  </si>
+  <si>
+    <t>13.03.202687</t>
+  </si>
+  <si>
+    <t>13.03.202688</t>
+  </si>
+  <si>
+    <t>13.03.202689</t>
+  </si>
+  <si>
+    <t>13.03.202690</t>
+  </si>
+  <si>
+    <t>13.03.202691</t>
+  </si>
+  <si>
+    <t>13.03.202692</t>
+  </si>
+  <si>
+    <t>13.03.202693</t>
+  </si>
+  <si>
+    <t>13.03.202694</t>
+  </si>
+  <si>
+    <t>13.03.202695</t>
+  </si>
+  <si>
+    <t>13.03.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="B2">
-        <v>44.907</v>
+        <v>89.187</v>
       </c>
       <c r="C2">
-        <v>-82.792</v>
+        <v>265.679</v>
       </c>
       <c r="D2">
-        <v>-82.792</v>
+        <v>265.679</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46078.01041666666</v>
+        <v>46093.01041666666</v>
       </c>
       <c r="B3">
-        <v>-56.21</v>
+        <v>47.851</v>
       </c>
       <c r="C3">
-        <v>608.658</v>
+        <v>39.532</v>
       </c>
       <c r="D3">
-        <v>608.658</v>
+        <v>39.532</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46078.02083333334</v>
+        <v>46093.02083333334</v>
       </c>
       <c r="B4">
-        <v>11.626</v>
+        <v>31.246</v>
       </c>
       <c r="C4">
-        <v>-64.63800000000001</v>
+        <v>33.99</v>
       </c>
       <c r="D4">
-        <v>-64.63800000000001</v>
+        <v>33.99</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46078.03125</v>
+        <v>46093.03125</v>
       </c>
       <c r="B5">
-        <v>49.604</v>
+        <v>39.489</v>
       </c>
       <c r="C5">
-        <v>-734.601</v>
+        <v>150.521</v>
       </c>
       <c r="D5">
-        <v>-734.601</v>
+        <v>150.521</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46078.04166666666</v>
+        <v>46093.04166666666</v>
       </c>
       <c r="B6">
-        <v>76.321</v>
+        <v>61.114</v>
       </c>
       <c r="C6">
-        <v>-3593.142</v>
+        <v>194.524</v>
       </c>
       <c r="D6">
-        <v>-3593.142</v>
+        <v>194.524</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46078.05208333334</v>
+        <v>46093.05208333334</v>
       </c>
       <c r="B7">
-        <v>75.95999999999999</v>
+        <v>42.234</v>
       </c>
       <c r="C7">
-        <v>-437.837</v>
+        <v>109.643</v>
       </c>
       <c r="D7">
-        <v>-437.837</v>
+        <v>109.643</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46078.0625</v>
+        <v>46093.0625</v>
       </c>
       <c r="B8">
-        <v>60.189</v>
+        <v>14.709</v>
       </c>
       <c r="C8">
-        <v>-88.477</v>
+        <v>224.356</v>
       </c>
       <c r="D8">
-        <v>-88.477</v>
+        <v>224.356</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46078.07291666666</v>
+        <v>46093.07291666666</v>
       </c>
       <c r="B9">
-        <v>71.431</v>
+        <v>-3.634</v>
       </c>
       <c r="C9">
-        <v>-130.33</v>
+        <v>600</v>
       </c>
       <c r="D9">
-        <v>-130.33</v>
+        <v>600</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46078.08333333334</v>
+        <v>46093.08333333334</v>
       </c>
       <c r="B10">
-        <v>71.06</v>
+        <v>0.957</v>
       </c>
       <c r="C10">
-        <v>-102.053</v>
+        <v>173.672</v>
       </c>
       <c r="D10">
-        <v>-102.053</v>
+        <v>173.672</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46078.09375</v>
+        <v>46093.09375</v>
       </c>
       <c r="B11">
-        <v>50.705</v>
+        <v>-13.301</v>
       </c>
       <c r="C11">
-        <v>-94.441</v>
+        <v>783.112</v>
       </c>
       <c r="D11">
-        <v>-94.441</v>
+        <v>783.112</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46078.10416666666</v>
+        <v>46093.10416666666</v>
       </c>
       <c r="B12">
-        <v>29.266</v>
+        <v>-3.16</v>
       </c>
       <c r="C12">
-        <v>-139.764</v>
+        <v>721.524</v>
       </c>
       <c r="D12">
-        <v>-139.764</v>
+        <v>721.524</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46078.11458333334</v>
+        <v>46093.11458333334</v>
       </c>
       <c r="B13">
-        <v>13.293</v>
+        <v>-26.228</v>
       </c>
       <c r="C13">
-        <v>-141</v>
+        <v>912.433</v>
       </c>
       <c r="D13">
-        <v>-141</v>
+        <v>912.433</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46078.125</v>
+        <v>46093.125</v>
       </c>
       <c r="B14">
-        <v>27.286</v>
+        <v>12.603</v>
       </c>
       <c r="C14">
-        <v>-106</v>
+        <v>400</v>
       </c>
       <c r="D14">
-        <v>-106</v>
+        <v>400</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46078.13541666666</v>
+        <v>46093.13541666666</v>
       </c>
       <c r="B15">
-        <v>31.08</v>
+        <v>5.899</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46078.14583333334</v>
+        <v>46093.14583333334</v>
       </c>
       <c r="B16">
-        <v>6.943</v>
+        <v>-15.992</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>946.085</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>946.085</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46078.15625</v>
+        <v>46093.15625</v>
       </c>
       <c r="B17">
-        <v>32.549</v>
+        <v>-23.319</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1128.24</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1128.24</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46078.16666666666</v>
+        <v>46093.16666666666</v>
       </c>
       <c r="B18">
-        <v>42.947</v>
+        <v>-30.246</v>
       </c>
       <c r="C18">
-        <v>-164</v>
+        <v>1174.476</v>
       </c>
       <c r="D18">
-        <v>-164</v>
+        <v>1174.476</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46078.17708333334</v>
+        <v>46093.17708333334</v>
       </c>
       <c r="B19">
-        <v>51.045</v>
+        <v>-33.793</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>843.506</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>843.506</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46078.1875</v>
+        <v>46093.1875</v>
       </c>
       <c r="B20">
-        <v>26.256</v>
+        <v>-28.845</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1130.686</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1130.686</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46078.19791666666</v>
+        <v>46093.19791666666</v>
       </c>
       <c r="B21">
-        <v>54.278</v>
+        <v>-58.786</v>
       </c>
       <c r="C21">
-        <v>-141.903</v>
+        <v>2903.506</v>
       </c>
       <c r="D21">
-        <v>-141.903</v>
+        <v>2903.506</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46078.20833333334</v>
+        <v>46093.20833333334</v>
       </c>
       <c r="B22">
-        <v>54.764</v>
+        <v>-3.493</v>
       </c>
       <c r="C22">
-        <v>-84.021</v>
+        <v>2263.644</v>
       </c>
       <c r="D22">
-        <v>-84.021</v>
+        <v>2263.644</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46078.21875</v>
+        <v>46093.21875</v>
       </c>
       <c r="B23">
-        <v>70.34099999999999</v>
+        <v>-4.642</v>
       </c>
       <c r="C23">
-        <v>-525.34</v>
+        <v>710.152</v>
       </c>
       <c r="D23">
-        <v>-525.34</v>
+        <v>710.152</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46078.22916666666</v>
+        <v>46093.22916666666</v>
       </c>
       <c r="B24">
-        <v>42.223</v>
+        <v>-5.52</v>
       </c>
       <c r="C24">
-        <v>-215.914</v>
+        <v>1012.19</v>
       </c>
       <c r="D24">
-        <v>-215.914</v>
+        <v>1012.19</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46078.23958333334</v>
+        <v>46093.23958333334</v>
       </c>
       <c r="B25">
-        <v>9.244999999999999</v>
+        <v>-18.444</v>
       </c>
       <c r="C25">
-        <v>247.752</v>
+        <v>1025.464</v>
       </c>
       <c r="D25">
-        <v>247.752</v>
+        <v>1025.464</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46078.25</v>
+        <v>46093.25</v>
       </c>
       <c r="B26">
-        <v>26.449</v>
+        <v>23.404</v>
       </c>
       <c r="C26">
-        <v>-197.097</v>
+        <v>253.211</v>
       </c>
       <c r="D26">
-        <v>-197.097</v>
+        <v>253.211</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46078.26041666666</v>
+        <v>46093.26041666666</v>
       </c>
       <c r="B27">
-        <v>25.623</v>
+        <v>11.014</v>
       </c>
       <c r="C27">
-        <v>238.138</v>
+        <v>253.603</v>
       </c>
       <c r="D27">
-        <v>238.138</v>
+        <v>253.603</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46078.27083333334</v>
+        <v>46093.27083333334</v>
       </c>
       <c r="B28">
-        <v>23.898</v>
+        <v>19.97</v>
       </c>
       <c r="C28">
-        <v>229.954</v>
+        <v>253.12</v>
       </c>
       <c r="D28">
-        <v>229.954</v>
+        <v>253.12</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46078.28125</v>
+        <v>46093.28125</v>
       </c>
       <c r="B29">
-        <v>36.455</v>
+        <v>8.662000000000001</v>
       </c>
       <c r="C29">
-        <v>46.177</v>
+        <v>400</v>
       </c>
       <c r="D29">
-        <v>46.177</v>
+        <v>400</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46078.29166666666</v>
+        <v>46093.29166666666</v>
       </c>
       <c r="B30">
-        <v>11.485</v>
+        <v>-22.458</v>
       </c>
       <c r="C30">
-        <v>18.557</v>
+        <v>1186.163</v>
       </c>
       <c r="D30">
-        <v>18.557</v>
+        <v>1186.163</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46078.30208333334</v>
+        <v>46093.30208333334</v>
       </c>
       <c r="B31">
-        <v>16.185</v>
+        <v>-0.718</v>
       </c>
       <c r="C31">
-        <v>-18.536</v>
+        <v>995.759</v>
       </c>
       <c r="D31">
-        <v>-18.536</v>
+        <v>995.759</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46078.3125</v>
+        <v>46093.3125</v>
       </c>
       <c r="B32">
-        <v>45.161</v>
+        <v>-6.198</v>
       </c>
       <c r="C32">
-        <v>-28.013</v>
+        <v>699</v>
       </c>
       <c r="D32">
-        <v>-28.013</v>
+        <v>699</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46078.32291666666</v>
+        <v>46093.32291666666</v>
       </c>
       <c r="B33">
-        <v>83.628</v>
+        <v>-11.082</v>
       </c>
       <c r="C33">
-        <v>-795.723</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>-795.723</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46078.33333333334</v>
+        <v>46093.33333333334</v>
       </c>
       <c r="B34">
-        <v>9.355</v>
+        <v>-57.211</v>
       </c>
       <c r="C34">
-        <v>-513.475</v>
+        <v>861.3390000000001</v>
       </c>
       <c r="D34">
-        <v>-513.475</v>
+        <v>861.3390000000001</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46078.34375</v>
+        <v>46093.34375</v>
       </c>
       <c r="B35">
-        <v>-17.324</v>
+        <v>-97.181</v>
       </c>
       <c r="C35">
-        <v>577.9589999999999</v>
+        <v>862.165</v>
       </c>
       <c r="D35">
-        <v>577.9589999999999</v>
+        <v>862.165</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46078.35416666666</v>
+        <v>46093.35416666666</v>
       </c>
       <c r="B36">
-        <v>35.88</v>
+        <v>-127.855</v>
       </c>
       <c r="C36">
-        <v>-464.591</v>
+        <v>1079.422</v>
       </c>
       <c r="D36">
-        <v>-464.591</v>
+        <v>1079.422</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46078.36458333334</v>
+        <v>46093.36458333334</v>
       </c>
       <c r="B37">
-        <v>44.776</v>
+        <v>-78.06399999999999</v>
       </c>
       <c r="C37">
-        <v>-596.026</v>
+        <v>914.936</v>
       </c>
       <c r="D37">
-        <v>-596.026</v>
+        <v>914.936</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46078.375</v>
+        <v>46093.375</v>
       </c>
       <c r="B38">
-        <v>-14.345</v>
+        <v>-68.723</v>
       </c>
       <c r="C38">
-        <v>827.862</v>
+        <v>743.187</v>
       </c>
       <c r="D38">
-        <v>827.862</v>
+        <v>743.187</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46078.38541666666</v>
+        <v>46093.38541666666</v>
       </c>
       <c r="B39">
-        <v>35.639</v>
+        <v>-52.466</v>
       </c>
       <c r="C39">
-        <v>-108.645</v>
+        <v>745.816</v>
       </c>
       <c r="D39">
-        <v>-108.645</v>
+        <v>745.816</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46078.39583333334</v>
+        <v>46093.39583333334</v>
       </c>
       <c r="B40">
-        <v>69.455</v>
+        <v>-48.477</v>
       </c>
       <c r="C40">
-        <v>-294.159</v>
+        <v>745.85</v>
       </c>
       <c r="D40">
-        <v>-294.159</v>
+        <v>745.85</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46078.40625</v>
+        <v>46093.40625</v>
       </c>
       <c r="B41">
-        <v>87.384</v>
+        <v>-12.508</v>
       </c>
       <c r="C41">
-        <v>-368.703</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>-368.703</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46078.41666666666</v>
+        <v>46093.41666666666</v>
       </c>
       <c r="B42">
-        <v>89.252</v>
+        <v>-26.469</v>
       </c>
       <c r="C42">
-        <v>-279.998</v>
+        <v>583.8920000000001</v>
       </c>
       <c r="D42">
-        <v>-279.998</v>
+        <v>583.8920000000001</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46078.42708333334</v>
+        <v>46093.42708333334</v>
       </c>
       <c r="B43">
-        <v>62.495</v>
+        <v>-1.503</v>
       </c>
       <c r="C43">
-        <v>-200.872</v>
+        <v>574.28</v>
       </c>
       <c r="D43">
-        <v>-200.872</v>
+        <v>574.28</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46078.4375</v>
+        <v>46093.4375</v>
       </c>
       <c r="B44">
-        <v>40.514</v>
+        <v>-20.371</v>
       </c>
       <c r="C44">
-        <v>-162.122</v>
+        <v>162.483</v>
       </c>
       <c r="D44">
-        <v>-162.122</v>
+        <v>162.483</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46078.44791666666</v>
+        <v>46093.44791666666</v>
       </c>
       <c r="B45">
-        <v>-1.759</v>
+        <v>6.363</v>
       </c>
       <c r="C45">
-        <v>486.5</v>
+        <v>-107.128</v>
       </c>
       <c r="D45">
-        <v>486.5</v>
+        <v>-107.128</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46078.45833333334</v>
+        <v>46093.45833333334</v>
       </c>
       <c r="B46">
-        <v>-19.342</v>
+        <v>23.287</v>
       </c>
       <c r="C46">
-        <v>607.3819999999999</v>
+        <v>-648.609</v>
       </c>
       <c r="D46">
-        <v>607.3819999999999</v>
+        <v>-648.609</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46078.46875</v>
+        <v>46093.46875</v>
       </c>
       <c r="B47">
-        <v>-95.97499999999999</v>
+        <v>20.155</v>
       </c>
       <c r="C47">
-        <v>600.466</v>
+        <v>-347.766</v>
       </c>
       <c r="D47">
-        <v>600.466</v>
+        <v>-347.766</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46078.47916666666</v>
+        <v>46093.47916666666</v>
       </c>
       <c r="B48">
-        <v>-73.01000000000001</v>
+        <v>38.513</v>
       </c>
       <c r="C48">
-        <v>672.434</v>
+        <v>-1100.384</v>
       </c>
       <c r="D48">
-        <v>672.434</v>
+        <v>-1100.384</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46078.48958333334</v>
+        <v>46093.48958333334</v>
       </c>
       <c r="B49">
-        <v>-148.957</v>
+        <v>38.106</v>
       </c>
       <c r="C49">
-        <v>1493.944</v>
+        <v>-878.722</v>
       </c>
       <c r="D49">
-        <v>1493.944</v>
+        <v>-878.722</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46078.5</v>
+        <v>46093.5</v>
       </c>
       <c r="B50">
-        <v>-105.966</v>
+        <v>39.109</v>
       </c>
       <c r="C50">
-        <v>849.998</v>
+        <v>-356.826</v>
       </c>
       <c r="D50">
-        <v>849.998</v>
+        <v>-356.826</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46078.51041666666</v>
+        <v>46093.51041666666</v>
       </c>
       <c r="B51">
-        <v>-53.433</v>
+        <v>76.30500000000001</v>
       </c>
       <c r="C51">
-        <v>477.484</v>
+        <v>-1998.29</v>
       </c>
       <c r="D51">
-        <v>477.484</v>
+        <v>-1998.29</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46078.52083333334</v>
+        <v>46093.52083333334</v>
       </c>
       <c r="B52">
-        <v>-77.301</v>
+        <v>94.717</v>
       </c>
       <c r="C52">
-        <v>463.211</v>
+        <v>-4721.954</v>
       </c>
       <c r="D52">
-        <v>463.211</v>
+        <v>-4721.954</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46078.53125</v>
+        <v>46093.53125</v>
       </c>
       <c r="B53">
-        <v>-42.254</v>
+        <v>186.374</v>
       </c>
       <c r="C53">
-        <v>457.846</v>
+        <v>-6557.66</v>
       </c>
       <c r="D53">
-        <v>457.846</v>
+        <v>-6557.66</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46078.54166666666</v>
+        <v>46093.54166666666</v>
       </c>
       <c r="B54">
-        <v>-50.738</v>
+        <v>152.303</v>
       </c>
       <c r="C54">
-        <v>454.607</v>
+        <v>-5392.297</v>
       </c>
       <c r="D54">
-        <v>454.607</v>
+        <v>-5392.297</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46078.55208333334</v>
+        <v>46093.55208333334</v>
       </c>
       <c r="B55">
-        <v>-16.174</v>
+        <v>124.628</v>
       </c>
       <c r="C55">
-        <v>455.4</v>
+        <v>-233.049</v>
       </c>
       <c r="D55">
-        <v>455.4</v>
+        <v>-233.049</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46078.5625</v>
+        <v>46093.5625</v>
       </c>
       <c r="B56">
-        <v>-26.733</v>
+        <v>95.548</v>
       </c>
       <c r="C56">
-        <v>340</v>
+        <v>6.059</v>
       </c>
       <c r="D56">
-        <v>340</v>
+        <v>6.059</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46078.57291666666</v>
+        <v>46093.57291666666</v>
       </c>
       <c r="B57">
-        <v>9.151999999999999</v>
+        <v>91.08799999999999</v>
       </c>
       <c r="C57">
-        <v>-344.221</v>
+        <v>7.038</v>
       </c>
       <c r="D57">
-        <v>-344.221</v>
+        <v>7.038</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46078.58333333334</v>
+        <v>46093.58333333334</v>
       </c>
       <c r="B58">
-        <v>37.819</v>
+        <v>123.455</v>
       </c>
       <c r="C58">
-        <v>-902.862</v>
+        <v>-0.224</v>
       </c>
       <c r="D58">
-        <v>-902.862</v>
+        <v>-0.224</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46078.59375</v>
+        <v>46093.59375</v>
       </c>
       <c r="B59">
-        <v>8.305999999999999</v>
+        <v>118.096</v>
       </c>
       <c r="C59">
-        <v>-14.359</v>
+        <v>-80.203</v>
       </c>
       <c r="D59">
-        <v>-14.359</v>
+        <v>-80.203</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46078.60416666666</v>
+        <v>46093.60416666666</v>
       </c>
       <c r="B60">
-        <v>-24.954</v>
+        <v>115.4</v>
       </c>
       <c r="C60">
-        <v>400</v>
+        <v>-81.411</v>
       </c>
       <c r="D60">
-        <v>400</v>
+        <v>-81.411</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46078.61458333334</v>
+        <v>46093.61458333334</v>
       </c>
       <c r="B61">
-        <v>-27.33</v>
+        <v>86.154</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>-26.838</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>-26.838</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46078.625</v>
+        <v>46093.625</v>
       </c>
       <c r="B62">
-        <v>0.466</v>
+        <v>82.178</v>
       </c>
       <c r="C62">
-        <v>12.337</v>
+        <v>12.215</v>
       </c>
       <c r="D62">
-        <v>12.337</v>
+        <v>12.215</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46078.63541666666</v>
+        <v>46093.63541666666</v>
       </c>
       <c r="B63">
-        <v>-35.642</v>
+        <v>43.55</v>
       </c>
       <c r="C63">
-        <v>598.419</v>
+        <v>0.414</v>
       </c>
       <c r="D63">
-        <v>598.419</v>
+        <v>0.414</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46078.64583333334</v>
+        <v>46093.64583333334</v>
       </c>
       <c r="B64">
-        <v>-25.256</v>
+        <v>19.34</v>
       </c>
       <c r="C64">
-        <v>510.13</v>
+        <v>0.412</v>
       </c>
       <c r="D64">
-        <v>510.13</v>
+        <v>0.412</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46078.65625</v>
+        <v>46093.65625</v>
       </c>
       <c r="B65">
-        <v>-3.503</v>
+        <v>-18.879</v>
       </c>
       <c r="C65">
-        <v>523.4880000000001</v>
+        <v>1343.811</v>
       </c>
       <c r="D65">
-        <v>523.4880000000001</v>
+        <v>1343.811</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46078.66666666666</v>
+        <v>46093.66666666666</v>
       </c>
       <c r="B66">
-        <v>7.751</v>
+        <v>15.55</v>
       </c>
       <c r="C66">
-        <v>-123.976</v>
+        <v>251.549</v>
       </c>
       <c r="D66">
-        <v>-123.976</v>
+        <v>251.549</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46078.67708333334</v>
+        <v>46093.67708333334</v>
       </c>
       <c r="B67">
-        <v>2.486</v>
+        <v>-13.599</v>
       </c>
       <c r="C67">
-        <v>274.516</v>
+        <v>1138.507</v>
       </c>
       <c r="D67">
-        <v>274.516</v>
+        <v>1138.507</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46078.6875</v>
+        <v>46093.6875</v>
       </c>
       <c r="B68">
-        <v>-10.364</v>
+        <v>-27.079</v>
       </c>
       <c r="C68">
-        <v>766.244</v>
+        <v>1205.506</v>
       </c>
       <c r="D68">
-        <v>766.244</v>
+        <v>1205.506</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46078.69791666666</v>
+        <v>46093.69791666666</v>
       </c>
       <c r="B69">
-        <v>-20.072</v>
+        <v>-40.916</v>
       </c>
       <c r="C69">
-        <v>616.146</v>
+        <v>1283.798</v>
       </c>
       <c r="D69">
-        <v>616.146</v>
+        <v>1283.798</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46078.70833333334</v>
+        <v>46093.70833333334</v>
       </c>
       <c r="B70">
-        <v>15.636</v>
+        <v>14.583</v>
       </c>
       <c r="C70">
-        <v>250.577</v>
+        <v>400</v>
       </c>
       <c r="D70">
-        <v>250.577</v>
+        <v>400</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46078.71875</v>
+        <v>46093.71875</v>
       </c>
       <c r="B71">
-        <v>3.097</v>
+        <v>9.625</v>
       </c>
       <c r="C71">
-        <v>374.89</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>374.89</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46078.72916666666</v>
+        <v>46093.72916666666</v>
       </c>
       <c r="B72">
-        <v>-28.207</v>
+        <v>-14.414</v>
       </c>
       <c r="C72">
-        <v>1246.129</v>
+        <v>1239.931</v>
       </c>
       <c r="D72">
-        <v>1246.129</v>
+        <v>1239.931</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46078.73958333334</v>
+        <v>46093.73958333334</v>
       </c>
       <c r="B73">
-        <v>-38.426</v>
+        <v>-35.533</v>
       </c>
       <c r="C73">
-        <v>2385.572</v>
+        <v>2248.593</v>
       </c>
       <c r="D73">
-        <v>2385.572</v>
+        <v>2248.593</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46078.75</v>
+        <v>46093.75</v>
       </c>
       <c r="B74">
-        <v>-74.77800000000001</v>
+        <v>-33.753</v>
       </c>
       <c r="C74">
-        <v>819.872</v>
+        <v>1445.44</v>
       </c>
       <c r="D74">
-        <v>819.872</v>
+        <v>1445.44</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46078.76041666666</v>
+        <v>46093.76041666666</v>
       </c>
       <c r="B75">
-        <v>-61.24</v>
+        <v>-36.634</v>
       </c>
       <c r="C75">
-        <v>790.6420000000001</v>
+        <v>1427.52</v>
       </c>
       <c r="D75">
-        <v>790.6420000000001</v>
+        <v>1427.52</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46078.77083333334</v>
+        <v>46093.77083333334</v>
       </c>
       <c r="B76">
-        <v>-61.638</v>
+        <v>-60.719</v>
       </c>
       <c r="C76">
-        <v>599</v>
+        <v>1518.985</v>
       </c>
       <c r="D76">
-        <v>599</v>
+        <v>1518.985</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46078.78125</v>
+        <v>46093.78125</v>
       </c>
       <c r="B77">
-        <v>-34.009</v>
+        <v>-15.768</v>
       </c>
       <c r="C77">
-        <v>687.147</v>
+        <v>1572.639</v>
       </c>
       <c r="D77">
-        <v>687.147</v>
+        <v>1572.639</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46078.79166666666</v>
+        <v>46093.79166666666</v>
       </c>
       <c r="B78">
-        <v>-31.627</v>
+        <v>38.684</v>
       </c>
       <c r="C78">
-        <v>744.761</v>
+        <v>173.539</v>
       </c>
       <c r="D78">
-        <v>744.761</v>
+        <v>173.539</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46078.80208333334</v>
+        <v>46093.80208333334</v>
       </c>
       <c r="B79">
-        <v>-32.017</v>
+        <v>16.207</v>
       </c>
       <c r="C79">
-        <v>653.404</v>
+        <v>301.144</v>
       </c>
       <c r="D79">
-        <v>653.404</v>
+        <v>301.144</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46078.8125</v>
+        <v>46093.8125</v>
       </c>
       <c r="B80">
-        <v>-4.42</v>
+        <v>2.324</v>
       </c>
       <c r="C80">
-        <v>605.447</v>
+        <v>368.637</v>
       </c>
       <c r="D80">
-        <v>605.447</v>
+        <v>368.637</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46078.82291666666</v>
+        <v>46093.82291666666</v>
       </c>
       <c r="B81">
-        <v>17.94</v>
+        <v>3.319</v>
       </c>
       <c r="C81">
-        <v>272.838</v>
+        <v>290.718</v>
       </c>
       <c r="D81">
-        <v>272.838</v>
+        <v>290.718</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46078.83333333334</v>
+        <v>46093.83333333334</v>
       </c>
       <c r="B82">
-        <v>-10.604</v>
+        <v>-15.001</v>
       </c>
       <c r="C82">
-        <v>767.564</v>
+        <v>803.629</v>
       </c>
       <c r="D82">
-        <v>767.564</v>
+        <v>803.629</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46078.84375</v>
+        <v>46093.84375</v>
       </c>
       <c r="B83">
-        <v>-25.131</v>
+        <v>-6.391</v>
       </c>
       <c r="C83">
-        <v>605.514</v>
+        <v>885.164</v>
       </c>
       <c r="D83">
-        <v>605.514</v>
+        <v>885.164</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46078.85416666666</v>
+        <v>46093.85416666666</v>
       </c>
       <c r="B84">
-        <v>-22.605</v>
+        <v>22.834</v>
       </c>
       <c r="C84">
-        <v>540.826</v>
+        <v>285.625</v>
       </c>
       <c r="D84">
-        <v>540.826</v>
+        <v>285.625</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46078.86458333334</v>
+        <v>46093.86458333334</v>
       </c>
       <c r="B85">
-        <v>-17.318</v>
+        <v>30.297</v>
       </c>
       <c r="C85">
-        <v>700.413</v>
+        <v>279.87</v>
       </c>
       <c r="D85">
-        <v>700.413</v>
+        <v>279.87</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46078.875</v>
+        <v>46093.875</v>
       </c>
       <c r="B86">
-        <v>-89.294</v>
+        <v>-18.197</v>
       </c>
       <c r="C86">
-        <v>866.672</v>
+        <v>1185.43</v>
       </c>
       <c r="D86">
-        <v>866.672</v>
+        <v>1185.43</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46078.88541666666</v>
+        <v>46093.88541666666</v>
       </c>
       <c r="B87">
-        <v>-63.386</v>
+        <v>-19.783</v>
       </c>
       <c r="C87">
-        <v>822.9640000000001</v>
+        <v>1194.464</v>
       </c>
       <c r="D87">
-        <v>822.9640000000001</v>
+        <v>1194.464</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46078.89583333334</v>
+        <v>46093.89583333334</v>
       </c>
       <c r="B88">
-        <v>-73.389</v>
+        <v>-2.837</v>
       </c>
       <c r="C88">
-        <v>599</v>
+        <v>885.105</v>
       </c>
       <c r="D88">
-        <v>599</v>
+        <v>885.105</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46078.90625</v>
+        <v>46093.90625</v>
       </c>
       <c r="B89">
-        <v>-30.43</v>
+        <v>-3.358</v>
       </c>
       <c r="C89">
-        <v>658.294</v>
+        <v>935.157</v>
       </c>
       <c r="D89">
-        <v>658.294</v>
+        <v>935.157</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46078.91666666666</v>
+        <v>46093.91666666666</v>
       </c>
       <c r="B90">
-        <v>-30.073</v>
+        <v>-27.527</v>
       </c>
       <c r="C90">
-        <v>882.535</v>
+        <v>1956.558</v>
       </c>
       <c r="D90">
-        <v>882.535</v>
+        <v>1956.558</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46078.92708333334</v>
+        <v>46093.92708333334</v>
       </c>
       <c r="B91">
-        <v>-16.772</v>
+        <v>-43.543</v>
       </c>
       <c r="C91">
-        <v>828.586</v>
+        <v>2192.735</v>
       </c>
       <c r="D91">
-        <v>828.586</v>
+        <v>2192.735</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46078.9375</v>
+        <v>46093.9375</v>
       </c>
       <c r="B92">
-        <v>9.163</v>
+        <v>-31.822</v>
       </c>
       <c r="C92">
-        <v>313.55</v>
+        <v>1109.858</v>
       </c>
       <c r="D92">
-        <v>313.55</v>
+        <v>1109.858</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46078.94791666666</v>
+        <v>46093.94791666666</v>
       </c>
       <c r="B93">
-        <v>16.136</v>
+        <v>-20.794</v>
       </c>
       <c r="C93">
-        <v>-70.87</v>
+        <v>1075.679</v>
       </c>
       <c r="D93">
-        <v>-70.87</v>
+        <v>1075.679</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46078.95833333334</v>
+        <v>46093.95833333334</v>
       </c>
       <c r="B94">
-        <v>6.174</v>
+        <v>-22.748</v>
       </c>
       <c r="C94">
-        <v>-34.608</v>
+        <v>1063.846</v>
       </c>
       <c r="D94">
-        <v>-34.608</v>
+        <v>1063.846</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46078.96875</v>
+        <v>46093.96875</v>
       </c>
       <c r="B95">
-        <v>-8.676</v>
+        <v>-24.905</v>
       </c>
       <c r="C95">
-        <v>203.789</v>
+        <v>1059.072</v>
       </c>
       <c r="D95">
-        <v>203.789</v>
+        <v>1059.072</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46078.97916666666</v>
+        <v>46093.97916666666</v>
       </c>
       <c r="B96">
-        <v>-37.901</v>
+        <v>-5.124</v>
       </c>
       <c r="C96">
-        <v>604.1609999999999</v>
+        <v>1074.63</v>
       </c>
       <c r="D96">
-        <v>604.1609999999999</v>
+        <v>1074.63</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46078.98958333334</v>
+        <v>46093.98958333334</v>
       </c>
       <c r="B97">
-        <v>-72.349</v>
+        <v>-5.282</v>
       </c>
       <c r="C97">
-        <v>678.611</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>678.611</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46079</v>
+        <v>46094</v>
       </c>
       <c r="B98">
-        <v>-22.741</v>
+        <v>-28.691</v>
       </c>
       <c r="C98">
-        <v>774.313</v>
+        <v>1178.345</v>
       </c>
       <c r="D98">
-        <v>774.313</v>
+        <v>1178.345</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B99">
-        <v>4.682</v>
+        <v>-30.587</v>
       </c>
       <c r="C99">
-        <v>83.178</v>
+        <v>1165.698</v>
       </c>
       <c r="D99">
-        <v>83.178</v>
+        <v>1165.698</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B100">
-        <v>-8.122999999999999</v>
+        <v>-19.411</v>
       </c>
       <c r="C100">
-        <v>599</v>
+        <v>979.946</v>
       </c>
       <c r="D100">
-        <v>599</v>
+        <v>979.946</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B101">
-        <v>-0.13</v>
+        <v>-12.578</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>775.513</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>775.513</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B102">
-        <v>-30.702</v>
+        <v>-10.373</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>929.798</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>929.798</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B103">
-        <v>-50.134</v>
+        <v>-11.451</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>775.728</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>775.728</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B104">
-        <v>-59.247</v>
+        <v>4.909</v>
       </c>
       <c r="C104">
-        <v>617.847</v>
+        <v>257.522</v>
       </c>
       <c r="D104">
-        <v>617.847</v>
+        <v>257.522</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B105">
-        <v>-55.759</v>
+        <v>23.089</v>
       </c>
       <c r="C105">
-        <v>838.4829999999999</v>
+        <v>114.976</v>
       </c>
       <c r="D105">
-        <v>838.4829999999999</v>
+        <v>114.976</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B106">
-        <v>-35.997</v>
+        <v>2.712</v>
       </c>
       <c r="C106">
-        <v>818.754</v>
+        <v>197.394</v>
       </c>
       <c r="D106">
-        <v>818.754</v>
+        <v>197.394</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B107">
-        <v>-50.597</v>
+        <v>13.565</v>
       </c>
       <c r="C107">
-        <v>818.8579999999999</v>
+        <v>268.342</v>
       </c>
       <c r="D107">
-        <v>818.8579999999999</v>
+        <v>268.342</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B108">
-        <v>-26.238</v>
+        <v>25.181</v>
       </c>
       <c r="C108">
-        <v>820.66</v>
+        <v>178.188</v>
       </c>
       <c r="D108">
-        <v>820.66</v>
+        <v>178.188</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B109">
-        <v>-46.693</v>
+        <v>18.132</v>
       </c>
       <c r="C109">
-        <v>819.76</v>
+        <v>88.285</v>
       </c>
       <c r="D109">
-        <v>819.76</v>
+        <v>88.285</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B110">
-        <v>-49.66</v>
+        <v>1.439</v>
       </c>
       <c r="C110">
-        <v>806.308</v>
+        <v>239.033</v>
       </c>
       <c r="D110">
-        <v>806.308</v>
+        <v>239.033</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B111">
-        <v>-57.377</v>
+        <v>14.472</v>
       </c>
       <c r="C111">
-        <v>809.302</v>
+        <v>249.672</v>
       </c>
       <c r="D111">
-        <v>809.302</v>
+        <v>249.672</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B112">
-        <v>-28.154</v>
+        <v>4.029</v>
       </c>
       <c r="C112">
-        <v>819.8200000000001</v>
+        <v>251.537</v>
       </c>
       <c r="D112">
-        <v>819.8200000000001</v>
+        <v>251.537</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B113">
-        <v>-7.904</v>
+        <v>12.18</v>
       </c>
       <c r="C113">
-        <v>820.11</v>
+        <v>241.523</v>
       </c>
       <c r="D113">
-        <v>820.11</v>
+        <v>241.523</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B114">
-        <v>-7.41</v>
+        <v>-8.609</v>
       </c>
       <c r="C114">
-        <v>817.7</v>
+        <v>254.249</v>
       </c>
       <c r="D114">
-        <v>817.7</v>
+        <v>254.249</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B115">
-        <v>-1.841</v>
+        <v>-24.721</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B116">
-        <v>-31.921</v>
+        <v>-25.206</v>
       </c>
       <c r="C116">
-        <v>628.0549999999999</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>628.0549999999999</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B117">
-        <v>-45.247</v>
+        <v>-51.309</v>
       </c>
       <c r="C117">
-        <v>940.821</v>
+        <v>719.9880000000001</v>
       </c>
       <c r="D117">
-        <v>940.821</v>
+        <v>719.9880000000001</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B118">
-        <v>-47.843</v>
+        <v>-8.218</v>
       </c>
       <c r="C118">
-        <v>651.956</v>
+        <v>765.553</v>
       </c>
       <c r="D118">
-        <v>651.956</v>
+        <v>765.553</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B119">
-        <v>-45.716</v>
+        <v>-32.516</v>
       </c>
       <c r="C119">
-        <v>599</v>
+        <v>700</v>
       </c>
       <c r="D119">
-        <v>599</v>
+        <v>700</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B120">
-        <v>-34.315</v>
+        <v>-8.347</v>
       </c>
       <c r="C120">
-        <v>810.152</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>810.152</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B121">
-        <v>-49.454</v>
+        <v>2.597</v>
       </c>
       <c r="C121">
-        <v>799.134</v>
+        <v>255.242</v>
       </c>
       <c r="D121">
-        <v>799.134</v>
+        <v>255.242</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B122">
-        <v>-6.591</v>
+        <v>39.945</v>
       </c>
       <c r="C122">
-        <v>862.88</v>
+        <v>-41.665</v>
       </c>
       <c r="D122">
-        <v>862.88</v>
+        <v>-41.665</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B123">
-        <v>-70.498</v>
+        <v>66.551</v>
       </c>
       <c r="C123">
-        <v>839.724</v>
+        <v>-191.064</v>
       </c>
       <c r="D123">
-        <v>839.724</v>
+        <v>-191.064</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B124">
-        <v>-95.556</v>
+        <v>64.331</v>
       </c>
       <c r="C124">
-        <v>653.474</v>
+        <v>-735.635</v>
       </c>
       <c r="D124">
-        <v>653.474</v>
+        <v>-735.635</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B125">
-        <v>-87.643</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="C125">
-        <v>603.234</v>
+        <v>-3400.417</v>
       </c>
       <c r="D125">
-        <v>603.234</v>
+        <v>-3400.417</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B126">
-        <v>-94.55200000000001</v>
+        <v>112.479</v>
       </c>
       <c r="C126">
-        <v>738.038</v>
+        <v>-495.009</v>
       </c>
       <c r="D126">
-        <v>738.038</v>
+        <v>-495.009</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B127">
-        <v>-18.38</v>
+        <v>89.85599999999999</v>
       </c>
       <c r="C127">
-        <v>764.827</v>
+        <v>-103.048</v>
       </c>
       <c r="D127">
-        <v>764.827</v>
+        <v>-103.048</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B128">
-        <v>27.838</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>-987.316</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>-987.316</v>
+        <v>0</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B129">
-        <v>50.508</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>-1053.942</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>-1053.942</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B130">
-        <v>58.238</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>-438.325</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>-438.325</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B131">
-        <v>82.988</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>-1183.734</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>-1183.734</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B132">
-        <v>100.276</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>-1910.267</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>-1910.267</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B133">
-        <v>130.633</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>-2673.297</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>-2673.297</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B134">
-        <v>71.419</v>
+        <v>0</v>
       </c>
       <c r="C134">
-        <v>-381.04</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>-381.04</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B135">
-        <v>47.361</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>-164.758</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>-164.758</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B136">
-        <v>83.899</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>-167.497</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>-167.497</v>
+        <v>0</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>12.03.20261</t>
-  </si>
-  <si>
-    <t>12.03.20262</t>
-  </si>
-  <si>
-    <t>12.03.20263</t>
-  </si>
-  <si>
-    <t>12.03.20264</t>
-  </si>
-  <si>
-    <t>12.03.20265</t>
-  </si>
-  <si>
-    <t>12.03.20266</t>
-  </si>
-  <si>
-    <t>12.03.20267</t>
-  </si>
-  <si>
-    <t>12.03.20268</t>
-  </si>
-  <si>
-    <t>12.03.20269</t>
-  </si>
-  <si>
-    <t>12.03.202610</t>
-  </si>
-  <si>
-    <t>12.03.202611</t>
-  </si>
-  <si>
-    <t>12.03.202612</t>
-  </si>
-  <si>
-    <t>12.03.202613</t>
-  </si>
-  <si>
-    <t>12.03.202614</t>
-  </si>
-  <si>
-    <t>12.03.202615</t>
-  </si>
-  <si>
-    <t>12.03.202616</t>
-  </si>
-  <si>
-    <t>12.03.202617</t>
-  </si>
-  <si>
-    <t>12.03.202618</t>
-  </si>
-  <si>
-    <t>12.03.202619</t>
-  </si>
-  <si>
-    <t>12.03.202620</t>
-  </si>
-  <si>
-    <t>12.03.202621</t>
-  </si>
-  <si>
-    <t>12.03.202622</t>
-  </si>
-  <si>
-    <t>12.03.202623</t>
-  </si>
-  <si>
-    <t>12.03.202624</t>
-  </si>
-  <si>
-    <t>12.03.202625</t>
-  </si>
-  <si>
-    <t>12.03.202626</t>
-  </si>
-  <si>
-    <t>12.03.202627</t>
-  </si>
-  <si>
-    <t>12.03.202628</t>
-  </si>
-  <si>
-    <t>12.03.202629</t>
-  </si>
-  <si>
-    <t>12.03.202630</t>
-  </si>
-  <si>
-    <t>12.03.202631</t>
-  </si>
-  <si>
-    <t>12.03.202632</t>
-  </si>
-  <si>
-    <t>12.03.202633</t>
-  </si>
-  <si>
-    <t>12.03.202634</t>
-  </si>
-  <si>
-    <t>12.03.202635</t>
-  </si>
-  <si>
-    <t>12.03.202636</t>
-  </si>
-  <si>
-    <t>12.03.202637</t>
-  </si>
-  <si>
-    <t>12.03.202638</t>
-  </si>
-  <si>
-    <t>12.03.202639</t>
-  </si>
-  <si>
-    <t>12.03.202640</t>
-  </si>
-  <si>
-    <t>12.03.202641</t>
-  </si>
-  <si>
-    <t>12.03.202642</t>
-  </si>
-  <si>
-    <t>12.03.202643</t>
-  </si>
-  <si>
-    <t>12.03.202644</t>
-  </si>
-  <si>
-    <t>12.03.202645</t>
-  </si>
-  <si>
-    <t>12.03.202646</t>
-  </si>
-  <si>
-    <t>12.03.202647</t>
-  </si>
-  <si>
-    <t>12.03.202648</t>
-  </si>
-  <si>
-    <t>12.03.202649</t>
-  </si>
-  <si>
-    <t>12.03.202650</t>
-  </si>
-  <si>
-    <t>12.03.202651</t>
-  </si>
-  <si>
-    <t>12.03.202652</t>
-  </si>
-  <si>
-    <t>12.03.202653</t>
-  </si>
-  <si>
-    <t>12.03.202654</t>
-  </si>
-  <si>
-    <t>12.03.202655</t>
-  </si>
-  <si>
-    <t>12.03.202656</t>
-  </si>
-  <si>
-    <t>12.03.202657</t>
-  </si>
-  <si>
-    <t>12.03.202658</t>
-  </si>
-  <si>
-    <t>12.03.202659</t>
-  </si>
-  <si>
-    <t>12.03.202660</t>
-  </si>
-  <si>
-    <t>12.03.202661</t>
-  </si>
-  <si>
-    <t>12.03.202662</t>
-  </si>
-  <si>
-    <t>12.03.202663</t>
-  </si>
-  <si>
-    <t>12.03.202664</t>
-  </si>
-  <si>
-    <t>12.03.202665</t>
-  </si>
-  <si>
-    <t>12.03.202666</t>
-  </si>
-  <si>
-    <t>12.03.202667</t>
-  </si>
-  <si>
-    <t>12.03.202668</t>
-  </si>
-  <si>
-    <t>12.03.202669</t>
-  </si>
-  <si>
-    <t>12.03.202670</t>
-  </si>
-  <si>
-    <t>12.03.202671</t>
-  </si>
-  <si>
-    <t>12.03.202672</t>
-  </si>
-  <si>
-    <t>12.03.202673</t>
-  </si>
-  <si>
-    <t>12.03.202674</t>
-  </si>
-  <si>
-    <t>12.03.202675</t>
-  </si>
-  <si>
-    <t>12.03.202676</t>
-  </si>
-  <si>
-    <t>12.03.202677</t>
-  </si>
-  <si>
-    <t>12.03.202678</t>
-  </si>
-  <si>
-    <t>12.03.202679</t>
-  </si>
-  <si>
-    <t>12.03.202680</t>
-  </si>
-  <si>
-    <t>12.03.202681</t>
-  </si>
-  <si>
-    <t>12.03.202682</t>
-  </si>
-  <si>
-    <t>12.03.202683</t>
-  </si>
-  <si>
-    <t>12.03.202684</t>
-  </si>
-  <si>
-    <t>12.03.202685</t>
-  </si>
-  <si>
-    <t>12.03.202686</t>
-  </si>
-  <si>
-    <t>12.03.202687</t>
-  </si>
-  <si>
-    <t>12.03.202688</t>
-  </si>
-  <si>
-    <t>12.03.202689</t>
-  </si>
-  <si>
-    <t>12.03.202690</t>
-  </si>
-  <si>
-    <t>12.03.202691</t>
-  </si>
-  <si>
-    <t>12.03.202692</t>
-  </si>
-  <si>
-    <t>12.03.202693</t>
-  </si>
-  <si>
-    <t>12.03.202694</t>
-  </si>
-  <si>
-    <t>12.03.202695</t>
-  </si>
-  <si>
-    <t>12.03.202696</t>
-  </si>
-  <si>
-    <t>13.03.20261</t>
-  </si>
-  <si>
-    <t>13.03.20262</t>
-  </si>
-  <si>
-    <t>13.03.20263</t>
-  </si>
-  <si>
-    <t>13.03.20264</t>
-  </si>
-  <si>
-    <t>13.03.20265</t>
-  </si>
-  <si>
-    <t>13.03.20266</t>
-  </si>
-  <si>
-    <t>13.03.20267</t>
-  </si>
-  <si>
-    <t>13.03.20268</t>
-  </si>
-  <si>
-    <t>13.03.20269</t>
-  </si>
-  <si>
-    <t>13.03.202610</t>
-  </si>
-  <si>
-    <t>13.03.202611</t>
-  </si>
-  <si>
-    <t>13.03.202612</t>
-  </si>
-  <si>
-    <t>13.03.202613</t>
-  </si>
-  <si>
-    <t>13.03.202614</t>
-  </si>
-  <si>
-    <t>13.03.202615</t>
-  </si>
-  <si>
-    <t>13.03.202616</t>
-  </si>
-  <si>
-    <t>13.03.202617</t>
-  </si>
-  <si>
-    <t>13.03.202618</t>
-  </si>
-  <si>
-    <t>13.03.202619</t>
-  </si>
-  <si>
-    <t>13.03.202620</t>
-  </si>
-  <si>
-    <t>13.03.202621</t>
-  </si>
-  <si>
-    <t>13.03.202622</t>
-  </si>
-  <si>
-    <t>13.03.202623</t>
-  </si>
-  <si>
-    <t>13.03.202624</t>
-  </si>
-  <si>
-    <t>13.03.202625</t>
-  </si>
-  <si>
-    <t>13.03.202626</t>
-  </si>
-  <si>
-    <t>13.03.202627</t>
-  </si>
-  <si>
-    <t>13.03.202628</t>
-  </si>
-  <si>
-    <t>13.03.202629</t>
-  </si>
-  <si>
-    <t>13.03.202630</t>
-  </si>
-  <si>
-    <t>13.03.202631</t>
-  </si>
-  <si>
-    <t>13.03.202632</t>
-  </si>
-  <si>
-    <t>13.03.202633</t>
-  </si>
-  <si>
-    <t>13.03.202634</t>
-  </si>
-  <si>
-    <t>13.03.202635</t>
-  </si>
-  <si>
-    <t>13.03.202636</t>
-  </si>
-  <si>
-    <t>13.03.202637</t>
-  </si>
-  <si>
-    <t>13.03.202638</t>
-  </si>
-  <si>
-    <t>13.03.202639</t>
-  </si>
-  <si>
-    <t>13.03.202640</t>
-  </si>
-  <si>
-    <t>13.03.202641</t>
-  </si>
-  <si>
-    <t>13.03.202642</t>
-  </si>
-  <si>
-    <t>13.03.202643</t>
-  </si>
-  <si>
-    <t>13.03.202644</t>
-  </si>
-  <si>
-    <t>13.03.202645</t>
-  </si>
-  <si>
-    <t>13.03.202646</t>
-  </si>
-  <si>
-    <t>13.03.202647</t>
-  </si>
-  <si>
-    <t>13.03.202648</t>
-  </si>
-  <si>
-    <t>13.03.202649</t>
-  </si>
-  <si>
-    <t>13.03.202650</t>
-  </si>
-  <si>
-    <t>13.03.202651</t>
-  </si>
-  <si>
-    <t>13.03.202652</t>
-  </si>
-  <si>
-    <t>13.03.202653</t>
-  </si>
-  <si>
-    <t>13.03.202654</t>
-  </si>
-  <si>
-    <t>13.03.202655</t>
-  </si>
-  <si>
-    <t>13.03.202656</t>
-  </si>
-  <si>
-    <t>13.03.202657</t>
-  </si>
-  <si>
-    <t>13.03.202658</t>
-  </si>
-  <si>
-    <t>13.03.202659</t>
-  </si>
-  <si>
-    <t>13.03.202660</t>
-  </si>
-  <si>
-    <t>13.03.202661</t>
-  </si>
-  <si>
-    <t>13.03.202662</t>
-  </si>
-  <si>
-    <t>13.03.202663</t>
-  </si>
-  <si>
-    <t>13.03.202664</t>
-  </si>
-  <si>
-    <t>13.03.202665</t>
-  </si>
-  <si>
-    <t>13.03.202666</t>
-  </si>
-  <si>
-    <t>13.03.202667</t>
-  </si>
-  <si>
-    <t>13.03.202668</t>
-  </si>
-  <si>
-    <t>13.03.202669</t>
-  </si>
-  <si>
-    <t>13.03.202670</t>
-  </si>
-  <si>
-    <t>13.03.202671</t>
-  </si>
-  <si>
-    <t>13.03.202672</t>
-  </si>
-  <si>
-    <t>13.03.202673</t>
-  </si>
-  <si>
-    <t>13.03.202674</t>
-  </si>
-  <si>
-    <t>13.03.202675</t>
-  </si>
-  <si>
-    <t>13.03.202676</t>
-  </si>
-  <si>
-    <t>13.03.202677</t>
-  </si>
-  <si>
-    <t>13.03.202678</t>
-  </si>
-  <si>
-    <t>13.03.202679</t>
-  </si>
-  <si>
-    <t>13.03.202680</t>
-  </si>
-  <si>
-    <t>13.03.202681</t>
-  </si>
-  <si>
-    <t>13.03.202682</t>
-  </si>
-  <si>
-    <t>13.03.202683</t>
-  </si>
-  <si>
-    <t>13.03.202684</t>
-  </si>
-  <si>
-    <t>13.03.202685</t>
-  </si>
-  <si>
-    <t>13.03.202686</t>
-  </si>
-  <si>
-    <t>13.03.202687</t>
-  </si>
-  <si>
-    <t>13.03.202688</t>
-  </si>
-  <si>
-    <t>13.03.202689</t>
-  </si>
-  <si>
-    <t>13.03.202690</t>
-  </si>
-  <si>
-    <t>13.03.202691</t>
-  </si>
-  <si>
-    <t>13.03.202692</t>
-  </si>
-  <si>
-    <t>13.03.202693</t>
-  </si>
-  <si>
-    <t>13.03.202694</t>
-  </si>
-  <si>
-    <t>13.03.202695</t>
-  </si>
-  <si>
-    <t>13.03.202696</t>
+    <t>25.03.20261</t>
+  </si>
+  <si>
+    <t>25.03.20262</t>
+  </si>
+  <si>
+    <t>25.03.20263</t>
+  </si>
+  <si>
+    <t>25.03.20264</t>
+  </si>
+  <si>
+    <t>25.03.20265</t>
+  </si>
+  <si>
+    <t>25.03.20266</t>
+  </si>
+  <si>
+    <t>25.03.20267</t>
+  </si>
+  <si>
+    <t>25.03.20268</t>
+  </si>
+  <si>
+    <t>25.03.20269</t>
+  </si>
+  <si>
+    <t>25.03.202610</t>
+  </si>
+  <si>
+    <t>25.03.202611</t>
+  </si>
+  <si>
+    <t>25.03.202612</t>
+  </si>
+  <si>
+    <t>25.03.202613</t>
+  </si>
+  <si>
+    <t>25.03.202614</t>
+  </si>
+  <si>
+    <t>25.03.202615</t>
+  </si>
+  <si>
+    <t>25.03.202616</t>
+  </si>
+  <si>
+    <t>25.03.202617</t>
+  </si>
+  <si>
+    <t>25.03.202618</t>
+  </si>
+  <si>
+    <t>25.03.202619</t>
+  </si>
+  <si>
+    <t>25.03.202620</t>
+  </si>
+  <si>
+    <t>25.03.202621</t>
+  </si>
+  <si>
+    <t>25.03.202622</t>
+  </si>
+  <si>
+    <t>25.03.202623</t>
+  </si>
+  <si>
+    <t>25.03.202624</t>
+  </si>
+  <si>
+    <t>25.03.202625</t>
+  </si>
+  <si>
+    <t>25.03.202626</t>
+  </si>
+  <si>
+    <t>25.03.202627</t>
+  </si>
+  <si>
+    <t>25.03.202628</t>
+  </si>
+  <si>
+    <t>25.03.202629</t>
+  </si>
+  <si>
+    <t>25.03.202630</t>
+  </si>
+  <si>
+    <t>25.03.202631</t>
+  </si>
+  <si>
+    <t>25.03.202632</t>
+  </si>
+  <si>
+    <t>25.03.202633</t>
+  </si>
+  <si>
+    <t>25.03.202634</t>
+  </si>
+  <si>
+    <t>25.03.202635</t>
+  </si>
+  <si>
+    <t>25.03.202636</t>
+  </si>
+  <si>
+    <t>25.03.202637</t>
+  </si>
+  <si>
+    <t>25.03.202638</t>
+  </si>
+  <si>
+    <t>25.03.202639</t>
+  </si>
+  <si>
+    <t>25.03.202640</t>
+  </si>
+  <si>
+    <t>25.03.202641</t>
+  </si>
+  <si>
+    <t>25.03.202642</t>
+  </si>
+  <si>
+    <t>25.03.202643</t>
+  </si>
+  <si>
+    <t>25.03.202644</t>
+  </si>
+  <si>
+    <t>25.03.202645</t>
+  </si>
+  <si>
+    <t>25.03.202646</t>
+  </si>
+  <si>
+    <t>25.03.202647</t>
+  </si>
+  <si>
+    <t>25.03.202648</t>
+  </si>
+  <si>
+    <t>25.03.202649</t>
+  </si>
+  <si>
+    <t>25.03.202650</t>
+  </si>
+  <si>
+    <t>25.03.202651</t>
+  </si>
+  <si>
+    <t>25.03.202652</t>
+  </si>
+  <si>
+    <t>25.03.202653</t>
+  </si>
+  <si>
+    <t>25.03.202654</t>
+  </si>
+  <si>
+    <t>25.03.202655</t>
+  </si>
+  <si>
+    <t>25.03.202656</t>
+  </si>
+  <si>
+    <t>25.03.202657</t>
+  </si>
+  <si>
+    <t>25.03.202658</t>
+  </si>
+  <si>
+    <t>25.03.202659</t>
+  </si>
+  <si>
+    <t>25.03.202660</t>
+  </si>
+  <si>
+    <t>25.03.202661</t>
+  </si>
+  <si>
+    <t>25.03.202662</t>
+  </si>
+  <si>
+    <t>25.03.202663</t>
+  </si>
+  <si>
+    <t>25.03.202664</t>
+  </si>
+  <si>
+    <t>25.03.202665</t>
+  </si>
+  <si>
+    <t>25.03.202666</t>
+  </si>
+  <si>
+    <t>25.03.202667</t>
+  </si>
+  <si>
+    <t>25.03.202668</t>
+  </si>
+  <si>
+    <t>25.03.202669</t>
+  </si>
+  <si>
+    <t>25.03.202670</t>
+  </si>
+  <si>
+    <t>25.03.202671</t>
+  </si>
+  <si>
+    <t>25.03.202672</t>
+  </si>
+  <si>
+    <t>25.03.202673</t>
+  </si>
+  <si>
+    <t>25.03.202674</t>
+  </si>
+  <si>
+    <t>25.03.202675</t>
+  </si>
+  <si>
+    <t>25.03.202676</t>
+  </si>
+  <si>
+    <t>25.03.202677</t>
+  </si>
+  <si>
+    <t>25.03.202678</t>
+  </si>
+  <si>
+    <t>25.03.202679</t>
+  </si>
+  <si>
+    <t>25.03.202680</t>
+  </si>
+  <si>
+    <t>25.03.202681</t>
+  </si>
+  <si>
+    <t>25.03.202682</t>
+  </si>
+  <si>
+    <t>25.03.202683</t>
+  </si>
+  <si>
+    <t>25.03.202684</t>
+  </si>
+  <si>
+    <t>25.03.202685</t>
+  </si>
+  <si>
+    <t>25.03.202686</t>
+  </si>
+  <si>
+    <t>25.03.202687</t>
+  </si>
+  <si>
+    <t>25.03.202688</t>
+  </si>
+  <si>
+    <t>25.03.202689</t>
+  </si>
+  <si>
+    <t>25.03.202690</t>
+  </si>
+  <si>
+    <t>25.03.202691</t>
+  </si>
+  <si>
+    <t>25.03.202692</t>
+  </si>
+  <si>
+    <t>25.03.202693</t>
+  </si>
+  <si>
+    <t>25.03.202694</t>
+  </si>
+  <si>
+    <t>25.03.202695</t>
+  </si>
+  <si>
+    <t>25.03.202696</t>
+  </si>
+  <si>
+    <t>26.03.20261</t>
+  </si>
+  <si>
+    <t>26.03.20262</t>
+  </si>
+  <si>
+    <t>26.03.20263</t>
+  </si>
+  <si>
+    <t>26.03.20264</t>
+  </si>
+  <si>
+    <t>26.03.20265</t>
+  </si>
+  <si>
+    <t>26.03.20266</t>
+  </si>
+  <si>
+    <t>26.03.20267</t>
+  </si>
+  <si>
+    <t>26.03.20268</t>
+  </si>
+  <si>
+    <t>26.03.20269</t>
+  </si>
+  <si>
+    <t>26.03.202610</t>
+  </si>
+  <si>
+    <t>26.03.202611</t>
+  </si>
+  <si>
+    <t>26.03.202612</t>
+  </si>
+  <si>
+    <t>26.03.202613</t>
+  </si>
+  <si>
+    <t>26.03.202614</t>
+  </si>
+  <si>
+    <t>26.03.202615</t>
+  </si>
+  <si>
+    <t>26.03.202616</t>
+  </si>
+  <si>
+    <t>26.03.202617</t>
+  </si>
+  <si>
+    <t>26.03.202618</t>
+  </si>
+  <si>
+    <t>26.03.202619</t>
+  </si>
+  <si>
+    <t>26.03.202620</t>
+  </si>
+  <si>
+    <t>26.03.202621</t>
+  </si>
+  <si>
+    <t>26.03.202622</t>
+  </si>
+  <si>
+    <t>26.03.202623</t>
+  </si>
+  <si>
+    <t>26.03.202624</t>
+  </si>
+  <si>
+    <t>26.03.202625</t>
+  </si>
+  <si>
+    <t>26.03.202626</t>
+  </si>
+  <si>
+    <t>26.03.202627</t>
+  </si>
+  <si>
+    <t>26.03.202628</t>
+  </si>
+  <si>
+    <t>26.03.202629</t>
+  </si>
+  <si>
+    <t>26.03.202630</t>
+  </si>
+  <si>
+    <t>26.03.202631</t>
+  </si>
+  <si>
+    <t>26.03.202632</t>
+  </si>
+  <si>
+    <t>26.03.202633</t>
+  </si>
+  <si>
+    <t>26.03.202634</t>
+  </si>
+  <si>
+    <t>26.03.202635</t>
+  </si>
+  <si>
+    <t>26.03.202636</t>
+  </si>
+  <si>
+    <t>26.03.202637</t>
+  </si>
+  <si>
+    <t>26.03.202638</t>
+  </si>
+  <si>
+    <t>26.03.202639</t>
+  </si>
+  <si>
+    <t>26.03.202640</t>
+  </si>
+  <si>
+    <t>26.03.202641</t>
+  </si>
+  <si>
+    <t>26.03.202642</t>
+  </si>
+  <si>
+    <t>26.03.202643</t>
+  </si>
+  <si>
+    <t>26.03.202644</t>
+  </si>
+  <si>
+    <t>26.03.202645</t>
+  </si>
+  <si>
+    <t>26.03.202646</t>
+  </si>
+  <si>
+    <t>26.03.202647</t>
+  </si>
+  <si>
+    <t>26.03.202648</t>
+  </si>
+  <si>
+    <t>26.03.202649</t>
+  </si>
+  <si>
+    <t>26.03.202650</t>
+  </si>
+  <si>
+    <t>26.03.202651</t>
+  </si>
+  <si>
+    <t>26.03.202652</t>
+  </si>
+  <si>
+    <t>26.03.202653</t>
+  </si>
+  <si>
+    <t>26.03.202654</t>
+  </si>
+  <si>
+    <t>26.03.202655</t>
+  </si>
+  <si>
+    <t>26.03.202656</t>
+  </si>
+  <si>
+    <t>26.03.202657</t>
+  </si>
+  <si>
+    <t>26.03.202658</t>
+  </si>
+  <si>
+    <t>26.03.202659</t>
+  </si>
+  <si>
+    <t>26.03.202660</t>
+  </si>
+  <si>
+    <t>26.03.202661</t>
+  </si>
+  <si>
+    <t>26.03.202662</t>
+  </si>
+  <si>
+    <t>26.03.202663</t>
+  </si>
+  <si>
+    <t>26.03.202664</t>
+  </si>
+  <si>
+    <t>26.03.202665</t>
+  </si>
+  <si>
+    <t>26.03.202666</t>
+  </si>
+  <si>
+    <t>26.03.202667</t>
+  </si>
+  <si>
+    <t>26.03.202668</t>
+  </si>
+  <si>
+    <t>26.03.202669</t>
+  </si>
+  <si>
+    <t>26.03.202670</t>
+  </si>
+  <si>
+    <t>26.03.202671</t>
+  </si>
+  <si>
+    <t>26.03.202672</t>
+  </si>
+  <si>
+    <t>26.03.202673</t>
+  </si>
+  <si>
+    <t>26.03.202674</t>
+  </si>
+  <si>
+    <t>26.03.202675</t>
+  </si>
+  <si>
+    <t>26.03.202676</t>
+  </si>
+  <si>
+    <t>26.03.202677</t>
+  </si>
+  <si>
+    <t>26.03.202678</t>
+  </si>
+  <si>
+    <t>26.03.202679</t>
+  </si>
+  <si>
+    <t>26.03.202680</t>
+  </si>
+  <si>
+    <t>26.03.202681</t>
+  </si>
+  <si>
+    <t>26.03.202682</t>
+  </si>
+  <si>
+    <t>26.03.202683</t>
+  </si>
+  <si>
+    <t>26.03.202684</t>
+  </si>
+  <si>
+    <t>26.03.202685</t>
+  </si>
+  <si>
+    <t>26.03.202686</t>
+  </si>
+  <si>
+    <t>26.03.202687</t>
+  </si>
+  <si>
+    <t>26.03.202688</t>
+  </si>
+  <si>
+    <t>26.03.202689</t>
+  </si>
+  <si>
+    <t>26.03.202690</t>
+  </si>
+  <si>
+    <t>26.03.202691</t>
+  </si>
+  <si>
+    <t>26.03.202692</t>
+  </si>
+  <si>
+    <t>26.03.202693</t>
+  </si>
+  <si>
+    <t>26.03.202694</t>
+  </si>
+  <si>
+    <t>26.03.202695</t>
+  </si>
+  <si>
+    <t>26.03.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46093</v>
+        <v>46106</v>
       </c>
       <c r="B2">
-        <v>89.187</v>
+        <v>1.996</v>
       </c>
       <c r="C2">
-        <v>265.679</v>
+        <v>271.653</v>
       </c>
       <c r="D2">
-        <v>265.679</v>
+        <v>271.653</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46093.01041666666</v>
+        <v>46106.01041666666</v>
       </c>
       <c r="B3">
-        <v>47.851</v>
+        <v>28.353</v>
       </c>
       <c r="C3">
-        <v>39.532</v>
+        <v>-36.049</v>
       </c>
       <c r="D3">
-        <v>39.532</v>
+        <v>-36.049</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46093.02083333334</v>
+        <v>46106.02083333334</v>
       </c>
       <c r="B4">
-        <v>31.246</v>
+        <v>17.791</v>
       </c>
       <c r="C4">
-        <v>33.99</v>
+        <v>220.335</v>
       </c>
       <c r="D4">
-        <v>33.99</v>
+        <v>220.335</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46093.03125</v>
+        <v>46106.03125</v>
       </c>
       <c r="B5">
-        <v>39.489</v>
+        <v>20.346</v>
       </c>
       <c r="C5">
-        <v>150.521</v>
+        <v>251</v>
       </c>
       <c r="D5">
-        <v>150.521</v>
+        <v>251</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46093.04166666666</v>
+        <v>46106.04166666666</v>
       </c>
       <c r="B6">
-        <v>61.114</v>
+        <v>19.937</v>
       </c>
       <c r="C6">
-        <v>194.524</v>
+        <v>257.424</v>
       </c>
       <c r="D6">
-        <v>194.524</v>
+        <v>257.424</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46093.05208333334</v>
+        <v>46106.05208333334</v>
       </c>
       <c r="B7">
-        <v>42.234</v>
+        <v>16.807</v>
       </c>
       <c r="C7">
-        <v>109.643</v>
+        <v>181.499</v>
       </c>
       <c r="D7">
-        <v>109.643</v>
+        <v>181.499</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46093.0625</v>
+        <v>46106.0625</v>
       </c>
       <c r="B8">
-        <v>14.709</v>
+        <v>7.619</v>
       </c>
       <c r="C8">
-        <v>224.356</v>
+        <v>253.101</v>
       </c>
       <c r="D8">
-        <v>224.356</v>
+        <v>253.101</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46093.07291666666</v>
+        <v>46106.07291666666</v>
       </c>
       <c r="B9">
-        <v>-3.634</v>
+        <v>17.5</v>
       </c>
       <c r="C9">
-        <v>600</v>
+        <v>17.961</v>
       </c>
       <c r="D9">
-        <v>600</v>
+        <v>17.961</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46093.08333333334</v>
+        <v>46106.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.957</v>
+        <v>3.675</v>
       </c>
       <c r="C10">
-        <v>173.672</v>
+        <v>147.45</v>
       </c>
       <c r="D10">
-        <v>173.672</v>
+        <v>147.45</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46093.09375</v>
+        <v>46106.09375</v>
       </c>
       <c r="B11">
-        <v>-13.301</v>
+        <v>-10.812</v>
       </c>
       <c r="C11">
-        <v>783.112</v>
+        <v>715.246</v>
       </c>
       <c r="D11">
-        <v>783.112</v>
+        <v>715.246</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46093.10416666666</v>
+        <v>46106.10416666666</v>
       </c>
       <c r="B12">
-        <v>-3.16</v>
+        <v>3.332</v>
       </c>
       <c r="C12">
-        <v>721.524</v>
+        <v>256.356</v>
       </c>
       <c r="D12">
-        <v>721.524</v>
+        <v>256.356</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46093.11458333334</v>
+        <v>46106.11458333334</v>
       </c>
       <c r="B13">
-        <v>-26.228</v>
+        <v>4.903</v>
       </c>
       <c r="C13">
-        <v>912.433</v>
+        <v>258.948</v>
       </c>
       <c r="D13">
-        <v>912.433</v>
+        <v>258.948</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46093.125</v>
+        <v>46106.125</v>
       </c>
       <c r="B14">
-        <v>12.603</v>
+        <v>-9.262</v>
       </c>
       <c r="C14">
-        <v>400</v>
+        <v>775.986</v>
       </c>
       <c r="D14">
-        <v>400</v>
+        <v>775.986</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46093.13541666666</v>
+        <v>46106.13541666666</v>
       </c>
       <c r="B15">
-        <v>5.899</v>
+        <v>-33.959</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>768.052</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>768.052</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46093.14583333334</v>
+        <v>46106.14583333334</v>
       </c>
       <c r="B16">
-        <v>-15.992</v>
+        <v>-28.573</v>
       </c>
       <c r="C16">
-        <v>946.085</v>
+        <v>771.369</v>
       </c>
       <c r="D16">
-        <v>946.085</v>
+        <v>771.369</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46093.15625</v>
+        <v>46106.15625</v>
       </c>
       <c r="B17">
-        <v>-23.319</v>
+        <v>-59.924</v>
       </c>
       <c r="C17">
-        <v>1128.24</v>
+        <v>1739.562</v>
       </c>
       <c r="D17">
-        <v>1128.24</v>
+        <v>1739.562</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46093.16666666666</v>
+        <v>46106.16666666666</v>
       </c>
       <c r="B18">
-        <v>-30.246</v>
+        <v>-28.635</v>
       </c>
       <c r="C18">
-        <v>1174.476</v>
+        <v>1179.102</v>
       </c>
       <c r="D18">
-        <v>1174.476</v>
+        <v>1179.102</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46093.17708333334</v>
+        <v>46106.17708333334</v>
       </c>
       <c r="B19">
-        <v>-33.793</v>
+        <v>-34.807</v>
       </c>
       <c r="C19">
-        <v>843.506</v>
+        <v>1384.662</v>
       </c>
       <c r="D19">
-        <v>843.506</v>
+        <v>1384.662</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46093.1875</v>
+        <v>46106.1875</v>
       </c>
       <c r="B20">
-        <v>-28.845</v>
+        <v>-50.208</v>
       </c>
       <c r="C20">
-        <v>1130.686</v>
+        <v>3536.136</v>
       </c>
       <c r="D20">
-        <v>1130.686</v>
+        <v>3536.136</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46093.19791666666</v>
+        <v>46106.19791666666</v>
       </c>
       <c r="B21">
-        <v>-58.786</v>
+        <v>-43.448</v>
       </c>
       <c r="C21">
-        <v>2903.506</v>
+        <v>2365.444</v>
       </c>
       <c r="D21">
-        <v>2903.506</v>
+        <v>2365.444</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46093.20833333334</v>
+        <v>46106.20833333334</v>
       </c>
       <c r="B22">
-        <v>-3.493</v>
+        <v>-33.994</v>
       </c>
       <c r="C22">
-        <v>2263.644</v>
+        <v>1337.735</v>
       </c>
       <c r="D22">
-        <v>2263.644</v>
+        <v>1337.735</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46093.21875</v>
+        <v>46106.21875</v>
       </c>
       <c r="B23">
-        <v>-4.642</v>
+        <v>-10.958</v>
       </c>
       <c r="C23">
-        <v>710.152</v>
+        <v>1034.264</v>
       </c>
       <c r="D23">
-        <v>710.152</v>
+        <v>1034.264</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46093.22916666666</v>
+        <v>46106.22916666666</v>
       </c>
       <c r="B24">
-        <v>-5.52</v>
+        <v>3.89</v>
       </c>
       <c r="C24">
-        <v>1012.19</v>
+        <v>772.123</v>
       </c>
       <c r="D24">
-        <v>1012.19</v>
+        <v>772.123</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46093.23958333334</v>
+        <v>46106.23958333334</v>
       </c>
       <c r="B25">
-        <v>-18.444</v>
+        <v>5.315</v>
       </c>
       <c r="C25">
-        <v>1025.464</v>
+        <v>395.288</v>
       </c>
       <c r="D25">
-        <v>1025.464</v>
+        <v>395.288</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46093.25</v>
+        <v>46106.25</v>
       </c>
       <c r="B26">
-        <v>23.404</v>
+        <v>51.141</v>
       </c>
       <c r="C26">
-        <v>253.211</v>
+        <v>217.443</v>
       </c>
       <c r="D26">
-        <v>253.211</v>
+        <v>217.443</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46093.26041666666</v>
+        <v>46106.26041666666</v>
       </c>
       <c r="B27">
-        <v>11.014</v>
+        <v>33.704</v>
       </c>
       <c r="C27">
-        <v>253.603</v>
+        <v>41.52</v>
       </c>
       <c r="D27">
-        <v>253.603</v>
+        <v>41.52</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46093.27083333334</v>
+        <v>46106.27083333334</v>
       </c>
       <c r="B28">
-        <v>19.97</v>
+        <v>19.431</v>
       </c>
       <c r="C28">
-        <v>253.12</v>
+        <v>194.167</v>
       </c>
       <c r="D28">
-        <v>253.12</v>
+        <v>194.167</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46093.28125</v>
+        <v>46106.28125</v>
       </c>
       <c r="B29">
-        <v>8.662000000000001</v>
+        <v>76.684</v>
       </c>
       <c r="C29">
-        <v>400</v>
+        <v>261.647</v>
       </c>
       <c r="D29">
-        <v>400</v>
+        <v>261.647</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46093.29166666666</v>
+        <v>46106.29166666666</v>
       </c>
       <c r="B30">
-        <v>-22.458</v>
+        <v>52.619</v>
       </c>
       <c r="C30">
-        <v>1186.163</v>
+        <v>296.732</v>
       </c>
       <c r="D30">
-        <v>1186.163</v>
+        <v>296.732</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46093.30208333334</v>
+        <v>46106.30208333334</v>
       </c>
       <c r="B31">
-        <v>-0.718</v>
+        <v>17.382</v>
       </c>
       <c r="C31">
-        <v>995.759</v>
+        <v>1.349</v>
       </c>
       <c r="D31">
-        <v>995.759</v>
+        <v>1.349</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46093.3125</v>
+        <v>46106.3125</v>
       </c>
       <c r="B32">
-        <v>-6.198</v>
+        <v>50.312</v>
       </c>
       <c r="C32">
-        <v>699</v>
+        <v>12.971</v>
       </c>
       <c r="D32">
-        <v>699</v>
+        <v>12.971</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46093.32291666666</v>
+        <v>46106.32291666666</v>
       </c>
       <c r="B33">
-        <v>-11.082</v>
+        <v>63.912</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>-23.081</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>-23.081</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46093.33333333334</v>
+        <v>46106.33333333334</v>
       </c>
       <c r="B34">
-        <v>-57.211</v>
+        <v>11.439</v>
       </c>
       <c r="C34">
-        <v>861.3390000000001</v>
+        <v>4.38</v>
       </c>
       <c r="D34">
-        <v>861.3390000000001</v>
+        <v>4.38</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46093.34375</v>
+        <v>46106.34375</v>
       </c>
       <c r="B35">
-        <v>-97.181</v>
+        <v>-7.281</v>
       </c>
       <c r="C35">
-        <v>862.165</v>
+        <v>889.244</v>
       </c>
       <c r="D35">
-        <v>862.165</v>
+        <v>889.244</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46093.35416666666</v>
+        <v>46106.35416666666</v>
       </c>
       <c r="B36">
-        <v>-127.855</v>
+        <v>-2.311</v>
       </c>
       <c r="C36">
-        <v>1079.422</v>
+        <v>667.29</v>
       </c>
       <c r="D36">
-        <v>1079.422</v>
+        <v>667.29</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46093.36458333334</v>
+        <v>46106.36458333334</v>
       </c>
       <c r="B37">
-        <v>-78.06399999999999</v>
+        <v>13.14</v>
       </c>
       <c r="C37">
-        <v>914.936</v>
+        <v>19.097</v>
       </c>
       <c r="D37">
-        <v>914.936</v>
+        <v>19.097</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46093.375</v>
+        <v>46106.375</v>
       </c>
       <c r="B38">
-        <v>-68.723</v>
+        <v>33.75</v>
       </c>
       <c r="C38">
-        <v>743.187</v>
+        <v>17.503</v>
       </c>
       <c r="D38">
-        <v>743.187</v>
+        <v>17.503</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46093.38541666666</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="B39">
-        <v>-52.466</v>
+        <v>65.041</v>
       </c>
       <c r="C39">
-        <v>745.816</v>
+        <v>11.771</v>
       </c>
       <c r="D39">
-        <v>745.816</v>
+        <v>11.771</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46093.39583333334</v>
+        <v>46106.39583333334</v>
       </c>
       <c r="B40">
-        <v>-48.477</v>
+        <v>75.465</v>
       </c>
       <c r="C40">
-        <v>745.85</v>
+        <v>-66.358</v>
       </c>
       <c r="D40">
-        <v>745.85</v>
+        <v>-66.358</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46093.40625</v>
+        <v>46106.40625</v>
       </c>
       <c r="B41">
-        <v>-12.508</v>
+        <v>112.059</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>-198.948</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>-198.948</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46093.41666666666</v>
+        <v>46106.41666666666</v>
       </c>
       <c r="B42">
-        <v>-26.469</v>
+        <v>83.452</v>
       </c>
       <c r="C42">
-        <v>583.8920000000001</v>
+        <v>-17.317</v>
       </c>
       <c r="D42">
-        <v>583.8920000000001</v>
+        <v>-17.317</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46093.42708333334</v>
+        <v>46106.42708333334</v>
       </c>
       <c r="B43">
-        <v>-1.503</v>
+        <v>82.88200000000001</v>
       </c>
       <c r="C43">
-        <v>574.28</v>
+        <v>-145.942</v>
       </c>
       <c r="D43">
-        <v>574.28</v>
+        <v>-145.942</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46093.4375</v>
+        <v>46106.4375</v>
       </c>
       <c r="B44">
-        <v>-20.371</v>
+        <v>90.07299999999999</v>
       </c>
       <c r="C44">
-        <v>162.483</v>
+        <v>0.631</v>
       </c>
       <c r="D44">
-        <v>162.483</v>
+        <v>0.631</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46093.44791666666</v>
+        <v>46106.44791666666</v>
       </c>
       <c r="B45">
-        <v>6.363</v>
+        <v>109.475</v>
       </c>
       <c r="C45">
-        <v>-107.128</v>
+        <v>21.201</v>
       </c>
       <c r="D45">
-        <v>-107.128</v>
+        <v>21.201</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46093.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="B46">
-        <v>23.287</v>
+        <v>197.595</v>
       </c>
       <c r="C46">
-        <v>-648.609</v>
+        <v>-98.145</v>
       </c>
       <c r="D46">
-        <v>-648.609</v>
+        <v>-98.145</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46093.46875</v>
+        <v>46106.46875</v>
       </c>
       <c r="B47">
-        <v>20.155</v>
+        <v>137.634</v>
       </c>
       <c r="C47">
-        <v>-347.766</v>
+        <v>-99.843</v>
       </c>
       <c r="D47">
-        <v>-347.766</v>
+        <v>-99.843</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46093.47916666666</v>
+        <v>46106.47916666666</v>
       </c>
       <c r="B48">
-        <v>38.513</v>
+        <v>43.2</v>
       </c>
       <c r="C48">
-        <v>-1100.384</v>
+        <v>2.319</v>
       </c>
       <c r="D48">
-        <v>-1100.384</v>
+        <v>2.319</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46093.48958333334</v>
+        <v>46106.48958333334</v>
       </c>
       <c r="B49">
-        <v>38.106</v>
+        <v>44.571</v>
       </c>
       <c r="C49">
-        <v>-878.722</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>-878.722</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46093.5</v>
+        <v>46106.5</v>
       </c>
       <c r="B50">
-        <v>39.109</v>
+        <v>106.285</v>
       </c>
       <c r="C50">
-        <v>-356.826</v>
+        <v>-10.069</v>
       </c>
       <c r="D50">
-        <v>-356.826</v>
+        <v>-10.069</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46093.51041666666</v>
+        <v>46106.51041666666</v>
       </c>
       <c r="B51">
-        <v>76.30500000000001</v>
+        <v>100.267</v>
       </c>
       <c r="C51">
-        <v>-1998.29</v>
+        <v>-0.608</v>
       </c>
       <c r="D51">
-        <v>-1998.29</v>
+        <v>-0.608</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46093.52083333334</v>
+        <v>46106.52083333334</v>
       </c>
       <c r="B52">
-        <v>94.717</v>
+        <v>90.41200000000001</v>
       </c>
       <c r="C52">
-        <v>-4721.954</v>
+        <v>7.077</v>
       </c>
       <c r="D52">
-        <v>-4721.954</v>
+        <v>7.077</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46093.53125</v>
+        <v>46106.53125</v>
       </c>
       <c r="B53">
-        <v>186.374</v>
+        <v>87.752</v>
       </c>
       <c r="C53">
-        <v>-6557.66</v>
+        <v>-622.215</v>
       </c>
       <c r="D53">
-        <v>-6557.66</v>
+        <v>-622.215</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46093.54166666666</v>
+        <v>46106.54166666666</v>
       </c>
       <c r="B54">
-        <v>152.303</v>
+        <v>89.72199999999999</v>
       </c>
       <c r="C54">
-        <v>-5392.297</v>
+        <v>-156.86</v>
       </c>
       <c r="D54">
-        <v>-5392.297</v>
+        <v>-156.86</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46093.55208333334</v>
+        <v>46106.55208333334</v>
       </c>
       <c r="B55">
-        <v>124.628</v>
+        <v>88.685</v>
       </c>
       <c r="C55">
-        <v>-233.049</v>
+        <v>15.136</v>
       </c>
       <c r="D55">
-        <v>-233.049</v>
+        <v>15.136</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46093.5625</v>
+        <v>46106.5625</v>
       </c>
       <c r="B56">
-        <v>95.548</v>
+        <v>77.59399999999999</v>
       </c>
       <c r="C56">
-        <v>6.059</v>
+        <v>-25.553</v>
       </c>
       <c r="D56">
-        <v>6.059</v>
+        <v>-25.553</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46093.57291666666</v>
+        <v>46106.57291666666</v>
       </c>
       <c r="B57">
-        <v>91.08799999999999</v>
+        <v>79.893</v>
       </c>
       <c r="C57">
-        <v>7.038</v>
+        <v>-84.7</v>
       </c>
       <c r="D57">
-        <v>7.038</v>
+        <v>-84.7</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46093.58333333334</v>
+        <v>46106.58333333334</v>
       </c>
       <c r="B58">
-        <v>123.455</v>
+        <v>121.02</v>
       </c>
       <c r="C58">
-        <v>-0.224</v>
+        <v>-1119.416</v>
       </c>
       <c r="D58">
-        <v>-0.224</v>
+        <v>-1119.416</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46093.59375</v>
+        <v>46106.59375</v>
       </c>
       <c r="B59">
-        <v>118.096</v>
+        <v>115.308</v>
       </c>
       <c r="C59">
-        <v>-80.203</v>
+        <v>-45.12</v>
       </c>
       <c r="D59">
-        <v>-80.203</v>
+        <v>-45.12</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46093.60416666666</v>
+        <v>46106.60416666666</v>
       </c>
       <c r="B60">
-        <v>115.4</v>
+        <v>74.131</v>
       </c>
       <c r="C60">
-        <v>-81.411</v>
+        <v>-24.504</v>
       </c>
       <c r="D60">
-        <v>-81.411</v>
+        <v>-24.504</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46093.61458333334</v>
+        <v>46106.61458333334</v>
       </c>
       <c r="B61">
-        <v>86.154</v>
+        <v>111.867</v>
       </c>
       <c r="C61">
-        <v>-26.838</v>
+        <v>9.644</v>
       </c>
       <c r="D61">
-        <v>-26.838</v>
+        <v>9.644</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46093.625</v>
+        <v>46106.625</v>
       </c>
       <c r="B62">
-        <v>82.178</v>
+        <v>179.933</v>
       </c>
       <c r="C62">
-        <v>12.215</v>
+        <v>-248.523</v>
       </c>
       <c r="D62">
-        <v>12.215</v>
+        <v>-248.523</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46093.63541666666</v>
+        <v>46106.63541666666</v>
       </c>
       <c r="B63">
-        <v>43.55</v>
+        <v>143.347</v>
       </c>
       <c r="C63">
-        <v>0.414</v>
+        <v>-156.815</v>
       </c>
       <c r="D63">
-        <v>0.414</v>
+        <v>-156.815</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46093.64583333334</v>
+        <v>46106.64583333334</v>
       </c>
       <c r="B64">
-        <v>19.34</v>
+        <v>110.442</v>
       </c>
       <c r="C64">
-        <v>0.412</v>
+        <v>-267.8</v>
       </c>
       <c r="D64">
-        <v>0.412</v>
+        <v>-267.8</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46093.65625</v>
+        <v>46106.65625</v>
       </c>
       <c r="B65">
-        <v>-18.879</v>
+        <v>85.992</v>
       </c>
       <c r="C65">
-        <v>1343.811</v>
+        <v>2.618</v>
       </c>
       <c r="D65">
-        <v>1343.811</v>
+        <v>2.618</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46093.66666666666</v>
+        <v>46106.66666666666</v>
       </c>
       <c r="B66">
-        <v>15.55</v>
+        <v>94.658</v>
       </c>
       <c r="C66">
-        <v>251.549</v>
+        <v>2.635</v>
       </c>
       <c r="D66">
-        <v>251.549</v>
+        <v>2.635</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46093.67708333334</v>
+        <v>46106.67708333334</v>
       </c>
       <c r="B67">
-        <v>-13.599</v>
+        <v>58.7</v>
       </c>
       <c r="C67">
-        <v>1138.507</v>
+        <v>9.287000000000001</v>
       </c>
       <c r="D67">
-        <v>1138.507</v>
+        <v>9.287000000000001</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46093.6875</v>
+        <v>46106.6875</v>
       </c>
       <c r="B68">
-        <v>-27.079</v>
+        <v>60.732</v>
       </c>
       <c r="C68">
-        <v>1205.506</v>
+        <v>0.948</v>
       </c>
       <c r="D68">
-        <v>1205.506</v>
+        <v>0.948</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46093.69791666666</v>
+        <v>46106.69791666666</v>
       </c>
       <c r="B69">
-        <v>-40.916</v>
+        <v>39.908</v>
       </c>
       <c r="C69">
-        <v>1283.798</v>
+        <v>16.464</v>
       </c>
       <c r="D69">
-        <v>1283.798</v>
+        <v>16.464</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46093.70833333334</v>
+        <v>46106.70833333334</v>
       </c>
       <c r="B70">
-        <v>14.583</v>
+        <v>69.35299999999999</v>
       </c>
       <c r="C70">
-        <v>400</v>
+        <v>50.142</v>
       </c>
       <c r="D70">
-        <v>400</v>
+        <v>50.142</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46093.71875</v>
+        <v>46106.71875</v>
       </c>
       <c r="B71">
-        <v>9.625</v>
+        <v>68.889</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>65.864</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>65.864</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46093.72916666666</v>
+        <v>46106.72916666666</v>
       </c>
       <c r="B72">
-        <v>-14.414</v>
+        <v>77.38</v>
       </c>
       <c r="C72">
-        <v>1239.931</v>
+        <v>122.929</v>
       </c>
       <c r="D72">
-        <v>1239.931</v>
+        <v>122.929</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46093.73958333334</v>
+        <v>46106.73958333334</v>
       </c>
       <c r="B73">
-        <v>-35.533</v>
+        <v>53.208</v>
       </c>
       <c r="C73">
-        <v>2248.593</v>
+        <v>500</v>
       </c>
       <c r="D73">
-        <v>2248.593</v>
+        <v>500</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46093.75</v>
+        <v>46106.75</v>
       </c>
       <c r="B74">
-        <v>-33.753</v>
+        <v>27.884</v>
       </c>
       <c r="C74">
-        <v>1445.44</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>1445.44</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46093.76041666666</v>
+        <v>46106.76041666666</v>
       </c>
       <c r="B75">
-        <v>-36.634</v>
+        <v>19.576</v>
       </c>
       <c r="C75">
-        <v>1427.52</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>1427.52</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46093.77083333334</v>
+        <v>46106.77083333334</v>
       </c>
       <c r="B76">
-        <v>-60.719</v>
+        <v>17.903</v>
       </c>
       <c r="C76">
-        <v>1518.985</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>1518.985</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46093.78125</v>
+        <v>46106.78125</v>
       </c>
       <c r="B77">
-        <v>-15.768</v>
+        <v>18.134</v>
       </c>
       <c r="C77">
-        <v>1572.639</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>1572.639</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46093.79166666666</v>
+        <v>46106.79166666666</v>
       </c>
       <c r="B78">
-        <v>38.684</v>
+        <v>20.448</v>
       </c>
       <c r="C78">
-        <v>173.539</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>173.539</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46093.80208333334</v>
+        <v>46106.80208333334</v>
       </c>
       <c r="B79">
-        <v>16.207</v>
+        <v>16.187</v>
       </c>
       <c r="C79">
-        <v>301.144</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>301.144</v>
+        <v>0</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46093.8125</v>
+        <v>46106.8125</v>
       </c>
       <c r="B80">
-        <v>2.324</v>
+        <v>39.744</v>
       </c>
       <c r="C80">
-        <v>368.637</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>368.637</v>
+        <v>0</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46093.82291666666</v>
+        <v>46106.82291666666</v>
       </c>
       <c r="B81">
-        <v>3.319</v>
+        <v>70.384</v>
       </c>
       <c r="C81">
-        <v>290.718</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>290.718</v>
+        <v>0</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46093.83333333334</v>
+        <v>46106.83333333334</v>
       </c>
       <c r="B82">
-        <v>-15.001</v>
+        <v>37.867</v>
       </c>
       <c r="C82">
-        <v>803.629</v>
+        <v>493.074</v>
       </c>
       <c r="D82">
-        <v>803.629</v>
+        <v>493.074</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46093.84375</v>
+        <v>46106.84375</v>
       </c>
       <c r="B83">
-        <v>-6.391</v>
+        <v>35.359</v>
       </c>
       <c r="C83">
-        <v>885.164</v>
+        <v>496.407</v>
       </c>
       <c r="D83">
-        <v>885.164</v>
+        <v>496.407</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46093.85416666666</v>
+        <v>46106.85416666666</v>
       </c>
       <c r="B84">
-        <v>22.834</v>
+        <v>36.848</v>
       </c>
       <c r="C84">
-        <v>285.625</v>
+        <v>51.862</v>
       </c>
       <c r="D84">
-        <v>285.625</v>
+        <v>51.862</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46093.86458333334</v>
+        <v>46106.86458333334</v>
       </c>
       <c r="B85">
-        <v>30.297</v>
+        <v>51.509</v>
       </c>
       <c r="C85">
-        <v>279.87</v>
+        <v>78.006</v>
       </c>
       <c r="D85">
-        <v>279.87</v>
+        <v>78.006</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46093.875</v>
+        <v>46106.875</v>
       </c>
       <c r="B86">
-        <v>-18.197</v>
+        <v>4.602</v>
       </c>
       <c r="C86">
-        <v>1185.43</v>
+        <v>188.341</v>
       </c>
       <c r="D86">
-        <v>1185.43</v>
+        <v>188.341</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46093.88541666666</v>
+        <v>46106.88541666666</v>
       </c>
       <c r="B87">
-        <v>-19.783</v>
+        <v>0</v>
       </c>
       <c r="C87">
-        <v>1194.464</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>1194.464</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46093.89583333334</v>
+        <v>46106.89583333334</v>
       </c>
       <c r="B88">
-        <v>-2.837</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>885.105</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>885.105</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46093.90625</v>
+        <v>46106.90625</v>
       </c>
       <c r="B89">
-        <v>-3.358</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>935.157</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>935.157</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46093.91666666666</v>
+        <v>46106.91666666666</v>
       </c>
       <c r="B90">
-        <v>-27.527</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>1956.558</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>1956.558</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46093.92708333334</v>
+        <v>46106.92708333334</v>
       </c>
       <c r="B91">
-        <v>-43.543</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>2192.735</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>2192.735</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46093.9375</v>
+        <v>46106.9375</v>
       </c>
       <c r="B92">
-        <v>-31.822</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>1109.858</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>1109.858</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46093.94791666666</v>
+        <v>46106.94791666666</v>
       </c>
       <c r="B93">
-        <v>-20.794</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>1075.679</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>1075.679</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46093.95833333334</v>
+        <v>46106.95833333334</v>
       </c>
       <c r="B94">
-        <v>-22.748</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>1063.846</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>1063.846</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46093.96875</v>
+        <v>46106.96875</v>
       </c>
       <c r="B95">
-        <v>-24.905</v>
+        <v>0</v>
       </c>
       <c r="C95">
-        <v>1059.072</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>1059.072</v>
+        <v>0</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46093.97916666666</v>
+        <v>46106.97916666666</v>
       </c>
       <c r="B96">
-        <v>-5.124</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>1074.63</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>1074.63</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,10 +2894,10 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46093.98958333334</v>
+        <v>46106.98958333334</v>
       </c>
       <c r="B97">
-        <v>-5.282</v>
+        <v>0</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46094</v>
+        <v>46107</v>
       </c>
       <c r="B98">
-        <v>-28.691</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>1178.345</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>1178.345</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B99">
-        <v>-30.587</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>1165.698</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>1165.698</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B100">
-        <v>-19.411</v>
+        <v>0</v>
       </c>
       <c r="C100">
-        <v>979.946</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>979.946</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B101">
-        <v>-12.578</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>775.513</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>775.513</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B102">
-        <v>-10.373</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>929.798</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>929.798</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B103">
-        <v>-11.451</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>775.728</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>775.728</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B104">
-        <v>4.909</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>257.522</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>257.522</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B105">
-        <v>23.089</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>114.976</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>114.976</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B106">
-        <v>2.712</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>197.394</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>197.394</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B107">
-        <v>13.565</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>268.342</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>268.342</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B108">
-        <v>25.181</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>178.188</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>178.188</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B109">
-        <v>18.132</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>88.285</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>88.285</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B110">
-        <v>1.439</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>239.033</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>239.033</v>
+        <v>0</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B111">
-        <v>14.472</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>249.672</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>249.672</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B112">
-        <v>4.029</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>251.537</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>251.537</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B113">
-        <v>12.18</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>241.523</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>241.523</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B114">
-        <v>-8.609</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>254.249</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>254.249</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B115">
-        <v>-24.721</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,10 +3274,10 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B116">
-        <v>-25.206</v>
+        <v>0</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B117">
-        <v>-51.309</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>719.9880000000001</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>719.9880000000001</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B118">
-        <v>-8.218</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>765.553</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>765.553</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B119">
-        <v>-32.516</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B120">
-        <v>-8.347</v>
+        <v>0</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B121">
-        <v>2.597</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>255.242</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>255.242</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B122">
-        <v>39.945</v>
+        <v>0</v>
       </c>
       <c r="C122">
-        <v>-41.665</v>
+        <v>0</v>
       </c>
       <c r="D122">
-        <v>-41.665</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B123">
-        <v>66.551</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>-191.064</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>-191.064</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B124">
-        <v>64.331</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>-735.635</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>-735.635</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B125">
-        <v>80.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>-3400.417</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>-3400.417</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B126">
-        <v>112.479</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>-495.009</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>-495.009</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B127">
-        <v>89.85599999999999</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>-103.048</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>-103.048</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3554,7 +3554,7 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.03.20261</t>
-  </si>
-  <si>
-    <t>25.03.20262</t>
-  </si>
-  <si>
-    <t>25.03.20263</t>
-  </si>
-  <si>
-    <t>25.03.20264</t>
-  </si>
-  <si>
-    <t>25.03.20265</t>
-  </si>
-  <si>
-    <t>25.03.20266</t>
-  </si>
-  <si>
-    <t>25.03.20267</t>
-  </si>
-  <si>
-    <t>25.03.20268</t>
-  </si>
-  <si>
-    <t>25.03.20269</t>
-  </si>
-  <si>
-    <t>25.03.202610</t>
-  </si>
-  <si>
-    <t>25.03.202611</t>
-  </si>
-  <si>
-    <t>25.03.202612</t>
-  </si>
-  <si>
-    <t>25.03.202613</t>
-  </si>
-  <si>
-    <t>25.03.202614</t>
-  </si>
-  <si>
-    <t>25.03.202615</t>
-  </si>
-  <si>
-    <t>25.03.202616</t>
-  </si>
-  <si>
-    <t>25.03.202617</t>
-  </si>
-  <si>
-    <t>25.03.202618</t>
-  </si>
-  <si>
-    <t>25.03.202619</t>
-  </si>
-  <si>
-    <t>25.03.202620</t>
-  </si>
-  <si>
-    <t>25.03.202621</t>
-  </si>
-  <si>
-    <t>25.03.202622</t>
-  </si>
-  <si>
-    <t>25.03.202623</t>
-  </si>
-  <si>
-    <t>25.03.202624</t>
-  </si>
-  <si>
-    <t>25.03.202625</t>
-  </si>
-  <si>
-    <t>25.03.202626</t>
-  </si>
-  <si>
-    <t>25.03.202627</t>
-  </si>
-  <si>
-    <t>25.03.202628</t>
-  </si>
-  <si>
-    <t>25.03.202629</t>
-  </si>
-  <si>
-    <t>25.03.202630</t>
-  </si>
-  <si>
-    <t>25.03.202631</t>
-  </si>
-  <si>
-    <t>25.03.202632</t>
-  </si>
-  <si>
-    <t>25.03.202633</t>
-  </si>
-  <si>
-    <t>25.03.202634</t>
-  </si>
-  <si>
-    <t>25.03.202635</t>
-  </si>
-  <si>
-    <t>25.03.202636</t>
-  </si>
-  <si>
-    <t>25.03.202637</t>
-  </si>
-  <si>
-    <t>25.03.202638</t>
-  </si>
-  <si>
-    <t>25.03.202639</t>
-  </si>
-  <si>
-    <t>25.03.202640</t>
-  </si>
-  <si>
-    <t>25.03.202641</t>
-  </si>
-  <si>
-    <t>25.03.202642</t>
-  </si>
-  <si>
-    <t>25.03.202643</t>
-  </si>
-  <si>
-    <t>25.03.202644</t>
-  </si>
-  <si>
-    <t>25.03.202645</t>
-  </si>
-  <si>
-    <t>25.03.202646</t>
-  </si>
-  <si>
-    <t>25.03.202647</t>
-  </si>
-  <si>
-    <t>25.03.202648</t>
-  </si>
-  <si>
-    <t>25.03.202649</t>
-  </si>
-  <si>
-    <t>25.03.202650</t>
-  </si>
-  <si>
-    <t>25.03.202651</t>
-  </si>
-  <si>
-    <t>25.03.202652</t>
-  </si>
-  <si>
-    <t>25.03.202653</t>
-  </si>
-  <si>
-    <t>25.03.202654</t>
-  </si>
-  <si>
-    <t>25.03.202655</t>
-  </si>
-  <si>
-    <t>25.03.202656</t>
-  </si>
-  <si>
-    <t>25.03.202657</t>
-  </si>
-  <si>
-    <t>25.03.202658</t>
-  </si>
-  <si>
-    <t>25.03.202659</t>
-  </si>
-  <si>
-    <t>25.03.202660</t>
-  </si>
-  <si>
-    <t>25.03.202661</t>
-  </si>
-  <si>
-    <t>25.03.202662</t>
-  </si>
-  <si>
-    <t>25.03.202663</t>
-  </si>
-  <si>
-    <t>25.03.202664</t>
-  </si>
-  <si>
-    <t>25.03.202665</t>
-  </si>
-  <si>
-    <t>25.03.202666</t>
-  </si>
-  <si>
-    <t>25.03.202667</t>
-  </si>
-  <si>
-    <t>25.03.202668</t>
-  </si>
-  <si>
-    <t>25.03.202669</t>
-  </si>
-  <si>
-    <t>25.03.202670</t>
-  </si>
-  <si>
-    <t>25.03.202671</t>
-  </si>
-  <si>
-    <t>25.03.202672</t>
-  </si>
-  <si>
-    <t>25.03.202673</t>
-  </si>
-  <si>
-    <t>25.03.202674</t>
-  </si>
-  <si>
-    <t>25.03.202675</t>
-  </si>
-  <si>
-    <t>25.03.202676</t>
-  </si>
-  <si>
-    <t>25.03.202677</t>
-  </si>
-  <si>
-    <t>25.03.202678</t>
-  </si>
-  <si>
-    <t>25.03.202679</t>
-  </si>
-  <si>
-    <t>25.03.202680</t>
-  </si>
-  <si>
-    <t>25.03.202681</t>
-  </si>
-  <si>
-    <t>25.03.202682</t>
-  </si>
-  <si>
-    <t>25.03.202683</t>
-  </si>
-  <si>
-    <t>25.03.202684</t>
-  </si>
-  <si>
-    <t>25.03.202685</t>
-  </si>
-  <si>
-    <t>25.03.202686</t>
-  </si>
-  <si>
-    <t>25.03.202687</t>
-  </si>
-  <si>
-    <t>25.03.202688</t>
-  </si>
-  <si>
-    <t>25.03.202689</t>
-  </si>
-  <si>
-    <t>25.03.202690</t>
-  </si>
-  <si>
-    <t>25.03.202691</t>
-  </si>
-  <si>
-    <t>25.03.202692</t>
-  </si>
-  <si>
-    <t>25.03.202693</t>
-  </si>
-  <si>
-    <t>25.03.202694</t>
-  </si>
-  <si>
-    <t>25.03.202695</t>
-  </si>
-  <si>
-    <t>25.03.202696</t>
-  </si>
-  <si>
     <t>26.03.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>26.03.202696</t>
+  </si>
+  <si>
+    <t>27.03.20261</t>
+  </si>
+  <si>
+    <t>27.03.20262</t>
+  </si>
+  <si>
+    <t>27.03.20263</t>
+  </si>
+  <si>
+    <t>27.03.20264</t>
+  </si>
+  <si>
+    <t>27.03.20265</t>
+  </si>
+  <si>
+    <t>27.03.20266</t>
+  </si>
+  <si>
+    <t>27.03.20267</t>
+  </si>
+  <si>
+    <t>27.03.20268</t>
+  </si>
+  <si>
+    <t>27.03.20269</t>
+  </si>
+  <si>
+    <t>27.03.202610</t>
+  </si>
+  <si>
+    <t>27.03.202611</t>
+  </si>
+  <si>
+    <t>27.03.202612</t>
+  </si>
+  <si>
+    <t>27.03.202613</t>
+  </si>
+  <si>
+    <t>27.03.202614</t>
+  </si>
+  <si>
+    <t>27.03.202615</t>
+  </si>
+  <si>
+    <t>27.03.202616</t>
+  </si>
+  <si>
+    <t>27.03.202617</t>
+  </si>
+  <si>
+    <t>27.03.202618</t>
+  </si>
+  <si>
+    <t>27.03.202619</t>
+  </si>
+  <si>
+    <t>27.03.202620</t>
+  </si>
+  <si>
+    <t>27.03.202621</t>
+  </si>
+  <si>
+    <t>27.03.202622</t>
+  </si>
+  <si>
+    <t>27.03.202623</t>
+  </si>
+  <si>
+    <t>27.03.202624</t>
+  </si>
+  <si>
+    <t>27.03.202625</t>
+  </si>
+  <si>
+    <t>27.03.202626</t>
+  </si>
+  <si>
+    <t>27.03.202627</t>
+  </si>
+  <si>
+    <t>27.03.202628</t>
+  </si>
+  <si>
+    <t>27.03.202629</t>
+  </si>
+  <si>
+    <t>27.03.202630</t>
+  </si>
+  <si>
+    <t>27.03.202631</t>
+  </si>
+  <si>
+    <t>27.03.202632</t>
+  </si>
+  <si>
+    <t>27.03.202633</t>
+  </si>
+  <si>
+    <t>27.03.202634</t>
+  </si>
+  <si>
+    <t>27.03.202635</t>
+  </si>
+  <si>
+    <t>27.03.202636</t>
+  </si>
+  <si>
+    <t>27.03.202637</t>
+  </si>
+  <si>
+    <t>27.03.202638</t>
+  </si>
+  <si>
+    <t>27.03.202639</t>
+  </si>
+  <si>
+    <t>27.03.202640</t>
+  </si>
+  <si>
+    <t>27.03.202641</t>
+  </si>
+  <si>
+    <t>27.03.202642</t>
+  </si>
+  <si>
+    <t>27.03.202643</t>
+  </si>
+  <si>
+    <t>27.03.202644</t>
+  </si>
+  <si>
+    <t>27.03.202645</t>
+  </si>
+  <si>
+    <t>27.03.202646</t>
+  </si>
+  <si>
+    <t>27.03.202647</t>
+  </si>
+  <si>
+    <t>27.03.202648</t>
+  </si>
+  <si>
+    <t>27.03.202649</t>
+  </si>
+  <si>
+    <t>27.03.202650</t>
+  </si>
+  <si>
+    <t>27.03.202651</t>
+  </si>
+  <si>
+    <t>27.03.202652</t>
+  </si>
+  <si>
+    <t>27.03.202653</t>
+  </si>
+  <si>
+    <t>27.03.202654</t>
+  </si>
+  <si>
+    <t>27.03.202655</t>
+  </si>
+  <si>
+    <t>27.03.202656</t>
+  </si>
+  <si>
+    <t>27.03.202657</t>
+  </si>
+  <si>
+    <t>27.03.202658</t>
+  </si>
+  <si>
+    <t>27.03.202659</t>
+  </si>
+  <si>
+    <t>27.03.202660</t>
+  </si>
+  <si>
+    <t>27.03.202661</t>
+  </si>
+  <si>
+    <t>27.03.202662</t>
+  </si>
+  <si>
+    <t>27.03.202663</t>
+  </si>
+  <si>
+    <t>27.03.202664</t>
+  </si>
+  <si>
+    <t>27.03.202665</t>
+  </si>
+  <si>
+    <t>27.03.202666</t>
+  </si>
+  <si>
+    <t>27.03.202667</t>
+  </si>
+  <si>
+    <t>27.03.202668</t>
+  </si>
+  <si>
+    <t>27.03.202669</t>
+  </si>
+  <si>
+    <t>27.03.202670</t>
+  </si>
+  <si>
+    <t>27.03.202671</t>
+  </si>
+  <si>
+    <t>27.03.202672</t>
+  </si>
+  <si>
+    <t>27.03.202673</t>
+  </si>
+  <si>
+    <t>27.03.202674</t>
+  </si>
+  <si>
+    <t>27.03.202675</t>
+  </si>
+  <si>
+    <t>27.03.202676</t>
+  </si>
+  <si>
+    <t>27.03.202677</t>
+  </si>
+  <si>
+    <t>27.03.202678</t>
+  </si>
+  <si>
+    <t>27.03.202679</t>
+  </si>
+  <si>
+    <t>27.03.202680</t>
+  </si>
+  <si>
+    <t>27.03.202681</t>
+  </si>
+  <si>
+    <t>27.03.202682</t>
+  </si>
+  <si>
+    <t>27.03.202683</t>
+  </si>
+  <si>
+    <t>27.03.202684</t>
+  </si>
+  <si>
+    <t>27.03.202685</t>
+  </si>
+  <si>
+    <t>27.03.202686</t>
+  </si>
+  <si>
+    <t>27.03.202687</t>
+  </si>
+  <si>
+    <t>27.03.202688</t>
+  </si>
+  <si>
+    <t>27.03.202689</t>
+  </si>
+  <si>
+    <t>27.03.202690</t>
+  </si>
+  <si>
+    <t>27.03.202691</t>
+  </si>
+  <si>
+    <t>27.03.202692</t>
+  </si>
+  <si>
+    <t>27.03.202693</t>
+  </si>
+  <si>
+    <t>27.03.202694</t>
+  </si>
+  <si>
+    <t>27.03.202695</t>
+  </si>
+  <si>
+    <t>27.03.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B2">
-        <v>1.996</v>
+        <v>-24.015</v>
       </c>
       <c r="C2">
-        <v>271.653</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>271.653</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46106.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B3">
-        <v>28.353</v>
+        <v>-21.818</v>
       </c>
       <c r="C3">
-        <v>-36.049</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>-36.049</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46106.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B4">
-        <v>17.791</v>
+        <v>-43.046</v>
       </c>
       <c r="C4">
-        <v>220.335</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>220.335</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46106.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B5">
-        <v>20.346</v>
+        <v>-21.354</v>
       </c>
       <c r="C5">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46106.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B6">
-        <v>19.937</v>
+        <v>-23.085</v>
       </c>
       <c r="C6">
-        <v>257.424</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>257.424</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46106.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B7">
-        <v>16.807</v>
+        <v>-16.714</v>
       </c>
       <c r="C7">
-        <v>181.499</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>181.499</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46106.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B8">
-        <v>7.619</v>
+        <v>13.058</v>
       </c>
       <c r="C8">
-        <v>253.101</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>253.101</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46106.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B9">
-        <v>17.5</v>
+        <v>6.128</v>
       </c>
       <c r="C9">
-        <v>17.961</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>17.961</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46106.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B10">
-        <v>3.675</v>
+        <v>-7.734</v>
       </c>
       <c r="C10">
-        <v>147.45</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>147.45</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46106.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B11">
-        <v>-10.812</v>
+        <v>-1.103</v>
       </c>
       <c r="C11">
-        <v>715.246</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>715.246</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46106.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B12">
-        <v>3.332</v>
+        <v>25.429</v>
       </c>
       <c r="C12">
-        <v>256.356</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>256.356</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46106.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B13">
-        <v>4.903</v>
+        <v>13.561</v>
       </c>
       <c r="C13">
-        <v>258.948</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>258.948</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46106.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B14">
-        <v>-9.262</v>
+        <v>-4.447</v>
       </c>
       <c r="C14">
-        <v>775.986</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>775.986</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46106.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B15">
-        <v>-33.959</v>
+        <v>-12.292</v>
       </c>
       <c r="C15">
-        <v>768.052</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>768.052</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46106.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B16">
-        <v>-28.573</v>
+        <v>-61.553</v>
       </c>
       <c r="C16">
-        <v>771.369</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>771.369</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46106.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B17">
-        <v>-59.924</v>
+        <v>-46.761</v>
       </c>
       <c r="C17">
-        <v>1739.562</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1739.562</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46106.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B18">
-        <v>-28.635</v>
+        <v>-12.262</v>
       </c>
       <c r="C18">
-        <v>1179.102</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1179.102</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46106.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B19">
-        <v>-34.807</v>
+        <v>-20.968</v>
       </c>
       <c r="C19">
-        <v>1384.662</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1384.662</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46106.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B20">
-        <v>-50.208</v>
+        <v>-30.556</v>
       </c>
       <c r="C20">
-        <v>3536.136</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>3536.136</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46106.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B21">
-        <v>-43.448</v>
+        <v>-32.861</v>
       </c>
       <c r="C21">
-        <v>2365.444</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>2365.444</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46106.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B22">
-        <v>-33.994</v>
+        <v>19.712</v>
       </c>
       <c r="C22">
-        <v>1337.735</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>1337.735</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46106.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B23">
-        <v>-10.958</v>
+        <v>6.758</v>
       </c>
       <c r="C23">
-        <v>1034.264</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1034.264</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46106.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B24">
-        <v>3.89</v>
+        <v>1.182</v>
       </c>
       <c r="C24">
-        <v>772.123</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>772.123</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46106.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B25">
-        <v>5.315</v>
+        <v>-1.635</v>
       </c>
       <c r="C25">
-        <v>395.288</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>395.288</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46106.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B26">
-        <v>51.141</v>
+        <v>3.806</v>
       </c>
       <c r="C26">
-        <v>217.443</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>217.443</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46106.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B27">
-        <v>33.704</v>
+        <v>-26.457</v>
       </c>
       <c r="C27">
-        <v>41.52</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>41.52</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46106.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B28">
-        <v>19.431</v>
+        <v>-69.5</v>
       </c>
       <c r="C28">
-        <v>194.167</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>194.167</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46106.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B29">
-        <v>76.684</v>
+        <v>-108.336</v>
       </c>
       <c r="C29">
-        <v>261.647</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>261.647</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46106.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B30">
-        <v>52.619</v>
+        <v>-158.114</v>
       </c>
       <c r="C30">
-        <v>296.732</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>296.732</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46106.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B31">
-        <v>17.382</v>
+        <v>-123.423</v>
       </c>
       <c r="C31">
-        <v>1.349</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1.349</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46106.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B32">
-        <v>50.312</v>
+        <v>-190.236</v>
       </c>
       <c r="C32">
-        <v>12.971</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>12.971</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46106.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B33">
-        <v>63.912</v>
+        <v>-154.44</v>
       </c>
       <c r="C33">
-        <v>-23.081</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>-23.081</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46106.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B34">
-        <v>11.439</v>
+        <v>-126.181</v>
       </c>
       <c r="C34">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46106.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B35">
-        <v>-7.281</v>
+        <v>-97.858</v>
       </c>
       <c r="C35">
-        <v>889.244</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>889.244</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46106.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B36">
-        <v>-2.311</v>
+        <v>-32.419</v>
       </c>
       <c r="C36">
-        <v>667.29</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>667.29</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46106.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B37">
-        <v>13.14</v>
+        <v>54.001</v>
       </c>
       <c r="C37">
-        <v>19.097</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>19.097</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46106.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B38">
-        <v>33.75</v>
+        <v>132.782</v>
       </c>
       <c r="C38">
-        <v>17.503</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>17.503</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46106.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B39">
-        <v>65.041</v>
+        <v>155.584</v>
       </c>
       <c r="C39">
-        <v>11.771</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>11.771</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46106.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B40">
-        <v>75.465</v>
+        <v>167.5</v>
       </c>
       <c r="C40">
-        <v>-66.358</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>-66.358</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46106.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B41">
-        <v>112.059</v>
+        <v>108.979</v>
       </c>
       <c r="C41">
-        <v>-198.948</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>-198.948</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46106.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B42">
-        <v>83.452</v>
+        <v>57.096</v>
       </c>
       <c r="C42">
-        <v>-17.317</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>-17.317</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46106.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B43">
-        <v>82.88200000000001</v>
+        <v>52.794</v>
       </c>
       <c r="C43">
-        <v>-145.942</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>-145.942</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46106.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B44">
-        <v>90.07299999999999</v>
+        <v>54.061</v>
       </c>
       <c r="C44">
-        <v>0.631</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0.631</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46106.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B45">
-        <v>109.475</v>
+        <v>68.61799999999999</v>
       </c>
       <c r="C45">
-        <v>21.201</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>21.201</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46106.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B46">
-        <v>197.595</v>
+        <v>55.443</v>
       </c>
       <c r="C46">
-        <v>-98.145</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>-98.145</v>
+        <v>0</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46106.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B47">
-        <v>137.634</v>
+        <v>61.786</v>
       </c>
       <c r="C47">
-        <v>-99.843</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>-99.843</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46106.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B48">
-        <v>43.2</v>
+        <v>53.485</v>
       </c>
       <c r="C48">
-        <v>2.319</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>2.319</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46106.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B49">
-        <v>44.571</v>
+        <v>15.648</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46106.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B50">
-        <v>106.285</v>
+        <v>-39.515</v>
       </c>
       <c r="C50">
-        <v>-10.069</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>-10.069</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46106.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B51">
-        <v>100.267</v>
+        <v>-97.114</v>
       </c>
       <c r="C51">
-        <v>-0.608</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>-0.608</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46106.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B52">
-        <v>90.41200000000001</v>
+        <v>-72.82899999999999</v>
       </c>
       <c r="C52">
-        <v>7.077</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>7.077</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46106.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B53">
-        <v>87.752</v>
+        <v>-113.795</v>
       </c>
       <c r="C53">
-        <v>-622.215</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>-622.215</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46106.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B54">
-        <v>89.72199999999999</v>
+        <v>-75.748</v>
       </c>
       <c r="C54">
-        <v>-156.86</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>-156.86</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46106.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B55">
-        <v>88.685</v>
+        <v>-96.358</v>
       </c>
       <c r="C55">
-        <v>15.136</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>15.136</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46106.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B56">
-        <v>77.59399999999999</v>
+        <v>-42.602</v>
       </c>
       <c r="C56">
-        <v>-25.553</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>-25.553</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46106.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B57">
-        <v>79.893</v>
+        <v>-18.103</v>
       </c>
       <c r="C57">
-        <v>-84.7</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>-84.7</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46106.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B58">
-        <v>121.02</v>
+        <v>59.021</v>
       </c>
       <c r="C58">
-        <v>-1119.416</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>-1119.416</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46106.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B59">
-        <v>115.308</v>
+        <v>62.205</v>
       </c>
       <c r="C59">
-        <v>-45.12</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>-45.12</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46106.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B60">
-        <v>74.131</v>
+        <v>40.837</v>
       </c>
       <c r="C60">
-        <v>-24.504</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>-24.504</v>
+        <v>0</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46106.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B61">
-        <v>111.867</v>
+        <v>2.961</v>
       </c>
       <c r="C61">
-        <v>9.644</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>9.644</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46106.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B62">
-        <v>179.933</v>
+        <v>-11.201</v>
       </c>
       <c r="C62">
-        <v>-248.523</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>-248.523</v>
+        <v>0</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46106.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B63">
-        <v>143.347</v>
+        <v>-4.216</v>
       </c>
       <c r="C63">
-        <v>-156.815</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>-156.815</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46106.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B64">
-        <v>110.442</v>
+        <v>-12.716</v>
       </c>
       <c r="C64">
-        <v>-267.8</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>-267.8</v>
+        <v>0</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46106.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B65">
-        <v>85.992</v>
+        <v>-45.943</v>
       </c>
       <c r="C65">
-        <v>2.618</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>2.618</v>
+        <v>0</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46106.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B66">
-        <v>94.658</v>
+        <v>-16.302</v>
       </c>
       <c r="C66">
-        <v>2.635</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>2.635</v>
+        <v>0</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46106.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B67">
-        <v>58.7</v>
+        <v>-12.866</v>
       </c>
       <c r="C67">
-        <v>9.287000000000001</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>9.287000000000001</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46106.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B68">
-        <v>60.732</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>0.948</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0.948</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46106.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B69">
-        <v>39.908</v>
+        <v>0</v>
       </c>
       <c r="C69">
-        <v>16.464</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>16.464</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46106.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B70">
-        <v>69.35299999999999</v>
+        <v>0</v>
       </c>
       <c r="C70">
-        <v>50.142</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>50.142</v>
+        <v>0</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46106.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B71">
-        <v>68.889</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>65.864</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>65.864</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46106.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B72">
-        <v>77.38</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>122.929</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>122.929</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46106.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B73">
-        <v>53.208</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46106.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B74">
-        <v>27.884</v>
+        <v>0</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46106.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B75">
-        <v>19.576</v>
+        <v>0</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46106.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B76">
-        <v>17.903</v>
+        <v>0</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46106.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B77">
-        <v>18.134</v>
+        <v>0</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46106.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B78">
-        <v>20.448</v>
+        <v>0</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46106.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B79">
-        <v>16.187</v>
+        <v>0</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46106.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B80">
-        <v>39.744</v>
+        <v>0</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46106.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B81">
-        <v>70.384</v>
+        <v>0</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46106.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B82">
-        <v>37.867</v>
+        <v>0</v>
       </c>
       <c r="C82">
-        <v>493.074</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>493.074</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46106.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B83">
-        <v>35.359</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>496.407</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>496.407</v>
+        <v>0</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46106.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B84">
-        <v>36.848</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>51.862</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>51.862</v>
+        <v>0</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46106.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B85">
-        <v>51.509</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>78.006</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>78.006</v>
+        <v>0</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46106.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B86">
-        <v>4.602</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>188.341</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>188.341</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46106.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46106.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2734,7 +2734,7 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46106.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46106.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46106.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2794,7 +2794,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46106.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46106.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46106.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46106.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2874,7 +2874,7 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46106.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46106.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46107.01041666666</v>
+        <v>46108.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2954,7 +2954,7 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46107.02083333334</v>
+        <v>46108.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2974,7 +2974,7 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46107.03125</v>
+        <v>46108.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46107.04166666666</v>
+        <v>46108.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46107.05208333334</v>
+        <v>46108.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46107.0625</v>
+        <v>46108.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3054,7 +3054,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46107.07291666666</v>
+        <v>46108.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46107.08333333334</v>
+        <v>46108.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46107.09375</v>
+        <v>46108.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46107.10416666666</v>
+        <v>46108.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46107.11458333334</v>
+        <v>46108.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3154,7 +3154,7 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46107.125</v>
+        <v>46108.125</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46107.13541666666</v>
+        <v>46108.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46107.14583333334</v>
+        <v>46108.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3214,7 +3214,7 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46107.15625</v>
+        <v>46108.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46107.16666666666</v>
+        <v>46108.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46107.17708333334</v>
+        <v>46108.17708333334</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46107.1875</v>
+        <v>46108.1875</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46107.19791666666</v>
+        <v>46108.19791666666</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46107.20833333334</v>
+        <v>46108.20833333334</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46107.21875</v>
+        <v>46108.21875</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46107.22916666666</v>
+        <v>46108.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46107.23958333334</v>
+        <v>46108.23958333334</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46107.25</v>
+        <v>46108.25</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46107.26041666666</v>
+        <v>46108.26041666666</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46107.27083333334</v>
+        <v>46108.27083333334</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46107.28125</v>
+        <v>46108.28125</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46107.29166666666</v>
+        <v>46108.29166666666</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46107.30208333334</v>
+        <v>46108.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46107.3125</v>
+        <v>46108.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46107.32291666666</v>
+        <v>46108.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3554,7 +3554,7 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46107.33333333334</v>
+        <v>46108.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46107.34375</v>
+        <v>46108.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46107.35416666666</v>
+        <v>46108.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46107.36458333334</v>
+        <v>46108.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46107.375</v>
+        <v>46108.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46107.38541666666</v>
+        <v>46108.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46107.39583333334</v>
+        <v>46108.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46107.40625</v>
+        <v>46108.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46107.41666666666</v>
+        <v>46108.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46107.42708333334</v>
+        <v>46108.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46107.4375</v>
+        <v>46108.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46107.44791666666</v>
+        <v>46108.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46107.45833333334</v>
+        <v>46108.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46107.46875</v>
+        <v>46108.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46107.47916666666</v>
+        <v>46108.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46107.48958333334</v>
+        <v>46108.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46107.5</v>
+        <v>46108.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46107.51041666666</v>
+        <v>46108.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46107.52083333334</v>
+        <v>46108.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46107.53125</v>
+        <v>46108.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46107.54166666666</v>
+        <v>46108.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46107.55208333334</v>
+        <v>46108.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46107.5625</v>
+        <v>46108.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46107.57291666666</v>
+        <v>46108.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46107.58333333334</v>
+        <v>46108.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46107.59375</v>
+        <v>46108.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46107.60416666666</v>
+        <v>46108.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46107.61458333334</v>
+        <v>46108.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46107.625</v>
+        <v>46108.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46107.63541666666</v>
+        <v>46108.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46107.64583333334</v>
+        <v>46108.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46107.65625</v>
+        <v>46108.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46107.66666666666</v>
+        <v>46108.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46107.67708333334</v>
+        <v>46108.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46107.6875</v>
+        <v>46108.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46107.69791666666</v>
+        <v>46108.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46107.70833333334</v>
+        <v>46108.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46107.71875</v>
+        <v>46108.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46107.72916666666</v>
+        <v>46108.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46107.73958333334</v>
+        <v>46108.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46107.75</v>
+        <v>46108.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46107.76041666666</v>
+        <v>46108.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46107.77083333334</v>
+        <v>46108.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46107.78125</v>
+        <v>46108.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46107.79166666666</v>
+        <v>46108.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46107.80208333334</v>
+        <v>46108.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46107.8125</v>
+        <v>46108.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46107.82291666666</v>
+        <v>46108.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46107.83333333334</v>
+        <v>46108.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46107.84375</v>
+        <v>46108.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46107.85416666666</v>
+        <v>46108.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46107.86458333334</v>
+        <v>46108.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46107.875</v>
+        <v>46108.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46107.88541666666</v>
+        <v>46108.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46107.89583333334</v>
+        <v>46108.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46107.90625</v>
+        <v>46108.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46107.91666666666</v>
+        <v>46108.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46107.92708333334</v>
+        <v>46108.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46107.9375</v>
+        <v>46108.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46107.94791666666</v>
+        <v>46108.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46107.95833333334</v>
+        <v>46108.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46107.96875</v>
+        <v>46108.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46107.97916666666</v>
+        <v>46108.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46107.98958333334</v>
+        <v>46108.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.04.20261</t>
-  </si>
-  <si>
-    <t>09.04.20262</t>
-  </si>
-  <si>
-    <t>09.04.20263</t>
-  </si>
-  <si>
-    <t>09.04.20264</t>
-  </si>
-  <si>
-    <t>09.04.20265</t>
-  </si>
-  <si>
-    <t>09.04.20266</t>
-  </si>
-  <si>
-    <t>09.04.20267</t>
-  </si>
-  <si>
-    <t>09.04.20268</t>
-  </si>
-  <si>
-    <t>09.04.20269</t>
-  </si>
-  <si>
-    <t>09.04.202610</t>
-  </si>
-  <si>
-    <t>09.04.202611</t>
-  </si>
-  <si>
-    <t>09.04.202612</t>
-  </si>
-  <si>
-    <t>09.04.202613</t>
-  </si>
-  <si>
-    <t>09.04.202614</t>
-  </si>
-  <si>
-    <t>09.04.202615</t>
-  </si>
-  <si>
-    <t>09.04.202616</t>
-  </si>
-  <si>
-    <t>09.04.202617</t>
-  </si>
-  <si>
-    <t>09.04.202618</t>
-  </si>
-  <si>
-    <t>09.04.202619</t>
-  </si>
-  <si>
-    <t>09.04.202620</t>
-  </si>
-  <si>
-    <t>09.04.202621</t>
-  </si>
-  <si>
-    <t>09.04.202622</t>
-  </si>
-  <si>
-    <t>09.04.202623</t>
-  </si>
-  <si>
-    <t>09.04.202624</t>
-  </si>
-  <si>
-    <t>09.04.202625</t>
-  </si>
-  <si>
-    <t>09.04.202626</t>
-  </si>
-  <si>
-    <t>09.04.202627</t>
-  </si>
-  <si>
-    <t>09.04.202628</t>
-  </si>
-  <si>
-    <t>09.04.202629</t>
-  </si>
-  <si>
-    <t>09.04.202630</t>
-  </si>
-  <si>
-    <t>09.04.202631</t>
-  </si>
-  <si>
-    <t>09.04.202632</t>
-  </si>
-  <si>
-    <t>09.04.202633</t>
-  </si>
-  <si>
-    <t>09.04.202634</t>
-  </si>
-  <si>
-    <t>09.04.202635</t>
-  </si>
-  <si>
-    <t>09.04.202636</t>
-  </si>
-  <si>
-    <t>09.04.202637</t>
-  </si>
-  <si>
-    <t>09.04.202638</t>
-  </si>
-  <si>
-    <t>09.04.202639</t>
-  </si>
-  <si>
-    <t>09.04.202640</t>
-  </si>
-  <si>
-    <t>09.04.202641</t>
-  </si>
-  <si>
-    <t>09.04.202642</t>
-  </si>
-  <si>
-    <t>09.04.202643</t>
-  </si>
-  <si>
-    <t>09.04.202644</t>
-  </si>
-  <si>
-    <t>09.04.202645</t>
-  </si>
-  <si>
-    <t>09.04.202646</t>
-  </si>
-  <si>
-    <t>09.04.202647</t>
-  </si>
-  <si>
-    <t>09.04.202648</t>
-  </si>
-  <si>
-    <t>09.04.202649</t>
-  </si>
-  <si>
-    <t>09.04.202650</t>
-  </si>
-  <si>
-    <t>09.04.202651</t>
-  </si>
-  <si>
-    <t>09.04.202652</t>
-  </si>
-  <si>
-    <t>09.04.202653</t>
-  </si>
-  <si>
-    <t>09.04.202654</t>
-  </si>
-  <si>
-    <t>09.04.202655</t>
-  </si>
-  <si>
-    <t>09.04.202656</t>
-  </si>
-  <si>
-    <t>09.04.202657</t>
-  </si>
-  <si>
-    <t>09.04.202658</t>
-  </si>
-  <si>
-    <t>09.04.202659</t>
-  </si>
-  <si>
-    <t>09.04.202660</t>
-  </si>
-  <si>
-    <t>09.04.202661</t>
-  </si>
-  <si>
-    <t>09.04.202662</t>
-  </si>
-  <si>
-    <t>09.04.202663</t>
-  </si>
-  <si>
-    <t>09.04.202664</t>
-  </si>
-  <si>
-    <t>09.04.202665</t>
-  </si>
-  <si>
-    <t>09.04.202666</t>
-  </si>
-  <si>
-    <t>09.04.202667</t>
-  </si>
-  <si>
-    <t>09.04.202668</t>
-  </si>
-  <si>
-    <t>09.04.202669</t>
-  </si>
-  <si>
-    <t>09.04.202670</t>
-  </si>
-  <si>
-    <t>09.04.202671</t>
-  </si>
-  <si>
-    <t>09.04.202672</t>
-  </si>
-  <si>
-    <t>09.04.202673</t>
-  </si>
-  <si>
-    <t>09.04.202674</t>
-  </si>
-  <si>
-    <t>09.04.202675</t>
-  </si>
-  <si>
-    <t>09.04.202676</t>
-  </si>
-  <si>
-    <t>09.04.202677</t>
-  </si>
-  <si>
-    <t>09.04.202678</t>
-  </si>
-  <si>
-    <t>09.04.202679</t>
-  </si>
-  <si>
-    <t>09.04.202680</t>
-  </si>
-  <si>
-    <t>09.04.202681</t>
-  </si>
-  <si>
-    <t>09.04.202682</t>
-  </si>
-  <si>
-    <t>09.04.202683</t>
-  </si>
-  <si>
-    <t>09.04.202684</t>
-  </si>
-  <si>
-    <t>09.04.202685</t>
-  </si>
-  <si>
-    <t>09.04.202686</t>
-  </si>
-  <si>
-    <t>09.04.202687</t>
-  </si>
-  <si>
-    <t>09.04.202688</t>
-  </si>
-  <si>
-    <t>09.04.202689</t>
-  </si>
-  <si>
-    <t>09.04.202690</t>
-  </si>
-  <si>
-    <t>09.04.202691</t>
-  </si>
-  <si>
-    <t>09.04.202692</t>
-  </si>
-  <si>
-    <t>09.04.202693</t>
-  </si>
-  <si>
-    <t>09.04.202694</t>
-  </si>
-  <si>
-    <t>09.04.202695</t>
-  </si>
-  <si>
-    <t>09.04.202696</t>
-  </si>
-  <si>
-    <t>10.04.20261</t>
-  </si>
-  <si>
-    <t>10.04.20262</t>
-  </si>
-  <si>
-    <t>10.04.20263</t>
-  </si>
-  <si>
-    <t>10.04.20264</t>
-  </si>
-  <si>
-    <t>10.04.20265</t>
-  </si>
-  <si>
-    <t>10.04.20266</t>
-  </si>
-  <si>
-    <t>10.04.20267</t>
-  </si>
-  <si>
-    <t>10.04.20268</t>
-  </si>
-  <si>
-    <t>10.04.20269</t>
-  </si>
-  <si>
-    <t>10.04.202610</t>
-  </si>
-  <si>
-    <t>10.04.202611</t>
-  </si>
-  <si>
-    <t>10.04.202612</t>
-  </si>
-  <si>
-    <t>10.04.202613</t>
-  </si>
-  <si>
-    <t>10.04.202614</t>
-  </si>
-  <si>
-    <t>10.04.202615</t>
-  </si>
-  <si>
-    <t>10.04.202616</t>
-  </si>
-  <si>
-    <t>10.04.202617</t>
-  </si>
-  <si>
-    <t>10.04.202618</t>
-  </si>
-  <si>
-    <t>10.04.202619</t>
-  </si>
-  <si>
-    <t>10.04.202620</t>
-  </si>
-  <si>
-    <t>10.04.202621</t>
-  </si>
-  <si>
-    <t>10.04.202622</t>
-  </si>
-  <si>
-    <t>10.04.202623</t>
-  </si>
-  <si>
-    <t>10.04.202624</t>
-  </si>
-  <si>
-    <t>10.04.202625</t>
-  </si>
-  <si>
-    <t>10.04.202626</t>
-  </si>
-  <si>
-    <t>10.04.202627</t>
-  </si>
-  <si>
-    <t>10.04.202628</t>
-  </si>
-  <si>
-    <t>10.04.202629</t>
-  </si>
-  <si>
-    <t>10.04.202630</t>
-  </si>
-  <si>
-    <t>10.04.202631</t>
-  </si>
-  <si>
-    <t>10.04.202632</t>
-  </si>
-  <si>
-    <t>10.04.202633</t>
-  </si>
-  <si>
-    <t>10.04.202634</t>
-  </si>
-  <si>
-    <t>10.04.202635</t>
-  </si>
-  <si>
-    <t>10.04.202636</t>
-  </si>
-  <si>
-    <t>10.04.202637</t>
-  </si>
-  <si>
-    <t>10.04.202638</t>
-  </si>
-  <si>
-    <t>10.04.202639</t>
-  </si>
-  <si>
-    <t>10.04.202640</t>
-  </si>
-  <si>
-    <t>10.04.202641</t>
-  </si>
-  <si>
-    <t>10.04.202642</t>
-  </si>
-  <si>
-    <t>10.04.202643</t>
-  </si>
-  <si>
-    <t>10.04.202644</t>
-  </si>
-  <si>
-    <t>10.04.202645</t>
-  </si>
-  <si>
-    <t>10.04.202646</t>
-  </si>
-  <si>
-    <t>10.04.202647</t>
-  </si>
-  <si>
-    <t>10.04.202648</t>
-  </si>
-  <si>
-    <t>10.04.202649</t>
-  </si>
-  <si>
-    <t>10.04.202650</t>
-  </si>
-  <si>
-    <t>10.04.202651</t>
-  </si>
-  <si>
-    <t>10.04.202652</t>
-  </si>
-  <si>
-    <t>10.04.202653</t>
-  </si>
-  <si>
-    <t>10.04.202654</t>
-  </si>
-  <si>
-    <t>10.04.202655</t>
-  </si>
-  <si>
-    <t>10.04.202656</t>
-  </si>
-  <si>
-    <t>10.04.202657</t>
-  </si>
-  <si>
-    <t>10.04.202658</t>
-  </si>
-  <si>
-    <t>10.04.202659</t>
-  </si>
-  <si>
-    <t>10.04.202660</t>
-  </si>
-  <si>
-    <t>10.04.202661</t>
-  </si>
-  <si>
-    <t>10.04.202662</t>
-  </si>
-  <si>
-    <t>10.04.202663</t>
-  </si>
-  <si>
-    <t>10.04.202664</t>
-  </si>
-  <si>
-    <t>10.04.202665</t>
-  </si>
-  <si>
-    <t>10.04.202666</t>
-  </si>
-  <si>
-    <t>10.04.202667</t>
-  </si>
-  <si>
-    <t>10.04.202668</t>
-  </si>
-  <si>
-    <t>10.04.202669</t>
-  </si>
-  <si>
-    <t>10.04.202670</t>
-  </si>
-  <si>
-    <t>10.04.202671</t>
-  </si>
-  <si>
-    <t>10.04.202672</t>
-  </si>
-  <si>
-    <t>10.04.202673</t>
-  </si>
-  <si>
-    <t>10.04.202674</t>
-  </si>
-  <si>
-    <t>10.04.202675</t>
-  </si>
-  <si>
-    <t>10.04.202676</t>
-  </si>
-  <si>
-    <t>10.04.202677</t>
-  </si>
-  <si>
-    <t>10.04.202678</t>
-  </si>
-  <si>
-    <t>10.04.202679</t>
-  </si>
-  <si>
-    <t>10.04.202680</t>
-  </si>
-  <si>
-    <t>10.04.202681</t>
-  </si>
-  <si>
-    <t>10.04.202682</t>
-  </si>
-  <si>
-    <t>10.04.202683</t>
-  </si>
-  <si>
-    <t>10.04.202684</t>
-  </si>
-  <si>
-    <t>10.04.202685</t>
-  </si>
-  <si>
-    <t>10.04.202686</t>
-  </si>
-  <si>
-    <t>10.04.202687</t>
-  </si>
-  <si>
-    <t>10.04.202688</t>
-  </si>
-  <si>
-    <t>10.04.202689</t>
-  </si>
-  <si>
-    <t>10.04.202690</t>
-  </si>
-  <si>
-    <t>10.04.202691</t>
-  </si>
-  <si>
-    <t>10.04.202692</t>
-  </si>
-  <si>
-    <t>10.04.202693</t>
-  </si>
-  <si>
-    <t>10.04.202694</t>
-  </si>
-  <si>
-    <t>10.04.202695</t>
-  </si>
-  <si>
-    <t>10.04.202696</t>
+    <t>16.04.20261</t>
+  </si>
+  <si>
+    <t>16.04.20262</t>
+  </si>
+  <si>
+    <t>16.04.20263</t>
+  </si>
+  <si>
+    <t>16.04.20264</t>
+  </si>
+  <si>
+    <t>16.04.20265</t>
+  </si>
+  <si>
+    <t>16.04.20266</t>
+  </si>
+  <si>
+    <t>16.04.20267</t>
+  </si>
+  <si>
+    <t>16.04.20268</t>
+  </si>
+  <si>
+    <t>16.04.20269</t>
+  </si>
+  <si>
+    <t>16.04.202610</t>
+  </si>
+  <si>
+    <t>16.04.202611</t>
+  </si>
+  <si>
+    <t>16.04.202612</t>
+  </si>
+  <si>
+    <t>16.04.202613</t>
+  </si>
+  <si>
+    <t>16.04.202614</t>
+  </si>
+  <si>
+    <t>16.04.202615</t>
+  </si>
+  <si>
+    <t>16.04.202616</t>
+  </si>
+  <si>
+    <t>16.04.202617</t>
+  </si>
+  <si>
+    <t>16.04.202618</t>
+  </si>
+  <si>
+    <t>16.04.202619</t>
+  </si>
+  <si>
+    <t>16.04.202620</t>
+  </si>
+  <si>
+    <t>16.04.202621</t>
+  </si>
+  <si>
+    <t>16.04.202622</t>
+  </si>
+  <si>
+    <t>16.04.202623</t>
+  </si>
+  <si>
+    <t>16.04.202624</t>
+  </si>
+  <si>
+    <t>16.04.202625</t>
+  </si>
+  <si>
+    <t>16.04.202626</t>
+  </si>
+  <si>
+    <t>16.04.202627</t>
+  </si>
+  <si>
+    <t>16.04.202628</t>
+  </si>
+  <si>
+    <t>16.04.202629</t>
+  </si>
+  <si>
+    <t>16.04.202630</t>
+  </si>
+  <si>
+    <t>16.04.202631</t>
+  </si>
+  <si>
+    <t>16.04.202632</t>
+  </si>
+  <si>
+    <t>16.04.202633</t>
+  </si>
+  <si>
+    <t>16.04.202634</t>
+  </si>
+  <si>
+    <t>16.04.202635</t>
+  </si>
+  <si>
+    <t>16.04.202636</t>
+  </si>
+  <si>
+    <t>16.04.202637</t>
+  </si>
+  <si>
+    <t>16.04.202638</t>
+  </si>
+  <si>
+    <t>16.04.202639</t>
+  </si>
+  <si>
+    <t>16.04.202640</t>
+  </si>
+  <si>
+    <t>16.04.202641</t>
+  </si>
+  <si>
+    <t>16.04.202642</t>
+  </si>
+  <si>
+    <t>16.04.202643</t>
+  </si>
+  <si>
+    <t>16.04.202644</t>
+  </si>
+  <si>
+    <t>16.04.202645</t>
+  </si>
+  <si>
+    <t>16.04.202646</t>
+  </si>
+  <si>
+    <t>16.04.202647</t>
+  </si>
+  <si>
+    <t>16.04.202648</t>
+  </si>
+  <si>
+    <t>16.04.202649</t>
+  </si>
+  <si>
+    <t>16.04.202650</t>
+  </si>
+  <si>
+    <t>16.04.202651</t>
+  </si>
+  <si>
+    <t>16.04.202652</t>
+  </si>
+  <si>
+    <t>16.04.202653</t>
+  </si>
+  <si>
+    <t>16.04.202654</t>
+  </si>
+  <si>
+    <t>16.04.202655</t>
+  </si>
+  <si>
+    <t>16.04.202656</t>
+  </si>
+  <si>
+    <t>16.04.202657</t>
+  </si>
+  <si>
+    <t>16.04.202658</t>
+  </si>
+  <si>
+    <t>16.04.202659</t>
+  </si>
+  <si>
+    <t>16.04.202660</t>
+  </si>
+  <si>
+    <t>16.04.202661</t>
+  </si>
+  <si>
+    <t>16.04.202662</t>
+  </si>
+  <si>
+    <t>16.04.202663</t>
+  </si>
+  <si>
+    <t>16.04.202664</t>
+  </si>
+  <si>
+    <t>16.04.202665</t>
+  </si>
+  <si>
+    <t>16.04.202666</t>
+  </si>
+  <si>
+    <t>16.04.202667</t>
+  </si>
+  <si>
+    <t>16.04.202668</t>
+  </si>
+  <si>
+    <t>16.04.202669</t>
+  </si>
+  <si>
+    <t>16.04.202670</t>
+  </si>
+  <si>
+    <t>16.04.202671</t>
+  </si>
+  <si>
+    <t>16.04.202672</t>
+  </si>
+  <si>
+    <t>16.04.202673</t>
+  </si>
+  <si>
+    <t>16.04.202674</t>
+  </si>
+  <si>
+    <t>16.04.202675</t>
+  </si>
+  <si>
+    <t>16.04.202676</t>
+  </si>
+  <si>
+    <t>16.04.202677</t>
+  </si>
+  <si>
+    <t>16.04.202678</t>
+  </si>
+  <si>
+    <t>16.04.202679</t>
+  </si>
+  <si>
+    <t>16.04.202680</t>
+  </si>
+  <si>
+    <t>16.04.202681</t>
+  </si>
+  <si>
+    <t>16.04.202682</t>
+  </si>
+  <si>
+    <t>16.04.202683</t>
+  </si>
+  <si>
+    <t>16.04.202684</t>
+  </si>
+  <si>
+    <t>16.04.202685</t>
+  </si>
+  <si>
+    <t>16.04.202686</t>
+  </si>
+  <si>
+    <t>16.04.202687</t>
+  </si>
+  <si>
+    <t>16.04.202688</t>
+  </si>
+  <si>
+    <t>16.04.202689</t>
+  </si>
+  <si>
+    <t>16.04.202690</t>
+  </si>
+  <si>
+    <t>16.04.202691</t>
+  </si>
+  <si>
+    <t>16.04.202692</t>
+  </si>
+  <si>
+    <t>16.04.202693</t>
+  </si>
+  <si>
+    <t>16.04.202694</t>
+  </si>
+  <si>
+    <t>16.04.202695</t>
+  </si>
+  <si>
+    <t>16.04.202696</t>
+  </si>
+  <si>
+    <t>17.04.20261</t>
+  </si>
+  <si>
+    <t>17.04.20262</t>
+  </si>
+  <si>
+    <t>17.04.20263</t>
+  </si>
+  <si>
+    <t>17.04.20264</t>
+  </si>
+  <si>
+    <t>17.04.20265</t>
+  </si>
+  <si>
+    <t>17.04.20266</t>
+  </si>
+  <si>
+    <t>17.04.20267</t>
+  </si>
+  <si>
+    <t>17.04.20268</t>
+  </si>
+  <si>
+    <t>17.04.20269</t>
+  </si>
+  <si>
+    <t>17.04.202610</t>
+  </si>
+  <si>
+    <t>17.04.202611</t>
+  </si>
+  <si>
+    <t>17.04.202612</t>
+  </si>
+  <si>
+    <t>17.04.202613</t>
+  </si>
+  <si>
+    <t>17.04.202614</t>
+  </si>
+  <si>
+    <t>17.04.202615</t>
+  </si>
+  <si>
+    <t>17.04.202616</t>
+  </si>
+  <si>
+    <t>17.04.202617</t>
+  </si>
+  <si>
+    <t>17.04.202618</t>
+  </si>
+  <si>
+    <t>17.04.202619</t>
+  </si>
+  <si>
+    <t>17.04.202620</t>
+  </si>
+  <si>
+    <t>17.04.202621</t>
+  </si>
+  <si>
+    <t>17.04.202622</t>
+  </si>
+  <si>
+    <t>17.04.202623</t>
+  </si>
+  <si>
+    <t>17.04.202624</t>
+  </si>
+  <si>
+    <t>17.04.202625</t>
+  </si>
+  <si>
+    <t>17.04.202626</t>
+  </si>
+  <si>
+    <t>17.04.202627</t>
+  </si>
+  <si>
+    <t>17.04.202628</t>
+  </si>
+  <si>
+    <t>17.04.202629</t>
+  </si>
+  <si>
+    <t>17.04.202630</t>
+  </si>
+  <si>
+    <t>17.04.202631</t>
+  </si>
+  <si>
+    <t>17.04.202632</t>
+  </si>
+  <si>
+    <t>17.04.202633</t>
+  </si>
+  <si>
+    <t>17.04.202634</t>
+  </si>
+  <si>
+    <t>17.04.202635</t>
+  </si>
+  <si>
+    <t>17.04.202636</t>
+  </si>
+  <si>
+    <t>17.04.202637</t>
+  </si>
+  <si>
+    <t>17.04.202638</t>
+  </si>
+  <si>
+    <t>17.04.202639</t>
+  </si>
+  <si>
+    <t>17.04.202640</t>
+  </si>
+  <si>
+    <t>17.04.202641</t>
+  </si>
+  <si>
+    <t>17.04.202642</t>
+  </si>
+  <si>
+    <t>17.04.202643</t>
+  </si>
+  <si>
+    <t>17.04.202644</t>
+  </si>
+  <si>
+    <t>17.04.202645</t>
+  </si>
+  <si>
+    <t>17.04.202646</t>
+  </si>
+  <si>
+    <t>17.04.202647</t>
+  </si>
+  <si>
+    <t>17.04.202648</t>
+  </si>
+  <si>
+    <t>17.04.202649</t>
+  </si>
+  <si>
+    <t>17.04.202650</t>
+  </si>
+  <si>
+    <t>17.04.202651</t>
+  </si>
+  <si>
+    <t>17.04.202652</t>
+  </si>
+  <si>
+    <t>17.04.202653</t>
+  </si>
+  <si>
+    <t>17.04.202654</t>
+  </si>
+  <si>
+    <t>17.04.202655</t>
+  </si>
+  <si>
+    <t>17.04.202656</t>
+  </si>
+  <si>
+    <t>17.04.202657</t>
+  </si>
+  <si>
+    <t>17.04.202658</t>
+  </si>
+  <si>
+    <t>17.04.202659</t>
+  </si>
+  <si>
+    <t>17.04.202660</t>
+  </si>
+  <si>
+    <t>17.04.202661</t>
+  </si>
+  <si>
+    <t>17.04.202662</t>
+  </si>
+  <si>
+    <t>17.04.202663</t>
+  </si>
+  <si>
+    <t>17.04.202664</t>
+  </si>
+  <si>
+    <t>17.04.202665</t>
+  </si>
+  <si>
+    <t>17.04.202666</t>
+  </si>
+  <si>
+    <t>17.04.202667</t>
+  </si>
+  <si>
+    <t>17.04.202668</t>
+  </si>
+  <si>
+    <t>17.04.202669</t>
+  </si>
+  <si>
+    <t>17.04.202670</t>
+  </si>
+  <si>
+    <t>17.04.202671</t>
+  </si>
+  <si>
+    <t>17.04.202672</t>
+  </si>
+  <si>
+    <t>17.04.202673</t>
+  </si>
+  <si>
+    <t>17.04.202674</t>
+  </si>
+  <si>
+    <t>17.04.202675</t>
+  </si>
+  <si>
+    <t>17.04.202676</t>
+  </si>
+  <si>
+    <t>17.04.202677</t>
+  </si>
+  <si>
+    <t>17.04.202678</t>
+  </si>
+  <si>
+    <t>17.04.202679</t>
+  </si>
+  <si>
+    <t>17.04.202680</t>
+  </si>
+  <si>
+    <t>17.04.202681</t>
+  </si>
+  <si>
+    <t>17.04.202682</t>
+  </si>
+  <si>
+    <t>17.04.202683</t>
+  </si>
+  <si>
+    <t>17.04.202684</t>
+  </si>
+  <si>
+    <t>17.04.202685</t>
+  </si>
+  <si>
+    <t>17.04.202686</t>
+  </si>
+  <si>
+    <t>17.04.202687</t>
+  </si>
+  <si>
+    <t>17.04.202688</t>
+  </si>
+  <si>
+    <t>17.04.202689</t>
+  </si>
+  <si>
+    <t>17.04.202690</t>
+  </si>
+  <si>
+    <t>17.04.202691</t>
+  </si>
+  <si>
+    <t>17.04.202692</t>
+  </si>
+  <si>
+    <t>17.04.202693</t>
+  </si>
+  <si>
+    <t>17.04.202694</t>
+  </si>
+  <si>
+    <t>17.04.202695</t>
+  </si>
+  <si>
+    <t>17.04.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46121.01041666666</v>
+        <v>46128.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46121.02083333334</v>
+        <v>46128.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46121.03125</v>
+        <v>46128.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46121.04166666666</v>
+        <v>46128.04166666666</v>
       </c>
       <c r="B6">
-        <v>66.71299999999999</v>
+        <v>39.864</v>
       </c>
       <c r="C6">
-        <v>139.683</v>
+        <v>-355.79</v>
       </c>
       <c r="D6">
-        <v>139.683</v>
+        <v>-355.79</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46121.05208333334</v>
+        <v>46128.05208333334</v>
       </c>
       <c r="B7">
-        <v>26.02</v>
+        <v>27.898</v>
       </c>
       <c r="C7">
-        <v>251</v>
+        <v>-41.227</v>
       </c>
       <c r="D7">
-        <v>251</v>
+        <v>-41.227</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46121.0625</v>
+        <v>46128.0625</v>
       </c>
       <c r="B8">
-        <v>29.858</v>
+        <v>49.083</v>
       </c>
       <c r="C8">
-        <v>185.128</v>
+        <v>-270.44</v>
       </c>
       <c r="D8">
-        <v>185.128</v>
+        <v>-270.44</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46121.07291666666</v>
+        <v>46128.07291666666</v>
       </c>
       <c r="B9">
-        <v>9.622999999999999</v>
+        <v>23.841</v>
       </c>
       <c r="C9">
-        <v>263.308</v>
+        <v>-230.508</v>
       </c>
       <c r="D9">
-        <v>263.308</v>
+        <v>-230.508</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46121.08333333334</v>
+        <v>46128.08333333334</v>
       </c>
       <c r="B10">
-        <v>-23.758</v>
+        <v>25.198</v>
       </c>
       <c r="C10">
-        <v>896.657</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>896.657</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46121.09375</v>
+        <v>46128.09375</v>
       </c>
       <c r="B11">
-        <v>-21.853</v>
+        <v>18.183</v>
       </c>
       <c r="C11">
-        <v>898.298</v>
+        <v>28.597</v>
       </c>
       <c r="D11">
-        <v>898.298</v>
+        <v>28.597</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46121.10416666666</v>
+        <v>46128.10416666666</v>
       </c>
       <c r="B12">
-        <v>-13.825</v>
+        <v>32.962</v>
       </c>
       <c r="C12">
-        <v>911.944</v>
+        <v>-61.647</v>
       </c>
       <c r="D12">
-        <v>911.944</v>
+        <v>-61.647</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46121.11458333334</v>
+        <v>46128.11458333334</v>
       </c>
       <c r="B13">
-        <v>-8.167999999999999</v>
+        <v>19.617</v>
       </c>
       <c r="C13">
-        <v>897.763</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>897.763</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46121.125</v>
+        <v>46128.125</v>
       </c>
       <c r="B14">
-        <v>17.44</v>
+        <v>21.431</v>
       </c>
       <c r="C14">
-        <v>147.724</v>
+        <v>-2.018</v>
       </c>
       <c r="D14">
-        <v>147.724</v>
+        <v>-2.018</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46121.13541666666</v>
+        <v>46128.13541666666</v>
       </c>
       <c r="B15">
-        <v>6.501</v>
+        <v>8.673</v>
       </c>
       <c r="C15">
-        <v>288.054</v>
+        <v>143.147</v>
       </c>
       <c r="D15">
-        <v>288.054</v>
+        <v>143.147</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46121.14583333334</v>
+        <v>46128.14583333334</v>
       </c>
       <c r="B16">
-        <v>12.187</v>
+        <v>18.244</v>
       </c>
       <c r="C16">
-        <v>283.757</v>
+        <v>21.838</v>
       </c>
       <c r="D16">
-        <v>283.757</v>
+        <v>21.838</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46121.15625</v>
+        <v>46128.15625</v>
       </c>
       <c r="B17">
-        <v>29.075</v>
+        <v>6.008</v>
       </c>
       <c r="C17">
-        <v>9.093999999999999</v>
+        <v>123.427</v>
       </c>
       <c r="D17">
-        <v>9.093999999999999</v>
+        <v>123.427</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46121.16666666666</v>
+        <v>46128.16666666666</v>
       </c>
       <c r="B18">
-        <v>46.533</v>
+        <v>5.97</v>
       </c>
       <c r="C18">
-        <v>5.456</v>
+        <v>99.179</v>
       </c>
       <c r="D18">
-        <v>5.456</v>
+        <v>99.179</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46121.17708333334</v>
+        <v>46128.17708333334</v>
       </c>
       <c r="B19">
-        <v>27.698</v>
+        <v>4.901</v>
       </c>
       <c r="C19">
-        <v>0.1</v>
+        <v>127.864</v>
       </c>
       <c r="D19">
-        <v>0.1</v>
+        <v>127.864</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46121.1875</v>
+        <v>46128.1875</v>
       </c>
       <c r="B20">
-        <v>41.323</v>
+        <v>21.227</v>
       </c>
       <c r="C20">
-        <v>56.767</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>56.767</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46121.19791666666</v>
+        <v>46128.19791666666</v>
       </c>
       <c r="B21">
-        <v>71.754</v>
+        <v>11.323</v>
       </c>
       <c r="C21">
-        <v>174.445</v>
+        <v>52.319</v>
       </c>
       <c r="D21">
-        <v>174.445</v>
+        <v>52.319</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46121.20833333334</v>
+        <v>46128.20833333334</v>
       </c>
       <c r="B22">
-        <v>77.291</v>
+        <v>21.133</v>
       </c>
       <c r="C22">
-        <v>221.816</v>
+        <v>16.139</v>
       </c>
       <c r="D22">
-        <v>221.816</v>
+        <v>16.139</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46121.21875</v>
+        <v>46128.21875</v>
       </c>
       <c r="B23">
-        <v>83.11799999999999</v>
+        <v>-4.357</v>
       </c>
       <c r="C23">
-        <v>19.763</v>
+        <v>800</v>
       </c>
       <c r="D23">
-        <v>19.763</v>
+        <v>800</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46121.22916666666</v>
+        <v>46128.22916666666</v>
       </c>
       <c r="B24">
-        <v>60.325</v>
+        <v>12.604</v>
       </c>
       <c r="C24">
-        <v>-107.028</v>
+        <v>260.777</v>
       </c>
       <c r="D24">
-        <v>-107.028</v>
+        <v>260.777</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46121.23958333334</v>
+        <v>46128.23958333334</v>
       </c>
       <c r="B25">
-        <v>52.397</v>
+        <v>8.949</v>
       </c>
       <c r="C25">
-        <v>-251.481</v>
+        <v>55.855</v>
       </c>
       <c r="D25">
-        <v>-251.481</v>
+        <v>55.855</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46121.25</v>
+        <v>46128.25</v>
       </c>
       <c r="B26">
-        <v>72.431</v>
+        <v>40.67</v>
       </c>
       <c r="C26">
-        <v>-3669.11</v>
+        <v>107.57</v>
       </c>
       <c r="D26">
-        <v>-3669.11</v>
+        <v>107.57</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46121.26041666666</v>
+        <v>46128.26041666666</v>
       </c>
       <c r="B27">
-        <v>71.792</v>
+        <v>29.402</v>
       </c>
       <c r="C27">
-        <v>341.884</v>
+        <v>260.141</v>
       </c>
       <c r="D27">
-        <v>341.884</v>
+        <v>260.141</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46121.27083333334</v>
+        <v>46128.27083333334</v>
       </c>
       <c r="B28">
-        <v>40.419</v>
+        <v>28.183</v>
       </c>
       <c r="C28">
-        <v>334.291</v>
+        <v>-194.492</v>
       </c>
       <c r="D28">
-        <v>334.291</v>
+        <v>-194.492</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46121.28125</v>
+        <v>46128.28125</v>
       </c>
       <c r="B29">
-        <v>11.194</v>
+        <v>44.817</v>
       </c>
       <c r="C29">
-        <v>254.575</v>
+        <v>-1204.343</v>
       </c>
       <c r="D29">
-        <v>254.575</v>
+        <v>-1204.343</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46121.29166666666</v>
+        <v>46128.29166666666</v>
       </c>
       <c r="B30">
-        <v>-17.658</v>
+        <v>87.47799999999999</v>
       </c>
       <c r="C30">
-        <v>1717.489</v>
+        <v>-835.7910000000001</v>
       </c>
       <c r="D30">
-        <v>1717.489</v>
+        <v>-835.7910000000001</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46121.30208333334</v>
+        <v>46128.30208333334</v>
       </c>
       <c r="B31">
-        <v>-5.029</v>
+        <v>80.97499999999999</v>
       </c>
       <c r="C31">
-        <v>1473.624</v>
+        <v>19.815</v>
       </c>
       <c r="D31">
-        <v>1473.624</v>
+        <v>19.815</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46121.3125</v>
+        <v>46128.3125</v>
       </c>
       <c r="B32">
-        <v>2.808</v>
+        <v>31.446</v>
       </c>
       <c r="C32">
-        <v>400</v>
+        <v>21.812</v>
       </c>
       <c r="D32">
-        <v>400</v>
+        <v>21.812</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46121.32291666666</v>
+        <v>46128.32291666666</v>
       </c>
       <c r="B33">
-        <v>20.702</v>
+        <v>53.329</v>
       </c>
       <c r="C33">
-        <v>-7.634</v>
+        <v>15.851</v>
       </c>
       <c r="D33">
-        <v>-7.634</v>
+        <v>15.851</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46121.33333333334</v>
+        <v>46128.33333333334</v>
       </c>
       <c r="B34">
-        <v>52.441</v>
+        <v>1.148</v>
       </c>
       <c r="C34">
-        <v>-139.192</v>
+        <v>1.873</v>
       </c>
       <c r="D34">
-        <v>-139.192</v>
+        <v>1.873</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46121.34375</v>
+        <v>46128.34375</v>
       </c>
       <c r="B35">
-        <v>76.736</v>
+        <v>2.821</v>
       </c>
       <c r="C35">
-        <v>-1174.291</v>
+        <v>0.75</v>
       </c>
       <c r="D35">
-        <v>-1174.291</v>
+        <v>0.75</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46121.35416666666</v>
+        <v>46128.35416666666</v>
       </c>
       <c r="B36">
-        <v>80.977</v>
+        <v>20.196</v>
       </c>
       <c r="C36">
-        <v>-4545.987</v>
+        <v>0.416</v>
       </c>
       <c r="D36">
-        <v>-4545.987</v>
+        <v>0.416</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46121.36458333334</v>
+        <v>46128.36458333334</v>
       </c>
       <c r="B37">
-        <v>75.126</v>
+        <v>56.256</v>
       </c>
       <c r="C37">
-        <v>-3218.287</v>
+        <v>12.835</v>
       </c>
       <c r="D37">
-        <v>-3218.287</v>
+        <v>12.835</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46121.375</v>
+        <v>46128.375</v>
       </c>
       <c r="B38">
-        <v>102.385</v>
+        <v>50.726</v>
       </c>
       <c r="C38">
-        <v>-1609.921</v>
+        <v>9.959</v>
       </c>
       <c r="D38">
-        <v>-1609.921</v>
+        <v>9.959</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46121.38541666666</v>
+        <v>46128.38541666666</v>
       </c>
       <c r="B39">
-        <v>60.969</v>
+        <v>58.042</v>
       </c>
       <c r="C39">
-        <v>-72.178</v>
+        <v>10.991</v>
       </c>
       <c r="D39">
-        <v>-72.178</v>
+        <v>10.991</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46121.39583333334</v>
+        <v>46128.39583333334</v>
       </c>
       <c r="B40">
-        <v>40.226</v>
+        <v>80.90900000000001</v>
       </c>
       <c r="C40">
-        <v>6.937</v>
+        <v>-4.674</v>
       </c>
       <c r="D40">
-        <v>6.937</v>
+        <v>-4.674</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46121.40625</v>
+        <v>46128.40625</v>
       </c>
       <c r="B41">
-        <v>24.271</v>
+        <v>97.53700000000001</v>
       </c>
       <c r="C41">
-        <v>-1.084</v>
+        <v>-330.36</v>
       </c>
       <c r="D41">
-        <v>-1.084</v>
+        <v>-330.36</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46121.41666666666</v>
+        <v>46128.41666666666</v>
       </c>
       <c r="B42">
-        <v>-52.707</v>
+        <v>74.474</v>
       </c>
       <c r="C42">
-        <v>336.417</v>
+        <v>-22.219</v>
       </c>
       <c r="D42">
-        <v>336.417</v>
+        <v>-22.219</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46121.42708333334</v>
+        <v>46128.42708333334</v>
       </c>
       <c r="B43">
-        <v>-109.416</v>
+        <v>100.254</v>
       </c>
       <c r="C43">
-        <v>285.827</v>
+        <v>3.089</v>
       </c>
       <c r="D43">
-        <v>285.827</v>
+        <v>3.089</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46121.4375</v>
+        <v>46128.4375</v>
       </c>
       <c r="B44">
-        <v>-66.64</v>
+        <v>122.602</v>
       </c>
       <c r="C44">
-        <v>100</v>
+        <v>-68.73999999999999</v>
       </c>
       <c r="D44">
-        <v>100</v>
+        <v>-68.73999999999999</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46121.44791666666</v>
+        <v>46128.44791666666</v>
       </c>
       <c r="B45">
-        <v>1.713</v>
+        <v>108.861</v>
       </c>
       <c r="C45">
-        <v>-1608.556</v>
+        <v>-570.803</v>
       </c>
       <c r="D45">
-        <v>-1608.556</v>
+        <v>-570.803</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46121.45833333334</v>
+        <v>46128.45833333334</v>
       </c>
       <c r="B46">
-        <v>-36.935</v>
+        <v>144.355</v>
       </c>
       <c r="C46">
-        <v>456.37</v>
+        <v>-481.625</v>
       </c>
       <c r="D46">
-        <v>456.37</v>
+        <v>-481.625</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46121.46875</v>
+        <v>46128.46875</v>
       </c>
       <c r="B47">
-        <v>-37.796</v>
+        <v>123.098</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>-43.029</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>-43.029</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46121.47916666666</v>
+        <v>46128.47916666666</v>
       </c>
       <c r="B48">
-        <v>74.571</v>
+        <v>125.364</v>
       </c>
       <c r="C48">
-        <v>-278.797</v>
+        <v>-2.448</v>
       </c>
       <c r="D48">
-        <v>-278.797</v>
+        <v>-2.448</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46121.48958333334</v>
+        <v>46128.48958333334</v>
       </c>
       <c r="B49">
-        <v>-20.302</v>
+        <v>110.943</v>
       </c>
       <c r="C49">
-        <v>1066.726</v>
+        <v>7.148</v>
       </c>
       <c r="D49">
-        <v>1066.726</v>
+        <v>7.148</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46121.5</v>
+        <v>46128.5</v>
       </c>
       <c r="B50">
-        <v>3.627</v>
+        <v>67.20099999999999</v>
       </c>
       <c r="C50">
-        <v>812.628</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D50">
-        <v>812.628</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46121.51041666666</v>
+        <v>46128.51041666666</v>
       </c>
       <c r="B51">
-        <v>19.253</v>
+        <v>50.13</v>
       </c>
       <c r="C51">
-        <v>70.462</v>
+        <v>0.053</v>
       </c>
       <c r="D51">
-        <v>70.462</v>
+        <v>0.053</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46121.52083333334</v>
+        <v>46128.52083333334</v>
       </c>
       <c r="B52">
-        <v>45.149</v>
+        <v>172.656</v>
       </c>
       <c r="C52">
-        <v>231.876</v>
+        <v>5.169</v>
       </c>
       <c r="D52">
-        <v>231.876</v>
+        <v>5.169</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46121.53125</v>
+        <v>46128.53125</v>
       </c>
       <c r="B53">
-        <v>18.967</v>
+        <v>188.477</v>
       </c>
       <c r="C53">
-        <v>348.245</v>
+        <v>4.435</v>
       </c>
       <c r="D53">
-        <v>348.245</v>
+        <v>4.435</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46121.54166666666</v>
+        <v>46128.54166666666</v>
       </c>
       <c r="B54">
-        <v>75.363</v>
+        <v>112.648</v>
       </c>
       <c r="C54">
-        <v>337.962</v>
+        <v>0.372</v>
       </c>
       <c r="D54">
-        <v>337.962</v>
+        <v>0.372</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46121.55208333334</v>
+        <v>46128.55208333334</v>
       </c>
       <c r="B55">
-        <v>160.128</v>
+        <v>89.149</v>
       </c>
       <c r="C55">
-        <v>312.492</v>
+        <v>1.31</v>
       </c>
       <c r="D55">
-        <v>312.492</v>
+        <v>1.31</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46121.5625</v>
+        <v>46128.5625</v>
       </c>
       <c r="B56">
-        <v>166.833</v>
+        <v>53.56</v>
       </c>
       <c r="C56">
-        <v>-36.788</v>
+        <v>5.689</v>
       </c>
       <c r="D56">
-        <v>-36.788</v>
+        <v>5.689</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46121.57291666666</v>
+        <v>46128.57291666666</v>
       </c>
       <c r="B57">
-        <v>41.744</v>
+        <v>40.543</v>
       </c>
       <c r="C57">
-        <v>4.25</v>
+        <v>0.38</v>
       </c>
       <c r="D57">
-        <v>4.25</v>
+        <v>0.38</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46121.58333333334</v>
+        <v>46128.58333333334</v>
       </c>
       <c r="B58">
-        <v>-66.072</v>
+        <v>37.902</v>
       </c>
       <c r="C58">
-        <v>450.99</v>
+        <v>0.592</v>
       </c>
       <c r="D58">
-        <v>450.99</v>
+        <v>0.592</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46121.59375</v>
+        <v>46128.59375</v>
       </c>
       <c r="B59">
-        <v>19.939</v>
+        <v>13.274</v>
       </c>
       <c r="C59">
-        <v>3.572</v>
+        <v>0.2</v>
       </c>
       <c r="D59">
-        <v>3.572</v>
+        <v>0.2</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46121.60416666666</v>
+        <v>46128.60416666666</v>
       </c>
       <c r="B60">
-        <v>58.564</v>
+        <v>48.867</v>
       </c>
       <c r="C60">
-        <v>-266.827</v>
+        <v>0.354</v>
       </c>
       <c r="D60">
-        <v>-266.827</v>
+        <v>0.354</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46121.61458333334</v>
+        <v>46128.61458333334</v>
       </c>
       <c r="B61">
-        <v>10.174</v>
+        <v>119.268</v>
       </c>
       <c r="C61">
-        <v>-180.316</v>
+        <v>-5372.954</v>
       </c>
       <c r="D61">
-        <v>-180.316</v>
+        <v>-5372.954</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46121.625</v>
+        <v>46128.625</v>
       </c>
       <c r="B62">
-        <v>-56.573</v>
+        <v>69.06699999999999</v>
       </c>
       <c r="C62">
-        <v>450.21</v>
+        <v>-4096.39</v>
       </c>
       <c r="D62">
-        <v>450.21</v>
+        <v>-4096.39</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46121.63541666666</v>
+        <v>46128.63541666666</v>
       </c>
       <c r="B63">
-        <v>-112.594</v>
+        <v>93.434</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>261.259</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>261.259</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46121.64583333334</v>
+        <v>46128.64583333334</v>
       </c>
       <c r="B64">
-        <v>-19.35</v>
+        <v>93.54600000000001</v>
       </c>
       <c r="C64">
-        <v>447.296</v>
+        <v>-70.211</v>
       </c>
       <c r="D64">
-        <v>447.296</v>
+        <v>-70.211</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46121.65625</v>
+        <v>46128.65625</v>
       </c>
       <c r="B65">
-        <v>34.431</v>
+        <v>93.258</v>
       </c>
       <c r="C65">
-        <v>341.101</v>
+        <v>12.604</v>
       </c>
       <c r="D65">
-        <v>341.101</v>
+        <v>12.604</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46121.66666666666</v>
+        <v>46128.66666666666</v>
       </c>
       <c r="B66">
-        <v>83.31399999999999</v>
+        <v>82.607</v>
       </c>
       <c r="C66">
-        <v>-203.761</v>
+        <v>-202.465</v>
       </c>
       <c r="D66">
-        <v>-203.761</v>
+        <v>-202.465</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46121.67708333334</v>
+        <v>46128.67708333334</v>
       </c>
       <c r="B67">
-        <v>39.612</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="C67">
-        <v>-42.515</v>
+        <v>7.439</v>
       </c>
       <c r="D67">
-        <v>-42.515</v>
+        <v>7.439</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46121.6875</v>
+        <v>46128.6875</v>
       </c>
       <c r="B68">
-        <v>32.877</v>
+        <v>36.647</v>
       </c>
       <c r="C68">
-        <v>-4.066</v>
+        <v>2.642</v>
       </c>
       <c r="D68">
-        <v>-4.066</v>
+        <v>2.642</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46121.69791666666</v>
+        <v>46128.69791666666</v>
       </c>
       <c r="B69">
-        <v>33.64</v>
+        <v>53.896</v>
       </c>
       <c r="C69">
-        <v>274.718</v>
+        <v>18.321</v>
       </c>
       <c r="D69">
-        <v>274.718</v>
+        <v>18.321</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46121.70833333334</v>
+        <v>46128.70833333334</v>
       </c>
       <c r="B70">
-        <v>141.172</v>
+        <v>48.097</v>
       </c>
       <c r="C70">
-        <v>95.71899999999999</v>
+        <v>207.631</v>
       </c>
       <c r="D70">
-        <v>95.71899999999999</v>
+        <v>207.631</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46121.71875</v>
+        <v>46128.71875</v>
       </c>
       <c r="B71">
-        <v>124.209</v>
+        <v>15.536</v>
       </c>
       <c r="C71">
-        <v>369.946</v>
+        <v>-16.717</v>
       </c>
       <c r="D71">
-        <v>369.946</v>
+        <v>-16.717</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46121.72916666666</v>
+        <v>46128.72916666666</v>
       </c>
       <c r="B72">
-        <v>122.937</v>
+        <v>1.377</v>
       </c>
       <c r="C72">
-        <v>328.215</v>
+        <v>335.063</v>
       </c>
       <c r="D72">
-        <v>328.215</v>
+        <v>335.063</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46121.73958333334</v>
+        <v>46128.73958333334</v>
       </c>
       <c r="B73">
-        <v>143.386</v>
+        <v>-18.988</v>
       </c>
       <c r="C73">
-        <v>7.713</v>
+        <v>1127.213</v>
       </c>
       <c r="D73">
-        <v>7.713</v>
+        <v>1127.213</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46121.75</v>
+        <v>46128.75</v>
       </c>
       <c r="B74">
-        <v>184.636</v>
+        <v>14.821</v>
       </c>
       <c r="C74">
-        <v>-4859.097</v>
+        <v>86.968</v>
       </c>
       <c r="D74">
-        <v>-4859.097</v>
+        <v>86.968</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46121.76041666666</v>
+        <v>46128.76041666666</v>
       </c>
       <c r="B75">
-        <v>224.67</v>
+        <v>-14.223</v>
       </c>
       <c r="C75">
-        <v>-5808.44</v>
+        <v>977.207</v>
       </c>
       <c r="D75">
-        <v>-5808.44</v>
+        <v>977.207</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46121.77083333334</v>
+        <v>46128.77083333334</v>
       </c>
       <c r="B76">
-        <v>169.324</v>
+        <v>6.18</v>
       </c>
       <c r="C76">
-        <v>6.629</v>
+        <v>304.337</v>
       </c>
       <c r="D76">
-        <v>6.629</v>
+        <v>304.337</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46121.78125</v>
+        <v>46128.78125</v>
       </c>
       <c r="B77">
-        <v>96.253</v>
+        <v>20.472</v>
       </c>
       <c r="C77">
-        <v>0.2</v>
+        <v>58.438</v>
       </c>
       <c r="D77">
-        <v>0.2</v>
+        <v>58.438</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46121.79166666666</v>
+        <v>46128.79166666666</v>
       </c>
       <c r="B78">
-        <v>49.725</v>
+        <v>40.972</v>
       </c>
       <c r="C78">
-        <v>0.244</v>
+        <v>270.77</v>
       </c>
       <c r="D78">
-        <v>0.244</v>
+        <v>270.77</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46121.80208333334</v>
+        <v>46128.80208333334</v>
       </c>
       <c r="B79">
-        <v>24.91</v>
+        <v>2.949</v>
       </c>
       <c r="C79">
-        <v>0.2</v>
+        <v>278.07</v>
       </c>
       <c r="D79">
-        <v>0.2</v>
+        <v>278.07</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46121.8125</v>
+        <v>46128.8125</v>
       </c>
       <c r="B80">
-        <v>16.962</v>
+        <v>3.117</v>
       </c>
       <c r="C80">
-        <v>0.3</v>
+        <v>400</v>
       </c>
       <c r="D80">
-        <v>0.3</v>
+        <v>400</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46121.82291666666</v>
+        <v>46128.82291666666</v>
       </c>
       <c r="B81">
-        <v>69.57599999999999</v>
+        <v>14.748</v>
       </c>
       <c r="C81">
-        <v>-56.659</v>
+        <v>385.464</v>
       </c>
       <c r="D81">
-        <v>-56.659</v>
+        <v>385.464</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46121.83333333334</v>
+        <v>46128.83333333334</v>
       </c>
       <c r="B82">
-        <v>47.409</v>
+        <v>-34.206</v>
       </c>
       <c r="C82">
-        <v>176.38</v>
+        <v>1126.75</v>
       </c>
       <c r="D82">
-        <v>176.38</v>
+        <v>1126.75</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46121.84375</v>
+        <v>46128.84375</v>
       </c>
       <c r="B83">
-        <v>67.652</v>
+        <v>-12.02</v>
       </c>
       <c r="C83">
-        <v>174.653</v>
+        <v>1220.987</v>
       </c>
       <c r="D83">
-        <v>174.653</v>
+        <v>1220.987</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46121.85416666666</v>
+        <v>46128.85416666666</v>
       </c>
       <c r="B84">
-        <v>57.165</v>
+        <v>8.887</v>
       </c>
       <c r="C84">
-        <v>-361.453</v>
+        <v>351.034</v>
       </c>
       <c r="D84">
-        <v>-361.453</v>
+        <v>351.034</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46121.86458333334</v>
+        <v>46128.86458333334</v>
       </c>
       <c r="B85">
-        <v>66.572</v>
+        <v>36.507</v>
       </c>
       <c r="C85">
-        <v>254.663</v>
+        <v>382.284</v>
       </c>
       <c r="D85">
-        <v>254.663</v>
+        <v>382.284</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46121.875</v>
+        <v>46128.875</v>
       </c>
       <c r="B86">
-        <v>26.509</v>
+        <v>-19.221</v>
       </c>
       <c r="C86">
-        <v>264.854</v>
+        <v>1303.928</v>
       </c>
       <c r="D86">
-        <v>264.854</v>
+        <v>1303.928</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46121.88541666666</v>
+        <v>46128.88541666666</v>
       </c>
       <c r="B87">
-        <v>20.271</v>
+        <v>-17.087</v>
       </c>
       <c r="C87">
-        <v>263.797</v>
+        <v>780</v>
       </c>
       <c r="D87">
-        <v>263.797</v>
+        <v>780</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46121.89583333334</v>
+        <v>46128.89583333334</v>
       </c>
       <c r="B88">
-        <v>35.814</v>
+        <v>11.36</v>
       </c>
       <c r="C88">
-        <v>-201.678</v>
+        <v>236.451</v>
       </c>
       <c r="D88">
-        <v>-201.678</v>
+        <v>236.451</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46121.90625</v>
+        <v>46128.90625</v>
       </c>
       <c r="B89">
-        <v>27.813</v>
+        <v>24.787</v>
       </c>
       <c r="C89">
-        <v>-164.925</v>
+        <v>-112.779</v>
       </c>
       <c r="D89">
-        <v>-164.925</v>
+        <v>-112.779</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46121.91666666666</v>
+        <v>46128.91666666666</v>
       </c>
       <c r="B90">
-        <v>43.895</v>
+        <v>35.697</v>
       </c>
       <c r="C90">
-        <v>102.729</v>
+        <v>-1140.45</v>
       </c>
       <c r="D90">
-        <v>102.729</v>
+        <v>-1140.45</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46121.92708333334</v>
+        <v>46128.92708333334</v>
       </c>
       <c r="B91">
-        <v>26.033</v>
+        <v>32.127</v>
       </c>
       <c r="C91">
-        <v>28.618</v>
+        <v>61.907</v>
       </c>
       <c r="D91">
-        <v>28.618</v>
+        <v>61.907</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46121.9375</v>
+        <v>46128.9375</v>
       </c>
       <c r="B92">
-        <v>28.602</v>
+        <v>46.674</v>
       </c>
       <c r="C92">
-        <v>32.535</v>
+        <v>180.152</v>
       </c>
       <c r="D92">
-        <v>32.535</v>
+        <v>180.152</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46121.94791666666</v>
+        <v>46128.94791666666</v>
       </c>
       <c r="B93">
-        <v>7.147</v>
+        <v>27.835</v>
       </c>
       <c r="C93">
-        <v>250.397</v>
+        <v>224.371</v>
       </c>
       <c r="D93">
-        <v>250.397</v>
+        <v>224.371</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46121.95833333334</v>
+        <v>46128.95833333334</v>
       </c>
       <c r="B94">
-        <v>-6.742</v>
+        <v>2.767</v>
       </c>
       <c r="C94">
-        <v>699</v>
+        <v>318.011</v>
       </c>
       <c r="D94">
-        <v>699</v>
+        <v>318.011</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46121.96875</v>
+        <v>46128.96875</v>
       </c>
       <c r="B95">
-        <v>2.878</v>
+        <v>-3.525</v>
       </c>
       <c r="C95">
-        <v>400</v>
+        <v>835.809</v>
       </c>
       <c r="D95">
-        <v>400</v>
+        <v>835.809</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46121.97916666666</v>
+        <v>46128.97916666666</v>
       </c>
       <c r="B96">
-        <v>7.013</v>
+        <v>12.561</v>
       </c>
       <c r="C96">
-        <v>279.859</v>
+        <v>93.474</v>
       </c>
       <c r="D96">
-        <v>279.859</v>
+        <v>93.474</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46121.98958333334</v>
+        <v>46128.98958333334</v>
       </c>
       <c r="B97">
-        <v>23.449</v>
+        <v>0.239</v>
       </c>
       <c r="C97">
-        <v>-152.788</v>
+        <v>115.488</v>
       </c>
       <c r="D97">
-        <v>-152.788</v>
+        <v>115.488</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46122</v>
+        <v>46129</v>
       </c>
       <c r="B98">
-        <v>68.492</v>
+        <v>2.306</v>
       </c>
       <c r="C98">
-        <v>-106.388</v>
+        <v>247.43</v>
       </c>
       <c r="D98">
-        <v>-106.388</v>
+        <v>247.43</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46122.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B99">
-        <v>-3.764</v>
+        <v>-5.658</v>
       </c>
       <c r="C99">
-        <v>795.603</v>
+        <v>899.446</v>
       </c>
       <c r="D99">
-        <v>795.603</v>
+        <v>899.446</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46122.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B100">
-        <v>10.501</v>
+        <v>5.362</v>
       </c>
       <c r="C100">
-        <v>258.255</v>
+        <v>262.143</v>
       </c>
       <c r="D100">
-        <v>258.255</v>
+        <v>262.143</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46122.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B101">
-        <v>2.038</v>
+        <v>-1.069</v>
       </c>
       <c r="C101">
-        <v>265.879</v>
+        <v>800</v>
       </c>
       <c r="D101">
-        <v>265.879</v>
+        <v>800</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46122.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B102">
-        <v>9.176</v>
+        <v>5.417</v>
       </c>
       <c r="C102">
-        <v>270.791</v>
+        <v>23.521</v>
       </c>
       <c r="D102">
-        <v>270.791</v>
+        <v>23.521</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46122.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B103">
-        <v>-12.53</v>
+        <v>1.374</v>
       </c>
       <c r="C103">
-        <v>699</v>
+        <v>11.503</v>
       </c>
       <c r="D103">
-        <v>699</v>
+        <v>11.503</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46122.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B104">
-        <v>-34.227</v>
+        <v>17.415</v>
       </c>
       <c r="C104">
-        <v>728.2859999999999</v>
+        <v>11.758</v>
       </c>
       <c r="D104">
-        <v>728.2859999999999</v>
+        <v>11.758</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46122.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B105">
-        <v>-37.392</v>
+        <v>22.052</v>
       </c>
       <c r="C105">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46122.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B106">
-        <v>3.541</v>
+        <v>45.62</v>
       </c>
       <c r="C106">
-        <v>127.841</v>
+        <v>54.257</v>
       </c>
       <c r="D106">
-        <v>127.841</v>
+        <v>54.257</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46122.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B107">
-        <v>3.002</v>
+        <v>43.437</v>
       </c>
       <c r="C107">
-        <v>272.026</v>
+        <v>-125.917</v>
       </c>
       <c r="D107">
-        <v>272.026</v>
+        <v>-125.917</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46122.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B108">
-        <v>-7.723</v>
+        <v>35.197</v>
       </c>
       <c r="C108">
-        <v>292.908</v>
+        <v>17.601</v>
       </c>
       <c r="D108">
-        <v>292.908</v>
+        <v>17.601</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46122.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B109">
-        <v>-5.969</v>
+        <v>30.173</v>
       </c>
       <c r="C109">
-        <v>699</v>
+        <v>34.159</v>
       </c>
       <c r="D109">
-        <v>699</v>
+        <v>34.159</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46122.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B110">
-        <v>7.806</v>
+        <v>46.387</v>
       </c>
       <c r="C110">
-        <v>42.259</v>
+        <v>179.01</v>
       </c>
       <c r="D110">
-        <v>42.259</v>
+        <v>179.01</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46122.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B111">
-        <v>31.953</v>
+        <v>52.983</v>
       </c>
       <c r="C111">
-        <v>0.452</v>
+        <v>140.894</v>
       </c>
       <c r="D111">
-        <v>0.452</v>
+        <v>140.894</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46122.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B112">
-        <v>29.574</v>
+        <v>31.174</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>53.078</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>53.078</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46122.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B113">
-        <v>37.416</v>
+        <v>-4.987</v>
       </c>
       <c r="C113">
-        <v>-12.421</v>
+        <v>865.535</v>
       </c>
       <c r="D113">
-        <v>-12.421</v>
+        <v>865.535</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46122.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B114">
-        <v>20.663</v>
+        <v>3.804</v>
       </c>
       <c r="C114">
-        <v>12.621</v>
+        <v>146.595</v>
       </c>
       <c r="D114">
-        <v>12.621</v>
+        <v>146.595</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46122.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B115">
-        <v>-2.103</v>
+        <v>14.364</v>
       </c>
       <c r="C115">
-        <v>699</v>
+        <v>12.677</v>
       </c>
       <c r="D115">
-        <v>699</v>
+        <v>12.677</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46122.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B116">
-        <v>17.982</v>
+        <v>3.425</v>
       </c>
       <c r="C116">
-        <v>111.373</v>
+        <v>132.97</v>
       </c>
       <c r="D116">
-        <v>111.373</v>
+        <v>132.97</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46122.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B117">
-        <v>16.727</v>
+        <v>-10.913</v>
       </c>
       <c r="C117">
-        <v>269.534</v>
+        <v>811.647</v>
       </c>
       <c r="D117">
-        <v>269.534</v>
+        <v>811.647</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46122.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B118">
-        <v>0.53</v>
+        <v>33.929</v>
       </c>
       <c r="C118">
-        <v>256.481</v>
+        <v>10.286</v>
       </c>
       <c r="D118">
-        <v>256.481</v>
+        <v>10.286</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46122.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B119">
-        <v>-28.042</v>
+        <v>24.287</v>
       </c>
       <c r="C119">
-        <v>969.904</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D119">
-        <v>969.904</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46122.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B120">
-        <v>-31.182</v>
+        <v>37.998</v>
       </c>
       <c r="C120">
-        <v>767.075</v>
+        <v>196.915</v>
       </c>
       <c r="D120">
-        <v>767.075</v>
+        <v>196.915</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46122.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B121">
-        <v>7.161</v>
+        <v>18.805</v>
       </c>
       <c r="C121">
-        <v>56.324</v>
+        <v>280.022</v>
       </c>
       <c r="D121">
-        <v>56.324</v>
+        <v>280.022</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46122.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B122">
-        <v>-19.757</v>
+        <v>-13.32</v>
       </c>
       <c r="C122">
-        <v>1092.13</v>
+        <v>1640.63</v>
       </c>
       <c r="D122">
-        <v>1092.13</v>
+        <v>1640.63</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46122.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B123">
-        <v>-9.414</v>
+        <v>-58.883</v>
       </c>
       <c r="C123">
-        <v>904.974</v>
+        <v>1322.752</v>
       </c>
       <c r="D123">
-        <v>904.974</v>
+        <v>1322.752</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46122.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B124">
-        <v>3.687</v>
+        <v>-10.618</v>
       </c>
       <c r="C124">
-        <v>108.604</v>
+        <v>840.367</v>
       </c>
       <c r="D124">
-        <v>108.604</v>
+        <v>840.367</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46122.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B125">
-        <v>-6.088</v>
+        <v>3.158</v>
       </c>
       <c r="C125">
-        <v>699</v>
+        <v>127.575</v>
       </c>
       <c r="D125">
-        <v>699</v>
+        <v>127.575</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46122.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B126">
-        <v>-55.347</v>
+        <v>38.352</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>95.242</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>95.242</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46122.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B127">
-        <v>-73.821</v>
+        <v>20.782</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>53.983</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>53.983</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46122.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B128">
-        <v>-50.894</v>
+        <v>33.71</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>61.16</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>61.16</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46122.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B129">
-        <v>-6.158</v>
+        <v>12.061</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>119.157</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>119.157</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46122.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B130">
-        <v>-41.855</v>
+        <v>13.807</v>
       </c>
       <c r="C130">
-        <v>912.477</v>
+        <v>139.996</v>
       </c>
       <c r="D130">
-        <v>912.477</v>
+        <v>139.996</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46122.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B131">
-        <v>-48.425</v>
+        <v>-5.418</v>
       </c>
       <c r="C131">
-        <v>921.9640000000001</v>
+        <v>732.774</v>
       </c>
       <c r="D131">
-        <v>921.9640000000001</v>
+        <v>732.774</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46122.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B132">
-        <v>-36.282</v>
+        <v>44.775</v>
       </c>
       <c r="C132">
-        <v>909.17</v>
+        <v>-404.801</v>
       </c>
       <c r="D132">
-        <v>909.17</v>
+        <v>-404.801</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46122.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B133">
-        <v>3.114</v>
+        <v>49.925</v>
       </c>
       <c r="C133">
-        <v>61.184</v>
+        <v>-824.0069999999999</v>
       </c>
       <c r="D133">
-        <v>61.184</v>
+        <v>-824.0069999999999</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46122.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B134">
-        <v>8.885</v>
+        <v>-20.477</v>
       </c>
       <c r="C134">
-        <v>131.119</v>
+        <v>875.174</v>
       </c>
       <c r="D134">
-        <v>131.119</v>
+        <v>875.174</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46122.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B135">
-        <v>63.845</v>
+        <v>-7.59</v>
       </c>
       <c r="C135">
-        <v>-137.284</v>
+        <v>716.356</v>
       </c>
       <c r="D135">
-        <v>-137.284</v>
+        <v>716.356</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46122.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B136">
-        <v>115.072</v>
+        <v>26.674</v>
       </c>
       <c r="C136">
-        <v>66.18000000000001</v>
+        <v>19.428</v>
       </c>
       <c r="D136">
-        <v>66.18000000000001</v>
+        <v>19.428</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46122.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B137">
-        <v>39.934</v>
+        <v>26.824</v>
       </c>
       <c r="C137">
-        <v>-280.869</v>
+        <v>69.723</v>
       </c>
       <c r="D137">
-        <v>-280.869</v>
+        <v>69.723</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46122.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B138">
-        <v>0.245</v>
+        <v>35.037</v>
       </c>
       <c r="C138">
-        <v>2.442</v>
+        <v>-12.304</v>
       </c>
       <c r="D138">
-        <v>2.442</v>
+        <v>-12.304</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46122.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>17.095</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>-203.139</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>-203.139</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46122.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>0.926</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>-138.332</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>-138.332</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46122.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>18.855</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>-223.825</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>-223.825</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46122.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>28.534</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>-66.886</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>-66.886</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46122.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>-14.567</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46122.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>7.466</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>101.275</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>101.275</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46122.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>-211.225</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>-211.225</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46122.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46122.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46122.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46122.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46122.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46122.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46122.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46122.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46122.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46122.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46122.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46122.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46122.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46122.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46122.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46122.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46122.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46122.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46122.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46122.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46122.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46122.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46122.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46122.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46122.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46122.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46122.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46122.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46122.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46122.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46122.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46122.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46122.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46122.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46122.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46122.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46122.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46122.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46122.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46122.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46122.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46122.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46122.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46122.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46122.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46122.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46122.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46122.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>16.04.20261</t>
-  </si>
-  <si>
-    <t>16.04.20262</t>
-  </si>
-  <si>
-    <t>16.04.20263</t>
-  </si>
-  <si>
-    <t>16.04.20264</t>
-  </si>
-  <si>
-    <t>16.04.20265</t>
-  </si>
-  <si>
-    <t>16.04.20266</t>
-  </si>
-  <si>
-    <t>16.04.20267</t>
-  </si>
-  <si>
-    <t>16.04.20268</t>
-  </si>
-  <si>
-    <t>16.04.20269</t>
-  </si>
-  <si>
-    <t>16.04.202610</t>
-  </si>
-  <si>
-    <t>16.04.202611</t>
-  </si>
-  <si>
-    <t>16.04.202612</t>
-  </si>
-  <si>
-    <t>16.04.202613</t>
-  </si>
-  <si>
-    <t>16.04.202614</t>
-  </si>
-  <si>
-    <t>16.04.202615</t>
-  </si>
-  <si>
-    <t>16.04.202616</t>
-  </si>
-  <si>
-    <t>16.04.202617</t>
-  </si>
-  <si>
-    <t>16.04.202618</t>
-  </si>
-  <si>
-    <t>16.04.202619</t>
-  </si>
-  <si>
-    <t>16.04.202620</t>
-  </si>
-  <si>
-    <t>16.04.202621</t>
-  </si>
-  <si>
-    <t>16.04.202622</t>
-  </si>
-  <si>
-    <t>16.04.202623</t>
-  </si>
-  <si>
-    <t>16.04.202624</t>
-  </si>
-  <si>
-    <t>16.04.202625</t>
-  </si>
-  <si>
-    <t>16.04.202626</t>
-  </si>
-  <si>
-    <t>16.04.202627</t>
-  </si>
-  <si>
-    <t>16.04.202628</t>
-  </si>
-  <si>
-    <t>16.04.202629</t>
-  </si>
-  <si>
-    <t>16.04.202630</t>
-  </si>
-  <si>
-    <t>16.04.202631</t>
-  </si>
-  <si>
-    <t>16.04.202632</t>
-  </si>
-  <si>
-    <t>16.04.202633</t>
-  </si>
-  <si>
-    <t>16.04.202634</t>
-  </si>
-  <si>
-    <t>16.04.202635</t>
-  </si>
-  <si>
-    <t>16.04.202636</t>
-  </si>
-  <si>
-    <t>16.04.202637</t>
-  </si>
-  <si>
-    <t>16.04.202638</t>
-  </si>
-  <si>
-    <t>16.04.202639</t>
-  </si>
-  <si>
-    <t>16.04.202640</t>
-  </si>
-  <si>
-    <t>16.04.202641</t>
-  </si>
-  <si>
-    <t>16.04.202642</t>
-  </si>
-  <si>
-    <t>16.04.202643</t>
-  </si>
-  <si>
-    <t>16.04.202644</t>
-  </si>
-  <si>
-    <t>16.04.202645</t>
-  </si>
-  <si>
-    <t>16.04.202646</t>
-  </si>
-  <si>
-    <t>16.04.202647</t>
-  </si>
-  <si>
-    <t>16.04.202648</t>
-  </si>
-  <si>
-    <t>16.04.202649</t>
-  </si>
-  <si>
-    <t>16.04.202650</t>
-  </si>
-  <si>
-    <t>16.04.202651</t>
-  </si>
-  <si>
-    <t>16.04.202652</t>
-  </si>
-  <si>
-    <t>16.04.202653</t>
-  </si>
-  <si>
-    <t>16.04.202654</t>
-  </si>
-  <si>
-    <t>16.04.202655</t>
-  </si>
-  <si>
-    <t>16.04.202656</t>
-  </si>
-  <si>
-    <t>16.04.202657</t>
-  </si>
-  <si>
-    <t>16.04.202658</t>
-  </si>
-  <si>
-    <t>16.04.202659</t>
-  </si>
-  <si>
-    <t>16.04.202660</t>
-  </si>
-  <si>
-    <t>16.04.202661</t>
-  </si>
-  <si>
-    <t>16.04.202662</t>
-  </si>
-  <si>
-    <t>16.04.202663</t>
-  </si>
-  <si>
-    <t>16.04.202664</t>
-  </si>
-  <si>
-    <t>16.04.202665</t>
-  </si>
-  <si>
-    <t>16.04.202666</t>
-  </si>
-  <si>
-    <t>16.04.202667</t>
-  </si>
-  <si>
-    <t>16.04.202668</t>
-  </si>
-  <si>
-    <t>16.04.202669</t>
-  </si>
-  <si>
-    <t>16.04.202670</t>
-  </si>
-  <si>
-    <t>16.04.202671</t>
-  </si>
-  <si>
-    <t>16.04.202672</t>
-  </si>
-  <si>
-    <t>16.04.202673</t>
-  </si>
-  <si>
-    <t>16.04.202674</t>
-  </si>
-  <si>
-    <t>16.04.202675</t>
-  </si>
-  <si>
-    <t>16.04.202676</t>
-  </si>
-  <si>
-    <t>16.04.202677</t>
-  </si>
-  <si>
-    <t>16.04.202678</t>
-  </si>
-  <si>
-    <t>16.04.202679</t>
-  </si>
-  <si>
-    <t>16.04.202680</t>
-  </si>
-  <si>
-    <t>16.04.202681</t>
-  </si>
-  <si>
-    <t>16.04.202682</t>
-  </si>
-  <si>
-    <t>16.04.202683</t>
-  </si>
-  <si>
-    <t>16.04.202684</t>
-  </si>
-  <si>
-    <t>16.04.202685</t>
-  </si>
-  <si>
-    <t>16.04.202686</t>
-  </si>
-  <si>
-    <t>16.04.202687</t>
-  </si>
-  <si>
-    <t>16.04.202688</t>
-  </si>
-  <si>
-    <t>16.04.202689</t>
-  </si>
-  <si>
-    <t>16.04.202690</t>
-  </si>
-  <si>
-    <t>16.04.202691</t>
-  </si>
-  <si>
-    <t>16.04.202692</t>
-  </si>
-  <si>
-    <t>16.04.202693</t>
-  </si>
-  <si>
-    <t>16.04.202694</t>
-  </si>
-  <si>
-    <t>16.04.202695</t>
-  </si>
-  <si>
-    <t>16.04.202696</t>
-  </si>
-  <si>
     <t>17.04.20261</t>
   </si>
   <si>
@@ -608,6 +320,870 @@
   </si>
   <si>
     <t>17.04.202696</t>
+  </si>
+  <si>
+    <t>18.04.20261</t>
+  </si>
+  <si>
+    <t>18.04.20262</t>
+  </si>
+  <si>
+    <t>18.04.20263</t>
+  </si>
+  <si>
+    <t>18.04.20264</t>
+  </si>
+  <si>
+    <t>18.04.20265</t>
+  </si>
+  <si>
+    <t>18.04.20266</t>
+  </si>
+  <si>
+    <t>18.04.20267</t>
+  </si>
+  <si>
+    <t>18.04.20268</t>
+  </si>
+  <si>
+    <t>18.04.20269</t>
+  </si>
+  <si>
+    <t>18.04.202610</t>
+  </si>
+  <si>
+    <t>18.04.202611</t>
+  </si>
+  <si>
+    <t>18.04.202612</t>
+  </si>
+  <si>
+    <t>18.04.202613</t>
+  </si>
+  <si>
+    <t>18.04.202614</t>
+  </si>
+  <si>
+    <t>18.04.202615</t>
+  </si>
+  <si>
+    <t>18.04.202616</t>
+  </si>
+  <si>
+    <t>18.04.202617</t>
+  </si>
+  <si>
+    <t>18.04.202618</t>
+  </si>
+  <si>
+    <t>18.04.202619</t>
+  </si>
+  <si>
+    <t>18.04.202620</t>
+  </si>
+  <si>
+    <t>18.04.202621</t>
+  </si>
+  <si>
+    <t>18.04.202622</t>
+  </si>
+  <si>
+    <t>18.04.202623</t>
+  </si>
+  <si>
+    <t>18.04.202624</t>
+  </si>
+  <si>
+    <t>18.04.202625</t>
+  </si>
+  <si>
+    <t>18.04.202626</t>
+  </si>
+  <si>
+    <t>18.04.202627</t>
+  </si>
+  <si>
+    <t>18.04.202628</t>
+  </si>
+  <si>
+    <t>18.04.202629</t>
+  </si>
+  <si>
+    <t>18.04.202630</t>
+  </si>
+  <si>
+    <t>18.04.202631</t>
+  </si>
+  <si>
+    <t>18.04.202632</t>
+  </si>
+  <si>
+    <t>18.04.202633</t>
+  </si>
+  <si>
+    <t>18.04.202634</t>
+  </si>
+  <si>
+    <t>18.04.202635</t>
+  </si>
+  <si>
+    <t>18.04.202636</t>
+  </si>
+  <si>
+    <t>18.04.202637</t>
+  </si>
+  <si>
+    <t>18.04.202638</t>
+  </si>
+  <si>
+    <t>18.04.202639</t>
+  </si>
+  <si>
+    <t>18.04.202640</t>
+  </si>
+  <si>
+    <t>18.04.202641</t>
+  </si>
+  <si>
+    <t>18.04.202642</t>
+  </si>
+  <si>
+    <t>18.04.202643</t>
+  </si>
+  <si>
+    <t>18.04.202644</t>
+  </si>
+  <si>
+    <t>18.04.202645</t>
+  </si>
+  <si>
+    <t>18.04.202646</t>
+  </si>
+  <si>
+    <t>18.04.202647</t>
+  </si>
+  <si>
+    <t>18.04.202648</t>
+  </si>
+  <si>
+    <t>18.04.202649</t>
+  </si>
+  <si>
+    <t>18.04.202650</t>
+  </si>
+  <si>
+    <t>18.04.202651</t>
+  </si>
+  <si>
+    <t>18.04.202652</t>
+  </si>
+  <si>
+    <t>18.04.202653</t>
+  </si>
+  <si>
+    <t>18.04.202654</t>
+  </si>
+  <si>
+    <t>18.04.202655</t>
+  </si>
+  <si>
+    <t>18.04.202656</t>
+  </si>
+  <si>
+    <t>18.04.202657</t>
+  </si>
+  <si>
+    <t>18.04.202658</t>
+  </si>
+  <si>
+    <t>18.04.202659</t>
+  </si>
+  <si>
+    <t>18.04.202660</t>
+  </si>
+  <si>
+    <t>18.04.202661</t>
+  </si>
+  <si>
+    <t>18.04.202662</t>
+  </si>
+  <si>
+    <t>18.04.202663</t>
+  </si>
+  <si>
+    <t>18.04.202664</t>
+  </si>
+  <si>
+    <t>18.04.202665</t>
+  </si>
+  <si>
+    <t>18.04.202666</t>
+  </si>
+  <si>
+    <t>18.04.202667</t>
+  </si>
+  <si>
+    <t>18.04.202668</t>
+  </si>
+  <si>
+    <t>18.04.202669</t>
+  </si>
+  <si>
+    <t>18.04.202670</t>
+  </si>
+  <si>
+    <t>18.04.202671</t>
+  </si>
+  <si>
+    <t>18.04.202672</t>
+  </si>
+  <si>
+    <t>18.04.202673</t>
+  </si>
+  <si>
+    <t>18.04.202674</t>
+  </si>
+  <si>
+    <t>18.04.202675</t>
+  </si>
+  <si>
+    <t>18.04.202676</t>
+  </si>
+  <si>
+    <t>18.04.202677</t>
+  </si>
+  <si>
+    <t>18.04.202678</t>
+  </si>
+  <si>
+    <t>18.04.202679</t>
+  </si>
+  <si>
+    <t>18.04.202680</t>
+  </si>
+  <si>
+    <t>18.04.202681</t>
+  </si>
+  <si>
+    <t>18.04.202682</t>
+  </si>
+  <si>
+    <t>18.04.202683</t>
+  </si>
+  <si>
+    <t>18.04.202684</t>
+  </si>
+  <si>
+    <t>18.04.202685</t>
+  </si>
+  <si>
+    <t>18.04.202686</t>
+  </si>
+  <si>
+    <t>18.04.202687</t>
+  </si>
+  <si>
+    <t>18.04.202688</t>
+  </si>
+  <si>
+    <t>18.04.202689</t>
+  </si>
+  <si>
+    <t>18.04.202690</t>
+  </si>
+  <si>
+    <t>18.04.202691</t>
+  </si>
+  <si>
+    <t>18.04.202692</t>
+  </si>
+  <si>
+    <t>18.04.202693</t>
+  </si>
+  <si>
+    <t>18.04.202694</t>
+  </si>
+  <si>
+    <t>18.04.202695</t>
+  </si>
+  <si>
+    <t>18.04.202696</t>
+  </si>
+  <si>
+    <t>19.04.20261</t>
+  </si>
+  <si>
+    <t>19.04.20262</t>
+  </si>
+  <si>
+    <t>19.04.20263</t>
+  </si>
+  <si>
+    <t>19.04.20264</t>
+  </si>
+  <si>
+    <t>19.04.20265</t>
+  </si>
+  <si>
+    <t>19.04.20266</t>
+  </si>
+  <si>
+    <t>19.04.20267</t>
+  </si>
+  <si>
+    <t>19.04.20268</t>
+  </si>
+  <si>
+    <t>19.04.20269</t>
+  </si>
+  <si>
+    <t>19.04.202610</t>
+  </si>
+  <si>
+    <t>19.04.202611</t>
+  </si>
+  <si>
+    <t>19.04.202612</t>
+  </si>
+  <si>
+    <t>19.04.202613</t>
+  </si>
+  <si>
+    <t>19.04.202614</t>
+  </si>
+  <si>
+    <t>19.04.202615</t>
+  </si>
+  <si>
+    <t>19.04.202616</t>
+  </si>
+  <si>
+    <t>19.04.202617</t>
+  </si>
+  <si>
+    <t>19.04.202618</t>
+  </si>
+  <si>
+    <t>19.04.202619</t>
+  </si>
+  <si>
+    <t>19.04.202620</t>
+  </si>
+  <si>
+    <t>19.04.202621</t>
+  </si>
+  <si>
+    <t>19.04.202622</t>
+  </si>
+  <si>
+    <t>19.04.202623</t>
+  </si>
+  <si>
+    <t>19.04.202624</t>
+  </si>
+  <si>
+    <t>19.04.202625</t>
+  </si>
+  <si>
+    <t>19.04.202626</t>
+  </si>
+  <si>
+    <t>19.04.202627</t>
+  </si>
+  <si>
+    <t>19.04.202628</t>
+  </si>
+  <si>
+    <t>19.04.202629</t>
+  </si>
+  <si>
+    <t>19.04.202630</t>
+  </si>
+  <si>
+    <t>19.04.202631</t>
+  </si>
+  <si>
+    <t>19.04.202632</t>
+  </si>
+  <si>
+    <t>19.04.202633</t>
+  </si>
+  <si>
+    <t>19.04.202634</t>
+  </si>
+  <si>
+    <t>19.04.202635</t>
+  </si>
+  <si>
+    <t>19.04.202636</t>
+  </si>
+  <si>
+    <t>19.04.202637</t>
+  </si>
+  <si>
+    <t>19.04.202638</t>
+  </si>
+  <si>
+    <t>19.04.202639</t>
+  </si>
+  <si>
+    <t>19.04.202640</t>
+  </si>
+  <si>
+    <t>19.04.202641</t>
+  </si>
+  <si>
+    <t>19.04.202642</t>
+  </si>
+  <si>
+    <t>19.04.202643</t>
+  </si>
+  <si>
+    <t>19.04.202644</t>
+  </si>
+  <si>
+    <t>19.04.202645</t>
+  </si>
+  <si>
+    <t>19.04.202646</t>
+  </si>
+  <si>
+    <t>19.04.202647</t>
+  </si>
+  <si>
+    <t>19.04.202648</t>
+  </si>
+  <si>
+    <t>19.04.202649</t>
+  </si>
+  <si>
+    <t>19.04.202650</t>
+  </si>
+  <si>
+    <t>19.04.202651</t>
+  </si>
+  <si>
+    <t>19.04.202652</t>
+  </si>
+  <si>
+    <t>19.04.202653</t>
+  </si>
+  <si>
+    <t>19.04.202654</t>
+  </si>
+  <si>
+    <t>19.04.202655</t>
+  </si>
+  <si>
+    <t>19.04.202656</t>
+  </si>
+  <si>
+    <t>19.04.202657</t>
+  </si>
+  <si>
+    <t>19.04.202658</t>
+  </si>
+  <si>
+    <t>19.04.202659</t>
+  </si>
+  <si>
+    <t>19.04.202660</t>
+  </si>
+  <si>
+    <t>19.04.202661</t>
+  </si>
+  <si>
+    <t>19.04.202662</t>
+  </si>
+  <si>
+    <t>19.04.202663</t>
+  </si>
+  <si>
+    <t>19.04.202664</t>
+  </si>
+  <si>
+    <t>19.04.202665</t>
+  </si>
+  <si>
+    <t>19.04.202666</t>
+  </si>
+  <si>
+    <t>19.04.202667</t>
+  </si>
+  <si>
+    <t>19.04.202668</t>
+  </si>
+  <si>
+    <t>19.04.202669</t>
+  </si>
+  <si>
+    <t>19.04.202670</t>
+  </si>
+  <si>
+    <t>19.04.202671</t>
+  </si>
+  <si>
+    <t>19.04.202672</t>
+  </si>
+  <si>
+    <t>19.04.202673</t>
+  </si>
+  <si>
+    <t>19.04.202674</t>
+  </si>
+  <si>
+    <t>19.04.202675</t>
+  </si>
+  <si>
+    <t>19.04.202676</t>
+  </si>
+  <si>
+    <t>19.04.202677</t>
+  </si>
+  <si>
+    <t>19.04.202678</t>
+  </si>
+  <si>
+    <t>19.04.202679</t>
+  </si>
+  <si>
+    <t>19.04.202680</t>
+  </si>
+  <si>
+    <t>19.04.202681</t>
+  </si>
+  <si>
+    <t>19.04.202682</t>
+  </si>
+  <si>
+    <t>19.04.202683</t>
+  </si>
+  <si>
+    <t>19.04.202684</t>
+  </si>
+  <si>
+    <t>19.04.202685</t>
+  </si>
+  <si>
+    <t>19.04.202686</t>
+  </si>
+  <si>
+    <t>19.04.202687</t>
+  </si>
+  <si>
+    <t>19.04.202688</t>
+  </si>
+  <si>
+    <t>19.04.202689</t>
+  </si>
+  <si>
+    <t>19.04.202690</t>
+  </si>
+  <si>
+    <t>19.04.202691</t>
+  </si>
+  <si>
+    <t>19.04.202692</t>
+  </si>
+  <si>
+    <t>19.04.202693</t>
+  </si>
+  <si>
+    <t>19.04.202694</t>
+  </si>
+  <si>
+    <t>19.04.202695</t>
+  </si>
+  <si>
+    <t>19.04.202696</t>
+  </si>
+  <si>
+    <t>20.04.20261</t>
+  </si>
+  <si>
+    <t>20.04.20262</t>
+  </si>
+  <si>
+    <t>20.04.20263</t>
+  </si>
+  <si>
+    <t>20.04.20264</t>
+  </si>
+  <si>
+    <t>20.04.20265</t>
+  </si>
+  <si>
+    <t>20.04.20266</t>
+  </si>
+  <si>
+    <t>20.04.20267</t>
+  </si>
+  <si>
+    <t>20.04.20268</t>
+  </si>
+  <si>
+    <t>20.04.20269</t>
+  </si>
+  <si>
+    <t>20.04.202610</t>
+  </si>
+  <si>
+    <t>20.04.202611</t>
+  </si>
+  <si>
+    <t>20.04.202612</t>
+  </si>
+  <si>
+    <t>20.04.202613</t>
+  </si>
+  <si>
+    <t>20.04.202614</t>
+  </si>
+  <si>
+    <t>20.04.202615</t>
+  </si>
+  <si>
+    <t>20.04.202616</t>
+  </si>
+  <si>
+    <t>20.04.202617</t>
+  </si>
+  <si>
+    <t>20.04.202618</t>
+  </si>
+  <si>
+    <t>20.04.202619</t>
+  </si>
+  <si>
+    <t>20.04.202620</t>
+  </si>
+  <si>
+    <t>20.04.202621</t>
+  </si>
+  <si>
+    <t>20.04.202622</t>
+  </si>
+  <si>
+    <t>20.04.202623</t>
+  </si>
+  <si>
+    <t>20.04.202624</t>
+  </si>
+  <si>
+    <t>20.04.202625</t>
+  </si>
+  <si>
+    <t>20.04.202626</t>
+  </si>
+  <si>
+    <t>20.04.202627</t>
+  </si>
+  <si>
+    <t>20.04.202628</t>
+  </si>
+  <si>
+    <t>20.04.202629</t>
+  </si>
+  <si>
+    <t>20.04.202630</t>
+  </si>
+  <si>
+    <t>20.04.202631</t>
+  </si>
+  <si>
+    <t>20.04.202632</t>
+  </si>
+  <si>
+    <t>20.04.202633</t>
+  </si>
+  <si>
+    <t>20.04.202634</t>
+  </si>
+  <si>
+    <t>20.04.202635</t>
+  </si>
+  <si>
+    <t>20.04.202636</t>
+  </si>
+  <si>
+    <t>20.04.202637</t>
+  </si>
+  <si>
+    <t>20.04.202638</t>
+  </si>
+  <si>
+    <t>20.04.202639</t>
+  </si>
+  <si>
+    <t>20.04.202640</t>
+  </si>
+  <si>
+    <t>20.04.202641</t>
+  </si>
+  <si>
+    <t>20.04.202642</t>
+  </si>
+  <si>
+    <t>20.04.202643</t>
+  </si>
+  <si>
+    <t>20.04.202644</t>
+  </si>
+  <si>
+    <t>20.04.202645</t>
+  </si>
+  <si>
+    <t>20.04.202646</t>
+  </si>
+  <si>
+    <t>20.04.202647</t>
+  </si>
+  <si>
+    <t>20.04.202648</t>
+  </si>
+  <si>
+    <t>20.04.202649</t>
+  </si>
+  <si>
+    <t>20.04.202650</t>
+  </si>
+  <si>
+    <t>20.04.202651</t>
+  </si>
+  <si>
+    <t>20.04.202652</t>
+  </si>
+  <si>
+    <t>20.04.202653</t>
+  </si>
+  <si>
+    <t>20.04.202654</t>
+  </si>
+  <si>
+    <t>20.04.202655</t>
+  </si>
+  <si>
+    <t>20.04.202656</t>
+  </si>
+  <si>
+    <t>20.04.202657</t>
+  </si>
+  <si>
+    <t>20.04.202658</t>
+  </si>
+  <si>
+    <t>20.04.202659</t>
+  </si>
+  <si>
+    <t>20.04.202660</t>
+  </si>
+  <si>
+    <t>20.04.202661</t>
+  </si>
+  <si>
+    <t>20.04.202662</t>
+  </si>
+  <si>
+    <t>20.04.202663</t>
+  </si>
+  <si>
+    <t>20.04.202664</t>
+  </si>
+  <si>
+    <t>20.04.202665</t>
+  </si>
+  <si>
+    <t>20.04.202666</t>
+  </si>
+  <si>
+    <t>20.04.202667</t>
+  </si>
+  <si>
+    <t>20.04.202668</t>
+  </si>
+  <si>
+    <t>20.04.202669</t>
+  </si>
+  <si>
+    <t>20.04.202670</t>
+  </si>
+  <si>
+    <t>20.04.202671</t>
+  </si>
+  <si>
+    <t>20.04.202672</t>
+  </si>
+  <si>
+    <t>20.04.202673</t>
+  </si>
+  <si>
+    <t>20.04.202674</t>
+  </si>
+  <si>
+    <t>20.04.202675</t>
+  </si>
+  <si>
+    <t>20.04.202676</t>
+  </si>
+  <si>
+    <t>20.04.202677</t>
+  </si>
+  <si>
+    <t>20.04.202678</t>
+  </si>
+  <si>
+    <t>20.04.202679</t>
+  </si>
+  <si>
+    <t>20.04.202680</t>
+  </si>
+  <si>
+    <t>20.04.202681</t>
+  </si>
+  <si>
+    <t>20.04.202682</t>
+  </si>
+  <si>
+    <t>20.04.202683</t>
+  </si>
+  <si>
+    <t>20.04.202684</t>
+  </si>
+  <si>
+    <t>20.04.202685</t>
+  </si>
+  <si>
+    <t>20.04.202686</t>
+  </si>
+  <si>
+    <t>20.04.202687</t>
+  </si>
+  <si>
+    <t>20.04.202688</t>
+  </si>
+  <si>
+    <t>20.04.202689</t>
+  </si>
+  <si>
+    <t>20.04.202690</t>
+  </si>
+  <si>
+    <t>20.04.202691</t>
+  </si>
+  <si>
+    <t>20.04.202692</t>
+  </si>
+  <si>
+    <t>20.04.202693</t>
+  </si>
+  <si>
+    <t>20.04.202694</t>
+  </si>
+  <si>
+    <t>20.04.202695</t>
+  </si>
+  <si>
+    <t>20.04.202696</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -994,7 +1570,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1590,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46128.01041666666</v>
+        <v>46129.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1610,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46128.02083333334</v>
+        <v>46129.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1630,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46128.03125</v>
+        <v>46129.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1650,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46128.04166666666</v>
+        <v>46129.04166666666</v>
       </c>
       <c r="B6">
-        <v>39.864</v>
+        <v>5.417</v>
       </c>
       <c r="C6">
-        <v>-355.79</v>
+        <v>23.521</v>
       </c>
       <c r="D6">
-        <v>-355.79</v>
+        <v>23.521</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1670,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46128.05208333334</v>
+        <v>46129.05208333334</v>
       </c>
       <c r="B7">
-        <v>27.898</v>
+        <v>1.374</v>
       </c>
       <c r="C7">
-        <v>-41.227</v>
+        <v>11.503</v>
       </c>
       <c r="D7">
-        <v>-41.227</v>
+        <v>11.503</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1690,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46128.0625</v>
+        <v>46129.0625</v>
       </c>
       <c r="B8">
-        <v>49.083</v>
+        <v>17.415</v>
       </c>
       <c r="C8">
-        <v>-270.44</v>
+        <v>11.758</v>
       </c>
       <c r="D8">
-        <v>-270.44</v>
+        <v>11.758</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1710,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46128.07291666666</v>
+        <v>46129.07291666666</v>
       </c>
       <c r="B9">
-        <v>23.841</v>
+        <v>22.052</v>
       </c>
       <c r="C9">
-        <v>-230.508</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>-230.508</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1730,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46128.08333333334</v>
+        <v>46129.08333333334</v>
       </c>
       <c r="B10">
-        <v>25.198</v>
+        <v>45.62</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>54.257</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>54.257</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1750,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46128.09375</v>
+        <v>46129.09375</v>
       </c>
       <c r="B11">
-        <v>18.183</v>
+        <v>43.437</v>
       </c>
       <c r="C11">
-        <v>28.597</v>
+        <v>-125.917</v>
       </c>
       <c r="D11">
-        <v>28.597</v>
+        <v>-125.917</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1770,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46128.10416666666</v>
+        <v>46129.10416666666</v>
       </c>
       <c r="B12">
-        <v>32.962</v>
+        <v>35.197</v>
       </c>
       <c r="C12">
-        <v>-61.647</v>
+        <v>17.601</v>
       </c>
       <c r="D12">
-        <v>-61.647</v>
+        <v>17.601</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1790,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46128.11458333334</v>
+        <v>46129.11458333334</v>
       </c>
       <c r="B13">
-        <v>19.617</v>
+        <v>30.173</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>34.159</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>34.159</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1810,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46128.125</v>
+        <v>46129.125</v>
       </c>
       <c r="B14">
-        <v>21.431</v>
+        <v>46.387</v>
       </c>
       <c r="C14">
-        <v>-2.018</v>
+        <v>179.01</v>
       </c>
       <c r="D14">
-        <v>-2.018</v>
+        <v>179.01</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1830,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46128.13541666666</v>
+        <v>46129.13541666666</v>
       </c>
       <c r="B15">
-        <v>8.673</v>
+        <v>52.983</v>
       </c>
       <c r="C15">
-        <v>143.147</v>
+        <v>140.894</v>
       </c>
       <c r="D15">
-        <v>143.147</v>
+        <v>140.894</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1850,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46128.14583333334</v>
+        <v>46129.14583333334</v>
       </c>
       <c r="B16">
-        <v>18.244</v>
+        <v>31.174</v>
       </c>
       <c r="C16">
-        <v>21.838</v>
+        <v>53.078</v>
       </c>
       <c r="D16">
-        <v>21.838</v>
+        <v>53.078</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1870,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46128.15625</v>
+        <v>46129.15625</v>
       </c>
       <c r="B17">
-        <v>6.008</v>
+        <v>-4.987</v>
       </c>
       <c r="C17">
-        <v>123.427</v>
+        <v>865.535</v>
       </c>
       <c r="D17">
-        <v>123.427</v>
+        <v>865.535</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1890,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46128.16666666666</v>
+        <v>46129.16666666666</v>
       </c>
       <c r="B18">
-        <v>5.97</v>
+        <v>3.804</v>
       </c>
       <c r="C18">
-        <v>99.179</v>
+        <v>146.595</v>
       </c>
       <c r="D18">
-        <v>99.179</v>
+        <v>146.595</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1910,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46128.17708333334</v>
+        <v>46129.17708333334</v>
       </c>
       <c r="B19">
-        <v>4.901</v>
+        <v>14.364</v>
       </c>
       <c r="C19">
-        <v>127.864</v>
+        <v>12.677</v>
       </c>
       <c r="D19">
-        <v>127.864</v>
+        <v>12.677</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1930,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46128.1875</v>
+        <v>46129.1875</v>
       </c>
       <c r="B20">
-        <v>21.227</v>
+        <v>3.425</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>132.97</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>132.97</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1950,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46128.19791666666</v>
+        <v>46129.19791666666</v>
       </c>
       <c r="B21">
-        <v>11.323</v>
+        <v>-10.913</v>
       </c>
       <c r="C21">
-        <v>52.319</v>
+        <v>811.647</v>
       </c>
       <c r="D21">
-        <v>52.319</v>
+        <v>811.647</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1970,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46128.20833333334</v>
+        <v>46129.20833333334</v>
       </c>
       <c r="B22">
-        <v>21.133</v>
+        <v>33.929</v>
       </c>
       <c r="C22">
-        <v>16.139</v>
+        <v>10.286</v>
       </c>
       <c r="D22">
-        <v>16.139</v>
+        <v>10.286</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1990,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46128.21875</v>
+        <v>46129.21875</v>
       </c>
       <c r="B23">
-        <v>-4.357</v>
+        <v>24.287</v>
       </c>
       <c r="C23">
-        <v>800</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D23">
-        <v>800</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +2010,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46128.22916666666</v>
+        <v>46129.22916666666</v>
       </c>
       <c r="B24">
-        <v>12.604</v>
+        <v>37.998</v>
       </c>
       <c r="C24">
-        <v>260.777</v>
+        <v>196.915</v>
       </c>
       <c r="D24">
-        <v>260.777</v>
+        <v>196.915</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +2030,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46128.23958333334</v>
+        <v>46129.23958333334</v>
       </c>
       <c r="B25">
-        <v>8.949</v>
+        <v>18.805</v>
       </c>
       <c r="C25">
-        <v>55.855</v>
+        <v>280.022</v>
       </c>
       <c r="D25">
-        <v>55.855</v>
+        <v>280.022</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +2050,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46128.25</v>
+        <v>46129.25</v>
       </c>
       <c r="B26">
-        <v>40.67</v>
+        <v>-13.32</v>
       </c>
       <c r="C26">
-        <v>107.57</v>
+        <v>1640.63</v>
       </c>
       <c r="D26">
-        <v>107.57</v>
+        <v>1640.63</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +2070,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46128.26041666666</v>
+        <v>46129.26041666666</v>
       </c>
       <c r="B27">
-        <v>29.402</v>
+        <v>-58.883</v>
       </c>
       <c r="C27">
-        <v>260.141</v>
+        <v>1322.752</v>
       </c>
       <c r="D27">
-        <v>260.141</v>
+        <v>1322.752</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +2090,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46128.27083333334</v>
+        <v>46129.27083333334</v>
       </c>
       <c r="B28">
-        <v>28.183</v>
+        <v>-10.618</v>
       </c>
       <c r="C28">
-        <v>-194.492</v>
+        <v>840.367</v>
       </c>
       <c r="D28">
-        <v>-194.492</v>
+        <v>840.367</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +2110,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46128.28125</v>
+        <v>46129.28125</v>
       </c>
       <c r="B29">
-        <v>44.817</v>
+        <v>3.158</v>
       </c>
       <c r="C29">
-        <v>-1204.343</v>
+        <v>127.575</v>
       </c>
       <c r="D29">
-        <v>-1204.343</v>
+        <v>127.575</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +2130,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46128.29166666666</v>
+        <v>46129.29166666666</v>
       </c>
       <c r="B30">
-        <v>87.47799999999999</v>
+        <v>38.352</v>
       </c>
       <c r="C30">
-        <v>-835.7910000000001</v>
+        <v>95.242</v>
       </c>
       <c r="D30">
-        <v>-835.7910000000001</v>
+        <v>95.242</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +2150,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46128.30208333334</v>
+        <v>46129.30208333334</v>
       </c>
       <c r="B31">
-        <v>80.97499999999999</v>
+        <v>20.782</v>
       </c>
       <c r="C31">
-        <v>19.815</v>
+        <v>53.983</v>
       </c>
       <c r="D31">
-        <v>19.815</v>
+        <v>53.983</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +2170,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46128.3125</v>
+        <v>46129.3125</v>
       </c>
       <c r="B32">
-        <v>31.446</v>
+        <v>33.71</v>
       </c>
       <c r="C32">
-        <v>21.812</v>
+        <v>61.16</v>
       </c>
       <c r="D32">
-        <v>21.812</v>
+        <v>61.16</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +2190,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46128.32291666666</v>
+        <v>46129.32291666666</v>
       </c>
       <c r="B33">
-        <v>53.329</v>
+        <v>12.061</v>
       </c>
       <c r="C33">
-        <v>15.851</v>
+        <v>119.157</v>
       </c>
       <c r="D33">
-        <v>15.851</v>
+        <v>119.157</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +2210,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46128.33333333334</v>
+        <v>46129.33333333334</v>
       </c>
       <c r="B34">
-        <v>1.148</v>
+        <v>13.807</v>
       </c>
       <c r="C34">
-        <v>1.873</v>
+        <v>139.996</v>
       </c>
       <c r="D34">
-        <v>1.873</v>
+        <v>139.996</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +2230,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46128.34375</v>
+        <v>46129.34375</v>
       </c>
       <c r="B35">
-        <v>2.821</v>
+        <v>-5.418</v>
       </c>
       <c r="C35">
-        <v>0.75</v>
+        <v>732.774</v>
       </c>
       <c r="D35">
-        <v>0.75</v>
+        <v>732.774</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +2250,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46128.35416666666</v>
+        <v>46129.35416666666</v>
       </c>
       <c r="B36">
-        <v>20.196</v>
+        <v>44.775</v>
       </c>
       <c r="C36">
-        <v>0.416</v>
+        <v>-404.801</v>
       </c>
       <c r="D36">
-        <v>0.416</v>
+        <v>-404.801</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +2270,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46128.36458333334</v>
+        <v>46129.36458333334</v>
       </c>
       <c r="B37">
-        <v>56.256</v>
+        <v>49.925</v>
       </c>
       <c r="C37">
-        <v>12.835</v>
+        <v>-824.0069999999999</v>
       </c>
       <c r="D37">
-        <v>12.835</v>
+        <v>-824.0069999999999</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +2290,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46128.375</v>
+        <v>46129.375</v>
       </c>
       <c r="B38">
-        <v>50.726</v>
+        <v>-20.477</v>
       </c>
       <c r="C38">
-        <v>9.959</v>
+        <v>875.174</v>
       </c>
       <c r="D38">
-        <v>9.959</v>
+        <v>875.174</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +2310,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46128.38541666666</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="B39">
-        <v>58.042</v>
+        <v>-7.59</v>
       </c>
       <c r="C39">
-        <v>10.991</v>
+        <v>716.356</v>
       </c>
       <c r="D39">
-        <v>10.991</v>
+        <v>716.356</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +2330,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46128.39583333334</v>
+        <v>46129.39583333334</v>
       </c>
       <c r="B40">
-        <v>80.90900000000001</v>
+        <v>26.674</v>
       </c>
       <c r="C40">
-        <v>-4.674</v>
+        <v>19.428</v>
       </c>
       <c r="D40">
-        <v>-4.674</v>
+        <v>19.428</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +2350,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46128.40625</v>
+        <v>46129.40625</v>
       </c>
       <c r="B41">
-        <v>97.53700000000001</v>
+        <v>26.824</v>
       </c>
       <c r="C41">
-        <v>-330.36</v>
+        <v>69.723</v>
       </c>
       <c r="D41">
-        <v>-330.36</v>
+        <v>69.723</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +2370,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46128.41666666666</v>
+        <v>46129.41666666666</v>
       </c>
       <c r="B42">
-        <v>74.474</v>
+        <v>35.037</v>
       </c>
       <c r="C42">
-        <v>-22.219</v>
+        <v>-12.304</v>
       </c>
       <c r="D42">
-        <v>-22.219</v>
+        <v>-12.304</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +2390,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46128.42708333334</v>
+        <v>46129.42708333334</v>
       </c>
       <c r="B43">
-        <v>100.254</v>
+        <v>17.095</v>
       </c>
       <c r="C43">
-        <v>3.089</v>
+        <v>-203.139</v>
       </c>
       <c r="D43">
-        <v>3.089</v>
+        <v>-203.139</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +2410,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46128.4375</v>
+        <v>46129.4375</v>
       </c>
       <c r="B44">
-        <v>122.602</v>
+        <v>0.926</v>
       </c>
       <c r="C44">
-        <v>-68.73999999999999</v>
+        <v>-138.332</v>
       </c>
       <c r="D44">
-        <v>-68.73999999999999</v>
+        <v>-138.332</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +2430,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46128.44791666666</v>
+        <v>46129.44791666666</v>
       </c>
       <c r="B45">
-        <v>108.861</v>
+        <v>18.855</v>
       </c>
       <c r="C45">
-        <v>-570.803</v>
+        <v>-223.825</v>
       </c>
       <c r="D45">
-        <v>-570.803</v>
+        <v>-223.825</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +2450,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46128.45833333334</v>
+        <v>46129.45833333334</v>
       </c>
       <c r="B46">
-        <v>144.355</v>
+        <v>28.534</v>
       </c>
       <c r="C46">
-        <v>-481.625</v>
+        <v>-66.886</v>
       </c>
       <c r="D46">
-        <v>-481.625</v>
+        <v>-66.886</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +2470,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46128.46875</v>
+        <v>46129.46875</v>
       </c>
       <c r="B47">
-        <v>123.098</v>
+        <v>-14.567</v>
       </c>
       <c r="C47">
-        <v>-43.029</v>
+        <v>499</v>
       </c>
       <c r="D47">
-        <v>-43.029</v>
+        <v>499</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +2490,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46128.47916666666</v>
+        <v>46129.47916666666</v>
       </c>
       <c r="B48">
-        <v>125.364</v>
+        <v>7.466</v>
       </c>
       <c r="C48">
-        <v>-2.448</v>
+        <v>101.275</v>
       </c>
       <c r="D48">
-        <v>-2.448</v>
+        <v>101.275</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +2510,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46128.48958333334</v>
+        <v>46129.48958333334</v>
       </c>
       <c r="B49">
-        <v>110.943</v>
+        <v>43</v>
       </c>
       <c r="C49">
-        <v>7.148</v>
+        <v>-211.225</v>
       </c>
       <c r="D49">
-        <v>7.148</v>
+        <v>-211.225</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +2530,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46128.5</v>
+        <v>46129.5</v>
       </c>
       <c r="B50">
-        <v>67.20099999999999</v>
+        <v>32.717</v>
       </c>
       <c r="C50">
-        <v>0.6929999999999999</v>
+        <v>-819.492</v>
       </c>
       <c r="D50">
-        <v>0.6929999999999999</v>
+        <v>-819.492</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +2550,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46128.51041666666</v>
+        <v>46129.51041666666</v>
       </c>
       <c r="B51">
-        <v>50.13</v>
+        <v>37.469</v>
       </c>
       <c r="C51">
-        <v>0.053</v>
+        <v>-904.888</v>
       </c>
       <c r="D51">
-        <v>0.053</v>
+        <v>-904.888</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +2570,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46128.52083333334</v>
+        <v>46129.52083333334</v>
       </c>
       <c r="B52">
-        <v>172.656</v>
+        <v>31.608</v>
       </c>
       <c r="C52">
-        <v>5.169</v>
+        <v>4.672</v>
       </c>
       <c r="D52">
-        <v>5.169</v>
+        <v>4.672</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2590,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46128.53125</v>
+        <v>46129.53125</v>
       </c>
       <c r="B53">
-        <v>188.477</v>
+        <v>51.793</v>
       </c>
       <c r="C53">
-        <v>4.435</v>
+        <v>-22.135</v>
       </c>
       <c r="D53">
-        <v>4.435</v>
+        <v>-22.135</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2610,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46128.54166666666</v>
+        <v>46129.54166666666</v>
       </c>
       <c r="B54">
-        <v>112.648</v>
+        <v>57.974</v>
       </c>
       <c r="C54">
-        <v>0.372</v>
+        <v>23.478</v>
       </c>
       <c r="D54">
-        <v>0.372</v>
+        <v>23.478</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2630,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46128.55208333334</v>
+        <v>46129.55208333334</v>
       </c>
       <c r="B55">
-        <v>89.149</v>
+        <v>113.887</v>
       </c>
       <c r="C55">
-        <v>1.31</v>
+        <v>12.966</v>
       </c>
       <c r="D55">
-        <v>1.31</v>
+        <v>12.966</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2650,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46128.5625</v>
+        <v>46129.5625</v>
       </c>
       <c r="B56">
-        <v>53.56</v>
+        <v>114.603</v>
       </c>
       <c r="C56">
-        <v>5.689</v>
+        <v>-154.288</v>
       </c>
       <c r="D56">
-        <v>5.689</v>
+        <v>-154.288</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2670,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46128.57291666666</v>
+        <v>46129.57291666666</v>
       </c>
       <c r="B57">
-        <v>40.543</v>
+        <v>66.953</v>
       </c>
       <c r="C57">
-        <v>0.38</v>
+        <v>-168.951</v>
       </c>
       <c r="D57">
-        <v>0.38</v>
+        <v>-168.951</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2690,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46128.58333333334</v>
+        <v>46129.58333333334</v>
       </c>
       <c r="B58">
-        <v>37.902</v>
+        <v>106.665</v>
       </c>
       <c r="C58">
-        <v>0.592</v>
+        <v>-509.471</v>
       </c>
       <c r="D58">
-        <v>0.592</v>
+        <v>-509.471</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2710,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46128.59375</v>
+        <v>46129.59375</v>
       </c>
       <c r="B59">
-        <v>13.274</v>
+        <v>55.416</v>
       </c>
       <c r="C59">
-        <v>0.2</v>
+        <v>0.191</v>
       </c>
       <c r="D59">
-        <v>0.2</v>
+        <v>0.191</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2730,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46128.60416666666</v>
+        <v>46129.60416666666</v>
       </c>
       <c r="B60">
-        <v>48.867</v>
+        <v>66.937</v>
       </c>
       <c r="C60">
-        <v>0.354</v>
+        <v>2.02</v>
       </c>
       <c r="D60">
-        <v>0.354</v>
+        <v>2.02</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2750,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46128.61458333334</v>
+        <v>46129.61458333334</v>
       </c>
       <c r="B61">
-        <v>119.268</v>
+        <v>58.791</v>
       </c>
       <c r="C61">
-        <v>-5372.954</v>
+        <v>5.527</v>
       </c>
       <c r="D61">
-        <v>-5372.954</v>
+        <v>5.527</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2770,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46128.625</v>
+        <v>46129.625</v>
       </c>
       <c r="B62">
-        <v>69.06699999999999</v>
+        <v>91.38800000000001</v>
       </c>
       <c r="C62">
-        <v>-4096.39</v>
+        <v>-24.939</v>
       </c>
       <c r="D62">
-        <v>-4096.39</v>
+        <v>-24.939</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2790,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46128.63541666666</v>
+        <v>46129.63541666666</v>
       </c>
       <c r="B63">
-        <v>93.434</v>
+        <v>63.858</v>
       </c>
       <c r="C63">
-        <v>261.259</v>
+        <v>-5.172</v>
       </c>
       <c r="D63">
-        <v>261.259</v>
+        <v>-5.172</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2810,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46128.64583333334</v>
+        <v>46129.64583333334</v>
       </c>
       <c r="B64">
-        <v>93.54600000000001</v>
+        <v>56.964</v>
       </c>
       <c r="C64">
-        <v>-70.211</v>
+        <v>8.41</v>
       </c>
       <c r="D64">
-        <v>-70.211</v>
+        <v>8.41</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2830,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46128.65625</v>
+        <v>46129.65625</v>
       </c>
       <c r="B65">
-        <v>93.258</v>
+        <v>21.863</v>
       </c>
       <c r="C65">
-        <v>12.604</v>
+        <v>0.98</v>
       </c>
       <c r="D65">
-        <v>12.604</v>
+        <v>0.98</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2850,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46128.66666666666</v>
+        <v>46129.66666666666</v>
       </c>
       <c r="B66">
-        <v>82.607</v>
+        <v>19.653</v>
       </c>
       <c r="C66">
-        <v>-202.465</v>
+        <v>0.1</v>
       </c>
       <c r="D66">
-        <v>-202.465</v>
+        <v>0.1</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2870,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46128.67708333334</v>
+        <v>46129.67708333334</v>
       </c>
       <c r="B67">
-        <v>81.48999999999999</v>
+        <v>5.714</v>
       </c>
       <c r="C67">
-        <v>7.439</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>7.439</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2890,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46128.6875</v>
+        <v>46129.6875</v>
       </c>
       <c r="B68">
-        <v>36.647</v>
+        <v>-20.226</v>
       </c>
       <c r="C68">
-        <v>2.642</v>
+        <v>939.2859999999999</v>
       </c>
       <c r="D68">
-        <v>2.642</v>
+        <v>939.2859999999999</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2910,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46128.69791666666</v>
+        <v>46129.69791666666</v>
       </c>
       <c r="B69">
-        <v>53.896</v>
+        <v>-23.053</v>
       </c>
       <c r="C69">
-        <v>18.321</v>
+        <v>925.631</v>
       </c>
       <c r="D69">
-        <v>18.321</v>
+        <v>925.631</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2930,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46128.70833333334</v>
+        <v>46129.70833333334</v>
       </c>
       <c r="B70">
-        <v>48.097</v>
+        <v>-36.788</v>
       </c>
       <c r="C70">
-        <v>207.631</v>
+        <v>699.2430000000001</v>
       </c>
       <c r="D70">
-        <v>207.631</v>
+        <v>699.2430000000001</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2950,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46128.71875</v>
+        <v>46129.71875</v>
       </c>
       <c r="B71">
-        <v>15.536</v>
+        <v>-28.864</v>
       </c>
       <c r="C71">
-        <v>-16.717</v>
+        <v>932.554</v>
       </c>
       <c r="D71">
-        <v>-16.717</v>
+        <v>932.554</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2970,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46128.72916666666</v>
+        <v>46129.72916666666</v>
       </c>
       <c r="B72">
-        <v>1.377</v>
+        <v>-22.257</v>
       </c>
       <c r="C72">
-        <v>335.063</v>
+        <v>938.5170000000001</v>
       </c>
       <c r="D72">
-        <v>335.063</v>
+        <v>938.5170000000001</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2990,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46128.73958333334</v>
+        <v>46129.73958333334</v>
       </c>
       <c r="B73">
-        <v>-18.988</v>
+        <v>17.567</v>
       </c>
       <c r="C73">
-        <v>1127.213</v>
+        <v>-38.196</v>
       </c>
       <c r="D73">
-        <v>1127.213</v>
+        <v>-38.196</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +3010,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46128.75</v>
+        <v>46129.75</v>
       </c>
       <c r="B74">
-        <v>14.821</v>
+        <v>12.805</v>
       </c>
       <c r="C74">
-        <v>86.968</v>
+        <v>-11.389</v>
       </c>
       <c r="D74">
-        <v>86.968</v>
+        <v>-11.389</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +3030,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46128.76041666666</v>
+        <v>46129.76041666666</v>
       </c>
       <c r="B75">
-        <v>-14.223</v>
+        <v>38.646</v>
       </c>
       <c r="C75">
-        <v>977.207</v>
+        <v>124.78</v>
       </c>
       <c r="D75">
-        <v>977.207</v>
+        <v>124.78</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +3050,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46128.77083333334</v>
+        <v>46129.77083333334</v>
       </c>
       <c r="B76">
-        <v>6.18</v>
+        <v>15.152</v>
       </c>
       <c r="C76">
-        <v>304.337</v>
+        <v>259.3</v>
       </c>
       <c r="D76">
-        <v>304.337</v>
+        <v>259.3</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +3070,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46128.78125</v>
+        <v>46129.78125</v>
       </c>
       <c r="B77">
-        <v>20.472</v>
+        <v>52.438</v>
       </c>
       <c r="C77">
-        <v>58.438</v>
+        <v>283.416</v>
       </c>
       <c r="D77">
-        <v>58.438</v>
+        <v>283.416</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +3090,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46128.79166666666</v>
+        <v>46129.79166666666</v>
       </c>
       <c r="B78">
-        <v>40.972</v>
+        <v>115.869</v>
       </c>
       <c r="C78">
-        <v>270.77</v>
+        <v>-4587.101</v>
       </c>
       <c r="D78">
-        <v>270.77</v>
+        <v>-4587.101</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +3110,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46128.80208333334</v>
+        <v>46129.80208333334</v>
       </c>
       <c r="B79">
-        <v>2.949</v>
+        <v>94.504</v>
       </c>
       <c r="C79">
-        <v>278.07</v>
+        <v>38.748</v>
       </c>
       <c r="D79">
-        <v>278.07</v>
+        <v>38.748</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +3130,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46128.8125</v>
+        <v>46129.8125</v>
       </c>
       <c r="B80">
-        <v>3.117</v>
+        <v>27.789</v>
       </c>
       <c r="C80">
-        <v>400</v>
+        <v>82.566</v>
       </c>
       <c r="D80">
-        <v>400</v>
+        <v>82.566</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +3150,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46128.82291666666</v>
+        <v>46129.82291666666</v>
       </c>
       <c r="B81">
-        <v>14.748</v>
+        <v>23.538</v>
       </c>
       <c r="C81">
-        <v>385.464</v>
+        <v>322.223</v>
       </c>
       <c r="D81">
-        <v>385.464</v>
+        <v>322.223</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +3170,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46128.83333333334</v>
+        <v>46129.83333333334</v>
       </c>
       <c r="B82">
-        <v>-34.206</v>
+        <v>24.473</v>
       </c>
       <c r="C82">
-        <v>1126.75</v>
+        <v>44.807</v>
       </c>
       <c r="D82">
-        <v>1126.75</v>
+        <v>44.807</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +3190,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46128.84375</v>
+        <v>46129.84375</v>
       </c>
       <c r="B83">
-        <v>-12.02</v>
+        <v>1.239</v>
       </c>
       <c r="C83">
-        <v>1220.987</v>
+        <v>261.927</v>
       </c>
       <c r="D83">
-        <v>1220.987</v>
+        <v>261.927</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +3210,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46128.85416666666</v>
+        <v>46129.85416666666</v>
       </c>
       <c r="B84">
-        <v>8.887</v>
+        <v>3.974</v>
       </c>
       <c r="C84">
-        <v>351.034</v>
+        <v>295.835</v>
       </c>
       <c r="D84">
-        <v>351.034</v>
+        <v>295.835</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +3230,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46128.86458333334</v>
+        <v>46129.86458333334</v>
       </c>
       <c r="B85">
-        <v>36.507</v>
+        <v>2.508</v>
       </c>
       <c r="C85">
-        <v>382.284</v>
+        <v>253.291</v>
       </c>
       <c r="D85">
-        <v>382.284</v>
+        <v>253.291</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +3250,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46128.875</v>
+        <v>46129.875</v>
       </c>
       <c r="B86">
-        <v>-19.221</v>
+        <v>1.407</v>
       </c>
       <c r="C86">
-        <v>1303.928</v>
+        <v>257.24</v>
       </c>
       <c r="D86">
-        <v>1303.928</v>
+        <v>257.24</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +3270,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46128.88541666666</v>
+        <v>46129.88541666666</v>
       </c>
       <c r="B87">
-        <v>-17.087</v>
+        <v>-25.806</v>
       </c>
       <c r="C87">
-        <v>780</v>
+        <v>1003.376</v>
       </c>
       <c r="D87">
-        <v>780</v>
+        <v>1003.376</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +3290,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46128.89583333334</v>
+        <v>46129.89583333334</v>
       </c>
       <c r="B88">
-        <v>11.36</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="C88">
-        <v>236.451</v>
+        <v>683</v>
       </c>
       <c r="D88">
-        <v>236.451</v>
+        <v>683</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +3310,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46128.90625</v>
+        <v>46129.90625</v>
       </c>
       <c r="B89">
-        <v>24.787</v>
+        <v>3.259</v>
       </c>
       <c r="C89">
-        <v>-112.779</v>
+        <v>257.127</v>
       </c>
       <c r="D89">
-        <v>-112.779</v>
+        <v>257.127</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +3330,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46128.91666666666</v>
+        <v>46129.91666666666</v>
       </c>
       <c r="B90">
-        <v>35.697</v>
+        <v>-15.983</v>
       </c>
       <c r="C90">
-        <v>-1140.45</v>
+        <v>868.809</v>
       </c>
       <c r="D90">
-        <v>-1140.45</v>
+        <v>868.809</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +3350,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46128.92708333334</v>
+        <v>46129.92708333334</v>
       </c>
       <c r="B91">
-        <v>32.127</v>
+        <v>-19.083</v>
       </c>
       <c r="C91">
-        <v>61.907</v>
+        <v>959.742</v>
       </c>
       <c r="D91">
-        <v>61.907</v>
+        <v>959.742</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +3370,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46128.9375</v>
+        <v>46129.9375</v>
       </c>
       <c r="B92">
-        <v>46.674</v>
+        <v>9.516999999999999</v>
       </c>
       <c r="C92">
-        <v>180.152</v>
+        <v>263.95</v>
       </c>
       <c r="D92">
-        <v>180.152</v>
+        <v>263.95</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +3390,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46128.94791666666</v>
+        <v>46129.94791666666</v>
       </c>
       <c r="B93">
-        <v>27.835</v>
+        <v>-1.033</v>
       </c>
       <c r="C93">
-        <v>224.371</v>
+        <v>800</v>
       </c>
       <c r="D93">
-        <v>224.371</v>
+        <v>800</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +3410,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46128.95833333334</v>
+        <v>46129.95833333334</v>
       </c>
       <c r="B94">
-        <v>2.767</v>
+        <v>-6.116</v>
       </c>
       <c r="C94">
-        <v>318.011</v>
+        <v>898.917</v>
       </c>
       <c r="D94">
-        <v>318.011</v>
+        <v>898.917</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +3430,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46128.96875</v>
+        <v>46129.96875</v>
       </c>
       <c r="B95">
-        <v>-3.525</v>
+        <v>-7.142</v>
       </c>
       <c r="C95">
-        <v>835.809</v>
+        <v>890.6319999999999</v>
       </c>
       <c r="D95">
-        <v>835.809</v>
+        <v>890.6319999999999</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +3450,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46128.97916666666</v>
+        <v>46129.97916666666</v>
       </c>
       <c r="B96">
-        <v>12.561</v>
+        <v>20.209</v>
       </c>
       <c r="C96">
-        <v>93.474</v>
+        <v>332.445</v>
       </c>
       <c r="D96">
-        <v>93.474</v>
+        <v>332.445</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +3470,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46128.98958333334</v>
+        <v>46129.98958333334</v>
       </c>
       <c r="B97">
-        <v>0.239</v>
+        <v>6.333</v>
       </c>
       <c r="C97">
-        <v>115.488</v>
+        <v>-35.598</v>
       </c>
       <c r="D97">
-        <v>115.488</v>
+        <v>-35.598</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +3490,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B98">
-        <v>2.306</v>
+        <v>20.699</v>
       </c>
       <c r="C98">
-        <v>247.43</v>
+        <v>191.446</v>
       </c>
       <c r="D98">
-        <v>247.43</v>
+        <v>191.446</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +3510,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46129.01041666666</v>
+        <v>46130.01041666666</v>
       </c>
       <c r="B99">
-        <v>-5.658</v>
+        <v>4.881</v>
       </c>
       <c r="C99">
-        <v>899.446</v>
+        <v>326.842</v>
       </c>
       <c r="D99">
-        <v>899.446</v>
+        <v>326.842</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +3530,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46129.02083333334</v>
+        <v>46130.02083333334</v>
       </c>
       <c r="B100">
-        <v>5.362</v>
+        <v>-14.886</v>
       </c>
       <c r="C100">
-        <v>262.143</v>
+        <v>955.5599999999999</v>
       </c>
       <c r="D100">
-        <v>262.143</v>
+        <v>955.5599999999999</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +3550,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46129.03125</v>
+        <v>46130.03125</v>
       </c>
       <c r="B101">
-        <v>-1.069</v>
+        <v>12.398</v>
       </c>
       <c r="C101">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="D101">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +3570,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46129.04166666666</v>
+        <v>46130.04166666666</v>
       </c>
       <c r="B102">
-        <v>5.417</v>
+        <v>-8.138</v>
       </c>
       <c r="C102">
-        <v>23.521</v>
+        <v>899.841</v>
       </c>
       <c r="D102">
-        <v>23.521</v>
+        <v>899.841</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3590,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46129.05208333334</v>
+        <v>46130.05208333334</v>
       </c>
       <c r="B103">
-        <v>1.374</v>
+        <v>-4.915</v>
       </c>
       <c r="C103">
-        <v>11.503</v>
+        <v>899.177</v>
       </c>
       <c r="D103">
-        <v>11.503</v>
+        <v>899.177</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3610,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46129.0625</v>
+        <v>46130.0625</v>
       </c>
       <c r="B104">
-        <v>17.415</v>
+        <v>-4.879</v>
       </c>
       <c r="C104">
-        <v>11.758</v>
+        <v>899.153</v>
       </c>
       <c r="D104">
-        <v>11.758</v>
+        <v>899.153</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3630,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46129.07291666666</v>
+        <v>46130.07291666666</v>
       </c>
       <c r="B105">
-        <v>22.052</v>
+        <v>35.864</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>262.348</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>262.348</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3650,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46129.08333333334</v>
+        <v>46130.08333333334</v>
       </c>
       <c r="B106">
-        <v>45.62</v>
+        <v>27.631</v>
       </c>
       <c r="C106">
-        <v>54.257</v>
+        <v>278.015</v>
       </c>
       <c r="D106">
-        <v>54.257</v>
+        <v>278.015</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3670,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46129.09375</v>
+        <v>46130.09375</v>
       </c>
       <c r="B107">
-        <v>43.437</v>
+        <v>39.892</v>
       </c>
       <c r="C107">
-        <v>-125.917</v>
+        <v>277.489</v>
       </c>
       <c r="D107">
-        <v>-125.917</v>
+        <v>277.489</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3690,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46129.10416666666</v>
+        <v>46130.10416666666</v>
       </c>
       <c r="B108">
-        <v>35.197</v>
+        <v>36</v>
       </c>
       <c r="C108">
-        <v>17.601</v>
+        <v>236.298</v>
       </c>
       <c r="D108">
-        <v>17.601</v>
+        <v>236.298</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3710,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46129.11458333334</v>
+        <v>46130.11458333334</v>
       </c>
       <c r="B109">
-        <v>30.173</v>
+        <v>48.379</v>
       </c>
       <c r="C109">
-        <v>34.159</v>
+        <v>135.344</v>
       </c>
       <c r="D109">
-        <v>34.159</v>
+        <v>135.344</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3730,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46129.125</v>
+        <v>46130.125</v>
       </c>
       <c r="B110">
-        <v>46.387</v>
+        <v>31.482</v>
       </c>
       <c r="C110">
-        <v>179.01</v>
+        <v>156.64</v>
       </c>
       <c r="D110">
-        <v>179.01</v>
+        <v>156.64</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3750,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46129.13541666666</v>
+        <v>46130.13541666666</v>
       </c>
       <c r="B111">
-        <v>52.983</v>
+        <v>16.804</v>
       </c>
       <c r="C111">
-        <v>140.894</v>
+        <v>141.78</v>
       </c>
       <c r="D111">
-        <v>140.894</v>
+        <v>141.78</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3770,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46129.14583333334</v>
+        <v>46130.14583333334</v>
       </c>
       <c r="B112">
-        <v>31.174</v>
+        <v>-12.562</v>
       </c>
       <c r="C112">
-        <v>53.078</v>
+        <v>289.974</v>
       </c>
       <c r="D112">
-        <v>53.078</v>
+        <v>289.974</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3790,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46129.15625</v>
+        <v>46130.15625</v>
       </c>
       <c r="B113">
-        <v>-4.987</v>
+        <v>8.308999999999999</v>
       </c>
       <c r="C113">
-        <v>865.535</v>
+        <v>130.858</v>
       </c>
       <c r="D113">
-        <v>865.535</v>
+        <v>130.858</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3810,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46129.16666666666</v>
+        <v>46130.16666666666</v>
       </c>
       <c r="B114">
-        <v>3.804</v>
+        <v>-18.105</v>
       </c>
       <c r="C114">
-        <v>146.595</v>
+        <v>924.567</v>
       </c>
       <c r="D114">
-        <v>146.595</v>
+        <v>924.567</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3830,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46129.17708333334</v>
+        <v>46130.17708333334</v>
       </c>
       <c r="B115">
-        <v>14.364</v>
+        <v>-25.43</v>
       </c>
       <c r="C115">
-        <v>12.677</v>
+        <v>966.022</v>
       </c>
       <c r="D115">
-        <v>12.677</v>
+        <v>966.022</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3850,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46129.1875</v>
+        <v>46130.1875</v>
       </c>
       <c r="B116">
-        <v>3.425</v>
+        <v>-77.63</v>
       </c>
       <c r="C116">
-        <v>132.97</v>
+        <v>5223.212</v>
       </c>
       <c r="D116">
-        <v>132.97</v>
+        <v>5223.212</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3870,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46129.19791666666</v>
+        <v>46130.19791666666</v>
       </c>
       <c r="B117">
-        <v>-10.913</v>
+        <v>-132.662</v>
       </c>
       <c r="C117">
-        <v>811.647</v>
+        <v>6827.918</v>
       </c>
       <c r="D117">
-        <v>811.647</v>
+        <v>6827.918</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3890,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46129.20833333334</v>
+        <v>46130.20833333334</v>
       </c>
       <c r="B118">
-        <v>33.929</v>
+        <v>-190.287</v>
       </c>
       <c r="C118">
-        <v>10.286</v>
+        <v>5585.544</v>
       </c>
       <c r="D118">
-        <v>10.286</v>
+        <v>5585.544</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3910,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46129.21875</v>
+        <v>46130.21875</v>
       </c>
       <c r="B119">
-        <v>24.287</v>
+        <v>-74.44799999999999</v>
       </c>
       <c r="C119">
-        <v>90.90000000000001</v>
+        <v>1046.327</v>
       </c>
       <c r="D119">
-        <v>90.90000000000001</v>
+        <v>1046.327</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3930,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46129.22916666666</v>
+        <v>46130.22916666666</v>
       </c>
       <c r="B120">
-        <v>37.998</v>
+        <v>-70.21899999999999</v>
       </c>
       <c r="C120">
-        <v>196.915</v>
+        <v>1030.44</v>
       </c>
       <c r="D120">
-        <v>196.915</v>
+        <v>1030.44</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3950,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46129.23958333334</v>
+        <v>46130.23958333334</v>
       </c>
       <c r="B121">
-        <v>18.805</v>
+        <v>-72.128</v>
       </c>
       <c r="C121">
-        <v>280.022</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>280.022</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3970,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46129.25</v>
+        <v>46130.25</v>
       </c>
       <c r="B122">
-        <v>-13.32</v>
+        <v>-119.327</v>
       </c>
       <c r="C122">
-        <v>1640.63</v>
+        <v>1025.614</v>
       </c>
       <c r="D122">
-        <v>1640.63</v>
+        <v>1025.614</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3990,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46129.26041666666</v>
+        <v>46130.26041666666</v>
       </c>
       <c r="B123">
-        <v>-58.883</v>
+        <v>-105.988</v>
       </c>
       <c r="C123">
-        <v>1322.752</v>
+        <v>1026.091</v>
       </c>
       <c r="D123">
-        <v>1322.752</v>
+        <v>1026.091</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +4010,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46129.27083333334</v>
+        <v>46130.27083333334</v>
       </c>
       <c r="B124">
-        <v>-10.618</v>
+        <v>-133.803</v>
       </c>
       <c r="C124">
-        <v>840.367</v>
+        <v>2453.284</v>
       </c>
       <c r="D124">
-        <v>840.367</v>
+        <v>2453.284</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +4030,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46129.28125</v>
+        <v>46130.28125</v>
       </c>
       <c r="B125">
-        <v>3.158</v>
+        <v>-187.155</v>
       </c>
       <c r="C125">
-        <v>127.575</v>
+        <v>4354.803</v>
       </c>
       <c r="D125">
-        <v>127.575</v>
+        <v>4354.803</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +4050,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46129.29166666666</v>
+        <v>46130.29166666666</v>
       </c>
       <c r="B126">
-        <v>38.352</v>
+        <v>-263.916</v>
       </c>
       <c r="C126">
-        <v>95.242</v>
+        <v>1122.315</v>
       </c>
       <c r="D126">
-        <v>95.242</v>
+        <v>1122.315</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +4070,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46129.30208333334</v>
+        <v>46130.30208333334</v>
       </c>
       <c r="B127">
-        <v>20.782</v>
+        <v>-153.025</v>
       </c>
       <c r="C127">
-        <v>53.983</v>
+        <v>1056.164</v>
       </c>
       <c r="D127">
-        <v>53.983</v>
+        <v>1056.164</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +4090,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46129.3125</v>
+        <v>46130.3125</v>
       </c>
       <c r="B128">
-        <v>33.71</v>
+        <v>-96.896</v>
       </c>
       <c r="C128">
-        <v>61.16</v>
+        <v>947.99</v>
       </c>
       <c r="D128">
-        <v>61.16</v>
+        <v>947.99</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +4110,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46129.32291666666</v>
+        <v>46130.32291666666</v>
       </c>
       <c r="B129">
-        <v>12.061</v>
+        <v>-65.89</v>
       </c>
       <c r="C129">
-        <v>119.157</v>
+        <v>947.966</v>
       </c>
       <c r="D129">
-        <v>119.157</v>
+        <v>947.966</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +4130,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46129.33333333334</v>
+        <v>46130.33333333334</v>
       </c>
       <c r="B130">
-        <v>13.807</v>
+        <v>-68.515</v>
       </c>
       <c r="C130">
-        <v>139.996</v>
+        <v>736.29</v>
       </c>
       <c r="D130">
-        <v>139.996</v>
+        <v>736.29</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +4150,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46129.34375</v>
+        <v>46130.34375</v>
       </c>
       <c r="B131">
-        <v>-5.418</v>
+        <v>-26.839</v>
       </c>
       <c r="C131">
-        <v>732.774</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>732.774</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +4170,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46129.35416666666</v>
+        <v>46130.35416666666</v>
       </c>
       <c r="B132">
-        <v>44.775</v>
+        <v>-69.452</v>
       </c>
       <c r="C132">
-        <v>-404.801</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>-404.801</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +4190,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46129.36458333334</v>
+        <v>46130.36458333334</v>
       </c>
       <c r="B133">
-        <v>49.925</v>
+        <v>-55.003</v>
       </c>
       <c r="C133">
-        <v>-824.0069999999999</v>
+        <v>774.672</v>
       </c>
       <c r="D133">
-        <v>-824.0069999999999</v>
+        <v>774.672</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +4210,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46129.375</v>
+        <v>46130.375</v>
       </c>
       <c r="B134">
-        <v>-20.477</v>
+        <v>-3.422</v>
       </c>
       <c r="C134">
-        <v>875.174</v>
+        <v>496.167</v>
       </c>
       <c r="D134">
-        <v>875.174</v>
+        <v>496.167</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +4230,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46129.38541666666</v>
+        <v>46130.38541666666</v>
       </c>
       <c r="B135">
-        <v>-7.59</v>
+        <v>38.347</v>
       </c>
       <c r="C135">
-        <v>716.356</v>
+        <v>-3516.693</v>
       </c>
       <c r="D135">
-        <v>716.356</v>
+        <v>-3516.693</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +4250,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46129.39583333334</v>
+        <v>46130.39583333334</v>
       </c>
       <c r="B136">
-        <v>26.674</v>
+        <v>50.238</v>
       </c>
       <c r="C136">
-        <v>19.428</v>
+        <v>-5094.809</v>
       </c>
       <c r="D136">
-        <v>19.428</v>
+        <v>-5094.809</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +4270,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46129.40625</v>
+        <v>46130.40625</v>
       </c>
       <c r="B137">
-        <v>26.824</v>
+        <v>83.13200000000001</v>
       </c>
       <c r="C137">
-        <v>69.723</v>
+        <v>-7326.441</v>
       </c>
       <c r="D137">
-        <v>69.723</v>
+        <v>-7326.441</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +4290,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46129.41666666666</v>
+        <v>46130.41666666666</v>
       </c>
       <c r="B138">
-        <v>35.037</v>
+        <v>50.31</v>
       </c>
       <c r="C138">
-        <v>-12.304</v>
+        <v>-890.89</v>
       </c>
       <c r="D138">
-        <v>-12.304</v>
+        <v>-890.89</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +4310,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46129.42708333334</v>
+        <v>46130.42708333334</v>
       </c>
       <c r="B139">
-        <v>17.095</v>
+        <v>80.38800000000001</v>
       </c>
       <c r="C139">
-        <v>-203.139</v>
+        <v>-826.754</v>
       </c>
       <c r="D139">
-        <v>-203.139</v>
+        <v>-826.754</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +4330,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46129.4375</v>
+        <v>46130.4375</v>
       </c>
       <c r="B140">
-        <v>0.926</v>
+        <v>61.756</v>
       </c>
       <c r="C140">
-        <v>-138.332</v>
+        <v>-466.385</v>
       </c>
       <c r="D140">
-        <v>-138.332</v>
+        <v>-466.385</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +4350,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46129.44791666666</v>
+        <v>46130.44791666666</v>
       </c>
       <c r="B141">
-        <v>18.855</v>
+        <v>72.42100000000001</v>
       </c>
       <c r="C141">
-        <v>-223.825</v>
+        <v>-123.585</v>
       </c>
       <c r="D141">
-        <v>-223.825</v>
+        <v>-123.585</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +4370,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46129.45833333334</v>
+        <v>46130.45833333334</v>
       </c>
       <c r="B142">
-        <v>28.534</v>
+        <v>96.52500000000001</v>
       </c>
       <c r="C142">
-        <v>-66.886</v>
+        <v>-5.198</v>
       </c>
       <c r="D142">
-        <v>-66.886</v>
+        <v>-5.198</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +4390,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46129.46875</v>
+        <v>46130.46875</v>
       </c>
       <c r="B143">
-        <v>-14.567</v>
+        <v>95.474</v>
       </c>
       <c r="C143">
-        <v>499</v>
+        <v>-0.356</v>
       </c>
       <c r="D143">
-        <v>499</v>
+        <v>-0.356</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +4410,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46129.47916666666</v>
+        <v>46130.47916666666</v>
       </c>
       <c r="B144">
-        <v>7.466</v>
+        <v>130.276</v>
       </c>
       <c r="C144">
-        <v>101.275</v>
+        <v>-113.624</v>
       </c>
       <c r="D144">
-        <v>101.275</v>
+        <v>-113.624</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +4430,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46129.48958333334</v>
+        <v>46130.48958333334</v>
       </c>
       <c r="B145">
-        <v>43</v>
+        <v>94.827</v>
       </c>
       <c r="C145">
-        <v>-211.225</v>
+        <v>-120.227</v>
       </c>
       <c r="D145">
-        <v>-211.225</v>
+        <v>-120.227</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +4450,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46129.5</v>
+        <v>46130.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>78.782</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1.688</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>1.688</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +4470,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46129.51041666666</v>
+        <v>46130.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>139.62</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +4490,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46129.52083333334</v>
+        <v>46130.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>122.168</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>0.679</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>0.679</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +4510,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46129.53125</v>
+        <v>46130.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>93.541</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>-19.356</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>-19.356</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,16 +4530,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46129.54166666666</v>
+        <v>46130.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>71.101</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>-19.644</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>-19.644</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3974,16 +4550,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46129.55208333334</v>
+        <v>46130.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>87.645</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>-17.997</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>-17.997</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -3994,16 +4570,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46129.5625</v>
+        <v>46130.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>92.566</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>-18.497</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>-18.497</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4014,16 +4590,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46129.57291666666</v>
+        <v>46130.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>74.393</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>-17.467</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>-17.467</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4034,16 +4610,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46129.58333333334</v>
+        <v>46130.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>7.693</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>-19.069</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>-19.069</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4054,10 +4630,10 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46129.59375</v>
+        <v>46130.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>21.875</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -4074,10 +4650,10 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46129.60416666666</v>
+        <v>46130.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>17.85</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -4094,10 +4670,10 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46129.61458333334</v>
+        <v>46130.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>18.094</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -4114,16 +4690,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46129.625</v>
+        <v>46130.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>54.735</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>4.314</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>4.314</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4134,16 +4710,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46129.63541666666</v>
+        <v>46130.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>6.174</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4154,16 +4730,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46129.64583333334</v>
+        <v>46130.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>-54.135</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>4486.337</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>4486.337</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46129.65625</v>
+        <v>46130.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>-18.805</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>771.042</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>771.042</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4194,16 +4770,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46129.66666666666</v>
+        <v>46130.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>6.102</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>-51.409</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>-51.409</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4214,16 +4790,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46129.67708333334</v>
+        <v>46130.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>12.341</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>-11.726</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>-11.726</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4234,16 +4810,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46129.6875</v>
+        <v>46130.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>-34.099</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>1104.296</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>1104.296</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4254,16 +4830,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46129.69791666666</v>
+        <v>46130.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>-61.44</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>809.492</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>809.492</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4274,16 +4850,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46129.70833333334</v>
+        <v>46130.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>34.041</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>-1132.398</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>-1132.398</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4294,16 +4870,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46129.71875</v>
+        <v>46130.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>18.585</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>-390.433</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>-390.433</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4314,16 +4890,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46129.72916666666</v>
+        <v>46130.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>20.95</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>26.859</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>26.859</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4334,16 +4910,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46129.73958333334</v>
+        <v>46130.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>16.612</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>293.782</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>293.782</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4354,16 +4930,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46129.75</v>
+        <v>46130.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>79.846</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>294.259</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>294.259</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4374,16 +4950,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46129.76041666666</v>
+        <v>46130.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>46.399</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>264.58</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>264.58</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4394,16 +4970,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46129.77083333334</v>
+        <v>46130.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>41.805</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>262.892</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>262.892</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4414,16 +4990,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46129.78125</v>
+        <v>46130.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>-32.949</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1033.699</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>1033.699</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4434,16 +5010,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46129.79166666666</v>
+        <v>46130.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>-16.883</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>915.735</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>915.735</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4454,16 +5030,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46129.80208333334</v>
+        <v>46130.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>-35.255</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>1099.405</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>1099.405</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4474,16 +5050,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46129.8125</v>
+        <v>46130.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>-83.533</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>925.078</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>925.078</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4494,16 +5070,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46129.82291666666</v>
+        <v>46130.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>-96.27200000000001</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>1033.129</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>1033.129</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4514,16 +5090,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46129.83333333334</v>
+        <v>46130.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>-138.415</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>1443.322</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>1443.322</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4534,16 +5110,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46129.84375</v>
+        <v>46130.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>-76.901</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>4205.063</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>4205.063</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4554,16 +5130,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46129.85416666666</v>
+        <v>46130.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>-66.64400000000001</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>4811.433</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>4811.433</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4574,16 +5150,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46129.86458333334</v>
+        <v>46130.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>-92.72199999999999</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>3662.135</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>3662.135</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4594,16 +5170,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46129.875</v>
+        <v>46130.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>-29.726</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>1328.537</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>1328.537</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4614,16 +5190,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46129.88541666666</v>
+        <v>46130.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>19.206</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>-404.832</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>-404.832</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4634,16 +5210,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46129.89583333334</v>
+        <v>46130.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>6.788</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>-97.751</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>-97.751</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4654,16 +5230,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46129.90625</v>
+        <v>46130.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>-1.878</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>190.986</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>190.986</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4674,16 +5250,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46129.91666666666</v>
+        <v>46130.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>-41.754</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>1059.91</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>1059.91</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4694,16 +5270,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46129.92708333334</v>
+        <v>46130.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>-58.335</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>934.458</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>934.458</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -4714,16 +5290,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46129.9375</v>
+        <v>46130.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>-61.111</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>951.523</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>951.523</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -4734,16 +5310,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46129.94791666666</v>
+        <v>46130.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>-70.40600000000001</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>699.192</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>699.192</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -4754,16 +5330,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46129.95833333334</v>
+        <v>46130.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>-59.169</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>796.9400000000001</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>796.9400000000001</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -4774,16 +5350,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46129.96875</v>
+        <v>46130.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>-28.272</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -4794,16 +5370,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46129.97916666666</v>
+        <v>46130.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>-32.619</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>847.371</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>847.371</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -4814,22 +5390,3862 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46129.98958333334</v>
+        <v>46130.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>-34.688</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>926.047</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>926.047</v>
       </c>
       <c r="E193">
         <v>96</v>
       </c>
       <c r="F193" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46131</v>
+      </c>
+      <c r="B194">
+        <v>-31.93</v>
+      </c>
+      <c r="C194">
+        <v>894.549</v>
+      </c>
+      <c r="D194">
+        <v>894.549</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46131.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>-44.853</v>
+      </c>
+      <c r="C195">
+        <v>864.91</v>
+      </c>
+      <c r="D195">
+        <v>864.91</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46131.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>-58.047</v>
+      </c>
+      <c r="C196">
+        <v>990.27</v>
+      </c>
+      <c r="D196">
+        <v>990.27</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46131.03125</v>
+      </c>
+      <c r="B197">
+        <v>-28.518</v>
+      </c>
+      <c r="C197">
+        <v>879.587</v>
+      </c>
+      <c r="D197">
+        <v>879.587</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
+        <v>46131.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>12.065</v>
+      </c>
+      <c r="C198">
+        <v>257.973</v>
+      </c>
+      <c r="D198">
+        <v>257.973</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
+        <v>46131.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>-6.984</v>
+      </c>
+      <c r="C199">
+        <v>801.751</v>
+      </c>
+      <c r="D199">
+        <v>801.751</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
+        <v>46131.0625</v>
+      </c>
+      <c r="B200">
+        <v>11.279</v>
+      </c>
+      <c r="C200">
+        <v>58.669</v>
+      </c>
+      <c r="D200">
+        <v>58.669</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
+        <v>46131.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>1.31</v>
+      </c>
+      <c r="C201">
+        <v>87.467</v>
+      </c>
+      <c r="D201">
+        <v>87.467</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
+        <v>46131.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>-4.99</v>
+      </c>
+      <c r="C202">
+        <v>765.921</v>
+      </c>
+      <c r="D202">
+        <v>765.921</v>
+      </c>
+      <c r="E202">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
+        <v>46131.09375</v>
+      </c>
+      <c r="B203">
+        <v>16.801</v>
+      </c>
+      <c r="C203">
+        <v>262.759</v>
+      </c>
+      <c r="D203">
+        <v>262.759</v>
+      </c>
+      <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
+        <v>46131.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>1.67</v>
+      </c>
+      <c r="C204">
+        <v>294.778</v>
+      </c>
+      <c r="D204">
+        <v>294.778</v>
+      </c>
+      <c r="E204">
+        <v>11</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
+        <v>46131.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>-22.925</v>
+      </c>
+      <c r="C205">
+        <v>881.778</v>
+      </c>
+      <c r="D205">
+        <v>881.778</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
+        <v>46131.125</v>
+      </c>
+      <c r="B206">
+        <v>-34.743</v>
+      </c>
+      <c r="C206">
+        <v>886.675</v>
+      </c>
+      <c r="D206">
+        <v>886.675</v>
+      </c>
+      <c r="E206">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
+        <v>46131.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>-19.541</v>
+      </c>
+      <c r="C207">
+        <v>699.03</v>
+      </c>
+      <c r="D207">
+        <v>699.03</v>
+      </c>
+      <c r="E207">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
+        <v>46131.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>8.368</v>
+      </c>
+      <c r="C208">
+        <v>253.286</v>
+      </c>
+      <c r="D208">
+        <v>253.286</v>
+      </c>
+      <c r="E208">
+        <v>15</v>
+      </c>
+      <c r="F208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
+        <v>46131.15625</v>
+      </c>
+      <c r="B209">
+        <v>-2.486</v>
+      </c>
+      <c r="C209">
+        <v>699</v>
+      </c>
+      <c r="D209">
+        <v>699</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
+        <v>46131.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>-26.524</v>
+      </c>
+      <c r="C210">
+        <v>774.898</v>
+      </c>
+      <c r="D210">
+        <v>774.898</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+      <c r="F210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
+        <v>46131.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>-21.966</v>
+      </c>
+      <c r="C211">
+        <v>895.912</v>
+      </c>
+      <c r="D211">
+        <v>895.912</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
+        <v>46131.1875</v>
+      </c>
+      <c r="B212">
+        <v>-52.885</v>
+      </c>
+      <c r="C212">
+        <v>1044.4</v>
+      </c>
+      <c r="D212">
+        <v>1044.4</v>
+      </c>
+      <c r="E212">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
+        <v>46131.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>-64.024</v>
+      </c>
+      <c r="C213">
+        <v>965.205</v>
+      </c>
+      <c r="D213">
+        <v>965.205</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
+        <v>46131.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>-41.142</v>
+      </c>
+      <c r="C214">
+        <v>1007.361</v>
+      </c>
+      <c r="D214">
+        <v>1007.361</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
+        <v>46131.21875</v>
+      </c>
+      <c r="B215">
+        <v>-63.123</v>
+      </c>
+      <c r="C215">
+        <v>840.7140000000001</v>
+      </c>
+      <c r="D215">
+        <v>840.7140000000001</v>
+      </c>
+      <c r="E215">
+        <v>22</v>
+      </c>
+      <c r="F215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
+        <v>46131.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>-36.856</v>
+      </c>
+      <c r="C216">
+        <v>712.912</v>
+      </c>
+      <c r="D216">
+        <v>712.912</v>
+      </c>
+      <c r="E216">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
+        <v>46131.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>5.996</v>
+      </c>
+      <c r="C217">
+        <v>261</v>
+      </c>
+      <c r="D217">
+        <v>261</v>
+      </c>
+      <c r="E217">
+        <v>24</v>
+      </c>
+      <c r="F217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
+        <v>46131.25</v>
+      </c>
+      <c r="B218">
+        <v>17.909</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
+        <v>46131.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>60.665</v>
+      </c>
+      <c r="C219">
+        <v>70.691</v>
+      </c>
+      <c r="D219">
+        <v>70.691</v>
+      </c>
+      <c r="E219">
+        <v>26</v>
+      </c>
+      <c r="F219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
+        <v>46131.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>50.018</v>
+      </c>
+      <c r="C220">
+        <v>14.353</v>
+      </c>
+      <c r="D220">
+        <v>14.353</v>
+      </c>
+      <c r="E220">
+        <v>27</v>
+      </c>
+      <c r="F220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
+        <v>46131.28125</v>
+      </c>
+      <c r="B221">
+        <v>48.876</v>
+      </c>
+      <c r="C221">
+        <v>-6.441</v>
+      </c>
+      <c r="D221">
+        <v>-6.441</v>
+      </c>
+      <c r="E221">
+        <v>28</v>
+      </c>
+      <c r="F221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
+        <v>46131.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>-41.583</v>
+      </c>
+      <c r="C222">
+        <v>702.597</v>
+      </c>
+      <c r="D222">
+        <v>702.597</v>
+      </c>
+      <c r="E222">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
+        <v>46131.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>-24.619</v>
+      </c>
+      <c r="C223">
+        <v>702.501</v>
+      </c>
+      <c r="D223">
+        <v>702.501</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="F223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
+        <v>46131.3125</v>
+      </c>
+      <c r="B224">
+        <v>-3.516</v>
+      </c>
+      <c r="C224">
+        <v>699</v>
+      </c>
+      <c r="D224">
+        <v>699</v>
+      </c>
+      <c r="E224">
+        <v>31</v>
+      </c>
+      <c r="F224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
+        <v>46131.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>28.523</v>
+      </c>
+      <c r="C225">
+        <v>-804.39</v>
+      </c>
+      <c r="D225">
+        <v>-804.39</v>
+      </c>
+      <c r="E225">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
+        <v>46131.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>-80.15600000000001</v>
+      </c>
+      <c r="C226">
+        <v>475.61</v>
+      </c>
+      <c r="D226">
+        <v>475.61</v>
+      </c>
+      <c r="E226">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
+        <v>46131.34375</v>
+      </c>
+      <c r="B227">
+        <v>-33.51</v>
+      </c>
+      <c r="C227">
+        <v>653.557</v>
+      </c>
+      <c r="D227">
+        <v>653.557</v>
+      </c>
+      <c r="E227">
+        <v>34</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
+        <v>46131.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>2.952</v>
+      </c>
+      <c r="C228">
+        <v>-216.083</v>
+      </c>
+      <c r="D228">
+        <v>-216.083</v>
+      </c>
+      <c r="E228">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
+        <v>46131.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>22.252</v>
+      </c>
+      <c r="C229">
+        <v>-473.623</v>
+      </c>
+      <c r="D229">
+        <v>-473.623</v>
+      </c>
+      <c r="E229">
+        <v>36</v>
+      </c>
+      <c r="F229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
+        <v>46131.375</v>
+      </c>
+      <c r="B230">
+        <v>-31.8</v>
+      </c>
+      <c r="C230">
+        <v>450.02</v>
+      </c>
+      <c r="D230">
+        <v>450.02</v>
+      </c>
+      <c r="E230">
+        <v>37</v>
+      </c>
+      <c r="F230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46131.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>-84.035</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46131.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>-33.948</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
+        <v>46131.40625</v>
+      </c>
+      <c r="B233">
+        <v>2.203</v>
+      </c>
+      <c r="C233">
+        <v>130.96</v>
+      </c>
+      <c r="D233">
+        <v>130.96</v>
+      </c>
+      <c r="E233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
+        <v>46131.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>-2.992</v>
+      </c>
+      <c r="C234">
+        <v>450</v>
+      </c>
+      <c r="D234">
+        <v>450</v>
+      </c>
+      <c r="E234">
+        <v>41</v>
+      </c>
+      <c r="F234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
+        <v>46131.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>9.067</v>
+      </c>
+      <c r="C235">
+        <v>-24.93</v>
+      </c>
+      <c r="D235">
+        <v>-24.93</v>
+      </c>
+      <c r="E235">
+        <v>42</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
+        <v>46131.4375</v>
+      </c>
+      <c r="B236">
+        <v>22.517</v>
+      </c>
+      <c r="C236">
+        <v>-153.242</v>
+      </c>
+      <c r="D236">
+        <v>-153.242</v>
+      </c>
+      <c r="E236">
+        <v>43</v>
+      </c>
+      <c r="F236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
+        <v>46131.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>27.498</v>
+      </c>
+      <c r="C237">
+        <v>-360.808</v>
+      </c>
+      <c r="D237">
+        <v>-360.808</v>
+      </c>
+      <c r="E237">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
+        <v>46131.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>-0.09</v>
+      </c>
+      <c r="C238">
+        <v>442.239</v>
+      </c>
+      <c r="D238">
+        <v>442.239</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
+        <v>46131.46875</v>
+      </c>
+      <c r="B239">
+        <v>-17.728</v>
+      </c>
+      <c r="C239">
+        <v>525.323</v>
+      </c>
+      <c r="D239">
+        <v>525.323</v>
+      </c>
+      <c r="E239">
+        <v>46</v>
+      </c>
+      <c r="F239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
+        <v>46131.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>85.184</v>
+      </c>
+      <c r="C240">
+        <v>175.665</v>
+      </c>
+      <c r="D240">
+        <v>175.665</v>
+      </c>
+      <c r="E240">
+        <v>47</v>
+      </c>
+      <c r="F240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
+        <v>46131.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>101.708</v>
+      </c>
+      <c r="C241">
+        <v>229.221</v>
+      </c>
+      <c r="D241">
+        <v>229.221</v>
+      </c>
+      <c r="E241">
+        <v>48</v>
+      </c>
+      <c r="F241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
+        <v>46131.5</v>
+      </c>
+      <c r="B242">
+        <v>52.163</v>
+      </c>
+      <c r="C242">
+        <v>-135.092</v>
+      </c>
+      <c r="D242">
+        <v>-135.092</v>
+      </c>
+      <c r="E242">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
+        <v>46131.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>37.73</v>
+      </c>
+      <c r="C243">
+        <v>-328.983</v>
+      </c>
+      <c r="D243">
+        <v>-328.983</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
+        <v>46131.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>36.699</v>
+      </c>
+      <c r="C244">
+        <v>-494.744</v>
+      </c>
+      <c r="D244">
+        <v>-494.744</v>
+      </c>
+      <c r="E244">
+        <v>51</v>
+      </c>
+      <c r="F244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
+        <v>46131.53125</v>
+      </c>
+      <c r="B245">
+        <v>7.56</v>
+      </c>
+      <c r="C245">
+        <v>31.483</v>
+      </c>
+      <c r="D245">
+        <v>31.483</v>
+      </c>
+      <c r="E245">
+        <v>52</v>
+      </c>
+      <c r="F245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
+        <v>46131.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>-5.263</v>
+      </c>
+      <c r="C246">
+        <v>399</v>
+      </c>
+      <c r="D246">
+        <v>399</v>
+      </c>
+      <c r="E246">
+        <v>53</v>
+      </c>
+      <c r="F246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
+        <v>46131.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>59.09</v>
+      </c>
+      <c r="C247">
+        <v>-343.365</v>
+      </c>
+      <c r="D247">
+        <v>-343.365</v>
+      </c>
+      <c r="E247">
+        <v>54</v>
+      </c>
+      <c r="F247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
+        <v>46131.5625</v>
+      </c>
+      <c r="B248">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="C248">
+        <v>-144.193</v>
+      </c>
+      <c r="D248">
+        <v>-144.193</v>
+      </c>
+      <c r="E248">
+        <v>55</v>
+      </c>
+      <c r="F248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
+        <v>46131.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>47.854</v>
+      </c>
+      <c r="C249">
+        <v>-790.524</v>
+      </c>
+      <c r="D249">
+        <v>-790.524</v>
+      </c>
+      <c r="E249">
+        <v>56</v>
+      </c>
+      <c r="F249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
+        <v>46131.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>71.05800000000001</v>
+      </c>
+      <c r="C250">
+        <v>-127.732</v>
+      </c>
+      <c r="D250">
+        <v>-127.732</v>
+      </c>
+      <c r="E250">
+        <v>57</v>
+      </c>
+      <c r="F250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
+        <v>46131.59375</v>
+      </c>
+      <c r="B251">
+        <v>53.976</v>
+      </c>
+      <c r="C251">
+        <v>-5.253</v>
+      </c>
+      <c r="D251">
+        <v>-5.253</v>
+      </c>
+      <c r="E251">
+        <v>58</v>
+      </c>
+      <c r="F251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
+        <v>46131.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>52.412</v>
+      </c>
+      <c r="C252">
+        <v>-812.1609999999999</v>
+      </c>
+      <c r="D252">
+        <v>-812.1609999999999</v>
+      </c>
+      <c r="E252">
+        <v>59</v>
+      </c>
+      <c r="F252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
+        <v>46131.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>58.428</v>
+      </c>
+      <c r="C253">
+        <v>-1405.836</v>
+      </c>
+      <c r="D253">
+        <v>-1405.836</v>
+      </c>
+      <c r="E253">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
+        <v>46131.625</v>
+      </c>
+      <c r="B254">
+        <v>25.86</v>
+      </c>
+      <c r="C254">
+        <v>-71.185</v>
+      </c>
+      <c r="D254">
+        <v>-71.185</v>
+      </c>
+      <c r="E254">
+        <v>61</v>
+      </c>
+      <c r="F254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
+        <v>46131.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>23.467</v>
+      </c>
+      <c r="C255">
+        <v>1.632</v>
+      </c>
+      <c r="D255">
+        <v>1.632</v>
+      </c>
+      <c r="E255">
+        <v>62</v>
+      </c>
+      <c r="F255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
+        <v>46131.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>2.214</v>
+      </c>
+      <c r="C256">
+        <v>6.375</v>
+      </c>
+      <c r="D256">
+        <v>6.375</v>
+      </c>
+      <c r="E256">
+        <v>63</v>
+      </c>
+      <c r="F256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
+        <v>46131.65625</v>
+      </c>
+      <c r="B257">
+        <v>-5.78</v>
+      </c>
+      <c r="C257">
+        <v>426.396</v>
+      </c>
+      <c r="D257">
+        <v>426.396</v>
+      </c>
+      <c r="E257">
+        <v>64</v>
+      </c>
+      <c r="F257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
+        <v>46131.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>17.125</v>
+      </c>
+      <c r="C258">
+        <v>-694.095</v>
+      </c>
+      <c r="D258">
+        <v>-694.095</v>
+      </c>
+      <c r="E258">
+        <v>65</v>
+      </c>
+      <c r="F258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
+        <v>46131.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>-23.057</v>
+      </c>
+      <c r="C259">
+        <v>399</v>
+      </c>
+      <c r="D259">
+        <v>399</v>
+      </c>
+      <c r="E259">
+        <v>66</v>
+      </c>
+      <c r="F259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
+        <v>46131.6875</v>
+      </c>
+      <c r="B260">
+        <v>-23.714</v>
+      </c>
+      <c r="C260">
+        <v>-21.311</v>
+      </c>
+      <c r="D260">
+        <v>-21.311</v>
+      </c>
+      <c r="E260">
+        <v>67</v>
+      </c>
+      <c r="F260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
+        <v>46131.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>-65.86</v>
+      </c>
+      <c r="C261">
+        <v>420.944</v>
+      </c>
+      <c r="D261">
+        <v>420.944</v>
+      </c>
+      <c r="E261">
+        <v>68</v>
+      </c>
+      <c r="F261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
+        <v>46131.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>43.572</v>
+      </c>
+      <c r="C262">
+        <v>-976.357</v>
+      </c>
+      <c r="D262">
+        <v>-976.357</v>
+      </c>
+      <c r="E262">
+        <v>69</v>
+      </c>
+      <c r="F262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
+        <v>46131.71875</v>
+      </c>
+      <c r="B263">
+        <v>49.196</v>
+      </c>
+      <c r="C263">
+        <v>-1192.139</v>
+      </c>
+      <c r="D263">
+        <v>-1192.139</v>
+      </c>
+      <c r="E263">
+        <v>70</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46131.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>37.817</v>
+      </c>
+      <c r="C264">
+        <v>258.035</v>
+      </c>
+      <c r="D264">
+        <v>258.035</v>
+      </c>
+      <c r="E264">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46131.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>37.127</v>
+      </c>
+      <c r="C265">
+        <v>-181.235</v>
+      </c>
+      <c r="D265">
+        <v>-181.235</v>
+      </c>
+      <c r="E265">
+        <v>72</v>
+      </c>
+      <c r="F265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46131.75</v>
+      </c>
+      <c r="B266">
+        <v>78.874</v>
+      </c>
+      <c r="C266">
+        <v>281.172</v>
+      </c>
+      <c r="D266">
+        <v>281.172</v>
+      </c>
+      <c r="E266">
+        <v>73</v>
+      </c>
+      <c r="F266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46131.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>64.791</v>
+      </c>
+      <c r="C267">
+        <v>364.599</v>
+      </c>
+      <c r="D267">
+        <v>364.599</v>
+      </c>
+      <c r="E267">
+        <v>74</v>
+      </c>
+      <c r="F267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46131.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>97.795</v>
+      </c>
+      <c r="C268">
+        <v>46.263</v>
+      </c>
+      <c r="D268">
+        <v>46.263</v>
+      </c>
+      <c r="E268">
+        <v>75</v>
+      </c>
+      <c r="F268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46131.78125</v>
+      </c>
+      <c r="B269">
+        <v>52.911</v>
+      </c>
+      <c r="C269">
+        <v>-430.443</v>
+      </c>
+      <c r="D269">
+        <v>-430.443</v>
+      </c>
+      <c r="E269">
+        <v>76</v>
+      </c>
+      <c r="F269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46131.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>62.742</v>
+      </c>
+      <c r="C270">
+        <v>-186.95</v>
+      </c>
+      <c r="D270">
+        <v>-186.95</v>
+      </c>
+      <c r="E270">
+        <v>77</v>
+      </c>
+      <c r="F270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46131.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>92.848</v>
+      </c>
+      <c r="C271">
+        <v>170.155</v>
+      </c>
+      <c r="D271">
+        <v>170.155</v>
+      </c>
+      <c r="E271">
+        <v>78</v>
+      </c>
+      <c r="F271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46131.8125</v>
+      </c>
+      <c r="B272">
+        <v>62.155</v>
+      </c>
+      <c r="C272">
+        <v>2.325</v>
+      </c>
+      <c r="D272">
+        <v>2.325</v>
+      </c>
+      <c r="E272">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46131.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>96.37</v>
+      </c>
+      <c r="C273">
+        <v>6.944</v>
+      </c>
+      <c r="D273">
+        <v>6.944</v>
+      </c>
+      <c r="E273">
+        <v>80</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46131.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>93.548</v>
+      </c>
+      <c r="C274">
+        <v>2.293</v>
+      </c>
+      <c r="D274">
+        <v>2.293</v>
+      </c>
+      <c r="E274">
+        <v>81</v>
+      </c>
+      <c r="F274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46131.84375</v>
+      </c>
+      <c r="B275">
+        <v>76.717</v>
+      </c>
+      <c r="C275">
+        <v>2.816</v>
+      </c>
+      <c r="D275">
+        <v>2.816</v>
+      </c>
+      <c r="E275">
+        <v>82</v>
+      </c>
+      <c r="F275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46131.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>78.523</v>
+      </c>
+      <c r="C276">
+        <v>0.972</v>
+      </c>
+      <c r="D276">
+        <v>0.972</v>
+      </c>
+      <c r="E276">
+        <v>83</v>
+      </c>
+      <c r="F276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46131.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>80.014</v>
+      </c>
+      <c r="C277">
+        <v>50.015</v>
+      </c>
+      <c r="D277">
+        <v>50.015</v>
+      </c>
+      <c r="E277">
+        <v>84</v>
+      </c>
+      <c r="F277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46131.875</v>
+      </c>
+      <c r="B278">
+        <v>54.089</v>
+      </c>
+      <c r="C278">
+        <v>-35.525</v>
+      </c>
+      <c r="D278">
+        <v>-35.525</v>
+      </c>
+      <c r="E278">
+        <v>85</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46131.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>96.265</v>
+      </c>
+      <c r="C279">
+        <v>-724.193</v>
+      </c>
+      <c r="D279">
+        <v>-724.193</v>
+      </c>
+      <c r="E279">
+        <v>86</v>
+      </c>
+      <c r="F279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46131.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>96.875</v>
+      </c>
+      <c r="C280">
+        <v>-153.973</v>
+      </c>
+      <c r="D280">
+        <v>-153.973</v>
+      </c>
+      <c r="E280">
+        <v>87</v>
+      </c>
+      <c r="F280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46131.90625</v>
+      </c>
+      <c r="B281">
+        <v>80.72199999999999</v>
+      </c>
+      <c r="C281">
+        <v>-94.98399999999999</v>
+      </c>
+      <c r="D281">
+        <v>-94.98399999999999</v>
+      </c>
+      <c r="E281">
+        <v>88</v>
+      </c>
+      <c r="F281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46131.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>72.489</v>
+      </c>
+      <c r="C282">
+        <v>-19.446</v>
+      </c>
+      <c r="D282">
+        <v>-19.446</v>
+      </c>
+      <c r="E282">
+        <v>89</v>
+      </c>
+      <c r="F282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46131.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>49.72</v>
+      </c>
+      <c r="C283">
+        <v>17.221</v>
+      </c>
+      <c r="D283">
+        <v>17.221</v>
+      </c>
+      <c r="E283">
+        <v>90</v>
+      </c>
+      <c r="F283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46131.9375</v>
+      </c>
+      <c r="B284">
+        <v>61.705</v>
+      </c>
+      <c r="C284">
+        <v>-14.324</v>
+      </c>
+      <c r="D284">
+        <v>-14.324</v>
+      </c>
+      <c r="E284">
+        <v>91</v>
+      </c>
+      <c r="F284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46131.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>74.00700000000001</v>
+      </c>
+      <c r="C285">
+        <v>-174.276</v>
+      </c>
+      <c r="D285">
+        <v>-174.276</v>
+      </c>
+      <c r="E285">
+        <v>92</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46131.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>48.936</v>
+      </c>
+      <c r="C286">
+        <v>-8.459</v>
+      </c>
+      <c r="D286">
+        <v>-8.459</v>
+      </c>
+      <c r="E286">
+        <v>93</v>
+      </c>
+      <c r="F286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46131.96875</v>
+      </c>
+      <c r="B287">
+        <v>68.06</v>
+      </c>
+      <c r="C287">
+        <v>-89.17100000000001</v>
+      </c>
+      <c r="D287">
+        <v>-89.17100000000001</v>
+      </c>
+      <c r="E287">
+        <v>94</v>
+      </c>
+      <c r="F287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46131.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>50.071</v>
+      </c>
+      <c r="C288">
+        <v>26.561</v>
+      </c>
+      <c r="D288">
+        <v>26.561</v>
+      </c>
+      <c r="E288">
+        <v>95</v>
+      </c>
+      <c r="F288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46131.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>49.165</v>
+      </c>
+      <c r="C289">
+        <v>-3.189</v>
+      </c>
+      <c r="D289">
+        <v>-3.189</v>
+      </c>
+      <c r="E289">
+        <v>96</v>
+      </c>
+      <c r="F289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B290">
+        <v>48.6</v>
+      </c>
+      <c r="C290">
+        <v>17.373</v>
+      </c>
+      <c r="D290">
+        <v>17.373</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46132.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>28.965</v>
+      </c>
+      <c r="C291">
+        <v>3.715</v>
+      </c>
+      <c r="D291">
+        <v>3.715</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46132.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>40.565</v>
+      </c>
+      <c r="C292">
+        <v>30.142</v>
+      </c>
+      <c r="D292">
+        <v>30.142</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46132.03125</v>
+      </c>
+      <c r="B293">
+        <v>38.007</v>
+      </c>
+      <c r="C293">
+        <v>12.786</v>
+      </c>
+      <c r="D293">
+        <v>12.786</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46132.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>97.637</v>
+      </c>
+      <c r="C294">
+        <v>-17.532</v>
+      </c>
+      <c r="D294">
+        <v>-17.532</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46132.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>113.153</v>
+      </c>
+      <c r="C295">
+        <v>-23.917</v>
+      </c>
+      <c r="D295">
+        <v>-23.917</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46132.0625</v>
+      </c>
+      <c r="B296">
+        <v>103.795</v>
+      </c>
+      <c r="C296">
+        <v>22.707</v>
+      </c>
+      <c r="D296">
+        <v>22.707</v>
+      </c>
+      <c r="E296">
+        <v>7</v>
+      </c>
+      <c r="F296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46132.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>72.583</v>
+      </c>
+      <c r="C297">
+        <v>7.7</v>
+      </c>
+      <c r="D297">
+        <v>7.7</v>
+      </c>
+      <c r="E297">
+        <v>8</v>
+      </c>
+      <c r="F297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46132.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>59.144</v>
+      </c>
+      <c r="C298">
+        <v>3.789</v>
+      </c>
+      <c r="D298">
+        <v>3.789</v>
+      </c>
+      <c r="E298">
+        <v>9</v>
+      </c>
+      <c r="F298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46132.09375</v>
+      </c>
+      <c r="B299">
+        <v>35.091</v>
+      </c>
+      <c r="C299">
+        <v>0.207</v>
+      </c>
+      <c r="D299">
+        <v>0.207</v>
+      </c>
+      <c r="E299">
+        <v>10</v>
+      </c>
+      <c r="F299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46132.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>66.47499999999999</v>
+      </c>
+      <c r="C300">
+        <v>7.249</v>
+      </c>
+      <c r="D300">
+        <v>7.249</v>
+      </c>
+      <c r="E300">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46132.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>56.098</v>
+      </c>
+      <c r="C301">
+        <v>2.369</v>
+      </c>
+      <c r="D301">
+        <v>2.369</v>
+      </c>
+      <c r="E301">
+        <v>12</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46132.125</v>
+      </c>
+      <c r="B302">
+        <v>67.633</v>
+      </c>
+      <c r="C302">
+        <v>0.118</v>
+      </c>
+      <c r="D302">
+        <v>0.118</v>
+      </c>
+      <c r="E302">
+        <v>13</v>
+      </c>
+      <c r="F302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46132.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>73.669</v>
+      </c>
+      <c r="C303">
+        <v>7.08</v>
+      </c>
+      <c r="D303">
+        <v>7.08</v>
+      </c>
+      <c r="E303">
+        <v>14</v>
+      </c>
+      <c r="F303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46132.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>51.183</v>
+      </c>
+      <c r="C304">
+        <v>35.102</v>
+      </c>
+      <c r="D304">
+        <v>35.102</v>
+      </c>
+      <c r="E304">
+        <v>15</v>
+      </c>
+      <c r="F304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46132.15625</v>
+      </c>
+      <c r="B305">
+        <v>33.355</v>
+      </c>
+      <c r="C305">
+        <v>18.308</v>
+      </c>
+      <c r="D305">
+        <v>18.308</v>
+      </c>
+      <c r="E305">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46132.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>28.944</v>
+      </c>
+      <c r="C306">
+        <v>4.417</v>
+      </c>
+      <c r="D306">
+        <v>4.417</v>
+      </c>
+      <c r="E306">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46132.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>42.108</v>
+      </c>
+      <c r="C307">
+        <v>14.931</v>
+      </c>
+      <c r="D307">
+        <v>14.931</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46132.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>7.273</v>
+      </c>
+      <c r="D308">
+        <v>7.273</v>
+      </c>
+      <c r="E308">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46132.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>22.903</v>
+      </c>
+      <c r="C309">
+        <v>0.2</v>
+      </c>
+      <c r="D309">
+        <v>0.2</v>
+      </c>
+      <c r="E309">
+        <v>20</v>
+      </c>
+      <c r="F309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46132.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>58.941</v>
+      </c>
+      <c r="C310">
+        <v>0.4</v>
+      </c>
+      <c r="D310">
+        <v>0.4</v>
+      </c>
+      <c r="E310">
+        <v>21</v>
+      </c>
+      <c r="F310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="2">
+        <v>46132.21875</v>
+      </c>
+      <c r="B311">
+        <v>28.05</v>
+      </c>
+      <c r="C311">
+        <v>0.5</v>
+      </c>
+      <c r="D311">
+        <v>0.5</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="2">
+        <v>46132.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>11.221</v>
+      </c>
+      <c r="C312">
+        <v>1.985</v>
+      </c>
+      <c r="D312">
+        <v>1.985</v>
+      </c>
+      <c r="E312">
+        <v>23</v>
+      </c>
+      <c r="F312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="2">
+        <v>46132.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>-10.052</v>
+      </c>
+      <c r="C313">
+        <v>1019.612</v>
+      </c>
+      <c r="D313">
+        <v>1019.612</v>
+      </c>
+      <c r="E313">
+        <v>24</v>
+      </c>
+      <c r="F313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="2">
+        <v>46132.25</v>
+      </c>
+      <c r="B314">
+        <v>45.741</v>
+      </c>
+      <c r="C314">
+        <v>6.797</v>
+      </c>
+      <c r="D314">
+        <v>6.797</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="2">
+        <v>46132.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>57.152</v>
+      </c>
+      <c r="C315">
+        <v>-2.174</v>
+      </c>
+      <c r="D315">
+        <v>-2.174</v>
+      </c>
+      <c r="E315">
+        <v>26</v>
+      </c>
+      <c r="F315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="2">
+        <v>46132.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>73.152</v>
+      </c>
+      <c r="C316">
+        <v>-38.308</v>
+      </c>
+      <c r="D316">
+        <v>-38.308</v>
+      </c>
+      <c r="E316">
+        <v>27</v>
+      </c>
+      <c r="F316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="2">
+        <v>46132.28125</v>
+      </c>
+      <c r="B317">
+        <v>80.764</v>
+      </c>
+      <c r="C317">
+        <v>-560.458</v>
+      </c>
+      <c r="D317">
+        <v>-560.458</v>
+      </c>
+      <c r="E317">
+        <v>28</v>
+      </c>
+      <c r="F317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="2">
+        <v>46132.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>57.32</v>
+      </c>
+      <c r="C318">
+        <v>-6132.267</v>
+      </c>
+      <c r="D318">
+        <v>-6132.267</v>
+      </c>
+      <c r="E318">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="2">
+        <v>46132.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>72.72199999999999</v>
+      </c>
+      <c r="C319">
+        <v>-6499</v>
+      </c>
+      <c r="D319">
+        <v>-6499</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="2">
+        <v>46132.3125</v>
+      </c>
+      <c r="B320">
+        <v>80.15300000000001</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+      <c r="E320">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="2">
+        <v>46132.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+      <c r="E321">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="2">
+        <v>46132.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+      <c r="E322">
+        <v>33</v>
+      </c>
+      <c r="F322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="2">
+        <v>46132.34375</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+      <c r="E323">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="2">
+        <v>46132.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+      <c r="E324">
+        <v>35</v>
+      </c>
+      <c r="F324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="2">
+        <v>46132.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+      <c r="E325">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="2">
+        <v>46132.375</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="2">
+        <v>46132.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="2">
+        <v>46132.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>39</v>
+      </c>
+      <c r="F328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="2">
+        <v>46132.40625</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>40</v>
+      </c>
+      <c r="F329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="2">
+        <v>46132.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>41</v>
+      </c>
+      <c r="F330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="2">
+        <v>46132.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>42</v>
+      </c>
+      <c r="F331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="2">
+        <v>46132.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>43</v>
+      </c>
+      <c r="F332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="2">
+        <v>46132.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>44</v>
+      </c>
+      <c r="F333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="2">
+        <v>46132.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>45</v>
+      </c>
+      <c r="F334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="2">
+        <v>46132.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>46</v>
+      </c>
+      <c r="F335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="2">
+        <v>46132.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>47</v>
+      </c>
+      <c r="F336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="2">
+        <v>46132.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>48</v>
+      </c>
+      <c r="F337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="2">
+        <v>46132.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>49</v>
+      </c>
+      <c r="F338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="2">
+        <v>46132.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>50</v>
+      </c>
+      <c r="F339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="2">
+        <v>46132.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>51</v>
+      </c>
+      <c r="F340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" s="2">
+        <v>46132.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>52</v>
+      </c>
+      <c r="F341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="2">
+        <v>46132.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>53</v>
+      </c>
+      <c r="F342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="2">
+        <v>46132.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>54</v>
+      </c>
+      <c r="F343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="2">
+        <v>46132.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>55</v>
+      </c>
+      <c r="F344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="2">
+        <v>46132.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>56</v>
+      </c>
+      <c r="F345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="2">
+        <v>46132.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>57</v>
+      </c>
+      <c r="F346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="2">
+        <v>46132.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>58</v>
+      </c>
+      <c r="F347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="2">
+        <v>46132.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>59</v>
+      </c>
+      <c r="F348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="2">
+        <v>46132.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>60</v>
+      </c>
+      <c r="F349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="2">
+        <v>46132.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>61</v>
+      </c>
+      <c r="F350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="2">
+        <v>46132.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>62</v>
+      </c>
+      <c r="F351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="2">
+        <v>46132.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>63</v>
+      </c>
+      <c r="F352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="2">
+        <v>46132.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>64</v>
+      </c>
+      <c r="F353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="2">
+        <v>46132.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>65</v>
+      </c>
+      <c r="F354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="2">
+        <v>46132.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>66</v>
+      </c>
+      <c r="F355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="2">
+        <v>46132.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>67</v>
+      </c>
+      <c r="F356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="2">
+        <v>46132.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>68</v>
+      </c>
+      <c r="F357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="2">
+        <v>46132.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>69</v>
+      </c>
+      <c r="F358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="2">
+        <v>46132.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>70</v>
+      </c>
+      <c r="F359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="2">
+        <v>46132.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>71</v>
+      </c>
+      <c r="F360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="2">
+        <v>46132.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>72</v>
+      </c>
+      <c r="F361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="2">
+        <v>46132.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>73</v>
+      </c>
+      <c r="F362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="2">
+        <v>46132.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>74</v>
+      </c>
+      <c r="F363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="2">
+        <v>46132.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>75</v>
+      </c>
+      <c r="F364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="2">
+        <v>46132.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>76</v>
+      </c>
+      <c r="F365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="2">
+        <v>46132.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>77</v>
+      </c>
+      <c r="F366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="2">
+        <v>46132.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>78</v>
+      </c>
+      <c r="F367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="2">
+        <v>46132.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>79</v>
+      </c>
+      <c r="F368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" s="2">
+        <v>46132.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>80</v>
+      </c>
+      <c r="F369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" s="2">
+        <v>46132.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>81</v>
+      </c>
+      <c r="F370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" s="2">
+        <v>46132.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>82</v>
+      </c>
+      <c r="F371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="2">
+        <v>46132.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>83</v>
+      </c>
+      <c r="F372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="2">
+        <v>46132.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>84</v>
+      </c>
+      <c r="F373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="2">
+        <v>46132.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>85</v>
+      </c>
+      <c r="F374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" s="2">
+        <v>46132.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>86</v>
+      </c>
+      <c r="F375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="2">
+        <v>46132.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>87</v>
+      </c>
+      <c r="F376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" s="2">
+        <v>46132.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>88</v>
+      </c>
+      <c r="F377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" s="2">
+        <v>46132.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>89</v>
+      </c>
+      <c r="F378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" s="2">
+        <v>46132.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>90</v>
+      </c>
+      <c r="F379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" s="2">
+        <v>46132.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>91</v>
+      </c>
+      <c r="F380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" s="2">
+        <v>46132.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>92</v>
+      </c>
+      <c r="F381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" s="2">
+        <v>46132.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>93</v>
+      </c>
+      <c r="F382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" s="2">
+        <v>46132.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>94</v>
+      </c>
+      <c r="F383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" s="2">
+        <v>46132.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>95</v>
+      </c>
+      <c r="F384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" s="2">
+        <v>46132.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>96</v>
+      </c>
+      <c r="F385" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.04.20261</t>
-  </si>
-  <si>
-    <t>20.04.20262</t>
-  </si>
-  <si>
-    <t>20.04.20263</t>
-  </si>
-  <si>
-    <t>20.04.20264</t>
-  </si>
-  <si>
-    <t>20.04.20265</t>
-  </si>
-  <si>
-    <t>20.04.20266</t>
-  </si>
-  <si>
-    <t>20.04.20267</t>
-  </si>
-  <si>
-    <t>20.04.20268</t>
-  </si>
-  <si>
-    <t>20.04.20269</t>
-  </si>
-  <si>
-    <t>20.04.202610</t>
-  </si>
-  <si>
-    <t>20.04.202611</t>
-  </si>
-  <si>
-    <t>20.04.202612</t>
-  </si>
-  <si>
-    <t>20.04.202613</t>
-  </si>
-  <si>
-    <t>20.04.202614</t>
-  </si>
-  <si>
-    <t>20.04.202615</t>
-  </si>
-  <si>
-    <t>20.04.202616</t>
-  </si>
-  <si>
-    <t>20.04.202617</t>
-  </si>
-  <si>
-    <t>20.04.202618</t>
-  </si>
-  <si>
-    <t>20.04.202619</t>
-  </si>
-  <si>
-    <t>20.04.202620</t>
-  </si>
-  <si>
-    <t>20.04.202621</t>
-  </si>
-  <si>
-    <t>20.04.202622</t>
-  </si>
-  <si>
-    <t>20.04.202623</t>
-  </si>
-  <si>
-    <t>20.04.202624</t>
-  </si>
-  <si>
-    <t>20.04.202625</t>
-  </si>
-  <si>
-    <t>20.04.202626</t>
-  </si>
-  <si>
-    <t>20.04.202627</t>
-  </si>
-  <si>
-    <t>20.04.202628</t>
-  </si>
-  <si>
-    <t>20.04.202629</t>
-  </si>
-  <si>
-    <t>20.04.202630</t>
-  </si>
-  <si>
-    <t>20.04.202631</t>
-  </si>
-  <si>
-    <t>20.04.202632</t>
-  </si>
-  <si>
-    <t>20.04.202633</t>
-  </si>
-  <si>
-    <t>20.04.202634</t>
-  </si>
-  <si>
-    <t>20.04.202635</t>
-  </si>
-  <si>
-    <t>20.04.202636</t>
-  </si>
-  <si>
-    <t>20.04.202637</t>
-  </si>
-  <si>
-    <t>20.04.202638</t>
-  </si>
-  <si>
-    <t>20.04.202639</t>
-  </si>
-  <si>
-    <t>20.04.202640</t>
-  </si>
-  <si>
-    <t>20.04.202641</t>
-  </si>
-  <si>
-    <t>20.04.202642</t>
-  </si>
-  <si>
-    <t>20.04.202643</t>
-  </si>
-  <si>
-    <t>20.04.202644</t>
-  </si>
-  <si>
-    <t>20.04.202645</t>
-  </si>
-  <si>
-    <t>20.04.202646</t>
-  </si>
-  <si>
-    <t>20.04.202647</t>
-  </si>
-  <si>
-    <t>20.04.202648</t>
-  </si>
-  <si>
-    <t>20.04.202649</t>
-  </si>
-  <si>
-    <t>20.04.202650</t>
-  </si>
-  <si>
-    <t>20.04.202651</t>
-  </si>
-  <si>
-    <t>20.04.202652</t>
-  </si>
-  <si>
-    <t>20.04.202653</t>
-  </si>
-  <si>
-    <t>20.04.202654</t>
-  </si>
-  <si>
-    <t>20.04.202655</t>
-  </si>
-  <si>
-    <t>20.04.202656</t>
-  </si>
-  <si>
-    <t>20.04.202657</t>
-  </si>
-  <si>
-    <t>20.04.202658</t>
-  </si>
-  <si>
-    <t>20.04.202659</t>
-  </si>
-  <si>
-    <t>20.04.202660</t>
-  </si>
-  <si>
-    <t>20.04.202661</t>
-  </si>
-  <si>
-    <t>20.04.202662</t>
-  </si>
-  <si>
-    <t>20.04.202663</t>
-  </si>
-  <si>
-    <t>20.04.202664</t>
-  </si>
-  <si>
-    <t>20.04.202665</t>
-  </si>
-  <si>
-    <t>20.04.202666</t>
-  </si>
-  <si>
-    <t>20.04.202667</t>
-  </si>
-  <si>
-    <t>20.04.202668</t>
-  </si>
-  <si>
-    <t>20.04.202669</t>
-  </si>
-  <si>
-    <t>20.04.202670</t>
-  </si>
-  <si>
-    <t>20.04.202671</t>
-  </si>
-  <si>
-    <t>20.04.202672</t>
-  </si>
-  <si>
-    <t>20.04.202673</t>
-  </si>
-  <si>
-    <t>20.04.202674</t>
-  </si>
-  <si>
-    <t>20.04.202675</t>
-  </si>
-  <si>
-    <t>20.04.202676</t>
-  </si>
-  <si>
-    <t>20.04.202677</t>
-  </si>
-  <si>
-    <t>20.04.202678</t>
-  </si>
-  <si>
-    <t>20.04.202679</t>
-  </si>
-  <si>
-    <t>20.04.202680</t>
-  </si>
-  <si>
-    <t>20.04.202681</t>
-  </si>
-  <si>
-    <t>20.04.202682</t>
-  </si>
-  <si>
-    <t>20.04.202683</t>
-  </si>
-  <si>
-    <t>20.04.202684</t>
-  </si>
-  <si>
-    <t>20.04.202685</t>
-  </si>
-  <si>
-    <t>20.04.202686</t>
-  </si>
-  <si>
-    <t>20.04.202687</t>
-  </si>
-  <si>
-    <t>20.04.202688</t>
-  </si>
-  <si>
-    <t>20.04.202689</t>
-  </si>
-  <si>
-    <t>20.04.202690</t>
-  </si>
-  <si>
-    <t>20.04.202691</t>
-  </si>
-  <si>
-    <t>20.04.202692</t>
-  </si>
-  <si>
-    <t>20.04.202693</t>
-  </si>
-  <si>
-    <t>20.04.202694</t>
-  </si>
-  <si>
-    <t>20.04.202695</t>
-  </si>
-  <si>
-    <t>20.04.202696</t>
-  </si>
-  <si>
     <t>21.04.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>21.04.202696</t>
+  </si>
+  <si>
+    <t>22.04.20261</t>
+  </si>
+  <si>
+    <t>22.04.20262</t>
+  </si>
+  <si>
+    <t>22.04.20263</t>
+  </si>
+  <si>
+    <t>22.04.20264</t>
+  </si>
+  <si>
+    <t>22.04.20265</t>
+  </si>
+  <si>
+    <t>22.04.20266</t>
+  </si>
+  <si>
+    <t>22.04.20267</t>
+  </si>
+  <si>
+    <t>22.04.20268</t>
+  </si>
+  <si>
+    <t>22.04.20269</t>
+  </si>
+  <si>
+    <t>22.04.202610</t>
+  </si>
+  <si>
+    <t>22.04.202611</t>
+  </si>
+  <si>
+    <t>22.04.202612</t>
+  </si>
+  <si>
+    <t>22.04.202613</t>
+  </si>
+  <si>
+    <t>22.04.202614</t>
+  </si>
+  <si>
+    <t>22.04.202615</t>
+  </si>
+  <si>
+    <t>22.04.202616</t>
+  </si>
+  <si>
+    <t>22.04.202617</t>
+  </si>
+  <si>
+    <t>22.04.202618</t>
+  </si>
+  <si>
+    <t>22.04.202619</t>
+  </si>
+  <si>
+    <t>22.04.202620</t>
+  </si>
+  <si>
+    <t>22.04.202621</t>
+  </si>
+  <si>
+    <t>22.04.202622</t>
+  </si>
+  <si>
+    <t>22.04.202623</t>
+  </si>
+  <si>
+    <t>22.04.202624</t>
+  </si>
+  <si>
+    <t>22.04.202625</t>
+  </si>
+  <si>
+    <t>22.04.202626</t>
+  </si>
+  <si>
+    <t>22.04.202627</t>
+  </si>
+  <si>
+    <t>22.04.202628</t>
+  </si>
+  <si>
+    <t>22.04.202629</t>
+  </si>
+  <si>
+    <t>22.04.202630</t>
+  </si>
+  <si>
+    <t>22.04.202631</t>
+  </si>
+  <si>
+    <t>22.04.202632</t>
+  </si>
+  <si>
+    <t>22.04.202633</t>
+  </si>
+  <si>
+    <t>22.04.202634</t>
+  </si>
+  <si>
+    <t>22.04.202635</t>
+  </si>
+  <si>
+    <t>22.04.202636</t>
+  </si>
+  <si>
+    <t>22.04.202637</t>
+  </si>
+  <si>
+    <t>22.04.202638</t>
+  </si>
+  <si>
+    <t>22.04.202639</t>
+  </si>
+  <si>
+    <t>22.04.202640</t>
+  </si>
+  <si>
+    <t>22.04.202641</t>
+  </si>
+  <si>
+    <t>22.04.202642</t>
+  </si>
+  <si>
+    <t>22.04.202643</t>
+  </si>
+  <si>
+    <t>22.04.202644</t>
+  </si>
+  <si>
+    <t>22.04.202645</t>
+  </si>
+  <si>
+    <t>22.04.202646</t>
+  </si>
+  <si>
+    <t>22.04.202647</t>
+  </si>
+  <si>
+    <t>22.04.202648</t>
+  </si>
+  <si>
+    <t>22.04.202649</t>
+  </si>
+  <si>
+    <t>22.04.202650</t>
+  </si>
+  <si>
+    <t>22.04.202651</t>
+  </si>
+  <si>
+    <t>22.04.202652</t>
+  </si>
+  <si>
+    <t>22.04.202653</t>
+  </si>
+  <si>
+    <t>22.04.202654</t>
+  </si>
+  <si>
+    <t>22.04.202655</t>
+  </si>
+  <si>
+    <t>22.04.202656</t>
+  </si>
+  <si>
+    <t>22.04.202657</t>
+  </si>
+  <si>
+    <t>22.04.202658</t>
+  </si>
+  <si>
+    <t>22.04.202659</t>
+  </si>
+  <si>
+    <t>22.04.202660</t>
+  </si>
+  <si>
+    <t>22.04.202661</t>
+  </si>
+  <si>
+    <t>22.04.202662</t>
+  </si>
+  <si>
+    <t>22.04.202663</t>
+  </si>
+  <si>
+    <t>22.04.202664</t>
+  </si>
+  <si>
+    <t>22.04.202665</t>
+  </si>
+  <si>
+    <t>22.04.202666</t>
+  </si>
+  <si>
+    <t>22.04.202667</t>
+  </si>
+  <si>
+    <t>22.04.202668</t>
+  </si>
+  <si>
+    <t>22.04.202669</t>
+  </si>
+  <si>
+    <t>22.04.202670</t>
+  </si>
+  <si>
+    <t>22.04.202671</t>
+  </si>
+  <si>
+    <t>22.04.202672</t>
+  </si>
+  <si>
+    <t>22.04.202673</t>
+  </si>
+  <si>
+    <t>22.04.202674</t>
+  </si>
+  <si>
+    <t>22.04.202675</t>
+  </si>
+  <si>
+    <t>22.04.202676</t>
+  </si>
+  <si>
+    <t>22.04.202677</t>
+  </si>
+  <si>
+    <t>22.04.202678</t>
+  </si>
+  <si>
+    <t>22.04.202679</t>
+  </si>
+  <si>
+    <t>22.04.202680</t>
+  </si>
+  <si>
+    <t>22.04.202681</t>
+  </si>
+  <si>
+    <t>22.04.202682</t>
+  </si>
+  <si>
+    <t>22.04.202683</t>
+  </si>
+  <si>
+    <t>22.04.202684</t>
+  </si>
+  <si>
+    <t>22.04.202685</t>
+  </si>
+  <si>
+    <t>22.04.202686</t>
+  </si>
+  <si>
+    <t>22.04.202687</t>
+  </si>
+  <si>
+    <t>22.04.202688</t>
+  </si>
+  <si>
+    <t>22.04.202689</t>
+  </si>
+  <si>
+    <t>22.04.202690</t>
+  </si>
+  <si>
+    <t>22.04.202691</t>
+  </si>
+  <si>
+    <t>22.04.202692</t>
+  </si>
+  <si>
+    <t>22.04.202693</t>
+  </si>
+  <si>
+    <t>22.04.202694</t>
+  </si>
+  <si>
+    <t>22.04.202695</t>
+  </si>
+  <si>
+    <t>22.04.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
-        <v>97.637</v>
+        <v>148.873</v>
       </c>
       <c r="C6">
-        <v>-17.532</v>
+        <v>-4321.272</v>
       </c>
       <c r="D6">
-        <v>-17.532</v>
+        <v>-4321.272</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
-        <v>113.153</v>
+        <v>200.676</v>
       </c>
       <c r="C7">
-        <v>-23.917</v>
+        <v>-2049.701</v>
       </c>
       <c r="D7">
-        <v>-23.917</v>
+        <v>-2049.701</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
-        <v>103.795</v>
+        <v>154.428</v>
       </c>
       <c r="C8">
-        <v>22.707</v>
+        <v>-6668.16</v>
       </c>
       <c r="D8">
-        <v>22.707</v>
+        <v>-6668.16</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
-        <v>72.583</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="C9">
-        <v>7.7</v>
+        <v>-749.404</v>
       </c>
       <c r="D9">
-        <v>7.7</v>
+        <v>-749.404</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
-        <v>59.144</v>
+        <v>90.03400000000001</v>
       </c>
       <c r="C10">
-        <v>3.789</v>
+        <v>3.182</v>
       </c>
       <c r="D10">
-        <v>3.789</v>
+        <v>3.182</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
-        <v>35.091</v>
+        <v>34.275</v>
       </c>
       <c r="C11">
-        <v>0.207</v>
+        <v>0.997</v>
       </c>
       <c r="D11">
-        <v>0.207</v>
+        <v>0.997</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
-        <v>66.47499999999999</v>
+        <v>70.977</v>
       </c>
       <c r="C12">
-        <v>7.249</v>
+        <v>2.363</v>
       </c>
       <c r="D12">
-        <v>7.249</v>
+        <v>2.363</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
-        <v>56.098</v>
+        <v>32.471</v>
       </c>
       <c r="C13">
-        <v>2.369</v>
+        <v>0.1</v>
       </c>
       <c r="D13">
-        <v>2.369</v>
+        <v>0.1</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
-        <v>67.633</v>
+        <v>54.087</v>
       </c>
       <c r="C14">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
-        <v>73.669</v>
+        <v>34.991</v>
       </c>
       <c r="C15">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
-        <v>51.183</v>
+        <v>25.736</v>
       </c>
       <c r="C16">
-        <v>35.102</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>35.102</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
-        <v>33.355</v>
+        <v>30.622</v>
       </c>
       <c r="C17">
-        <v>18.308</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>18.308</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
-        <v>28.944</v>
+        <v>44.432</v>
       </c>
       <c r="C18">
-        <v>4.417</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>4.417</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
-        <v>42.108</v>
+        <v>19.559</v>
       </c>
       <c r="C19">
-        <v>14.931</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>14.931</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>-25.436</v>
       </c>
       <c r="C20">
-        <v>7.273</v>
+        <v>928.45</v>
       </c>
       <c r="D20">
-        <v>7.273</v>
+        <v>928.45</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
-        <v>22.903</v>
+        <v>20.03</v>
       </c>
       <c r="C21">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D21">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
-        <v>58.941</v>
+        <v>45.741</v>
       </c>
       <c r="C22">
-        <v>0.4</v>
+        <v>1.907</v>
       </c>
       <c r="D22">
-        <v>0.4</v>
+        <v>1.907</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
-        <v>28.05</v>
+        <v>26.095</v>
       </c>
       <c r="C23">
-        <v>0.5</v>
+        <v>299.48</v>
       </c>
       <c r="D23">
-        <v>0.5</v>
+        <v>299.48</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
-        <v>11.221</v>
+        <v>52.926</v>
       </c>
       <c r="C24">
-        <v>1.985</v>
+        <v>16.595</v>
       </c>
       <c r="D24">
-        <v>1.985</v>
+        <v>16.595</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
-        <v>-10.052</v>
+        <v>25.922</v>
       </c>
       <c r="C25">
-        <v>1019.612</v>
+        <v>34.092</v>
       </c>
       <c r="D25">
-        <v>1019.612</v>
+        <v>34.092</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
-        <v>45.741</v>
+        <v>24.286</v>
       </c>
       <c r="C26">
-        <v>6.797</v>
+        <v>17.156</v>
       </c>
       <c r="D26">
-        <v>6.797</v>
+        <v>17.156</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
-        <v>57.152</v>
+        <v>48.657</v>
       </c>
       <c r="C27">
-        <v>-2.174</v>
+        <v>4.904</v>
       </c>
       <c r="D27">
-        <v>-2.174</v>
+        <v>4.904</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
-        <v>73.152</v>
+        <v>30.856</v>
       </c>
       <c r="C28">
-        <v>-38.308</v>
+        <v>15.459</v>
       </c>
       <c r="D28">
-        <v>-38.308</v>
+        <v>15.459</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
-        <v>80.764</v>
+        <v>11.988</v>
       </c>
       <c r="C29">
-        <v>-560.458</v>
+        <v>1.539</v>
       </c>
       <c r="D29">
-        <v>-560.458</v>
+        <v>1.539</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
-        <v>57.32</v>
+        <v>32.308</v>
       </c>
       <c r="C30">
-        <v>-6132.267</v>
+        <v>251.991</v>
       </c>
       <c r="D30">
-        <v>-6132.267</v>
+        <v>251.991</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
-        <v>72.72199999999999</v>
+        <v>-2.967</v>
       </c>
       <c r="C31">
-        <v>-6499</v>
+        <v>890.456</v>
       </c>
       <c r="D31">
-        <v>-6499</v>
+        <v>890.456</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
-        <v>80.15300000000001</v>
+        <v>-7.156</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>896.1079999999999</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>896.1079999999999</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
-        <v>103.348</v>
+        <v>16.727</v>
       </c>
       <c r="C33">
-        <v>-610.155</v>
+        <v>181.034</v>
       </c>
       <c r="D33">
-        <v>-610.155</v>
+        <v>181.034</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
-        <v>55.714</v>
+        <v>-44.19</v>
       </c>
       <c r="C34">
-        <v>-0.172</v>
+        <v>2547.653</v>
       </c>
       <c r="D34">
-        <v>-0.172</v>
+        <v>2547.653</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
-        <v>38.281</v>
+        <v>-18.855</v>
       </c>
       <c r="C35">
-        <v>1.095</v>
+        <v>1722.957</v>
       </c>
       <c r="D35">
-        <v>1.095</v>
+        <v>1722.957</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
-        <v>53.491</v>
+        <v>-30.555</v>
       </c>
       <c r="C36">
-        <v>3.147</v>
+        <v>899.528</v>
       </c>
       <c r="D36">
-        <v>3.147</v>
+        <v>899.528</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
-        <v>94.965</v>
+        <v>-7.02</v>
       </c>
       <c r="C37">
-        <v>-700.978</v>
+        <v>1021.741</v>
       </c>
       <c r="D37">
-        <v>-700.978</v>
+        <v>1021.741</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
-        <v>46.051</v>
+        <v>45.319</v>
       </c>
       <c r="C38">
-        <v>-124.542</v>
+        <v>43.404</v>
       </c>
       <c r="D38">
-        <v>-124.542</v>
+        <v>43.404</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
-        <v>56.215</v>
+        <v>-16.549</v>
       </c>
       <c r="C39">
-        <v>3.671</v>
+        <v>699</v>
       </c>
       <c r="D39">
-        <v>3.671</v>
+        <v>699</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
-        <v>71.943</v>
+        <v>-14.42</v>
       </c>
       <c r="C40">
-        <v>-694.873</v>
+        <v>904.251</v>
       </c>
       <c r="D40">
-        <v>-694.873</v>
+        <v>904.251</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
-        <v>90.01000000000001</v>
+        <v>-52.692</v>
       </c>
       <c r="C41">
-        <v>-249.803</v>
+        <v>1155.757</v>
       </c>
       <c r="D41">
-        <v>-249.803</v>
+        <v>1155.757</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
-        <v>41.765</v>
+        <v>-63.599</v>
       </c>
       <c r="C42">
-        <v>0.878</v>
+        <v>5270.55</v>
       </c>
       <c r="D42">
-        <v>0.878</v>
+        <v>5270.55</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
-        <v>93.401</v>
+        <v>-51.62</v>
       </c>
       <c r="C43">
-        <v>-69.46899999999999</v>
+        <v>896.359</v>
       </c>
       <c r="D43">
-        <v>-69.46899999999999</v>
+        <v>896.359</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
-        <v>98.82299999999999</v>
+        <v>-78.807</v>
       </c>
       <c r="C44">
-        <v>-47.601</v>
+        <v>899.429</v>
       </c>
       <c r="D44">
-        <v>-47.601</v>
+        <v>899.429</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
-        <v>124.928</v>
+        <v>-89.642</v>
       </c>
       <c r="C45">
-        <v>-96.398</v>
+        <v>897.275</v>
       </c>
       <c r="D45">
-        <v>-96.398</v>
+        <v>897.275</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
-        <v>138.286</v>
+        <v>-36.111</v>
       </c>
       <c r="C46">
-        <v>-63.259</v>
+        <v>713.6</v>
       </c>
       <c r="D46">
-        <v>-63.259</v>
+        <v>713.6</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
-        <v>128.66</v>
+        <v>-63.771</v>
       </c>
       <c r="C47">
-        <v>-149.514</v>
+        <v>713.554</v>
       </c>
       <c r="D47">
-        <v>-149.514</v>
+        <v>713.554</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
-        <v>148.165</v>
+        <v>-20.363</v>
       </c>
       <c r="C48">
-        <v>-854.412</v>
+        <v>713.6</v>
       </c>
       <c r="D48">
-        <v>-854.412</v>
+        <v>713.6</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
-        <v>166.244</v>
+        <v>-19.476</v>
       </c>
       <c r="C49">
-        <v>-3683.08</v>
+        <v>713.598</v>
       </c>
       <c r="D49">
-        <v>-3683.08</v>
+        <v>713.598</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
-        <v>169.349</v>
+        <v>52.608</v>
       </c>
       <c r="C50">
-        <v>-2843.102</v>
+        <v>129.989</v>
       </c>
       <c r="D50">
-        <v>-2843.102</v>
+        <v>129.989</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
-        <v>180.325</v>
+        <v>89.497</v>
       </c>
       <c r="C51">
-        <v>-338.954</v>
+        <v>161.997</v>
       </c>
       <c r="D51">
-        <v>-338.954</v>
+        <v>161.997</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
-        <v>163.682</v>
+        <v>69.001</v>
       </c>
       <c r="C52">
-        <v>-220.252</v>
+        <v>150.634</v>
       </c>
       <c r="D52">
-        <v>-220.252</v>
+        <v>150.634</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
-        <v>113.961</v>
+        <v>33.757</v>
       </c>
       <c r="C53">
-        <v>-292.516</v>
+        <v>259.084</v>
       </c>
       <c r="D53">
-        <v>-292.516</v>
+        <v>259.084</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
-        <v>178.117</v>
+        <v>-41.838</v>
       </c>
       <c r="C54">
-        <v>-1369.292</v>
+        <v>6290.171</v>
       </c>
       <c r="D54">
-        <v>-1369.292</v>
+        <v>6290.171</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
-        <v>206.097</v>
+        <v>-14.633</v>
       </c>
       <c r="C55">
-        <v>-3089.749</v>
+        <v>1185.871</v>
       </c>
       <c r="D55">
-        <v>-3089.749</v>
+        <v>1185.871</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
-        <v>229.181</v>
+        <v>28.399</v>
       </c>
       <c r="C56">
-        <v>-3611.507</v>
+        <v>266.601</v>
       </c>
       <c r="D56">
-        <v>-3611.507</v>
+        <v>266.601</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
-        <v>128.162</v>
+        <v>16.109</v>
       </c>
       <c r="C57">
-        <v>-567.009</v>
+        <v>232.41</v>
       </c>
       <c r="D57">
-        <v>-567.009</v>
+        <v>232.41</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
-        <v>130.53</v>
+        <v>15.85</v>
       </c>
       <c r="C58">
-        <v>-236.046</v>
+        <v>359.025</v>
       </c>
       <c r="D58">
-        <v>-236.046</v>
+        <v>359.025</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
-        <v>103.988</v>
+        <v>-9.981</v>
       </c>
       <c r="C59">
-        <v>-240</v>
+        <v>817.515</v>
       </c>
       <c r="D59">
-        <v>-240</v>
+        <v>817.515</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
-        <v>158.458</v>
+        <v>5.834</v>
       </c>
       <c r="C60">
-        <v>-205.428</v>
+        <v>311.194</v>
       </c>
       <c r="D60">
-        <v>-205.428</v>
+        <v>311.194</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
-        <v>162.284</v>
+        <v>-15.259</v>
       </c>
       <c r="C61">
-        <v>-395.894</v>
+        <v>819.152</v>
       </c>
       <c r="D61">
-        <v>-395.894</v>
+        <v>819.152</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
-        <v>143.34</v>
+        <v>46.73</v>
       </c>
       <c r="C62">
-        <v>-417.114</v>
+        <v>287</v>
       </c>
       <c r="D62">
-        <v>-417.114</v>
+        <v>287</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
-        <v>59.217</v>
+        <v>44.12</v>
       </c>
       <c r="C63">
-        <v>-160.903</v>
+        <v>313.06</v>
       </c>
       <c r="D63">
-        <v>-160.903</v>
+        <v>313.06</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
-        <v>135.906</v>
+        <v>15.279</v>
       </c>
       <c r="C64">
-        <v>-153.019</v>
+        <v>321.491</v>
       </c>
       <c r="D64">
-        <v>-153.019</v>
+        <v>321.491</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
-        <v>102.734</v>
+        <v>-4.04</v>
       </c>
       <c r="C65">
-        <v>9.154999999999999</v>
+        <v>824.861</v>
       </c>
       <c r="D65">
-        <v>9.154999999999999</v>
+        <v>824.861</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
-        <v>97.96599999999999</v>
+        <v>78.962</v>
       </c>
       <c r="C66">
-        <v>-138.81</v>
+        <v>370.889</v>
       </c>
       <c r="D66">
-        <v>-138.81</v>
+        <v>370.889</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
-        <v>20.416</v>
+        <v>29.19</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
-        <v>16.038</v>
+        <v>37.041</v>
       </c>
       <c r="C68">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
-        <v>-17.975</v>
+        <v>15.137</v>
       </c>
       <c r="C69">
-        <v>1086.26</v>
+        <v>353.611</v>
       </c>
       <c r="D69">
-        <v>1086.26</v>
+        <v>353.611</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
-        <v>-21.327</v>
+        <v>17.031</v>
       </c>
       <c r="C70">
-        <v>4192.618</v>
+        <v>339.356</v>
       </c>
       <c r="D70">
-        <v>4192.618</v>
+        <v>339.356</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
-        <v>-17.975</v>
+        <v>7.198</v>
       </c>
       <c r="C71">
-        <v>1102.133</v>
+        <v>402</v>
       </c>
       <c r="D71">
-        <v>1102.133</v>
+        <v>402</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
-        <v>25.737</v>
+        <v>2.024</v>
       </c>
       <c r="C72">
-        <v>-76.584</v>
+        <v>971.42</v>
       </c>
       <c r="D72">
-        <v>-76.584</v>
+        <v>971.42</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
-        <v>52.884</v>
+        <v>-2.636</v>
       </c>
       <c r="C73">
-        <v>-2011.79</v>
+        <v>1022.191</v>
       </c>
       <c r="D73">
-        <v>-2011.79</v>
+        <v>1022.191</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
-        <v>80.51600000000001</v>
+        <v>-8.743</v>
       </c>
       <c r="C74">
-        <v>-1000.82</v>
+        <v>1287.001</v>
       </c>
       <c r="D74">
-        <v>-1000.82</v>
+        <v>1287.001</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
-        <v>138.151</v>
+        <v>-31.632</v>
       </c>
       <c r="C75">
-        <v>-397.257</v>
+        <v>1766.636</v>
       </c>
       <c r="D75">
-        <v>-397.257</v>
+        <v>1766.636</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
-        <v>75.502</v>
+        <v>-37.048</v>
       </c>
       <c r="C76">
-        <v>2.564</v>
+        <v>2274.86</v>
       </c>
       <c r="D76">
-        <v>2.564</v>
+        <v>2274.86</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
-        <v>59.739</v>
+        <v>-52.737</v>
       </c>
       <c r="C77">
-        <v>0.3</v>
+        <v>5767.801</v>
       </c>
       <c r="D77">
-        <v>0.3</v>
+        <v>5767.801</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
-        <v>131.878</v>
+        <v>-28.796</v>
       </c>
       <c r="C78">
-        <v>-1395.745</v>
+        <v>2211.597</v>
       </c>
       <c r="D78">
-        <v>-1395.745</v>
+        <v>2211.597</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
-        <v>79.121</v>
+        <v>-39.417</v>
       </c>
       <c r="C79">
-        <v>1.419</v>
+        <v>4208.757</v>
       </c>
       <c r="D79">
-        <v>1.419</v>
+        <v>4208.757</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
-        <v>-13.73</v>
+        <v>-74.21299999999999</v>
       </c>
       <c r="C80">
-        <v>1237.239</v>
+        <v>2009.316</v>
       </c>
       <c r="D80">
-        <v>1237.239</v>
+        <v>2009.316</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
-        <v>-57.927</v>
+        <v>-76.479</v>
       </c>
       <c r="C81">
-        <v>1189.435</v>
+        <v>3430.597</v>
       </c>
       <c r="D81">
-        <v>1189.435</v>
+        <v>3430.597</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
-        <v>-33.702</v>
+        <v>-40.81</v>
       </c>
       <c r="C82">
-        <v>3954.346</v>
+        <v>1437.187</v>
       </c>
       <c r="D82">
-        <v>3954.346</v>
+        <v>1437.187</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
-        <v>-65.2</v>
+        <v>-53.474</v>
       </c>
       <c r="C83">
-        <v>3118.465</v>
+        <v>1399.082</v>
       </c>
       <c r="D83">
-        <v>3118.465</v>
+        <v>1399.082</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
-        <v>-69.17700000000001</v>
+        <v>-6.486</v>
       </c>
       <c r="C84">
-        <v>1146.949</v>
+        <v>1445.237</v>
       </c>
       <c r="D84">
-        <v>1146.949</v>
+        <v>1445.237</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
-        <v>-53.617</v>
+        <v>5.755</v>
       </c>
       <c r="C85">
-        <v>1153.433</v>
+        <v>291.354</v>
       </c>
       <c r="D85">
-        <v>1153.433</v>
+        <v>291.354</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
-        <v>-0.144</v>
+        <v>-68.22499999999999</v>
       </c>
       <c r="C86">
-        <v>1145.062</v>
+        <v>4617.921</v>
       </c>
       <c r="D86">
-        <v>1145.062</v>
+        <v>4617.921</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
-        <v>7.87</v>
+        <v>-35.538</v>
       </c>
       <c r="C87">
-        <v>18.634</v>
+        <v>4758.783</v>
       </c>
       <c r="D87">
-        <v>18.634</v>
+        <v>4758.783</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
-        <v>25.451</v>
+        <v>-21.749</v>
       </c>
       <c r="C88">
-        <v>-2562.566</v>
+        <v>1350.866</v>
       </c>
       <c r="D88">
-        <v>-2562.566</v>
+        <v>1350.866</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
-        <v>48.59</v>
+        <v>-28.024</v>
       </c>
       <c r="C89">
-        <v>-6681.715</v>
+        <v>1920.231</v>
       </c>
       <c r="D89">
-        <v>-6681.715</v>
+        <v>1920.231</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
-        <v>52.103</v>
+        <v>-8.728999999999999</v>
       </c>
       <c r="C90">
-        <v>-1913.007</v>
+        <v>1184.11</v>
       </c>
       <c r="D90">
-        <v>-1913.007</v>
+        <v>1184.11</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
-        <v>80.431</v>
+        <v>-23.535</v>
       </c>
       <c r="C91">
-        <v>-1017.334</v>
+        <v>1031.704</v>
       </c>
       <c r="D91">
-        <v>-1017.334</v>
+        <v>1031.704</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
-        <v>55.225</v>
+        <v>-24.807</v>
       </c>
       <c r="C92">
-        <v>-1407.7</v>
+        <v>884.683</v>
       </c>
       <c r="D92">
-        <v>-1407.7</v>
+        <v>884.683</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
-        <v>32.723</v>
+        <v>-0.571</v>
       </c>
       <c r="C93">
-        <v>-632.658</v>
+        <v>896.542</v>
       </c>
       <c r="D93">
-        <v>-632.658</v>
+        <v>896.542</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
-        <v>-62.15</v>
+        <v>-31.753</v>
       </c>
       <c r="C94">
-        <v>863.213</v>
+        <v>924.687</v>
       </c>
       <c r="D94">
-        <v>863.213</v>
+        <v>924.687</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
-        <v>-72.56100000000001</v>
+        <v>-32.992</v>
       </c>
       <c r="C95">
-        <v>838.893</v>
+        <v>896.053</v>
       </c>
       <c r="D95">
-        <v>838.893</v>
+        <v>896.053</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
-        <v>-50.051</v>
+        <v>-32.26</v>
       </c>
       <c r="C96">
-        <v>894.995</v>
+        <v>804.659</v>
       </c>
       <c r="D96">
-        <v>894.995</v>
+        <v>804.659</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B97">
-        <v>-20.924</v>
+        <v>-9.146000000000001</v>
       </c>
       <c r="C97">
-        <v>902.852</v>
+        <v>894.02</v>
       </c>
       <c r="D97">
-        <v>902.852</v>
+        <v>894.02</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B98">
-        <v>70.131</v>
+        <v>-16.696</v>
       </c>
       <c r="C98">
-        <v>159.062</v>
+        <v>899.319</v>
       </c>
       <c r="D98">
-        <v>159.062</v>
+        <v>899.319</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46133.01041666666</v>
+        <v>46134.01041666666</v>
       </c>
       <c r="B99">
-        <v>89.557</v>
+        <v>-9.294</v>
       </c>
       <c r="C99">
-        <v>188.768</v>
+        <v>987.2430000000001</v>
       </c>
       <c r="D99">
-        <v>188.768</v>
+        <v>987.2430000000001</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46133.02083333334</v>
+        <v>46134.02083333334</v>
       </c>
       <c r="B100">
-        <v>86.83499999999999</v>
+        <v>-10.977</v>
       </c>
       <c r="C100">
-        <v>-1220.143</v>
+        <v>927.523</v>
       </c>
       <c r="D100">
-        <v>-1220.143</v>
+        <v>927.523</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46133.03125</v>
+        <v>46134.03125</v>
       </c>
       <c r="B101">
-        <v>70.631</v>
+        <v>-2.208</v>
       </c>
       <c r="C101">
-        <v>-4320.081</v>
+        <v>917.615</v>
       </c>
       <c r="D101">
-        <v>-4320.081</v>
+        <v>917.615</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46133.04166666666</v>
+        <v>46134.04166666666</v>
       </c>
       <c r="B102">
-        <v>148.873</v>
+        <v>-2.366</v>
       </c>
       <c r="C102">
-        <v>-4321.272</v>
+        <v>899.662</v>
       </c>
       <c r="D102">
-        <v>-4321.272</v>
+        <v>899.662</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46133.05208333334</v>
+        <v>46134.05208333334</v>
       </c>
       <c r="B103">
-        <v>200.676</v>
+        <v>-23.314</v>
       </c>
       <c r="C103">
-        <v>-2049.701</v>
+        <v>1059.207</v>
       </c>
       <c r="D103">
-        <v>-2049.701</v>
+        <v>1059.207</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46133.0625</v>
+        <v>46134.0625</v>
       </c>
       <c r="B104">
-        <v>154.428</v>
+        <v>-26.641</v>
       </c>
       <c r="C104">
-        <v>-6668.16</v>
+        <v>1039.351</v>
       </c>
       <c r="D104">
-        <v>-6668.16</v>
+        <v>1039.351</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46133.07291666666</v>
+        <v>46134.07291666666</v>
       </c>
       <c r="B105">
-        <v>89.70999999999999</v>
+        <v>-45.913</v>
       </c>
       <c r="C105">
-        <v>-749.404</v>
+        <v>899.048</v>
       </c>
       <c r="D105">
-        <v>-749.404</v>
+        <v>899.048</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46133.08333333334</v>
+        <v>46134.08333333334</v>
       </c>
       <c r="B106">
-        <v>90.03400000000001</v>
+        <v>-35.797</v>
       </c>
       <c r="C106">
-        <v>3.182</v>
+        <v>892.914</v>
       </c>
       <c r="D106">
-        <v>3.182</v>
+        <v>892.914</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46133.09375</v>
+        <v>46134.09375</v>
       </c>
       <c r="B107">
-        <v>34.275</v>
+        <v>-7.817</v>
       </c>
       <c r="C107">
-        <v>0.997</v>
+        <v>899.379</v>
       </c>
       <c r="D107">
-        <v>0.997</v>
+        <v>899.379</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46133.10416666666</v>
+        <v>46134.10416666666</v>
       </c>
       <c r="B108">
-        <v>70.977</v>
+        <v>-14.414</v>
       </c>
       <c r="C108">
-        <v>2.363</v>
+        <v>899.6609999999999</v>
       </c>
       <c r="D108">
-        <v>2.363</v>
+        <v>899.6609999999999</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46133.11458333334</v>
+        <v>46134.11458333334</v>
       </c>
       <c r="B109">
-        <v>32.471</v>
+        <v>-19.355</v>
       </c>
       <c r="C109">
-        <v>0.1</v>
+        <v>897.769</v>
       </c>
       <c r="D109">
-        <v>0.1</v>
+        <v>897.769</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46133.125</v>
+        <v>46134.125</v>
       </c>
       <c r="B110">
-        <v>54.087</v>
+        <v>-9.414</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>899.468</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>899.468</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46133.13541666666</v>
+        <v>46134.13541666666</v>
       </c>
       <c r="B111">
-        <v>34.991</v>
+        <v>-13.557</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>892.745</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>892.745</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46133.14583333334</v>
+        <v>46134.14583333334</v>
       </c>
       <c r="B112">
-        <v>25.736</v>
+        <v>-17.277</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>828.932</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>828.932</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46133.15625</v>
+        <v>46134.15625</v>
       </c>
       <c r="B113">
-        <v>30.622</v>
+        <v>-27.686</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>895.575</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>895.575</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46133.16666666666</v>
+        <v>46134.16666666666</v>
       </c>
       <c r="B114">
-        <v>44.432</v>
+        <v>-29.688</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>869.075</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>869.075</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46133.17708333334</v>
+        <v>46134.17708333334</v>
       </c>
       <c r="B115">
-        <v>19.559</v>
+        <v>-23.188</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>896.074</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>896.074</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46133.1875</v>
+        <v>46134.1875</v>
       </c>
       <c r="B116">
-        <v>-25.436</v>
+        <v>-30.014</v>
       </c>
       <c r="C116">
-        <v>928.45</v>
+        <v>940.436</v>
       </c>
       <c r="D116">
-        <v>928.45</v>
+        <v>940.436</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46133.19791666666</v>
+        <v>46134.19791666666</v>
       </c>
       <c r="B117">
-        <v>20.03</v>
+        <v>-23.18</v>
       </c>
       <c r="C117">
-        <v>0.1</v>
+        <v>899.273</v>
       </c>
       <c r="D117">
-        <v>0.1</v>
+        <v>899.273</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46133.20833333334</v>
+        <v>46134.20833333334</v>
       </c>
       <c r="B118">
-        <v>45.741</v>
+        <v>4.009</v>
       </c>
       <c r="C118">
-        <v>1.907</v>
+        <v>176.897</v>
       </c>
       <c r="D118">
-        <v>1.907</v>
+        <v>176.897</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46133.21875</v>
+        <v>46134.21875</v>
       </c>
       <c r="B119">
-        <v>26.095</v>
+        <v>20.227</v>
       </c>
       <c r="C119">
-        <v>299.48</v>
+        <v>400</v>
       </c>
       <c r="D119">
-        <v>299.48</v>
+        <v>400</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46133.22916666666</v>
+        <v>46134.22916666666</v>
       </c>
       <c r="B120">
-        <v>52.926</v>
+        <v>7.332</v>
       </c>
       <c r="C120">
-        <v>16.595</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>16.595</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46133.23958333334</v>
+        <v>46134.23958333334</v>
       </c>
       <c r="B121">
-        <v>25.922</v>
+        <v>5.653</v>
       </c>
       <c r="C121">
-        <v>34.092</v>
+        <v>372.2</v>
       </c>
       <c r="D121">
-        <v>34.092</v>
+        <v>372.2</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46133.25</v>
+        <v>46134.25</v>
       </c>
       <c r="B122">
-        <v>24.286</v>
+        <v>33.415</v>
       </c>
       <c r="C122">
-        <v>17.156</v>
+        <v>-221.24</v>
       </c>
       <c r="D122">
-        <v>17.156</v>
+        <v>-221.24</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46133.26041666666</v>
+        <v>46134.26041666666</v>
       </c>
       <c r="B123">
-        <v>48.657</v>
+        <v>4.428</v>
       </c>
       <c r="C123">
-        <v>4.904</v>
+        <v>400</v>
       </c>
       <c r="D123">
-        <v>4.904</v>
+        <v>400</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46133.27083333334</v>
+        <v>46134.27083333334</v>
       </c>
       <c r="B124">
-        <v>30.856</v>
+        <v>-4.864</v>
       </c>
       <c r="C124">
-        <v>15.459</v>
+        <v>897.872</v>
       </c>
       <c r="D124">
-        <v>15.459</v>
+        <v>897.872</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46133.28125</v>
+        <v>46134.28125</v>
       </c>
       <c r="B125">
-        <v>11.988</v>
+        <v>26.892</v>
       </c>
       <c r="C125">
-        <v>1.539</v>
+        <v>321.053</v>
       </c>
       <c r="D125">
-        <v>1.539</v>
+        <v>321.053</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46133.29166666666</v>
+        <v>46134.29166666666</v>
       </c>
       <c r="B126">
-        <v>32.308</v>
+        <v>86.658</v>
       </c>
       <c r="C126">
-        <v>251.991</v>
+        <v>290.83</v>
       </c>
       <c r="D126">
-        <v>251.991</v>
+        <v>290.83</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46133.30208333334</v>
+        <v>46134.30208333334</v>
       </c>
       <c r="B127">
-        <v>-2.967</v>
+        <v>54.527</v>
       </c>
       <c r="C127">
-        <v>890.456</v>
+        <v>-168.064</v>
       </c>
       <c r="D127">
-        <v>890.456</v>
+        <v>-168.064</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46133.3125</v>
+        <v>46134.3125</v>
       </c>
       <c r="B128">
-        <v>-7.156</v>
+        <v>58.408</v>
       </c>
       <c r="C128">
-        <v>896.1079999999999</v>
+        <v>-195.799</v>
       </c>
       <c r="D128">
-        <v>896.1079999999999</v>
+        <v>-195.799</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46133.32291666666</v>
+        <v>46134.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>65.322</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>21.548</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>21.548</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46133.33333333334</v>
+        <v>46134.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>120.213</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>9.595000000000001</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>9.595000000000001</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46133.34375</v>
+        <v>46134.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>71.986</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>28.078</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>28.078</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46133.35416666666</v>
+        <v>46134.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>29.625</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1.583</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>1.583</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46133.36458333334</v>
+        <v>46134.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>17.966</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46133.375</v>
+        <v>46134.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>18.756</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46133.38541666666</v>
+        <v>46134.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>6.724</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46133.39583333334</v>
+        <v>46134.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>39.638</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>4.765</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>4.765</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46133.40625</v>
+        <v>46134.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>83.667</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>191.436</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>191.436</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46133.41666666666</v>
+        <v>46134.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>78.29600000000001</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>-2707.818</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>-2707.818</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46133.42708333334</v>
+        <v>46134.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46133.4375</v>
+        <v>46134.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46133.44791666666</v>
+        <v>46134.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46133.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46133.46875</v>
+        <v>46134.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46133.47916666666</v>
+        <v>46134.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46133.48958333334</v>
+        <v>46134.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46133.5</v>
+        <v>46134.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46133.51041666666</v>
+        <v>46134.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46133.52083333334</v>
+        <v>46134.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46133.53125</v>
+        <v>46134.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46133.54166666666</v>
+        <v>46134.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46133.55208333334</v>
+        <v>46134.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46133.5625</v>
+        <v>46134.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46133.57291666666</v>
+        <v>46134.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46133.58333333334</v>
+        <v>46134.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46133.59375</v>
+        <v>46134.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46133.60416666666</v>
+        <v>46134.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46133.61458333334</v>
+        <v>46134.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46133.625</v>
+        <v>46134.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46133.63541666666</v>
+        <v>46134.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46133.64583333334</v>
+        <v>46134.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46133.65625</v>
+        <v>46134.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46133.66666666666</v>
+        <v>46134.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46133.67708333334</v>
+        <v>46134.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46133.6875</v>
+        <v>46134.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46133.69791666666</v>
+        <v>46134.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46133.70833333334</v>
+        <v>46134.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46133.71875</v>
+        <v>46134.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46133.72916666666</v>
+        <v>46134.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46133.73958333334</v>
+        <v>46134.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46133.75</v>
+        <v>46134.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46133.76041666666</v>
+        <v>46134.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46133.77083333334</v>
+        <v>46134.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46133.78125</v>
+        <v>46134.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46133.79166666666</v>
+        <v>46134.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46133.80208333334</v>
+        <v>46134.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46133.8125</v>
+        <v>46134.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46133.82291666666</v>
+        <v>46134.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46133.83333333334</v>
+        <v>46134.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46133.84375</v>
+        <v>46134.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46133.85416666666</v>
+        <v>46134.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46133.86458333334</v>
+        <v>46134.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46133.875</v>
+        <v>46134.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46133.88541666666</v>
+        <v>46134.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46133.89583333334</v>
+        <v>46134.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46133.90625</v>
+        <v>46134.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46133.91666666666</v>
+        <v>46134.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46133.92708333334</v>
+        <v>46134.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46133.9375</v>
+        <v>46134.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46133.94791666666</v>
+        <v>46134.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46133.95833333334</v>
+        <v>46134.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46133.96875</v>
+        <v>46134.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46133.97916666666</v>
+        <v>46134.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46133.98958333334</v>
+        <v>46134.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,580 +34,1156 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.04.20261</t>
-  </si>
-  <si>
-    <t>21.04.20262</t>
-  </si>
-  <si>
-    <t>21.04.20263</t>
-  </si>
-  <si>
-    <t>21.04.20264</t>
-  </si>
-  <si>
-    <t>21.04.20265</t>
-  </si>
-  <si>
-    <t>21.04.20266</t>
-  </si>
-  <si>
-    <t>21.04.20267</t>
-  </si>
-  <si>
-    <t>21.04.20268</t>
-  </si>
-  <si>
-    <t>21.04.20269</t>
-  </si>
-  <si>
-    <t>21.04.202610</t>
-  </si>
-  <si>
-    <t>21.04.202611</t>
-  </si>
-  <si>
-    <t>21.04.202612</t>
-  </si>
-  <si>
-    <t>21.04.202613</t>
-  </si>
-  <si>
-    <t>21.04.202614</t>
-  </si>
-  <si>
-    <t>21.04.202615</t>
-  </si>
-  <si>
-    <t>21.04.202616</t>
-  </si>
-  <si>
-    <t>21.04.202617</t>
-  </si>
-  <si>
-    <t>21.04.202618</t>
-  </si>
-  <si>
-    <t>21.04.202619</t>
-  </si>
-  <si>
-    <t>21.04.202620</t>
-  </si>
-  <si>
-    <t>21.04.202621</t>
-  </si>
-  <si>
-    <t>21.04.202622</t>
-  </si>
-  <si>
-    <t>21.04.202623</t>
-  </si>
-  <si>
-    <t>21.04.202624</t>
-  </si>
-  <si>
-    <t>21.04.202625</t>
-  </si>
-  <si>
-    <t>21.04.202626</t>
-  </si>
-  <si>
-    <t>21.04.202627</t>
-  </si>
-  <si>
-    <t>21.04.202628</t>
-  </si>
-  <si>
-    <t>21.04.202629</t>
-  </si>
-  <si>
-    <t>21.04.202630</t>
-  </si>
-  <si>
-    <t>21.04.202631</t>
-  </si>
-  <si>
-    <t>21.04.202632</t>
-  </si>
-  <si>
-    <t>21.04.202633</t>
-  </si>
-  <si>
-    <t>21.04.202634</t>
-  </si>
-  <si>
-    <t>21.04.202635</t>
-  </si>
-  <si>
-    <t>21.04.202636</t>
-  </si>
-  <si>
-    <t>21.04.202637</t>
-  </si>
-  <si>
-    <t>21.04.202638</t>
-  </si>
-  <si>
-    <t>21.04.202639</t>
-  </si>
-  <si>
-    <t>21.04.202640</t>
-  </si>
-  <si>
-    <t>21.04.202641</t>
-  </si>
-  <si>
-    <t>21.04.202642</t>
-  </si>
-  <si>
-    <t>21.04.202643</t>
-  </si>
-  <si>
-    <t>21.04.202644</t>
-  </si>
-  <si>
-    <t>21.04.202645</t>
-  </si>
-  <si>
-    <t>21.04.202646</t>
-  </si>
-  <si>
-    <t>21.04.202647</t>
-  </si>
-  <si>
-    <t>21.04.202648</t>
-  </si>
-  <si>
-    <t>21.04.202649</t>
-  </si>
-  <si>
-    <t>21.04.202650</t>
-  </si>
-  <si>
-    <t>21.04.202651</t>
-  </si>
-  <si>
-    <t>21.04.202652</t>
-  </si>
-  <si>
-    <t>21.04.202653</t>
-  </si>
-  <si>
-    <t>21.04.202654</t>
-  </si>
-  <si>
-    <t>21.04.202655</t>
-  </si>
-  <si>
-    <t>21.04.202656</t>
-  </si>
-  <si>
-    <t>21.04.202657</t>
-  </si>
-  <si>
-    <t>21.04.202658</t>
-  </si>
-  <si>
-    <t>21.04.202659</t>
-  </si>
-  <si>
-    <t>21.04.202660</t>
-  </si>
-  <si>
-    <t>21.04.202661</t>
-  </si>
-  <si>
-    <t>21.04.202662</t>
-  </si>
-  <si>
-    <t>21.04.202663</t>
-  </si>
-  <si>
-    <t>21.04.202664</t>
-  </si>
-  <si>
-    <t>21.04.202665</t>
-  </si>
-  <si>
-    <t>21.04.202666</t>
-  </si>
-  <si>
-    <t>21.04.202667</t>
-  </si>
-  <si>
-    <t>21.04.202668</t>
-  </si>
-  <si>
-    <t>21.04.202669</t>
-  </si>
-  <si>
-    <t>21.04.202670</t>
-  </si>
-  <si>
-    <t>21.04.202671</t>
-  </si>
-  <si>
-    <t>21.04.202672</t>
-  </si>
-  <si>
-    <t>21.04.202673</t>
-  </si>
-  <si>
-    <t>21.04.202674</t>
-  </si>
-  <si>
-    <t>21.04.202675</t>
-  </si>
-  <si>
-    <t>21.04.202676</t>
-  </si>
-  <si>
-    <t>21.04.202677</t>
-  </si>
-  <si>
-    <t>21.04.202678</t>
-  </si>
-  <si>
-    <t>21.04.202679</t>
-  </si>
-  <si>
-    <t>21.04.202680</t>
-  </si>
-  <si>
-    <t>21.04.202681</t>
-  </si>
-  <si>
-    <t>21.04.202682</t>
-  </si>
-  <si>
-    <t>21.04.202683</t>
-  </si>
-  <si>
-    <t>21.04.202684</t>
-  </si>
-  <si>
-    <t>21.04.202685</t>
-  </si>
-  <si>
-    <t>21.04.202686</t>
-  </si>
-  <si>
-    <t>21.04.202687</t>
-  </si>
-  <si>
-    <t>21.04.202688</t>
-  </si>
-  <si>
-    <t>21.04.202689</t>
-  </si>
-  <si>
-    <t>21.04.202690</t>
-  </si>
-  <si>
-    <t>21.04.202691</t>
-  </si>
-  <si>
-    <t>21.04.202692</t>
-  </si>
-  <si>
-    <t>21.04.202693</t>
-  </si>
-  <si>
-    <t>21.04.202694</t>
-  </si>
-  <si>
-    <t>21.04.202695</t>
-  </si>
-  <si>
-    <t>21.04.202696</t>
-  </si>
-  <si>
-    <t>22.04.20261</t>
-  </si>
-  <si>
-    <t>22.04.20262</t>
-  </si>
-  <si>
-    <t>22.04.20263</t>
-  </si>
-  <si>
-    <t>22.04.20264</t>
-  </si>
-  <si>
-    <t>22.04.20265</t>
-  </si>
-  <si>
-    <t>22.04.20266</t>
-  </si>
-  <si>
-    <t>22.04.20267</t>
-  </si>
-  <si>
-    <t>22.04.20268</t>
-  </si>
-  <si>
-    <t>22.04.20269</t>
-  </si>
-  <si>
-    <t>22.04.202610</t>
-  </si>
-  <si>
-    <t>22.04.202611</t>
-  </si>
-  <si>
-    <t>22.04.202612</t>
-  </si>
-  <si>
-    <t>22.04.202613</t>
-  </si>
-  <si>
-    <t>22.04.202614</t>
-  </si>
-  <si>
-    <t>22.04.202615</t>
-  </si>
-  <si>
-    <t>22.04.202616</t>
-  </si>
-  <si>
-    <t>22.04.202617</t>
-  </si>
-  <si>
-    <t>22.04.202618</t>
-  </si>
-  <si>
-    <t>22.04.202619</t>
-  </si>
-  <si>
-    <t>22.04.202620</t>
-  </si>
-  <si>
-    <t>22.04.202621</t>
-  </si>
-  <si>
-    <t>22.04.202622</t>
-  </si>
-  <si>
-    <t>22.04.202623</t>
-  </si>
-  <si>
-    <t>22.04.202624</t>
-  </si>
-  <si>
-    <t>22.04.202625</t>
-  </si>
-  <si>
-    <t>22.04.202626</t>
-  </si>
-  <si>
-    <t>22.04.202627</t>
-  </si>
-  <si>
-    <t>22.04.202628</t>
-  </si>
-  <si>
-    <t>22.04.202629</t>
-  </si>
-  <si>
-    <t>22.04.202630</t>
-  </si>
-  <si>
-    <t>22.04.202631</t>
-  </si>
-  <si>
-    <t>22.04.202632</t>
-  </si>
-  <si>
-    <t>22.04.202633</t>
-  </si>
-  <si>
-    <t>22.04.202634</t>
-  </si>
-  <si>
-    <t>22.04.202635</t>
-  </si>
-  <si>
-    <t>22.04.202636</t>
-  </si>
-  <si>
-    <t>22.04.202637</t>
-  </si>
-  <si>
-    <t>22.04.202638</t>
-  </si>
-  <si>
-    <t>22.04.202639</t>
-  </si>
-  <si>
-    <t>22.04.202640</t>
-  </si>
-  <si>
-    <t>22.04.202641</t>
-  </si>
-  <si>
-    <t>22.04.202642</t>
-  </si>
-  <si>
-    <t>22.04.202643</t>
-  </si>
-  <si>
-    <t>22.04.202644</t>
-  </si>
-  <si>
-    <t>22.04.202645</t>
-  </si>
-  <si>
-    <t>22.04.202646</t>
-  </si>
-  <si>
-    <t>22.04.202647</t>
-  </si>
-  <si>
-    <t>22.04.202648</t>
-  </si>
-  <si>
-    <t>22.04.202649</t>
-  </si>
-  <si>
-    <t>22.04.202650</t>
-  </si>
-  <si>
-    <t>22.04.202651</t>
-  </si>
-  <si>
-    <t>22.04.202652</t>
-  </si>
-  <si>
-    <t>22.04.202653</t>
-  </si>
-  <si>
-    <t>22.04.202654</t>
-  </si>
-  <si>
-    <t>22.04.202655</t>
-  </si>
-  <si>
-    <t>22.04.202656</t>
-  </si>
-  <si>
-    <t>22.04.202657</t>
-  </si>
-  <si>
-    <t>22.04.202658</t>
-  </si>
-  <si>
-    <t>22.04.202659</t>
-  </si>
-  <si>
-    <t>22.04.202660</t>
-  </si>
-  <si>
-    <t>22.04.202661</t>
-  </si>
-  <si>
-    <t>22.04.202662</t>
-  </si>
-  <si>
-    <t>22.04.202663</t>
-  </si>
-  <si>
-    <t>22.04.202664</t>
-  </si>
-  <si>
-    <t>22.04.202665</t>
-  </si>
-  <si>
-    <t>22.04.202666</t>
-  </si>
-  <si>
-    <t>22.04.202667</t>
-  </si>
-  <si>
-    <t>22.04.202668</t>
-  </si>
-  <si>
-    <t>22.04.202669</t>
-  </si>
-  <si>
-    <t>22.04.202670</t>
-  </si>
-  <si>
-    <t>22.04.202671</t>
-  </si>
-  <si>
-    <t>22.04.202672</t>
-  </si>
-  <si>
-    <t>22.04.202673</t>
-  </si>
-  <si>
-    <t>22.04.202674</t>
-  </si>
-  <si>
-    <t>22.04.202675</t>
-  </si>
-  <si>
-    <t>22.04.202676</t>
-  </si>
-  <si>
-    <t>22.04.202677</t>
-  </si>
-  <si>
-    <t>22.04.202678</t>
-  </si>
-  <si>
-    <t>22.04.202679</t>
-  </si>
-  <si>
-    <t>22.04.202680</t>
-  </si>
-  <si>
-    <t>22.04.202681</t>
-  </si>
-  <si>
-    <t>22.04.202682</t>
-  </si>
-  <si>
-    <t>22.04.202683</t>
-  </si>
-  <si>
-    <t>22.04.202684</t>
-  </si>
-  <si>
-    <t>22.04.202685</t>
-  </si>
-  <si>
-    <t>22.04.202686</t>
-  </si>
-  <si>
-    <t>22.04.202687</t>
-  </si>
-  <si>
-    <t>22.04.202688</t>
-  </si>
-  <si>
-    <t>22.04.202689</t>
-  </si>
-  <si>
-    <t>22.04.202690</t>
-  </si>
-  <si>
-    <t>22.04.202691</t>
-  </si>
-  <si>
-    <t>22.04.202692</t>
-  </si>
-  <si>
-    <t>22.04.202693</t>
-  </si>
-  <si>
-    <t>22.04.202694</t>
-  </si>
-  <si>
-    <t>22.04.202695</t>
-  </si>
-  <si>
-    <t>22.04.202696</t>
+    <t>24.04.20261</t>
+  </si>
+  <si>
+    <t>24.04.20262</t>
+  </si>
+  <si>
+    <t>24.04.20263</t>
+  </si>
+  <si>
+    <t>24.04.20264</t>
+  </si>
+  <si>
+    <t>24.04.20265</t>
+  </si>
+  <si>
+    <t>24.04.20266</t>
+  </si>
+  <si>
+    <t>24.04.20267</t>
+  </si>
+  <si>
+    <t>24.04.20268</t>
+  </si>
+  <si>
+    <t>24.04.20269</t>
+  </si>
+  <si>
+    <t>24.04.202610</t>
+  </si>
+  <si>
+    <t>24.04.202611</t>
+  </si>
+  <si>
+    <t>24.04.202612</t>
+  </si>
+  <si>
+    <t>24.04.202613</t>
+  </si>
+  <si>
+    <t>24.04.202614</t>
+  </si>
+  <si>
+    <t>24.04.202615</t>
+  </si>
+  <si>
+    <t>24.04.202616</t>
+  </si>
+  <si>
+    <t>24.04.202617</t>
+  </si>
+  <si>
+    <t>24.04.202618</t>
+  </si>
+  <si>
+    <t>24.04.202619</t>
+  </si>
+  <si>
+    <t>24.04.202620</t>
+  </si>
+  <si>
+    <t>24.04.202621</t>
+  </si>
+  <si>
+    <t>24.04.202622</t>
+  </si>
+  <si>
+    <t>24.04.202623</t>
+  </si>
+  <si>
+    <t>24.04.202624</t>
+  </si>
+  <si>
+    <t>24.04.202625</t>
+  </si>
+  <si>
+    <t>24.04.202626</t>
+  </si>
+  <si>
+    <t>24.04.202627</t>
+  </si>
+  <si>
+    <t>24.04.202628</t>
+  </si>
+  <si>
+    <t>24.04.202629</t>
+  </si>
+  <si>
+    <t>24.04.202630</t>
+  </si>
+  <si>
+    <t>24.04.202631</t>
+  </si>
+  <si>
+    <t>24.04.202632</t>
+  </si>
+  <si>
+    <t>24.04.202633</t>
+  </si>
+  <si>
+    <t>24.04.202634</t>
+  </si>
+  <si>
+    <t>24.04.202635</t>
+  </si>
+  <si>
+    <t>24.04.202636</t>
+  </si>
+  <si>
+    <t>24.04.202637</t>
+  </si>
+  <si>
+    <t>24.04.202638</t>
+  </si>
+  <si>
+    <t>24.04.202639</t>
+  </si>
+  <si>
+    <t>24.04.202640</t>
+  </si>
+  <si>
+    <t>24.04.202641</t>
+  </si>
+  <si>
+    <t>24.04.202642</t>
+  </si>
+  <si>
+    <t>24.04.202643</t>
+  </si>
+  <si>
+    <t>24.04.202644</t>
+  </si>
+  <si>
+    <t>24.04.202645</t>
+  </si>
+  <si>
+    <t>24.04.202646</t>
+  </si>
+  <si>
+    <t>24.04.202647</t>
+  </si>
+  <si>
+    <t>24.04.202648</t>
+  </si>
+  <si>
+    <t>24.04.202649</t>
+  </si>
+  <si>
+    <t>24.04.202650</t>
+  </si>
+  <si>
+    <t>24.04.202651</t>
+  </si>
+  <si>
+    <t>24.04.202652</t>
+  </si>
+  <si>
+    <t>24.04.202653</t>
+  </si>
+  <si>
+    <t>24.04.202654</t>
+  </si>
+  <si>
+    <t>24.04.202655</t>
+  </si>
+  <si>
+    <t>24.04.202656</t>
+  </si>
+  <si>
+    <t>24.04.202657</t>
+  </si>
+  <si>
+    <t>24.04.202658</t>
+  </si>
+  <si>
+    <t>24.04.202659</t>
+  </si>
+  <si>
+    <t>24.04.202660</t>
+  </si>
+  <si>
+    <t>24.04.202661</t>
+  </si>
+  <si>
+    <t>24.04.202662</t>
+  </si>
+  <si>
+    <t>24.04.202663</t>
+  </si>
+  <si>
+    <t>24.04.202664</t>
+  </si>
+  <si>
+    <t>24.04.202665</t>
+  </si>
+  <si>
+    <t>24.04.202666</t>
+  </si>
+  <si>
+    <t>24.04.202667</t>
+  </si>
+  <si>
+    <t>24.04.202668</t>
+  </si>
+  <si>
+    <t>24.04.202669</t>
+  </si>
+  <si>
+    <t>24.04.202670</t>
+  </si>
+  <si>
+    <t>24.04.202671</t>
+  </si>
+  <si>
+    <t>24.04.202672</t>
+  </si>
+  <si>
+    <t>24.04.202673</t>
+  </si>
+  <si>
+    <t>24.04.202674</t>
+  </si>
+  <si>
+    <t>24.04.202675</t>
+  </si>
+  <si>
+    <t>24.04.202676</t>
+  </si>
+  <si>
+    <t>24.04.202677</t>
+  </si>
+  <si>
+    <t>24.04.202678</t>
+  </si>
+  <si>
+    <t>24.04.202679</t>
+  </si>
+  <si>
+    <t>24.04.202680</t>
+  </si>
+  <si>
+    <t>24.04.202681</t>
+  </si>
+  <si>
+    <t>24.04.202682</t>
+  </si>
+  <si>
+    <t>24.04.202683</t>
+  </si>
+  <si>
+    <t>24.04.202684</t>
+  </si>
+  <si>
+    <t>24.04.202685</t>
+  </si>
+  <si>
+    <t>24.04.202686</t>
+  </si>
+  <si>
+    <t>24.04.202687</t>
+  </si>
+  <si>
+    <t>24.04.202688</t>
+  </si>
+  <si>
+    <t>24.04.202689</t>
+  </si>
+  <si>
+    <t>24.04.202690</t>
+  </si>
+  <si>
+    <t>24.04.202691</t>
+  </si>
+  <si>
+    <t>24.04.202692</t>
+  </si>
+  <si>
+    <t>24.04.202693</t>
+  </si>
+  <si>
+    <t>24.04.202694</t>
+  </si>
+  <si>
+    <t>24.04.202695</t>
+  </si>
+  <si>
+    <t>24.04.202696</t>
+  </si>
+  <si>
+    <t>25.04.20261</t>
+  </si>
+  <si>
+    <t>25.04.20262</t>
+  </si>
+  <si>
+    <t>25.04.20263</t>
+  </si>
+  <si>
+    <t>25.04.20264</t>
+  </si>
+  <si>
+    <t>25.04.20265</t>
+  </si>
+  <si>
+    <t>25.04.20266</t>
+  </si>
+  <si>
+    <t>25.04.20267</t>
+  </si>
+  <si>
+    <t>25.04.20268</t>
+  </si>
+  <si>
+    <t>25.04.20269</t>
+  </si>
+  <si>
+    <t>25.04.202610</t>
+  </si>
+  <si>
+    <t>25.04.202611</t>
+  </si>
+  <si>
+    <t>25.04.202612</t>
+  </si>
+  <si>
+    <t>25.04.202613</t>
+  </si>
+  <si>
+    <t>25.04.202614</t>
+  </si>
+  <si>
+    <t>25.04.202615</t>
+  </si>
+  <si>
+    <t>25.04.202616</t>
+  </si>
+  <si>
+    <t>25.04.202617</t>
+  </si>
+  <si>
+    <t>25.04.202618</t>
+  </si>
+  <si>
+    <t>25.04.202619</t>
+  </si>
+  <si>
+    <t>25.04.202620</t>
+  </si>
+  <si>
+    <t>25.04.202621</t>
+  </si>
+  <si>
+    <t>25.04.202622</t>
+  </si>
+  <si>
+    <t>25.04.202623</t>
+  </si>
+  <si>
+    <t>25.04.202624</t>
+  </si>
+  <si>
+    <t>25.04.202625</t>
+  </si>
+  <si>
+    <t>25.04.202626</t>
+  </si>
+  <si>
+    <t>25.04.202627</t>
+  </si>
+  <si>
+    <t>25.04.202628</t>
+  </si>
+  <si>
+    <t>25.04.202629</t>
+  </si>
+  <si>
+    <t>25.04.202630</t>
+  </si>
+  <si>
+    <t>25.04.202631</t>
+  </si>
+  <si>
+    <t>25.04.202632</t>
+  </si>
+  <si>
+    <t>25.04.202633</t>
+  </si>
+  <si>
+    <t>25.04.202634</t>
+  </si>
+  <si>
+    <t>25.04.202635</t>
+  </si>
+  <si>
+    <t>25.04.202636</t>
+  </si>
+  <si>
+    <t>25.04.202637</t>
+  </si>
+  <si>
+    <t>25.04.202638</t>
+  </si>
+  <si>
+    <t>25.04.202639</t>
+  </si>
+  <si>
+    <t>25.04.202640</t>
+  </si>
+  <si>
+    <t>25.04.202641</t>
+  </si>
+  <si>
+    <t>25.04.202642</t>
+  </si>
+  <si>
+    <t>25.04.202643</t>
+  </si>
+  <si>
+    <t>25.04.202644</t>
+  </si>
+  <si>
+    <t>25.04.202645</t>
+  </si>
+  <si>
+    <t>25.04.202646</t>
+  </si>
+  <si>
+    <t>25.04.202647</t>
+  </si>
+  <si>
+    <t>25.04.202648</t>
+  </si>
+  <si>
+    <t>25.04.202649</t>
+  </si>
+  <si>
+    <t>25.04.202650</t>
+  </si>
+  <si>
+    <t>25.04.202651</t>
+  </si>
+  <si>
+    <t>25.04.202652</t>
+  </si>
+  <si>
+    <t>25.04.202653</t>
+  </si>
+  <si>
+    <t>25.04.202654</t>
+  </si>
+  <si>
+    <t>25.04.202655</t>
+  </si>
+  <si>
+    <t>25.04.202656</t>
+  </si>
+  <si>
+    <t>25.04.202657</t>
+  </si>
+  <si>
+    <t>25.04.202658</t>
+  </si>
+  <si>
+    <t>25.04.202659</t>
+  </si>
+  <si>
+    <t>25.04.202660</t>
+  </si>
+  <si>
+    <t>25.04.202661</t>
+  </si>
+  <si>
+    <t>25.04.202662</t>
+  </si>
+  <si>
+    <t>25.04.202663</t>
+  </si>
+  <si>
+    <t>25.04.202664</t>
+  </si>
+  <si>
+    <t>25.04.202665</t>
+  </si>
+  <si>
+    <t>25.04.202666</t>
+  </si>
+  <si>
+    <t>25.04.202667</t>
+  </si>
+  <si>
+    <t>25.04.202668</t>
+  </si>
+  <si>
+    <t>25.04.202669</t>
+  </si>
+  <si>
+    <t>25.04.202670</t>
+  </si>
+  <si>
+    <t>25.04.202671</t>
+  </si>
+  <si>
+    <t>25.04.202672</t>
+  </si>
+  <si>
+    <t>25.04.202673</t>
+  </si>
+  <si>
+    <t>25.04.202674</t>
+  </si>
+  <si>
+    <t>25.04.202675</t>
+  </si>
+  <si>
+    <t>25.04.202676</t>
+  </si>
+  <si>
+    <t>25.04.202677</t>
+  </si>
+  <si>
+    <t>25.04.202678</t>
+  </si>
+  <si>
+    <t>25.04.202679</t>
+  </si>
+  <si>
+    <t>25.04.202680</t>
+  </si>
+  <si>
+    <t>25.04.202681</t>
+  </si>
+  <si>
+    <t>25.04.202682</t>
+  </si>
+  <si>
+    <t>25.04.202683</t>
+  </si>
+  <si>
+    <t>25.04.202684</t>
+  </si>
+  <si>
+    <t>25.04.202685</t>
+  </si>
+  <si>
+    <t>25.04.202686</t>
+  </si>
+  <si>
+    <t>25.04.202687</t>
+  </si>
+  <si>
+    <t>25.04.202688</t>
+  </si>
+  <si>
+    <t>25.04.202689</t>
+  </si>
+  <si>
+    <t>25.04.202690</t>
+  </si>
+  <si>
+    <t>25.04.202691</t>
+  </si>
+  <si>
+    <t>25.04.202692</t>
+  </si>
+  <si>
+    <t>25.04.202693</t>
+  </si>
+  <si>
+    <t>25.04.202694</t>
+  </si>
+  <si>
+    <t>25.04.202695</t>
+  </si>
+  <si>
+    <t>25.04.202696</t>
+  </si>
+  <si>
+    <t>26.04.20261</t>
+  </si>
+  <si>
+    <t>26.04.20262</t>
+  </si>
+  <si>
+    <t>26.04.20263</t>
+  </si>
+  <si>
+    <t>26.04.20264</t>
+  </si>
+  <si>
+    <t>26.04.20265</t>
+  </si>
+  <si>
+    <t>26.04.20266</t>
+  </si>
+  <si>
+    <t>26.04.20267</t>
+  </si>
+  <si>
+    <t>26.04.20268</t>
+  </si>
+  <si>
+    <t>26.04.20269</t>
+  </si>
+  <si>
+    <t>26.04.202610</t>
+  </si>
+  <si>
+    <t>26.04.202611</t>
+  </si>
+  <si>
+    <t>26.04.202612</t>
+  </si>
+  <si>
+    <t>26.04.202613</t>
+  </si>
+  <si>
+    <t>26.04.202614</t>
+  </si>
+  <si>
+    <t>26.04.202615</t>
+  </si>
+  <si>
+    <t>26.04.202616</t>
+  </si>
+  <si>
+    <t>26.04.202617</t>
+  </si>
+  <si>
+    <t>26.04.202618</t>
+  </si>
+  <si>
+    <t>26.04.202619</t>
+  </si>
+  <si>
+    <t>26.04.202620</t>
+  </si>
+  <si>
+    <t>26.04.202621</t>
+  </si>
+  <si>
+    <t>26.04.202622</t>
+  </si>
+  <si>
+    <t>26.04.202623</t>
+  </si>
+  <si>
+    <t>26.04.202624</t>
+  </si>
+  <si>
+    <t>26.04.202625</t>
+  </si>
+  <si>
+    <t>26.04.202626</t>
+  </si>
+  <si>
+    <t>26.04.202627</t>
+  </si>
+  <si>
+    <t>26.04.202628</t>
+  </si>
+  <si>
+    <t>26.04.202629</t>
+  </si>
+  <si>
+    <t>26.04.202630</t>
+  </si>
+  <si>
+    <t>26.04.202631</t>
+  </si>
+  <si>
+    <t>26.04.202632</t>
+  </si>
+  <si>
+    <t>26.04.202633</t>
+  </si>
+  <si>
+    <t>26.04.202634</t>
+  </si>
+  <si>
+    <t>26.04.202635</t>
+  </si>
+  <si>
+    <t>26.04.202636</t>
+  </si>
+  <si>
+    <t>26.04.202637</t>
+  </si>
+  <si>
+    <t>26.04.202638</t>
+  </si>
+  <si>
+    <t>26.04.202639</t>
+  </si>
+  <si>
+    <t>26.04.202640</t>
+  </si>
+  <si>
+    <t>26.04.202641</t>
+  </si>
+  <si>
+    <t>26.04.202642</t>
+  </si>
+  <si>
+    <t>26.04.202643</t>
+  </si>
+  <si>
+    <t>26.04.202644</t>
+  </si>
+  <si>
+    <t>26.04.202645</t>
+  </si>
+  <si>
+    <t>26.04.202646</t>
+  </si>
+  <si>
+    <t>26.04.202647</t>
+  </si>
+  <si>
+    <t>26.04.202648</t>
+  </si>
+  <si>
+    <t>26.04.202649</t>
+  </si>
+  <si>
+    <t>26.04.202650</t>
+  </si>
+  <si>
+    <t>26.04.202651</t>
+  </si>
+  <si>
+    <t>26.04.202652</t>
+  </si>
+  <si>
+    <t>26.04.202653</t>
+  </si>
+  <si>
+    <t>26.04.202654</t>
+  </si>
+  <si>
+    <t>26.04.202655</t>
+  </si>
+  <si>
+    <t>26.04.202656</t>
+  </si>
+  <si>
+    <t>26.04.202657</t>
+  </si>
+  <si>
+    <t>26.04.202658</t>
+  </si>
+  <si>
+    <t>26.04.202659</t>
+  </si>
+  <si>
+    <t>26.04.202660</t>
+  </si>
+  <si>
+    <t>26.04.202661</t>
+  </si>
+  <si>
+    <t>26.04.202662</t>
+  </si>
+  <si>
+    <t>26.04.202663</t>
+  </si>
+  <si>
+    <t>26.04.202664</t>
+  </si>
+  <si>
+    <t>26.04.202665</t>
+  </si>
+  <si>
+    <t>26.04.202666</t>
+  </si>
+  <si>
+    <t>26.04.202667</t>
+  </si>
+  <si>
+    <t>26.04.202668</t>
+  </si>
+  <si>
+    <t>26.04.202669</t>
+  </si>
+  <si>
+    <t>26.04.202670</t>
+  </si>
+  <si>
+    <t>26.04.202671</t>
+  </si>
+  <si>
+    <t>26.04.202672</t>
+  </si>
+  <si>
+    <t>26.04.202673</t>
+  </si>
+  <si>
+    <t>26.04.202674</t>
+  </si>
+  <si>
+    <t>26.04.202675</t>
+  </si>
+  <si>
+    <t>26.04.202676</t>
+  </si>
+  <si>
+    <t>26.04.202677</t>
+  </si>
+  <si>
+    <t>26.04.202678</t>
+  </si>
+  <si>
+    <t>26.04.202679</t>
+  </si>
+  <si>
+    <t>26.04.202680</t>
+  </si>
+  <si>
+    <t>26.04.202681</t>
+  </si>
+  <si>
+    <t>26.04.202682</t>
+  </si>
+  <si>
+    <t>26.04.202683</t>
+  </si>
+  <si>
+    <t>26.04.202684</t>
+  </si>
+  <si>
+    <t>26.04.202685</t>
+  </si>
+  <si>
+    <t>26.04.202686</t>
+  </si>
+  <si>
+    <t>26.04.202687</t>
+  </si>
+  <si>
+    <t>26.04.202688</t>
+  </si>
+  <si>
+    <t>26.04.202689</t>
+  </si>
+  <si>
+    <t>26.04.202690</t>
+  </si>
+  <si>
+    <t>26.04.202691</t>
+  </si>
+  <si>
+    <t>26.04.202692</t>
+  </si>
+  <si>
+    <t>26.04.202693</t>
+  </si>
+  <si>
+    <t>26.04.202694</t>
+  </si>
+  <si>
+    <t>26.04.202695</t>
+  </si>
+  <si>
+    <t>26.04.202696</t>
+  </si>
+  <si>
+    <t>27.04.20261</t>
+  </si>
+  <si>
+    <t>27.04.20262</t>
+  </si>
+  <si>
+    <t>27.04.20263</t>
+  </si>
+  <si>
+    <t>27.04.20264</t>
+  </si>
+  <si>
+    <t>27.04.20265</t>
+  </si>
+  <si>
+    <t>27.04.20266</t>
+  </si>
+  <si>
+    <t>27.04.20267</t>
+  </si>
+  <si>
+    <t>27.04.20268</t>
+  </si>
+  <si>
+    <t>27.04.20269</t>
+  </si>
+  <si>
+    <t>27.04.202610</t>
+  </si>
+  <si>
+    <t>27.04.202611</t>
+  </si>
+  <si>
+    <t>27.04.202612</t>
+  </si>
+  <si>
+    <t>27.04.202613</t>
+  </si>
+  <si>
+    <t>27.04.202614</t>
+  </si>
+  <si>
+    <t>27.04.202615</t>
+  </si>
+  <si>
+    <t>27.04.202616</t>
+  </si>
+  <si>
+    <t>27.04.202617</t>
+  </si>
+  <si>
+    <t>27.04.202618</t>
+  </si>
+  <si>
+    <t>27.04.202619</t>
+  </si>
+  <si>
+    <t>27.04.202620</t>
+  </si>
+  <si>
+    <t>27.04.202621</t>
+  </si>
+  <si>
+    <t>27.04.202622</t>
+  </si>
+  <si>
+    <t>27.04.202623</t>
+  </si>
+  <si>
+    <t>27.04.202624</t>
+  </si>
+  <si>
+    <t>27.04.202625</t>
+  </si>
+  <si>
+    <t>27.04.202626</t>
+  </si>
+  <si>
+    <t>27.04.202627</t>
+  </si>
+  <si>
+    <t>27.04.202628</t>
+  </si>
+  <si>
+    <t>27.04.202629</t>
+  </si>
+  <si>
+    <t>27.04.202630</t>
+  </si>
+  <si>
+    <t>27.04.202631</t>
+  </si>
+  <si>
+    <t>27.04.202632</t>
+  </si>
+  <si>
+    <t>27.04.202633</t>
+  </si>
+  <si>
+    <t>27.04.202634</t>
+  </si>
+  <si>
+    <t>27.04.202635</t>
+  </si>
+  <si>
+    <t>27.04.202636</t>
+  </si>
+  <si>
+    <t>27.04.202637</t>
+  </si>
+  <si>
+    <t>27.04.202638</t>
+  </si>
+  <si>
+    <t>27.04.202639</t>
+  </si>
+  <si>
+    <t>27.04.202640</t>
+  </si>
+  <si>
+    <t>27.04.202641</t>
+  </si>
+  <si>
+    <t>27.04.202642</t>
+  </si>
+  <si>
+    <t>27.04.202643</t>
+  </si>
+  <si>
+    <t>27.04.202644</t>
+  </si>
+  <si>
+    <t>27.04.202645</t>
+  </si>
+  <si>
+    <t>27.04.202646</t>
+  </si>
+  <si>
+    <t>27.04.202647</t>
+  </si>
+  <si>
+    <t>27.04.202648</t>
+  </si>
+  <si>
+    <t>27.04.202649</t>
+  </si>
+  <si>
+    <t>27.04.202650</t>
+  </si>
+  <si>
+    <t>27.04.202651</t>
+  </si>
+  <si>
+    <t>27.04.202652</t>
+  </si>
+  <si>
+    <t>27.04.202653</t>
+  </si>
+  <si>
+    <t>27.04.202654</t>
+  </si>
+  <si>
+    <t>27.04.202655</t>
+  </si>
+  <si>
+    <t>27.04.202656</t>
+  </si>
+  <si>
+    <t>27.04.202657</t>
+  </si>
+  <si>
+    <t>27.04.202658</t>
+  </si>
+  <si>
+    <t>27.04.202659</t>
+  </si>
+  <si>
+    <t>27.04.202660</t>
+  </si>
+  <si>
+    <t>27.04.202661</t>
+  </si>
+  <si>
+    <t>27.04.202662</t>
+  </si>
+  <si>
+    <t>27.04.202663</t>
+  </si>
+  <si>
+    <t>27.04.202664</t>
+  </si>
+  <si>
+    <t>27.04.202665</t>
+  </si>
+  <si>
+    <t>27.04.202666</t>
+  </si>
+  <si>
+    <t>27.04.202667</t>
+  </si>
+  <si>
+    <t>27.04.202668</t>
+  </si>
+  <si>
+    <t>27.04.202669</t>
+  </si>
+  <si>
+    <t>27.04.202670</t>
+  </si>
+  <si>
+    <t>27.04.202671</t>
+  </si>
+  <si>
+    <t>27.04.202672</t>
+  </si>
+  <si>
+    <t>27.04.202673</t>
+  </si>
+  <si>
+    <t>27.04.202674</t>
+  </si>
+  <si>
+    <t>27.04.202675</t>
+  </si>
+  <si>
+    <t>27.04.202676</t>
+  </si>
+  <si>
+    <t>27.04.202677</t>
+  </si>
+  <si>
+    <t>27.04.202678</t>
+  </si>
+  <si>
+    <t>27.04.202679</t>
+  </si>
+  <si>
+    <t>27.04.202680</t>
+  </si>
+  <si>
+    <t>27.04.202681</t>
+  </si>
+  <si>
+    <t>27.04.202682</t>
+  </si>
+  <si>
+    <t>27.04.202683</t>
+  </si>
+  <si>
+    <t>27.04.202684</t>
+  </si>
+  <si>
+    <t>27.04.202685</t>
+  </si>
+  <si>
+    <t>27.04.202686</t>
+  </si>
+  <si>
+    <t>27.04.202687</t>
+  </si>
+  <si>
+    <t>27.04.202688</t>
+  </si>
+  <si>
+    <t>27.04.202689</t>
+  </si>
+  <si>
+    <t>27.04.202690</t>
+  </si>
+  <si>
+    <t>27.04.202691</t>
+  </si>
+  <si>
+    <t>27.04.202692</t>
+  </si>
+  <si>
+    <t>27.04.202693</t>
+  </si>
+  <si>
+    <t>27.04.202694</t>
+  </si>
+  <si>
+    <t>27.04.202695</t>
+  </si>
+  <si>
+    <t>27.04.202696</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -994,7 +1570,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1590,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46133.01041666666</v>
+        <v>46136.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1610,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46133.02083333334</v>
+        <v>46136.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1630,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46133.03125</v>
+        <v>46136.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1650,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46133.04166666666</v>
+        <v>46136.04166666666</v>
       </c>
       <c r="B6">
-        <v>148.873</v>
+        <v>-48.335</v>
       </c>
       <c r="C6">
-        <v>-4321.272</v>
+        <v>1004.554</v>
       </c>
       <c r="D6">
-        <v>-4321.272</v>
+        <v>1004.554</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1670,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46133.05208333334</v>
+        <v>46136.05208333334</v>
       </c>
       <c r="B7">
-        <v>200.676</v>
+        <v>-59.162</v>
       </c>
       <c r="C7">
-        <v>-2049.701</v>
+        <v>1004.268</v>
       </c>
       <c r="D7">
-        <v>-2049.701</v>
+        <v>1004.268</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1690,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46133.0625</v>
+        <v>46136.0625</v>
       </c>
       <c r="B8">
-        <v>154.428</v>
+        <v>-34.045</v>
       </c>
       <c r="C8">
-        <v>-6668.16</v>
+        <v>1004.62</v>
       </c>
       <c r="D8">
-        <v>-6668.16</v>
+        <v>1004.62</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1710,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46133.07291666666</v>
+        <v>46136.07291666666</v>
       </c>
       <c r="B9">
-        <v>89.70999999999999</v>
+        <v>-27.856</v>
       </c>
       <c r="C9">
-        <v>-749.404</v>
+        <v>972.223</v>
       </c>
       <c r="D9">
-        <v>-749.404</v>
+        <v>972.223</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1730,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46133.08333333334</v>
+        <v>46136.08333333334</v>
       </c>
       <c r="B10">
-        <v>90.03400000000001</v>
+        <v>-23.053</v>
       </c>
       <c r="C10">
-        <v>3.182</v>
+        <v>991.057</v>
       </c>
       <c r="D10">
-        <v>3.182</v>
+        <v>991.057</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1750,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46133.09375</v>
+        <v>46136.09375</v>
       </c>
       <c r="B11">
-        <v>34.275</v>
+        <v>-23.578</v>
       </c>
       <c r="C11">
-        <v>0.997</v>
+        <v>992.066</v>
       </c>
       <c r="D11">
-        <v>0.997</v>
+        <v>992.066</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1770,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46133.10416666666</v>
+        <v>46136.10416666666</v>
       </c>
       <c r="B12">
-        <v>70.977</v>
+        <v>-30.105</v>
       </c>
       <c r="C12">
-        <v>2.363</v>
+        <v>988.966</v>
       </c>
       <c r="D12">
-        <v>2.363</v>
+        <v>988.966</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1790,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46133.11458333334</v>
+        <v>46136.11458333334</v>
       </c>
       <c r="B13">
-        <v>32.471</v>
+        <v>-13.873</v>
       </c>
       <c r="C13">
-        <v>0.1</v>
+        <v>941.349</v>
       </c>
       <c r="D13">
-        <v>0.1</v>
+        <v>941.349</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1810,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46133.125</v>
+        <v>46136.125</v>
       </c>
       <c r="B14">
-        <v>54.087</v>
+        <v>10.259</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>293.712</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>293.712</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1830,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46133.13541666666</v>
+        <v>46136.13541666666</v>
       </c>
       <c r="B15">
-        <v>34.991</v>
+        <v>-16.294</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>840.021</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>840.021</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1850,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46133.14583333334</v>
+        <v>46136.14583333334</v>
       </c>
       <c r="B16">
-        <v>25.736</v>
+        <v>-14.933</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>911.385</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>911.385</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1870,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46133.15625</v>
+        <v>46136.15625</v>
       </c>
       <c r="B17">
-        <v>30.622</v>
+        <v>-22.664</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>899.164</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>899.164</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1890,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46133.16666666666</v>
+        <v>46136.16666666666</v>
       </c>
       <c r="B18">
-        <v>44.432</v>
+        <v>-0.659</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1451.844</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1451.844</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1910,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46133.17708333334</v>
+        <v>46136.17708333334</v>
       </c>
       <c r="B19">
-        <v>19.559</v>
+        <v>4.409</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>265.186</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>265.186</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1930,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46133.1875</v>
+        <v>46136.1875</v>
       </c>
       <c r="B20">
-        <v>-25.436</v>
+        <v>-4.539</v>
       </c>
       <c r="C20">
-        <v>928.45</v>
+        <v>897.6319999999999</v>
       </c>
       <c r="D20">
-        <v>928.45</v>
+        <v>897.6319999999999</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1950,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46133.19791666666</v>
+        <v>46136.19791666666</v>
       </c>
       <c r="B21">
-        <v>20.03</v>
+        <v>-25.495</v>
       </c>
       <c r="C21">
-        <v>0.1</v>
+        <v>995.756</v>
       </c>
       <c r="D21">
-        <v>0.1</v>
+        <v>995.756</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1970,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46133.20833333334</v>
+        <v>46136.20833333334</v>
       </c>
       <c r="B22">
-        <v>45.741</v>
+        <v>-22.49</v>
       </c>
       <c r="C22">
-        <v>1.907</v>
+        <v>1058.944</v>
       </c>
       <c r="D22">
-        <v>1.907</v>
+        <v>1058.944</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1990,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46133.21875</v>
+        <v>46136.21875</v>
       </c>
       <c r="B23">
-        <v>26.095</v>
+        <v>-22.498</v>
       </c>
       <c r="C23">
-        <v>299.48</v>
+        <v>934.763</v>
       </c>
       <c r="D23">
-        <v>299.48</v>
+        <v>934.763</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +2010,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46133.22916666666</v>
+        <v>46136.22916666666</v>
       </c>
       <c r="B24">
-        <v>52.926</v>
+        <v>-25.72</v>
       </c>
       <c r="C24">
-        <v>16.595</v>
+        <v>1046.584</v>
       </c>
       <c r="D24">
-        <v>16.595</v>
+        <v>1046.584</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +2030,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46133.23958333334</v>
+        <v>46136.23958333334</v>
       </c>
       <c r="B25">
-        <v>25.922</v>
+        <v>-45.908</v>
       </c>
       <c r="C25">
-        <v>34.092</v>
+        <v>1194.479</v>
       </c>
       <c r="D25">
-        <v>34.092</v>
+        <v>1194.479</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +2050,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46133.25</v>
+        <v>46136.25</v>
       </c>
       <c r="B26">
-        <v>24.286</v>
+        <v>-59.144</v>
       </c>
       <c r="C26">
-        <v>17.156</v>
+        <v>2736.222</v>
       </c>
       <c r="D26">
-        <v>17.156</v>
+        <v>2736.222</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +2070,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46133.26041666666</v>
+        <v>46136.26041666666</v>
       </c>
       <c r="B27">
-        <v>48.657</v>
+        <v>-63.921</v>
       </c>
       <c r="C27">
-        <v>4.904</v>
+        <v>2469.713</v>
       </c>
       <c r="D27">
-        <v>4.904</v>
+        <v>2469.713</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +2090,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46133.27083333334</v>
+        <v>46136.27083333334</v>
       </c>
       <c r="B28">
-        <v>30.856</v>
+        <v>-66.92100000000001</v>
       </c>
       <c r="C28">
-        <v>15.459</v>
+        <v>3338.519</v>
       </c>
       <c r="D28">
-        <v>15.459</v>
+        <v>3338.519</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +2110,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46133.28125</v>
+        <v>46136.28125</v>
       </c>
       <c r="B29">
-        <v>11.988</v>
+        <v>-24.935</v>
       </c>
       <c r="C29">
-        <v>1.539</v>
+        <v>1193.93</v>
       </c>
       <c r="D29">
-        <v>1.539</v>
+        <v>1193.93</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +2130,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46133.29166666666</v>
+        <v>46136.29166666666</v>
       </c>
       <c r="B30">
-        <v>32.308</v>
+        <v>-77.002</v>
       </c>
       <c r="C30">
-        <v>251.991</v>
+        <v>5534.292</v>
       </c>
       <c r="D30">
-        <v>251.991</v>
+        <v>5534.292</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +2150,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46133.30208333334</v>
+        <v>46136.30208333334</v>
       </c>
       <c r="B31">
-        <v>-2.967</v>
+        <v>-57.822</v>
       </c>
       <c r="C31">
-        <v>890.456</v>
+        <v>1854.699</v>
       </c>
       <c r="D31">
-        <v>890.456</v>
+        <v>1854.699</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +2170,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46133.3125</v>
+        <v>46136.3125</v>
       </c>
       <c r="B32">
-        <v>-7.156</v>
+        <v>-64.155</v>
       </c>
       <c r="C32">
-        <v>896.1079999999999</v>
+        <v>899.777</v>
       </c>
       <c r="D32">
-        <v>896.1079999999999</v>
+        <v>899.777</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +2190,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46133.32291666666</v>
+        <v>46136.32291666666</v>
       </c>
       <c r="B33">
-        <v>16.727</v>
+        <v>17.02</v>
       </c>
       <c r="C33">
-        <v>181.034</v>
+        <v>148.76</v>
       </c>
       <c r="D33">
-        <v>181.034</v>
+        <v>148.76</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +2210,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46133.33333333334</v>
+        <v>46136.33333333334</v>
       </c>
       <c r="B34">
-        <v>-44.19</v>
+        <v>62.02</v>
       </c>
       <c r="C34">
-        <v>2547.653</v>
+        <v>330.551</v>
       </c>
       <c r="D34">
-        <v>2547.653</v>
+        <v>330.551</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +2230,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46133.34375</v>
+        <v>46136.34375</v>
       </c>
       <c r="B35">
-        <v>-18.855</v>
+        <v>109.706</v>
       </c>
       <c r="C35">
-        <v>1722.957</v>
+        <v>-3964.732</v>
       </c>
       <c r="D35">
-        <v>1722.957</v>
+        <v>-3964.732</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +2250,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46133.35416666666</v>
+        <v>46136.35416666666</v>
       </c>
       <c r="B36">
-        <v>-30.555</v>
+        <v>77.086</v>
       </c>
       <c r="C36">
-        <v>899.528</v>
+        <v>-275.677</v>
       </c>
       <c r="D36">
-        <v>899.528</v>
+        <v>-275.677</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +2270,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46133.36458333334</v>
+        <v>46136.36458333334</v>
       </c>
       <c r="B37">
-        <v>-7.02</v>
+        <v>55.143</v>
       </c>
       <c r="C37">
-        <v>1021.741</v>
+        <v>1.706</v>
       </c>
       <c r="D37">
-        <v>1021.741</v>
+        <v>1.706</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +2290,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46133.375</v>
+        <v>46136.375</v>
       </c>
       <c r="B38">
-        <v>45.319</v>
+        <v>20.565</v>
       </c>
       <c r="C38">
-        <v>43.404</v>
+        <v>0.313</v>
       </c>
       <c r="D38">
-        <v>43.404</v>
+        <v>0.313</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +2310,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46133.38541666666</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="B39">
-        <v>-16.549</v>
+        <v>25.31</v>
       </c>
       <c r="C39">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +2330,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46133.39583333334</v>
+        <v>46136.39583333334</v>
       </c>
       <c r="B40">
-        <v>-14.42</v>
+        <v>21.075</v>
       </c>
       <c r="C40">
-        <v>904.251</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>904.251</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +2350,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46133.40625</v>
+        <v>46136.40625</v>
       </c>
       <c r="B41">
-        <v>-52.692</v>
+        <v>-6.015</v>
       </c>
       <c r="C41">
-        <v>1155.757</v>
+        <v>619.591</v>
       </c>
       <c r="D41">
-        <v>1155.757</v>
+        <v>619.591</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +2370,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46133.41666666666</v>
+        <v>46136.41666666666</v>
       </c>
       <c r="B42">
-        <v>-63.599</v>
+        <v>-28.856</v>
       </c>
       <c r="C42">
-        <v>5270.55</v>
+        <v>1579.59</v>
       </c>
       <c r="D42">
-        <v>5270.55</v>
+        <v>1579.59</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +2390,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46133.42708333334</v>
+        <v>46136.42708333334</v>
       </c>
       <c r="B43">
-        <v>-51.62</v>
+        <v>-33.236</v>
       </c>
       <c r="C43">
-        <v>896.359</v>
+        <v>466.502</v>
       </c>
       <c r="D43">
-        <v>896.359</v>
+        <v>466.502</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +2410,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46133.4375</v>
+        <v>46136.4375</v>
       </c>
       <c r="B44">
-        <v>-78.807</v>
+        <v>12.429</v>
       </c>
       <c r="C44">
-        <v>899.429</v>
+        <v>-223.582</v>
       </c>
       <c r="D44">
-        <v>899.429</v>
+        <v>-223.582</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +2430,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46133.44791666666</v>
+        <v>46136.44791666666</v>
       </c>
       <c r="B45">
-        <v>-89.642</v>
+        <v>53.69</v>
       </c>
       <c r="C45">
-        <v>897.275</v>
+        <v>-681.33</v>
       </c>
       <c r="D45">
-        <v>897.275</v>
+        <v>-681.33</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +2450,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46133.45833333334</v>
+        <v>46136.45833333334</v>
       </c>
       <c r="B46">
-        <v>-36.111</v>
+        <v>65.14400000000001</v>
       </c>
       <c r="C46">
-        <v>713.6</v>
+        <v>-341.336</v>
       </c>
       <c r="D46">
-        <v>713.6</v>
+        <v>-341.336</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +2470,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46133.46875</v>
+        <v>46136.46875</v>
       </c>
       <c r="B47">
-        <v>-63.771</v>
+        <v>-45.792</v>
       </c>
       <c r="C47">
-        <v>713.554</v>
+        <v>450</v>
       </c>
       <c r="D47">
-        <v>713.554</v>
+        <v>450</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +2490,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46133.47916666666</v>
+        <v>46136.47916666666</v>
       </c>
       <c r="B48">
-        <v>-20.363</v>
+        <v>-82.06999999999999</v>
       </c>
       <c r="C48">
-        <v>713.6</v>
+        <v>1178.803</v>
       </c>
       <c r="D48">
-        <v>713.6</v>
+        <v>1178.803</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +2510,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46133.48958333334</v>
+        <v>46136.48958333334</v>
       </c>
       <c r="B49">
-        <v>-19.476</v>
+        <v>-83.033</v>
       </c>
       <c r="C49">
-        <v>713.598</v>
+        <v>2441.168</v>
       </c>
       <c r="D49">
-        <v>713.598</v>
+        <v>2441.168</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +2530,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46133.5</v>
+        <v>46136.5</v>
       </c>
       <c r="B50">
-        <v>52.608</v>
+        <v>-79.428</v>
       </c>
       <c r="C50">
-        <v>129.989</v>
+        <v>529.601</v>
       </c>
       <c r="D50">
-        <v>129.989</v>
+        <v>529.601</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +2550,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46133.51041666666</v>
+        <v>46136.51041666666</v>
       </c>
       <c r="B51">
-        <v>89.497</v>
+        <v>-25.15</v>
       </c>
       <c r="C51">
-        <v>161.997</v>
+        <v>447.172</v>
       </c>
       <c r="D51">
-        <v>161.997</v>
+        <v>447.172</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +2570,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46133.52083333334</v>
+        <v>46136.52083333334</v>
       </c>
       <c r="B52">
-        <v>69.001</v>
+        <v>20.832</v>
       </c>
       <c r="C52">
-        <v>150.634</v>
+        <v>-230.849</v>
       </c>
       <c r="D52">
-        <v>150.634</v>
+        <v>-230.849</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2590,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46133.53125</v>
+        <v>46136.53125</v>
       </c>
       <c r="B53">
-        <v>33.757</v>
+        <v>28.98</v>
       </c>
       <c r="C53">
-        <v>259.084</v>
+        <v>-2856.152</v>
       </c>
       <c r="D53">
-        <v>259.084</v>
+        <v>-2856.152</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2610,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46133.54166666666</v>
+        <v>46136.54166666666</v>
       </c>
       <c r="B54">
-        <v>-41.838</v>
+        <v>34.451</v>
       </c>
       <c r="C54">
-        <v>6290.171</v>
+        <v>-2061.562</v>
       </c>
       <c r="D54">
-        <v>6290.171</v>
+        <v>-2061.562</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2630,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46133.55208333334</v>
+        <v>46136.55208333334</v>
       </c>
       <c r="B55">
-        <v>-14.633</v>
+        <v>45.066</v>
       </c>
       <c r="C55">
-        <v>1185.871</v>
+        <v>-108.335</v>
       </c>
       <c r="D55">
-        <v>1185.871</v>
+        <v>-108.335</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2650,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46133.5625</v>
+        <v>46136.5625</v>
       </c>
       <c r="B56">
-        <v>28.399</v>
+        <v>107.932</v>
       </c>
       <c r="C56">
-        <v>266.601</v>
+        <v>-711.0940000000001</v>
       </c>
       <c r="D56">
-        <v>266.601</v>
+        <v>-711.0940000000001</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2670,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46133.57291666666</v>
+        <v>46136.57291666666</v>
       </c>
       <c r="B57">
-        <v>16.109</v>
+        <v>99.048</v>
       </c>
       <c r="C57">
-        <v>232.41</v>
+        <v>-3521.818</v>
       </c>
       <c r="D57">
-        <v>232.41</v>
+        <v>-3521.818</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2690,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46133.58333333334</v>
+        <v>46136.58333333334</v>
       </c>
       <c r="B58">
-        <v>15.85</v>
+        <v>55.021</v>
       </c>
       <c r="C58">
-        <v>359.025</v>
+        <v>-5524.456</v>
       </c>
       <c r="D58">
-        <v>359.025</v>
+        <v>-5524.456</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2710,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46133.59375</v>
+        <v>46136.59375</v>
       </c>
       <c r="B59">
-        <v>-9.981</v>
+        <v>25.958</v>
       </c>
       <c r="C59">
-        <v>817.515</v>
+        <v>-329.867</v>
       </c>
       <c r="D59">
-        <v>817.515</v>
+        <v>-329.867</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2730,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46133.60416666666</v>
+        <v>46136.60416666666</v>
       </c>
       <c r="B60">
-        <v>5.834</v>
+        <v>30.699</v>
       </c>
       <c r="C60">
-        <v>311.194</v>
+        <v>-90.792</v>
       </c>
       <c r="D60">
-        <v>311.194</v>
+        <v>-90.792</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2750,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46133.61458333334</v>
+        <v>46136.61458333334</v>
       </c>
       <c r="B61">
-        <v>-15.259</v>
+        <v>17.502</v>
       </c>
       <c r="C61">
-        <v>819.152</v>
+        <v>-58.471</v>
       </c>
       <c r="D61">
-        <v>819.152</v>
+        <v>-58.471</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2770,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46133.625</v>
+        <v>46136.625</v>
       </c>
       <c r="B62">
-        <v>46.73</v>
+        <v>28.716</v>
       </c>
       <c r="C62">
-        <v>287</v>
+        <v>-315.278</v>
       </c>
       <c r="D62">
-        <v>287</v>
+        <v>-315.278</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2790,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46133.63541666666</v>
+        <v>46136.63541666666</v>
       </c>
       <c r="B63">
-        <v>44.12</v>
+        <v>26.284</v>
       </c>
       <c r="C63">
-        <v>313.06</v>
+        <v>-108.784</v>
       </c>
       <c r="D63">
-        <v>313.06</v>
+        <v>-108.784</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2810,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46133.64583333334</v>
+        <v>46136.64583333334</v>
       </c>
       <c r="B64">
-        <v>15.279</v>
+        <v>55.08</v>
       </c>
       <c r="C64">
-        <v>321.491</v>
+        <v>-39.088</v>
       </c>
       <c r="D64">
-        <v>321.491</v>
+        <v>-39.088</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2830,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46133.65625</v>
+        <v>46136.65625</v>
       </c>
       <c r="B65">
-        <v>-4.04</v>
+        <v>52.591</v>
       </c>
       <c r="C65">
-        <v>824.861</v>
+        <v>-488.625</v>
       </c>
       <c r="D65">
-        <v>824.861</v>
+        <v>-488.625</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2850,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46133.66666666666</v>
+        <v>46136.66666666666</v>
       </c>
       <c r="B66">
-        <v>78.962</v>
+        <v>102.508</v>
       </c>
       <c r="C66">
-        <v>370.889</v>
+        <v>-6363.792</v>
       </c>
       <c r="D66">
-        <v>370.889</v>
+        <v>-6363.792</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2870,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46133.67708333334</v>
+        <v>46136.67708333334</v>
       </c>
       <c r="B67">
-        <v>29.19</v>
+        <v>79.798</v>
       </c>
       <c r="C67">
-        <v>401</v>
+        <v>-5284.295</v>
       </c>
       <c r="D67">
-        <v>401</v>
+        <v>-5284.295</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2890,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46133.6875</v>
+        <v>46136.6875</v>
       </c>
       <c r="B68">
-        <v>37.041</v>
+        <v>136.999</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>-5771.636</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>-5771.636</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2910,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46133.69791666666</v>
+        <v>46136.69791666666</v>
       </c>
       <c r="B69">
-        <v>15.137</v>
+        <v>113.964</v>
       </c>
       <c r="C69">
-        <v>353.611</v>
+        <v>-338.083</v>
       </c>
       <c r="D69">
-        <v>353.611</v>
+        <v>-338.083</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2930,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46133.70833333334</v>
+        <v>46136.70833333334</v>
       </c>
       <c r="B70">
-        <v>17.031</v>
+        <v>187.504</v>
       </c>
       <c r="C70">
-        <v>339.356</v>
+        <v>-8.928000000000001</v>
       </c>
       <c r="D70">
-        <v>339.356</v>
+        <v>-8.928000000000001</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2950,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46133.71875</v>
+        <v>46136.71875</v>
       </c>
       <c r="B71">
-        <v>7.198</v>
+        <v>104.504</v>
       </c>
       <c r="C71">
-        <v>402</v>
+        <v>2.646</v>
       </c>
       <c r="D71">
-        <v>402</v>
+        <v>2.646</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2970,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46133.72916666666</v>
+        <v>46136.72916666666</v>
       </c>
       <c r="B72">
-        <v>2.024</v>
+        <v>112.76</v>
       </c>
       <c r="C72">
-        <v>971.42</v>
+        <v>3.213</v>
       </c>
       <c r="D72">
-        <v>971.42</v>
+        <v>3.213</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2990,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46133.73958333334</v>
+        <v>46136.73958333334</v>
       </c>
       <c r="B73">
-        <v>-2.636</v>
+        <v>-0.914</v>
       </c>
       <c r="C73">
-        <v>1022.191</v>
+        <v>852.527</v>
       </c>
       <c r="D73">
-        <v>1022.191</v>
+        <v>852.527</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +3010,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46133.75</v>
+        <v>46136.75</v>
       </c>
       <c r="B74">
-        <v>-8.743</v>
+        <v>7.806</v>
       </c>
       <c r="C74">
-        <v>1287.001</v>
+        <v>0.5</v>
       </c>
       <c r="D74">
-        <v>1287.001</v>
+        <v>0.5</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +3030,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46133.76041666666</v>
+        <v>46136.76041666666</v>
       </c>
       <c r="B75">
-        <v>-31.632</v>
+        <v>-40.888</v>
       </c>
       <c r="C75">
-        <v>1766.636</v>
+        <v>5252.978</v>
       </c>
       <c r="D75">
-        <v>1766.636</v>
+        <v>5252.978</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +3050,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46133.77083333334</v>
+        <v>46136.77083333334</v>
       </c>
       <c r="B76">
-        <v>-37.048</v>
+        <v>-32.514</v>
       </c>
       <c r="C76">
-        <v>2274.86</v>
+        <v>3605.494</v>
       </c>
       <c r="D76">
-        <v>2274.86</v>
+        <v>3605.494</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +3070,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46133.78125</v>
+        <v>46136.78125</v>
       </c>
       <c r="B77">
-        <v>-52.737</v>
+        <v>-60.687</v>
       </c>
       <c r="C77">
-        <v>5767.801</v>
+        <v>3815.376</v>
       </c>
       <c r="D77">
-        <v>5767.801</v>
+        <v>3815.376</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +3090,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46133.79166666666</v>
+        <v>46136.79166666666</v>
       </c>
       <c r="B78">
-        <v>-28.796</v>
+        <v>26.105</v>
       </c>
       <c r="C78">
-        <v>2211.597</v>
+        <v>8.978</v>
       </c>
       <c r="D78">
-        <v>2211.597</v>
+        <v>8.978</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +3110,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46133.80208333334</v>
+        <v>46136.80208333334</v>
       </c>
       <c r="B79">
-        <v>-39.417</v>
+        <v>18.486</v>
       </c>
       <c r="C79">
-        <v>4208.757</v>
+        <v>256.85</v>
       </c>
       <c r="D79">
-        <v>4208.757</v>
+        <v>256.85</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +3130,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46133.8125</v>
+        <v>46136.8125</v>
       </c>
       <c r="B80">
-        <v>-74.21299999999999</v>
+        <v>31.104</v>
       </c>
       <c r="C80">
-        <v>2009.316</v>
+        <v>271.517</v>
       </c>
       <c r="D80">
-        <v>2009.316</v>
+        <v>271.517</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +3150,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46133.82291666666</v>
+        <v>46136.82291666666</v>
       </c>
       <c r="B81">
-        <v>-76.479</v>
+        <v>31.166</v>
       </c>
       <c r="C81">
-        <v>3430.597</v>
+        <v>363.165</v>
       </c>
       <c r="D81">
-        <v>3430.597</v>
+        <v>363.165</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +3170,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46133.83333333334</v>
+        <v>46136.83333333334</v>
       </c>
       <c r="B82">
-        <v>-40.81</v>
+        <v>47.599</v>
       </c>
       <c r="C82">
-        <v>1437.187</v>
+        <v>-64.434</v>
       </c>
       <c r="D82">
-        <v>1437.187</v>
+        <v>-64.434</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +3190,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46133.84375</v>
+        <v>46136.84375</v>
       </c>
       <c r="B83">
-        <v>-53.474</v>
+        <v>48.194</v>
       </c>
       <c r="C83">
-        <v>1399.082</v>
+        <v>-24.657</v>
       </c>
       <c r="D83">
-        <v>1399.082</v>
+        <v>-24.657</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +3210,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46133.85416666666</v>
+        <v>46136.85416666666</v>
       </c>
       <c r="B84">
-        <v>-6.486</v>
+        <v>91.363</v>
       </c>
       <c r="C84">
-        <v>1445.237</v>
+        <v>15.16</v>
       </c>
       <c r="D84">
-        <v>1445.237</v>
+        <v>15.16</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +3230,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46133.86458333334</v>
+        <v>46136.86458333334</v>
       </c>
       <c r="B85">
-        <v>5.755</v>
+        <v>63.113</v>
       </c>
       <c r="C85">
-        <v>291.354</v>
+        <v>300.065</v>
       </c>
       <c r="D85">
-        <v>291.354</v>
+        <v>300.065</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +3250,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46133.875</v>
+        <v>46136.875</v>
       </c>
       <c r="B86">
-        <v>-68.22499999999999</v>
+        <v>13.912</v>
       </c>
       <c r="C86">
-        <v>4617.921</v>
+        <v>400</v>
       </c>
       <c r="D86">
-        <v>4617.921</v>
+        <v>400</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +3270,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46133.88541666666</v>
+        <v>46136.88541666666</v>
       </c>
       <c r="B87">
-        <v>-35.538</v>
+        <v>33.899</v>
       </c>
       <c r="C87">
-        <v>4758.783</v>
+        <v>283.661</v>
       </c>
       <c r="D87">
-        <v>4758.783</v>
+        <v>283.661</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +3290,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46133.89583333334</v>
+        <v>46136.89583333334</v>
       </c>
       <c r="B88">
-        <v>-21.749</v>
+        <v>25.246</v>
       </c>
       <c r="C88">
-        <v>1350.866</v>
+        <v>277.612</v>
       </c>
       <c r="D88">
-        <v>1350.866</v>
+        <v>277.612</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +3310,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46133.90625</v>
+        <v>46136.90625</v>
       </c>
       <c r="B89">
-        <v>-28.024</v>
+        <v>9.205</v>
       </c>
       <c r="C89">
-        <v>1920.231</v>
+        <v>264.092</v>
       </c>
       <c r="D89">
-        <v>1920.231</v>
+        <v>264.092</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +3330,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46133.91666666666</v>
+        <v>46136.91666666666</v>
       </c>
       <c r="B90">
-        <v>-8.728999999999999</v>
+        <v>-20.59</v>
       </c>
       <c r="C90">
-        <v>1184.11</v>
+        <v>882.21</v>
       </c>
       <c r="D90">
-        <v>1184.11</v>
+        <v>882.21</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +3350,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46133.92708333334</v>
+        <v>46136.92708333334</v>
       </c>
       <c r="B91">
-        <v>-23.535</v>
+        <v>1.346</v>
       </c>
       <c r="C91">
-        <v>1031.704</v>
+        <v>265.608</v>
       </c>
       <c r="D91">
-        <v>1031.704</v>
+        <v>265.608</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +3370,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46133.9375</v>
+        <v>46136.9375</v>
       </c>
       <c r="B92">
-        <v>-24.807</v>
+        <v>3.655</v>
       </c>
       <c r="C92">
-        <v>884.683</v>
+        <v>257.127</v>
       </c>
       <c r="D92">
-        <v>884.683</v>
+        <v>257.127</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +3390,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46133.94791666666</v>
+        <v>46136.94791666666</v>
       </c>
       <c r="B93">
-        <v>-0.571</v>
+        <v>28.599</v>
       </c>
       <c r="C93">
-        <v>896.542</v>
+        <v>-143.875</v>
       </c>
       <c r="D93">
-        <v>896.542</v>
+        <v>-143.875</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +3410,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46133.95833333334</v>
+        <v>46136.95833333334</v>
       </c>
       <c r="B94">
-        <v>-31.753</v>
+        <v>19.003</v>
       </c>
       <c r="C94">
-        <v>924.687</v>
+        <v>113.564</v>
       </c>
       <c r="D94">
-        <v>924.687</v>
+        <v>113.564</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +3430,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46133.96875</v>
+        <v>46136.96875</v>
       </c>
       <c r="B95">
-        <v>-32.992</v>
+        <v>19.555</v>
       </c>
       <c r="C95">
-        <v>896.053</v>
+        <v>259.244</v>
       </c>
       <c r="D95">
-        <v>896.053</v>
+        <v>259.244</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +3450,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46133.97916666666</v>
+        <v>46136.97916666666</v>
       </c>
       <c r="B96">
-        <v>-32.26</v>
+        <v>20.897</v>
       </c>
       <c r="C96">
-        <v>804.659</v>
+        <v>292.523</v>
       </c>
       <c r="D96">
-        <v>804.659</v>
+        <v>292.523</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +3470,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46133.98958333334</v>
+        <v>46136.98958333334</v>
       </c>
       <c r="B97">
-        <v>-9.146000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="C97">
-        <v>894.02</v>
+        <v>379.803</v>
       </c>
       <c r="D97">
-        <v>894.02</v>
+        <v>379.803</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +3490,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46134</v>
+        <v>46137</v>
       </c>
       <c r="B98">
-        <v>-16.696</v>
+        <v>51.687</v>
       </c>
       <c r="C98">
-        <v>899.319</v>
+        <v>298.695</v>
       </c>
       <c r="D98">
-        <v>899.319</v>
+        <v>298.695</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +3510,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46134.01041666666</v>
+        <v>46137.01041666666</v>
       </c>
       <c r="B99">
-        <v>-9.294</v>
+        <v>-4.493</v>
       </c>
       <c r="C99">
-        <v>987.2430000000001</v>
+        <v>650</v>
       </c>
       <c r="D99">
-        <v>987.2430000000001</v>
+        <v>650</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +3530,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46134.02083333334</v>
+        <v>46137.02083333334</v>
       </c>
       <c r="B100">
-        <v>-10.977</v>
+        <v>7.283</v>
       </c>
       <c r="C100">
-        <v>927.523</v>
+        <v>104.16</v>
       </c>
       <c r="D100">
-        <v>927.523</v>
+        <v>104.16</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +3550,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46134.03125</v>
+        <v>46137.03125</v>
       </c>
       <c r="B101">
-        <v>-2.208</v>
+        <v>14.032</v>
       </c>
       <c r="C101">
-        <v>917.615</v>
+        <v>155.733</v>
       </c>
       <c r="D101">
-        <v>917.615</v>
+        <v>155.733</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +3570,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46134.04166666666</v>
+        <v>46137.04166666666</v>
       </c>
       <c r="B102">
-        <v>-2.366</v>
+        <v>-6.859</v>
       </c>
       <c r="C102">
-        <v>899.662</v>
+        <v>894.928</v>
       </c>
       <c r="D102">
-        <v>899.662</v>
+        <v>894.928</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3590,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46134.05208333334</v>
+        <v>46137.05208333334</v>
       </c>
       <c r="B103">
-        <v>-23.314</v>
+        <v>-2.156</v>
       </c>
       <c r="C103">
-        <v>1059.207</v>
+        <v>894.823</v>
       </c>
       <c r="D103">
-        <v>1059.207</v>
+        <v>894.823</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3610,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46134.0625</v>
+        <v>46137.0625</v>
       </c>
       <c r="B104">
-        <v>-26.641</v>
+        <v>1.386</v>
       </c>
       <c r="C104">
-        <v>1039.351</v>
+        <v>390.414</v>
       </c>
       <c r="D104">
-        <v>1039.351</v>
+        <v>390.414</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3630,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46134.07291666666</v>
+        <v>46137.07291666666</v>
       </c>
       <c r="B105">
-        <v>-45.913</v>
+        <v>36.4</v>
       </c>
       <c r="C105">
-        <v>899.048</v>
+        <v>-200.415</v>
       </c>
       <c r="D105">
-        <v>899.048</v>
+        <v>-200.415</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3650,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46134.08333333334</v>
+        <v>46137.08333333334</v>
       </c>
       <c r="B106">
-        <v>-35.797</v>
+        <v>16.874</v>
       </c>
       <c r="C106">
-        <v>892.914</v>
+        <v>13.316</v>
       </c>
       <c r="D106">
-        <v>892.914</v>
+        <v>13.316</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3670,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46134.09375</v>
+        <v>46137.09375</v>
       </c>
       <c r="B107">
-        <v>-7.817</v>
+        <v>23.921</v>
       </c>
       <c r="C107">
-        <v>899.379</v>
+        <v>-34.383</v>
       </c>
       <c r="D107">
-        <v>899.379</v>
+        <v>-34.383</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3690,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46134.10416666666</v>
+        <v>46137.10416666666</v>
       </c>
       <c r="B108">
-        <v>-14.414</v>
+        <v>20.257</v>
       </c>
       <c r="C108">
-        <v>899.6609999999999</v>
+        <v>-60.581</v>
       </c>
       <c r="D108">
-        <v>899.6609999999999</v>
+        <v>-60.581</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3710,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46134.11458333334</v>
+        <v>46137.11458333334</v>
       </c>
       <c r="B109">
-        <v>-19.355</v>
+        <v>24.377</v>
       </c>
       <c r="C109">
-        <v>897.769</v>
+        <v>-121.838</v>
       </c>
       <c r="D109">
-        <v>897.769</v>
+        <v>-121.838</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3730,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46134.125</v>
+        <v>46137.125</v>
       </c>
       <c r="B110">
-        <v>-9.414</v>
+        <v>29.61</v>
       </c>
       <c r="C110">
-        <v>899.468</v>
+        <v>160.008</v>
       </c>
       <c r="D110">
-        <v>899.468</v>
+        <v>160.008</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3750,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46134.13541666666</v>
+        <v>46137.13541666666</v>
       </c>
       <c r="B111">
-        <v>-13.557</v>
+        <v>19.293</v>
       </c>
       <c r="C111">
-        <v>892.745</v>
+        <v>120.94</v>
       </c>
       <c r="D111">
-        <v>892.745</v>
+        <v>120.94</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3770,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46134.14583333334</v>
+        <v>46137.14583333334</v>
       </c>
       <c r="B112">
-        <v>-17.277</v>
+        <v>-4.189</v>
       </c>
       <c r="C112">
-        <v>828.932</v>
+        <v>898.53</v>
       </c>
       <c r="D112">
-        <v>828.932</v>
+        <v>898.53</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3790,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46134.15625</v>
+        <v>46137.15625</v>
       </c>
       <c r="B113">
-        <v>-27.686</v>
+        <v>15.128</v>
       </c>
       <c r="C113">
-        <v>895.575</v>
+        <v>255.53</v>
       </c>
       <c r="D113">
-        <v>895.575</v>
+        <v>255.53</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3810,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46134.16666666666</v>
+        <v>46137.16666666666</v>
       </c>
       <c r="B114">
-        <v>-29.688</v>
+        <v>43.063</v>
       </c>
       <c r="C114">
-        <v>869.075</v>
+        <v>264.184</v>
       </c>
       <c r="D114">
-        <v>869.075</v>
+        <v>264.184</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3830,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46134.17708333334</v>
+        <v>46137.17708333334</v>
       </c>
       <c r="B115">
-        <v>-23.188</v>
+        <v>34.66</v>
       </c>
       <c r="C115">
-        <v>896.074</v>
+        <v>385.724</v>
       </c>
       <c r="D115">
-        <v>896.074</v>
+        <v>385.724</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3850,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46134.1875</v>
+        <v>46137.1875</v>
       </c>
       <c r="B116">
-        <v>-30.014</v>
+        <v>18.719</v>
       </c>
       <c r="C116">
-        <v>940.436</v>
+        <v>269.637</v>
       </c>
       <c r="D116">
-        <v>940.436</v>
+        <v>269.637</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3870,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46134.19791666666</v>
+        <v>46137.19791666666</v>
       </c>
       <c r="B117">
-        <v>-23.18</v>
+        <v>12.827</v>
       </c>
       <c r="C117">
-        <v>899.273</v>
+        <v>-178.719</v>
       </c>
       <c r="D117">
-        <v>899.273</v>
+        <v>-178.719</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3890,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46134.20833333334</v>
+        <v>46137.20833333334</v>
       </c>
       <c r="B118">
-        <v>4.009</v>
+        <v>36.844</v>
       </c>
       <c r="C118">
-        <v>176.897</v>
+        <v>-221.562</v>
       </c>
       <c r="D118">
-        <v>176.897</v>
+        <v>-221.562</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3910,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46134.21875</v>
+        <v>46137.21875</v>
       </c>
       <c r="B119">
-        <v>20.227</v>
+        <v>45.306</v>
       </c>
       <c r="C119">
-        <v>400</v>
+        <v>-68.851</v>
       </c>
       <c r="D119">
-        <v>400</v>
+        <v>-68.851</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3930,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46134.22916666666</v>
+        <v>46137.22916666666</v>
       </c>
       <c r="B120">
-        <v>7.332</v>
+        <v>37.179</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>109.94</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>109.94</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3950,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46134.23958333334</v>
+        <v>46137.23958333334</v>
       </c>
       <c r="B121">
-        <v>5.653</v>
+        <v>25.49</v>
       </c>
       <c r="C121">
-        <v>372.2</v>
+        <v>-184.976</v>
       </c>
       <c r="D121">
-        <v>372.2</v>
+        <v>-184.976</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3970,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46134.25</v>
+        <v>46137.25</v>
       </c>
       <c r="B122">
-        <v>33.415</v>
+        <v>-3.362</v>
       </c>
       <c r="C122">
-        <v>-221.24</v>
+        <v>887.619</v>
       </c>
       <c r="D122">
-        <v>-221.24</v>
+        <v>887.619</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3990,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46134.26041666666</v>
+        <v>46137.26041666666</v>
       </c>
       <c r="B123">
-        <v>4.428</v>
+        <v>7.101</v>
       </c>
       <c r="C123">
-        <v>400</v>
+        <v>391.313</v>
       </c>
       <c r="D123">
-        <v>400</v>
+        <v>391.313</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +4010,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46134.27083333334</v>
+        <v>46137.27083333334</v>
       </c>
       <c r="B124">
-        <v>-4.864</v>
+        <v>8.244999999999999</v>
       </c>
       <c r="C124">
-        <v>897.872</v>
+        <v>137.165</v>
       </c>
       <c r="D124">
-        <v>897.872</v>
+        <v>137.165</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +4030,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46134.28125</v>
+        <v>46137.28125</v>
       </c>
       <c r="B125">
-        <v>26.892</v>
+        <v>17.962</v>
       </c>
       <c r="C125">
-        <v>321.053</v>
+        <v>240.3</v>
       </c>
       <c r="D125">
-        <v>321.053</v>
+        <v>240.3</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +4050,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46134.29166666666</v>
+        <v>46137.29166666666</v>
       </c>
       <c r="B126">
-        <v>86.658</v>
+        <v>-23.003</v>
       </c>
       <c r="C126">
-        <v>290.83</v>
+        <v>858.901</v>
       </c>
       <c r="D126">
-        <v>290.83</v>
+        <v>858.901</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +4070,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46134.30208333334</v>
+        <v>46137.30208333334</v>
       </c>
       <c r="B127">
-        <v>54.527</v>
+        <v>-31.378</v>
       </c>
       <c r="C127">
-        <v>-168.064</v>
+        <v>852.235</v>
       </c>
       <c r="D127">
-        <v>-168.064</v>
+        <v>852.235</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +4090,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46134.3125</v>
+        <v>46137.3125</v>
       </c>
       <c r="B128">
-        <v>58.408</v>
+        <v>-72.526</v>
       </c>
       <c r="C128">
-        <v>-195.799</v>
+        <v>923.139</v>
       </c>
       <c r="D128">
-        <v>-195.799</v>
+        <v>923.139</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +4110,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46134.32291666666</v>
+        <v>46137.32291666666</v>
       </c>
       <c r="B129">
-        <v>65.322</v>
+        <v>-40.244</v>
       </c>
       <c r="C129">
-        <v>21.548</v>
+        <v>2117.671</v>
       </c>
       <c r="D129">
-        <v>21.548</v>
+        <v>2117.671</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +4130,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46134.33333333334</v>
+        <v>46137.33333333334</v>
       </c>
       <c r="B130">
-        <v>120.213</v>
+        <v>-18.98</v>
       </c>
       <c r="C130">
-        <v>9.595000000000001</v>
+        <v>1332.708</v>
       </c>
       <c r="D130">
-        <v>9.595000000000001</v>
+        <v>1332.708</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +4150,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46134.34375</v>
+        <v>46137.34375</v>
       </c>
       <c r="B131">
-        <v>71.986</v>
+        <v>-28.204</v>
       </c>
       <c r="C131">
-        <v>28.078</v>
+        <v>1054.496</v>
       </c>
       <c r="D131">
-        <v>28.078</v>
+        <v>1054.496</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +4170,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46134.35416666666</v>
+        <v>46137.35416666666</v>
       </c>
       <c r="B132">
-        <v>29.625</v>
+        <v>-28.404</v>
       </c>
       <c r="C132">
-        <v>1.583</v>
+        <v>454.707</v>
       </c>
       <c r="D132">
-        <v>1.583</v>
+        <v>454.707</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +4190,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46134.36458333334</v>
+        <v>46137.36458333334</v>
       </c>
       <c r="B133">
-        <v>17.966</v>
+        <v>-13.797</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>540.224</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>540.224</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +4210,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46134.375</v>
+        <v>46137.375</v>
       </c>
       <c r="B134">
-        <v>18.756</v>
+        <v>13.926</v>
       </c>
       <c r="C134">
-        <v>0.6</v>
+        <v>281.1</v>
       </c>
       <c r="D134">
-        <v>0.6</v>
+        <v>281.1</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +4230,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46134.38541666666</v>
+        <v>46137.38541666666</v>
       </c>
       <c r="B135">
-        <v>6.724</v>
+        <v>56.031</v>
       </c>
       <c r="C135">
-        <v>2</v>
+        <v>-643.5549999999999</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>-643.5549999999999</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +4250,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46134.39583333334</v>
+        <v>46137.39583333334</v>
       </c>
       <c r="B136">
-        <v>39.638</v>
+        <v>16.071</v>
       </c>
       <c r="C136">
-        <v>4.765</v>
+        <v>-879.753</v>
       </c>
       <c r="D136">
-        <v>4.765</v>
+        <v>-879.753</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +4270,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46134.40625</v>
+        <v>46137.40625</v>
       </c>
       <c r="B137">
-        <v>83.667</v>
+        <v>57.087</v>
       </c>
       <c r="C137">
-        <v>191.436</v>
+        <v>-6.444</v>
       </c>
       <c r="D137">
-        <v>191.436</v>
+        <v>-6.444</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +4290,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46134.41666666666</v>
+        <v>46137.41666666666</v>
       </c>
       <c r="B138">
-        <v>78.29600000000001</v>
+        <v>13.312</v>
       </c>
       <c r="C138">
-        <v>-2707.818</v>
+        <v>-107.97</v>
       </c>
       <c r="D138">
-        <v>-2707.818</v>
+        <v>-107.97</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +4310,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46134.42708333334</v>
+        <v>46137.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>2.381</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>-108</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>-108</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +4330,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46134.4375</v>
+        <v>46137.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>33.573</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>-17.346</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>-17.346</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +4350,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46134.44791666666</v>
+        <v>46137.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>13.304</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>2.936</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>2.936</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +4370,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46134.45833333334</v>
+        <v>46137.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>11.115</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +4390,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46134.46875</v>
+        <v>46137.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>10.903</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>4.511</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>4.511</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +4410,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46134.47916666666</v>
+        <v>46137.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>55.767</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>-1165.615</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>-1165.615</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +4430,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46134.48958333334</v>
+        <v>46137.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>22.154</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>-53.48</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>-53.48</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +4450,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46134.5</v>
+        <v>46137.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>45.573</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>-1199.711</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>-1199.711</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +4470,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46134.51041666666</v>
+        <v>46137.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>48.428</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>282.614</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>282.614</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +4490,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46134.52083333334</v>
+        <v>46137.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>61.227</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>350.664</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>350.664</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +4510,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46134.53125</v>
+        <v>46137.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>342.543</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>342.543</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,16 +4530,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46134.54166666666</v>
+        <v>46137.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>104.616</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>-520.5119999999999</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>-520.5119999999999</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3974,16 +4550,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46134.55208333334</v>
+        <v>46137.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>73.94499999999999</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>-3579.838</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>-3579.838</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -3994,16 +4570,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46134.5625</v>
+        <v>46137.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>50.044</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>-2944.563</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>-2944.563</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4014,16 +4590,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46134.57291666666</v>
+        <v>46137.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>-7499</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>-7499</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4034,10 +4610,10 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46134.58333333334</v>
+        <v>46137.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>94.51900000000001</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -4054,10 +4630,10 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46134.59375</v>
+        <v>46137.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>113.994</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -4074,16 +4650,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46134.60416666666</v>
+        <v>46137.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>103.257</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>-1204.393</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>-1204.393</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4094,16 +4670,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46134.61458333334</v>
+        <v>46137.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>54.659</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>-281.597</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>-281.597</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4114,16 +4690,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46134.625</v>
+        <v>46137.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>67.411</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>-287.982</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>-287.982</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4134,16 +4710,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46134.63541666666</v>
+        <v>46137.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>65.017</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>-279.584</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>-279.584</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4154,16 +4730,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46134.64583333334</v>
+        <v>46137.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>61.959</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>-277.876</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>-277.876</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46134.65625</v>
+        <v>46137.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>59.469</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>-288.89</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>-288.89</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4194,16 +4770,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46134.66666666666</v>
+        <v>46137.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>119.803</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>-308.949</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>-308.949</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4214,16 +4790,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46134.67708333334</v>
+        <v>46137.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>90.52</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>-133.911</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>-133.911</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4234,16 +4810,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46134.6875</v>
+        <v>46137.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>67.78700000000001</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>-107.158</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>-107.158</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4254,16 +4830,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46134.69791666666</v>
+        <v>46137.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>45.457</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>-100.08</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>-100.08</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4274,16 +4850,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46134.70833333334</v>
+        <v>46137.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>79.08799999999999</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>-1045.49</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>-1045.49</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4294,16 +4870,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46134.71875</v>
+        <v>46137.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>57.416</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>-26.761</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>-26.761</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4314,10 +4890,10 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46134.72916666666</v>
+        <v>46137.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>10.356</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -4334,16 +4910,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46134.73958333334</v>
+        <v>46137.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>18.525</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>6.298</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>6.298</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4354,16 +4930,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46134.75</v>
+        <v>46137.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>90.31100000000001</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>-514.269</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>-514.269</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4374,16 +4950,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46134.76041666666</v>
+        <v>46137.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>32.448</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>-218.441</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>-218.441</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4394,16 +4970,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46134.77083333334</v>
+        <v>46137.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>47.235</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>-35.68</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>-35.68</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4414,16 +4990,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46134.78125</v>
+        <v>46137.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>32.246</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>103.08</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>103.08</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4434,16 +5010,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46134.79166666666</v>
+        <v>46137.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>65.337</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>-667.612</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>-667.612</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4454,16 +5030,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46134.80208333334</v>
+        <v>46137.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>46.784</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>6.478</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>6.478</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4474,16 +5050,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46134.8125</v>
+        <v>46137.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>26.157</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>1.339</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>1.339</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4494,16 +5070,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46134.82291666666</v>
+        <v>46137.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>-31.711</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>1673.622</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>1673.622</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4514,16 +5090,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46134.83333333334</v>
+        <v>46137.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>-46.173</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>1418.963</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>1418.963</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4534,16 +5110,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46134.84375</v>
+        <v>46137.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>-41.124</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>969.9349999999999</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>969.9349999999999</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4554,16 +5130,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46134.85416666666</v>
+        <v>46137.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>-24.843</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>890.088</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>890.088</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4574,16 +5150,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46134.86458333334</v>
+        <v>46137.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>-16.367</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>915.712</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>915.712</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4594,16 +5170,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46134.875</v>
+        <v>46137.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>-17.691</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>890.41</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>890.41</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4614,16 +5190,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46134.88541666666</v>
+        <v>46137.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>-4.425</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>896.974</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>896.974</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4634,16 +5210,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46134.89583333334</v>
+        <v>46137.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>23.559</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>16.601</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>16.601</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4654,16 +5230,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46134.90625</v>
+        <v>46137.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>-0.778</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>887.174</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>887.174</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4674,16 +5250,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46134.91666666666</v>
+        <v>46137.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>12.975</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>202.135</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>202.135</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4694,16 +5270,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46134.92708333334</v>
+        <v>46137.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>897.518</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>897.518</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -4714,16 +5290,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46134.9375</v>
+        <v>46137.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>32.739</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>265.16</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>265.16</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -4734,16 +5310,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46134.94791666666</v>
+        <v>46137.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>1.503</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>263.117</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>263.117</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -4754,16 +5330,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46134.95833333334</v>
+        <v>46137.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>-10.772</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>953.918</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>953.918</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -4774,16 +5350,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46134.96875</v>
+        <v>46137.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>-21.763</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>919.187</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>919.187</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -4794,16 +5370,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46134.97916666666</v>
+        <v>46137.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>15.335</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>264.856</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>264.856</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -4814,22 +5390,3862 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46134.98958333334</v>
+        <v>46137.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>-2.286</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>897.462</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>897.462</v>
       </c>
       <c r="E193">
         <v>96</v>
       </c>
       <c r="F193" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46138</v>
+      </c>
+      <c r="B194">
+        <v>-20.136</v>
+      </c>
+      <c r="C194">
+        <v>909.698</v>
+      </c>
+      <c r="D194">
+        <v>909.698</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46138.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>-16.398</v>
+      </c>
+      <c r="C195">
+        <v>949.926</v>
+      </c>
+      <c r="D195">
+        <v>949.926</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46138.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>1.125</v>
+      </c>
+      <c r="C196">
+        <v>898.04</v>
+      </c>
+      <c r="D196">
+        <v>898.04</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46138.03125</v>
+      </c>
+      <c r="B197">
+        <v>1.534</v>
+      </c>
+      <c r="C197">
+        <v>270.599</v>
+      </c>
+      <c r="D197">
+        <v>270.599</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
+        <v>46138.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>-2.417</v>
+      </c>
+      <c r="C198">
+        <v>945.621</v>
+      </c>
+      <c r="D198">
+        <v>945.621</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
+        <v>46138.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>-31.449</v>
+      </c>
+      <c r="C199">
+        <v>933.703</v>
+      </c>
+      <c r="D199">
+        <v>933.703</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
+        <v>46138.0625</v>
+      </c>
+      <c r="B200">
+        <v>-21.583</v>
+      </c>
+      <c r="C200">
+        <v>967.509</v>
+      </c>
+      <c r="D200">
+        <v>967.509</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
+        <v>46138.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>-7.897</v>
+      </c>
+      <c r="C201">
+        <v>898.117</v>
+      </c>
+      <c r="D201">
+        <v>898.117</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
+        <v>46138.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>-32.871</v>
+      </c>
+      <c r="C202">
+        <v>891.718</v>
+      </c>
+      <c r="D202">
+        <v>891.718</v>
+      </c>
+      <c r="E202">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
+        <v>46138.09375</v>
+      </c>
+      <c r="B203">
+        <v>-43.755</v>
+      </c>
+      <c r="C203">
+        <v>885.182</v>
+      </c>
+      <c r="D203">
+        <v>885.182</v>
+      </c>
+      <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
+        <v>46138.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>4.74</v>
+      </c>
+      <c r="C204">
+        <v>400</v>
+      </c>
+      <c r="D204">
+        <v>400</v>
+      </c>
+      <c r="E204">
+        <v>11</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
+        <v>46138.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>3.061</v>
+      </c>
+      <c r="C205">
+        <v>255.657</v>
+      </c>
+      <c r="D205">
+        <v>255.657</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
+        <v>46138.125</v>
+      </c>
+      <c r="B206">
+        <v>-13.829</v>
+      </c>
+      <c r="C206">
+        <v>872.812</v>
+      </c>
+      <c r="D206">
+        <v>872.812</v>
+      </c>
+      <c r="E206">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
+        <v>46138.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>-7.477</v>
+      </c>
+      <c r="C207">
+        <v>863.413</v>
+      </c>
+      <c r="D207">
+        <v>863.413</v>
+      </c>
+      <c r="E207">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
+        <v>46138.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>-8.798</v>
+      </c>
+      <c r="C208">
+        <v>849.944</v>
+      </c>
+      <c r="D208">
+        <v>849.944</v>
+      </c>
+      <c r="E208">
+        <v>15</v>
+      </c>
+      <c r="F208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
+        <v>46138.15625</v>
+      </c>
+      <c r="B209">
+        <v>-10.385</v>
+      </c>
+      <c r="C209">
+        <v>860.79</v>
+      </c>
+      <c r="D209">
+        <v>860.79</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
+        <v>46138.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>-3.14</v>
+      </c>
+      <c r="C210">
+        <v>859.688</v>
+      </c>
+      <c r="D210">
+        <v>859.688</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+      <c r="F210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
+        <v>46138.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>26.682</v>
+      </c>
+      <c r="C211">
+        <v>241.351</v>
+      </c>
+      <c r="D211">
+        <v>241.351</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
+        <v>46138.1875</v>
+      </c>
+      <c r="B212">
+        <v>47.769</v>
+      </c>
+      <c r="C212">
+        <v>66.364</v>
+      </c>
+      <c r="D212">
+        <v>66.364</v>
+      </c>
+      <c r="E212">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
+        <v>46138.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>51.999</v>
+      </c>
+      <c r="C213">
+        <v>118.938</v>
+      </c>
+      <c r="D213">
+        <v>118.938</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
+        <v>46138.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>54.64</v>
+      </c>
+      <c r="C214">
+        <v>136.195</v>
+      </c>
+      <c r="D214">
+        <v>136.195</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
+        <v>46138.21875</v>
+      </c>
+      <c r="B215">
+        <v>41.397</v>
+      </c>
+      <c r="C215">
+        <v>-1851.687</v>
+      </c>
+      <c r="D215">
+        <v>-1851.687</v>
+      </c>
+      <c r="E215">
+        <v>22</v>
+      </c>
+      <c r="F215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
+        <v>46138.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>29.54</v>
+      </c>
+      <c r="C216">
+        <v>-2012.005</v>
+      </c>
+      <c r="D216">
+        <v>-2012.005</v>
+      </c>
+      <c r="E216">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
+        <v>46138.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>29.211</v>
+      </c>
+      <c r="C217">
+        <v>-408.405</v>
+      </c>
+      <c r="D217">
+        <v>-408.405</v>
+      </c>
+      <c r="E217">
+        <v>24</v>
+      </c>
+      <c r="F217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
+        <v>46138.25</v>
+      </c>
+      <c r="B218">
+        <v>8.637</v>
+      </c>
+      <c r="C218">
+        <v>117.089</v>
+      </c>
+      <c r="D218">
+        <v>117.089</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
+        <v>46138.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>7.045</v>
+      </c>
+      <c r="C219">
+        <v>127.051</v>
+      </c>
+      <c r="D219">
+        <v>127.051</v>
+      </c>
+      <c r="E219">
+        <v>26</v>
+      </c>
+      <c r="F219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
+        <v>46138.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>17.889</v>
+      </c>
+      <c r="C220">
+        <v>-524.4930000000001</v>
+      </c>
+      <c r="D220">
+        <v>-524.4930000000001</v>
+      </c>
+      <c r="E220">
+        <v>27</v>
+      </c>
+      <c r="F220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
+        <v>46138.28125</v>
+      </c>
+      <c r="B221">
+        <v>52.396</v>
+      </c>
+      <c r="C221">
+        <v>-3147.368</v>
+      </c>
+      <c r="D221">
+        <v>-3147.368</v>
+      </c>
+      <c r="E221">
+        <v>28</v>
+      </c>
+      <c r="F221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
+        <v>46138.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>45.271</v>
+      </c>
+      <c r="C222">
+        <v>-1544.754</v>
+      </c>
+      <c r="D222">
+        <v>-1544.754</v>
+      </c>
+      <c r="E222">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
+        <v>46138.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>17.139</v>
+      </c>
+      <c r="C223">
+        <v>-444.615</v>
+      </c>
+      <c r="D223">
+        <v>-444.615</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="F223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
+        <v>46138.3125</v>
+      </c>
+      <c r="B224">
+        <v>3.486</v>
+      </c>
+      <c r="C224">
+        <v>-11.13</v>
+      </c>
+      <c r="D224">
+        <v>-11.13</v>
+      </c>
+      <c r="E224">
+        <v>31</v>
+      </c>
+      <c r="F224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
+        <v>46138.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>-0.482</v>
+      </c>
+      <c r="C225">
+        <v>-8.089</v>
+      </c>
+      <c r="D225">
+        <v>-8.089</v>
+      </c>
+      <c r="E225">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
+        <v>46138.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>-96.461</v>
+      </c>
+      <c r="C226">
+        <v>4998.662</v>
+      </c>
+      <c r="D226">
+        <v>4998.662</v>
+      </c>
+      <c r="E226">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
+        <v>46138.34375</v>
+      </c>
+      <c r="B227">
+        <v>-133.325</v>
+      </c>
+      <c r="C227">
+        <v>4346.372</v>
+      </c>
+      <c r="D227">
+        <v>4346.372</v>
+      </c>
+      <c r="E227">
+        <v>34</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
+        <v>46138.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>-168.585</v>
+      </c>
+      <c r="C228">
+        <v>436.147</v>
+      </c>
+      <c r="D228">
+        <v>436.147</v>
+      </c>
+      <c r="E228">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
+        <v>46138.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>-78.675</v>
+      </c>
+      <c r="C229">
+        <v>448</v>
+      </c>
+      <c r="D229">
+        <v>448</v>
+      </c>
+      <c r="E229">
+        <v>36</v>
+      </c>
+      <c r="F229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
+        <v>46138.375</v>
+      </c>
+      <c r="B230">
+        <v>-148.21</v>
+      </c>
+      <c r="C230">
+        <v>516.943</v>
+      </c>
+      <c r="D230">
+        <v>516.943</v>
+      </c>
+      <c r="E230">
+        <v>37</v>
+      </c>
+      <c r="F230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46138.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>-98.04900000000001</v>
+      </c>
+      <c r="C231">
+        <v>447.811</v>
+      </c>
+      <c r="D231">
+        <v>447.811</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46138.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>3.215</v>
+      </c>
+      <c r="C232">
+        <v>-2644.325</v>
+      </c>
+      <c r="D232">
+        <v>-2644.325</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
+        <v>46138.40625</v>
+      </c>
+      <c r="B233">
+        <v>17.853</v>
+      </c>
+      <c r="C233">
+        <v>-1251.864</v>
+      </c>
+      <c r="D233">
+        <v>-1251.864</v>
+      </c>
+      <c r="E233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
+        <v>46138.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>53.449</v>
+      </c>
+      <c r="C234">
+        <v>-257.106</v>
+      </c>
+      <c r="D234">
+        <v>-257.106</v>
+      </c>
+      <c r="E234">
+        <v>41</v>
+      </c>
+      <c r="F234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
+        <v>46138.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>66.271</v>
+      </c>
+      <c r="C235">
+        <v>-1970.07</v>
+      </c>
+      <c r="D235">
+        <v>-1970.07</v>
+      </c>
+      <c r="E235">
+        <v>42</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
+        <v>46138.4375</v>
+      </c>
+      <c r="B236">
+        <v>106.808</v>
+      </c>
+      <c r="C236">
+        <v>-690.574</v>
+      </c>
+      <c r="D236">
+        <v>-690.574</v>
+      </c>
+      <c r="E236">
+        <v>43</v>
+      </c>
+      <c r="F236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
+        <v>46138.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>65.99299999999999</v>
+      </c>
+      <c r="C237">
+        <v>-196.198</v>
+      </c>
+      <c r="D237">
+        <v>-196.198</v>
+      </c>
+      <c r="E237">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
+        <v>46138.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>32.992</v>
+      </c>
+      <c r="C238">
+        <v>-57.454</v>
+      </c>
+      <c r="D238">
+        <v>-57.454</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
+        <v>46138.46875</v>
+      </c>
+      <c r="B239">
+        <v>25.671</v>
+      </c>
+      <c r="C239">
+        <v>15.507</v>
+      </c>
+      <c r="D239">
+        <v>15.507</v>
+      </c>
+      <c r="E239">
+        <v>46</v>
+      </c>
+      <c r="F239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
+        <v>46138.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>50.279</v>
+      </c>
+      <c r="C240">
+        <v>-113.433</v>
+      </c>
+      <c r="D240">
+        <v>-113.433</v>
+      </c>
+      <c r="E240">
+        <v>47</v>
+      </c>
+      <c r="F240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
+        <v>46138.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>60.451</v>
+      </c>
+      <c r="C241">
+        <v>-762.825</v>
+      </c>
+      <c r="D241">
+        <v>-762.825</v>
+      </c>
+      <c r="E241">
+        <v>48</v>
+      </c>
+      <c r="F241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
+        <v>46138.5</v>
+      </c>
+      <c r="B242">
+        <v>76.503</v>
+      </c>
+      <c r="C242">
+        <v>-1506.036</v>
+      </c>
+      <c r="D242">
+        <v>-1506.036</v>
+      </c>
+      <c r="E242">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
+        <v>46138.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>93.69499999999999</v>
+      </c>
+      <c r="C243">
+        <v>-5198.447</v>
+      </c>
+      <c r="D243">
+        <v>-5198.447</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
+        <v>46138.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>111.405</v>
+      </c>
+      <c r="C244">
+        <v>-4657.286</v>
+      </c>
+      <c r="D244">
+        <v>-4657.286</v>
+      </c>
+      <c r="E244">
+        <v>51</v>
+      </c>
+      <c r="F244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
+        <v>46138.53125</v>
+      </c>
+      <c r="B245">
+        <v>122.023</v>
+      </c>
+      <c r="C245">
+        <v>-1366.13</v>
+      </c>
+      <c r="D245">
+        <v>-1366.13</v>
+      </c>
+      <c r="E245">
+        <v>52</v>
+      </c>
+      <c r="F245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
+        <v>46138.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>143.015</v>
+      </c>
+      <c r="C246">
+        <v>-2641.154</v>
+      </c>
+      <c r="D246">
+        <v>-2641.154</v>
+      </c>
+      <c r="E246">
+        <v>53</v>
+      </c>
+      <c r="F246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
+        <v>46138.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>149.552</v>
+      </c>
+      <c r="C247">
+        <v>-2575.747</v>
+      </c>
+      <c r="D247">
+        <v>-2575.747</v>
+      </c>
+      <c r="E247">
+        <v>54</v>
+      </c>
+      <c r="F247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
+        <v>46138.5625</v>
+      </c>
+      <c r="B248">
+        <v>159.818</v>
+      </c>
+      <c r="C248">
+        <v>-2341.085</v>
+      </c>
+      <c r="D248">
+        <v>-2341.085</v>
+      </c>
+      <c r="E248">
+        <v>55</v>
+      </c>
+      <c r="F248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
+        <v>46138.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>168.07</v>
+      </c>
+      <c r="C249">
+        <v>-1549.507</v>
+      </c>
+      <c r="D249">
+        <v>-1549.507</v>
+      </c>
+      <c r="E249">
+        <v>56</v>
+      </c>
+      <c r="F249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
+        <v>46138.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>192.031</v>
+      </c>
+      <c r="C250">
+        <v>-1593.836</v>
+      </c>
+      <c r="D250">
+        <v>-1593.836</v>
+      </c>
+      <c r="E250">
+        <v>57</v>
+      </c>
+      <c r="F250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
+        <v>46138.59375</v>
+      </c>
+      <c r="B251">
+        <v>152.803</v>
+      </c>
+      <c r="C251">
+        <v>-1064.527</v>
+      </c>
+      <c r="D251">
+        <v>-1064.527</v>
+      </c>
+      <c r="E251">
+        <v>58</v>
+      </c>
+      <c r="F251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
+        <v>46138.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>140.513</v>
+      </c>
+      <c r="C252">
+        <v>-1030.91</v>
+      </c>
+      <c r="D252">
+        <v>-1030.91</v>
+      </c>
+      <c r="E252">
+        <v>59</v>
+      </c>
+      <c r="F252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
+        <v>46138.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>132.503</v>
+      </c>
+      <c r="C253">
+        <v>-890.896</v>
+      </c>
+      <c r="D253">
+        <v>-890.896</v>
+      </c>
+      <c r="E253">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
+        <v>46138.625</v>
+      </c>
+      <c r="B254">
+        <v>148.324</v>
+      </c>
+      <c r="C254">
+        <v>-832.66</v>
+      </c>
+      <c r="D254">
+        <v>-832.66</v>
+      </c>
+      <c r="E254">
+        <v>61</v>
+      </c>
+      <c r="F254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
+        <v>46138.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>104.431</v>
+      </c>
+      <c r="C255">
+        <v>-287.117</v>
+      </c>
+      <c r="D255">
+        <v>-287.117</v>
+      </c>
+      <c r="E255">
+        <v>62</v>
+      </c>
+      <c r="F255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
+        <v>46138.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>63.441</v>
+      </c>
+      <c r="C256">
+        <v>-295</v>
+      </c>
+      <c r="D256">
+        <v>-295</v>
+      </c>
+      <c r="E256">
+        <v>63</v>
+      </c>
+      <c r="F256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
+        <v>46138.65625</v>
+      </c>
+      <c r="B257">
+        <v>50.244</v>
+      </c>
+      <c r="C257">
+        <v>-165</v>
+      </c>
+      <c r="D257">
+        <v>-165</v>
+      </c>
+      <c r="E257">
+        <v>64</v>
+      </c>
+      <c r="F257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
+        <v>46138.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>91.093</v>
+      </c>
+      <c r="C258">
+        <v>-185.252</v>
+      </c>
+      <c r="D258">
+        <v>-185.252</v>
+      </c>
+      <c r="E258">
+        <v>65</v>
+      </c>
+      <c r="F258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
+        <v>46138.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>67.066</v>
+      </c>
+      <c r="C259">
+        <v>-703.057</v>
+      </c>
+      <c r="D259">
+        <v>-703.057</v>
+      </c>
+      <c r="E259">
+        <v>66</v>
+      </c>
+      <c r="F259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
+        <v>46138.6875</v>
+      </c>
+      <c r="B260">
+        <v>73.61799999999999</v>
+      </c>
+      <c r="C260">
+        <v>-716.418</v>
+      </c>
+      <c r="D260">
+        <v>-716.418</v>
+      </c>
+      <c r="E260">
+        <v>67</v>
+      </c>
+      <c r="F260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
+        <v>46138.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>125.402</v>
+      </c>
+      <c r="C261">
+        <v>-82</v>
+      </c>
+      <c r="D261">
+        <v>-82</v>
+      </c>
+      <c r="E261">
+        <v>68</v>
+      </c>
+      <c r="F261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
+        <v>46138.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>129.479</v>
+      </c>
+      <c r="C262">
+        <v>-4171.758</v>
+      </c>
+      <c r="D262">
+        <v>-4171.758</v>
+      </c>
+      <c r="E262">
+        <v>69</v>
+      </c>
+      <c r="F262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
+        <v>46138.71875</v>
+      </c>
+      <c r="B263">
+        <v>63.249</v>
+      </c>
+      <c r="C263">
+        <v>-772.359</v>
+      </c>
+      <c r="D263">
+        <v>-772.359</v>
+      </c>
+      <c r="E263">
+        <v>70</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46138.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>4.104</v>
+      </c>
+      <c r="C264">
+        <v>-165</v>
+      </c>
+      <c r="D264">
+        <v>-165</v>
+      </c>
+      <c r="E264">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46138.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>50.843</v>
+      </c>
+      <c r="C265">
+        <v>0.413</v>
+      </c>
+      <c r="D265">
+        <v>0.413</v>
+      </c>
+      <c r="E265">
+        <v>72</v>
+      </c>
+      <c r="F265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46138.75</v>
+      </c>
+      <c r="B266">
+        <v>44.362</v>
+      </c>
+      <c r="C266">
+        <v>-3.204</v>
+      </c>
+      <c r="D266">
+        <v>-3.204</v>
+      </c>
+      <c r="E266">
+        <v>73</v>
+      </c>
+      <c r="F266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46138.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>19.805</v>
+      </c>
+      <c r="C267">
+        <v>0.5</v>
+      </c>
+      <c r="D267">
+        <v>0.5</v>
+      </c>
+      <c r="E267">
+        <v>74</v>
+      </c>
+      <c r="F267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46138.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>43.164</v>
+      </c>
+      <c r="C268">
+        <v>400</v>
+      </c>
+      <c r="D268">
+        <v>400</v>
+      </c>
+      <c r="E268">
+        <v>75</v>
+      </c>
+      <c r="F268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46138.78125</v>
+      </c>
+      <c r="B269">
+        <v>5.551</v>
+      </c>
+      <c r="C269">
+        <v>276.01</v>
+      </c>
+      <c r="D269">
+        <v>276.01</v>
+      </c>
+      <c r="E269">
+        <v>76</v>
+      </c>
+      <c r="F269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46138.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>21.72</v>
+      </c>
+      <c r="C270">
+        <v>-36.113</v>
+      </c>
+      <c r="D270">
+        <v>-36.113</v>
+      </c>
+      <c r="E270">
+        <v>77</v>
+      </c>
+      <c r="F270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46138.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>15.27</v>
+      </c>
+      <c r="C271">
+        <v>270.973</v>
+      </c>
+      <c r="D271">
+        <v>270.973</v>
+      </c>
+      <c r="E271">
+        <v>78</v>
+      </c>
+      <c r="F271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46138.8125</v>
+      </c>
+      <c r="B272">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="C272">
+        <v>957.904</v>
+      </c>
+      <c r="D272">
+        <v>957.904</v>
+      </c>
+      <c r="E272">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46138.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>-25.381</v>
+      </c>
+      <c r="C273">
+        <v>2177.185</v>
+      </c>
+      <c r="D273">
+        <v>2177.185</v>
+      </c>
+      <c r="E273">
+        <v>80</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46138.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>-36.257</v>
+      </c>
+      <c r="C274">
+        <v>1240.081</v>
+      </c>
+      <c r="D274">
+        <v>1240.081</v>
+      </c>
+      <c r="E274">
+        <v>81</v>
+      </c>
+      <c r="F274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46138.84375</v>
+      </c>
+      <c r="B275">
+        <v>-54.847</v>
+      </c>
+      <c r="C275">
+        <v>1725.198</v>
+      </c>
+      <c r="D275">
+        <v>1725.198</v>
+      </c>
+      <c r="E275">
+        <v>82</v>
+      </c>
+      <c r="F275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46138.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>-95.38500000000001</v>
+      </c>
+      <c r="C276">
+        <v>3456.674</v>
+      </c>
+      <c r="D276">
+        <v>3456.674</v>
+      </c>
+      <c r="E276">
+        <v>83</v>
+      </c>
+      <c r="F276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46138.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>-65.09</v>
+      </c>
+      <c r="C277">
+        <v>4086.197</v>
+      </c>
+      <c r="D277">
+        <v>4086.197</v>
+      </c>
+      <c r="E277">
+        <v>84</v>
+      </c>
+      <c r="F277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46138.875</v>
+      </c>
+      <c r="B278">
+        <v>-79.583</v>
+      </c>
+      <c r="C278">
+        <v>6571.524</v>
+      </c>
+      <c r="D278">
+        <v>6571.524</v>
+      </c>
+      <c r="E278">
+        <v>85</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46138.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>-110.769</v>
+      </c>
+      <c r="C279">
+        <v>5213.072</v>
+      </c>
+      <c r="D279">
+        <v>5213.072</v>
+      </c>
+      <c r="E279">
+        <v>86</v>
+      </c>
+      <c r="F279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46138.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>-90.55</v>
+      </c>
+      <c r="C280">
+        <v>4574.334</v>
+      </c>
+      <c r="D280">
+        <v>4574.334</v>
+      </c>
+      <c r="E280">
+        <v>87</v>
+      </c>
+      <c r="F280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46138.90625</v>
+      </c>
+      <c r="B281">
+        <v>-78.92100000000001</v>
+      </c>
+      <c r="C281">
+        <v>3222.109</v>
+      </c>
+      <c r="D281">
+        <v>3222.109</v>
+      </c>
+      <c r="E281">
+        <v>88</v>
+      </c>
+      <c r="F281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46138.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>-89.396</v>
+      </c>
+      <c r="C282">
+        <v>1869.966</v>
+      </c>
+      <c r="D282">
+        <v>1869.966</v>
+      </c>
+      <c r="E282">
+        <v>89</v>
+      </c>
+      <c r="F282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46138.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>-68.745</v>
+      </c>
+      <c r="C283">
+        <v>4256.604</v>
+      </c>
+      <c r="D283">
+        <v>4256.604</v>
+      </c>
+      <c r="E283">
+        <v>90</v>
+      </c>
+      <c r="F283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46138.9375</v>
+      </c>
+      <c r="B284">
+        <v>-79.286</v>
+      </c>
+      <c r="C284">
+        <v>4554.097</v>
+      </c>
+      <c r="D284">
+        <v>4554.097</v>
+      </c>
+      <c r="E284">
+        <v>91</v>
+      </c>
+      <c r="F284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46138.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>-99.532</v>
+      </c>
+      <c r="C285">
+        <v>2333.476</v>
+      </c>
+      <c r="D285">
+        <v>2333.476</v>
+      </c>
+      <c r="E285">
+        <v>92</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46138.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>-78.67</v>
+      </c>
+      <c r="C286">
+        <v>1078.473</v>
+      </c>
+      <c r="D286">
+        <v>1078.473</v>
+      </c>
+      <c r="E286">
+        <v>93</v>
+      </c>
+      <c r="F286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46138.96875</v>
+      </c>
+      <c r="B287">
+        <v>-32.204</v>
+      </c>
+      <c r="C287">
+        <v>1065.02</v>
+      </c>
+      <c r="D287">
+        <v>1065.02</v>
+      </c>
+      <c r="E287">
+        <v>94</v>
+      </c>
+      <c r="F287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46138.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>36.912</v>
+      </c>
+      <c r="C288">
+        <v>-3291.851</v>
+      </c>
+      <c r="D288">
+        <v>-3291.851</v>
+      </c>
+      <c r="E288">
+        <v>95</v>
+      </c>
+      <c r="F288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46138.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>64.57899999999999</v>
+      </c>
+      <c r="C289">
+        <v>-3636.358</v>
+      </c>
+      <c r="D289">
+        <v>-3636.358</v>
+      </c>
+      <c r="E289">
+        <v>96</v>
+      </c>
+      <c r="F289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B290">
+        <v>140.004</v>
+      </c>
+      <c r="C290">
+        <v>-1314.902</v>
+      </c>
+      <c r="D290">
+        <v>-1314.902</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46139.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>158.374</v>
+      </c>
+      <c r="C291">
+        <v>76.37</v>
+      </c>
+      <c r="D291">
+        <v>76.37</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46139.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>122.708</v>
+      </c>
+      <c r="C292">
+        <v>4.256</v>
+      </c>
+      <c r="D292">
+        <v>4.256</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46139.03125</v>
+      </c>
+      <c r="B293">
+        <v>60.282</v>
+      </c>
+      <c r="C293">
+        <v>3.801</v>
+      </c>
+      <c r="D293">
+        <v>3.801</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46139.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>66.09399999999999</v>
+      </c>
+      <c r="C294">
+        <v>4.62</v>
+      </c>
+      <c r="D294">
+        <v>4.62</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46139.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>60.975</v>
+      </c>
+      <c r="C295">
+        <v>2.203</v>
+      </c>
+      <c r="D295">
+        <v>2.203</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46139.0625</v>
+      </c>
+      <c r="B296">
+        <v>30.817</v>
+      </c>
+      <c r="C296">
+        <v>0.5</v>
+      </c>
+      <c r="D296">
+        <v>0.5</v>
+      </c>
+      <c r="E296">
+        <v>7</v>
+      </c>
+      <c r="F296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46139.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>60.497</v>
+      </c>
+      <c r="C297">
+        <v>1.907</v>
+      </c>
+      <c r="D297">
+        <v>1.907</v>
+      </c>
+      <c r="E297">
+        <v>8</v>
+      </c>
+      <c r="F297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46139.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>117.696</v>
+      </c>
+      <c r="C298">
+        <v>-1689.276</v>
+      </c>
+      <c r="D298">
+        <v>-1689.276</v>
+      </c>
+      <c r="E298">
+        <v>9</v>
+      </c>
+      <c r="F298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46139.09375</v>
+      </c>
+      <c r="B299">
+        <v>139.115</v>
+      </c>
+      <c r="C299">
+        <v>-1971.872</v>
+      </c>
+      <c r="D299">
+        <v>-1971.872</v>
+      </c>
+      <c r="E299">
+        <v>10</v>
+      </c>
+      <c r="F299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46139.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>75.628</v>
+      </c>
+      <c r="C300">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="D300">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E300">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46139.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>76.35299999999999</v>
+      </c>
+      <c r="C301">
+        <v>13.109</v>
+      </c>
+      <c r="D301">
+        <v>13.109</v>
+      </c>
+      <c r="E301">
+        <v>12</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46139.125</v>
+      </c>
+      <c r="B302">
+        <v>68.977</v>
+      </c>
+      <c r="C302">
+        <v>3.787</v>
+      </c>
+      <c r="D302">
+        <v>3.787</v>
+      </c>
+      <c r="E302">
+        <v>13</v>
+      </c>
+      <c r="F302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46139.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>59.734</v>
+      </c>
+      <c r="C303">
+        <v>2.122</v>
+      </c>
+      <c r="D303">
+        <v>2.122</v>
+      </c>
+      <c r="E303">
+        <v>14</v>
+      </c>
+      <c r="F303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46139.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>138.501</v>
+      </c>
+      <c r="C304">
+        <v>3.834</v>
+      </c>
+      <c r="D304">
+        <v>3.834</v>
+      </c>
+      <c r="E304">
+        <v>15</v>
+      </c>
+      <c r="F304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46139.15625</v>
+      </c>
+      <c r="B305">
+        <v>125.856</v>
+      </c>
+      <c r="C305">
+        <v>1.688</v>
+      </c>
+      <c r="D305">
+        <v>1.688</v>
+      </c>
+      <c r="E305">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46139.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>25.584</v>
+      </c>
+      <c r="C306">
+        <v>0.6</v>
+      </c>
+      <c r="D306">
+        <v>0.6</v>
+      </c>
+      <c r="E306">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46139.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>-25.932</v>
+      </c>
+      <c r="C307">
+        <v>988.99</v>
+      </c>
+      <c r="D307">
+        <v>988.99</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46139.1875</v>
+      </c>
+      <c r="B308">
+        <v>-25.206</v>
+      </c>
+      <c r="C308">
+        <v>2662.526</v>
+      </c>
+      <c r="D308">
+        <v>2662.526</v>
+      </c>
+      <c r="E308">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46139.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>-19.353</v>
+      </c>
+      <c r="C309">
+        <v>1547.525</v>
+      </c>
+      <c r="D309">
+        <v>1547.525</v>
+      </c>
+      <c r="E309">
+        <v>20</v>
+      </c>
+      <c r="F309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46139.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>-33.354</v>
+      </c>
+      <c r="C310">
+        <v>1607.849</v>
+      </c>
+      <c r="D310">
+        <v>1607.849</v>
+      </c>
+      <c r="E310">
+        <v>21</v>
+      </c>
+      <c r="F310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="2">
+        <v>46139.21875</v>
+      </c>
+      <c r="B311">
+        <v>0.226</v>
+      </c>
+      <c r="C311">
+        <v>341.474</v>
+      </c>
+      <c r="D311">
+        <v>341.474</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="2">
+        <v>46139.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>-0.263</v>
+      </c>
+      <c r="C312">
+        <v>939.401</v>
+      </c>
+      <c r="D312">
+        <v>939.401</v>
+      </c>
+      <c r="E312">
+        <v>23</v>
+      </c>
+      <c r="F312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="2">
+        <v>46139.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>-4.182</v>
+      </c>
+      <c r="C313">
+        <v>961.6950000000001</v>
+      </c>
+      <c r="D313">
+        <v>961.6950000000001</v>
+      </c>
+      <c r="E313">
+        <v>24</v>
+      </c>
+      <c r="F313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="2">
+        <v>46139.25</v>
+      </c>
+      <c r="B314">
+        <v>36.265</v>
+      </c>
+      <c r="C314">
+        <v>-106.121</v>
+      </c>
+      <c r="D314">
+        <v>-106.121</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="2">
+        <v>46139.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>42.64</v>
+      </c>
+      <c r="C315">
+        <v>334.08</v>
+      </c>
+      <c r="D315">
+        <v>334.08</v>
+      </c>
+      <c r="E315">
+        <v>26</v>
+      </c>
+      <c r="F315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="2">
+        <v>46139.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>21.409</v>
+      </c>
+      <c r="C316">
+        <v>162.782</v>
+      </c>
+      <c r="D316">
+        <v>162.782</v>
+      </c>
+      <c r="E316">
+        <v>27</v>
+      </c>
+      <c r="F316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="2">
+        <v>46139.28125</v>
+      </c>
+      <c r="B317">
+        <v>23.237</v>
+      </c>
+      <c r="C317">
+        <v>-436.125</v>
+      </c>
+      <c r="D317">
+        <v>-436.125</v>
+      </c>
+      <c r="E317">
+        <v>28</v>
+      </c>
+      <c r="F317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="2">
+        <v>46139.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>32.175</v>
+      </c>
+      <c r="C318">
+        <v>-527.456</v>
+      </c>
+      <c r="D318">
+        <v>-527.456</v>
+      </c>
+      <c r="E318">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="2">
+        <v>46139.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>35.968</v>
+      </c>
+      <c r="C319">
+        <v>-494.599</v>
+      </c>
+      <c r="D319">
+        <v>-494.599</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="2">
+        <v>46139.3125</v>
+      </c>
+      <c r="B320">
+        <v>49.268</v>
+      </c>
+      <c r="C320">
+        <v>-11.454</v>
+      </c>
+      <c r="D320">
+        <v>-11.454</v>
+      </c>
+      <c r="E320">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="2">
+        <v>46139.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>83.163</v>
+      </c>
+      <c r="C321">
+        <v>-359.979</v>
+      </c>
+      <c r="D321">
+        <v>-359.979</v>
+      </c>
+      <c r="E321">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="2">
+        <v>46139.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>99.53</v>
+      </c>
+      <c r="C322">
+        <v>-752.978</v>
+      </c>
+      <c r="D322">
+        <v>-752.978</v>
+      </c>
+      <c r="E322">
+        <v>33</v>
+      </c>
+      <c r="F322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="2">
+        <v>46139.34375</v>
+      </c>
+      <c r="B323">
+        <v>73.666</v>
+      </c>
+      <c r="C323">
+        <v>-84.887</v>
+      </c>
+      <c r="D323">
+        <v>-84.887</v>
+      </c>
+      <c r="E323">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="2">
+        <v>46139.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>74.98399999999999</v>
+      </c>
+      <c r="C324">
+        <v>-8.407999999999999</v>
+      </c>
+      <c r="D324">
+        <v>-8.407999999999999</v>
+      </c>
+      <c r="E324">
+        <v>35</v>
+      </c>
+      <c r="F324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="2">
+        <v>46139.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>76.70099999999999</v>
+      </c>
+      <c r="C325">
+        <v>-43.964</v>
+      </c>
+      <c r="D325">
+        <v>-43.964</v>
+      </c>
+      <c r="E325">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="2">
+        <v>46139.375</v>
+      </c>
+      <c r="B326">
+        <v>1.05</v>
+      </c>
+      <c r="C326">
+        <v>5.11</v>
+      </c>
+      <c r="D326">
+        <v>5.11</v>
+      </c>
+      <c r="E326">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="2">
+        <v>46139.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>24.699</v>
+      </c>
+      <c r="C327">
+        <v>2.002</v>
+      </c>
+      <c r="D327">
+        <v>2.002</v>
+      </c>
+      <c r="E327">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="2">
+        <v>46139.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>74.232</v>
+      </c>
+      <c r="C328">
+        <v>-45.815</v>
+      </c>
+      <c r="D328">
+        <v>-45.815</v>
+      </c>
+      <c r="E328">
+        <v>39</v>
+      </c>
+      <c r="F328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="2">
+        <v>46139.40625</v>
+      </c>
+      <c r="B329">
+        <v>100.925</v>
+      </c>
+      <c r="C329">
+        <v>-488.561</v>
+      </c>
+      <c r="D329">
+        <v>-488.561</v>
+      </c>
+      <c r="E329">
+        <v>40</v>
+      </c>
+      <c r="F329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="2">
+        <v>46139.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>54.484</v>
+      </c>
+      <c r="C330">
+        <v>-202.984</v>
+      </c>
+      <c r="D330">
+        <v>-202.984</v>
+      </c>
+      <c r="E330">
+        <v>41</v>
+      </c>
+      <c r="F330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="2">
+        <v>46139.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>28.842</v>
+      </c>
+      <c r="C331">
+        <v>-105.208</v>
+      </c>
+      <c r="D331">
+        <v>-105.208</v>
+      </c>
+      <c r="E331">
+        <v>42</v>
+      </c>
+      <c r="F331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="2">
+        <v>46139.4375</v>
+      </c>
+      <c r="B332">
+        <v>59.555</v>
+      </c>
+      <c r="C332">
+        <v>-105.717</v>
+      </c>
+      <c r="D332">
+        <v>-105.717</v>
+      </c>
+      <c r="E332">
+        <v>43</v>
+      </c>
+      <c r="F332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="2">
+        <v>46139.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>78.38800000000001</v>
+      </c>
+      <c r="C333">
+        <v>-125.809</v>
+      </c>
+      <c r="D333">
+        <v>-125.809</v>
+      </c>
+      <c r="E333">
+        <v>44</v>
+      </c>
+      <c r="F333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="2">
+        <v>46139.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>55.47</v>
+      </c>
+      <c r="C334">
+        <v>-290.094</v>
+      </c>
+      <c r="D334">
+        <v>-290.094</v>
+      </c>
+      <c r="E334">
+        <v>45</v>
+      </c>
+      <c r="F334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="2">
+        <v>46139.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>46</v>
+      </c>
+      <c r="F335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="2">
+        <v>46139.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>47</v>
+      </c>
+      <c r="F336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="2">
+        <v>46139.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>48</v>
+      </c>
+      <c r="F337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="2">
+        <v>46139.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>49</v>
+      </c>
+      <c r="F338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="2">
+        <v>46139.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>50</v>
+      </c>
+      <c r="F339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="2">
+        <v>46139.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>51</v>
+      </c>
+      <c r="F340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" s="2">
+        <v>46139.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>52</v>
+      </c>
+      <c r="F341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="2">
+        <v>46139.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>53</v>
+      </c>
+      <c r="F342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="2">
+        <v>46139.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>54</v>
+      </c>
+      <c r="F343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="2">
+        <v>46139.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>55</v>
+      </c>
+      <c r="F344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="2">
+        <v>46139.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>56</v>
+      </c>
+      <c r="F345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="2">
+        <v>46139.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>57</v>
+      </c>
+      <c r="F346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="2">
+        <v>46139.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>58</v>
+      </c>
+      <c r="F347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="2">
+        <v>46139.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>59</v>
+      </c>
+      <c r="F348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="2">
+        <v>46139.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>60</v>
+      </c>
+      <c r="F349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="2">
+        <v>46139.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>61</v>
+      </c>
+      <c r="F350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="2">
+        <v>46139.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>62</v>
+      </c>
+      <c r="F351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="2">
+        <v>46139.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>63</v>
+      </c>
+      <c r="F352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="2">
+        <v>46139.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>64</v>
+      </c>
+      <c r="F353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="2">
+        <v>46139.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>65</v>
+      </c>
+      <c r="F354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="2">
+        <v>46139.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>66</v>
+      </c>
+      <c r="F355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="2">
+        <v>46139.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>67</v>
+      </c>
+      <c r="F356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="2">
+        <v>46139.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>68</v>
+      </c>
+      <c r="F357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="2">
+        <v>46139.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>69</v>
+      </c>
+      <c r="F358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="2">
+        <v>46139.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>70</v>
+      </c>
+      <c r="F359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="2">
+        <v>46139.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>71</v>
+      </c>
+      <c r="F360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="2">
+        <v>46139.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>72</v>
+      </c>
+      <c r="F361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="2">
+        <v>46139.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>73</v>
+      </c>
+      <c r="F362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="2">
+        <v>46139.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>74</v>
+      </c>
+      <c r="F363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="2">
+        <v>46139.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>75</v>
+      </c>
+      <c r="F364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="2">
+        <v>46139.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>76</v>
+      </c>
+      <c r="F365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="2">
+        <v>46139.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>77</v>
+      </c>
+      <c r="F366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="2">
+        <v>46139.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>78</v>
+      </c>
+      <c r="F367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="2">
+        <v>46139.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>79</v>
+      </c>
+      <c r="F368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" s="2">
+        <v>46139.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>80</v>
+      </c>
+      <c r="F369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" s="2">
+        <v>46139.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>81</v>
+      </c>
+      <c r="F370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" s="2">
+        <v>46139.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>82</v>
+      </c>
+      <c r="F371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="2">
+        <v>46139.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>83</v>
+      </c>
+      <c r="F372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="2">
+        <v>46139.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>84</v>
+      </c>
+      <c r="F373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="2">
+        <v>46139.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>85</v>
+      </c>
+      <c r="F374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" s="2">
+        <v>46139.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>86</v>
+      </c>
+      <c r="F375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="2">
+        <v>46139.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>87</v>
+      </c>
+      <c r="F376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" s="2">
+        <v>46139.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>88</v>
+      </c>
+      <c r="F377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" s="2">
+        <v>46139.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>89</v>
+      </c>
+      <c r="F378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" s="2">
+        <v>46139.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>90</v>
+      </c>
+      <c r="F379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" s="2">
+        <v>46139.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>91</v>
+      </c>
+      <c r="F380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" s="2">
+        <v>46139.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>92</v>
+      </c>
+      <c r="F381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" s="2">
+        <v>46139.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>93</v>
+      </c>
+      <c r="F382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" s="2">
+        <v>46139.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>94</v>
+      </c>
+      <c r="F383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" s="2">
+        <v>46139.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>95</v>
+      </c>
+      <c r="F384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" s="2">
+        <v>46139.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>96</v>
+      </c>
+      <c r="F385" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,1156 +34,868 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>24.04.20261</t>
-  </si>
-  <si>
-    <t>24.04.20262</t>
-  </si>
-  <si>
-    <t>24.04.20263</t>
-  </si>
-  <si>
-    <t>24.04.20264</t>
-  </si>
-  <si>
-    <t>24.04.20265</t>
-  </si>
-  <si>
-    <t>24.04.20266</t>
-  </si>
-  <si>
-    <t>24.04.20267</t>
-  </si>
-  <si>
-    <t>24.04.20268</t>
-  </si>
-  <si>
-    <t>24.04.20269</t>
-  </si>
-  <si>
-    <t>24.04.202610</t>
-  </si>
-  <si>
-    <t>24.04.202611</t>
-  </si>
-  <si>
-    <t>24.04.202612</t>
-  </si>
-  <si>
-    <t>24.04.202613</t>
-  </si>
-  <si>
-    <t>24.04.202614</t>
-  </si>
-  <si>
-    <t>24.04.202615</t>
-  </si>
-  <si>
-    <t>24.04.202616</t>
-  </si>
-  <si>
-    <t>24.04.202617</t>
-  </si>
-  <si>
-    <t>24.04.202618</t>
-  </si>
-  <si>
-    <t>24.04.202619</t>
-  </si>
-  <si>
-    <t>24.04.202620</t>
-  </si>
-  <si>
-    <t>24.04.202621</t>
-  </si>
-  <si>
-    <t>24.04.202622</t>
-  </si>
-  <si>
-    <t>24.04.202623</t>
-  </si>
-  <si>
-    <t>24.04.202624</t>
-  </si>
-  <si>
-    <t>24.04.202625</t>
-  </si>
-  <si>
-    <t>24.04.202626</t>
-  </si>
-  <si>
-    <t>24.04.202627</t>
-  </si>
-  <si>
-    <t>24.04.202628</t>
-  </si>
-  <si>
-    <t>24.04.202629</t>
-  </si>
-  <si>
-    <t>24.04.202630</t>
-  </si>
-  <si>
-    <t>24.04.202631</t>
-  </si>
-  <si>
-    <t>24.04.202632</t>
-  </si>
-  <si>
-    <t>24.04.202633</t>
-  </si>
-  <si>
-    <t>24.04.202634</t>
-  </si>
-  <si>
-    <t>24.04.202635</t>
-  </si>
-  <si>
-    <t>24.04.202636</t>
-  </si>
-  <si>
-    <t>24.04.202637</t>
-  </si>
-  <si>
-    <t>24.04.202638</t>
-  </si>
-  <si>
-    <t>24.04.202639</t>
-  </si>
-  <si>
-    <t>24.04.202640</t>
-  </si>
-  <si>
-    <t>24.04.202641</t>
-  </si>
-  <si>
-    <t>24.04.202642</t>
-  </si>
-  <si>
-    <t>24.04.202643</t>
-  </si>
-  <si>
-    <t>24.04.202644</t>
-  </si>
-  <si>
-    <t>24.04.202645</t>
-  </si>
-  <si>
-    <t>24.04.202646</t>
-  </si>
-  <si>
-    <t>24.04.202647</t>
-  </si>
-  <si>
-    <t>24.04.202648</t>
-  </si>
-  <si>
-    <t>24.04.202649</t>
-  </si>
-  <si>
-    <t>24.04.202650</t>
-  </si>
-  <si>
-    <t>24.04.202651</t>
-  </si>
-  <si>
-    <t>24.04.202652</t>
-  </si>
-  <si>
-    <t>24.04.202653</t>
-  </si>
-  <si>
-    <t>24.04.202654</t>
-  </si>
-  <si>
-    <t>24.04.202655</t>
-  </si>
-  <si>
-    <t>24.04.202656</t>
-  </si>
-  <si>
-    <t>24.04.202657</t>
-  </si>
-  <si>
-    <t>24.04.202658</t>
-  </si>
-  <si>
-    <t>24.04.202659</t>
-  </si>
-  <si>
-    <t>24.04.202660</t>
-  </si>
-  <si>
-    <t>24.04.202661</t>
-  </si>
-  <si>
-    <t>24.04.202662</t>
-  </si>
-  <si>
-    <t>24.04.202663</t>
-  </si>
-  <si>
-    <t>24.04.202664</t>
-  </si>
-  <si>
-    <t>24.04.202665</t>
-  </si>
-  <si>
-    <t>24.04.202666</t>
-  </si>
-  <si>
-    <t>24.04.202667</t>
-  </si>
-  <si>
-    <t>24.04.202668</t>
-  </si>
-  <si>
-    <t>24.04.202669</t>
-  </si>
-  <si>
-    <t>24.04.202670</t>
-  </si>
-  <si>
-    <t>24.04.202671</t>
-  </si>
-  <si>
-    <t>24.04.202672</t>
-  </si>
-  <si>
-    <t>24.04.202673</t>
-  </si>
-  <si>
-    <t>24.04.202674</t>
-  </si>
-  <si>
-    <t>24.04.202675</t>
-  </si>
-  <si>
-    <t>24.04.202676</t>
-  </si>
-  <si>
-    <t>24.04.202677</t>
-  </si>
-  <si>
-    <t>24.04.202678</t>
-  </si>
-  <si>
-    <t>24.04.202679</t>
-  </si>
-  <si>
-    <t>24.04.202680</t>
-  </si>
-  <si>
-    <t>24.04.202681</t>
-  </si>
-  <si>
-    <t>24.04.202682</t>
-  </si>
-  <si>
-    <t>24.04.202683</t>
-  </si>
-  <si>
-    <t>24.04.202684</t>
-  </si>
-  <si>
-    <t>24.04.202685</t>
-  </si>
-  <si>
-    <t>24.04.202686</t>
-  </si>
-  <si>
-    <t>24.04.202687</t>
-  </si>
-  <si>
-    <t>24.04.202688</t>
-  </si>
-  <si>
-    <t>24.04.202689</t>
-  </si>
-  <si>
-    <t>24.04.202690</t>
-  </si>
-  <si>
-    <t>24.04.202691</t>
-  </si>
-  <si>
-    <t>24.04.202692</t>
-  </si>
-  <si>
-    <t>24.04.202693</t>
-  </si>
-  <si>
-    <t>24.04.202694</t>
-  </si>
-  <si>
-    <t>24.04.202695</t>
-  </si>
-  <si>
-    <t>24.04.202696</t>
-  </si>
-  <si>
-    <t>25.04.20261</t>
-  </si>
-  <si>
-    <t>25.04.20262</t>
-  </si>
-  <si>
-    <t>25.04.20263</t>
-  </si>
-  <si>
-    <t>25.04.20264</t>
-  </si>
-  <si>
-    <t>25.04.20265</t>
-  </si>
-  <si>
-    <t>25.04.20266</t>
-  </si>
-  <si>
-    <t>25.04.20267</t>
-  </si>
-  <si>
-    <t>25.04.20268</t>
-  </si>
-  <si>
-    <t>25.04.20269</t>
-  </si>
-  <si>
-    <t>25.04.202610</t>
-  </si>
-  <si>
-    <t>25.04.202611</t>
-  </si>
-  <si>
-    <t>25.04.202612</t>
-  </si>
-  <si>
-    <t>25.04.202613</t>
-  </si>
-  <si>
-    <t>25.04.202614</t>
-  </si>
-  <si>
-    <t>25.04.202615</t>
-  </si>
-  <si>
-    <t>25.04.202616</t>
-  </si>
-  <si>
-    <t>25.04.202617</t>
-  </si>
-  <si>
-    <t>25.04.202618</t>
-  </si>
-  <si>
-    <t>25.04.202619</t>
-  </si>
-  <si>
-    <t>25.04.202620</t>
-  </si>
-  <si>
-    <t>25.04.202621</t>
-  </si>
-  <si>
-    <t>25.04.202622</t>
-  </si>
-  <si>
-    <t>25.04.202623</t>
-  </si>
-  <si>
-    <t>25.04.202624</t>
-  </si>
-  <si>
-    <t>25.04.202625</t>
-  </si>
-  <si>
-    <t>25.04.202626</t>
-  </si>
-  <si>
-    <t>25.04.202627</t>
-  </si>
-  <si>
-    <t>25.04.202628</t>
-  </si>
-  <si>
-    <t>25.04.202629</t>
-  </si>
-  <si>
-    <t>25.04.202630</t>
-  </si>
-  <si>
-    <t>25.04.202631</t>
-  </si>
-  <si>
-    <t>25.04.202632</t>
-  </si>
-  <si>
-    <t>25.04.202633</t>
-  </si>
-  <si>
-    <t>25.04.202634</t>
-  </si>
-  <si>
-    <t>25.04.202635</t>
-  </si>
-  <si>
-    <t>25.04.202636</t>
-  </si>
-  <si>
-    <t>25.04.202637</t>
-  </si>
-  <si>
-    <t>25.04.202638</t>
-  </si>
-  <si>
-    <t>25.04.202639</t>
-  </si>
-  <si>
-    <t>25.04.202640</t>
-  </si>
-  <si>
-    <t>25.04.202641</t>
-  </si>
-  <si>
-    <t>25.04.202642</t>
-  </si>
-  <si>
-    <t>25.04.202643</t>
-  </si>
-  <si>
-    <t>25.04.202644</t>
-  </si>
-  <si>
-    <t>25.04.202645</t>
-  </si>
-  <si>
-    <t>25.04.202646</t>
-  </si>
-  <si>
-    <t>25.04.202647</t>
-  </si>
-  <si>
-    <t>25.04.202648</t>
-  </si>
-  <si>
-    <t>25.04.202649</t>
-  </si>
-  <si>
-    <t>25.04.202650</t>
-  </si>
-  <si>
-    <t>25.04.202651</t>
-  </si>
-  <si>
-    <t>25.04.202652</t>
-  </si>
-  <si>
-    <t>25.04.202653</t>
-  </si>
-  <si>
-    <t>25.04.202654</t>
-  </si>
-  <si>
-    <t>25.04.202655</t>
-  </si>
-  <si>
-    <t>25.04.202656</t>
-  </si>
-  <si>
-    <t>25.04.202657</t>
-  </si>
-  <si>
-    <t>25.04.202658</t>
-  </si>
-  <si>
-    <t>25.04.202659</t>
-  </si>
-  <si>
-    <t>25.04.202660</t>
-  </si>
-  <si>
-    <t>25.04.202661</t>
-  </si>
-  <si>
-    <t>25.04.202662</t>
-  </si>
-  <si>
-    <t>25.04.202663</t>
-  </si>
-  <si>
-    <t>25.04.202664</t>
-  </si>
-  <si>
-    <t>25.04.202665</t>
-  </si>
-  <si>
-    <t>25.04.202666</t>
-  </si>
-  <si>
-    <t>25.04.202667</t>
-  </si>
-  <si>
-    <t>25.04.202668</t>
-  </si>
-  <si>
-    <t>25.04.202669</t>
-  </si>
-  <si>
-    <t>25.04.202670</t>
-  </si>
-  <si>
-    <t>25.04.202671</t>
-  </si>
-  <si>
-    <t>25.04.202672</t>
-  </si>
-  <si>
-    <t>25.04.202673</t>
-  </si>
-  <si>
-    <t>25.04.202674</t>
-  </si>
-  <si>
-    <t>25.04.202675</t>
-  </si>
-  <si>
-    <t>25.04.202676</t>
-  </si>
-  <si>
-    <t>25.04.202677</t>
-  </si>
-  <si>
-    <t>25.04.202678</t>
-  </si>
-  <si>
-    <t>25.04.202679</t>
-  </si>
-  <si>
-    <t>25.04.202680</t>
-  </si>
-  <si>
-    <t>25.04.202681</t>
-  </si>
-  <si>
-    <t>25.04.202682</t>
-  </si>
-  <si>
-    <t>25.04.202683</t>
-  </si>
-  <si>
-    <t>25.04.202684</t>
-  </si>
-  <si>
-    <t>25.04.202685</t>
-  </si>
-  <si>
-    <t>25.04.202686</t>
-  </si>
-  <si>
-    <t>25.04.202687</t>
-  </si>
-  <si>
-    <t>25.04.202688</t>
-  </si>
-  <si>
-    <t>25.04.202689</t>
-  </si>
-  <si>
-    <t>25.04.202690</t>
-  </si>
-  <si>
-    <t>25.04.202691</t>
-  </si>
-  <si>
-    <t>25.04.202692</t>
-  </si>
-  <si>
-    <t>25.04.202693</t>
-  </si>
-  <si>
-    <t>25.04.202694</t>
-  </si>
-  <si>
-    <t>25.04.202695</t>
-  </si>
-  <si>
-    <t>25.04.202696</t>
-  </si>
-  <si>
-    <t>26.04.20261</t>
-  </si>
-  <si>
-    <t>26.04.20262</t>
-  </si>
-  <si>
-    <t>26.04.20263</t>
-  </si>
-  <si>
-    <t>26.04.20264</t>
-  </si>
-  <si>
-    <t>26.04.20265</t>
-  </si>
-  <si>
-    <t>26.04.20266</t>
-  </si>
-  <si>
-    <t>26.04.20267</t>
-  </si>
-  <si>
-    <t>26.04.20268</t>
-  </si>
-  <si>
-    <t>26.04.20269</t>
-  </si>
-  <si>
-    <t>26.04.202610</t>
-  </si>
-  <si>
-    <t>26.04.202611</t>
-  </si>
-  <si>
-    <t>26.04.202612</t>
-  </si>
-  <si>
-    <t>26.04.202613</t>
-  </si>
-  <si>
-    <t>26.04.202614</t>
-  </si>
-  <si>
-    <t>26.04.202615</t>
-  </si>
-  <si>
-    <t>26.04.202616</t>
-  </si>
-  <si>
-    <t>26.04.202617</t>
-  </si>
-  <si>
-    <t>26.04.202618</t>
-  </si>
-  <si>
-    <t>26.04.202619</t>
-  </si>
-  <si>
-    <t>26.04.202620</t>
-  </si>
-  <si>
-    <t>26.04.202621</t>
-  </si>
-  <si>
-    <t>26.04.202622</t>
-  </si>
-  <si>
-    <t>26.04.202623</t>
-  </si>
-  <si>
-    <t>26.04.202624</t>
-  </si>
-  <si>
-    <t>26.04.202625</t>
-  </si>
-  <si>
-    <t>26.04.202626</t>
-  </si>
-  <si>
-    <t>26.04.202627</t>
-  </si>
-  <si>
-    <t>26.04.202628</t>
-  </si>
-  <si>
-    <t>26.04.202629</t>
-  </si>
-  <si>
-    <t>26.04.202630</t>
-  </si>
-  <si>
-    <t>26.04.202631</t>
-  </si>
-  <si>
-    <t>26.04.202632</t>
-  </si>
-  <si>
-    <t>26.04.202633</t>
-  </si>
-  <si>
-    <t>26.04.202634</t>
-  </si>
-  <si>
-    <t>26.04.202635</t>
-  </si>
-  <si>
-    <t>26.04.202636</t>
-  </si>
-  <si>
-    <t>26.04.202637</t>
-  </si>
-  <si>
-    <t>26.04.202638</t>
-  </si>
-  <si>
-    <t>26.04.202639</t>
-  </si>
-  <si>
-    <t>26.04.202640</t>
-  </si>
-  <si>
-    <t>26.04.202641</t>
-  </si>
-  <si>
-    <t>26.04.202642</t>
-  </si>
-  <si>
-    <t>26.04.202643</t>
-  </si>
-  <si>
-    <t>26.04.202644</t>
-  </si>
-  <si>
-    <t>26.04.202645</t>
-  </si>
-  <si>
-    <t>26.04.202646</t>
-  </si>
-  <si>
-    <t>26.04.202647</t>
-  </si>
-  <si>
-    <t>26.04.202648</t>
-  </si>
-  <si>
-    <t>26.04.202649</t>
-  </si>
-  <si>
-    <t>26.04.202650</t>
-  </si>
-  <si>
-    <t>26.04.202651</t>
-  </si>
-  <si>
-    <t>26.04.202652</t>
-  </si>
-  <si>
-    <t>26.04.202653</t>
-  </si>
-  <si>
-    <t>26.04.202654</t>
-  </si>
-  <si>
-    <t>26.04.202655</t>
-  </si>
-  <si>
-    <t>26.04.202656</t>
-  </si>
-  <si>
-    <t>26.04.202657</t>
-  </si>
-  <si>
-    <t>26.04.202658</t>
-  </si>
-  <si>
-    <t>26.04.202659</t>
-  </si>
-  <si>
-    <t>26.04.202660</t>
-  </si>
-  <si>
-    <t>26.04.202661</t>
-  </si>
-  <si>
-    <t>26.04.202662</t>
-  </si>
-  <si>
-    <t>26.04.202663</t>
-  </si>
-  <si>
-    <t>26.04.202664</t>
-  </si>
-  <si>
-    <t>26.04.202665</t>
-  </si>
-  <si>
-    <t>26.04.202666</t>
-  </si>
-  <si>
-    <t>26.04.202667</t>
-  </si>
-  <si>
-    <t>26.04.202668</t>
-  </si>
-  <si>
-    <t>26.04.202669</t>
-  </si>
-  <si>
-    <t>26.04.202670</t>
-  </si>
-  <si>
-    <t>26.04.202671</t>
-  </si>
-  <si>
-    <t>26.04.202672</t>
-  </si>
-  <si>
-    <t>26.04.202673</t>
-  </si>
-  <si>
-    <t>26.04.202674</t>
-  </si>
-  <si>
-    <t>26.04.202675</t>
-  </si>
-  <si>
-    <t>26.04.202676</t>
-  </si>
-  <si>
-    <t>26.04.202677</t>
-  </si>
-  <si>
-    <t>26.04.202678</t>
-  </si>
-  <si>
-    <t>26.04.202679</t>
-  </si>
-  <si>
-    <t>26.04.202680</t>
-  </si>
-  <si>
-    <t>26.04.202681</t>
-  </si>
-  <si>
-    <t>26.04.202682</t>
-  </si>
-  <si>
-    <t>26.04.202683</t>
-  </si>
-  <si>
-    <t>26.04.202684</t>
-  </si>
-  <si>
-    <t>26.04.202685</t>
-  </si>
-  <si>
-    <t>26.04.202686</t>
-  </si>
-  <si>
-    <t>26.04.202687</t>
-  </si>
-  <si>
-    <t>26.04.202688</t>
-  </si>
-  <si>
-    <t>26.04.202689</t>
-  </si>
-  <si>
-    <t>26.04.202690</t>
-  </si>
-  <si>
-    <t>26.04.202691</t>
-  </si>
-  <si>
-    <t>26.04.202692</t>
-  </si>
-  <si>
-    <t>26.04.202693</t>
-  </si>
-  <si>
-    <t>26.04.202694</t>
-  </si>
-  <si>
-    <t>26.04.202695</t>
-  </si>
-  <si>
-    <t>26.04.202696</t>
-  </si>
-  <si>
-    <t>27.04.20261</t>
-  </si>
-  <si>
-    <t>27.04.20262</t>
-  </si>
-  <si>
-    <t>27.04.20263</t>
-  </si>
-  <si>
-    <t>27.04.20264</t>
-  </si>
-  <si>
-    <t>27.04.20265</t>
-  </si>
-  <si>
-    <t>27.04.20266</t>
-  </si>
-  <si>
-    <t>27.04.20267</t>
-  </si>
-  <si>
-    <t>27.04.20268</t>
-  </si>
-  <si>
-    <t>27.04.20269</t>
-  </si>
-  <si>
-    <t>27.04.202610</t>
-  </si>
-  <si>
-    <t>27.04.202611</t>
-  </si>
-  <si>
-    <t>27.04.202612</t>
-  </si>
-  <si>
-    <t>27.04.202613</t>
-  </si>
-  <si>
-    <t>27.04.202614</t>
-  </si>
-  <si>
-    <t>27.04.202615</t>
-  </si>
-  <si>
-    <t>27.04.202616</t>
-  </si>
-  <si>
-    <t>27.04.202617</t>
-  </si>
-  <si>
-    <t>27.04.202618</t>
-  </si>
-  <si>
-    <t>27.04.202619</t>
-  </si>
-  <si>
-    <t>27.04.202620</t>
-  </si>
-  <si>
-    <t>27.04.202621</t>
-  </si>
-  <si>
-    <t>27.04.202622</t>
-  </si>
-  <si>
-    <t>27.04.202623</t>
-  </si>
-  <si>
-    <t>27.04.202624</t>
-  </si>
-  <si>
-    <t>27.04.202625</t>
-  </si>
-  <si>
-    <t>27.04.202626</t>
-  </si>
-  <si>
-    <t>27.04.202627</t>
-  </si>
-  <si>
-    <t>27.04.202628</t>
-  </si>
-  <si>
-    <t>27.04.202629</t>
-  </si>
-  <si>
-    <t>27.04.202630</t>
-  </si>
-  <si>
-    <t>27.04.202631</t>
-  </si>
-  <si>
-    <t>27.04.202632</t>
-  </si>
-  <si>
-    <t>27.04.202633</t>
-  </si>
-  <si>
-    <t>27.04.202634</t>
-  </si>
-  <si>
-    <t>27.04.202635</t>
-  </si>
-  <si>
-    <t>27.04.202636</t>
-  </si>
-  <si>
-    <t>27.04.202637</t>
-  </si>
-  <si>
-    <t>27.04.202638</t>
-  </si>
-  <si>
-    <t>27.04.202639</t>
-  </si>
-  <si>
-    <t>27.04.202640</t>
-  </si>
-  <si>
-    <t>27.04.202641</t>
-  </si>
-  <si>
-    <t>27.04.202642</t>
-  </si>
-  <si>
-    <t>27.04.202643</t>
-  </si>
-  <si>
-    <t>27.04.202644</t>
-  </si>
-  <si>
-    <t>27.04.202645</t>
-  </si>
-  <si>
-    <t>27.04.202646</t>
-  </si>
-  <si>
-    <t>27.04.202647</t>
-  </si>
-  <si>
-    <t>27.04.202648</t>
-  </si>
-  <si>
-    <t>27.04.202649</t>
-  </si>
-  <si>
-    <t>27.04.202650</t>
-  </si>
-  <si>
-    <t>27.04.202651</t>
-  </si>
-  <si>
-    <t>27.04.202652</t>
-  </si>
-  <si>
-    <t>27.04.202653</t>
-  </si>
-  <si>
-    <t>27.04.202654</t>
-  </si>
-  <si>
-    <t>27.04.202655</t>
-  </si>
-  <si>
-    <t>27.04.202656</t>
-  </si>
-  <si>
-    <t>27.04.202657</t>
-  </si>
-  <si>
-    <t>27.04.202658</t>
-  </si>
-  <si>
-    <t>27.04.202659</t>
-  </si>
-  <si>
-    <t>27.04.202660</t>
-  </si>
-  <si>
-    <t>27.04.202661</t>
-  </si>
-  <si>
-    <t>27.04.202662</t>
-  </si>
-  <si>
-    <t>27.04.202663</t>
-  </si>
-  <si>
-    <t>27.04.202664</t>
-  </si>
-  <si>
-    <t>27.04.202665</t>
-  </si>
-  <si>
-    <t>27.04.202666</t>
-  </si>
-  <si>
-    <t>27.04.202667</t>
-  </si>
-  <si>
-    <t>27.04.202668</t>
-  </si>
-  <si>
-    <t>27.04.202669</t>
-  </si>
-  <si>
-    <t>27.04.202670</t>
-  </si>
-  <si>
-    <t>27.04.202671</t>
-  </si>
-  <si>
-    <t>27.04.202672</t>
-  </si>
-  <si>
-    <t>27.04.202673</t>
-  </si>
-  <si>
-    <t>27.04.202674</t>
-  </si>
-  <si>
-    <t>27.04.202675</t>
-  </si>
-  <si>
-    <t>27.04.202676</t>
-  </si>
-  <si>
-    <t>27.04.202677</t>
-  </si>
-  <si>
-    <t>27.04.202678</t>
-  </si>
-  <si>
-    <t>27.04.202679</t>
-  </si>
-  <si>
-    <t>27.04.202680</t>
-  </si>
-  <si>
-    <t>27.04.202681</t>
-  </si>
-  <si>
-    <t>27.04.202682</t>
-  </si>
-  <si>
-    <t>27.04.202683</t>
-  </si>
-  <si>
-    <t>27.04.202684</t>
-  </si>
-  <si>
-    <t>27.04.202685</t>
-  </si>
-  <si>
-    <t>27.04.202686</t>
-  </si>
-  <si>
-    <t>27.04.202687</t>
-  </si>
-  <si>
-    <t>27.04.202688</t>
-  </si>
-  <si>
-    <t>27.04.202689</t>
-  </si>
-  <si>
-    <t>27.04.202690</t>
-  </si>
-  <si>
-    <t>27.04.202691</t>
-  </si>
-  <si>
-    <t>27.04.202692</t>
-  </si>
-  <si>
-    <t>27.04.202693</t>
-  </si>
-  <si>
-    <t>27.04.202694</t>
-  </si>
-  <si>
-    <t>27.04.202695</t>
-  </si>
-  <si>
-    <t>27.04.202696</t>
+    <t>28.04.20261</t>
+  </si>
+  <si>
+    <t>28.04.20262</t>
+  </si>
+  <si>
+    <t>28.04.20263</t>
+  </si>
+  <si>
+    <t>28.04.20264</t>
+  </si>
+  <si>
+    <t>28.04.20265</t>
+  </si>
+  <si>
+    <t>28.04.20266</t>
+  </si>
+  <si>
+    <t>28.04.20267</t>
+  </si>
+  <si>
+    <t>28.04.20268</t>
+  </si>
+  <si>
+    <t>28.04.20269</t>
+  </si>
+  <si>
+    <t>28.04.202610</t>
+  </si>
+  <si>
+    <t>28.04.202611</t>
+  </si>
+  <si>
+    <t>28.04.202612</t>
+  </si>
+  <si>
+    <t>28.04.202613</t>
+  </si>
+  <si>
+    <t>28.04.202614</t>
+  </si>
+  <si>
+    <t>28.04.202615</t>
+  </si>
+  <si>
+    <t>28.04.202616</t>
+  </si>
+  <si>
+    <t>28.04.202617</t>
+  </si>
+  <si>
+    <t>28.04.202618</t>
+  </si>
+  <si>
+    <t>28.04.202619</t>
+  </si>
+  <si>
+    <t>28.04.202620</t>
+  </si>
+  <si>
+    <t>28.04.202621</t>
+  </si>
+  <si>
+    <t>28.04.202622</t>
+  </si>
+  <si>
+    <t>28.04.202623</t>
+  </si>
+  <si>
+    <t>28.04.202624</t>
+  </si>
+  <si>
+    <t>28.04.202625</t>
+  </si>
+  <si>
+    <t>28.04.202626</t>
+  </si>
+  <si>
+    <t>28.04.202627</t>
+  </si>
+  <si>
+    <t>28.04.202628</t>
+  </si>
+  <si>
+    <t>28.04.202629</t>
+  </si>
+  <si>
+    <t>28.04.202630</t>
+  </si>
+  <si>
+    <t>28.04.202631</t>
+  </si>
+  <si>
+    <t>28.04.202632</t>
+  </si>
+  <si>
+    <t>28.04.202633</t>
+  </si>
+  <si>
+    <t>28.04.202634</t>
+  </si>
+  <si>
+    <t>28.04.202635</t>
+  </si>
+  <si>
+    <t>28.04.202636</t>
+  </si>
+  <si>
+    <t>28.04.202637</t>
+  </si>
+  <si>
+    <t>28.04.202638</t>
+  </si>
+  <si>
+    <t>28.04.202639</t>
+  </si>
+  <si>
+    <t>28.04.202640</t>
+  </si>
+  <si>
+    <t>28.04.202641</t>
+  </si>
+  <si>
+    <t>28.04.202642</t>
+  </si>
+  <si>
+    <t>28.04.202643</t>
+  </si>
+  <si>
+    <t>28.04.202644</t>
+  </si>
+  <si>
+    <t>28.04.202645</t>
+  </si>
+  <si>
+    <t>28.04.202646</t>
+  </si>
+  <si>
+    <t>28.04.202647</t>
+  </si>
+  <si>
+    <t>28.04.202648</t>
+  </si>
+  <si>
+    <t>28.04.202649</t>
+  </si>
+  <si>
+    <t>28.04.202650</t>
+  </si>
+  <si>
+    <t>28.04.202651</t>
+  </si>
+  <si>
+    <t>28.04.202652</t>
+  </si>
+  <si>
+    <t>28.04.202653</t>
+  </si>
+  <si>
+    <t>28.04.202654</t>
+  </si>
+  <si>
+    <t>28.04.202655</t>
+  </si>
+  <si>
+    <t>28.04.202656</t>
+  </si>
+  <si>
+    <t>28.04.202657</t>
+  </si>
+  <si>
+    <t>28.04.202658</t>
+  </si>
+  <si>
+    <t>28.04.202659</t>
+  </si>
+  <si>
+    <t>28.04.202660</t>
+  </si>
+  <si>
+    <t>28.04.202661</t>
+  </si>
+  <si>
+    <t>28.04.202662</t>
+  </si>
+  <si>
+    <t>28.04.202663</t>
+  </si>
+  <si>
+    <t>28.04.202664</t>
+  </si>
+  <si>
+    <t>28.04.202665</t>
+  </si>
+  <si>
+    <t>28.04.202666</t>
+  </si>
+  <si>
+    <t>28.04.202667</t>
+  </si>
+  <si>
+    <t>28.04.202668</t>
+  </si>
+  <si>
+    <t>28.04.202669</t>
+  </si>
+  <si>
+    <t>28.04.202670</t>
+  </si>
+  <si>
+    <t>28.04.202671</t>
+  </si>
+  <si>
+    <t>28.04.202672</t>
+  </si>
+  <si>
+    <t>28.04.202673</t>
+  </si>
+  <si>
+    <t>28.04.202674</t>
+  </si>
+  <si>
+    <t>28.04.202675</t>
+  </si>
+  <si>
+    <t>28.04.202676</t>
+  </si>
+  <si>
+    <t>28.04.202677</t>
+  </si>
+  <si>
+    <t>28.04.202678</t>
+  </si>
+  <si>
+    <t>28.04.202679</t>
+  </si>
+  <si>
+    <t>28.04.202680</t>
+  </si>
+  <si>
+    <t>28.04.202681</t>
+  </si>
+  <si>
+    <t>28.04.202682</t>
+  </si>
+  <si>
+    <t>28.04.202683</t>
+  </si>
+  <si>
+    <t>28.04.202684</t>
+  </si>
+  <si>
+    <t>28.04.202685</t>
+  </si>
+  <si>
+    <t>28.04.202686</t>
+  </si>
+  <si>
+    <t>28.04.202687</t>
+  </si>
+  <si>
+    <t>28.04.202688</t>
+  </si>
+  <si>
+    <t>28.04.202689</t>
+  </si>
+  <si>
+    <t>28.04.202690</t>
+  </si>
+  <si>
+    <t>28.04.202691</t>
+  </si>
+  <si>
+    <t>28.04.202692</t>
+  </si>
+  <si>
+    <t>28.04.202693</t>
+  </si>
+  <si>
+    <t>28.04.202694</t>
+  </si>
+  <si>
+    <t>28.04.202695</t>
+  </si>
+  <si>
+    <t>28.04.202696</t>
+  </si>
+  <si>
+    <t>29.04.20261</t>
+  </si>
+  <si>
+    <t>29.04.20262</t>
+  </si>
+  <si>
+    <t>29.04.20263</t>
+  </si>
+  <si>
+    <t>29.04.20264</t>
+  </si>
+  <si>
+    <t>29.04.20265</t>
+  </si>
+  <si>
+    <t>29.04.20266</t>
+  </si>
+  <si>
+    <t>29.04.20267</t>
+  </si>
+  <si>
+    <t>29.04.20268</t>
+  </si>
+  <si>
+    <t>29.04.20269</t>
+  </si>
+  <si>
+    <t>29.04.202610</t>
+  </si>
+  <si>
+    <t>29.04.202611</t>
+  </si>
+  <si>
+    <t>29.04.202612</t>
+  </si>
+  <si>
+    <t>29.04.202613</t>
+  </si>
+  <si>
+    <t>29.04.202614</t>
+  </si>
+  <si>
+    <t>29.04.202615</t>
+  </si>
+  <si>
+    <t>29.04.202616</t>
+  </si>
+  <si>
+    <t>29.04.202617</t>
+  </si>
+  <si>
+    <t>29.04.202618</t>
+  </si>
+  <si>
+    <t>29.04.202619</t>
+  </si>
+  <si>
+    <t>29.04.202620</t>
+  </si>
+  <si>
+    <t>29.04.202621</t>
+  </si>
+  <si>
+    <t>29.04.202622</t>
+  </si>
+  <si>
+    <t>29.04.202623</t>
+  </si>
+  <si>
+    <t>29.04.202624</t>
+  </si>
+  <si>
+    <t>29.04.202625</t>
+  </si>
+  <si>
+    <t>29.04.202626</t>
+  </si>
+  <si>
+    <t>29.04.202627</t>
+  </si>
+  <si>
+    <t>29.04.202628</t>
+  </si>
+  <si>
+    <t>29.04.202629</t>
+  </si>
+  <si>
+    <t>29.04.202630</t>
+  </si>
+  <si>
+    <t>29.04.202631</t>
+  </si>
+  <si>
+    <t>29.04.202632</t>
+  </si>
+  <si>
+    <t>29.04.202633</t>
+  </si>
+  <si>
+    <t>29.04.202634</t>
+  </si>
+  <si>
+    <t>29.04.202635</t>
+  </si>
+  <si>
+    <t>29.04.202636</t>
+  </si>
+  <si>
+    <t>29.04.202637</t>
+  </si>
+  <si>
+    <t>29.04.202638</t>
+  </si>
+  <si>
+    <t>29.04.202639</t>
+  </si>
+  <si>
+    <t>29.04.202640</t>
+  </si>
+  <si>
+    <t>29.04.202641</t>
+  </si>
+  <si>
+    <t>29.04.202642</t>
+  </si>
+  <si>
+    <t>29.04.202643</t>
+  </si>
+  <si>
+    <t>29.04.202644</t>
+  </si>
+  <si>
+    <t>29.04.202645</t>
+  </si>
+  <si>
+    <t>29.04.202646</t>
+  </si>
+  <si>
+    <t>29.04.202647</t>
+  </si>
+  <si>
+    <t>29.04.202648</t>
+  </si>
+  <si>
+    <t>29.04.202649</t>
+  </si>
+  <si>
+    <t>29.04.202650</t>
+  </si>
+  <si>
+    <t>29.04.202651</t>
+  </si>
+  <si>
+    <t>29.04.202652</t>
+  </si>
+  <si>
+    <t>29.04.202653</t>
+  </si>
+  <si>
+    <t>29.04.202654</t>
+  </si>
+  <si>
+    <t>29.04.202655</t>
+  </si>
+  <si>
+    <t>29.04.202656</t>
+  </si>
+  <si>
+    <t>29.04.202657</t>
+  </si>
+  <si>
+    <t>29.04.202658</t>
+  </si>
+  <si>
+    <t>29.04.202659</t>
+  </si>
+  <si>
+    <t>29.04.202660</t>
+  </si>
+  <si>
+    <t>29.04.202661</t>
+  </si>
+  <si>
+    <t>29.04.202662</t>
+  </si>
+  <si>
+    <t>29.04.202663</t>
+  </si>
+  <si>
+    <t>29.04.202664</t>
+  </si>
+  <si>
+    <t>29.04.202665</t>
+  </si>
+  <si>
+    <t>29.04.202666</t>
+  </si>
+  <si>
+    <t>29.04.202667</t>
+  </si>
+  <si>
+    <t>29.04.202668</t>
+  </si>
+  <si>
+    <t>29.04.202669</t>
+  </si>
+  <si>
+    <t>29.04.202670</t>
+  </si>
+  <si>
+    <t>29.04.202671</t>
+  </si>
+  <si>
+    <t>29.04.202672</t>
+  </si>
+  <si>
+    <t>29.04.202673</t>
+  </si>
+  <si>
+    <t>29.04.202674</t>
+  </si>
+  <si>
+    <t>29.04.202675</t>
+  </si>
+  <si>
+    <t>29.04.202676</t>
+  </si>
+  <si>
+    <t>29.04.202677</t>
+  </si>
+  <si>
+    <t>29.04.202678</t>
+  </si>
+  <si>
+    <t>29.04.202679</t>
+  </si>
+  <si>
+    <t>29.04.202680</t>
+  </si>
+  <si>
+    <t>29.04.202681</t>
+  </si>
+  <si>
+    <t>29.04.202682</t>
+  </si>
+  <si>
+    <t>29.04.202683</t>
+  </si>
+  <si>
+    <t>29.04.202684</t>
+  </si>
+  <si>
+    <t>29.04.202685</t>
+  </si>
+  <si>
+    <t>29.04.202686</t>
+  </si>
+  <si>
+    <t>29.04.202687</t>
+  </si>
+  <si>
+    <t>29.04.202688</t>
+  </si>
+  <si>
+    <t>29.04.202689</t>
+  </si>
+  <si>
+    <t>29.04.202690</t>
+  </si>
+  <si>
+    <t>29.04.202691</t>
+  </si>
+  <si>
+    <t>29.04.202692</t>
+  </si>
+  <si>
+    <t>29.04.202693</t>
+  </si>
+  <si>
+    <t>29.04.202694</t>
+  </si>
+  <si>
+    <t>29.04.202695</t>
+  </si>
+  <si>
+    <t>29.04.202696</t>
+  </si>
+  <si>
+    <t>30.04.20261</t>
+  </si>
+  <si>
+    <t>30.04.20262</t>
+  </si>
+  <si>
+    <t>30.04.20263</t>
+  </si>
+  <si>
+    <t>30.04.20264</t>
+  </si>
+  <si>
+    <t>30.04.20265</t>
+  </si>
+  <si>
+    <t>30.04.20266</t>
+  </si>
+  <si>
+    <t>30.04.20267</t>
+  </si>
+  <si>
+    <t>30.04.20268</t>
+  </si>
+  <si>
+    <t>30.04.20269</t>
+  </si>
+  <si>
+    <t>30.04.202610</t>
+  </si>
+  <si>
+    <t>30.04.202611</t>
+  </si>
+  <si>
+    <t>30.04.202612</t>
+  </si>
+  <si>
+    <t>30.04.202613</t>
+  </si>
+  <si>
+    <t>30.04.202614</t>
+  </si>
+  <si>
+    <t>30.04.202615</t>
+  </si>
+  <si>
+    <t>30.04.202616</t>
+  </si>
+  <si>
+    <t>30.04.202617</t>
+  </si>
+  <si>
+    <t>30.04.202618</t>
+  </si>
+  <si>
+    <t>30.04.202619</t>
+  </si>
+  <si>
+    <t>30.04.202620</t>
+  </si>
+  <si>
+    <t>30.04.202621</t>
+  </si>
+  <si>
+    <t>30.04.202622</t>
+  </si>
+  <si>
+    <t>30.04.202623</t>
+  </si>
+  <si>
+    <t>30.04.202624</t>
+  </si>
+  <si>
+    <t>30.04.202625</t>
+  </si>
+  <si>
+    <t>30.04.202626</t>
+  </si>
+  <si>
+    <t>30.04.202627</t>
+  </si>
+  <si>
+    <t>30.04.202628</t>
+  </si>
+  <si>
+    <t>30.04.202629</t>
+  </si>
+  <si>
+    <t>30.04.202630</t>
+  </si>
+  <si>
+    <t>30.04.202631</t>
+  </si>
+  <si>
+    <t>30.04.202632</t>
+  </si>
+  <si>
+    <t>30.04.202633</t>
+  </si>
+  <si>
+    <t>30.04.202634</t>
+  </si>
+  <si>
+    <t>30.04.202635</t>
+  </si>
+  <si>
+    <t>30.04.202636</t>
+  </si>
+  <si>
+    <t>30.04.202637</t>
+  </si>
+  <si>
+    <t>30.04.202638</t>
+  </si>
+  <si>
+    <t>30.04.202639</t>
+  </si>
+  <si>
+    <t>30.04.202640</t>
+  </si>
+  <si>
+    <t>30.04.202641</t>
+  </si>
+  <si>
+    <t>30.04.202642</t>
+  </si>
+  <si>
+    <t>30.04.202643</t>
+  </si>
+  <si>
+    <t>30.04.202644</t>
+  </si>
+  <si>
+    <t>30.04.202645</t>
+  </si>
+  <si>
+    <t>30.04.202646</t>
+  </si>
+  <si>
+    <t>30.04.202647</t>
+  </si>
+  <si>
+    <t>30.04.202648</t>
+  </si>
+  <si>
+    <t>30.04.202649</t>
+  </si>
+  <si>
+    <t>30.04.202650</t>
+  </si>
+  <si>
+    <t>30.04.202651</t>
+  </si>
+  <si>
+    <t>30.04.202652</t>
+  </si>
+  <si>
+    <t>30.04.202653</t>
+  </si>
+  <si>
+    <t>30.04.202654</t>
+  </si>
+  <si>
+    <t>30.04.202655</t>
+  </si>
+  <si>
+    <t>30.04.202656</t>
+  </si>
+  <si>
+    <t>30.04.202657</t>
+  </si>
+  <si>
+    <t>30.04.202658</t>
+  </si>
+  <si>
+    <t>30.04.202659</t>
+  </si>
+  <si>
+    <t>30.04.202660</t>
+  </si>
+  <si>
+    <t>30.04.202661</t>
+  </si>
+  <si>
+    <t>30.04.202662</t>
+  </si>
+  <si>
+    <t>30.04.202663</t>
+  </si>
+  <si>
+    <t>30.04.202664</t>
+  </si>
+  <si>
+    <t>30.04.202665</t>
+  </si>
+  <si>
+    <t>30.04.202666</t>
+  </si>
+  <si>
+    <t>30.04.202667</t>
+  </si>
+  <si>
+    <t>30.04.202668</t>
+  </si>
+  <si>
+    <t>30.04.202669</t>
+  </si>
+  <si>
+    <t>30.04.202670</t>
+  </si>
+  <si>
+    <t>30.04.202671</t>
+  </si>
+  <si>
+    <t>30.04.202672</t>
+  </si>
+  <si>
+    <t>30.04.202673</t>
+  </si>
+  <si>
+    <t>30.04.202674</t>
+  </si>
+  <si>
+    <t>30.04.202675</t>
+  </si>
+  <si>
+    <t>30.04.202676</t>
+  </si>
+  <si>
+    <t>30.04.202677</t>
+  </si>
+  <si>
+    <t>30.04.202678</t>
+  </si>
+  <si>
+    <t>30.04.202679</t>
+  </si>
+  <si>
+    <t>30.04.202680</t>
+  </si>
+  <si>
+    <t>30.04.202681</t>
+  </si>
+  <si>
+    <t>30.04.202682</t>
+  </si>
+  <si>
+    <t>30.04.202683</t>
+  </si>
+  <si>
+    <t>30.04.202684</t>
+  </si>
+  <si>
+    <t>30.04.202685</t>
+  </si>
+  <si>
+    <t>30.04.202686</t>
+  </si>
+  <si>
+    <t>30.04.202687</t>
+  </si>
+  <si>
+    <t>30.04.202688</t>
+  </si>
+  <si>
+    <t>30.04.202689</t>
+  </si>
+  <si>
+    <t>30.04.202690</t>
+  </si>
+  <si>
+    <t>30.04.202691</t>
+  </si>
+  <si>
+    <t>30.04.202692</t>
+  </si>
+  <si>
+    <t>30.04.202693</t>
+  </si>
+  <si>
+    <t>30.04.202694</t>
+  </si>
+  <si>
+    <t>30.04.202695</t>
+  </si>
+  <si>
+    <t>30.04.202696</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F385"/>
+  <dimension ref="A1:F289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1570,7 +1282,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1590,7 +1302,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46136.01041666666</v>
+        <v>46140.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1610,7 +1322,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46136.02083333334</v>
+        <v>46140.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1630,7 +1342,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46136.03125</v>
+        <v>46140.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1650,16 +1362,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46136.04166666666</v>
+        <v>46140.04166666666</v>
       </c>
       <c r="B6">
-        <v>-48.335</v>
+        <v>31.963</v>
       </c>
       <c r="C6">
-        <v>1004.554</v>
+        <v>6.706</v>
       </c>
       <c r="D6">
-        <v>1004.554</v>
+        <v>6.706</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1670,16 +1382,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46136.05208333334</v>
+        <v>46140.05208333334</v>
       </c>
       <c r="B7">
-        <v>-59.162</v>
+        <v>21.232</v>
       </c>
       <c r="C7">
-        <v>1004.268</v>
+        <v>1.1</v>
       </c>
       <c r="D7">
-        <v>1004.268</v>
+        <v>1.1</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1690,16 +1402,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46136.0625</v>
+        <v>46140.0625</v>
       </c>
       <c r="B8">
-        <v>-34.045</v>
+        <v>40.771</v>
       </c>
       <c r="C8">
-        <v>1004.62</v>
+        <v>27.601</v>
       </c>
       <c r="D8">
-        <v>1004.62</v>
+        <v>27.601</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1710,16 +1422,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46136.07291666666</v>
+        <v>46140.07291666666</v>
       </c>
       <c r="B9">
-        <v>-27.856</v>
+        <v>22.973</v>
       </c>
       <c r="C9">
-        <v>972.223</v>
+        <v>252.963</v>
       </c>
       <c r="D9">
-        <v>972.223</v>
+        <v>252.963</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1730,16 +1442,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46136.08333333334</v>
+        <v>46140.08333333334</v>
       </c>
       <c r="B10">
-        <v>-23.053</v>
+        <v>63.593</v>
       </c>
       <c r="C10">
-        <v>991.057</v>
+        <v>-430.993</v>
       </c>
       <c r="D10">
-        <v>991.057</v>
+        <v>-430.993</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1750,16 +1462,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46136.09375</v>
+        <v>46140.09375</v>
       </c>
       <c r="B11">
-        <v>-23.578</v>
+        <v>55.56</v>
       </c>
       <c r="C11">
-        <v>992.066</v>
+        <v>155.118</v>
       </c>
       <c r="D11">
-        <v>992.066</v>
+        <v>155.118</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1770,16 +1482,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46136.10416666666</v>
+        <v>46140.10416666666</v>
       </c>
       <c r="B12">
-        <v>-30.105</v>
+        <v>32.746</v>
       </c>
       <c r="C12">
-        <v>988.966</v>
+        <v>207.759</v>
       </c>
       <c r="D12">
-        <v>988.966</v>
+        <v>207.759</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1790,16 +1502,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46136.11458333334</v>
+        <v>46140.11458333334</v>
       </c>
       <c r="B13">
-        <v>-13.873</v>
+        <v>32.342</v>
       </c>
       <c r="C13">
-        <v>941.349</v>
+        <v>150.115</v>
       </c>
       <c r="D13">
-        <v>941.349</v>
+        <v>150.115</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1810,16 +1522,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46136.125</v>
+        <v>46140.125</v>
       </c>
       <c r="B14">
-        <v>10.259</v>
+        <v>1.05</v>
       </c>
       <c r="C14">
-        <v>293.712</v>
+        <v>247.449</v>
       </c>
       <c r="D14">
-        <v>293.712</v>
+        <v>247.449</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1830,16 +1542,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46136.13541666666</v>
+        <v>46140.13541666666</v>
       </c>
       <c r="B15">
-        <v>-16.294</v>
+        <v>15.368</v>
       </c>
       <c r="C15">
-        <v>840.021</v>
+        <v>251.681</v>
       </c>
       <c r="D15">
-        <v>840.021</v>
+        <v>251.681</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1850,16 +1562,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46136.14583333334</v>
+        <v>46140.14583333334</v>
       </c>
       <c r="B16">
-        <v>-14.933</v>
+        <v>-25.83</v>
       </c>
       <c r="C16">
-        <v>911.385</v>
+        <v>925.033</v>
       </c>
       <c r="D16">
-        <v>911.385</v>
+        <v>925.033</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1870,16 +1582,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46136.15625</v>
+        <v>46140.15625</v>
       </c>
       <c r="B17">
-        <v>-22.664</v>
+        <v>-43.618</v>
       </c>
       <c r="C17">
-        <v>899.164</v>
+        <v>925.992</v>
       </c>
       <c r="D17">
-        <v>899.164</v>
+        <v>925.992</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1890,16 +1602,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46136.16666666666</v>
+        <v>46140.16666666666</v>
       </c>
       <c r="B18">
-        <v>-0.659</v>
+        <v>9.167999999999999</v>
       </c>
       <c r="C18">
-        <v>1451.844</v>
+        <v>252.764</v>
       </c>
       <c r="D18">
-        <v>1451.844</v>
+        <v>252.764</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1910,16 +1622,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46136.17708333334</v>
+        <v>46140.17708333334</v>
       </c>
       <c r="B19">
-        <v>4.409</v>
+        <v>1.328</v>
       </c>
       <c r="C19">
-        <v>265.186</v>
+        <v>337.051</v>
       </c>
       <c r="D19">
-        <v>265.186</v>
+        <v>337.051</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1930,16 +1642,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46136.1875</v>
+        <v>46140.1875</v>
       </c>
       <c r="B20">
-        <v>-4.539</v>
+        <v>-25.095</v>
       </c>
       <c r="C20">
-        <v>897.6319999999999</v>
+        <v>919.258</v>
       </c>
       <c r="D20">
-        <v>897.6319999999999</v>
+        <v>919.258</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1950,16 +1662,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46136.19791666666</v>
+        <v>46140.19791666666</v>
       </c>
       <c r="B21">
-        <v>-25.495</v>
+        <v>-54.951</v>
       </c>
       <c r="C21">
-        <v>995.756</v>
+        <v>915.056</v>
       </c>
       <c r="D21">
-        <v>995.756</v>
+        <v>915.056</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1970,16 +1682,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46136.20833333334</v>
+        <v>46140.20833333334</v>
       </c>
       <c r="B22">
-        <v>-22.49</v>
+        <v>-14.726</v>
       </c>
       <c r="C22">
-        <v>1058.944</v>
+        <v>851.8150000000001</v>
       </c>
       <c r="D22">
-        <v>1058.944</v>
+        <v>851.8150000000001</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1990,16 +1702,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46136.21875</v>
+        <v>46140.21875</v>
       </c>
       <c r="B23">
-        <v>-22.498</v>
+        <v>7.909</v>
       </c>
       <c r="C23">
-        <v>934.763</v>
+        <v>18.142</v>
       </c>
       <c r="D23">
-        <v>934.763</v>
+        <v>18.142</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -2010,16 +1722,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46136.22916666666</v>
+        <v>46140.22916666666</v>
       </c>
       <c r="B24">
-        <v>-25.72</v>
+        <v>19.322</v>
       </c>
       <c r="C24">
-        <v>1046.584</v>
+        <v>-68.492</v>
       </c>
       <c r="D24">
-        <v>1046.584</v>
+        <v>-68.492</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -2030,16 +1742,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46136.23958333334</v>
+        <v>46140.23958333334</v>
       </c>
       <c r="B25">
-        <v>-45.908</v>
+        <v>10.96</v>
       </c>
       <c r="C25">
-        <v>1194.479</v>
+        <v>-4.528</v>
       </c>
       <c r="D25">
-        <v>1194.479</v>
+        <v>-4.528</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -2050,16 +1762,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46136.25</v>
+        <v>46140.25</v>
       </c>
       <c r="B26">
-        <v>-59.144</v>
+        <v>21.843</v>
       </c>
       <c r="C26">
-        <v>2736.222</v>
+        <v>90.54600000000001</v>
       </c>
       <c r="D26">
-        <v>2736.222</v>
+        <v>90.54600000000001</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -2070,16 +1782,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46136.26041666666</v>
+        <v>46140.26041666666</v>
       </c>
       <c r="B27">
-        <v>-63.921</v>
+        <v>11.472</v>
       </c>
       <c r="C27">
-        <v>2469.713</v>
+        <v>240.161</v>
       </c>
       <c r="D27">
-        <v>2469.713</v>
+        <v>240.161</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -2090,16 +1802,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46136.27083333334</v>
+        <v>46140.27083333334</v>
       </c>
       <c r="B28">
-        <v>-66.92100000000001</v>
+        <v>22.526</v>
       </c>
       <c r="C28">
-        <v>3338.519</v>
+        <v>-78.449</v>
       </c>
       <c r="D28">
-        <v>3338.519</v>
+        <v>-78.449</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -2110,16 +1822,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46136.28125</v>
+        <v>46140.28125</v>
       </c>
       <c r="B29">
-        <v>-24.935</v>
+        <v>56.547</v>
       </c>
       <c r="C29">
-        <v>1193.93</v>
+        <v>-129.818</v>
       </c>
       <c r="D29">
-        <v>1193.93</v>
+        <v>-129.818</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -2130,16 +1842,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46136.29166666666</v>
+        <v>46140.29166666666</v>
       </c>
       <c r="B30">
-        <v>-77.002</v>
+        <v>39.098</v>
       </c>
       <c r="C30">
-        <v>5534.292</v>
+        <v>-1647.602</v>
       </c>
       <c r="D30">
-        <v>5534.292</v>
+        <v>-1647.602</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -2150,16 +1862,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46136.30208333334</v>
+        <v>46140.30208333334</v>
       </c>
       <c r="B31">
-        <v>-57.822</v>
+        <v>32.253</v>
       </c>
       <c r="C31">
-        <v>1854.699</v>
+        <v>-1291.338</v>
       </c>
       <c r="D31">
-        <v>1854.699</v>
+        <v>-1291.338</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -2170,16 +1882,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46136.3125</v>
+        <v>46140.3125</v>
       </c>
       <c r="B32">
-        <v>-64.155</v>
+        <v>40.817</v>
       </c>
       <c r="C32">
-        <v>899.777</v>
+        <v>-40.165</v>
       </c>
       <c r="D32">
-        <v>899.777</v>
+        <v>-40.165</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -2190,16 +1902,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46136.32291666666</v>
+        <v>46140.32291666666</v>
       </c>
       <c r="B33">
-        <v>17.02</v>
+        <v>66.908</v>
       </c>
       <c r="C33">
-        <v>148.76</v>
+        <v>-1520.27</v>
       </c>
       <c r="D33">
-        <v>148.76</v>
+        <v>-1520.27</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -2210,16 +1922,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46136.33333333334</v>
+        <v>46140.33333333334</v>
       </c>
       <c r="B34">
-        <v>62.02</v>
+        <v>53.921</v>
       </c>
       <c r="C34">
-        <v>330.551</v>
+        <v>-313.67</v>
       </c>
       <c r="D34">
-        <v>330.551</v>
+        <v>-313.67</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -2230,16 +1942,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46136.34375</v>
+        <v>46140.34375</v>
       </c>
       <c r="B35">
-        <v>109.706</v>
+        <v>111.161</v>
       </c>
       <c r="C35">
-        <v>-3964.732</v>
+        <v>-96.645</v>
       </c>
       <c r="D35">
-        <v>-3964.732</v>
+        <v>-96.645</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -2250,16 +1962,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46136.35416666666</v>
+        <v>46140.35416666666</v>
       </c>
       <c r="B36">
-        <v>77.086</v>
+        <v>97.048</v>
       </c>
       <c r="C36">
-        <v>-275.677</v>
+        <v>-83.13500000000001</v>
       </c>
       <c r="D36">
-        <v>-275.677</v>
+        <v>-83.13500000000001</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -2270,16 +1982,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46136.36458333334</v>
+        <v>46140.36458333334</v>
       </c>
       <c r="B37">
-        <v>55.143</v>
+        <v>80.345</v>
       </c>
       <c r="C37">
-        <v>1.706</v>
+        <v>7.775</v>
       </c>
       <c r="D37">
-        <v>1.706</v>
+        <v>7.775</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -2290,16 +2002,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46136.375</v>
+        <v>46140.375</v>
       </c>
       <c r="B38">
-        <v>20.565</v>
+        <v>51.336</v>
       </c>
       <c r="C38">
-        <v>0.313</v>
+        <v>2.226</v>
       </c>
       <c r="D38">
-        <v>0.313</v>
+        <v>2.226</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -2310,16 +2022,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46136.38541666666</v>
+        <v>46140.38541666666</v>
       </c>
       <c r="B39">
-        <v>25.31</v>
+        <v>52.959</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>4.398</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>4.398</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -2330,16 +2042,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46136.39583333334</v>
+        <v>46140.39583333334</v>
       </c>
       <c r="B40">
-        <v>21.075</v>
+        <v>88.54900000000001</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>-17.285</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>-17.285</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -2350,16 +2062,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46136.40625</v>
+        <v>46140.40625</v>
       </c>
       <c r="B41">
-        <v>-6.015</v>
+        <v>95.937</v>
       </c>
       <c r="C41">
-        <v>619.591</v>
+        <v>-86.181</v>
       </c>
       <c r="D41">
-        <v>619.591</v>
+        <v>-86.181</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -2370,16 +2082,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46136.41666666666</v>
+        <v>46140.41666666666</v>
       </c>
       <c r="B42">
-        <v>-28.856</v>
+        <v>39.996</v>
       </c>
       <c r="C42">
-        <v>1579.59</v>
+        <v>-105.466</v>
       </c>
       <c r="D42">
-        <v>1579.59</v>
+        <v>-105.466</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -2390,16 +2102,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46136.42708333334</v>
+        <v>46140.42708333334</v>
       </c>
       <c r="B43">
-        <v>-33.236</v>
+        <v>53.121</v>
       </c>
       <c r="C43">
-        <v>466.502</v>
+        <v>-96.995</v>
       </c>
       <c r="D43">
-        <v>466.502</v>
+        <v>-96.995</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -2410,16 +2122,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46136.4375</v>
+        <v>46140.4375</v>
       </c>
       <c r="B44">
-        <v>12.429</v>
+        <v>53.825</v>
       </c>
       <c r="C44">
-        <v>-223.582</v>
+        <v>-107.142</v>
       </c>
       <c r="D44">
-        <v>-223.582</v>
+        <v>-107.142</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -2430,16 +2142,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46136.44791666666</v>
+        <v>46140.44791666666</v>
       </c>
       <c r="B45">
-        <v>53.69</v>
+        <v>109.29</v>
       </c>
       <c r="C45">
-        <v>-681.33</v>
+        <v>-116.516</v>
       </c>
       <c r="D45">
-        <v>-681.33</v>
+        <v>-116.516</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -2450,16 +2162,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46136.45833333334</v>
+        <v>46140.45833333334</v>
       </c>
       <c r="B46">
-        <v>65.14400000000001</v>
+        <v>101.56</v>
       </c>
       <c r="C46">
-        <v>-341.336</v>
+        <v>-165.02</v>
       </c>
       <c r="D46">
-        <v>-341.336</v>
+        <v>-165.02</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -2470,16 +2182,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46136.46875</v>
+        <v>46140.46875</v>
       </c>
       <c r="B47">
-        <v>-45.792</v>
+        <v>87.872</v>
       </c>
       <c r="C47">
-        <v>450</v>
+        <v>-158.93</v>
       </c>
       <c r="D47">
-        <v>450</v>
+        <v>-158.93</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -2490,16 +2202,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46136.47916666666</v>
+        <v>46140.47916666666</v>
       </c>
       <c r="B48">
-        <v>-82.06999999999999</v>
+        <v>69.459</v>
       </c>
       <c r="C48">
-        <v>1178.803</v>
+        <v>-163.461</v>
       </c>
       <c r="D48">
-        <v>1178.803</v>
+        <v>-163.461</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -2510,16 +2222,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46136.48958333334</v>
+        <v>46140.48958333334</v>
       </c>
       <c r="B49">
-        <v>-83.033</v>
+        <v>53.477</v>
       </c>
       <c r="C49">
-        <v>2441.168</v>
+        <v>-163.24</v>
       </c>
       <c r="D49">
-        <v>2441.168</v>
+        <v>-163.24</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -2530,16 +2242,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46136.5</v>
+        <v>46140.5</v>
       </c>
       <c r="B50">
-        <v>-79.428</v>
+        <v>116.495</v>
       </c>
       <c r="C50">
-        <v>529.601</v>
+        <v>-159.874</v>
       </c>
       <c r="D50">
-        <v>529.601</v>
+        <v>-159.874</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -2550,16 +2262,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46136.51041666666</v>
+        <v>46140.51041666666</v>
       </c>
       <c r="B51">
-        <v>-25.15</v>
+        <v>134.519</v>
       </c>
       <c r="C51">
-        <v>447.172</v>
+        <v>-159.715</v>
       </c>
       <c r="D51">
-        <v>447.172</v>
+        <v>-159.715</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -2570,16 +2282,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46136.52083333334</v>
+        <v>46140.52083333334</v>
       </c>
       <c r="B52">
-        <v>20.832</v>
+        <v>110.394</v>
       </c>
       <c r="C52">
-        <v>-230.849</v>
+        <v>-160.709</v>
       </c>
       <c r="D52">
-        <v>-230.849</v>
+        <v>-160.709</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2590,16 +2302,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46136.53125</v>
+        <v>46140.53125</v>
       </c>
       <c r="B53">
-        <v>28.98</v>
+        <v>102.903</v>
       </c>
       <c r="C53">
-        <v>-2856.152</v>
+        <v>-159.551</v>
       </c>
       <c r="D53">
-        <v>-2856.152</v>
+        <v>-159.551</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2610,16 +2322,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46136.54166666666</v>
+        <v>46140.54166666666</v>
       </c>
       <c r="B54">
-        <v>34.451</v>
+        <v>100.453</v>
       </c>
       <c r="C54">
-        <v>-2061.562</v>
+        <v>-114.249</v>
       </c>
       <c r="D54">
-        <v>-2061.562</v>
+        <v>-114.249</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2630,16 +2342,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46136.55208333334</v>
+        <v>46140.55208333334</v>
       </c>
       <c r="B55">
-        <v>45.066</v>
+        <v>109.705</v>
       </c>
       <c r="C55">
-        <v>-108.335</v>
+        <v>-119.99</v>
       </c>
       <c r="D55">
-        <v>-108.335</v>
+        <v>-119.99</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2650,16 +2362,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46136.5625</v>
+        <v>46140.5625</v>
       </c>
       <c r="B56">
-        <v>107.932</v>
+        <v>151.637</v>
       </c>
       <c r="C56">
-        <v>-711.0940000000001</v>
+        <v>-520.351</v>
       </c>
       <c r="D56">
-        <v>-711.0940000000001</v>
+        <v>-520.351</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2670,16 +2382,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46136.57291666666</v>
+        <v>46140.57291666666</v>
       </c>
       <c r="B57">
-        <v>99.048</v>
+        <v>119.42</v>
       </c>
       <c r="C57">
-        <v>-3521.818</v>
+        <v>-122.356</v>
       </c>
       <c r="D57">
-        <v>-3521.818</v>
+        <v>-122.356</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2690,16 +2402,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46136.58333333334</v>
+        <v>46140.58333333334</v>
       </c>
       <c r="B58">
-        <v>55.021</v>
+        <v>149.159</v>
       </c>
       <c r="C58">
-        <v>-5524.456</v>
+        <v>-335.306</v>
       </c>
       <c r="D58">
-        <v>-5524.456</v>
+        <v>-335.306</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2710,16 +2422,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46136.59375</v>
+        <v>46140.59375</v>
       </c>
       <c r="B59">
-        <v>25.958</v>
+        <v>119.247</v>
       </c>
       <c r="C59">
-        <v>-329.867</v>
+        <v>-106.806</v>
       </c>
       <c r="D59">
-        <v>-329.867</v>
+        <v>-106.806</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2730,16 +2442,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46136.60416666666</v>
+        <v>46140.60416666666</v>
       </c>
       <c r="B60">
-        <v>30.699</v>
+        <v>132.533</v>
       </c>
       <c r="C60">
-        <v>-90.792</v>
+        <v>-141.83</v>
       </c>
       <c r="D60">
-        <v>-90.792</v>
+        <v>-141.83</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2750,16 +2462,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46136.61458333334</v>
+        <v>46140.61458333334</v>
       </c>
       <c r="B61">
-        <v>17.502</v>
+        <v>93.667</v>
       </c>
       <c r="C61">
-        <v>-58.471</v>
+        <v>-112.533</v>
       </c>
       <c r="D61">
-        <v>-58.471</v>
+        <v>-112.533</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2770,16 +2482,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46136.625</v>
+        <v>46140.625</v>
       </c>
       <c r="B62">
-        <v>28.716</v>
+        <v>84.741</v>
       </c>
       <c r="C62">
-        <v>-315.278</v>
+        <v>-123.89</v>
       </c>
       <c r="D62">
-        <v>-315.278</v>
+        <v>-123.89</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2790,16 +2502,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46136.63541666666</v>
+        <v>46140.63541666666</v>
       </c>
       <c r="B63">
-        <v>26.284</v>
+        <v>87.232</v>
       </c>
       <c r="C63">
-        <v>-108.784</v>
+        <v>-117.491</v>
       </c>
       <c r="D63">
-        <v>-108.784</v>
+        <v>-117.491</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2810,16 +2522,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46136.64583333334</v>
+        <v>46140.64583333334</v>
       </c>
       <c r="B64">
-        <v>55.08</v>
+        <v>20.918</v>
       </c>
       <c r="C64">
-        <v>-39.088</v>
+        <v>0.923</v>
       </c>
       <c r="D64">
-        <v>-39.088</v>
+        <v>0.923</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2830,16 +2542,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46136.65625</v>
+        <v>46140.65625</v>
       </c>
       <c r="B65">
-        <v>52.591</v>
+        <v>69.176</v>
       </c>
       <c r="C65">
-        <v>-488.625</v>
+        <v>-16.225</v>
       </c>
       <c r="D65">
-        <v>-488.625</v>
+        <v>-16.225</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2850,16 +2562,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46136.66666666666</v>
+        <v>46140.66666666666</v>
       </c>
       <c r="B66">
-        <v>102.508</v>
+        <v>94.38200000000001</v>
       </c>
       <c r="C66">
-        <v>-6363.792</v>
+        <v>-1658.035</v>
       </c>
       <c r="D66">
-        <v>-6363.792</v>
+        <v>-1658.035</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2870,16 +2582,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46136.67708333334</v>
+        <v>46140.67708333334</v>
       </c>
       <c r="B67">
-        <v>79.798</v>
+        <v>94.31</v>
       </c>
       <c r="C67">
-        <v>-5284.295</v>
+        <v>-156.388</v>
       </c>
       <c r="D67">
-        <v>-5284.295</v>
+        <v>-156.388</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2890,16 +2602,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46136.6875</v>
+        <v>46140.6875</v>
       </c>
       <c r="B68">
-        <v>136.999</v>
+        <v>78.23399999999999</v>
       </c>
       <c r="C68">
-        <v>-5771.636</v>
+        <v>-19.937</v>
       </c>
       <c r="D68">
-        <v>-5771.636</v>
+        <v>-19.937</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2910,16 +2622,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46136.69791666666</v>
+        <v>46140.69791666666</v>
       </c>
       <c r="B69">
-        <v>113.964</v>
+        <v>55.638</v>
       </c>
       <c r="C69">
-        <v>-338.083</v>
+        <v>0.644</v>
       </c>
       <c r="D69">
-        <v>-338.083</v>
+        <v>0.644</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2930,16 +2642,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46136.70833333334</v>
+        <v>46140.70833333334</v>
       </c>
       <c r="B70">
-        <v>187.504</v>
+        <v>105.211</v>
       </c>
       <c r="C70">
-        <v>-8.928000000000001</v>
+        <v>2.795</v>
       </c>
       <c r="D70">
-        <v>-8.928000000000001</v>
+        <v>2.795</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2950,16 +2662,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46136.71875</v>
+        <v>46140.71875</v>
       </c>
       <c r="B71">
-        <v>104.504</v>
+        <v>112.19</v>
       </c>
       <c r="C71">
-        <v>2.646</v>
+        <v>8.029</v>
       </c>
       <c r="D71">
-        <v>2.646</v>
+        <v>8.029</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2970,16 +2682,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46136.72916666666</v>
+        <v>46140.72916666666</v>
       </c>
       <c r="B72">
-        <v>112.76</v>
+        <v>24.021</v>
       </c>
       <c r="C72">
-        <v>3.213</v>
+        <v>0.3</v>
       </c>
       <c r="D72">
-        <v>3.213</v>
+        <v>0.3</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2990,16 +2702,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46136.73958333334</v>
+        <v>46140.73958333334</v>
       </c>
       <c r="B73">
-        <v>-0.914</v>
+        <v>21.793</v>
       </c>
       <c r="C73">
-        <v>852.527</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>852.527</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -3010,16 +2722,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46136.75</v>
+        <v>46140.75</v>
       </c>
       <c r="B74">
-        <v>7.806</v>
+        <v>33.491</v>
       </c>
       <c r="C74">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D74">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -3030,16 +2742,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46136.76041666666</v>
+        <v>46140.76041666666</v>
       </c>
       <c r="B75">
-        <v>-40.888</v>
+        <v>45.179</v>
       </c>
       <c r="C75">
-        <v>5252.978</v>
+        <v>0.869</v>
       </c>
       <c r="D75">
-        <v>5252.978</v>
+        <v>0.869</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -3050,16 +2762,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46136.77083333334</v>
+        <v>46140.77083333334</v>
       </c>
       <c r="B76">
-        <v>-32.514</v>
+        <v>32.76</v>
       </c>
       <c r="C76">
-        <v>3605.494</v>
+        <v>348.075</v>
       </c>
       <c r="D76">
-        <v>3605.494</v>
+        <v>348.075</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -3070,16 +2782,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46136.78125</v>
+        <v>46140.78125</v>
       </c>
       <c r="B77">
-        <v>-60.687</v>
+        <v>37.651</v>
       </c>
       <c r="C77">
-        <v>3815.376</v>
+        <v>211.684</v>
       </c>
       <c r="D77">
-        <v>3815.376</v>
+        <v>211.684</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -3090,16 +2802,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46136.79166666666</v>
+        <v>46140.79166666666</v>
       </c>
       <c r="B78">
-        <v>26.105</v>
+        <v>65.203</v>
       </c>
       <c r="C78">
-        <v>8.978</v>
+        <v>-250.252</v>
       </c>
       <c r="D78">
-        <v>8.978</v>
+        <v>-250.252</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -3110,16 +2822,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46136.80208333334</v>
+        <v>46140.80208333334</v>
       </c>
       <c r="B79">
-        <v>18.486</v>
+        <v>52.631</v>
       </c>
       <c r="C79">
-        <v>256.85</v>
+        <v>-232.844</v>
       </c>
       <c r="D79">
-        <v>256.85</v>
+        <v>-232.844</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -3130,16 +2842,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46136.8125</v>
+        <v>46140.8125</v>
       </c>
       <c r="B80">
-        <v>31.104</v>
+        <v>53.457</v>
       </c>
       <c r="C80">
-        <v>271.517</v>
+        <v>272.597</v>
       </c>
       <c r="D80">
-        <v>271.517</v>
+        <v>272.597</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -3150,16 +2862,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46136.82291666666</v>
+        <v>46140.82291666666</v>
       </c>
       <c r="B81">
-        <v>31.166</v>
+        <v>53.201</v>
       </c>
       <c r="C81">
-        <v>363.165</v>
+        <v>212.517</v>
       </c>
       <c r="D81">
-        <v>363.165</v>
+        <v>212.517</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -3170,16 +2882,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46136.83333333334</v>
+        <v>46140.83333333334</v>
       </c>
       <c r="B82">
-        <v>47.599</v>
+        <v>53.532</v>
       </c>
       <c r="C82">
-        <v>-64.434</v>
+        <v>268.952</v>
       </c>
       <c r="D82">
-        <v>-64.434</v>
+        <v>268.952</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -3190,16 +2902,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46136.84375</v>
+        <v>46140.84375</v>
       </c>
       <c r="B83">
-        <v>48.194</v>
+        <v>29.862</v>
       </c>
       <c r="C83">
-        <v>-24.657</v>
+        <v>-110.993</v>
       </c>
       <c r="D83">
-        <v>-24.657</v>
+        <v>-110.993</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -3210,16 +2922,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46136.85416666666</v>
+        <v>46140.85416666666</v>
       </c>
       <c r="B84">
-        <v>91.363</v>
+        <v>39.068</v>
       </c>
       <c r="C84">
-        <v>15.16</v>
+        <v>-203.118</v>
       </c>
       <c r="D84">
-        <v>15.16</v>
+        <v>-203.118</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -3230,16 +2942,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46136.86458333334</v>
+        <v>46140.86458333334</v>
       </c>
       <c r="B85">
-        <v>63.113</v>
+        <v>56.454</v>
       </c>
       <c r="C85">
-        <v>300.065</v>
+        <v>-1644.845</v>
       </c>
       <c r="D85">
-        <v>300.065</v>
+        <v>-1644.845</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -3250,16 +2962,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46136.875</v>
+        <v>46140.875</v>
       </c>
       <c r="B86">
-        <v>13.912</v>
+        <v>15.899</v>
       </c>
       <c r="C86">
-        <v>400</v>
+        <v>27.608</v>
       </c>
       <c r="D86">
-        <v>400</v>
+        <v>27.608</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -3270,16 +2982,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46136.88541666666</v>
+        <v>46140.88541666666</v>
       </c>
       <c r="B87">
-        <v>33.899</v>
+        <v>48.967</v>
       </c>
       <c r="C87">
-        <v>283.661</v>
+        <v>18.084</v>
       </c>
       <c r="D87">
-        <v>283.661</v>
+        <v>18.084</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -3290,16 +3002,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46136.89583333334</v>
+        <v>46140.89583333334</v>
       </c>
       <c r="B88">
-        <v>25.246</v>
+        <v>45.224</v>
       </c>
       <c r="C88">
-        <v>277.612</v>
+        <v>47.292</v>
       </c>
       <c r="D88">
-        <v>277.612</v>
+        <v>47.292</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -3310,16 +3022,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46136.90625</v>
+        <v>46140.90625</v>
       </c>
       <c r="B89">
-        <v>9.205</v>
+        <v>9.131</v>
       </c>
       <c r="C89">
-        <v>264.092</v>
+        <v>8.792</v>
       </c>
       <c r="D89">
-        <v>264.092</v>
+        <v>8.792</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -3330,16 +3042,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46136.91666666666</v>
+        <v>46140.91666666666</v>
       </c>
       <c r="B90">
-        <v>-20.59</v>
+        <v>-5.921</v>
       </c>
       <c r="C90">
-        <v>882.21</v>
+        <v>2486.853</v>
       </c>
       <c r="D90">
-        <v>882.21</v>
+        <v>2486.853</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -3350,16 +3062,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46136.92708333334</v>
+        <v>46140.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.346</v>
+        <v>18.991</v>
       </c>
       <c r="C91">
-        <v>265.608</v>
+        <v>1.1</v>
       </c>
       <c r="D91">
-        <v>265.608</v>
+        <v>1.1</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -3370,16 +3082,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46136.9375</v>
+        <v>46140.9375</v>
       </c>
       <c r="B92">
-        <v>3.655</v>
+        <v>21.628</v>
       </c>
       <c r="C92">
-        <v>257.127</v>
+        <v>77.087</v>
       </c>
       <c r="D92">
-        <v>257.127</v>
+        <v>77.087</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -3390,16 +3102,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46136.94791666666</v>
+        <v>46140.94791666666</v>
       </c>
       <c r="B93">
-        <v>28.599</v>
+        <v>26.06</v>
       </c>
       <c r="C93">
-        <v>-143.875</v>
+        <v>-92.39400000000001</v>
       </c>
       <c r="D93">
-        <v>-143.875</v>
+        <v>-92.39400000000001</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -3410,16 +3122,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46136.95833333334</v>
+        <v>46140.95833333334</v>
       </c>
       <c r="B94">
-        <v>19.003</v>
+        <v>21.581</v>
       </c>
       <c r="C94">
-        <v>113.564</v>
+        <v>14.892</v>
       </c>
       <c r="D94">
-        <v>113.564</v>
+        <v>14.892</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -3430,16 +3142,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46136.96875</v>
+        <v>46140.96875</v>
       </c>
       <c r="B95">
-        <v>19.555</v>
+        <v>31.531</v>
       </c>
       <c r="C95">
-        <v>259.244</v>
+        <v>303.597</v>
       </c>
       <c r="D95">
-        <v>259.244</v>
+        <v>303.597</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -3450,16 +3162,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46136.97916666666</v>
+        <v>46140.97916666666</v>
       </c>
       <c r="B96">
-        <v>20.897</v>
+        <v>-0.343</v>
       </c>
       <c r="C96">
-        <v>292.523</v>
+        <v>894.398</v>
       </c>
       <c r="D96">
-        <v>292.523</v>
+        <v>894.398</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -3470,16 +3182,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46136.98958333334</v>
+        <v>46140.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.13</v>
+        <v>11.067</v>
       </c>
       <c r="C97">
-        <v>379.803</v>
+        <v>-34.652</v>
       </c>
       <c r="D97">
-        <v>379.803</v>
+        <v>-34.652</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -3490,16 +3202,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46137</v>
+        <v>46141</v>
       </c>
       <c r="B98">
-        <v>51.687</v>
+        <v>13.48</v>
       </c>
       <c r="C98">
-        <v>298.695</v>
+        <v>37.605</v>
       </c>
       <c r="D98">
-        <v>298.695</v>
+        <v>37.605</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -3510,16 +3222,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46137.01041666666</v>
+        <v>46141.01041666666</v>
       </c>
       <c r="B99">
-        <v>-4.493</v>
+        <v>36.429</v>
       </c>
       <c r="C99">
-        <v>650</v>
+        <v>321.097</v>
       </c>
       <c r="D99">
-        <v>650</v>
+        <v>321.097</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -3530,16 +3242,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46137.02083333334</v>
+        <v>46141.02083333334</v>
       </c>
       <c r="B100">
-        <v>7.283</v>
+        <v>22.004</v>
       </c>
       <c r="C100">
-        <v>104.16</v>
+        <v>73.93300000000001</v>
       </c>
       <c r="D100">
-        <v>104.16</v>
+        <v>73.93300000000001</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -3550,16 +3262,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46137.03125</v>
+        <v>46141.03125</v>
       </c>
       <c r="B101">
-        <v>14.032</v>
+        <v>27.462</v>
       </c>
       <c r="C101">
-        <v>155.733</v>
+        <v>35.858</v>
       </c>
       <c r="D101">
-        <v>155.733</v>
+        <v>35.858</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -3570,16 +3282,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46137.04166666666</v>
+        <v>46141.04166666666</v>
       </c>
       <c r="B102">
-        <v>-6.859</v>
+        <v>-4.38</v>
       </c>
       <c r="C102">
-        <v>894.928</v>
+        <v>894.367</v>
       </c>
       <c r="D102">
-        <v>894.928</v>
+        <v>894.367</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3590,16 +3302,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46137.05208333334</v>
+        <v>46141.05208333334</v>
       </c>
       <c r="B103">
-        <v>-2.156</v>
+        <v>-1.511</v>
       </c>
       <c r="C103">
-        <v>894.823</v>
+        <v>789.13</v>
       </c>
       <c r="D103">
-        <v>894.823</v>
+        <v>789.13</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3610,16 +3322,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46137.0625</v>
+        <v>46141.0625</v>
       </c>
       <c r="B104">
-        <v>1.386</v>
+        <v>21.698</v>
       </c>
       <c r="C104">
-        <v>390.414</v>
+        <v>-83.43000000000001</v>
       </c>
       <c r="D104">
-        <v>390.414</v>
+        <v>-83.43000000000001</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3630,16 +3342,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46137.07291666666</v>
+        <v>46141.07291666666</v>
       </c>
       <c r="B105">
-        <v>36.4</v>
+        <v>13.909</v>
       </c>
       <c r="C105">
-        <v>-200.415</v>
+        <v>-15.148</v>
       </c>
       <c r="D105">
-        <v>-200.415</v>
+        <v>-15.148</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3650,16 +3362,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46137.08333333334</v>
+        <v>46141.08333333334</v>
       </c>
       <c r="B106">
-        <v>16.874</v>
+        <v>-1.805</v>
       </c>
       <c r="C106">
-        <v>13.316</v>
+        <v>843.597</v>
       </c>
       <c r="D106">
-        <v>13.316</v>
+        <v>843.597</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3670,16 +3382,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46137.09375</v>
+        <v>46141.09375</v>
       </c>
       <c r="B107">
-        <v>23.921</v>
+        <v>-45.025</v>
       </c>
       <c r="C107">
-        <v>-34.383</v>
+        <v>884.9400000000001</v>
       </c>
       <c r="D107">
-        <v>-34.383</v>
+        <v>884.9400000000001</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3690,16 +3402,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46137.10416666666</v>
+        <v>46141.10416666666</v>
       </c>
       <c r="B108">
-        <v>20.257</v>
+        <v>-36.388</v>
       </c>
       <c r="C108">
-        <v>-60.581</v>
+        <v>1431.468</v>
       </c>
       <c r="D108">
-        <v>-60.581</v>
+        <v>1431.468</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3710,16 +3422,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46137.11458333334</v>
+        <v>46141.11458333334</v>
       </c>
       <c r="B109">
-        <v>24.377</v>
+        <v>-29.094</v>
       </c>
       <c r="C109">
-        <v>-121.838</v>
+        <v>1095.23</v>
       </c>
       <c r="D109">
-        <v>-121.838</v>
+        <v>1095.23</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3730,16 +3442,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46137.125</v>
+        <v>46141.125</v>
       </c>
       <c r="B110">
-        <v>29.61</v>
+        <v>-2.54</v>
       </c>
       <c r="C110">
-        <v>160.008</v>
+        <v>873.193</v>
       </c>
       <c r="D110">
-        <v>160.008</v>
+        <v>873.193</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3750,16 +3462,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46137.13541666666</v>
+        <v>46141.13541666666</v>
       </c>
       <c r="B111">
-        <v>19.293</v>
+        <v>-13.355</v>
       </c>
       <c r="C111">
-        <v>120.94</v>
+        <v>878.354</v>
       </c>
       <c r="D111">
-        <v>120.94</v>
+        <v>878.354</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3770,16 +3482,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46137.14583333334</v>
+        <v>46141.14583333334</v>
       </c>
       <c r="B112">
-        <v>-4.189</v>
+        <v>-14.757</v>
       </c>
       <c r="C112">
-        <v>898.53</v>
+        <v>873.347</v>
       </c>
       <c r="D112">
-        <v>898.53</v>
+        <v>873.347</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3790,16 +3502,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46137.15625</v>
+        <v>46141.15625</v>
       </c>
       <c r="B113">
-        <v>15.128</v>
+        <v>0.491</v>
       </c>
       <c r="C113">
-        <v>255.53</v>
+        <v>225.758</v>
       </c>
       <c r="D113">
-        <v>255.53</v>
+        <v>225.758</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3810,16 +3522,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46137.16666666666</v>
+        <v>46141.16666666666</v>
       </c>
       <c r="B114">
-        <v>43.063</v>
+        <v>30.455</v>
       </c>
       <c r="C114">
-        <v>264.184</v>
+        <v>181.059</v>
       </c>
       <c r="D114">
-        <v>264.184</v>
+        <v>181.059</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3830,16 +3542,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46137.17708333334</v>
+        <v>46141.17708333334</v>
       </c>
       <c r="B115">
-        <v>34.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C115">
-        <v>385.724</v>
+        <v>50.733</v>
       </c>
       <c r="D115">
-        <v>385.724</v>
+        <v>50.733</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3850,16 +3562,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46137.1875</v>
+        <v>46141.1875</v>
       </c>
       <c r="B116">
-        <v>18.719</v>
+        <v>20.547</v>
       </c>
       <c r="C116">
-        <v>269.637</v>
+        <v>254.797</v>
       </c>
       <c r="D116">
-        <v>269.637</v>
+        <v>254.797</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3870,16 +3582,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46137.19791666666</v>
+        <v>46141.19791666666</v>
       </c>
       <c r="B117">
-        <v>12.827</v>
+        <v>-30.131</v>
       </c>
       <c r="C117">
-        <v>-178.719</v>
+        <v>1070.923</v>
       </c>
       <c r="D117">
-        <v>-178.719</v>
+        <v>1070.923</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3890,16 +3602,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46137.20833333334</v>
+        <v>46141.20833333334</v>
       </c>
       <c r="B118">
-        <v>36.844</v>
+        <v>40.888</v>
       </c>
       <c r="C118">
-        <v>-221.562</v>
+        <v>103.19</v>
       </c>
       <c r="D118">
-        <v>-221.562</v>
+        <v>103.19</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3910,16 +3622,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46137.21875</v>
+        <v>46141.21875</v>
       </c>
       <c r="B119">
-        <v>45.306</v>
+        <v>25.07</v>
       </c>
       <c r="C119">
-        <v>-68.851</v>
+        <v>149.79</v>
       </c>
       <c r="D119">
-        <v>-68.851</v>
+        <v>149.79</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3930,16 +3642,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46137.22916666666</v>
+        <v>46141.22916666666</v>
       </c>
       <c r="B120">
-        <v>37.179</v>
+        <v>45.434</v>
       </c>
       <c r="C120">
-        <v>109.94</v>
+        <v>143.198</v>
       </c>
       <c r="D120">
-        <v>109.94</v>
+        <v>143.198</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3950,16 +3662,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46137.23958333334</v>
+        <v>46141.23958333334</v>
       </c>
       <c r="B121">
-        <v>25.49</v>
+        <v>40.479</v>
       </c>
       <c r="C121">
-        <v>-184.976</v>
+        <v>-54.735</v>
       </c>
       <c r="D121">
-        <v>-184.976</v>
+        <v>-54.735</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3970,16 +3682,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46137.25</v>
+        <v>46141.25</v>
       </c>
       <c r="B122">
-        <v>-3.362</v>
+        <v>63.654</v>
       </c>
       <c r="C122">
-        <v>887.619</v>
+        <v>-70.86799999999999</v>
       </c>
       <c r="D122">
-        <v>887.619</v>
+        <v>-70.86799999999999</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3990,16 +3702,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46137.26041666666</v>
+        <v>46141.26041666666</v>
       </c>
       <c r="B123">
-        <v>7.101</v>
+        <v>93.774</v>
       </c>
       <c r="C123">
-        <v>391.313</v>
+        <v>119.607</v>
       </c>
       <c r="D123">
-        <v>391.313</v>
+        <v>119.607</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -4010,16 +3722,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46137.27083333334</v>
+        <v>46141.27083333334</v>
       </c>
       <c r="B124">
-        <v>8.244999999999999</v>
+        <v>83.637</v>
       </c>
       <c r="C124">
-        <v>137.165</v>
+        <v>-147.035</v>
       </c>
       <c r="D124">
-        <v>137.165</v>
+        <v>-147.035</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -4030,16 +3742,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46137.28125</v>
+        <v>46141.28125</v>
       </c>
       <c r="B125">
-        <v>17.962</v>
+        <v>94.25</v>
       </c>
       <c r="C125">
-        <v>240.3</v>
+        <v>-717.414</v>
       </c>
       <c r="D125">
-        <v>240.3</v>
+        <v>-717.414</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -4050,16 +3762,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46137.29166666666</v>
+        <v>46141.29166666666</v>
       </c>
       <c r="B126">
-        <v>-23.003</v>
+        <v>96.068</v>
       </c>
       <c r="C126">
-        <v>858.901</v>
+        <v>-373.608</v>
       </c>
       <c r="D126">
-        <v>858.901</v>
+        <v>-373.608</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -4070,16 +3782,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46137.30208333334</v>
+        <v>46141.30208333334</v>
       </c>
       <c r="B127">
-        <v>-31.378</v>
+        <v>79.869</v>
       </c>
       <c r="C127">
-        <v>852.235</v>
+        <v>64.191</v>
       </c>
       <c r="D127">
-        <v>852.235</v>
+        <v>64.191</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -4090,16 +3802,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46137.3125</v>
+        <v>46141.3125</v>
       </c>
       <c r="B128">
-        <v>-72.526</v>
+        <v>93.57299999999999</v>
       </c>
       <c r="C128">
-        <v>923.139</v>
+        <v>-1285.585</v>
       </c>
       <c r="D128">
-        <v>923.139</v>
+        <v>-1285.585</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -4110,16 +3822,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46137.32291666666</v>
+        <v>46141.32291666666</v>
       </c>
       <c r="B129">
-        <v>-40.244</v>
+        <v>155.971</v>
       </c>
       <c r="C129">
-        <v>2117.671</v>
+        <v>-975.755</v>
       </c>
       <c r="D129">
-        <v>2117.671</v>
+        <v>-975.755</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -4130,16 +3842,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46137.33333333334</v>
+        <v>46141.33333333334</v>
       </c>
       <c r="B130">
-        <v>-18.98</v>
+        <v>130.578</v>
       </c>
       <c r="C130">
-        <v>1332.708</v>
+        <v>-48.928</v>
       </c>
       <c r="D130">
-        <v>1332.708</v>
+        <v>-48.928</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -4150,16 +3862,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46137.34375</v>
+        <v>46141.34375</v>
       </c>
       <c r="B131">
-        <v>-28.204</v>
+        <v>33.136</v>
       </c>
       <c r="C131">
-        <v>1054.496</v>
+        <v>0.3</v>
       </c>
       <c r="D131">
-        <v>1054.496</v>
+        <v>0.3</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -4170,16 +3882,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46137.35416666666</v>
+        <v>46141.35416666666</v>
       </c>
       <c r="B132">
-        <v>-28.404</v>
+        <v>39.102</v>
       </c>
       <c r="C132">
-        <v>454.707</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>454.707</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -4190,16 +3902,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46137.36458333334</v>
+        <v>46141.36458333334</v>
       </c>
       <c r="B133">
-        <v>-13.797</v>
+        <v>69.105</v>
       </c>
       <c r="C133">
-        <v>540.224</v>
+        <v>1.198</v>
       </c>
       <c r="D133">
-        <v>540.224</v>
+        <v>1.198</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -4210,16 +3922,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46137.375</v>
+        <v>46141.375</v>
       </c>
       <c r="B134">
-        <v>13.926</v>
+        <v>64.265</v>
       </c>
       <c r="C134">
-        <v>281.1</v>
+        <v>0.348</v>
       </c>
       <c r="D134">
-        <v>281.1</v>
+        <v>0.348</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -4230,16 +3942,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46137.38541666666</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="B135">
-        <v>56.031</v>
+        <v>114.908</v>
       </c>
       <c r="C135">
-        <v>-643.5549999999999</v>
+        <v>-331.694</v>
       </c>
       <c r="D135">
-        <v>-643.5549999999999</v>
+        <v>-331.694</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -4250,16 +3962,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46137.39583333334</v>
+        <v>46141.39583333334</v>
       </c>
       <c r="B136">
-        <v>16.071</v>
+        <v>128.345</v>
       </c>
       <c r="C136">
-        <v>-879.753</v>
+        <v>-2071.429</v>
       </c>
       <c r="D136">
-        <v>-879.753</v>
+        <v>-2071.429</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -4270,16 +3982,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46137.40625</v>
+        <v>46141.40625</v>
       </c>
       <c r="B137">
-        <v>57.087</v>
+        <v>197.132</v>
       </c>
       <c r="C137">
-        <v>-6.444</v>
+        <v>-4628.017</v>
       </c>
       <c r="D137">
-        <v>-6.444</v>
+        <v>-4628.017</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -4290,16 +4002,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46137.41666666666</v>
+        <v>46141.41666666666</v>
       </c>
       <c r="B138">
-        <v>13.312</v>
+        <v>237.683</v>
       </c>
       <c r="C138">
-        <v>-107.97</v>
+        <v>-2485.169</v>
       </c>
       <c r="D138">
-        <v>-107.97</v>
+        <v>-2485.169</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -4310,16 +4022,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46137.42708333334</v>
+        <v>46141.42708333334</v>
       </c>
       <c r="B139">
-        <v>2.381</v>
+        <v>221.958</v>
       </c>
       <c r="C139">
-        <v>-108</v>
+        <v>-3643.235</v>
       </c>
       <c r="D139">
-        <v>-108</v>
+        <v>-3643.235</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -4330,16 +4042,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46137.4375</v>
+        <v>46141.4375</v>
       </c>
       <c r="B140">
-        <v>33.573</v>
+        <v>199.49</v>
       </c>
       <c r="C140">
-        <v>-17.346</v>
+        <v>-522.539</v>
       </c>
       <c r="D140">
-        <v>-17.346</v>
+        <v>-522.539</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -4350,16 +4062,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46137.44791666666</v>
+        <v>46141.44791666666</v>
       </c>
       <c r="B141">
-        <v>13.304</v>
+        <v>219.814</v>
       </c>
       <c r="C141">
-        <v>2.936</v>
+        <v>-453.129</v>
       </c>
       <c r="D141">
-        <v>2.936</v>
+        <v>-453.129</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -4370,16 +4082,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46137.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="B142">
-        <v>11.115</v>
+        <v>275.14</v>
       </c>
       <c r="C142">
-        <v>1.154</v>
+        <v>-1902.981</v>
       </c>
       <c r="D142">
-        <v>1.154</v>
+        <v>-1902.981</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -4390,16 +4102,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46137.46875</v>
+        <v>46141.46875</v>
       </c>
       <c r="B143">
-        <v>10.903</v>
+        <v>276.41</v>
       </c>
       <c r="C143">
-        <v>4.511</v>
+        <v>-3228.805</v>
       </c>
       <c r="D143">
-        <v>4.511</v>
+        <v>-3228.805</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -4410,16 +4122,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46137.47916666666</v>
+        <v>46141.47916666666</v>
       </c>
       <c r="B144">
-        <v>55.767</v>
+        <v>265.942</v>
       </c>
       <c r="C144">
-        <v>-1165.615</v>
+        <v>-2790.645</v>
       </c>
       <c r="D144">
-        <v>-1165.615</v>
+        <v>-2790.645</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -4430,16 +4142,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46137.48958333334</v>
+        <v>46141.48958333334</v>
       </c>
       <c r="B145">
-        <v>22.154</v>
+        <v>258.133</v>
       </c>
       <c r="C145">
-        <v>-53.48</v>
+        <v>-2289.573</v>
       </c>
       <c r="D145">
-        <v>-53.48</v>
+        <v>-2289.573</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -4450,16 +4162,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46137.5</v>
+        <v>46141.5</v>
       </c>
       <c r="B146">
-        <v>45.573</v>
+        <v>261.879</v>
       </c>
       <c r="C146">
-        <v>-1199.711</v>
+        <v>-3455.081</v>
       </c>
       <c r="D146">
-        <v>-1199.711</v>
+        <v>-3455.081</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -4470,16 +4182,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46137.51041666666</v>
+        <v>46141.51041666666</v>
       </c>
       <c r="B147">
-        <v>48.428</v>
+        <v>251.511</v>
       </c>
       <c r="C147">
-        <v>282.614</v>
+        <v>-3246.75</v>
       </c>
       <c r="D147">
-        <v>282.614</v>
+        <v>-3246.75</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -4490,16 +4202,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46137.52083333334</v>
+        <v>46141.52083333334</v>
       </c>
       <c r="B148">
-        <v>61.227</v>
+        <v>227.736</v>
       </c>
       <c r="C148">
-        <v>350.664</v>
+        <v>-2525.318</v>
       </c>
       <c r="D148">
-        <v>350.664</v>
+        <v>-2525.318</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -4510,16 +4222,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46137.53125</v>
+        <v>46141.53125</v>
       </c>
       <c r="B149">
-        <v>86.7</v>
+        <v>222.184</v>
       </c>
       <c r="C149">
-        <v>342.543</v>
+        <v>-1633.741</v>
       </c>
       <c r="D149">
-        <v>342.543</v>
+        <v>-1633.741</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -4530,16 +4242,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46137.54166666666</v>
+        <v>46141.54166666666</v>
       </c>
       <c r="B150">
-        <v>104.616</v>
+        <v>181.357</v>
       </c>
       <c r="C150">
-        <v>-520.5119999999999</v>
+        <v>-299.859</v>
       </c>
       <c r="D150">
-        <v>-520.5119999999999</v>
+        <v>-299.859</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -4550,16 +4262,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46137.55208333334</v>
+        <v>46141.55208333334</v>
       </c>
       <c r="B151">
-        <v>73.94499999999999</v>
+        <v>165.645</v>
       </c>
       <c r="C151">
-        <v>-3579.838</v>
+        <v>-276.102</v>
       </c>
       <c r="D151">
-        <v>-3579.838</v>
+        <v>-276.102</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -4570,16 +4282,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46137.5625</v>
+        <v>46141.5625</v>
       </c>
       <c r="B152">
-        <v>50.044</v>
+        <v>150.026</v>
       </c>
       <c r="C152">
-        <v>-2944.563</v>
+        <v>-169.259</v>
       </c>
       <c r="D152">
-        <v>-2944.563</v>
+        <v>-169.259</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4590,16 +4302,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46137.57291666666</v>
+        <v>46141.57291666666</v>
       </c>
       <c r="B153">
-        <v>90.5</v>
+        <v>93.616</v>
       </c>
       <c r="C153">
-        <v>-7499</v>
+        <v>-159.64</v>
       </c>
       <c r="D153">
-        <v>-7499</v>
+        <v>-159.64</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4610,16 +4322,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46137.58333333334</v>
+        <v>46141.58333333334</v>
       </c>
       <c r="B154">
-        <v>94.51900000000001</v>
+        <v>132.365</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>-46.987</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>-46.987</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4630,16 +4342,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46137.59375</v>
+        <v>46141.59375</v>
       </c>
       <c r="B155">
-        <v>113.994</v>
+        <v>85.886</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4650,16 +4362,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46137.60416666666</v>
+        <v>46141.60416666666</v>
       </c>
       <c r="B156">
-        <v>103.257</v>
+        <v>86.55500000000001</v>
       </c>
       <c r="C156">
-        <v>-1204.393</v>
+        <v>-12.14</v>
       </c>
       <c r="D156">
-        <v>-1204.393</v>
+        <v>-12.14</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4670,16 +4382,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46137.61458333334</v>
+        <v>46141.61458333334</v>
       </c>
       <c r="B157">
-        <v>54.659</v>
+        <v>93.557</v>
       </c>
       <c r="C157">
-        <v>-281.597</v>
+        <v>-37.999</v>
       </c>
       <c r="D157">
-        <v>-281.597</v>
+        <v>-37.999</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4690,16 +4402,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46137.625</v>
+        <v>46141.625</v>
       </c>
       <c r="B158">
-        <v>67.411</v>
+        <v>92.55200000000001</v>
       </c>
       <c r="C158">
-        <v>-287.982</v>
+        <v>-422.525</v>
       </c>
       <c r="D158">
-        <v>-287.982</v>
+        <v>-422.525</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4710,16 +4422,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46137.63541666666</v>
+        <v>46141.63541666666</v>
       </c>
       <c r="B159">
-        <v>65.017</v>
+        <v>51.759</v>
       </c>
       <c r="C159">
-        <v>-279.584</v>
+        <v>-34.247</v>
       </c>
       <c r="D159">
-        <v>-279.584</v>
+        <v>-34.247</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4730,16 +4442,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46137.64583333334</v>
+        <v>46141.64583333334</v>
       </c>
       <c r="B160">
-        <v>61.959</v>
+        <v>30.596</v>
       </c>
       <c r="C160">
-        <v>-277.876</v>
+        <v>3.36</v>
       </c>
       <c r="D160">
-        <v>-277.876</v>
+        <v>3.36</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4750,16 +4462,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46137.65625</v>
+        <v>46141.65625</v>
       </c>
       <c r="B161">
-        <v>59.469</v>
+        <v>21.849</v>
       </c>
       <c r="C161">
-        <v>-288.89</v>
+        <v>-3.636</v>
       </c>
       <c r="D161">
-        <v>-288.89</v>
+        <v>-3.636</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4770,16 +4482,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46137.66666666666</v>
+        <v>46141.66666666666</v>
       </c>
       <c r="B162">
-        <v>119.803</v>
+        <v>92.82299999999999</v>
       </c>
       <c r="C162">
-        <v>-308.949</v>
+        <v>-1151.806</v>
       </c>
       <c r="D162">
-        <v>-308.949</v>
+        <v>-1151.806</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4790,16 +4502,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46137.67708333334</v>
+        <v>46141.67708333334</v>
       </c>
       <c r="B163">
-        <v>90.52</v>
+        <v>63.07</v>
       </c>
       <c r="C163">
-        <v>-133.911</v>
+        <v>0.253</v>
       </c>
       <c r="D163">
-        <v>-133.911</v>
+        <v>0.253</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4810,16 +4522,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46137.6875</v>
+        <v>46141.6875</v>
       </c>
       <c r="B164">
-        <v>67.78700000000001</v>
+        <v>33.263</v>
       </c>
       <c r="C164">
-        <v>-107.158</v>
+        <v>24.094</v>
       </c>
       <c r="D164">
-        <v>-107.158</v>
+        <v>24.094</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4830,16 +4542,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46137.69791666666</v>
+        <v>46141.69791666666</v>
       </c>
       <c r="B165">
-        <v>45.457</v>
+        <v>12.719</v>
       </c>
       <c r="C165">
-        <v>-100.08</v>
+        <v>1.1</v>
       </c>
       <c r="D165">
-        <v>-100.08</v>
+        <v>1.1</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4850,16 +4562,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46137.70833333334</v>
+        <v>46141.70833333334</v>
       </c>
       <c r="B166">
-        <v>79.08799999999999</v>
+        <v>20.293</v>
       </c>
       <c r="C166">
-        <v>-1045.49</v>
+        <v>33.065</v>
       </c>
       <c r="D166">
-        <v>-1045.49</v>
+        <v>33.065</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4870,16 +4582,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46137.71875</v>
+        <v>46141.71875</v>
       </c>
       <c r="B167">
-        <v>57.416</v>
+        <v>12.487</v>
       </c>
       <c r="C167">
-        <v>-26.761</v>
+        <v>266.487</v>
       </c>
       <c r="D167">
-        <v>-26.761</v>
+        <v>266.487</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4890,16 +4602,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46137.72916666666</v>
+        <v>46141.72916666666</v>
       </c>
       <c r="B168">
-        <v>10.356</v>
+        <v>-1.59</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>883.851</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>883.851</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4910,16 +4622,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46137.73958333334</v>
+        <v>46141.73958333334</v>
       </c>
       <c r="B169">
-        <v>18.525</v>
+        <v>-6.619</v>
       </c>
       <c r="C169">
-        <v>6.298</v>
+        <v>1220.505</v>
       </c>
       <c r="D169">
-        <v>6.298</v>
+        <v>1220.505</v>
       </c>
       <c r="E169">
         <v>72</v>
@@ -4930,16 +4642,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46137.75</v>
+        <v>46141.75</v>
       </c>
       <c r="B170">
-        <v>90.31100000000001</v>
+        <v>1.153</v>
       </c>
       <c r="C170">
-        <v>-514.269</v>
+        <v>284.207</v>
       </c>
       <c r="D170">
-        <v>-514.269</v>
+        <v>284.207</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4950,16 +4662,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46137.76041666666</v>
+        <v>46141.76041666666</v>
       </c>
       <c r="B171">
-        <v>32.448</v>
+        <v>5.384</v>
       </c>
       <c r="C171">
-        <v>-218.441</v>
+        <v>400</v>
       </c>
       <c r="D171">
-        <v>-218.441</v>
+        <v>400</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4970,16 +4682,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46137.77083333334</v>
+        <v>46141.77083333334</v>
       </c>
       <c r="B172">
-        <v>47.235</v>
+        <v>7.702</v>
       </c>
       <c r="C172">
-        <v>-35.68</v>
+        <v>303.746</v>
       </c>
       <c r="D172">
-        <v>-35.68</v>
+        <v>303.746</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4990,16 +4702,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46137.78125</v>
+        <v>46141.78125</v>
       </c>
       <c r="B173">
-        <v>32.246</v>
+        <v>13.218</v>
       </c>
       <c r="C173">
-        <v>103.08</v>
+        <v>280.763</v>
       </c>
       <c r="D173">
-        <v>103.08</v>
+        <v>280.763</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -5010,16 +4722,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46137.79166666666</v>
+        <v>46141.79166666666</v>
       </c>
       <c r="B174">
-        <v>65.337</v>
+        <v>73.889</v>
       </c>
       <c r="C174">
-        <v>-667.612</v>
+        <v>285.808</v>
       </c>
       <c r="D174">
-        <v>-667.612</v>
+        <v>285.808</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -5030,16 +4742,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46137.80208333334</v>
+        <v>46141.80208333334</v>
       </c>
       <c r="B175">
-        <v>46.784</v>
+        <v>51.182</v>
       </c>
       <c r="C175">
-        <v>6.478</v>
+        <v>276.218</v>
       </c>
       <c r="D175">
-        <v>6.478</v>
+        <v>276.218</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -5050,16 +4762,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46137.8125</v>
+        <v>46141.8125</v>
       </c>
       <c r="B176">
-        <v>26.157</v>
+        <v>0.35</v>
       </c>
       <c r="C176">
-        <v>1.339</v>
+        <v>272.215</v>
       </c>
       <c r="D176">
-        <v>1.339</v>
+        <v>272.215</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -5070,16 +4782,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46137.82291666666</v>
+        <v>46141.82291666666</v>
       </c>
       <c r="B177">
-        <v>-31.711</v>
+        <v>-47.266</v>
       </c>
       <c r="C177">
-        <v>1673.622</v>
+        <v>2522.402</v>
       </c>
       <c r="D177">
-        <v>1673.622</v>
+        <v>2522.402</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -5090,16 +4802,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46137.83333333334</v>
+        <v>46141.83333333334</v>
       </c>
       <c r="B178">
-        <v>-46.173</v>
+        <v>-16.331</v>
       </c>
       <c r="C178">
-        <v>1418.963</v>
+        <v>1382.189</v>
       </c>
       <c r="D178">
-        <v>1418.963</v>
+        <v>1382.189</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -5110,16 +4822,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46137.84375</v>
+        <v>46141.84375</v>
       </c>
       <c r="B179">
-        <v>-41.124</v>
+        <v>-5.73</v>
       </c>
       <c r="C179">
-        <v>969.9349999999999</v>
+        <v>898.905</v>
       </c>
       <c r="D179">
-        <v>969.9349999999999</v>
+        <v>898.905</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -5130,16 +4842,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46137.85416666666</v>
+        <v>46141.85416666666</v>
       </c>
       <c r="B180">
-        <v>-24.843</v>
+        <v>61.182</v>
       </c>
       <c r="C180">
-        <v>890.088</v>
+        <v>103.568</v>
       </c>
       <c r="D180">
-        <v>890.088</v>
+        <v>103.568</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -5150,16 +4862,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46137.86458333334</v>
+        <v>46141.86458333334</v>
       </c>
       <c r="B181">
-        <v>-16.367</v>
+        <v>92.824</v>
       </c>
       <c r="C181">
-        <v>915.712</v>
+        <v>-598.2569999999999</v>
       </c>
       <c r="D181">
-        <v>915.712</v>
+        <v>-598.2569999999999</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -5170,16 +4882,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46137.875</v>
+        <v>46141.875</v>
       </c>
       <c r="B182">
-        <v>-17.691</v>
+        <v>95.04300000000001</v>
       </c>
       <c r="C182">
-        <v>890.41</v>
+        <v>106.136</v>
       </c>
       <c r="D182">
-        <v>890.41</v>
+        <v>106.136</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -5190,16 +4902,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46137.88541666666</v>
+        <v>46141.88541666666</v>
       </c>
       <c r="B183">
-        <v>-4.425</v>
+        <v>95.871</v>
       </c>
       <c r="C183">
-        <v>896.974</v>
+        <v>270.862</v>
       </c>
       <c r="D183">
-        <v>896.974</v>
+        <v>270.862</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -5210,16 +4922,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46137.89583333334</v>
+        <v>46141.89583333334</v>
       </c>
       <c r="B184">
-        <v>23.559</v>
+        <v>63.122</v>
       </c>
       <c r="C184">
-        <v>16.601</v>
+        <v>-27.152</v>
       </c>
       <c r="D184">
-        <v>16.601</v>
+        <v>-27.152</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -5230,16 +4942,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46137.90625</v>
+        <v>46141.90625</v>
       </c>
       <c r="B185">
-        <v>-0.778</v>
+        <v>48.628</v>
       </c>
       <c r="C185">
-        <v>887.174</v>
+        <v>-485.353</v>
       </c>
       <c r="D185">
-        <v>887.174</v>
+        <v>-485.353</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -5250,16 +4962,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46137.91666666666</v>
+        <v>46141.91666666666</v>
       </c>
       <c r="B186">
-        <v>12.975</v>
+        <v>64.613</v>
       </c>
       <c r="C186">
-        <v>202.135</v>
+        <v>-64.27800000000001</v>
       </c>
       <c r="D186">
-        <v>202.135</v>
+        <v>-64.27800000000001</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -5270,16 +4982,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46137.92708333334</v>
+        <v>46141.92708333334</v>
       </c>
       <c r="B187">
-        <v>-0.9409999999999999</v>
+        <v>52.666</v>
       </c>
       <c r="C187">
-        <v>897.518</v>
+        <v>333.211</v>
       </c>
       <c r="D187">
-        <v>897.518</v>
+        <v>333.211</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -5290,16 +5002,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46137.9375</v>
+        <v>46141.9375</v>
       </c>
       <c r="B188">
-        <v>32.739</v>
+        <v>43.146</v>
       </c>
       <c r="C188">
-        <v>265.16</v>
+        <v>269.766</v>
       </c>
       <c r="D188">
-        <v>265.16</v>
+        <v>269.766</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -5310,16 +5022,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46137.94791666666</v>
+        <v>46141.94791666666</v>
       </c>
       <c r="B189">
-        <v>1.503</v>
+        <v>80.41800000000001</v>
       </c>
       <c r="C189">
-        <v>263.117</v>
+        <v>-17.585</v>
       </c>
       <c r="D189">
-        <v>263.117</v>
+        <v>-17.585</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -5330,16 +5042,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46137.95833333334</v>
+        <v>46141.95833333334</v>
       </c>
       <c r="B190">
-        <v>-10.772</v>
+        <v>9.509</v>
       </c>
       <c r="C190">
-        <v>953.918</v>
+        <v>11.465</v>
       </c>
       <c r="D190">
-        <v>953.918</v>
+        <v>11.465</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -5350,16 +5062,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46137.96875</v>
+        <v>46141.96875</v>
       </c>
       <c r="B191">
-        <v>-21.763</v>
+        <v>-1.702</v>
       </c>
       <c r="C191">
-        <v>919.187</v>
+        <v>899.518</v>
       </c>
       <c r="D191">
-        <v>919.187</v>
+        <v>899.518</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -5370,16 +5082,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46137.97916666666</v>
+        <v>46141.97916666666</v>
       </c>
       <c r="B192">
-        <v>15.335</v>
+        <v>-3.074</v>
       </c>
       <c r="C192">
-        <v>264.856</v>
+        <v>1044.609</v>
       </c>
       <c r="D192">
-        <v>264.856</v>
+        <v>1044.609</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -5390,16 +5102,16 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46137.98958333334</v>
+        <v>46141.98958333334</v>
       </c>
       <c r="B193">
-        <v>-2.286</v>
+        <v>3.095</v>
       </c>
       <c r="C193">
-        <v>897.462</v>
+        <v>311.962</v>
       </c>
       <c r="D193">
-        <v>897.462</v>
+        <v>311.962</v>
       </c>
       <c r="E193">
         <v>96</v>
@@ -5410,16 +5122,16 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="2">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B194">
-        <v>-20.136</v>
+        <v>32.34</v>
       </c>
       <c r="C194">
-        <v>909.698</v>
+        <v>314.688</v>
       </c>
       <c r="D194">
-        <v>909.698</v>
+        <v>314.688</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -5430,16 +5142,16 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="2">
-        <v>46138.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B195">
-        <v>-16.398</v>
+        <v>35.069</v>
       </c>
       <c r="C195">
-        <v>949.926</v>
+        <v>338.37</v>
       </c>
       <c r="D195">
-        <v>949.926</v>
+        <v>338.37</v>
       </c>
       <c r="E195">
         <v>2</v>
@@ -5450,16 +5162,16 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="2">
-        <v>46138.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B196">
-        <v>1.125</v>
+        <v>18.807</v>
       </c>
       <c r="C196">
-        <v>898.04</v>
+        <v>382.895</v>
       </c>
       <c r="D196">
-        <v>898.04</v>
+        <v>382.895</v>
       </c>
       <c r="E196">
         <v>3</v>
@@ -5470,16 +5182,16 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="2">
-        <v>46138.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B197">
-        <v>1.534</v>
+        <v>-5.121</v>
       </c>
       <c r="C197">
-        <v>270.599</v>
+        <v>896.693</v>
       </c>
       <c r="D197">
-        <v>270.599</v>
+        <v>896.693</v>
       </c>
       <c r="E197">
         <v>4</v>
@@ -5490,16 +5202,16 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="2">
-        <v>46138.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B198">
-        <v>-2.417</v>
+        <v>0.171</v>
       </c>
       <c r="C198">
-        <v>945.621</v>
+        <v>292.128</v>
       </c>
       <c r="D198">
-        <v>945.621</v>
+        <v>292.128</v>
       </c>
       <c r="E198">
         <v>5</v>
@@ -5510,16 +5222,16 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="2">
-        <v>46138.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B199">
-        <v>-31.449</v>
+        <v>12.158</v>
       </c>
       <c r="C199">
-        <v>933.703</v>
+        <v>322.456</v>
       </c>
       <c r="D199">
-        <v>933.703</v>
+        <v>322.456</v>
       </c>
       <c r="E199">
         <v>6</v>
@@ -5530,16 +5242,16 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="2">
-        <v>46138.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B200">
-        <v>-21.583</v>
+        <v>-1.229</v>
       </c>
       <c r="C200">
-        <v>967.509</v>
+        <v>899.5549999999999</v>
       </c>
       <c r="D200">
-        <v>967.509</v>
+        <v>899.5549999999999</v>
       </c>
       <c r="E200">
         <v>7</v>
@@ -5550,16 +5262,16 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="2">
-        <v>46138.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B201">
-        <v>-7.897</v>
+        <v>7.464</v>
       </c>
       <c r="C201">
-        <v>898.117</v>
+        <v>269.866</v>
       </c>
       <c r="D201">
-        <v>898.117</v>
+        <v>269.866</v>
       </c>
       <c r="E201">
         <v>8</v>
@@ -5570,16 +5282,16 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="2">
-        <v>46138.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B202">
-        <v>-32.871</v>
+        <v>-9.772</v>
       </c>
       <c r="C202">
-        <v>891.718</v>
+        <v>891.706</v>
       </c>
       <c r="D202">
-        <v>891.718</v>
+        <v>891.706</v>
       </c>
       <c r="E202">
         <v>9</v>
@@ -5590,16 +5302,16 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="2">
-        <v>46138.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B203">
-        <v>-43.755</v>
+        <v>-26.617</v>
       </c>
       <c r="C203">
-        <v>885.182</v>
+        <v>969.599</v>
       </c>
       <c r="D203">
-        <v>885.182</v>
+        <v>969.599</v>
       </c>
       <c r="E203">
         <v>10</v>
@@ -5610,16 +5322,16 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="2">
-        <v>46138.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B204">
-        <v>4.74</v>
+        <v>-19.434</v>
       </c>
       <c r="C204">
-        <v>400</v>
+        <v>1025.294</v>
       </c>
       <c r="D204">
-        <v>400</v>
+        <v>1025.294</v>
       </c>
       <c r="E204">
         <v>11</v>
@@ -5630,16 +5342,16 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="2">
-        <v>46138.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B205">
-        <v>3.061</v>
+        <v>-40.392</v>
       </c>
       <c r="C205">
-        <v>255.657</v>
+        <v>899.072</v>
       </c>
       <c r="D205">
-        <v>255.657</v>
+        <v>899.072</v>
       </c>
       <c r="E205">
         <v>12</v>
@@ -5650,16 +5362,16 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="2">
-        <v>46138.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B206">
-        <v>-13.829</v>
+        <v>-59.982</v>
       </c>
       <c r="C206">
-        <v>872.812</v>
+        <v>867.347</v>
       </c>
       <c r="D206">
-        <v>872.812</v>
+        <v>867.347</v>
       </c>
       <c r="E206">
         <v>13</v>
@@ -5670,16 +5382,16 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="2">
-        <v>46138.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B207">
-        <v>-7.477</v>
+        <v>-50.794</v>
       </c>
       <c r="C207">
-        <v>863.413</v>
+        <v>1317.847</v>
       </c>
       <c r="D207">
-        <v>863.413</v>
+        <v>1317.847</v>
       </c>
       <c r="E207">
         <v>14</v>
@@ -5690,16 +5402,16 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="2">
-        <v>46138.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B208">
-        <v>-8.798</v>
+        <v>-90.17100000000001</v>
       </c>
       <c r="C208">
-        <v>849.944</v>
+        <v>1488.527</v>
       </c>
       <c r="D208">
-        <v>849.944</v>
+        <v>1488.527</v>
       </c>
       <c r="E208">
         <v>15</v>
@@ -5710,16 +5422,16 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="2">
-        <v>46138.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B209">
-        <v>-10.385</v>
+        <v>-65.43899999999999</v>
       </c>
       <c r="C209">
-        <v>860.79</v>
+        <v>1081.54</v>
       </c>
       <c r="D209">
-        <v>860.79</v>
+        <v>1081.54</v>
       </c>
       <c r="E209">
         <v>16</v>
@@ -5730,16 +5442,16 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="2">
-        <v>46138.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B210">
-        <v>-3.14</v>
+        <v>-50.884</v>
       </c>
       <c r="C210">
-        <v>859.688</v>
+        <v>884.65</v>
       </c>
       <c r="D210">
-        <v>859.688</v>
+        <v>884.65</v>
       </c>
       <c r="E210">
         <v>17</v>
@@ -5750,16 +5462,16 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="2">
-        <v>46138.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B211">
-        <v>26.682</v>
+        <v>-66.774</v>
       </c>
       <c r="C211">
-        <v>241.351</v>
+        <v>1022.064</v>
       </c>
       <c r="D211">
-        <v>241.351</v>
+        <v>1022.064</v>
       </c>
       <c r="E211">
         <v>18</v>
@@ -5770,16 +5482,16 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="2">
-        <v>46138.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B212">
-        <v>47.769</v>
+        <v>-55.938</v>
       </c>
       <c r="C212">
-        <v>66.364</v>
+        <v>1174.276</v>
       </c>
       <c r="D212">
-        <v>66.364</v>
+        <v>1174.276</v>
       </c>
       <c r="E212">
         <v>19</v>
@@ -5790,16 +5502,16 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="2">
-        <v>46138.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B213">
-        <v>51.999</v>
+        <v>-22.406</v>
       </c>
       <c r="C213">
-        <v>118.938</v>
+        <v>1087.736</v>
       </c>
       <c r="D213">
-        <v>118.938</v>
+        <v>1087.736</v>
       </c>
       <c r="E213">
         <v>20</v>
@@ -5810,16 +5522,16 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="2">
-        <v>46138.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B214">
-        <v>54.64</v>
+        <v>-4.306</v>
       </c>
       <c r="C214">
-        <v>136.195</v>
+        <v>1006.148</v>
       </c>
       <c r="D214">
-        <v>136.195</v>
+        <v>1006.148</v>
       </c>
       <c r="E214">
         <v>21</v>
@@ -5830,16 +5542,16 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="2">
-        <v>46138.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B215">
-        <v>41.397</v>
+        <v>-20.98</v>
       </c>
       <c r="C215">
-        <v>-1851.687</v>
+        <v>1243.263</v>
       </c>
       <c r="D215">
-        <v>-1851.687</v>
+        <v>1243.263</v>
       </c>
       <c r="E215">
         <v>22</v>
@@ -5850,16 +5562,16 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="2">
-        <v>46138.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B216">
-        <v>29.54</v>
+        <v>-55.896</v>
       </c>
       <c r="C216">
-        <v>-2012.005</v>
+        <v>1619.01</v>
       </c>
       <c r="D216">
-        <v>-2012.005</v>
+        <v>1619.01</v>
       </c>
       <c r="E216">
         <v>23</v>
@@ -5870,16 +5582,16 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="2">
-        <v>46138.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B217">
-        <v>29.211</v>
+        <v>-64.786</v>
       </c>
       <c r="C217">
-        <v>-408.405</v>
+        <v>3050.067</v>
       </c>
       <c r="D217">
-        <v>-408.405</v>
+        <v>3050.067</v>
       </c>
       <c r="E217">
         <v>24</v>
@@ -5890,16 +5602,16 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" s="2">
-        <v>46138.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B218">
-        <v>8.637</v>
+        <v>-88.824</v>
       </c>
       <c r="C218">
-        <v>117.089</v>
+        <v>6023.555</v>
       </c>
       <c r="D218">
-        <v>117.089</v>
+        <v>6023.555</v>
       </c>
       <c r="E218">
         <v>25</v>
@@ -5910,16 +5622,16 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" s="2">
-        <v>46138.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B219">
-        <v>7.045</v>
+        <v>-142.337</v>
       </c>
       <c r="C219">
-        <v>127.051</v>
+        <v>5260.779</v>
       </c>
       <c r="D219">
-        <v>127.051</v>
+        <v>5260.779</v>
       </c>
       <c r="E219">
         <v>26</v>
@@ -5930,16 +5642,16 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="2">
-        <v>46138.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B220">
-        <v>17.889</v>
+        <v>-114.825</v>
       </c>
       <c r="C220">
-        <v>-524.4930000000001</v>
+        <v>1381.865</v>
       </c>
       <c r="D220">
-        <v>-524.4930000000001</v>
+        <v>1381.865</v>
       </c>
       <c r="E220">
         <v>27</v>
@@ -5950,16 +5662,16 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="2">
-        <v>46138.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B221">
-        <v>52.396</v>
+        <v>-126.472</v>
       </c>
       <c r="C221">
-        <v>-3147.368</v>
+        <v>1276.53</v>
       </c>
       <c r="D221">
-        <v>-3147.368</v>
+        <v>1276.53</v>
       </c>
       <c r="E221">
         <v>28</v>
@@ -5970,16 +5682,16 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="2">
-        <v>46138.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B222">
-        <v>45.271</v>
+        <v>-135.052</v>
       </c>
       <c r="C222">
-        <v>-1544.754</v>
+        <v>1083.479</v>
       </c>
       <c r="D222">
-        <v>-1544.754</v>
+        <v>1083.479</v>
       </c>
       <c r="E222">
         <v>29</v>
@@ -5990,16 +5702,16 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="2">
-        <v>46138.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B223">
-        <v>17.139</v>
+        <v>-139.143</v>
       </c>
       <c r="C223">
-        <v>-444.615</v>
+        <v>1103.259</v>
       </c>
       <c r="D223">
-        <v>-444.615</v>
+        <v>1103.259</v>
       </c>
       <c r="E223">
         <v>30</v>
@@ -6010,16 +5722,16 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="2">
-        <v>46138.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B224">
-        <v>3.486</v>
+        <v>-124.127</v>
       </c>
       <c r="C224">
-        <v>-11.13</v>
+        <v>1128.387</v>
       </c>
       <c r="D224">
-        <v>-11.13</v>
+        <v>1128.387</v>
       </c>
       <c r="E224">
         <v>31</v>
@@ -6030,16 +5742,16 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2">
-        <v>46138.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B225">
-        <v>-0.482</v>
+        <v>-106.561</v>
       </c>
       <c r="C225">
-        <v>-8.089</v>
+        <v>1101.335</v>
       </c>
       <c r="D225">
-        <v>-8.089</v>
+        <v>1101.335</v>
       </c>
       <c r="E225">
         <v>32</v>
@@ -6050,16 +5762,16 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="2">
-        <v>46138.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B226">
-        <v>-96.461</v>
+        <v>-72.571</v>
       </c>
       <c r="C226">
-        <v>4998.662</v>
+        <v>980.986</v>
       </c>
       <c r="D226">
-        <v>4998.662</v>
+        <v>980.986</v>
       </c>
       <c r="E226">
         <v>33</v>
@@ -6070,16 +5782,16 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="2">
-        <v>46138.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B227">
-        <v>-133.325</v>
+        <v>-81.511</v>
       </c>
       <c r="C227">
-        <v>4346.372</v>
+        <v>980.927</v>
       </c>
       <c r="D227">
-        <v>4346.372</v>
+        <v>980.927</v>
       </c>
       <c r="E227">
         <v>34</v>
@@ -6090,16 +5802,16 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" s="2">
-        <v>46138.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B228">
-        <v>-168.585</v>
+        <v>-32.585</v>
       </c>
       <c r="C228">
-        <v>436.147</v>
+        <v>981.746</v>
       </c>
       <c r="D228">
-        <v>436.147</v>
+        <v>981.746</v>
       </c>
       <c r="E228">
         <v>35</v>
@@ -6110,16 +5822,16 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="2">
-        <v>46138.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B229">
-        <v>-78.675</v>
+        <v>-1.26</v>
       </c>
       <c r="C229">
-        <v>448</v>
+        <v>980.76</v>
       </c>
       <c r="D229">
-        <v>448</v>
+        <v>980.76</v>
       </c>
       <c r="E229">
         <v>36</v>
@@ -6130,16 +5842,16 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="2">
-        <v>46138.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B230">
-        <v>-148.21</v>
+        <v>-29.41</v>
       </c>
       <c r="C230">
-        <v>516.943</v>
+        <v>696.89</v>
       </c>
       <c r="D230">
-        <v>516.943</v>
+        <v>696.89</v>
       </c>
       <c r="E230">
         <v>37</v>
@@ -6150,16 +5862,16 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="2">
-        <v>46138.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B231">
-        <v>-98.04900000000001</v>
+        <v>-3.986</v>
       </c>
       <c r="C231">
-        <v>447.811</v>
+        <v>0</v>
       </c>
       <c r="D231">
-        <v>447.811</v>
+        <v>0</v>
       </c>
       <c r="E231">
         <v>38</v>
@@ -6170,16 +5882,16 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="2">
-        <v>46138.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B232">
-        <v>3.215</v>
+        <v>47.843</v>
       </c>
       <c r="C232">
-        <v>-2644.325</v>
+        <v>-3451.259</v>
       </c>
       <c r="D232">
-        <v>-2644.325</v>
+        <v>-3451.259</v>
       </c>
       <c r="E232">
         <v>39</v>
@@ -6190,16 +5902,16 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="2">
-        <v>46138.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B233">
-        <v>17.853</v>
+        <v>26.882</v>
       </c>
       <c r="C233">
-        <v>-1251.864</v>
+        <v>-498.11</v>
       </c>
       <c r="D233">
-        <v>-1251.864</v>
+        <v>-498.11</v>
       </c>
       <c r="E233">
         <v>40</v>
@@ -6210,16 +5922,16 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="2">
-        <v>46138.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B234">
-        <v>53.449</v>
+        <v>28.258</v>
       </c>
       <c r="C234">
-        <v>-257.106</v>
+        <v>-363.328</v>
       </c>
       <c r="D234">
-        <v>-257.106</v>
+        <v>-363.328</v>
       </c>
       <c r="E234">
         <v>41</v>
@@ -6230,16 +5942,16 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" s="2">
-        <v>46138.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B235">
-        <v>66.271</v>
+        <v>53.554</v>
       </c>
       <c r="C235">
-        <v>-1970.07</v>
+        <v>-984.421</v>
       </c>
       <c r="D235">
-        <v>-1970.07</v>
+        <v>-984.421</v>
       </c>
       <c r="E235">
         <v>42</v>
@@ -6250,16 +5962,16 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="2">
-        <v>46138.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B236">
-        <v>106.808</v>
+        <v>56.093</v>
       </c>
       <c r="C236">
-        <v>-690.574</v>
+        <v>-282.93</v>
       </c>
       <c r="D236">
-        <v>-690.574</v>
+        <v>-282.93</v>
       </c>
       <c r="E236">
         <v>43</v>
@@ -6270,16 +5982,16 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" s="2">
-        <v>46138.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B237">
-        <v>65.99299999999999</v>
+        <v>16.53</v>
       </c>
       <c r="C237">
-        <v>-196.198</v>
+        <v>12.224</v>
       </c>
       <c r="D237">
-        <v>-196.198</v>
+        <v>12.224</v>
       </c>
       <c r="E237">
         <v>44</v>
@@ -6290,16 +6002,16 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="2">
-        <v>46138.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B238">
-        <v>32.992</v>
+        <v>-52.847</v>
       </c>
       <c r="C238">
-        <v>-57.454</v>
+        <v>3914.981</v>
       </c>
       <c r="D238">
-        <v>-57.454</v>
+        <v>3914.981</v>
       </c>
       <c r="E238">
         <v>45</v>
@@ -6310,16 +6022,16 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="2">
-        <v>46138.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B239">
-        <v>25.671</v>
+        <v>0</v>
       </c>
       <c r="C239">
-        <v>15.507</v>
+        <v>0</v>
       </c>
       <c r="D239">
-        <v>15.507</v>
+        <v>0</v>
       </c>
       <c r="E239">
         <v>46</v>
@@ -6330,16 +6042,16 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="2">
-        <v>46138.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B240">
-        <v>50.279</v>
+        <v>0</v>
       </c>
       <c r="C240">
-        <v>-113.433</v>
+        <v>0</v>
       </c>
       <c r="D240">
-        <v>-113.433</v>
+        <v>0</v>
       </c>
       <c r="E240">
         <v>47</v>
@@ -6350,16 +6062,16 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="2">
-        <v>46138.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B241">
-        <v>60.451</v>
+        <v>0</v>
       </c>
       <c r="C241">
-        <v>-762.825</v>
+        <v>0</v>
       </c>
       <c r="D241">
-        <v>-762.825</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>48</v>
@@ -6370,16 +6082,16 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" s="2">
-        <v>46138.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B242">
-        <v>76.503</v>
+        <v>0</v>
       </c>
       <c r="C242">
-        <v>-1506.036</v>
+        <v>0</v>
       </c>
       <c r="D242">
-        <v>-1506.036</v>
+        <v>0</v>
       </c>
       <c r="E242">
         <v>49</v>
@@ -6390,16 +6102,16 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" s="2">
-        <v>46138.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B243">
-        <v>93.69499999999999</v>
+        <v>0</v>
       </c>
       <c r="C243">
-        <v>-5198.447</v>
+        <v>0</v>
       </c>
       <c r="D243">
-        <v>-5198.447</v>
+        <v>0</v>
       </c>
       <c r="E243">
         <v>50</v>
@@ -6410,16 +6122,16 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="2">
-        <v>46138.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B244">
-        <v>111.405</v>
+        <v>0</v>
       </c>
       <c r="C244">
-        <v>-4657.286</v>
+        <v>0</v>
       </c>
       <c r="D244">
-        <v>-4657.286</v>
+        <v>0</v>
       </c>
       <c r="E244">
         <v>51</v>
@@ -6430,16 +6142,16 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="2">
-        <v>46138.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B245">
-        <v>122.023</v>
+        <v>0</v>
       </c>
       <c r="C245">
-        <v>-1366.13</v>
+        <v>0</v>
       </c>
       <c r="D245">
-        <v>-1366.13</v>
+        <v>0</v>
       </c>
       <c r="E245">
         <v>52</v>
@@ -6450,16 +6162,16 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="2">
-        <v>46138.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B246">
-        <v>143.015</v>
+        <v>0</v>
       </c>
       <c r="C246">
-        <v>-2641.154</v>
+        <v>0</v>
       </c>
       <c r="D246">
-        <v>-2641.154</v>
+        <v>0</v>
       </c>
       <c r="E246">
         <v>53</v>
@@ -6470,16 +6182,16 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="2">
-        <v>46138.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B247">
-        <v>149.552</v>
+        <v>0</v>
       </c>
       <c r="C247">
-        <v>-2575.747</v>
+        <v>0</v>
       </c>
       <c r="D247">
-        <v>-2575.747</v>
+        <v>0</v>
       </c>
       <c r="E247">
         <v>54</v>
@@ -6490,16 +6202,16 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="2">
-        <v>46138.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B248">
-        <v>159.818</v>
+        <v>0</v>
       </c>
       <c r="C248">
-        <v>-2341.085</v>
+        <v>0</v>
       </c>
       <c r="D248">
-        <v>-2341.085</v>
+        <v>0</v>
       </c>
       <c r="E248">
         <v>55</v>
@@ -6510,16 +6222,16 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="2">
-        <v>46138.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B249">
-        <v>168.07</v>
+        <v>0</v>
       </c>
       <c r="C249">
-        <v>-1549.507</v>
+        <v>0</v>
       </c>
       <c r="D249">
-        <v>-1549.507</v>
+        <v>0</v>
       </c>
       <c r="E249">
         <v>56</v>
@@ -6530,16 +6242,16 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="2">
-        <v>46138.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B250">
-        <v>192.031</v>
+        <v>0</v>
       </c>
       <c r="C250">
-        <v>-1593.836</v>
+        <v>0</v>
       </c>
       <c r="D250">
-        <v>-1593.836</v>
+        <v>0</v>
       </c>
       <c r="E250">
         <v>57</v>
@@ -6550,16 +6262,16 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="2">
-        <v>46138.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B251">
-        <v>152.803</v>
+        <v>0</v>
       </c>
       <c r="C251">
-        <v>-1064.527</v>
+        <v>0</v>
       </c>
       <c r="D251">
-        <v>-1064.527</v>
+        <v>0</v>
       </c>
       <c r="E251">
         <v>58</v>
@@ -6570,16 +6282,16 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="2">
-        <v>46138.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B252">
-        <v>140.513</v>
+        <v>0</v>
       </c>
       <c r="C252">
-        <v>-1030.91</v>
+        <v>0</v>
       </c>
       <c r="D252">
-        <v>-1030.91</v>
+        <v>0</v>
       </c>
       <c r="E252">
         <v>59</v>
@@ -6590,16 +6302,16 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="2">
-        <v>46138.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B253">
-        <v>132.503</v>
+        <v>0</v>
       </c>
       <c r="C253">
-        <v>-890.896</v>
+        <v>0</v>
       </c>
       <c r="D253">
-        <v>-890.896</v>
+        <v>0</v>
       </c>
       <c r="E253">
         <v>60</v>
@@ -6610,16 +6322,16 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="2">
-        <v>46138.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B254">
-        <v>148.324</v>
+        <v>0</v>
       </c>
       <c r="C254">
-        <v>-832.66</v>
+        <v>0</v>
       </c>
       <c r="D254">
-        <v>-832.66</v>
+        <v>0</v>
       </c>
       <c r="E254">
         <v>61</v>
@@ -6630,16 +6342,16 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="2">
-        <v>46138.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B255">
-        <v>104.431</v>
+        <v>0</v>
       </c>
       <c r="C255">
-        <v>-287.117</v>
+        <v>0</v>
       </c>
       <c r="D255">
-        <v>-287.117</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>62</v>
@@ -6650,16 +6362,16 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="2">
-        <v>46138.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B256">
-        <v>63.441</v>
+        <v>0</v>
       </c>
       <c r="C256">
-        <v>-295</v>
+        <v>0</v>
       </c>
       <c r="D256">
-        <v>-295</v>
+        <v>0</v>
       </c>
       <c r="E256">
         <v>63</v>
@@ -6670,16 +6382,16 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="2">
-        <v>46138.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B257">
-        <v>50.244</v>
+        <v>0</v>
       </c>
       <c r="C257">
-        <v>-165</v>
+        <v>0</v>
       </c>
       <c r="D257">
-        <v>-165</v>
+        <v>0</v>
       </c>
       <c r="E257">
         <v>64</v>
@@ -6690,16 +6402,16 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" s="2">
-        <v>46138.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B258">
-        <v>91.093</v>
+        <v>0</v>
       </c>
       <c r="C258">
-        <v>-185.252</v>
+        <v>0</v>
       </c>
       <c r="D258">
-        <v>-185.252</v>
+        <v>0</v>
       </c>
       <c r="E258">
         <v>65</v>
@@ -6710,16 +6422,16 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" s="2">
-        <v>46138.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B259">
-        <v>67.066</v>
+        <v>0</v>
       </c>
       <c r="C259">
-        <v>-703.057</v>
+        <v>0</v>
       </c>
       <c r="D259">
-        <v>-703.057</v>
+        <v>0</v>
       </c>
       <c r="E259">
         <v>66</v>
@@ -6730,16 +6442,16 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" s="2">
-        <v>46138.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B260">
-        <v>73.61799999999999</v>
+        <v>0</v>
       </c>
       <c r="C260">
-        <v>-716.418</v>
+        <v>0</v>
       </c>
       <c r="D260">
-        <v>-716.418</v>
+        <v>0</v>
       </c>
       <c r="E260">
         <v>67</v>
@@ -6750,16 +6462,16 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" s="2">
-        <v>46138.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B261">
-        <v>125.402</v>
+        <v>0</v>
       </c>
       <c r="C261">
-        <v>-82</v>
+        <v>0</v>
       </c>
       <c r="D261">
-        <v>-82</v>
+        <v>0</v>
       </c>
       <c r="E261">
         <v>68</v>
@@ -6770,16 +6482,16 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" s="2">
-        <v>46138.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B262">
-        <v>129.479</v>
+        <v>0</v>
       </c>
       <c r="C262">
-        <v>-4171.758</v>
+        <v>0</v>
       </c>
       <c r="D262">
-        <v>-4171.758</v>
+        <v>0</v>
       </c>
       <c r="E262">
         <v>69</v>
@@ -6790,16 +6502,16 @@
     </row>
     <row r="263" spans="1:6">
       <c r="A263" s="2">
-        <v>46138.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B263">
-        <v>63.249</v>
+        <v>0</v>
       </c>
       <c r="C263">
-        <v>-772.359</v>
+        <v>0</v>
       </c>
       <c r="D263">
-        <v>-772.359</v>
+        <v>0</v>
       </c>
       <c r="E263">
         <v>70</v>
@@ -6810,16 +6522,16 @@
     </row>
     <row r="264" spans="1:6">
       <c r="A264" s="2">
-        <v>46138.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B264">
-        <v>4.104</v>
+        <v>0</v>
       </c>
       <c r="C264">
-        <v>-165</v>
+        <v>0</v>
       </c>
       <c r="D264">
-        <v>-165</v>
+        <v>0</v>
       </c>
       <c r="E264">
         <v>71</v>
@@ -6830,16 +6542,16 @@
     </row>
     <row r="265" spans="1:6">
       <c r="A265" s="2">
-        <v>46138.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B265">
-        <v>50.843</v>
+        <v>0</v>
       </c>
       <c r="C265">
-        <v>0.413</v>
+        <v>0</v>
       </c>
       <c r="D265">
-        <v>0.413</v>
+        <v>0</v>
       </c>
       <c r="E265">
         <v>72</v>
@@ -6850,16 +6562,16 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" s="2">
-        <v>46138.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B266">
-        <v>44.362</v>
+        <v>0</v>
       </c>
       <c r="C266">
-        <v>-3.204</v>
+        <v>0</v>
       </c>
       <c r="D266">
-        <v>-3.204</v>
+        <v>0</v>
       </c>
       <c r="E266">
         <v>73</v>
@@ -6870,16 +6582,16 @@
     </row>
     <row r="267" spans="1:6">
       <c r="A267" s="2">
-        <v>46138.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B267">
-        <v>19.805</v>
+        <v>0</v>
       </c>
       <c r="C267">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D267">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E267">
         <v>74</v>
@@ -6890,16 +6602,16 @@
     </row>
     <row r="268" spans="1:6">
       <c r="A268" s="2">
-        <v>46138.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B268">
-        <v>43.164</v>
+        <v>0</v>
       </c>
       <c r="C268">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D268">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E268">
         <v>75</v>
@@ -6910,16 +6622,16 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" s="2">
-        <v>46138.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B269">
-        <v>5.551</v>
+        <v>0</v>
       </c>
       <c r="C269">
-        <v>276.01</v>
+        <v>0</v>
       </c>
       <c r="D269">
-        <v>276.01</v>
+        <v>0</v>
       </c>
       <c r="E269">
         <v>76</v>
@@ -6930,16 +6642,16 @@
     </row>
     <row r="270" spans="1:6">
       <c r="A270" s="2">
-        <v>46138.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B270">
-        <v>21.72</v>
+        <v>0</v>
       </c>
       <c r="C270">
-        <v>-36.113</v>
+        <v>0</v>
       </c>
       <c r="D270">
-        <v>-36.113</v>
+        <v>0</v>
       </c>
       <c r="E270">
         <v>77</v>
@@ -6950,16 +6662,16 @@
     </row>
     <row r="271" spans="1:6">
       <c r="A271" s="2">
-        <v>46138.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B271">
-        <v>15.27</v>
+        <v>0</v>
       </c>
       <c r="C271">
-        <v>270.973</v>
+        <v>0</v>
       </c>
       <c r="D271">
-        <v>270.973</v>
+        <v>0</v>
       </c>
       <c r="E271">
         <v>78</v>
@@ -6970,16 +6682,16 @@
     </row>
     <row r="272" spans="1:6">
       <c r="A272" s="2">
-        <v>46138.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B272">
-        <v>-8.609999999999999</v>
+        <v>0</v>
       </c>
       <c r="C272">
-        <v>957.904</v>
+        <v>0</v>
       </c>
       <c r="D272">
-        <v>957.904</v>
+        <v>0</v>
       </c>
       <c r="E272">
         <v>79</v>
@@ -6990,16 +6702,16 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" s="2">
-        <v>46138.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B273">
-        <v>-25.381</v>
+        <v>0</v>
       </c>
       <c r="C273">
-        <v>2177.185</v>
+        <v>0</v>
       </c>
       <c r="D273">
-        <v>2177.185</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>80</v>
@@ -7010,16 +6722,16 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" s="2">
-        <v>46138.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B274">
-        <v>-36.257</v>
+        <v>0</v>
       </c>
       <c r="C274">
-        <v>1240.081</v>
+        <v>0</v>
       </c>
       <c r="D274">
-        <v>1240.081</v>
+        <v>0</v>
       </c>
       <c r="E274">
         <v>81</v>
@@ -7030,16 +6742,16 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" s="2">
-        <v>46138.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B275">
-        <v>-54.847</v>
+        <v>0</v>
       </c>
       <c r="C275">
-        <v>1725.198</v>
+        <v>0</v>
       </c>
       <c r="D275">
-        <v>1725.198</v>
+        <v>0</v>
       </c>
       <c r="E275">
         <v>82</v>
@@ -7050,16 +6762,16 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" s="2">
-        <v>46138.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B276">
-        <v>-95.38500000000001</v>
+        <v>0</v>
       </c>
       <c r="C276">
-        <v>3456.674</v>
+        <v>0</v>
       </c>
       <c r="D276">
-        <v>3456.674</v>
+        <v>0</v>
       </c>
       <c r="E276">
         <v>83</v>
@@ -7070,16 +6782,16 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" s="2">
-        <v>46138.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B277">
-        <v>-65.09</v>
+        <v>0</v>
       </c>
       <c r="C277">
-        <v>4086.197</v>
+        <v>0</v>
       </c>
       <c r="D277">
-        <v>4086.197</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>84</v>
@@ -7090,16 +6802,16 @@
     </row>
     <row r="278" spans="1:6">
       <c r="A278" s="2">
-        <v>46138.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B278">
-        <v>-79.583</v>
+        <v>0</v>
       </c>
       <c r="C278">
-        <v>6571.524</v>
+        <v>0</v>
       </c>
       <c r="D278">
-        <v>6571.524</v>
+        <v>0</v>
       </c>
       <c r="E278">
         <v>85</v>
@@ -7110,16 +6822,16 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" s="2">
-        <v>46138.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B279">
-        <v>-110.769</v>
+        <v>0</v>
       </c>
       <c r="C279">
-        <v>5213.072</v>
+        <v>0</v>
       </c>
       <c r="D279">
-        <v>5213.072</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>86</v>
@@ -7130,16 +6842,16 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" s="2">
-        <v>46138.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B280">
-        <v>-90.55</v>
+        <v>0</v>
       </c>
       <c r="C280">
-        <v>4574.334</v>
+        <v>0</v>
       </c>
       <c r="D280">
-        <v>4574.334</v>
+        <v>0</v>
       </c>
       <c r="E280">
         <v>87</v>
@@ -7150,16 +6862,16 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" s="2">
-        <v>46138.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B281">
-        <v>-78.92100000000001</v>
+        <v>0</v>
       </c>
       <c r="C281">
-        <v>3222.109</v>
+        <v>0</v>
       </c>
       <c r="D281">
-        <v>3222.109</v>
+        <v>0</v>
       </c>
       <c r="E281">
         <v>88</v>
@@ -7170,16 +6882,16 @@
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="2">
-        <v>46138.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B282">
-        <v>-89.396</v>
+        <v>0</v>
       </c>
       <c r="C282">
-        <v>1869.966</v>
+        <v>0</v>
       </c>
       <c r="D282">
-        <v>1869.966</v>
+        <v>0</v>
       </c>
       <c r="E282">
         <v>89</v>
@@ -7190,16 +6902,16 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" s="2">
-        <v>46138.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B283">
-        <v>-68.745</v>
+        <v>0</v>
       </c>
       <c r="C283">
-        <v>4256.604</v>
+        <v>0</v>
       </c>
       <c r="D283">
-        <v>4256.604</v>
+        <v>0</v>
       </c>
       <c r="E283">
         <v>90</v>
@@ -7210,16 +6922,16 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" s="2">
-        <v>46138.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B284">
-        <v>-79.286</v>
+        <v>0</v>
       </c>
       <c r="C284">
-        <v>4554.097</v>
+        <v>0</v>
       </c>
       <c r="D284">
-        <v>4554.097</v>
+        <v>0</v>
       </c>
       <c r="E284">
         <v>91</v>
@@ -7230,16 +6942,16 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" s="2">
-        <v>46138.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B285">
-        <v>-99.532</v>
+        <v>0</v>
       </c>
       <c r="C285">
-        <v>2333.476</v>
+        <v>0</v>
       </c>
       <c r="D285">
-        <v>2333.476</v>
+        <v>0</v>
       </c>
       <c r="E285">
         <v>92</v>
@@ -7250,16 +6962,16 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="2">
-        <v>46138.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B286">
-        <v>-78.67</v>
+        <v>0</v>
       </c>
       <c r="C286">
-        <v>1078.473</v>
+        <v>0</v>
       </c>
       <c r="D286">
-        <v>1078.473</v>
+        <v>0</v>
       </c>
       <c r="E286">
         <v>93</v>
@@ -7270,16 +6982,16 @@
     </row>
     <row r="287" spans="1:6">
       <c r="A287" s="2">
-        <v>46138.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B287">
-        <v>-32.204</v>
+        <v>0</v>
       </c>
       <c r="C287">
-        <v>1065.02</v>
+        <v>0</v>
       </c>
       <c r="D287">
-        <v>1065.02</v>
+        <v>0</v>
       </c>
       <c r="E287">
         <v>94</v>
@@ -7290,16 +7002,16 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" s="2">
-        <v>46138.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B288">
-        <v>36.912</v>
+        <v>0</v>
       </c>
       <c r="C288">
-        <v>-3291.851</v>
+        <v>0</v>
       </c>
       <c r="D288">
-        <v>-3291.851</v>
+        <v>0</v>
       </c>
       <c r="E288">
         <v>95</v>
@@ -7310,1942 +7022,22 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="2">
-        <v>46138.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B289">
-        <v>64.57899999999999</v>
+        <v>0</v>
       </c>
       <c r="C289">
-        <v>-3636.358</v>
+        <v>0</v>
       </c>
       <c r="D289">
-        <v>-3636.358</v>
+        <v>0</v>
       </c>
       <c r="E289">
         <v>96</v>
       </c>
       <c r="F289" t="s">
         <v>293</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6">
-      <c r="A290" s="2">
-        <v>46139</v>
-      </c>
-      <c r="B290">
-        <v>140.004</v>
-      </c>
-      <c r="C290">
-        <v>-1314.902</v>
-      </c>
-      <c r="D290">
-        <v>-1314.902</v>
-      </c>
-      <c r="E290">
-        <v>1</v>
-      </c>
-      <c r="F290" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
-      <c r="A291" s="2">
-        <v>46139.01041666666</v>
-      </c>
-      <c r="B291">
-        <v>158.374</v>
-      </c>
-      <c r="C291">
-        <v>76.37</v>
-      </c>
-      <c r="D291">
-        <v>76.37</v>
-      </c>
-      <c r="E291">
-        <v>2</v>
-      </c>
-      <c r="F291" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6">
-      <c r="A292" s="2">
-        <v>46139.02083333334</v>
-      </c>
-      <c r="B292">
-        <v>122.708</v>
-      </c>
-      <c r="C292">
-        <v>4.256</v>
-      </c>
-      <c r="D292">
-        <v>4.256</v>
-      </c>
-      <c r="E292">
-        <v>3</v>
-      </c>
-      <c r="F292" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6">
-      <c r="A293" s="2">
-        <v>46139.03125</v>
-      </c>
-      <c r="B293">
-        <v>60.282</v>
-      </c>
-      <c r="C293">
-        <v>3.801</v>
-      </c>
-      <c r="D293">
-        <v>3.801</v>
-      </c>
-      <c r="E293">
-        <v>4</v>
-      </c>
-      <c r="F293" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6">
-      <c r="A294" s="2">
-        <v>46139.04166666666</v>
-      </c>
-      <c r="B294">
-        <v>66.09399999999999</v>
-      </c>
-      <c r="C294">
-        <v>4.62</v>
-      </c>
-      <c r="D294">
-        <v>4.62</v>
-      </c>
-      <c r="E294">
-        <v>5</v>
-      </c>
-      <c r="F294" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
-      <c r="A295" s="2">
-        <v>46139.05208333334</v>
-      </c>
-      <c r="B295">
-        <v>60.975</v>
-      </c>
-      <c r="C295">
-        <v>2.203</v>
-      </c>
-      <c r="D295">
-        <v>2.203</v>
-      </c>
-      <c r="E295">
-        <v>6</v>
-      </c>
-      <c r="F295" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6">
-      <c r="A296" s="2">
-        <v>46139.0625</v>
-      </c>
-      <c r="B296">
-        <v>30.817</v>
-      </c>
-      <c r="C296">
-        <v>0.5</v>
-      </c>
-      <c r="D296">
-        <v>0.5</v>
-      </c>
-      <c r="E296">
-        <v>7</v>
-      </c>
-      <c r="F296" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6">
-      <c r="A297" s="2">
-        <v>46139.07291666666</v>
-      </c>
-      <c r="B297">
-        <v>60.497</v>
-      </c>
-      <c r="C297">
-        <v>1.907</v>
-      </c>
-      <c r="D297">
-        <v>1.907</v>
-      </c>
-      <c r="E297">
-        <v>8</v>
-      </c>
-      <c r="F297" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6">
-      <c r="A298" s="2">
-        <v>46139.08333333334</v>
-      </c>
-      <c r="B298">
-        <v>117.696</v>
-      </c>
-      <c r="C298">
-        <v>-1689.276</v>
-      </c>
-      <c r="D298">
-        <v>-1689.276</v>
-      </c>
-      <c r="E298">
-        <v>9</v>
-      </c>
-      <c r="F298" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6">
-      <c r="A299" s="2">
-        <v>46139.09375</v>
-      </c>
-      <c r="B299">
-        <v>139.115</v>
-      </c>
-      <c r="C299">
-        <v>-1971.872</v>
-      </c>
-      <c r="D299">
-        <v>-1971.872</v>
-      </c>
-      <c r="E299">
-        <v>10</v>
-      </c>
-      <c r="F299" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6">
-      <c r="A300" s="2">
-        <v>46139.10416666666</v>
-      </c>
-      <c r="B300">
-        <v>75.628</v>
-      </c>
-      <c r="C300">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="D300">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="E300">
-        <v>11</v>
-      </c>
-      <c r="F300" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6">
-      <c r="A301" s="2">
-        <v>46139.11458333334</v>
-      </c>
-      <c r="B301">
-        <v>76.35299999999999</v>
-      </c>
-      <c r="C301">
-        <v>13.109</v>
-      </c>
-      <c r="D301">
-        <v>13.109</v>
-      </c>
-      <c r="E301">
-        <v>12</v>
-      </c>
-      <c r="F301" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6">
-      <c r="A302" s="2">
-        <v>46139.125</v>
-      </c>
-      <c r="B302">
-        <v>68.977</v>
-      </c>
-      <c r="C302">
-        <v>3.787</v>
-      </c>
-      <c r="D302">
-        <v>3.787</v>
-      </c>
-      <c r="E302">
-        <v>13</v>
-      </c>
-      <c r="F302" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6">
-      <c r="A303" s="2">
-        <v>46139.13541666666</v>
-      </c>
-      <c r="B303">
-        <v>59.734</v>
-      </c>
-      <c r="C303">
-        <v>2.122</v>
-      </c>
-      <c r="D303">
-        <v>2.122</v>
-      </c>
-      <c r="E303">
-        <v>14</v>
-      </c>
-      <c r="F303" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6">
-      <c r="A304" s="2">
-        <v>46139.14583333334</v>
-      </c>
-      <c r="B304">
-        <v>138.501</v>
-      </c>
-      <c r="C304">
-        <v>3.834</v>
-      </c>
-      <c r="D304">
-        <v>3.834</v>
-      </c>
-      <c r="E304">
-        <v>15</v>
-      </c>
-      <c r="F304" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6">
-      <c r="A305" s="2">
-        <v>46139.15625</v>
-      </c>
-      <c r="B305">
-        <v>125.856</v>
-      </c>
-      <c r="C305">
-        <v>1.688</v>
-      </c>
-      <c r="D305">
-        <v>1.688</v>
-      </c>
-      <c r="E305">
-        <v>16</v>
-      </c>
-      <c r="F305" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6">
-      <c r="A306" s="2">
-        <v>46139.16666666666</v>
-      </c>
-      <c r="B306">
-        <v>25.584</v>
-      </c>
-      <c r="C306">
-        <v>0.6</v>
-      </c>
-      <c r="D306">
-        <v>0.6</v>
-      </c>
-      <c r="E306">
-        <v>17</v>
-      </c>
-      <c r="F306" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6">
-      <c r="A307" s="2">
-        <v>46139.17708333334</v>
-      </c>
-      <c r="B307">
-        <v>-25.932</v>
-      </c>
-      <c r="C307">
-        <v>988.99</v>
-      </c>
-      <c r="D307">
-        <v>988.99</v>
-      </c>
-      <c r="E307">
-        <v>18</v>
-      </c>
-      <c r="F307" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6">
-      <c r="A308" s="2">
-        <v>46139.1875</v>
-      </c>
-      <c r="B308">
-        <v>-25.206</v>
-      </c>
-      <c r="C308">
-        <v>2662.526</v>
-      </c>
-      <c r="D308">
-        <v>2662.526</v>
-      </c>
-      <c r="E308">
-        <v>19</v>
-      </c>
-      <c r="F308" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6">
-      <c r="A309" s="2">
-        <v>46139.19791666666</v>
-      </c>
-      <c r="B309">
-        <v>-19.353</v>
-      </c>
-      <c r="C309">
-        <v>1547.525</v>
-      </c>
-      <c r="D309">
-        <v>1547.525</v>
-      </c>
-      <c r="E309">
-        <v>20</v>
-      </c>
-      <c r="F309" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6">
-      <c r="A310" s="2">
-        <v>46139.20833333334</v>
-      </c>
-      <c r="B310">
-        <v>-33.354</v>
-      </c>
-      <c r="C310">
-        <v>1607.849</v>
-      </c>
-      <c r="D310">
-        <v>1607.849</v>
-      </c>
-      <c r="E310">
-        <v>21</v>
-      </c>
-      <c r="F310" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6">
-      <c r="A311" s="2">
-        <v>46139.21875</v>
-      </c>
-      <c r="B311">
-        <v>0.226</v>
-      </c>
-      <c r="C311">
-        <v>341.474</v>
-      </c>
-      <c r="D311">
-        <v>341.474</v>
-      </c>
-      <c r="E311">
-        <v>22</v>
-      </c>
-      <c r="F311" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6">
-      <c r="A312" s="2">
-        <v>46139.22916666666</v>
-      </c>
-      <c r="B312">
-        <v>-0.263</v>
-      </c>
-      <c r="C312">
-        <v>939.401</v>
-      </c>
-      <c r="D312">
-        <v>939.401</v>
-      </c>
-      <c r="E312">
-        <v>23</v>
-      </c>
-      <c r="F312" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6">
-      <c r="A313" s="2">
-        <v>46139.23958333334</v>
-      </c>
-      <c r="B313">
-        <v>-4.182</v>
-      </c>
-      <c r="C313">
-        <v>961.6950000000001</v>
-      </c>
-      <c r="D313">
-        <v>961.6950000000001</v>
-      </c>
-      <c r="E313">
-        <v>24</v>
-      </c>
-      <c r="F313" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6">
-      <c r="A314" s="2">
-        <v>46139.25</v>
-      </c>
-      <c r="B314">
-        <v>36.265</v>
-      </c>
-      <c r="C314">
-        <v>-106.121</v>
-      </c>
-      <c r="D314">
-        <v>-106.121</v>
-      </c>
-      <c r="E314">
-        <v>25</v>
-      </c>
-      <c r="F314" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6">
-      <c r="A315" s="2">
-        <v>46139.26041666666</v>
-      </c>
-      <c r="B315">
-        <v>42.64</v>
-      </c>
-      <c r="C315">
-        <v>334.08</v>
-      </c>
-      <c r="D315">
-        <v>334.08</v>
-      </c>
-      <c r="E315">
-        <v>26</v>
-      </c>
-      <c r="F315" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6">
-      <c r="A316" s="2">
-        <v>46139.27083333334</v>
-      </c>
-      <c r="B316">
-        <v>21.409</v>
-      </c>
-      <c r="C316">
-        <v>162.782</v>
-      </c>
-      <c r="D316">
-        <v>162.782</v>
-      </c>
-      <c r="E316">
-        <v>27</v>
-      </c>
-      <c r="F316" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6">
-      <c r="A317" s="2">
-        <v>46139.28125</v>
-      </c>
-      <c r="B317">
-        <v>23.237</v>
-      </c>
-      <c r="C317">
-        <v>-436.125</v>
-      </c>
-      <c r="D317">
-        <v>-436.125</v>
-      </c>
-      <c r="E317">
-        <v>28</v>
-      </c>
-      <c r="F317" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6">
-      <c r="A318" s="2">
-        <v>46139.29166666666</v>
-      </c>
-      <c r="B318">
-        <v>32.175</v>
-      </c>
-      <c r="C318">
-        <v>-527.456</v>
-      </c>
-      <c r="D318">
-        <v>-527.456</v>
-      </c>
-      <c r="E318">
-        <v>29</v>
-      </c>
-      <c r="F318" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6">
-      <c r="A319" s="2">
-        <v>46139.30208333334</v>
-      </c>
-      <c r="B319">
-        <v>35.968</v>
-      </c>
-      <c r="C319">
-        <v>-494.599</v>
-      </c>
-      <c r="D319">
-        <v>-494.599</v>
-      </c>
-      <c r="E319">
-        <v>30</v>
-      </c>
-      <c r="F319" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6">
-      <c r="A320" s="2">
-        <v>46139.3125</v>
-      </c>
-      <c r="B320">
-        <v>49.268</v>
-      </c>
-      <c r="C320">
-        <v>-11.454</v>
-      </c>
-      <c r="D320">
-        <v>-11.454</v>
-      </c>
-      <c r="E320">
-        <v>31</v>
-      </c>
-      <c r="F320" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6">
-      <c r="A321" s="2">
-        <v>46139.32291666666</v>
-      </c>
-      <c r="B321">
-        <v>83.163</v>
-      </c>
-      <c r="C321">
-        <v>-359.979</v>
-      </c>
-      <c r="D321">
-        <v>-359.979</v>
-      </c>
-      <c r="E321">
-        <v>32</v>
-      </c>
-      <c r="F321" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6">
-      <c r="A322" s="2">
-        <v>46139.33333333334</v>
-      </c>
-      <c r="B322">
-        <v>99.53</v>
-      </c>
-      <c r="C322">
-        <v>-752.978</v>
-      </c>
-      <c r="D322">
-        <v>-752.978</v>
-      </c>
-      <c r="E322">
-        <v>33</v>
-      </c>
-      <c r="F322" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6">
-      <c r="A323" s="2">
-        <v>46139.34375</v>
-      </c>
-      <c r="B323">
-        <v>73.666</v>
-      </c>
-      <c r="C323">
-        <v>-84.887</v>
-      </c>
-      <c r="D323">
-        <v>-84.887</v>
-      </c>
-      <c r="E323">
-        <v>34</v>
-      </c>
-      <c r="F323" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6">
-      <c r="A324" s="2">
-        <v>46139.35416666666</v>
-      </c>
-      <c r="B324">
-        <v>74.98399999999999</v>
-      </c>
-      <c r="C324">
-        <v>-8.407999999999999</v>
-      </c>
-      <c r="D324">
-        <v>-8.407999999999999</v>
-      </c>
-      <c r="E324">
-        <v>35</v>
-      </c>
-      <c r="F324" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="325" spans="1:6">
-      <c r="A325" s="2">
-        <v>46139.36458333334</v>
-      </c>
-      <c r="B325">
-        <v>76.70099999999999</v>
-      </c>
-      <c r="C325">
-        <v>-43.964</v>
-      </c>
-      <c r="D325">
-        <v>-43.964</v>
-      </c>
-      <c r="E325">
-        <v>36</v>
-      </c>
-      <c r="F325" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6">
-      <c r="A326" s="2">
-        <v>46139.375</v>
-      </c>
-      <c r="B326">
-        <v>1.05</v>
-      </c>
-      <c r="C326">
-        <v>5.11</v>
-      </c>
-      <c r="D326">
-        <v>5.11</v>
-      </c>
-      <c r="E326">
-        <v>37</v>
-      </c>
-      <c r="F326" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6">
-      <c r="A327" s="2">
-        <v>46139.38541666666</v>
-      </c>
-      <c r="B327">
-        <v>24.699</v>
-      </c>
-      <c r="C327">
-        <v>2.002</v>
-      </c>
-      <c r="D327">
-        <v>2.002</v>
-      </c>
-      <c r="E327">
-        <v>38</v>
-      </c>
-      <c r="F327" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6">
-      <c r="A328" s="2">
-        <v>46139.39583333334</v>
-      </c>
-      <c r="B328">
-        <v>74.232</v>
-      </c>
-      <c r="C328">
-        <v>-45.815</v>
-      </c>
-      <c r="D328">
-        <v>-45.815</v>
-      </c>
-      <c r="E328">
-        <v>39</v>
-      </c>
-      <c r="F328" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6">
-      <c r="A329" s="2">
-        <v>46139.40625</v>
-      </c>
-      <c r="B329">
-        <v>100.925</v>
-      </c>
-      <c r="C329">
-        <v>-488.561</v>
-      </c>
-      <c r="D329">
-        <v>-488.561</v>
-      </c>
-      <c r="E329">
-        <v>40</v>
-      </c>
-      <c r="F329" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6">
-      <c r="A330" s="2">
-        <v>46139.41666666666</v>
-      </c>
-      <c r="B330">
-        <v>54.484</v>
-      </c>
-      <c r="C330">
-        <v>-202.984</v>
-      </c>
-      <c r="D330">
-        <v>-202.984</v>
-      </c>
-      <c r="E330">
-        <v>41</v>
-      </c>
-      <c r="F330" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6">
-      <c r="A331" s="2">
-        <v>46139.42708333334</v>
-      </c>
-      <c r="B331">
-        <v>28.842</v>
-      </c>
-      <c r="C331">
-        <v>-105.208</v>
-      </c>
-      <c r="D331">
-        <v>-105.208</v>
-      </c>
-      <c r="E331">
-        <v>42</v>
-      </c>
-      <c r="F331" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6">
-      <c r="A332" s="2">
-        <v>46139.4375</v>
-      </c>
-      <c r="B332">
-        <v>59.555</v>
-      </c>
-      <c r="C332">
-        <v>-105.717</v>
-      </c>
-      <c r="D332">
-        <v>-105.717</v>
-      </c>
-      <c r="E332">
-        <v>43</v>
-      </c>
-      <c r="F332" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6">
-      <c r="A333" s="2">
-        <v>46139.44791666666</v>
-      </c>
-      <c r="B333">
-        <v>78.38800000000001</v>
-      </c>
-      <c r="C333">
-        <v>-125.809</v>
-      </c>
-      <c r="D333">
-        <v>-125.809</v>
-      </c>
-      <c r="E333">
-        <v>44</v>
-      </c>
-      <c r="F333" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6">
-      <c r="A334" s="2">
-        <v>46139.45833333334</v>
-      </c>
-      <c r="B334">
-        <v>55.47</v>
-      </c>
-      <c r="C334">
-        <v>-290.094</v>
-      </c>
-      <c r="D334">
-        <v>-290.094</v>
-      </c>
-      <c r="E334">
-        <v>45</v>
-      </c>
-      <c r="F334" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6">
-      <c r="A335" s="2">
-        <v>46139.46875</v>
-      </c>
-      <c r="B335">
-        <v>0</v>
-      </c>
-      <c r="C335">
-        <v>0</v>
-      </c>
-      <c r="D335">
-        <v>0</v>
-      </c>
-      <c r="E335">
-        <v>46</v>
-      </c>
-      <c r="F335" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6">
-      <c r="A336" s="2">
-        <v>46139.47916666666</v>
-      </c>
-      <c r="B336">
-        <v>0</v>
-      </c>
-      <c r="C336">
-        <v>0</v>
-      </c>
-      <c r="D336">
-        <v>0</v>
-      </c>
-      <c r="E336">
-        <v>47</v>
-      </c>
-      <c r="F336" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6">
-      <c r="A337" s="2">
-        <v>46139.48958333334</v>
-      </c>
-      <c r="B337">
-        <v>0</v>
-      </c>
-      <c r="C337">
-        <v>0</v>
-      </c>
-      <c r="D337">
-        <v>0</v>
-      </c>
-      <c r="E337">
-        <v>48</v>
-      </c>
-      <c r="F337" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6">
-      <c r="A338" s="2">
-        <v>46139.5</v>
-      </c>
-      <c r="B338">
-        <v>0</v>
-      </c>
-      <c r="C338">
-        <v>0</v>
-      </c>
-      <c r="D338">
-        <v>0</v>
-      </c>
-      <c r="E338">
-        <v>49</v>
-      </c>
-      <c r="F338" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6">
-      <c r="A339" s="2">
-        <v>46139.51041666666</v>
-      </c>
-      <c r="B339">
-        <v>0</v>
-      </c>
-      <c r="C339">
-        <v>0</v>
-      </c>
-      <c r="D339">
-        <v>0</v>
-      </c>
-      <c r="E339">
-        <v>50</v>
-      </c>
-      <c r="F339" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6">
-      <c r="A340" s="2">
-        <v>46139.52083333334</v>
-      </c>
-      <c r="B340">
-        <v>0</v>
-      </c>
-      <c r="C340">
-        <v>0</v>
-      </c>
-      <c r="D340">
-        <v>0</v>
-      </c>
-      <c r="E340">
-        <v>51</v>
-      </c>
-      <c r="F340" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6">
-      <c r="A341" s="2">
-        <v>46139.53125</v>
-      </c>
-      <c r="B341">
-        <v>0</v>
-      </c>
-      <c r="C341">
-        <v>0</v>
-      </c>
-      <c r="D341">
-        <v>0</v>
-      </c>
-      <c r="E341">
-        <v>52</v>
-      </c>
-      <c r="F341" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="342" spans="1:6">
-      <c r="A342" s="2">
-        <v>46139.54166666666</v>
-      </c>
-      <c r="B342">
-        <v>0</v>
-      </c>
-      <c r="C342">
-        <v>0</v>
-      </c>
-      <c r="D342">
-        <v>0</v>
-      </c>
-      <c r="E342">
-        <v>53</v>
-      </c>
-      <c r="F342" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="343" spans="1:6">
-      <c r="A343" s="2">
-        <v>46139.55208333334</v>
-      </c>
-      <c r="B343">
-        <v>0</v>
-      </c>
-      <c r="C343">
-        <v>0</v>
-      </c>
-      <c r="D343">
-        <v>0</v>
-      </c>
-      <c r="E343">
-        <v>54</v>
-      </c>
-      <c r="F343" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="344" spans="1:6">
-      <c r="A344" s="2">
-        <v>46139.5625</v>
-      </c>
-      <c r="B344">
-        <v>0</v>
-      </c>
-      <c r="C344">
-        <v>0</v>
-      </c>
-      <c r="D344">
-        <v>0</v>
-      </c>
-      <c r="E344">
-        <v>55</v>
-      </c>
-      <c r="F344" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6">
-      <c r="A345" s="2">
-        <v>46139.57291666666</v>
-      </c>
-      <c r="B345">
-        <v>0</v>
-      </c>
-      <c r="C345">
-        <v>0</v>
-      </c>
-      <c r="D345">
-        <v>0</v>
-      </c>
-      <c r="E345">
-        <v>56</v>
-      </c>
-      <c r="F345" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="346" spans="1:6">
-      <c r="A346" s="2">
-        <v>46139.58333333334</v>
-      </c>
-      <c r="B346">
-        <v>0</v>
-      </c>
-      <c r="C346">
-        <v>0</v>
-      </c>
-      <c r="D346">
-        <v>0</v>
-      </c>
-      <c r="E346">
-        <v>57</v>
-      </c>
-      <c r="F346" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="347" spans="1:6">
-      <c r="A347" s="2">
-        <v>46139.59375</v>
-      </c>
-      <c r="B347">
-        <v>0</v>
-      </c>
-      <c r="C347">
-        <v>0</v>
-      </c>
-      <c r="D347">
-        <v>0</v>
-      </c>
-      <c r="E347">
-        <v>58</v>
-      </c>
-      <c r="F347" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6">
-      <c r="A348" s="2">
-        <v>46139.60416666666</v>
-      </c>
-      <c r="B348">
-        <v>0</v>
-      </c>
-      <c r="C348">
-        <v>0</v>
-      </c>
-      <c r="D348">
-        <v>0</v>
-      </c>
-      <c r="E348">
-        <v>59</v>
-      </c>
-      <c r="F348" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6">
-      <c r="A349" s="2">
-        <v>46139.61458333334</v>
-      </c>
-      <c r="B349">
-        <v>0</v>
-      </c>
-      <c r="C349">
-        <v>0</v>
-      </c>
-      <c r="D349">
-        <v>0</v>
-      </c>
-      <c r="E349">
-        <v>60</v>
-      </c>
-      <c r="F349" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="350" spans="1:6">
-      <c r="A350" s="2">
-        <v>46139.625</v>
-      </c>
-      <c r="B350">
-        <v>0</v>
-      </c>
-      <c r="C350">
-        <v>0</v>
-      </c>
-      <c r="D350">
-        <v>0</v>
-      </c>
-      <c r="E350">
-        <v>61</v>
-      </c>
-      <c r="F350" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6">
-      <c r="A351" s="2">
-        <v>46139.63541666666</v>
-      </c>
-      <c r="B351">
-        <v>0</v>
-      </c>
-      <c r="C351">
-        <v>0</v>
-      </c>
-      <c r="D351">
-        <v>0</v>
-      </c>
-      <c r="E351">
-        <v>62</v>
-      </c>
-      <c r="F351" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="352" spans="1:6">
-      <c r="A352" s="2">
-        <v>46139.64583333334</v>
-      </c>
-      <c r="B352">
-        <v>0</v>
-      </c>
-      <c r="C352">
-        <v>0</v>
-      </c>
-      <c r="D352">
-        <v>0</v>
-      </c>
-      <c r="E352">
-        <v>63</v>
-      </c>
-      <c r="F352" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6">
-      <c r="A353" s="2">
-        <v>46139.65625</v>
-      </c>
-      <c r="B353">
-        <v>0</v>
-      </c>
-      <c r="C353">
-        <v>0</v>
-      </c>
-      <c r="D353">
-        <v>0</v>
-      </c>
-      <c r="E353">
-        <v>64</v>
-      </c>
-      <c r="F353" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6">
-      <c r="A354" s="2">
-        <v>46139.66666666666</v>
-      </c>
-      <c r="B354">
-        <v>0</v>
-      </c>
-      <c r="C354">
-        <v>0</v>
-      </c>
-      <c r="D354">
-        <v>0</v>
-      </c>
-      <c r="E354">
-        <v>65</v>
-      </c>
-      <c r="F354" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6">
-      <c r="A355" s="2">
-        <v>46139.67708333334</v>
-      </c>
-      <c r="B355">
-        <v>0</v>
-      </c>
-      <c r="C355">
-        <v>0</v>
-      </c>
-      <c r="D355">
-        <v>0</v>
-      </c>
-      <c r="E355">
-        <v>66</v>
-      </c>
-      <c r="F355" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6">
-      <c r="A356" s="2">
-        <v>46139.6875</v>
-      </c>
-      <c r="B356">
-        <v>0</v>
-      </c>
-      <c r="C356">
-        <v>0</v>
-      </c>
-      <c r="D356">
-        <v>0</v>
-      </c>
-      <c r="E356">
-        <v>67</v>
-      </c>
-      <c r="F356" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="357" spans="1:6">
-      <c r="A357" s="2">
-        <v>46139.69791666666</v>
-      </c>
-      <c r="B357">
-        <v>0</v>
-      </c>
-      <c r="C357">
-        <v>0</v>
-      </c>
-      <c r="D357">
-        <v>0</v>
-      </c>
-      <c r="E357">
-        <v>68</v>
-      </c>
-      <c r="F357" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="358" spans="1:6">
-      <c r="A358" s="2">
-        <v>46139.70833333334</v>
-      </c>
-      <c r="B358">
-        <v>0</v>
-      </c>
-      <c r="C358">
-        <v>0</v>
-      </c>
-      <c r="D358">
-        <v>0</v>
-      </c>
-      <c r="E358">
-        <v>69</v>
-      </c>
-      <c r="F358" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="359" spans="1:6">
-      <c r="A359" s="2">
-        <v>46139.71875</v>
-      </c>
-      <c r="B359">
-        <v>0</v>
-      </c>
-      <c r="C359">
-        <v>0</v>
-      </c>
-      <c r="D359">
-        <v>0</v>
-      </c>
-      <c r="E359">
-        <v>70</v>
-      </c>
-      <c r="F359" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="360" spans="1:6">
-      <c r="A360" s="2">
-        <v>46139.72916666666</v>
-      </c>
-      <c r="B360">
-        <v>0</v>
-      </c>
-      <c r="C360">
-        <v>0</v>
-      </c>
-      <c r="D360">
-        <v>0</v>
-      </c>
-      <c r="E360">
-        <v>71</v>
-      </c>
-      <c r="F360" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="361" spans="1:6">
-      <c r="A361" s="2">
-        <v>46139.73958333334</v>
-      </c>
-      <c r="B361">
-        <v>0</v>
-      </c>
-      <c r="C361">
-        <v>0</v>
-      </c>
-      <c r="D361">
-        <v>0</v>
-      </c>
-      <c r="E361">
-        <v>72</v>
-      </c>
-      <c r="F361" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="362" spans="1:6">
-      <c r="A362" s="2">
-        <v>46139.75</v>
-      </c>
-      <c r="B362">
-        <v>0</v>
-      </c>
-      <c r="C362">
-        <v>0</v>
-      </c>
-      <c r="D362">
-        <v>0</v>
-      </c>
-      <c r="E362">
-        <v>73</v>
-      </c>
-      <c r="F362" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6">
-      <c r="A363" s="2">
-        <v>46139.76041666666</v>
-      </c>
-      <c r="B363">
-        <v>0</v>
-      </c>
-      <c r="C363">
-        <v>0</v>
-      </c>
-      <c r="D363">
-        <v>0</v>
-      </c>
-      <c r="E363">
-        <v>74</v>
-      </c>
-      <c r="F363" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="364" spans="1:6">
-      <c r="A364" s="2">
-        <v>46139.77083333334</v>
-      </c>
-      <c r="B364">
-        <v>0</v>
-      </c>
-      <c r="C364">
-        <v>0</v>
-      </c>
-      <c r="D364">
-        <v>0</v>
-      </c>
-      <c r="E364">
-        <v>75</v>
-      </c>
-      <c r="F364" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="365" spans="1:6">
-      <c r="A365" s="2">
-        <v>46139.78125</v>
-      </c>
-      <c r="B365">
-        <v>0</v>
-      </c>
-      <c r="C365">
-        <v>0</v>
-      </c>
-      <c r="D365">
-        <v>0</v>
-      </c>
-      <c r="E365">
-        <v>76</v>
-      </c>
-      <c r="F365" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="366" spans="1:6">
-      <c r="A366" s="2">
-        <v>46139.79166666666</v>
-      </c>
-      <c r="B366">
-        <v>0</v>
-      </c>
-      <c r="C366">
-        <v>0</v>
-      </c>
-      <c r="D366">
-        <v>0</v>
-      </c>
-      <c r="E366">
-        <v>77</v>
-      </c>
-      <c r="F366" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="367" spans="1:6">
-      <c r="A367" s="2">
-        <v>46139.80208333334</v>
-      </c>
-      <c r="B367">
-        <v>0</v>
-      </c>
-      <c r="C367">
-        <v>0</v>
-      </c>
-      <c r="D367">
-        <v>0</v>
-      </c>
-      <c r="E367">
-        <v>78</v>
-      </c>
-      <c r="F367" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="368" spans="1:6">
-      <c r="A368" s="2">
-        <v>46139.8125</v>
-      </c>
-      <c r="B368">
-        <v>0</v>
-      </c>
-      <c r="C368">
-        <v>0</v>
-      </c>
-      <c r="D368">
-        <v>0</v>
-      </c>
-      <c r="E368">
-        <v>79</v>
-      </c>
-      <c r="F368" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="369" spans="1:6">
-      <c r="A369" s="2">
-        <v>46139.82291666666</v>
-      </c>
-      <c r="B369">
-        <v>0</v>
-      </c>
-      <c r="C369">
-        <v>0</v>
-      </c>
-      <c r="D369">
-        <v>0</v>
-      </c>
-      <c r="E369">
-        <v>80</v>
-      </c>
-      <c r="F369" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="370" spans="1:6">
-      <c r="A370" s="2">
-        <v>46139.83333333334</v>
-      </c>
-      <c r="B370">
-        <v>0</v>
-      </c>
-      <c r="C370">
-        <v>0</v>
-      </c>
-      <c r="D370">
-        <v>0</v>
-      </c>
-      <c r="E370">
-        <v>81</v>
-      </c>
-      <c r="F370" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="371" spans="1:6">
-      <c r="A371" s="2">
-        <v>46139.84375</v>
-      </c>
-      <c r="B371">
-        <v>0</v>
-      </c>
-      <c r="C371">
-        <v>0</v>
-      </c>
-      <c r="D371">
-        <v>0</v>
-      </c>
-      <c r="E371">
-        <v>82</v>
-      </c>
-      <c r="F371" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="372" spans="1:6">
-      <c r="A372" s="2">
-        <v>46139.85416666666</v>
-      </c>
-      <c r="B372">
-        <v>0</v>
-      </c>
-      <c r="C372">
-        <v>0</v>
-      </c>
-      <c r="D372">
-        <v>0</v>
-      </c>
-      <c r="E372">
-        <v>83</v>
-      </c>
-      <c r="F372" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="373" spans="1:6">
-      <c r="A373" s="2">
-        <v>46139.86458333334</v>
-      </c>
-      <c r="B373">
-        <v>0</v>
-      </c>
-      <c r="C373">
-        <v>0</v>
-      </c>
-      <c r="D373">
-        <v>0</v>
-      </c>
-      <c r="E373">
-        <v>84</v>
-      </c>
-      <c r="F373" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6">
-      <c r="A374" s="2">
-        <v>46139.875</v>
-      </c>
-      <c r="B374">
-        <v>0</v>
-      </c>
-      <c r="C374">
-        <v>0</v>
-      </c>
-      <c r="D374">
-        <v>0</v>
-      </c>
-      <c r="E374">
-        <v>85</v>
-      </c>
-      <c r="F374" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="375" spans="1:6">
-      <c r="A375" s="2">
-        <v>46139.88541666666</v>
-      </c>
-      <c r="B375">
-        <v>0</v>
-      </c>
-      <c r="C375">
-        <v>0</v>
-      </c>
-      <c r="D375">
-        <v>0</v>
-      </c>
-      <c r="E375">
-        <v>86</v>
-      </c>
-      <c r="F375" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="376" spans="1:6">
-      <c r="A376" s="2">
-        <v>46139.89583333334</v>
-      </c>
-      <c r="B376">
-        <v>0</v>
-      </c>
-      <c r="C376">
-        <v>0</v>
-      </c>
-      <c r="D376">
-        <v>0</v>
-      </c>
-      <c r="E376">
-        <v>87</v>
-      </c>
-      <c r="F376" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="377" spans="1:6">
-      <c r="A377" s="2">
-        <v>46139.90625</v>
-      </c>
-      <c r="B377">
-        <v>0</v>
-      </c>
-      <c r="C377">
-        <v>0</v>
-      </c>
-      <c r="D377">
-        <v>0</v>
-      </c>
-      <c r="E377">
-        <v>88</v>
-      </c>
-      <c r="F377" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="378" spans="1:6">
-      <c r="A378" s="2">
-        <v>46139.91666666666</v>
-      </c>
-      <c r="B378">
-        <v>0</v>
-      </c>
-      <c r="C378">
-        <v>0</v>
-      </c>
-      <c r="D378">
-        <v>0</v>
-      </c>
-      <c r="E378">
-        <v>89</v>
-      </c>
-      <c r="F378" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="379" spans="1:6">
-      <c r="A379" s="2">
-        <v>46139.92708333334</v>
-      </c>
-      <c r="B379">
-        <v>0</v>
-      </c>
-      <c r="C379">
-        <v>0</v>
-      </c>
-      <c r="D379">
-        <v>0</v>
-      </c>
-      <c r="E379">
-        <v>90</v>
-      </c>
-      <c r="F379" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="380" spans="1:6">
-      <c r="A380" s="2">
-        <v>46139.9375</v>
-      </c>
-      <c r="B380">
-        <v>0</v>
-      </c>
-      <c r="C380">
-        <v>0</v>
-      </c>
-      <c r="D380">
-        <v>0</v>
-      </c>
-      <c r="E380">
-        <v>91</v>
-      </c>
-      <c r="F380" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6">
-      <c r="A381" s="2">
-        <v>46139.94791666666</v>
-      </c>
-      <c r="B381">
-        <v>0</v>
-      </c>
-      <c r="C381">
-        <v>0</v>
-      </c>
-      <c r="D381">
-        <v>0</v>
-      </c>
-      <c r="E381">
-        <v>92</v>
-      </c>
-      <c r="F381" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="382" spans="1:6">
-      <c r="A382" s="2">
-        <v>46139.95833333334</v>
-      </c>
-      <c r="B382">
-        <v>0</v>
-      </c>
-      <c r="C382">
-        <v>0</v>
-      </c>
-      <c r="D382">
-        <v>0</v>
-      </c>
-      <c r="E382">
-        <v>93</v>
-      </c>
-      <c r="F382" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6">
-      <c r="A383" s="2">
-        <v>46139.96875</v>
-      </c>
-      <c r="B383">
-        <v>0</v>
-      </c>
-      <c r="C383">
-        <v>0</v>
-      </c>
-      <c r="D383">
-        <v>0</v>
-      </c>
-      <c r="E383">
-        <v>94</v>
-      </c>
-      <c r="F383" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="384" spans="1:6">
-      <c r="A384" s="2">
-        <v>46139.97916666666</v>
-      </c>
-      <c r="B384">
-        <v>0</v>
-      </c>
-      <c r="C384">
-        <v>0</v>
-      </c>
-      <c r="D384">
-        <v>0</v>
-      </c>
-      <c r="E384">
-        <v>95</v>
-      </c>
-      <c r="F384" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6">
-      <c r="A385" s="2">
-        <v>46139.98958333334</v>
-      </c>
-      <c r="B385">
-        <v>0</v>
-      </c>
-      <c r="C385">
-        <v>0</v>
-      </c>
-      <c r="D385">
-        <v>0</v>
-      </c>
-      <c r="E385">
-        <v>96</v>
-      </c>
-      <c r="F385" t="s">
-        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>05.05.20261</t>
-  </si>
-  <si>
-    <t>05.05.20262</t>
-  </si>
-  <si>
-    <t>05.05.20263</t>
-  </si>
-  <si>
-    <t>05.05.20264</t>
-  </si>
-  <si>
-    <t>05.05.20265</t>
-  </si>
-  <si>
-    <t>05.05.20266</t>
-  </si>
-  <si>
-    <t>05.05.20267</t>
-  </si>
-  <si>
-    <t>05.05.20268</t>
-  </si>
-  <si>
-    <t>05.05.20269</t>
-  </si>
-  <si>
-    <t>05.05.202610</t>
-  </si>
-  <si>
-    <t>05.05.202611</t>
-  </si>
-  <si>
-    <t>05.05.202612</t>
-  </si>
-  <si>
-    <t>05.05.202613</t>
-  </si>
-  <si>
-    <t>05.05.202614</t>
-  </si>
-  <si>
-    <t>05.05.202615</t>
-  </si>
-  <si>
-    <t>05.05.202616</t>
-  </si>
-  <si>
-    <t>05.05.202617</t>
-  </si>
-  <si>
-    <t>05.05.202618</t>
-  </si>
-  <si>
-    <t>05.05.202619</t>
-  </si>
-  <si>
-    <t>05.05.202620</t>
-  </si>
-  <si>
-    <t>05.05.202621</t>
-  </si>
-  <si>
-    <t>05.05.202622</t>
-  </si>
-  <si>
-    <t>05.05.202623</t>
-  </si>
-  <si>
-    <t>05.05.202624</t>
-  </si>
-  <si>
-    <t>05.05.202625</t>
-  </si>
-  <si>
-    <t>05.05.202626</t>
-  </si>
-  <si>
-    <t>05.05.202627</t>
-  </si>
-  <si>
-    <t>05.05.202628</t>
-  </si>
-  <si>
-    <t>05.05.202629</t>
-  </si>
-  <si>
-    <t>05.05.202630</t>
-  </si>
-  <si>
-    <t>05.05.202631</t>
-  </si>
-  <si>
-    <t>05.05.202632</t>
-  </si>
-  <si>
-    <t>05.05.202633</t>
-  </si>
-  <si>
-    <t>05.05.202634</t>
-  </si>
-  <si>
-    <t>05.05.202635</t>
-  </si>
-  <si>
-    <t>05.05.202636</t>
-  </si>
-  <si>
-    <t>05.05.202637</t>
-  </si>
-  <si>
-    <t>05.05.202638</t>
-  </si>
-  <si>
-    <t>05.05.202639</t>
-  </si>
-  <si>
-    <t>05.05.202640</t>
-  </si>
-  <si>
-    <t>05.05.202641</t>
-  </si>
-  <si>
-    <t>05.05.202642</t>
-  </si>
-  <si>
-    <t>05.05.202643</t>
-  </si>
-  <si>
-    <t>05.05.202644</t>
-  </si>
-  <si>
-    <t>05.05.202645</t>
-  </si>
-  <si>
-    <t>05.05.202646</t>
-  </si>
-  <si>
-    <t>05.05.202647</t>
-  </si>
-  <si>
-    <t>05.05.202648</t>
-  </si>
-  <si>
-    <t>05.05.202649</t>
-  </si>
-  <si>
-    <t>05.05.202650</t>
-  </si>
-  <si>
-    <t>05.05.202651</t>
-  </si>
-  <si>
-    <t>05.05.202652</t>
-  </si>
-  <si>
-    <t>05.05.202653</t>
-  </si>
-  <si>
-    <t>05.05.202654</t>
-  </si>
-  <si>
-    <t>05.05.202655</t>
-  </si>
-  <si>
-    <t>05.05.202656</t>
-  </si>
-  <si>
-    <t>05.05.202657</t>
-  </si>
-  <si>
-    <t>05.05.202658</t>
-  </si>
-  <si>
-    <t>05.05.202659</t>
-  </si>
-  <si>
-    <t>05.05.202660</t>
-  </si>
-  <si>
-    <t>05.05.202661</t>
-  </si>
-  <si>
-    <t>05.05.202662</t>
-  </si>
-  <si>
-    <t>05.05.202663</t>
-  </si>
-  <si>
-    <t>05.05.202664</t>
-  </si>
-  <si>
-    <t>05.05.202665</t>
-  </si>
-  <si>
-    <t>05.05.202666</t>
-  </si>
-  <si>
-    <t>05.05.202667</t>
-  </si>
-  <si>
-    <t>05.05.202668</t>
-  </si>
-  <si>
-    <t>05.05.202669</t>
-  </si>
-  <si>
-    <t>05.05.202670</t>
-  </si>
-  <si>
-    <t>05.05.202671</t>
-  </si>
-  <si>
-    <t>05.05.202672</t>
-  </si>
-  <si>
-    <t>05.05.202673</t>
-  </si>
-  <si>
-    <t>05.05.202674</t>
-  </si>
-  <si>
-    <t>05.05.202675</t>
-  </si>
-  <si>
-    <t>05.05.202676</t>
-  </si>
-  <si>
-    <t>05.05.202677</t>
-  </si>
-  <si>
-    <t>05.05.202678</t>
-  </si>
-  <si>
-    <t>05.05.202679</t>
-  </si>
-  <si>
-    <t>05.05.202680</t>
-  </si>
-  <si>
-    <t>05.05.202681</t>
-  </si>
-  <si>
-    <t>05.05.202682</t>
-  </si>
-  <si>
-    <t>05.05.202683</t>
-  </si>
-  <si>
-    <t>05.05.202684</t>
-  </si>
-  <si>
-    <t>05.05.202685</t>
-  </si>
-  <si>
-    <t>05.05.202686</t>
-  </si>
-  <si>
-    <t>05.05.202687</t>
-  </si>
-  <si>
-    <t>05.05.202688</t>
-  </si>
-  <si>
-    <t>05.05.202689</t>
-  </si>
-  <si>
-    <t>05.05.202690</t>
-  </si>
-  <si>
-    <t>05.05.202691</t>
-  </si>
-  <si>
-    <t>05.05.202692</t>
-  </si>
-  <si>
-    <t>05.05.202693</t>
-  </si>
-  <si>
-    <t>05.05.202694</t>
-  </si>
-  <si>
-    <t>05.05.202695</t>
-  </si>
-  <si>
-    <t>05.05.202696</t>
-  </si>
-  <si>
-    <t>06.05.20261</t>
-  </si>
-  <si>
-    <t>06.05.20262</t>
-  </si>
-  <si>
-    <t>06.05.20263</t>
-  </si>
-  <si>
-    <t>06.05.20264</t>
-  </si>
-  <si>
-    <t>06.05.20265</t>
-  </si>
-  <si>
-    <t>06.05.20266</t>
-  </si>
-  <si>
-    <t>06.05.20267</t>
-  </si>
-  <si>
-    <t>06.05.20268</t>
-  </si>
-  <si>
-    <t>06.05.20269</t>
-  </si>
-  <si>
-    <t>06.05.202610</t>
-  </si>
-  <si>
-    <t>06.05.202611</t>
-  </si>
-  <si>
-    <t>06.05.202612</t>
-  </si>
-  <si>
-    <t>06.05.202613</t>
-  </si>
-  <si>
-    <t>06.05.202614</t>
-  </si>
-  <si>
-    <t>06.05.202615</t>
-  </si>
-  <si>
-    <t>06.05.202616</t>
-  </si>
-  <si>
-    <t>06.05.202617</t>
-  </si>
-  <si>
-    <t>06.05.202618</t>
-  </si>
-  <si>
-    <t>06.05.202619</t>
-  </si>
-  <si>
-    <t>06.05.202620</t>
-  </si>
-  <si>
-    <t>06.05.202621</t>
-  </si>
-  <si>
-    <t>06.05.202622</t>
-  </si>
-  <si>
-    <t>06.05.202623</t>
-  </si>
-  <si>
-    <t>06.05.202624</t>
-  </si>
-  <si>
-    <t>06.05.202625</t>
-  </si>
-  <si>
-    <t>06.05.202626</t>
-  </si>
-  <si>
-    <t>06.05.202627</t>
-  </si>
-  <si>
-    <t>06.05.202628</t>
-  </si>
-  <si>
-    <t>06.05.202629</t>
-  </si>
-  <si>
-    <t>06.05.202630</t>
-  </si>
-  <si>
-    <t>06.05.202631</t>
-  </si>
-  <si>
-    <t>06.05.202632</t>
-  </si>
-  <si>
-    <t>06.05.202633</t>
-  </si>
-  <si>
-    <t>06.05.202634</t>
-  </si>
-  <si>
-    <t>06.05.202635</t>
-  </si>
-  <si>
-    <t>06.05.202636</t>
-  </si>
-  <si>
-    <t>06.05.202637</t>
-  </si>
-  <si>
-    <t>06.05.202638</t>
-  </si>
-  <si>
-    <t>06.05.202639</t>
-  </si>
-  <si>
-    <t>06.05.202640</t>
-  </si>
-  <si>
-    <t>06.05.202641</t>
-  </si>
-  <si>
-    <t>06.05.202642</t>
-  </si>
-  <si>
-    <t>06.05.202643</t>
-  </si>
-  <si>
-    <t>06.05.202644</t>
-  </si>
-  <si>
-    <t>06.05.202645</t>
-  </si>
-  <si>
-    <t>06.05.202646</t>
-  </si>
-  <si>
-    <t>06.05.202647</t>
-  </si>
-  <si>
-    <t>06.05.202648</t>
-  </si>
-  <si>
-    <t>06.05.202649</t>
-  </si>
-  <si>
-    <t>06.05.202650</t>
-  </si>
-  <si>
-    <t>06.05.202651</t>
-  </si>
-  <si>
-    <t>06.05.202652</t>
-  </si>
-  <si>
-    <t>06.05.202653</t>
-  </si>
-  <si>
-    <t>06.05.202654</t>
-  </si>
-  <si>
-    <t>06.05.202655</t>
-  </si>
-  <si>
-    <t>06.05.202656</t>
-  </si>
-  <si>
-    <t>06.05.202657</t>
-  </si>
-  <si>
-    <t>06.05.202658</t>
-  </si>
-  <si>
-    <t>06.05.202659</t>
-  </si>
-  <si>
-    <t>06.05.202660</t>
-  </si>
-  <si>
-    <t>06.05.202661</t>
-  </si>
-  <si>
-    <t>06.05.202662</t>
-  </si>
-  <si>
-    <t>06.05.202663</t>
-  </si>
-  <si>
-    <t>06.05.202664</t>
-  </si>
-  <si>
-    <t>06.05.202665</t>
-  </si>
-  <si>
-    <t>06.05.202666</t>
-  </si>
-  <si>
-    <t>06.05.202667</t>
-  </si>
-  <si>
-    <t>06.05.202668</t>
-  </si>
-  <si>
-    <t>06.05.202669</t>
-  </si>
-  <si>
-    <t>06.05.202670</t>
-  </si>
-  <si>
-    <t>06.05.202671</t>
-  </si>
-  <si>
-    <t>06.05.202672</t>
-  </si>
-  <si>
-    <t>06.05.202673</t>
-  </si>
-  <si>
-    <t>06.05.202674</t>
-  </si>
-  <si>
-    <t>06.05.202675</t>
-  </si>
-  <si>
-    <t>06.05.202676</t>
-  </si>
-  <si>
-    <t>06.05.202677</t>
-  </si>
-  <si>
-    <t>06.05.202678</t>
-  </si>
-  <si>
-    <t>06.05.202679</t>
-  </si>
-  <si>
-    <t>06.05.202680</t>
-  </si>
-  <si>
-    <t>06.05.202681</t>
-  </si>
-  <si>
-    <t>06.05.202682</t>
-  </si>
-  <si>
-    <t>06.05.202683</t>
-  </si>
-  <si>
-    <t>06.05.202684</t>
-  </si>
-  <si>
-    <t>06.05.202685</t>
-  </si>
-  <si>
-    <t>06.05.202686</t>
-  </si>
-  <si>
-    <t>06.05.202687</t>
-  </si>
-  <si>
-    <t>06.05.202688</t>
-  </si>
-  <si>
-    <t>06.05.202689</t>
-  </si>
-  <si>
-    <t>06.05.202690</t>
-  </si>
-  <si>
-    <t>06.05.202691</t>
-  </si>
-  <si>
-    <t>06.05.202692</t>
-  </si>
-  <si>
-    <t>06.05.202693</t>
-  </si>
-  <si>
-    <t>06.05.202694</t>
-  </si>
-  <si>
-    <t>06.05.202695</t>
-  </si>
-  <si>
-    <t>06.05.202696</t>
+    <t>07.05.20261</t>
+  </si>
+  <si>
+    <t>07.05.20262</t>
+  </si>
+  <si>
+    <t>07.05.20263</t>
+  </si>
+  <si>
+    <t>07.05.20264</t>
+  </si>
+  <si>
+    <t>07.05.20265</t>
+  </si>
+  <si>
+    <t>07.05.20266</t>
+  </si>
+  <si>
+    <t>07.05.20267</t>
+  </si>
+  <si>
+    <t>07.05.20268</t>
+  </si>
+  <si>
+    <t>07.05.20269</t>
+  </si>
+  <si>
+    <t>07.05.202610</t>
+  </si>
+  <si>
+    <t>07.05.202611</t>
+  </si>
+  <si>
+    <t>07.05.202612</t>
+  </si>
+  <si>
+    <t>07.05.202613</t>
+  </si>
+  <si>
+    <t>07.05.202614</t>
+  </si>
+  <si>
+    <t>07.05.202615</t>
+  </si>
+  <si>
+    <t>07.05.202616</t>
+  </si>
+  <si>
+    <t>07.05.202617</t>
+  </si>
+  <si>
+    <t>07.05.202618</t>
+  </si>
+  <si>
+    <t>07.05.202619</t>
+  </si>
+  <si>
+    <t>07.05.202620</t>
+  </si>
+  <si>
+    <t>07.05.202621</t>
+  </si>
+  <si>
+    <t>07.05.202622</t>
+  </si>
+  <si>
+    <t>07.05.202623</t>
+  </si>
+  <si>
+    <t>07.05.202624</t>
+  </si>
+  <si>
+    <t>07.05.202625</t>
+  </si>
+  <si>
+    <t>07.05.202626</t>
+  </si>
+  <si>
+    <t>07.05.202627</t>
+  </si>
+  <si>
+    <t>07.05.202628</t>
+  </si>
+  <si>
+    <t>07.05.202629</t>
+  </si>
+  <si>
+    <t>07.05.202630</t>
+  </si>
+  <si>
+    <t>07.05.202631</t>
+  </si>
+  <si>
+    <t>07.05.202632</t>
+  </si>
+  <si>
+    <t>07.05.202633</t>
+  </si>
+  <si>
+    <t>07.05.202634</t>
+  </si>
+  <si>
+    <t>07.05.202635</t>
+  </si>
+  <si>
+    <t>07.05.202636</t>
+  </si>
+  <si>
+    <t>07.05.202637</t>
+  </si>
+  <si>
+    <t>07.05.202638</t>
+  </si>
+  <si>
+    <t>07.05.202639</t>
+  </si>
+  <si>
+    <t>07.05.202640</t>
+  </si>
+  <si>
+    <t>07.05.202641</t>
+  </si>
+  <si>
+    <t>07.05.202642</t>
+  </si>
+  <si>
+    <t>07.05.202643</t>
+  </si>
+  <si>
+    <t>07.05.202644</t>
+  </si>
+  <si>
+    <t>07.05.202645</t>
+  </si>
+  <si>
+    <t>07.05.202646</t>
+  </si>
+  <si>
+    <t>07.05.202647</t>
+  </si>
+  <si>
+    <t>07.05.202648</t>
+  </si>
+  <si>
+    <t>07.05.202649</t>
+  </si>
+  <si>
+    <t>07.05.202650</t>
+  </si>
+  <si>
+    <t>07.05.202651</t>
+  </si>
+  <si>
+    <t>07.05.202652</t>
+  </si>
+  <si>
+    <t>07.05.202653</t>
+  </si>
+  <si>
+    <t>07.05.202654</t>
+  </si>
+  <si>
+    <t>07.05.202655</t>
+  </si>
+  <si>
+    <t>07.05.202656</t>
+  </si>
+  <si>
+    <t>07.05.202657</t>
+  </si>
+  <si>
+    <t>07.05.202658</t>
+  </si>
+  <si>
+    <t>07.05.202659</t>
+  </si>
+  <si>
+    <t>07.05.202660</t>
+  </si>
+  <si>
+    <t>07.05.202661</t>
+  </si>
+  <si>
+    <t>07.05.202662</t>
+  </si>
+  <si>
+    <t>07.05.202663</t>
+  </si>
+  <si>
+    <t>07.05.202664</t>
+  </si>
+  <si>
+    <t>07.05.202665</t>
+  </si>
+  <si>
+    <t>07.05.202666</t>
+  </si>
+  <si>
+    <t>07.05.202667</t>
+  </si>
+  <si>
+    <t>07.05.202668</t>
+  </si>
+  <si>
+    <t>07.05.202669</t>
+  </si>
+  <si>
+    <t>07.05.202670</t>
+  </si>
+  <si>
+    <t>07.05.202671</t>
+  </si>
+  <si>
+    <t>07.05.202672</t>
+  </si>
+  <si>
+    <t>07.05.202673</t>
+  </si>
+  <si>
+    <t>07.05.202674</t>
+  </si>
+  <si>
+    <t>07.05.202675</t>
+  </si>
+  <si>
+    <t>07.05.202676</t>
+  </si>
+  <si>
+    <t>07.05.202677</t>
+  </si>
+  <si>
+    <t>07.05.202678</t>
+  </si>
+  <si>
+    <t>07.05.202679</t>
+  </si>
+  <si>
+    <t>07.05.202680</t>
+  </si>
+  <si>
+    <t>07.05.202681</t>
+  </si>
+  <si>
+    <t>07.05.202682</t>
+  </si>
+  <si>
+    <t>07.05.202683</t>
+  </si>
+  <si>
+    <t>07.05.202684</t>
+  </si>
+  <si>
+    <t>07.05.202685</t>
+  </si>
+  <si>
+    <t>07.05.202686</t>
+  </si>
+  <si>
+    <t>07.05.202687</t>
+  </si>
+  <si>
+    <t>07.05.202688</t>
+  </si>
+  <si>
+    <t>07.05.202689</t>
+  </si>
+  <si>
+    <t>07.05.202690</t>
+  </si>
+  <si>
+    <t>07.05.202691</t>
+  </si>
+  <si>
+    <t>07.05.202692</t>
+  </si>
+  <si>
+    <t>07.05.202693</t>
+  </si>
+  <si>
+    <t>07.05.202694</t>
+  </si>
+  <si>
+    <t>07.05.202695</t>
+  </si>
+  <si>
+    <t>07.05.202696</t>
+  </si>
+  <si>
+    <t>08.05.20261</t>
+  </si>
+  <si>
+    <t>08.05.20262</t>
+  </si>
+  <si>
+    <t>08.05.20263</t>
+  </si>
+  <si>
+    <t>08.05.20264</t>
+  </si>
+  <si>
+    <t>08.05.20265</t>
+  </si>
+  <si>
+    <t>08.05.20266</t>
+  </si>
+  <si>
+    <t>08.05.20267</t>
+  </si>
+  <si>
+    <t>08.05.20268</t>
+  </si>
+  <si>
+    <t>08.05.20269</t>
+  </si>
+  <si>
+    <t>08.05.202610</t>
+  </si>
+  <si>
+    <t>08.05.202611</t>
+  </si>
+  <si>
+    <t>08.05.202612</t>
+  </si>
+  <si>
+    <t>08.05.202613</t>
+  </si>
+  <si>
+    <t>08.05.202614</t>
+  </si>
+  <si>
+    <t>08.05.202615</t>
+  </si>
+  <si>
+    <t>08.05.202616</t>
+  </si>
+  <si>
+    <t>08.05.202617</t>
+  </si>
+  <si>
+    <t>08.05.202618</t>
+  </si>
+  <si>
+    <t>08.05.202619</t>
+  </si>
+  <si>
+    <t>08.05.202620</t>
+  </si>
+  <si>
+    <t>08.05.202621</t>
+  </si>
+  <si>
+    <t>08.05.202622</t>
+  </si>
+  <si>
+    <t>08.05.202623</t>
+  </si>
+  <si>
+    <t>08.05.202624</t>
+  </si>
+  <si>
+    <t>08.05.202625</t>
+  </si>
+  <si>
+    <t>08.05.202626</t>
+  </si>
+  <si>
+    <t>08.05.202627</t>
+  </si>
+  <si>
+    <t>08.05.202628</t>
+  </si>
+  <si>
+    <t>08.05.202629</t>
+  </si>
+  <si>
+    <t>08.05.202630</t>
+  </si>
+  <si>
+    <t>08.05.202631</t>
+  </si>
+  <si>
+    <t>08.05.202632</t>
+  </si>
+  <si>
+    <t>08.05.202633</t>
+  </si>
+  <si>
+    <t>08.05.202634</t>
+  </si>
+  <si>
+    <t>08.05.202635</t>
+  </si>
+  <si>
+    <t>08.05.202636</t>
+  </si>
+  <si>
+    <t>08.05.202637</t>
+  </si>
+  <si>
+    <t>08.05.202638</t>
+  </si>
+  <si>
+    <t>08.05.202639</t>
+  </si>
+  <si>
+    <t>08.05.202640</t>
+  </si>
+  <si>
+    <t>08.05.202641</t>
+  </si>
+  <si>
+    <t>08.05.202642</t>
+  </si>
+  <si>
+    <t>08.05.202643</t>
+  </si>
+  <si>
+    <t>08.05.202644</t>
+  </si>
+  <si>
+    <t>08.05.202645</t>
+  </si>
+  <si>
+    <t>08.05.202646</t>
+  </si>
+  <si>
+    <t>08.05.202647</t>
+  </si>
+  <si>
+    <t>08.05.202648</t>
+  </si>
+  <si>
+    <t>08.05.202649</t>
+  </si>
+  <si>
+    <t>08.05.202650</t>
+  </si>
+  <si>
+    <t>08.05.202651</t>
+  </si>
+  <si>
+    <t>08.05.202652</t>
+  </si>
+  <si>
+    <t>08.05.202653</t>
+  </si>
+  <si>
+    <t>08.05.202654</t>
+  </si>
+  <si>
+    <t>08.05.202655</t>
+  </si>
+  <si>
+    <t>08.05.202656</t>
+  </si>
+  <si>
+    <t>08.05.202657</t>
+  </si>
+  <si>
+    <t>08.05.202658</t>
+  </si>
+  <si>
+    <t>08.05.202659</t>
+  </si>
+  <si>
+    <t>08.05.202660</t>
+  </si>
+  <si>
+    <t>08.05.202661</t>
+  </si>
+  <si>
+    <t>08.05.202662</t>
+  </si>
+  <si>
+    <t>08.05.202663</t>
+  </si>
+  <si>
+    <t>08.05.202664</t>
+  </si>
+  <si>
+    <t>08.05.202665</t>
+  </si>
+  <si>
+    <t>08.05.202666</t>
+  </si>
+  <si>
+    <t>08.05.202667</t>
+  </si>
+  <si>
+    <t>08.05.202668</t>
+  </si>
+  <si>
+    <t>08.05.202669</t>
+  </si>
+  <si>
+    <t>08.05.202670</t>
+  </si>
+  <si>
+    <t>08.05.202671</t>
+  </si>
+  <si>
+    <t>08.05.202672</t>
+  </si>
+  <si>
+    <t>08.05.202673</t>
+  </si>
+  <si>
+    <t>08.05.202674</t>
+  </si>
+  <si>
+    <t>08.05.202675</t>
+  </si>
+  <si>
+    <t>08.05.202676</t>
+  </si>
+  <si>
+    <t>08.05.202677</t>
+  </si>
+  <si>
+    <t>08.05.202678</t>
+  </si>
+  <si>
+    <t>08.05.202679</t>
+  </si>
+  <si>
+    <t>08.05.202680</t>
+  </si>
+  <si>
+    <t>08.05.202681</t>
+  </si>
+  <si>
+    <t>08.05.202682</t>
+  </si>
+  <si>
+    <t>08.05.202683</t>
+  </si>
+  <si>
+    <t>08.05.202684</t>
+  </si>
+  <si>
+    <t>08.05.202685</t>
+  </si>
+  <si>
+    <t>08.05.202686</t>
+  </si>
+  <si>
+    <t>08.05.202687</t>
+  </si>
+  <si>
+    <t>08.05.202688</t>
+  </si>
+  <si>
+    <t>08.05.202689</t>
+  </si>
+  <si>
+    <t>08.05.202690</t>
+  </si>
+  <si>
+    <t>08.05.202691</t>
+  </si>
+  <si>
+    <t>08.05.202692</t>
+  </si>
+  <si>
+    <t>08.05.202693</t>
+  </si>
+  <si>
+    <t>08.05.202694</t>
+  </si>
+  <si>
+    <t>08.05.202695</t>
+  </si>
+  <si>
+    <t>08.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46147.01041666666</v>
+        <v>46149.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46147.02083333334</v>
+        <v>46149.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46147.03125</v>
+        <v>46149.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46147.04166666666</v>
+        <v>46149.04166666666</v>
       </c>
       <c r="B6">
-        <v>-99.619</v>
+        <v>75.64400000000001</v>
       </c>
       <c r="C6">
-        <v>1164.294</v>
+        <v>173.336</v>
       </c>
       <c r="D6">
-        <v>1164.294</v>
+        <v>173.336</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46147.05208333334</v>
+        <v>46149.05208333334</v>
       </c>
       <c r="B7">
-        <v>-109.956</v>
+        <v>67.268</v>
       </c>
       <c r="C7">
-        <v>1257.116</v>
+        <v>318</v>
       </c>
       <c r="D7">
-        <v>1257.116</v>
+        <v>318</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46147.0625</v>
+        <v>46149.0625</v>
       </c>
       <c r="B8">
-        <v>-99.02</v>
+        <v>50.75</v>
       </c>
       <c r="C8">
-        <v>1629.485</v>
+        <v>171.627</v>
       </c>
       <c r="D8">
-        <v>1629.485</v>
+        <v>171.627</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46147.07291666666</v>
+        <v>46149.07291666666</v>
       </c>
       <c r="B9">
-        <v>-89.221</v>
+        <v>30.632</v>
       </c>
       <c r="C9">
-        <v>1299.499</v>
+        <v>-75.285</v>
       </c>
       <c r="D9">
-        <v>1299.499</v>
+        <v>-75.285</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46147.08333333334</v>
+        <v>46149.08333333334</v>
       </c>
       <c r="B10">
-        <v>-78.13</v>
+        <v>51.825</v>
       </c>
       <c r="C10">
-        <v>1068.811</v>
+        <v>139.692</v>
       </c>
       <c r="D10">
-        <v>1068.811</v>
+        <v>139.692</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46147.09375</v>
+        <v>46149.09375</v>
       </c>
       <c r="B11">
-        <v>-75.896</v>
+        <v>34.007</v>
       </c>
       <c r="C11">
-        <v>1052.604</v>
+        <v>197.004</v>
       </c>
       <c r="D11">
-        <v>1052.604</v>
+        <v>197.004</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46147.10416666666</v>
+        <v>46149.10416666666</v>
       </c>
       <c r="B12">
-        <v>-93.526</v>
+        <v>34.843</v>
       </c>
       <c r="C12">
-        <v>1111.591</v>
+        <v>288.953</v>
       </c>
       <c r="D12">
-        <v>1111.591</v>
+        <v>288.953</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46147.11458333334</v>
+        <v>46149.11458333334</v>
       </c>
       <c r="B13">
-        <v>-85.70999999999999</v>
+        <v>4.537</v>
       </c>
       <c r="C13">
-        <v>1067.589</v>
+        <v>256.841</v>
       </c>
       <c r="D13">
-        <v>1067.589</v>
+        <v>256.841</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46147.125</v>
+        <v>46149.125</v>
       </c>
       <c r="B14">
-        <v>-24.673</v>
+        <v>19.757</v>
       </c>
       <c r="C14">
-        <v>1091.81</v>
+        <v>-7.642</v>
       </c>
       <c r="D14">
-        <v>1091.81</v>
+        <v>-7.642</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46147.13541666666</v>
+        <v>46149.13541666666</v>
       </c>
       <c r="B15">
-        <v>-35.141</v>
+        <v>9.137</v>
       </c>
       <c r="C15">
-        <v>1091.763</v>
+        <v>20.29</v>
       </c>
       <c r="D15">
-        <v>1091.763</v>
+        <v>20.29</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46147.14583333334</v>
+        <v>46149.14583333334</v>
       </c>
       <c r="B16">
-        <v>-70.654</v>
+        <v>24.103</v>
       </c>
       <c r="C16">
-        <v>1082.068</v>
+        <v>51.473</v>
       </c>
       <c r="D16">
-        <v>1082.068</v>
+        <v>51.473</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46147.15625</v>
+        <v>46149.15625</v>
       </c>
       <c r="B17">
-        <v>-61.512</v>
+        <v>12.723</v>
       </c>
       <c r="C17">
-        <v>1080.867</v>
+        <v>199.796</v>
       </c>
       <c r="D17">
-        <v>1080.867</v>
+        <v>199.796</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46147.16666666666</v>
+        <v>46149.16666666666</v>
       </c>
       <c r="B18">
-        <v>-161.08</v>
+        <v>67.488</v>
       </c>
       <c r="C18">
-        <v>3671.891</v>
+        <v>-83.077</v>
       </c>
       <c r="D18">
-        <v>3671.891</v>
+        <v>-83.077</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46147.17708333334</v>
+        <v>46149.17708333334</v>
       </c>
       <c r="B19">
-        <v>-165.769</v>
+        <v>31.634</v>
       </c>
       <c r="C19">
-        <v>1247.805</v>
+        <v>-144.797</v>
       </c>
       <c r="D19">
-        <v>1247.805</v>
+        <v>-144.797</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46147.1875</v>
+        <v>46149.1875</v>
       </c>
       <c r="B20">
-        <v>-158.954</v>
+        <v>32.177</v>
       </c>
       <c r="C20">
-        <v>1343.669</v>
+        <v>-118.031</v>
       </c>
       <c r="D20">
-        <v>1343.669</v>
+        <v>-118.031</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46147.19791666666</v>
+        <v>46149.19791666666</v>
       </c>
       <c r="B21">
-        <v>-178.356</v>
+        <v>33.746</v>
       </c>
       <c r="C21">
-        <v>1230.424</v>
+        <v>-119.257</v>
       </c>
       <c r="D21">
-        <v>1230.424</v>
+        <v>-119.257</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46147.20833333334</v>
+        <v>46149.20833333334</v>
       </c>
       <c r="B22">
-        <v>-124.318</v>
+        <v>77.446</v>
       </c>
       <c r="C22">
-        <v>1153.948</v>
+        <v>-1413.477</v>
       </c>
       <c r="D22">
-        <v>1153.948</v>
+        <v>-1413.477</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46147.21875</v>
+        <v>46149.21875</v>
       </c>
       <c r="B23">
-        <v>-143.924</v>
+        <v>55.876</v>
       </c>
       <c r="C23">
-        <v>1151.275</v>
+        <v>-253.469</v>
       </c>
       <c r="D23">
-        <v>1151.275</v>
+        <v>-253.469</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46147.22916666666</v>
+        <v>46149.22916666666</v>
       </c>
       <c r="B24">
-        <v>-100.496</v>
+        <v>57.595</v>
       </c>
       <c r="C24">
-        <v>1162.097</v>
+        <v>-44.415</v>
       </c>
       <c r="D24">
-        <v>1162.097</v>
+        <v>-44.415</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46147.23958333334</v>
+        <v>46149.23958333334</v>
       </c>
       <c r="B25">
-        <v>-103.872</v>
+        <v>77.68899999999999</v>
       </c>
       <c r="C25">
-        <v>1165.181</v>
+        <v>-35.297</v>
       </c>
       <c r="D25">
-        <v>1165.181</v>
+        <v>-35.297</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46147.25</v>
+        <v>46149.25</v>
       </c>
       <c r="B26">
-        <v>-165.124</v>
+        <v>95.67700000000001</v>
       </c>
       <c r="C26">
-        <v>1969.817</v>
+        <v>-117.377</v>
       </c>
       <c r="D26">
-        <v>1969.817</v>
+        <v>-117.377</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46147.26041666666</v>
+        <v>46149.26041666666</v>
       </c>
       <c r="B27">
-        <v>-161.159</v>
+        <v>107.79</v>
       </c>
       <c r="C27">
-        <v>1217.643</v>
+        <v>-47.194</v>
       </c>
       <c r="D27">
-        <v>1217.643</v>
+        <v>-47.194</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46147.27083333334</v>
+        <v>46149.27083333334</v>
       </c>
       <c r="B28">
-        <v>-78.318</v>
+        <v>27.708</v>
       </c>
       <c r="C28">
-        <v>1250</v>
+        <v>18.519</v>
       </c>
       <c r="D28">
-        <v>1250</v>
+        <v>18.519</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46147.28125</v>
+        <v>46149.28125</v>
       </c>
       <c r="B29">
-        <v>-29.996</v>
+        <v>35.892</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>10.101</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>10.101</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46147.29166666666</v>
+        <v>46149.29166666666</v>
       </c>
       <c r="B30">
-        <v>-58.221</v>
+        <v>-3.227</v>
       </c>
       <c r="C30">
-        <v>1470.297</v>
+        <v>1301.983</v>
       </c>
       <c r="D30">
-        <v>1470.297</v>
+        <v>1301.983</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46147.30208333334</v>
+        <v>46149.30208333334</v>
       </c>
       <c r="B31">
-        <v>-75.43899999999999</v>
+        <v>7.408</v>
       </c>
       <c r="C31">
-        <v>2863.146</v>
+        <v>1.1</v>
       </c>
       <c r="D31">
-        <v>2863.146</v>
+        <v>1.1</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46147.3125</v>
+        <v>46149.3125</v>
       </c>
       <c r="B32">
-        <v>-39.686</v>
+        <v>-13.462</v>
       </c>
       <c r="C32">
-        <v>1318.006</v>
+        <v>1607.59</v>
       </c>
       <c r="D32">
-        <v>1318.006</v>
+        <v>1607.59</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46147.32291666666</v>
+        <v>46149.32291666666</v>
       </c>
       <c r="B33">
-        <v>-44.703</v>
+        <v>4.767</v>
       </c>
       <c r="C33">
-        <v>2204.711</v>
+        <v>820.591</v>
       </c>
       <c r="D33">
-        <v>2204.711</v>
+        <v>820.591</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46147.33333333334</v>
+        <v>46149.33333333334</v>
       </c>
       <c r="B34">
-        <v>-95.836</v>
+        <v>-56.475</v>
       </c>
       <c r="C34">
-        <v>6912.9</v>
+        <v>920.081</v>
       </c>
       <c r="D34">
-        <v>6912.9</v>
+        <v>920.081</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46147.34375</v>
+        <v>46149.34375</v>
       </c>
       <c r="B35">
-        <v>-102.403</v>
+        <v>-39.985</v>
       </c>
       <c r="C35">
-        <v>6999</v>
+        <v>1209.327</v>
       </c>
       <c r="D35">
-        <v>6999</v>
+        <v>1209.327</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46147.35416666666</v>
+        <v>46149.35416666666</v>
       </c>
       <c r="B36">
-        <v>-142.406</v>
+        <v>-69.292</v>
       </c>
       <c r="C36">
-        <v>5228.328</v>
+        <v>1410.982</v>
       </c>
       <c r="D36">
-        <v>5228.328</v>
+        <v>1410.982</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46147.36458333334</v>
+        <v>46149.36458333334</v>
       </c>
       <c r="B37">
-        <v>-209.516</v>
+        <v>-83.377</v>
       </c>
       <c r="C37">
-        <v>3033.607</v>
+        <v>1475.663</v>
       </c>
       <c r="D37">
-        <v>3033.607</v>
+        <v>1475.663</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46147.375</v>
+        <v>46149.375</v>
       </c>
       <c r="B38">
-        <v>-196.448</v>
+        <v>-92.592</v>
       </c>
       <c r="C38">
-        <v>2931.292</v>
+        <v>2762.582</v>
       </c>
       <c r="D38">
-        <v>2931.292</v>
+        <v>2762.582</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46147.38541666666</v>
+        <v>46149.38541666666</v>
       </c>
       <c r="B39">
-        <v>-171.934</v>
+        <v>-50.236</v>
       </c>
       <c r="C39">
-        <v>1714.121</v>
+        <v>1807.783</v>
       </c>
       <c r="D39">
-        <v>1714.121</v>
+        <v>1807.783</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46147.39583333334</v>
+        <v>46149.39583333334</v>
       </c>
       <c r="B40">
-        <v>-155.383</v>
+        <v>-88.441</v>
       </c>
       <c r="C40">
-        <v>848.487</v>
+        <v>1941.374</v>
       </c>
       <c r="D40">
-        <v>848.487</v>
+        <v>1941.374</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46147.40625</v>
+        <v>46149.40625</v>
       </c>
       <c r="B41">
-        <v>-111.79</v>
+        <v>-40.827</v>
       </c>
       <c r="C41">
-        <v>828.9880000000001</v>
+        <v>899</v>
       </c>
       <c r="D41">
-        <v>828.9880000000001</v>
+        <v>899</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46147.41666666666</v>
+        <v>46149.41666666666</v>
       </c>
       <c r="B42">
-        <v>-114.429</v>
+        <v>-27.452</v>
       </c>
       <c r="C42">
-        <v>647.88</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>647.88</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46147.42708333334</v>
+        <v>46149.42708333334</v>
       </c>
       <c r="B43">
-        <v>-69.30200000000001</v>
+        <v>43.107</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>261.483</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>261.483</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46147.4375</v>
+        <v>46149.4375</v>
       </c>
       <c r="B44">
-        <v>-87.822</v>
+        <v>46.88</v>
       </c>
       <c r="C44">
-        <v>650.972</v>
+        <v>189.421</v>
       </c>
       <c r="D44">
-        <v>650.972</v>
+        <v>189.421</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46147.44791666666</v>
+        <v>46149.44791666666</v>
       </c>
       <c r="B45">
-        <v>-47.8</v>
+        <v>16.858</v>
       </c>
       <c r="C45">
-        <v>652.162</v>
+        <v>426.787</v>
       </c>
       <c r="D45">
-        <v>652.162</v>
+        <v>426.787</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46147.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="B46">
-        <v>-21.955</v>
+        <v>9.254</v>
       </c>
       <c r="C46">
-        <v>583.53</v>
+        <v>401</v>
       </c>
       <c r="D46">
-        <v>583.53</v>
+        <v>401</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46147.46875</v>
+        <v>46149.46875</v>
       </c>
       <c r="B47">
-        <v>-31.533</v>
+        <v>41.555</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>300.895</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>300.895</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46147.47916666666</v>
+        <v>46149.47916666666</v>
       </c>
       <c r="B48">
-        <v>-15.078</v>
+        <v>35.981</v>
       </c>
       <c r="C48">
-        <v>581.53</v>
+        <v>344.617</v>
       </c>
       <c r="D48">
-        <v>581.53</v>
+        <v>344.617</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46147.48958333334</v>
+        <v>46149.48958333334</v>
       </c>
       <c r="B49">
-        <v>34.962</v>
+        <v>14.462</v>
       </c>
       <c r="C49">
-        <v>-2135.564</v>
+        <v>500</v>
       </c>
       <c r="D49">
-        <v>-2135.564</v>
+        <v>500</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46147.5</v>
+        <v>46149.5</v>
       </c>
       <c r="B50">
-        <v>219.44</v>
+        <v>47.905</v>
       </c>
       <c r="C50">
-        <v>-7499</v>
+        <v>400.867</v>
       </c>
       <c r="D50">
-        <v>-7499</v>
+        <v>400.867</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46147.51041666666</v>
+        <v>46149.51041666666</v>
       </c>
       <c r="B51">
-        <v>200.217</v>
+        <v>43.117</v>
       </c>
       <c r="C51">
-        <v>-6910.188</v>
+        <v>348.611</v>
       </c>
       <c r="D51">
-        <v>-6910.188</v>
+        <v>348.611</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46147.52083333334</v>
+        <v>46149.52083333334</v>
       </c>
       <c r="B52">
-        <v>166.701</v>
+        <v>24.234</v>
       </c>
       <c r="C52">
-        <v>16.876</v>
+        <v>393.182</v>
       </c>
       <c r="D52">
-        <v>16.876</v>
+        <v>393.182</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46147.53125</v>
+        <v>46149.53125</v>
       </c>
       <c r="B53">
-        <v>163.791</v>
+        <v>29.19</v>
       </c>
       <c r="C53">
-        <v>-162.339</v>
+        <v>346.429</v>
       </c>
       <c r="D53">
-        <v>-162.339</v>
+        <v>346.429</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46147.54166666666</v>
+        <v>46149.54166666666</v>
       </c>
       <c r="B54">
-        <v>127.354</v>
+        <v>-8.287000000000001</v>
       </c>
       <c r="C54">
-        <v>-163.535</v>
+        <v>1058.799</v>
       </c>
       <c r="D54">
-        <v>-163.535</v>
+        <v>1058.799</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46147.55208333334</v>
+        <v>46149.55208333334</v>
       </c>
       <c r="B55">
-        <v>137.43</v>
+        <v>-24.784</v>
       </c>
       <c r="C55">
-        <v>-143.03</v>
+        <v>1091.616</v>
       </c>
       <c r="D55">
-        <v>-143.03</v>
+        <v>1091.616</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46147.5625</v>
+        <v>46149.5625</v>
       </c>
       <c r="B56">
-        <v>120.674</v>
+        <v>-17.18</v>
       </c>
       <c r="C56">
-        <v>-144.207</v>
+        <v>899.393</v>
       </c>
       <c r="D56">
-        <v>-144.207</v>
+        <v>899.393</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46147.57291666666</v>
+        <v>46149.57291666666</v>
       </c>
       <c r="B57">
-        <v>68.751</v>
+        <v>25.095</v>
       </c>
       <c r="C57">
-        <v>-164</v>
+        <v>400</v>
       </c>
       <c r="D57">
-        <v>-164</v>
+        <v>400</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46147.58333333334</v>
+        <v>46149.58333333334</v>
       </c>
       <c r="B58">
-        <v>47.549</v>
+        <v>66.602</v>
       </c>
       <c r="C58">
-        <v>-108</v>
+        <v>427.177</v>
       </c>
       <c r="D58">
-        <v>-108</v>
+        <v>427.177</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46147.59375</v>
+        <v>46149.59375</v>
       </c>
       <c r="B59">
-        <v>79.703</v>
+        <v>17.997</v>
       </c>
       <c r="C59">
-        <v>-103.096</v>
+        <v>442.274</v>
       </c>
       <c r="D59">
-        <v>-103.096</v>
+        <v>442.274</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46147.60416666666</v>
+        <v>46149.60416666666</v>
       </c>
       <c r="B60">
-        <v>81.121</v>
+        <v>75.72</v>
       </c>
       <c r="C60">
-        <v>1.203</v>
+        <v>420.947</v>
       </c>
       <c r="D60">
-        <v>1.203</v>
+        <v>420.947</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46147.61458333334</v>
+        <v>46149.61458333334</v>
       </c>
       <c r="B61">
-        <v>17.612</v>
+        <v>77.23099999999999</v>
       </c>
       <c r="C61">
-        <v>6.889</v>
+        <v>419.827</v>
       </c>
       <c r="D61">
-        <v>6.889</v>
+        <v>419.827</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46147.625</v>
+        <v>46149.625</v>
       </c>
       <c r="B62">
-        <v>38.295</v>
+        <v>37.323</v>
       </c>
       <c r="C62">
-        <v>0.6</v>
+        <v>-3.859</v>
       </c>
       <c r="D62">
-        <v>0.6</v>
+        <v>-3.859</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46147.63541666666</v>
+        <v>46149.63541666666</v>
       </c>
       <c r="B63">
-        <v>-11.95</v>
+        <v>35.618</v>
       </c>
       <c r="C63">
-        <v>980.546</v>
+        <v>-77.01000000000001</v>
       </c>
       <c r="D63">
-        <v>980.546</v>
+        <v>-77.01000000000001</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46147.64583333334</v>
+        <v>46149.64583333334</v>
       </c>
       <c r="B64">
-        <v>-17.947</v>
+        <v>23.865</v>
       </c>
       <c r="C64">
-        <v>1007.869</v>
+        <v>3.927</v>
       </c>
       <c r="D64">
-        <v>1007.869</v>
+        <v>3.927</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46147.65625</v>
+        <v>46149.65625</v>
       </c>
       <c r="B65">
-        <v>-22.326</v>
+        <v>22.882</v>
       </c>
       <c r="C65">
-        <v>1166.849</v>
+        <v>1.1</v>
       </c>
       <c r="D65">
-        <v>1166.849</v>
+        <v>1.1</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46147.66666666666</v>
+        <v>46149.66666666666</v>
       </c>
       <c r="B66">
-        <v>90.512</v>
+        <v>-41.431</v>
       </c>
       <c r="C66">
-        <v>-103.84</v>
+        <v>529.226</v>
       </c>
       <c r="D66">
-        <v>-103.84</v>
+        <v>529.226</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46147.67708333334</v>
+        <v>46149.67708333334</v>
       </c>
       <c r="B67">
-        <v>60.384</v>
+        <v>-72.706</v>
       </c>
       <c r="C67">
-        <v>13.611</v>
+        <v>3460.521</v>
       </c>
       <c r="D67">
-        <v>13.611</v>
+        <v>3460.521</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46147.6875</v>
+        <v>46149.6875</v>
       </c>
       <c r="B68">
-        <v>78.979</v>
+        <v>-0.011</v>
       </c>
       <c r="C68">
-        <v>3.568</v>
+        <v>1450.205</v>
       </c>
       <c r="D68">
-        <v>3.568</v>
+        <v>1450.205</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46147.69791666666</v>
+        <v>46149.69791666666</v>
       </c>
       <c r="B69">
-        <v>70.86199999999999</v>
+        <v>24.411</v>
       </c>
       <c r="C69">
-        <v>3.071</v>
+        <v>401</v>
       </c>
       <c r="D69">
-        <v>3.071</v>
+        <v>401</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46147.70833333334</v>
+        <v>46149.70833333334</v>
       </c>
       <c r="B70">
-        <v>136.82</v>
+        <v>38.976</v>
       </c>
       <c r="C70">
-        <v>9.781000000000001</v>
+        <v>196.049</v>
       </c>
       <c r="D70">
-        <v>9.781000000000001</v>
+        <v>196.049</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46147.71875</v>
+        <v>46149.71875</v>
       </c>
       <c r="B71">
-        <v>71.889</v>
+        <v>67.94199999999999</v>
       </c>
       <c r="C71">
-        <v>2.894</v>
+        <v>-30.232</v>
       </c>
       <c r="D71">
-        <v>2.894</v>
+        <v>-30.232</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46147.72916666666</v>
+        <v>46149.72916666666</v>
       </c>
       <c r="B72">
-        <v>32.547</v>
+        <v>56.225</v>
       </c>
       <c r="C72">
-        <v>0.5</v>
+        <v>144.116</v>
       </c>
       <c r="D72">
-        <v>0.5</v>
+        <v>144.116</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46147.73958333334</v>
+        <v>46149.73958333334</v>
       </c>
       <c r="B73">
-        <v>1.579</v>
+        <v>76.06</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>351.402</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>351.402</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46147.75</v>
+        <v>46149.75</v>
       </c>
       <c r="B74">
-        <v>43.99</v>
+        <v>84.43300000000001</v>
       </c>
       <c r="C74">
-        <v>0.6</v>
+        <v>-56.658</v>
       </c>
       <c r="D74">
-        <v>0.6</v>
+        <v>-56.658</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46147.76041666666</v>
+        <v>46149.76041666666</v>
       </c>
       <c r="B75">
-        <v>17.787</v>
+        <v>57.919</v>
       </c>
       <c r="C75">
-        <v>1.18</v>
+        <v>401</v>
       </c>
       <c r="D75">
-        <v>1.18</v>
+        <v>401</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46147.77083333334</v>
+        <v>46149.77083333334</v>
       </c>
       <c r="B76">
-        <v>20.116</v>
+        <v>61.307</v>
       </c>
       <c r="C76">
-        <v>1.1</v>
+        <v>16.49</v>
       </c>
       <c r="D76">
-        <v>1.1</v>
+        <v>16.49</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46147.78125</v>
+        <v>46149.78125</v>
       </c>
       <c r="B77">
-        <v>-4.35</v>
+        <v>47.832</v>
       </c>
       <c r="C77">
-        <v>924.423</v>
+        <v>133.359</v>
       </c>
       <c r="D77">
-        <v>924.423</v>
+        <v>133.359</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46147.79166666666</v>
+        <v>46149.79166666666</v>
       </c>
       <c r="B78">
-        <v>51.517</v>
+        <v>85.95399999999999</v>
       </c>
       <c r="C78">
-        <v>401</v>
+        <v>-251.621</v>
       </c>
       <c r="D78">
-        <v>401</v>
+        <v>-251.621</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46147.80208333334</v>
+        <v>46149.80208333334</v>
       </c>
       <c r="B79">
-        <v>66.872</v>
+        <v>86.988</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>-464.302</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>-464.302</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46147.8125</v>
+        <v>46149.8125</v>
       </c>
       <c r="B80">
-        <v>90.617</v>
+        <v>59.543</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>-2.853</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>-2.853</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46147.82291666666</v>
+        <v>46149.82291666666</v>
       </c>
       <c r="B81">
-        <v>76.28700000000001</v>
+        <v>47.885</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46147.83333333334</v>
+        <v>46149.83333333334</v>
       </c>
       <c r="B82">
-        <v>-12.673</v>
+        <v>27.64</v>
       </c>
       <c r="C82">
-        <v>1069.525</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>1069.525</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46147.84375</v>
+        <v>46149.84375</v>
       </c>
       <c r="B83">
-        <v>-2.435</v>
+        <v>19.129</v>
       </c>
       <c r="C83">
-        <v>1328.308</v>
+        <v>182.659</v>
       </c>
       <c r="D83">
-        <v>1328.308</v>
+        <v>182.659</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46147.85416666666</v>
+        <v>46149.85416666666</v>
       </c>
       <c r="B84">
-        <v>8.577999999999999</v>
+        <v>17.03</v>
       </c>
       <c r="C84">
-        <v>450</v>
+        <v>365.23</v>
       </c>
       <c r="D84">
-        <v>450</v>
+        <v>365.23</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46147.86458333334</v>
+        <v>46149.86458333334</v>
       </c>
       <c r="B85">
-        <v>13.309</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="C85">
-        <v>405.84</v>
+        <v>897.1900000000001</v>
       </c>
       <c r="D85">
-        <v>405.84</v>
+        <v>897.1900000000001</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46147.875</v>
+        <v>46149.875</v>
       </c>
       <c r="B86">
-        <v>152.941</v>
+        <v>-5.758</v>
       </c>
       <c r="C86">
-        <v>318.007</v>
+        <v>1146.777</v>
       </c>
       <c r="D86">
-        <v>318.007</v>
+        <v>1146.777</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46147.88541666666</v>
+        <v>46149.88541666666</v>
       </c>
       <c r="B87">
-        <v>123.955</v>
+        <v>7.924</v>
       </c>
       <c r="C87">
-        <v>383.273</v>
+        <v>400</v>
       </c>
       <c r="D87">
-        <v>383.273</v>
+        <v>400</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46147.89583333334</v>
+        <v>46149.89583333334</v>
       </c>
       <c r="B88">
-        <v>50.782</v>
+        <v>5.319</v>
       </c>
       <c r="C88">
-        <v>0.6</v>
+        <v>317.871</v>
       </c>
       <c r="D88">
-        <v>0.6</v>
+        <v>317.871</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46147.90625</v>
+        <v>46149.90625</v>
       </c>
       <c r="B89">
-        <v>27.657</v>
+        <v>12.729</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>-72.608</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>-72.608</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46147.91666666666</v>
+        <v>46149.91666666666</v>
       </c>
       <c r="B90">
-        <v>20.654</v>
+        <v>6.973</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>123.878</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>123.878</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46147.92708333334</v>
+        <v>46149.92708333334</v>
       </c>
       <c r="B91">
-        <v>2.71</v>
+        <v>40.916</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>-10.47</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>-10.47</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46147.9375</v>
+        <v>46149.9375</v>
       </c>
       <c r="B92">
-        <v>-32.025</v>
+        <v>35.862</v>
       </c>
       <c r="C92">
-        <v>3214.468</v>
+        <v>14.282</v>
       </c>
       <c r="D92">
-        <v>3214.468</v>
+        <v>14.282</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46147.94791666666</v>
+        <v>46149.94791666666</v>
       </c>
       <c r="B93">
-        <v>-14.995</v>
+        <v>56.9</v>
       </c>
       <c r="C93">
-        <v>4105.752</v>
+        <v>76.246</v>
       </c>
       <c r="D93">
-        <v>4105.752</v>
+        <v>76.246</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46147.95833333334</v>
+        <v>46149.95833333334</v>
       </c>
       <c r="B94">
-        <v>24.408</v>
+        <v>41.376</v>
       </c>
       <c r="C94">
-        <v>15.669</v>
+        <v>119.387</v>
       </c>
       <c r="D94">
-        <v>15.669</v>
+        <v>119.387</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46147.96875</v>
+        <v>46149.96875</v>
       </c>
       <c r="B95">
-        <v>42.015</v>
+        <v>32.236</v>
       </c>
       <c r="C95">
-        <v>264.521</v>
+        <v>83.075</v>
       </c>
       <c r="D95">
-        <v>264.521</v>
+        <v>83.075</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46147.97916666666</v>
+        <v>46149.97916666666</v>
       </c>
       <c r="B96">
-        <v>40.75</v>
+        <v>48.664</v>
       </c>
       <c r="C96">
-        <v>-28.555</v>
+        <v>-45.506</v>
       </c>
       <c r="D96">
-        <v>-28.555</v>
+        <v>-45.506</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46147.98958333334</v>
+        <v>46149.98958333334</v>
       </c>
       <c r="B97">
-        <v>37.51</v>
+        <v>41.203</v>
       </c>
       <c r="C97">
-        <v>-11.053</v>
+        <v>-27.195</v>
       </c>
       <c r="D97">
-        <v>-11.053</v>
+        <v>-27.195</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B98">
-        <v>65.244</v>
+        <v>63.241</v>
       </c>
       <c r="C98">
-        <v>35.681</v>
+        <v>192.803</v>
       </c>
       <c r="D98">
-        <v>35.681</v>
+        <v>192.803</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B99">
-        <v>82.59</v>
+        <v>77.193</v>
       </c>
       <c r="C99">
-        <v>-162.006</v>
+        <v>354.429</v>
       </c>
       <c r="D99">
-        <v>-162.006</v>
+        <v>354.429</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B100">
-        <v>81.366</v>
+        <v>122.479</v>
       </c>
       <c r="C100">
-        <v>-79.688</v>
+        <v>338.239</v>
       </c>
       <c r="D100">
-        <v>-79.688</v>
+        <v>338.239</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B101">
-        <v>67.499</v>
+        <v>64.41500000000001</v>
       </c>
       <c r="C101">
-        <v>20.95</v>
+        <v>-11.319</v>
       </c>
       <c r="D101">
-        <v>20.95</v>
+        <v>-11.319</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B102">
-        <v>143.565</v>
+        <v>64.501</v>
       </c>
       <c r="C102">
-        <v>126.363</v>
+        <v>6.206</v>
       </c>
       <c r="D102">
-        <v>126.363</v>
+        <v>6.206</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B103">
-        <v>41.821</v>
+        <v>51.712</v>
       </c>
       <c r="C103">
-        <v>189.573</v>
+        <v>-8.954000000000001</v>
       </c>
       <c r="D103">
-        <v>189.573</v>
+        <v>-8.954000000000001</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B104">
-        <v>7.605</v>
+        <v>79.038</v>
       </c>
       <c r="C104">
-        <v>260.25</v>
+        <v>-83.652</v>
       </c>
       <c r="D104">
-        <v>260.25</v>
+        <v>-83.652</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B105">
-        <v>6.846</v>
+        <v>76.267</v>
       </c>
       <c r="C105">
-        <v>304.554</v>
+        <v>1.867</v>
       </c>
       <c r="D105">
-        <v>304.554</v>
+        <v>1.867</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B106">
-        <v>4.823</v>
+        <v>121.323</v>
       </c>
       <c r="C106">
-        <v>895.487</v>
+        <v>8.298</v>
       </c>
       <c r="D106">
-        <v>895.487</v>
+        <v>8.298</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B107">
-        <v>16.679</v>
+        <v>97.538</v>
       </c>
       <c r="C107">
-        <v>400</v>
+        <v>-5.535</v>
       </c>
       <c r="D107">
-        <v>400</v>
+        <v>-5.535</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B108">
-        <v>-1.877</v>
+        <v>95.926</v>
       </c>
       <c r="C108">
-        <v>879.967</v>
+        <v>-5.968</v>
       </c>
       <c r="D108">
-        <v>879.967</v>
+        <v>-5.968</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B109">
-        <v>27.41</v>
+        <v>42.734</v>
       </c>
       <c r="C109">
-        <v>279.441</v>
+        <v>20.491</v>
       </c>
       <c r="D109">
-        <v>279.441</v>
+        <v>20.491</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B110">
-        <v>4.402</v>
+        <v>64.39</v>
       </c>
       <c r="C110">
-        <v>256.1</v>
+        <v>17.934</v>
       </c>
       <c r="D110">
-        <v>256.1</v>
+        <v>17.934</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B111">
-        <v>7.206</v>
+        <v>23.996</v>
       </c>
       <c r="C111">
-        <v>264.1</v>
+        <v>1.89</v>
       </c>
       <c r="D111">
-        <v>264.1</v>
+        <v>1.89</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B112">
-        <v>-7.35</v>
+        <v>38.831</v>
       </c>
       <c r="C112">
-        <v>898.901</v>
+        <v>1.403</v>
       </c>
       <c r="D112">
-        <v>898.901</v>
+        <v>1.403</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B113">
-        <v>-0.381</v>
+        <v>42.896</v>
       </c>
       <c r="C113">
-        <v>897.127</v>
+        <v>4.732</v>
       </c>
       <c r="D113">
-        <v>897.127</v>
+        <v>4.732</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B114">
-        <v>40.681</v>
+        <v>102.239</v>
       </c>
       <c r="C114">
-        <v>280.657</v>
+        <v>289.538</v>
       </c>
       <c r="D114">
-        <v>280.657</v>
+        <v>289.538</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B115">
-        <v>24.328</v>
+        <v>99.46299999999999</v>
       </c>
       <c r="C115">
-        <v>256.867</v>
+        <v>43.265</v>
       </c>
       <c r="D115">
-        <v>256.867</v>
+        <v>43.265</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B116">
-        <v>29.295</v>
+        <v>84.414</v>
       </c>
       <c r="C116">
-        <v>257.655</v>
+        <v>-254.86</v>
       </c>
       <c r="D116">
-        <v>257.655</v>
+        <v>-254.86</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B117">
-        <v>25.918</v>
+        <v>107.469</v>
       </c>
       <c r="C117">
-        <v>291.58</v>
+        <v>195.065</v>
       </c>
       <c r="D117">
-        <v>291.58</v>
+        <v>195.065</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B118">
-        <v>32.819</v>
+        <v>155.849</v>
       </c>
       <c r="C118">
-        <v>277.648</v>
+        <v>21.05</v>
       </c>
       <c r="D118">
-        <v>277.648</v>
+        <v>21.05</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B119">
-        <v>70.642</v>
+        <v>114.822</v>
       </c>
       <c r="C119">
-        <v>339.036</v>
+        <v>9.85</v>
       </c>
       <c r="D119">
-        <v>339.036</v>
+        <v>9.85</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B120">
-        <v>25.821</v>
+        <v>95.06699999999999</v>
       </c>
       <c r="C120">
-        <v>326.747</v>
+        <v>9.073</v>
       </c>
       <c r="D120">
-        <v>326.747</v>
+        <v>9.073</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B121">
-        <v>17.045</v>
+        <v>90.866</v>
       </c>
       <c r="C121">
-        <v>258.329</v>
+        <v>-8.052</v>
       </c>
       <c r="D121">
-        <v>258.329</v>
+        <v>-8.052</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B122">
-        <v>60.99</v>
+        <v>79.943</v>
       </c>
       <c r="C122">
-        <v>268.959</v>
+        <v>-640.484</v>
       </c>
       <c r="D122">
-        <v>268.959</v>
+        <v>-640.484</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B123">
-        <v>81.895</v>
+        <v>107.323</v>
       </c>
       <c r="C123">
-        <v>-36.562</v>
+        <v>5.334</v>
       </c>
       <c r="D123">
-        <v>-36.562</v>
+        <v>5.334</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B124">
-        <v>75.386</v>
+        <v>49.965</v>
       </c>
       <c r="C124">
-        <v>-131.442</v>
+        <v>325.925</v>
       </c>
       <c r="D124">
-        <v>-131.442</v>
+        <v>325.925</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B125">
-        <v>93.131</v>
+        <v>22.551</v>
       </c>
       <c r="C125">
-        <v>-223.733</v>
+        <v>334.99</v>
       </c>
       <c r="D125">
-        <v>-223.733</v>
+        <v>334.99</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B126">
-        <v>49.694</v>
+        <v>46.846</v>
       </c>
       <c r="C126">
-        <v>14.689</v>
+        <v>290.623</v>
       </c>
       <c r="D126">
-        <v>14.689</v>
+        <v>290.623</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B127">
-        <v>52.8</v>
+        <v>77.444</v>
       </c>
       <c r="C127">
-        <v>44.163</v>
+        <v>273.29</v>
       </c>
       <c r="D127">
-        <v>44.163</v>
+        <v>273.29</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>57.612</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>-58.385</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>-58.385</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3554,7 +3554,7 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.05.20261</t>
-  </si>
-  <si>
-    <t>07.05.20262</t>
-  </si>
-  <si>
-    <t>07.05.20263</t>
-  </si>
-  <si>
-    <t>07.05.20264</t>
-  </si>
-  <si>
-    <t>07.05.20265</t>
-  </si>
-  <si>
-    <t>07.05.20266</t>
-  </si>
-  <si>
-    <t>07.05.20267</t>
-  </si>
-  <si>
-    <t>07.05.20268</t>
-  </si>
-  <si>
-    <t>07.05.20269</t>
-  </si>
-  <si>
-    <t>07.05.202610</t>
-  </si>
-  <si>
-    <t>07.05.202611</t>
-  </si>
-  <si>
-    <t>07.05.202612</t>
-  </si>
-  <si>
-    <t>07.05.202613</t>
-  </si>
-  <si>
-    <t>07.05.202614</t>
-  </si>
-  <si>
-    <t>07.05.202615</t>
-  </si>
-  <si>
-    <t>07.05.202616</t>
-  </si>
-  <si>
-    <t>07.05.202617</t>
-  </si>
-  <si>
-    <t>07.05.202618</t>
-  </si>
-  <si>
-    <t>07.05.202619</t>
-  </si>
-  <si>
-    <t>07.05.202620</t>
-  </si>
-  <si>
-    <t>07.05.202621</t>
-  </si>
-  <si>
-    <t>07.05.202622</t>
-  </si>
-  <si>
-    <t>07.05.202623</t>
-  </si>
-  <si>
-    <t>07.05.202624</t>
-  </si>
-  <si>
-    <t>07.05.202625</t>
-  </si>
-  <si>
-    <t>07.05.202626</t>
-  </si>
-  <si>
-    <t>07.05.202627</t>
-  </si>
-  <si>
-    <t>07.05.202628</t>
-  </si>
-  <si>
-    <t>07.05.202629</t>
-  </si>
-  <si>
-    <t>07.05.202630</t>
-  </si>
-  <si>
-    <t>07.05.202631</t>
-  </si>
-  <si>
-    <t>07.05.202632</t>
-  </si>
-  <si>
-    <t>07.05.202633</t>
-  </si>
-  <si>
-    <t>07.05.202634</t>
-  </si>
-  <si>
-    <t>07.05.202635</t>
-  </si>
-  <si>
-    <t>07.05.202636</t>
-  </si>
-  <si>
-    <t>07.05.202637</t>
-  </si>
-  <si>
-    <t>07.05.202638</t>
-  </si>
-  <si>
-    <t>07.05.202639</t>
-  </si>
-  <si>
-    <t>07.05.202640</t>
-  </si>
-  <si>
-    <t>07.05.202641</t>
-  </si>
-  <si>
-    <t>07.05.202642</t>
-  </si>
-  <si>
-    <t>07.05.202643</t>
-  </si>
-  <si>
-    <t>07.05.202644</t>
-  </si>
-  <si>
-    <t>07.05.202645</t>
-  </si>
-  <si>
-    <t>07.05.202646</t>
-  </si>
-  <si>
-    <t>07.05.202647</t>
-  </si>
-  <si>
-    <t>07.05.202648</t>
-  </si>
-  <si>
-    <t>07.05.202649</t>
-  </si>
-  <si>
-    <t>07.05.202650</t>
-  </si>
-  <si>
-    <t>07.05.202651</t>
-  </si>
-  <si>
-    <t>07.05.202652</t>
-  </si>
-  <si>
-    <t>07.05.202653</t>
-  </si>
-  <si>
-    <t>07.05.202654</t>
-  </si>
-  <si>
-    <t>07.05.202655</t>
-  </si>
-  <si>
-    <t>07.05.202656</t>
-  </si>
-  <si>
-    <t>07.05.202657</t>
-  </si>
-  <si>
-    <t>07.05.202658</t>
-  </si>
-  <si>
-    <t>07.05.202659</t>
-  </si>
-  <si>
-    <t>07.05.202660</t>
-  </si>
-  <si>
-    <t>07.05.202661</t>
-  </si>
-  <si>
-    <t>07.05.202662</t>
-  </si>
-  <si>
-    <t>07.05.202663</t>
-  </si>
-  <si>
-    <t>07.05.202664</t>
-  </si>
-  <si>
-    <t>07.05.202665</t>
-  </si>
-  <si>
-    <t>07.05.202666</t>
-  </si>
-  <si>
-    <t>07.05.202667</t>
-  </si>
-  <si>
-    <t>07.05.202668</t>
-  </si>
-  <si>
-    <t>07.05.202669</t>
-  </si>
-  <si>
-    <t>07.05.202670</t>
-  </si>
-  <si>
-    <t>07.05.202671</t>
-  </si>
-  <si>
-    <t>07.05.202672</t>
-  </si>
-  <si>
-    <t>07.05.202673</t>
-  </si>
-  <si>
-    <t>07.05.202674</t>
-  </si>
-  <si>
-    <t>07.05.202675</t>
-  </si>
-  <si>
-    <t>07.05.202676</t>
-  </si>
-  <si>
-    <t>07.05.202677</t>
-  </si>
-  <si>
-    <t>07.05.202678</t>
-  </si>
-  <si>
-    <t>07.05.202679</t>
-  </si>
-  <si>
-    <t>07.05.202680</t>
-  </si>
-  <si>
-    <t>07.05.202681</t>
-  </si>
-  <si>
-    <t>07.05.202682</t>
-  </si>
-  <si>
-    <t>07.05.202683</t>
-  </si>
-  <si>
-    <t>07.05.202684</t>
-  </si>
-  <si>
-    <t>07.05.202685</t>
-  </si>
-  <si>
-    <t>07.05.202686</t>
-  </si>
-  <si>
-    <t>07.05.202687</t>
-  </si>
-  <si>
-    <t>07.05.202688</t>
-  </si>
-  <si>
-    <t>07.05.202689</t>
-  </si>
-  <si>
-    <t>07.05.202690</t>
-  </si>
-  <si>
-    <t>07.05.202691</t>
-  </si>
-  <si>
-    <t>07.05.202692</t>
-  </si>
-  <si>
-    <t>07.05.202693</t>
-  </si>
-  <si>
-    <t>07.05.202694</t>
-  </si>
-  <si>
-    <t>07.05.202695</t>
-  </si>
-  <si>
-    <t>07.05.202696</t>
-  </si>
-  <si>
-    <t>08.05.20261</t>
-  </si>
-  <si>
-    <t>08.05.20262</t>
-  </si>
-  <si>
-    <t>08.05.20263</t>
-  </si>
-  <si>
-    <t>08.05.20264</t>
-  </si>
-  <si>
-    <t>08.05.20265</t>
-  </si>
-  <si>
-    <t>08.05.20266</t>
-  </si>
-  <si>
-    <t>08.05.20267</t>
-  </si>
-  <si>
-    <t>08.05.20268</t>
-  </si>
-  <si>
-    <t>08.05.20269</t>
-  </si>
-  <si>
-    <t>08.05.202610</t>
-  </si>
-  <si>
-    <t>08.05.202611</t>
-  </si>
-  <si>
-    <t>08.05.202612</t>
-  </si>
-  <si>
-    <t>08.05.202613</t>
-  </si>
-  <si>
-    <t>08.05.202614</t>
-  </si>
-  <si>
-    <t>08.05.202615</t>
-  </si>
-  <si>
-    <t>08.05.202616</t>
-  </si>
-  <si>
-    <t>08.05.202617</t>
-  </si>
-  <si>
-    <t>08.05.202618</t>
-  </si>
-  <si>
-    <t>08.05.202619</t>
-  </si>
-  <si>
-    <t>08.05.202620</t>
-  </si>
-  <si>
-    <t>08.05.202621</t>
-  </si>
-  <si>
-    <t>08.05.202622</t>
-  </si>
-  <si>
-    <t>08.05.202623</t>
-  </si>
-  <si>
-    <t>08.05.202624</t>
-  </si>
-  <si>
-    <t>08.05.202625</t>
-  </si>
-  <si>
-    <t>08.05.202626</t>
-  </si>
-  <si>
-    <t>08.05.202627</t>
-  </si>
-  <si>
-    <t>08.05.202628</t>
-  </si>
-  <si>
-    <t>08.05.202629</t>
-  </si>
-  <si>
-    <t>08.05.202630</t>
-  </si>
-  <si>
-    <t>08.05.202631</t>
-  </si>
-  <si>
-    <t>08.05.202632</t>
-  </si>
-  <si>
-    <t>08.05.202633</t>
-  </si>
-  <si>
-    <t>08.05.202634</t>
-  </si>
-  <si>
-    <t>08.05.202635</t>
-  </si>
-  <si>
-    <t>08.05.202636</t>
-  </si>
-  <si>
-    <t>08.05.202637</t>
-  </si>
-  <si>
-    <t>08.05.202638</t>
-  </si>
-  <si>
-    <t>08.05.202639</t>
-  </si>
-  <si>
-    <t>08.05.202640</t>
-  </si>
-  <si>
-    <t>08.05.202641</t>
-  </si>
-  <si>
-    <t>08.05.202642</t>
-  </si>
-  <si>
-    <t>08.05.202643</t>
-  </si>
-  <si>
-    <t>08.05.202644</t>
-  </si>
-  <si>
-    <t>08.05.202645</t>
-  </si>
-  <si>
-    <t>08.05.202646</t>
-  </si>
-  <si>
-    <t>08.05.202647</t>
-  </si>
-  <si>
-    <t>08.05.202648</t>
-  </si>
-  <si>
-    <t>08.05.202649</t>
-  </si>
-  <si>
-    <t>08.05.202650</t>
-  </si>
-  <si>
-    <t>08.05.202651</t>
-  </si>
-  <si>
-    <t>08.05.202652</t>
-  </si>
-  <si>
-    <t>08.05.202653</t>
-  </si>
-  <si>
-    <t>08.05.202654</t>
-  </si>
-  <si>
-    <t>08.05.202655</t>
-  </si>
-  <si>
-    <t>08.05.202656</t>
-  </si>
-  <si>
-    <t>08.05.202657</t>
-  </si>
-  <si>
-    <t>08.05.202658</t>
-  </si>
-  <si>
-    <t>08.05.202659</t>
-  </si>
-  <si>
-    <t>08.05.202660</t>
-  </si>
-  <si>
-    <t>08.05.202661</t>
-  </si>
-  <si>
-    <t>08.05.202662</t>
-  </si>
-  <si>
-    <t>08.05.202663</t>
-  </si>
-  <si>
-    <t>08.05.202664</t>
-  </si>
-  <si>
-    <t>08.05.202665</t>
-  </si>
-  <si>
-    <t>08.05.202666</t>
-  </si>
-  <si>
-    <t>08.05.202667</t>
-  </si>
-  <si>
-    <t>08.05.202668</t>
-  </si>
-  <si>
-    <t>08.05.202669</t>
-  </si>
-  <si>
-    <t>08.05.202670</t>
-  </si>
-  <si>
-    <t>08.05.202671</t>
-  </si>
-  <si>
-    <t>08.05.202672</t>
-  </si>
-  <si>
-    <t>08.05.202673</t>
-  </si>
-  <si>
-    <t>08.05.202674</t>
-  </si>
-  <si>
-    <t>08.05.202675</t>
-  </si>
-  <si>
-    <t>08.05.202676</t>
-  </si>
-  <si>
-    <t>08.05.202677</t>
-  </si>
-  <si>
-    <t>08.05.202678</t>
-  </si>
-  <si>
-    <t>08.05.202679</t>
-  </si>
-  <si>
-    <t>08.05.202680</t>
-  </si>
-  <si>
-    <t>08.05.202681</t>
-  </si>
-  <si>
-    <t>08.05.202682</t>
-  </si>
-  <si>
-    <t>08.05.202683</t>
-  </si>
-  <si>
-    <t>08.05.202684</t>
-  </si>
-  <si>
-    <t>08.05.202685</t>
-  </si>
-  <si>
-    <t>08.05.202686</t>
-  </si>
-  <si>
-    <t>08.05.202687</t>
-  </si>
-  <si>
-    <t>08.05.202688</t>
-  </si>
-  <si>
-    <t>08.05.202689</t>
-  </si>
-  <si>
-    <t>08.05.202690</t>
-  </si>
-  <si>
-    <t>08.05.202691</t>
-  </si>
-  <si>
-    <t>08.05.202692</t>
-  </si>
-  <si>
-    <t>08.05.202693</t>
-  </si>
-  <si>
-    <t>08.05.202694</t>
-  </si>
-  <si>
-    <t>08.05.202695</t>
-  </si>
-  <si>
-    <t>08.05.202696</t>
+    <t>11.05.20261</t>
+  </si>
+  <si>
+    <t>11.05.20262</t>
+  </si>
+  <si>
+    <t>11.05.20263</t>
+  </si>
+  <si>
+    <t>11.05.20264</t>
+  </si>
+  <si>
+    <t>11.05.20265</t>
+  </si>
+  <si>
+    <t>11.05.20266</t>
+  </si>
+  <si>
+    <t>11.05.20267</t>
+  </si>
+  <si>
+    <t>11.05.20268</t>
+  </si>
+  <si>
+    <t>11.05.20269</t>
+  </si>
+  <si>
+    <t>11.05.202610</t>
+  </si>
+  <si>
+    <t>11.05.202611</t>
+  </si>
+  <si>
+    <t>11.05.202612</t>
+  </si>
+  <si>
+    <t>11.05.202613</t>
+  </si>
+  <si>
+    <t>11.05.202614</t>
+  </si>
+  <si>
+    <t>11.05.202615</t>
+  </si>
+  <si>
+    <t>11.05.202616</t>
+  </si>
+  <si>
+    <t>11.05.202617</t>
+  </si>
+  <si>
+    <t>11.05.202618</t>
+  </si>
+  <si>
+    <t>11.05.202619</t>
+  </si>
+  <si>
+    <t>11.05.202620</t>
+  </si>
+  <si>
+    <t>11.05.202621</t>
+  </si>
+  <si>
+    <t>11.05.202622</t>
+  </si>
+  <si>
+    <t>11.05.202623</t>
+  </si>
+  <si>
+    <t>11.05.202624</t>
+  </si>
+  <si>
+    <t>11.05.202625</t>
+  </si>
+  <si>
+    <t>11.05.202626</t>
+  </si>
+  <si>
+    <t>11.05.202627</t>
+  </si>
+  <si>
+    <t>11.05.202628</t>
+  </si>
+  <si>
+    <t>11.05.202629</t>
+  </si>
+  <si>
+    <t>11.05.202630</t>
+  </si>
+  <si>
+    <t>11.05.202631</t>
+  </si>
+  <si>
+    <t>11.05.202632</t>
+  </si>
+  <si>
+    <t>11.05.202633</t>
+  </si>
+  <si>
+    <t>11.05.202634</t>
+  </si>
+  <si>
+    <t>11.05.202635</t>
+  </si>
+  <si>
+    <t>11.05.202636</t>
+  </si>
+  <si>
+    <t>11.05.202637</t>
+  </si>
+  <si>
+    <t>11.05.202638</t>
+  </si>
+  <si>
+    <t>11.05.202639</t>
+  </si>
+  <si>
+    <t>11.05.202640</t>
+  </si>
+  <si>
+    <t>11.05.202641</t>
+  </si>
+  <si>
+    <t>11.05.202642</t>
+  </si>
+  <si>
+    <t>11.05.202643</t>
+  </si>
+  <si>
+    <t>11.05.202644</t>
+  </si>
+  <si>
+    <t>11.05.202645</t>
+  </si>
+  <si>
+    <t>11.05.202646</t>
+  </si>
+  <si>
+    <t>11.05.202647</t>
+  </si>
+  <si>
+    <t>11.05.202648</t>
+  </si>
+  <si>
+    <t>11.05.202649</t>
+  </si>
+  <si>
+    <t>11.05.202650</t>
+  </si>
+  <si>
+    <t>11.05.202651</t>
+  </si>
+  <si>
+    <t>11.05.202652</t>
+  </si>
+  <si>
+    <t>11.05.202653</t>
+  </si>
+  <si>
+    <t>11.05.202654</t>
+  </si>
+  <si>
+    <t>11.05.202655</t>
+  </si>
+  <si>
+    <t>11.05.202656</t>
+  </si>
+  <si>
+    <t>11.05.202657</t>
+  </si>
+  <si>
+    <t>11.05.202658</t>
+  </si>
+  <si>
+    <t>11.05.202659</t>
+  </si>
+  <si>
+    <t>11.05.202660</t>
+  </si>
+  <si>
+    <t>11.05.202661</t>
+  </si>
+  <si>
+    <t>11.05.202662</t>
+  </si>
+  <si>
+    <t>11.05.202663</t>
+  </si>
+  <si>
+    <t>11.05.202664</t>
+  </si>
+  <si>
+    <t>11.05.202665</t>
+  </si>
+  <si>
+    <t>11.05.202666</t>
+  </si>
+  <si>
+    <t>11.05.202667</t>
+  </si>
+  <si>
+    <t>11.05.202668</t>
+  </si>
+  <si>
+    <t>11.05.202669</t>
+  </si>
+  <si>
+    <t>11.05.202670</t>
+  </si>
+  <si>
+    <t>11.05.202671</t>
+  </si>
+  <si>
+    <t>11.05.202672</t>
+  </si>
+  <si>
+    <t>11.05.202673</t>
+  </si>
+  <si>
+    <t>11.05.202674</t>
+  </si>
+  <si>
+    <t>11.05.202675</t>
+  </si>
+  <si>
+    <t>11.05.202676</t>
+  </si>
+  <si>
+    <t>11.05.202677</t>
+  </si>
+  <si>
+    <t>11.05.202678</t>
+  </si>
+  <si>
+    <t>11.05.202679</t>
+  </si>
+  <si>
+    <t>11.05.202680</t>
+  </si>
+  <si>
+    <t>11.05.202681</t>
+  </si>
+  <si>
+    <t>11.05.202682</t>
+  </si>
+  <si>
+    <t>11.05.202683</t>
+  </si>
+  <si>
+    <t>11.05.202684</t>
+  </si>
+  <si>
+    <t>11.05.202685</t>
+  </si>
+  <si>
+    <t>11.05.202686</t>
+  </si>
+  <si>
+    <t>11.05.202687</t>
+  </si>
+  <si>
+    <t>11.05.202688</t>
+  </si>
+  <si>
+    <t>11.05.202689</t>
+  </si>
+  <si>
+    <t>11.05.202690</t>
+  </si>
+  <si>
+    <t>11.05.202691</t>
+  </si>
+  <si>
+    <t>11.05.202692</t>
+  </si>
+  <si>
+    <t>11.05.202693</t>
+  </si>
+  <si>
+    <t>11.05.202694</t>
+  </si>
+  <si>
+    <t>11.05.202695</t>
+  </si>
+  <si>
+    <t>11.05.202696</t>
+  </si>
+  <si>
+    <t>12.05.20261</t>
+  </si>
+  <si>
+    <t>12.05.20262</t>
+  </si>
+  <si>
+    <t>12.05.20263</t>
+  </si>
+  <si>
+    <t>12.05.20264</t>
+  </si>
+  <si>
+    <t>12.05.20265</t>
+  </si>
+  <si>
+    <t>12.05.20266</t>
+  </si>
+  <si>
+    <t>12.05.20267</t>
+  </si>
+  <si>
+    <t>12.05.20268</t>
+  </si>
+  <si>
+    <t>12.05.20269</t>
+  </si>
+  <si>
+    <t>12.05.202610</t>
+  </si>
+  <si>
+    <t>12.05.202611</t>
+  </si>
+  <si>
+    <t>12.05.202612</t>
+  </si>
+  <si>
+    <t>12.05.202613</t>
+  </si>
+  <si>
+    <t>12.05.202614</t>
+  </si>
+  <si>
+    <t>12.05.202615</t>
+  </si>
+  <si>
+    <t>12.05.202616</t>
+  </si>
+  <si>
+    <t>12.05.202617</t>
+  </si>
+  <si>
+    <t>12.05.202618</t>
+  </si>
+  <si>
+    <t>12.05.202619</t>
+  </si>
+  <si>
+    <t>12.05.202620</t>
+  </si>
+  <si>
+    <t>12.05.202621</t>
+  </si>
+  <si>
+    <t>12.05.202622</t>
+  </si>
+  <si>
+    <t>12.05.202623</t>
+  </si>
+  <si>
+    <t>12.05.202624</t>
+  </si>
+  <si>
+    <t>12.05.202625</t>
+  </si>
+  <si>
+    <t>12.05.202626</t>
+  </si>
+  <si>
+    <t>12.05.202627</t>
+  </si>
+  <si>
+    <t>12.05.202628</t>
+  </si>
+  <si>
+    <t>12.05.202629</t>
+  </si>
+  <si>
+    <t>12.05.202630</t>
+  </si>
+  <si>
+    <t>12.05.202631</t>
+  </si>
+  <si>
+    <t>12.05.202632</t>
+  </si>
+  <si>
+    <t>12.05.202633</t>
+  </si>
+  <si>
+    <t>12.05.202634</t>
+  </si>
+  <si>
+    <t>12.05.202635</t>
+  </si>
+  <si>
+    <t>12.05.202636</t>
+  </si>
+  <si>
+    <t>12.05.202637</t>
+  </si>
+  <si>
+    <t>12.05.202638</t>
+  </si>
+  <si>
+    <t>12.05.202639</t>
+  </si>
+  <si>
+    <t>12.05.202640</t>
+  </si>
+  <si>
+    <t>12.05.202641</t>
+  </si>
+  <si>
+    <t>12.05.202642</t>
+  </si>
+  <si>
+    <t>12.05.202643</t>
+  </si>
+  <si>
+    <t>12.05.202644</t>
+  </si>
+  <si>
+    <t>12.05.202645</t>
+  </si>
+  <si>
+    <t>12.05.202646</t>
+  </si>
+  <si>
+    <t>12.05.202647</t>
+  </si>
+  <si>
+    <t>12.05.202648</t>
+  </si>
+  <si>
+    <t>12.05.202649</t>
+  </si>
+  <si>
+    <t>12.05.202650</t>
+  </si>
+  <si>
+    <t>12.05.202651</t>
+  </si>
+  <si>
+    <t>12.05.202652</t>
+  </si>
+  <si>
+    <t>12.05.202653</t>
+  </si>
+  <si>
+    <t>12.05.202654</t>
+  </si>
+  <si>
+    <t>12.05.202655</t>
+  </si>
+  <si>
+    <t>12.05.202656</t>
+  </si>
+  <si>
+    <t>12.05.202657</t>
+  </si>
+  <si>
+    <t>12.05.202658</t>
+  </si>
+  <si>
+    <t>12.05.202659</t>
+  </si>
+  <si>
+    <t>12.05.202660</t>
+  </si>
+  <si>
+    <t>12.05.202661</t>
+  </si>
+  <si>
+    <t>12.05.202662</t>
+  </si>
+  <si>
+    <t>12.05.202663</t>
+  </si>
+  <si>
+    <t>12.05.202664</t>
+  </si>
+  <si>
+    <t>12.05.202665</t>
+  </si>
+  <si>
+    <t>12.05.202666</t>
+  </si>
+  <si>
+    <t>12.05.202667</t>
+  </si>
+  <si>
+    <t>12.05.202668</t>
+  </si>
+  <si>
+    <t>12.05.202669</t>
+  </si>
+  <si>
+    <t>12.05.202670</t>
+  </si>
+  <si>
+    <t>12.05.202671</t>
+  </si>
+  <si>
+    <t>12.05.202672</t>
+  </si>
+  <si>
+    <t>12.05.202673</t>
+  </si>
+  <si>
+    <t>12.05.202674</t>
+  </si>
+  <si>
+    <t>12.05.202675</t>
+  </si>
+  <si>
+    <t>12.05.202676</t>
+  </si>
+  <si>
+    <t>12.05.202677</t>
+  </si>
+  <si>
+    <t>12.05.202678</t>
+  </si>
+  <si>
+    <t>12.05.202679</t>
+  </si>
+  <si>
+    <t>12.05.202680</t>
+  </si>
+  <si>
+    <t>12.05.202681</t>
+  </si>
+  <si>
+    <t>12.05.202682</t>
+  </si>
+  <si>
+    <t>12.05.202683</t>
+  </si>
+  <si>
+    <t>12.05.202684</t>
+  </si>
+  <si>
+    <t>12.05.202685</t>
+  </si>
+  <si>
+    <t>12.05.202686</t>
+  </si>
+  <si>
+    <t>12.05.202687</t>
+  </si>
+  <si>
+    <t>12.05.202688</t>
+  </si>
+  <si>
+    <t>12.05.202689</t>
+  </si>
+  <si>
+    <t>12.05.202690</t>
+  </si>
+  <si>
+    <t>12.05.202691</t>
+  </si>
+  <si>
+    <t>12.05.202692</t>
+  </si>
+  <si>
+    <t>12.05.202693</t>
+  </si>
+  <si>
+    <t>12.05.202694</t>
+  </si>
+  <si>
+    <t>12.05.202695</t>
+  </si>
+  <si>
+    <t>12.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46149.01041666666</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46149.02083333334</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46149.03125</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46149.04166666666</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
-        <v>75.64400000000001</v>
+        <v>-14.168</v>
       </c>
       <c r="C6">
-        <v>173.336</v>
+        <v>600</v>
       </c>
       <c r="D6">
-        <v>173.336</v>
+        <v>600</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46149.05208333334</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
-        <v>67.268</v>
+        <v>-8.077999999999999</v>
       </c>
       <c r="C7">
-        <v>318</v>
+        <v>2500.833</v>
       </c>
       <c r="D7">
-        <v>318</v>
+        <v>2500.833</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46149.0625</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
-        <v>50.75</v>
+        <v>-0.38</v>
       </c>
       <c r="C8">
-        <v>171.627</v>
+        <v>270.979</v>
       </c>
       <c r="D8">
-        <v>171.627</v>
+        <v>270.979</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46149.07291666666</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
-        <v>30.632</v>
+        <v>-14.341</v>
       </c>
       <c r="C9">
-        <v>-75.285</v>
+        <v>886.681</v>
       </c>
       <c r="D9">
-        <v>-75.285</v>
+        <v>886.681</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46149.08333333334</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
-        <v>51.825</v>
+        <v>-17.073</v>
       </c>
       <c r="C10">
-        <v>139.692</v>
+        <v>891.8200000000001</v>
       </c>
       <c r="D10">
-        <v>139.692</v>
+        <v>891.8200000000001</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46149.09375</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
-        <v>34.007</v>
+        <v>-46.73</v>
       </c>
       <c r="C11">
-        <v>197.004</v>
+        <v>936.24</v>
       </c>
       <c r="D11">
-        <v>197.004</v>
+        <v>936.24</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46149.10416666666</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
-        <v>34.843</v>
+        <v>-34.524</v>
       </c>
       <c r="C12">
-        <v>288.953</v>
+        <v>884.273</v>
       </c>
       <c r="D12">
-        <v>288.953</v>
+        <v>884.273</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46149.11458333334</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>4.537</v>
+        <v>-46.921</v>
       </c>
       <c r="C13">
-        <v>256.841</v>
+        <v>889.89</v>
       </c>
       <c r="D13">
-        <v>256.841</v>
+        <v>889.89</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46149.125</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>19.757</v>
+        <v>-18.139</v>
       </c>
       <c r="C14">
-        <v>-7.642</v>
+        <v>897.4</v>
       </c>
       <c r="D14">
-        <v>-7.642</v>
+        <v>897.4</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46149.13541666666</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>9.137</v>
+        <v>-38.346</v>
       </c>
       <c r="C15">
-        <v>20.29</v>
+        <v>950.441</v>
       </c>
       <c r="D15">
-        <v>20.29</v>
+        <v>950.441</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46149.14583333334</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>24.103</v>
+        <v>-6.504</v>
       </c>
       <c r="C16">
-        <v>51.473</v>
+        <v>899.159</v>
       </c>
       <c r="D16">
-        <v>51.473</v>
+        <v>899.159</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46149.15625</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>12.723</v>
+        <v>5.774</v>
       </c>
       <c r="C17">
-        <v>199.796</v>
+        <v>400</v>
       </c>
       <c r="D17">
-        <v>199.796</v>
+        <v>400</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46149.16666666666</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>67.488</v>
+        <v>9.487</v>
       </c>
       <c r="C18">
-        <v>-83.077</v>
+        <v>340.947</v>
       </c>
       <c r="D18">
-        <v>-83.077</v>
+        <v>340.947</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46149.17708333334</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>31.634</v>
+        <v>-3.326</v>
       </c>
       <c r="C19">
-        <v>-144.797</v>
+        <v>899.295</v>
       </c>
       <c r="D19">
-        <v>-144.797</v>
+        <v>899.295</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46149.1875</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>32.177</v>
+        <v>-2.319</v>
       </c>
       <c r="C20">
-        <v>-118.031</v>
+        <v>898.38</v>
       </c>
       <c r="D20">
-        <v>-118.031</v>
+        <v>898.38</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46149.19791666666</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>33.746</v>
+        <v>29.408</v>
       </c>
       <c r="C21">
-        <v>-119.257</v>
+        <v>314.432</v>
       </c>
       <c r="D21">
-        <v>-119.257</v>
+        <v>314.432</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46149.20833333334</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>77.446</v>
+        <v>79.20699999999999</v>
       </c>
       <c r="C22">
-        <v>-1413.477</v>
+        <v>259.73</v>
       </c>
       <c r="D22">
-        <v>-1413.477</v>
+        <v>259.73</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46149.21875</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>55.876</v>
+        <v>58.444</v>
       </c>
       <c r="C23">
-        <v>-253.469</v>
+        <v>283.661</v>
       </c>
       <c r="D23">
-        <v>-253.469</v>
+        <v>283.661</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46149.22916666666</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>57.595</v>
+        <v>36.431</v>
       </c>
       <c r="C24">
-        <v>-44.415</v>
+        <v>-9.872999999999999</v>
       </c>
       <c r="D24">
-        <v>-44.415</v>
+        <v>-9.872999999999999</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46149.23958333334</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>77.68899999999999</v>
+        <v>50.171</v>
       </c>
       <c r="C25">
-        <v>-35.297</v>
+        <v>-60.349</v>
       </c>
       <c r="D25">
-        <v>-35.297</v>
+        <v>-60.349</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46149.25</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>95.67700000000001</v>
+        <v>77.51300000000001</v>
       </c>
       <c r="C26">
-        <v>-117.377</v>
+        <v>-821.896</v>
       </c>
       <c r="D26">
-        <v>-117.377</v>
+        <v>-821.896</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46149.26041666666</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>107.79</v>
+        <v>105.659</v>
       </c>
       <c r="C27">
-        <v>-47.194</v>
+        <v>-1279.248</v>
       </c>
       <c r="D27">
-        <v>-47.194</v>
+        <v>-1279.248</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46149.27083333334</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>27.708</v>
+        <v>84.858</v>
       </c>
       <c r="C28">
-        <v>18.519</v>
+        <v>-736.158</v>
       </c>
       <c r="D28">
-        <v>18.519</v>
+        <v>-736.158</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46149.28125</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>35.892</v>
+        <v>127.552</v>
       </c>
       <c r="C29">
-        <v>10.101</v>
+        <v>19.42</v>
       </c>
       <c r="D29">
-        <v>10.101</v>
+        <v>19.42</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46149.29166666666</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>-3.227</v>
+        <v>112.201</v>
       </c>
       <c r="C30">
-        <v>1301.983</v>
+        <v>10.1</v>
       </c>
       <c r="D30">
-        <v>1301.983</v>
+        <v>10.1</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46149.30208333334</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>7.408</v>
+        <v>86.818</v>
       </c>
       <c r="C31">
-        <v>1.1</v>
+        <v>-6.984</v>
       </c>
       <c r="D31">
-        <v>1.1</v>
+        <v>-6.984</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46149.3125</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>-13.462</v>
+        <v>120.677</v>
       </c>
       <c r="C32">
-        <v>1607.59</v>
+        <v>18.573</v>
       </c>
       <c r="D32">
-        <v>1607.59</v>
+        <v>18.573</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46149.32291666666</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>4.767</v>
+        <v>79.68300000000001</v>
       </c>
       <c r="C33">
-        <v>820.591</v>
+        <v>-10.835</v>
       </c>
       <c r="D33">
-        <v>820.591</v>
+        <v>-10.835</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46149.33333333334</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>-56.475</v>
+        <v>87.498</v>
       </c>
       <c r="C34">
-        <v>920.081</v>
+        <v>-61.359</v>
       </c>
       <c r="D34">
-        <v>920.081</v>
+        <v>-61.359</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46149.34375</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>-39.985</v>
+        <v>88.902</v>
       </c>
       <c r="C35">
-        <v>1209.327</v>
+        <v>-296.583</v>
       </c>
       <c r="D35">
-        <v>1209.327</v>
+        <v>-296.583</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46149.35416666666</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>-69.292</v>
+        <v>110.341</v>
       </c>
       <c r="C36">
-        <v>1410.982</v>
+        <v>-772.063</v>
       </c>
       <c r="D36">
-        <v>1410.982</v>
+        <v>-772.063</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46149.36458333334</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>-83.377</v>
+        <v>110.856</v>
       </c>
       <c r="C37">
-        <v>1475.663</v>
+        <v>-425.411</v>
       </c>
       <c r="D37">
-        <v>1475.663</v>
+        <v>-425.411</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46149.375</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>-92.592</v>
+        <v>92.789</v>
       </c>
       <c r="C38">
-        <v>2762.582</v>
+        <v>1.967</v>
       </c>
       <c r="D38">
-        <v>2762.582</v>
+        <v>1.967</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46149.38541666666</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>-50.236</v>
+        <v>145.429</v>
       </c>
       <c r="C39">
-        <v>1807.783</v>
+        <v>2.294</v>
       </c>
       <c r="D39">
-        <v>1807.783</v>
+        <v>2.294</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46149.39583333334</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>-88.441</v>
+        <v>140.161</v>
       </c>
       <c r="C40">
-        <v>1941.374</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="D40">
-        <v>1941.374</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46149.40625</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>-40.827</v>
+        <v>66.036</v>
       </c>
       <c r="C41">
-        <v>899</v>
+        <v>-1.19</v>
       </c>
       <c r="D41">
-        <v>899</v>
+        <v>-1.19</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46149.41666666666</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>-27.452</v>
+        <v>5.39</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1.382</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1.382</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46149.42708333334</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>43.107</v>
+        <v>43.794</v>
       </c>
       <c r="C43">
-        <v>261.483</v>
+        <v>1.092</v>
       </c>
       <c r="D43">
-        <v>261.483</v>
+        <v>1.092</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46149.4375</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>46.88</v>
+        <v>-19.363</v>
       </c>
       <c r="C44">
-        <v>189.421</v>
+        <v>700</v>
       </c>
       <c r="D44">
-        <v>189.421</v>
+        <v>700</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46149.44791666666</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>16.858</v>
+        <v>26.403</v>
       </c>
       <c r="C45">
-        <v>426.787</v>
+        <v>-49.97</v>
       </c>
       <c r="D45">
-        <v>426.787</v>
+        <v>-49.97</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46149.45833333334</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>9.254</v>
+        <v>14.558</v>
       </c>
       <c r="C46">
-        <v>401</v>
+        <v>-12.656</v>
       </c>
       <c r="D46">
-        <v>401</v>
+        <v>-12.656</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46149.46875</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>41.555</v>
+        <v>41.945</v>
       </c>
       <c r="C47">
-        <v>300.895</v>
+        <v>-2.018</v>
       </c>
       <c r="D47">
-        <v>300.895</v>
+        <v>-2.018</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46149.47916666666</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>35.981</v>
+        <v>55.558</v>
       </c>
       <c r="C48">
-        <v>344.617</v>
+        <v>39.791</v>
       </c>
       <c r="D48">
-        <v>344.617</v>
+        <v>39.791</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46149.48958333334</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>14.462</v>
+        <v>6.997</v>
       </c>
       <c r="C49">
-        <v>500</v>
+        <v>0.6</v>
       </c>
       <c r="D49">
-        <v>500</v>
+        <v>0.6</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46149.5</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>47.905</v>
+        <v>-39.435</v>
       </c>
       <c r="C50">
-        <v>400.867</v>
+        <v>771.495</v>
       </c>
       <c r="D50">
-        <v>400.867</v>
+        <v>771.495</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46149.51041666666</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>43.117</v>
+        <v>-16.057</v>
       </c>
       <c r="C51">
-        <v>348.611</v>
+        <v>841.759</v>
       </c>
       <c r="D51">
-        <v>348.611</v>
+        <v>841.759</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46149.52083333334</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>24.234</v>
+        <v>-4.555</v>
       </c>
       <c r="C52">
-        <v>393.182</v>
+        <v>700</v>
       </c>
       <c r="D52">
-        <v>393.182</v>
+        <v>700</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46149.53125</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>29.19</v>
+        <v>42.623</v>
       </c>
       <c r="C53">
-        <v>346.429</v>
+        <v>-288.757</v>
       </c>
       <c r="D53">
-        <v>346.429</v>
+        <v>-288.757</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46149.54166666666</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>-8.287000000000001</v>
+        <v>-29.489</v>
       </c>
       <c r="C54">
-        <v>1058.799</v>
+        <v>716.197</v>
       </c>
       <c r="D54">
-        <v>1058.799</v>
+        <v>716.197</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46149.55208333334</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
-        <v>-24.784</v>
+        <v>-50.073</v>
       </c>
       <c r="C55">
-        <v>1091.616</v>
+        <v>816.669</v>
       </c>
       <c r="D55">
-        <v>1091.616</v>
+        <v>816.669</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46149.5625</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>-17.18</v>
+        <v>18.373</v>
       </c>
       <c r="C56">
-        <v>899.393</v>
+        <v>-89.765</v>
       </c>
       <c r="D56">
-        <v>899.393</v>
+        <v>-89.765</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46149.57291666666</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>25.095</v>
+        <v>57.757</v>
       </c>
       <c r="C57">
-        <v>400</v>
+        <v>-893.168</v>
       </c>
       <c r="D57">
-        <v>400</v>
+        <v>-893.168</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46149.58333333334</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>66.602</v>
+        <v>69.015</v>
       </c>
       <c r="C58">
-        <v>427.177</v>
+        <v>-3442.658</v>
       </c>
       <c r="D58">
-        <v>427.177</v>
+        <v>-3442.658</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46149.59375</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>17.997</v>
+        <v>80.52</v>
       </c>
       <c r="C59">
-        <v>442.274</v>
+        <v>-3219.49</v>
       </c>
       <c r="D59">
-        <v>442.274</v>
+        <v>-3219.49</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46149.60416666666</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>75.72</v>
+        <v>41.556</v>
       </c>
       <c r="C60">
-        <v>420.947</v>
+        <v>-71.377</v>
       </c>
       <c r="D60">
-        <v>420.947</v>
+        <v>-71.377</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46149.61458333334</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>77.23099999999999</v>
+        <v>41.449</v>
       </c>
       <c r="C61">
-        <v>419.827</v>
+        <v>-1.125</v>
       </c>
       <c r="D61">
-        <v>419.827</v>
+        <v>-1.125</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46149.625</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>37.323</v>
+        <v>57.01</v>
       </c>
       <c r="C62">
-        <v>-3.859</v>
+        <v>-20.927</v>
       </c>
       <c r="D62">
-        <v>-3.859</v>
+        <v>-20.927</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46149.63541666666</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>35.618</v>
+        <v>92.24299999999999</v>
       </c>
       <c r="C63">
-        <v>-77.01000000000001</v>
+        <v>-7.109</v>
       </c>
       <c r="D63">
-        <v>-77.01000000000001</v>
+        <v>-7.109</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46149.64583333334</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>23.865</v>
+        <v>125.296</v>
       </c>
       <c r="C64">
-        <v>3.927</v>
+        <v>-97.05200000000001</v>
       </c>
       <c r="D64">
-        <v>3.927</v>
+        <v>-97.05200000000001</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46149.65625</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>22.882</v>
+        <v>78.84099999999999</v>
       </c>
       <c r="C65">
-        <v>1.1</v>
+        <v>-513.053</v>
       </c>
       <c r="D65">
-        <v>1.1</v>
+        <v>-513.053</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46149.66666666666</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>-41.431</v>
+        <v>61.731</v>
       </c>
       <c r="C66">
-        <v>529.226</v>
+        <v>-3.514</v>
       </c>
       <c r="D66">
-        <v>529.226</v>
+        <v>-3.514</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46149.67708333334</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>-72.706</v>
+        <v>93.375</v>
       </c>
       <c r="C67">
-        <v>3460.521</v>
+        <v>-25.985</v>
       </c>
       <c r="D67">
-        <v>3460.521</v>
+        <v>-25.985</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46149.6875</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>-0.011</v>
+        <v>81.027</v>
       </c>
       <c r="C68">
-        <v>1450.205</v>
+        <v>1.65</v>
       </c>
       <c r="D68">
-        <v>1450.205</v>
+        <v>1.65</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46149.69791666666</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>24.411</v>
+        <v>27.03</v>
       </c>
       <c r="C69">
-        <v>401</v>
+        <v>4.038</v>
       </c>
       <c r="D69">
-        <v>401</v>
+        <v>4.038</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46149.70833333334</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>38.976</v>
+        <v>-21.747</v>
       </c>
       <c r="C70">
-        <v>196.049</v>
+        <v>804.516</v>
       </c>
       <c r="D70">
-        <v>196.049</v>
+        <v>804.516</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46149.71875</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>67.94199999999999</v>
+        <v>-29.609</v>
       </c>
       <c r="C71">
-        <v>-30.232</v>
+        <v>1909.084</v>
       </c>
       <c r="D71">
-        <v>-30.232</v>
+        <v>1909.084</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46149.72916666666</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>56.225</v>
+        <v>-36.645</v>
       </c>
       <c r="C72">
-        <v>144.116</v>
+        <v>1104.124</v>
       </c>
       <c r="D72">
-        <v>144.116</v>
+        <v>1104.124</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46149.73958333334</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>76.06</v>
+        <v>-81.491</v>
       </c>
       <c r="C73">
-        <v>351.402</v>
+        <v>1157.284</v>
       </c>
       <c r="D73">
-        <v>351.402</v>
+        <v>1157.284</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46149.75</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>84.43300000000001</v>
+        <v>-3.795</v>
       </c>
       <c r="C74">
-        <v>-56.658</v>
+        <v>1128.499</v>
       </c>
       <c r="D74">
-        <v>-56.658</v>
+        <v>1128.499</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46149.76041666666</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>57.919</v>
+        <v>-74.571</v>
       </c>
       <c r="C75">
-        <v>401</v>
+        <v>1038.935</v>
       </c>
       <c r="D75">
-        <v>401</v>
+        <v>1038.935</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46149.77083333334</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>61.307</v>
+        <v>-38.374</v>
       </c>
       <c r="C76">
-        <v>16.49</v>
+        <v>1146.026</v>
       </c>
       <c r="D76">
-        <v>16.49</v>
+        <v>1146.026</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46149.78125</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>47.832</v>
+        <v>0.037</v>
       </c>
       <c r="C77">
-        <v>133.359</v>
+        <v>186.623</v>
       </c>
       <c r="D77">
-        <v>133.359</v>
+        <v>186.623</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46149.79166666666</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>85.95399999999999</v>
+        <v>46.075</v>
       </c>
       <c r="C78">
-        <v>-251.621</v>
+        <v>222.342</v>
       </c>
       <c r="D78">
-        <v>-251.621</v>
+        <v>222.342</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46149.80208333334</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>86.988</v>
+        <v>59.373</v>
       </c>
       <c r="C79">
-        <v>-464.302</v>
+        <v>286.824</v>
       </c>
       <c r="D79">
-        <v>-464.302</v>
+        <v>286.824</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46149.8125</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>59.543</v>
+        <v>58.935</v>
       </c>
       <c r="C80">
-        <v>-2.853</v>
+        <v>275.17</v>
       </c>
       <c r="D80">
-        <v>-2.853</v>
+        <v>275.17</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46149.82291666666</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>47.885</v>
+        <v>61.706</v>
       </c>
       <c r="C81">
-        <v>401</v>
+        <v>17.654</v>
       </c>
       <c r="D81">
-        <v>401</v>
+        <v>17.654</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46149.83333333334</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
-        <v>27.64</v>
+        <v>12.185</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>64.041</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>64.041</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46149.84375</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>19.129</v>
+        <v>18.576</v>
       </c>
       <c r="C83">
-        <v>182.659</v>
+        <v>217.631</v>
       </c>
       <c r="D83">
-        <v>182.659</v>
+        <v>217.631</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46149.85416666666</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>17.03</v>
+        <v>20.495</v>
       </c>
       <c r="C84">
-        <v>365.23</v>
+        <v>303.149</v>
       </c>
       <c r="D84">
-        <v>365.23</v>
+        <v>303.149</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46149.86458333334</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>-0.8090000000000001</v>
+        <v>20.291</v>
       </c>
       <c r="C85">
-        <v>897.1900000000001</v>
+        <v>258.511</v>
       </c>
       <c r="D85">
-        <v>897.1900000000001</v>
+        <v>258.511</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46149.875</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>-5.758</v>
+        <v>7.847</v>
       </c>
       <c r="C86">
-        <v>1146.777</v>
+        <v>208.907</v>
       </c>
       <c r="D86">
-        <v>1146.777</v>
+        <v>208.907</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46149.88541666666</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>7.924</v>
+        <v>10.225</v>
       </c>
       <c r="C87">
-        <v>400</v>
+        <v>255.679</v>
       </c>
       <c r="D87">
-        <v>400</v>
+        <v>255.679</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46149.89583333334</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>5.319</v>
+        <v>58.774</v>
       </c>
       <c r="C88">
-        <v>317.871</v>
+        <v>210.098</v>
       </c>
       <c r="D88">
-        <v>317.871</v>
+        <v>210.098</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46149.90625</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>12.729</v>
+        <v>68.07899999999999</v>
       </c>
       <c r="C89">
-        <v>-72.608</v>
+        <v>-178.056</v>
       </c>
       <c r="D89">
-        <v>-72.608</v>
+        <v>-178.056</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46149.91666666666</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>6.973</v>
+        <v>76.911</v>
       </c>
       <c r="C90">
-        <v>123.878</v>
+        <v>-59.874</v>
       </c>
       <c r="D90">
-        <v>123.878</v>
+        <v>-59.874</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46149.92708333334</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>40.916</v>
+        <v>27.274</v>
       </c>
       <c r="C91">
-        <v>-10.47</v>
+        <v>115.015</v>
       </c>
       <c r="D91">
-        <v>-10.47</v>
+        <v>115.015</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46149.9375</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
-        <v>35.862</v>
+        <v>13.165</v>
       </c>
       <c r="C92">
-        <v>14.282</v>
+        <v>111.03</v>
       </c>
       <c r="D92">
-        <v>14.282</v>
+        <v>111.03</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46149.94791666666</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
-        <v>56.9</v>
+        <v>5.592</v>
       </c>
       <c r="C93">
-        <v>76.246</v>
+        <v>209.729</v>
       </c>
       <c r="D93">
-        <v>76.246</v>
+        <v>209.729</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46149.95833333334</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
-        <v>41.376</v>
+        <v>48.15</v>
       </c>
       <c r="C94">
-        <v>119.387</v>
+        <v>228.831</v>
       </c>
       <c r="D94">
-        <v>119.387</v>
+        <v>228.831</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46149.96875</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
-        <v>32.236</v>
+        <v>63.33</v>
       </c>
       <c r="C95">
-        <v>83.075</v>
+        <v>-246.371</v>
       </c>
       <c r="D95">
-        <v>83.075</v>
+        <v>-246.371</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46149.97916666666</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
-        <v>48.664</v>
+        <v>50.686</v>
       </c>
       <c r="C96">
-        <v>-45.506</v>
+        <v>10.338</v>
       </c>
       <c r="D96">
-        <v>-45.506</v>
+        <v>10.338</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46149.98958333334</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
-        <v>41.203</v>
+        <v>39.261</v>
       </c>
       <c r="C97">
-        <v>-27.195</v>
+        <v>16.994</v>
       </c>
       <c r="D97">
-        <v>-27.195</v>
+        <v>16.994</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B98">
-        <v>63.241</v>
+        <v>22.91</v>
       </c>
       <c r="C98">
-        <v>192.803</v>
+        <v>7.253</v>
       </c>
       <c r="D98">
-        <v>192.803</v>
+        <v>7.253</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46150.01041666666</v>
+        <v>46154.01041666666</v>
       </c>
       <c r="B99">
-        <v>77.193</v>
+        <v>30.921</v>
       </c>
       <c r="C99">
-        <v>354.429</v>
+        <v>1.1</v>
       </c>
       <c r="D99">
-        <v>354.429</v>
+        <v>1.1</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46150.02083333334</v>
+        <v>46154.02083333334</v>
       </c>
       <c r="B100">
-        <v>122.479</v>
+        <v>37.232</v>
       </c>
       <c r="C100">
-        <v>338.239</v>
+        <v>1.451</v>
       </c>
       <c r="D100">
-        <v>338.239</v>
+        <v>1.451</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46150.03125</v>
+        <v>46154.03125</v>
       </c>
       <c r="B101">
-        <v>64.41500000000001</v>
+        <v>3.079</v>
       </c>
       <c r="C101">
-        <v>-11.319</v>
+        <v>1.1</v>
       </c>
       <c r="D101">
-        <v>-11.319</v>
+        <v>1.1</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46150.04166666666</v>
+        <v>46154.04166666666</v>
       </c>
       <c r="B102">
-        <v>64.501</v>
+        <v>49.171</v>
       </c>
       <c r="C102">
-        <v>6.206</v>
+        <v>3.209</v>
       </c>
       <c r="D102">
-        <v>6.206</v>
+        <v>3.209</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46150.05208333334</v>
+        <v>46154.05208333334</v>
       </c>
       <c r="B103">
-        <v>51.712</v>
+        <v>57.152</v>
       </c>
       <c r="C103">
-        <v>-8.954000000000001</v>
+        <v>26.288</v>
       </c>
       <c r="D103">
-        <v>-8.954000000000001</v>
+        <v>26.288</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46150.0625</v>
+        <v>46154.0625</v>
       </c>
       <c r="B104">
-        <v>79.038</v>
+        <v>83.49299999999999</v>
       </c>
       <c r="C104">
-        <v>-83.652</v>
+        <v>32.937</v>
       </c>
       <c r="D104">
-        <v>-83.652</v>
+        <v>32.937</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46150.07291666666</v>
+        <v>46154.07291666666</v>
       </c>
       <c r="B105">
-        <v>76.267</v>
+        <v>52.954</v>
       </c>
       <c r="C105">
-        <v>1.867</v>
+        <v>-56.494</v>
       </c>
       <c r="D105">
-        <v>1.867</v>
+        <v>-56.494</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46150.08333333334</v>
+        <v>46154.08333333334</v>
       </c>
       <c r="B106">
-        <v>121.323</v>
+        <v>85.873</v>
       </c>
       <c r="C106">
-        <v>8.298</v>
+        <v>37.527</v>
       </c>
       <c r="D106">
-        <v>8.298</v>
+        <v>37.527</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46150.09375</v>
+        <v>46154.09375</v>
       </c>
       <c r="B107">
-        <v>97.538</v>
+        <v>41.985</v>
       </c>
       <c r="C107">
-        <v>-5.535</v>
+        <v>58.64</v>
       </c>
       <c r="D107">
-        <v>-5.535</v>
+        <v>58.64</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46150.10416666666</v>
+        <v>46154.10416666666</v>
       </c>
       <c r="B108">
-        <v>95.926</v>
+        <v>28.262</v>
       </c>
       <c r="C108">
-        <v>-5.968</v>
+        <v>-7.602</v>
       </c>
       <c r="D108">
-        <v>-5.968</v>
+        <v>-7.602</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46150.11458333334</v>
+        <v>46154.11458333334</v>
       </c>
       <c r="B109">
-        <v>42.734</v>
+        <v>18.471</v>
       </c>
       <c r="C109">
-        <v>20.491</v>
+        <v>12.646</v>
       </c>
       <c r="D109">
-        <v>20.491</v>
+        <v>12.646</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46150.125</v>
+        <v>46154.125</v>
       </c>
       <c r="B110">
-        <v>64.39</v>
+        <v>-9.81</v>
       </c>
       <c r="C110">
-        <v>17.934</v>
+        <v>894.082</v>
       </c>
       <c r="D110">
-        <v>17.934</v>
+        <v>894.082</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46150.13541666666</v>
+        <v>46154.13541666666</v>
       </c>
       <c r="B111">
-        <v>23.996</v>
+        <v>-59.708</v>
       </c>
       <c r="C111">
-        <v>1.89</v>
+        <v>814.499</v>
       </c>
       <c r="D111">
-        <v>1.89</v>
+        <v>814.499</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46150.14583333334</v>
+        <v>46154.14583333334</v>
       </c>
       <c r="B112">
-        <v>38.831</v>
+        <v>-65.226</v>
       </c>
       <c r="C112">
-        <v>1.403</v>
+        <v>918.426</v>
       </c>
       <c r="D112">
-        <v>1.403</v>
+        <v>918.426</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46150.15625</v>
+        <v>46154.15625</v>
       </c>
       <c r="B113">
-        <v>42.896</v>
+        <v>-82.996</v>
       </c>
       <c r="C113">
-        <v>4.732</v>
+        <v>866.374</v>
       </c>
       <c r="D113">
-        <v>4.732</v>
+        <v>866.374</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46150.16666666666</v>
+        <v>46154.16666666666</v>
       </c>
       <c r="B114">
-        <v>102.239</v>
+        <v>-89.926</v>
       </c>
       <c r="C114">
-        <v>289.538</v>
+        <v>1463.553</v>
       </c>
       <c r="D114">
-        <v>289.538</v>
+        <v>1463.553</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46150.17708333334</v>
+        <v>46154.17708333334</v>
       </c>
       <c r="B115">
-        <v>99.46299999999999</v>
+        <v>-102.381</v>
       </c>
       <c r="C115">
-        <v>43.265</v>
+        <v>3799.622</v>
       </c>
       <c r="D115">
-        <v>43.265</v>
+        <v>3799.622</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46150.1875</v>
+        <v>46154.1875</v>
       </c>
       <c r="B116">
-        <v>84.414</v>
+        <v>-83.84399999999999</v>
       </c>
       <c r="C116">
-        <v>-254.86</v>
+        <v>1074.528</v>
       </c>
       <c r="D116">
-        <v>-254.86</v>
+        <v>1074.528</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46150.19791666666</v>
+        <v>46154.19791666666</v>
       </c>
       <c r="B117">
-        <v>107.469</v>
+        <v>-63.075</v>
       </c>
       <c r="C117">
-        <v>195.065</v>
+        <v>1087.546</v>
       </c>
       <c r="D117">
-        <v>195.065</v>
+        <v>1087.546</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46150.20833333334</v>
+        <v>46154.20833333334</v>
       </c>
       <c r="B118">
-        <v>155.849</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>21.05</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>21.05</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46150.21875</v>
+        <v>46154.21875</v>
       </c>
       <c r="B119">
-        <v>114.822</v>
+        <v>-40.118</v>
       </c>
       <c r="C119">
-        <v>9.85</v>
+        <v>1187.709</v>
       </c>
       <c r="D119">
-        <v>9.85</v>
+        <v>1187.709</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46150.22916666666</v>
+        <v>46154.22916666666</v>
       </c>
       <c r="B120">
-        <v>95.06699999999999</v>
+        <v>-34.442</v>
       </c>
       <c r="C120">
-        <v>9.073</v>
+        <v>1172.691</v>
       </c>
       <c r="D120">
-        <v>9.073</v>
+        <v>1172.691</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46150.23958333334</v>
+        <v>46154.23958333334</v>
       </c>
       <c r="B121">
-        <v>90.866</v>
+        <v>-40.241</v>
       </c>
       <c r="C121">
-        <v>-8.052</v>
+        <v>1177.233</v>
       </c>
       <c r="D121">
-        <v>-8.052</v>
+        <v>1177.233</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46150.25</v>
+        <v>46154.25</v>
       </c>
       <c r="B122">
-        <v>79.943</v>
+        <v>-16.118</v>
       </c>
       <c r="C122">
-        <v>-640.484</v>
+        <v>1508.113</v>
       </c>
       <c r="D122">
-        <v>-640.484</v>
+        <v>1508.113</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46150.26041666666</v>
+        <v>46154.26041666666</v>
       </c>
       <c r="B123">
-        <v>107.323</v>
+        <v>-60.464</v>
       </c>
       <c r="C123">
-        <v>5.334</v>
+        <v>1189.467</v>
       </c>
       <c r="D123">
-        <v>5.334</v>
+        <v>1189.467</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46150.27083333334</v>
+        <v>46154.27083333334</v>
       </c>
       <c r="B124">
-        <v>49.965</v>
+        <v>8.606</v>
       </c>
       <c r="C124">
-        <v>325.925</v>
+        <v>-77.48</v>
       </c>
       <c r="D124">
-        <v>325.925</v>
+        <v>-77.48</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46150.28125</v>
+        <v>46154.28125</v>
       </c>
       <c r="B125">
-        <v>22.551</v>
+        <v>33.602</v>
       </c>
       <c r="C125">
-        <v>334.99</v>
+        <v>-54.995</v>
       </c>
       <c r="D125">
-        <v>334.99</v>
+        <v>-54.995</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46150.29166666666</v>
+        <v>46154.29166666666</v>
       </c>
       <c r="B126">
-        <v>46.846</v>
+        <v>82.63500000000001</v>
       </c>
       <c r="C126">
-        <v>290.623</v>
+        <v>60.365</v>
       </c>
       <c r="D126">
-        <v>290.623</v>
+        <v>60.365</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46150.30208333334</v>
+        <v>46154.30208333334</v>
       </c>
       <c r="B127">
-        <v>77.444</v>
+        <v>71.577</v>
       </c>
       <c r="C127">
-        <v>273.29</v>
+        <v>-399.22</v>
       </c>
       <c r="D127">
-        <v>273.29</v>
+        <v>-399.22</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46150.3125</v>
+        <v>46154.3125</v>
       </c>
       <c r="B128">
-        <v>57.612</v>
+        <v>104.235</v>
       </c>
       <c r="C128">
-        <v>-58.385</v>
+        <v>-232.443</v>
       </c>
       <c r="D128">
-        <v>-58.385</v>
+        <v>-232.443</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46150.32291666666</v>
+        <v>46154.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>28.477</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>-6.641</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>-6.641</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46150.33333333334</v>
+        <v>46154.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>-128.632</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>917.957</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>917.957</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46150.34375</v>
+        <v>46154.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>-139.276</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>5093.388</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>5093.388</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46150.35416666666</v>
+        <v>46154.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>-128.529</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>4634.56</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>4634.56</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46150.36458333334</v>
+        <v>46154.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>-149.961</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>3297.331</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>3297.331</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46150.375</v>
+        <v>46154.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>-233.197</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>2831.181</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>2831.181</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46150.38541666666</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>-214.142</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>957.452</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>957.452</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46150.39583333334</v>
+        <v>46154.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>-98.373</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>942.62</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>942.62</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46150.40625</v>
+        <v>46154.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>-40.696</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46150.41666666666</v>
+        <v>46154.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>120.943</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>-1873.474</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>-1873.474</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46150.42708333334</v>
+        <v>46154.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>62.745</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>-518.845</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>-518.845</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46150.4375</v>
+        <v>46154.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46150.44791666666</v>
+        <v>46154.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46150.45833333334</v>
+        <v>46154.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46150.46875</v>
+        <v>46154.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46150.47916666666</v>
+        <v>46154.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46150.48958333334</v>
+        <v>46154.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46150.5</v>
+        <v>46154.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46150.51041666666</v>
+        <v>46154.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46150.52083333334</v>
+        <v>46154.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46150.53125</v>
+        <v>46154.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46150.54166666666</v>
+        <v>46154.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46150.55208333334</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46150.5625</v>
+        <v>46154.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46150.57291666666</v>
+        <v>46154.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46150.58333333334</v>
+        <v>46154.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46150.59375</v>
+        <v>46154.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46150.60416666666</v>
+        <v>46154.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46150.61458333334</v>
+        <v>46154.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46150.625</v>
+        <v>46154.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46150.63541666666</v>
+        <v>46154.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46150.64583333334</v>
+        <v>46154.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46150.65625</v>
+        <v>46154.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46150.66666666666</v>
+        <v>46154.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46150.67708333334</v>
+        <v>46154.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46150.6875</v>
+        <v>46154.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46150.69791666666</v>
+        <v>46154.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46150.70833333334</v>
+        <v>46154.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46150.71875</v>
+        <v>46154.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46150.72916666666</v>
+        <v>46154.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46150.73958333334</v>
+        <v>46154.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46150.75</v>
+        <v>46154.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46150.76041666666</v>
+        <v>46154.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46150.77083333334</v>
+        <v>46154.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46150.78125</v>
+        <v>46154.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46150.79166666666</v>
+        <v>46154.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46150.80208333334</v>
+        <v>46154.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46150.8125</v>
+        <v>46154.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46150.82291666666</v>
+        <v>46154.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46150.83333333334</v>
+        <v>46154.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46150.84375</v>
+        <v>46154.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46150.85416666666</v>
+        <v>46154.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46150.86458333334</v>
+        <v>46154.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46150.875</v>
+        <v>46154.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46150.88541666666</v>
+        <v>46154.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46150.89583333334</v>
+        <v>46154.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46150.90625</v>
+        <v>46154.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46150.91666666666</v>
+        <v>46154.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46150.92708333334</v>
+        <v>46154.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46150.9375</v>
+        <v>46154.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46150.94791666666</v>
+        <v>46154.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46150.95833333334</v>
+        <v>46154.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46150.96875</v>
+        <v>46154.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46150.97916666666</v>
+        <v>46154.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46150.98958333334</v>
+        <v>46154.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.05.20261</t>
-  </si>
-  <si>
-    <t>11.05.20262</t>
-  </si>
-  <si>
-    <t>11.05.20263</t>
-  </si>
-  <si>
-    <t>11.05.20264</t>
-  </si>
-  <si>
-    <t>11.05.20265</t>
-  </si>
-  <si>
-    <t>11.05.20266</t>
-  </si>
-  <si>
-    <t>11.05.20267</t>
-  </si>
-  <si>
-    <t>11.05.20268</t>
-  </si>
-  <si>
-    <t>11.05.20269</t>
-  </si>
-  <si>
-    <t>11.05.202610</t>
-  </si>
-  <si>
-    <t>11.05.202611</t>
-  </si>
-  <si>
-    <t>11.05.202612</t>
-  </si>
-  <si>
-    <t>11.05.202613</t>
-  </si>
-  <si>
-    <t>11.05.202614</t>
-  </si>
-  <si>
-    <t>11.05.202615</t>
-  </si>
-  <si>
-    <t>11.05.202616</t>
-  </si>
-  <si>
-    <t>11.05.202617</t>
-  </si>
-  <si>
-    <t>11.05.202618</t>
-  </si>
-  <si>
-    <t>11.05.202619</t>
-  </si>
-  <si>
-    <t>11.05.202620</t>
-  </si>
-  <si>
-    <t>11.05.202621</t>
-  </si>
-  <si>
-    <t>11.05.202622</t>
-  </si>
-  <si>
-    <t>11.05.202623</t>
-  </si>
-  <si>
-    <t>11.05.202624</t>
-  </si>
-  <si>
-    <t>11.05.202625</t>
-  </si>
-  <si>
-    <t>11.05.202626</t>
-  </si>
-  <si>
-    <t>11.05.202627</t>
-  </si>
-  <si>
-    <t>11.05.202628</t>
-  </si>
-  <si>
-    <t>11.05.202629</t>
-  </si>
-  <si>
-    <t>11.05.202630</t>
-  </si>
-  <si>
-    <t>11.05.202631</t>
-  </si>
-  <si>
-    <t>11.05.202632</t>
-  </si>
-  <si>
-    <t>11.05.202633</t>
-  </si>
-  <si>
-    <t>11.05.202634</t>
-  </si>
-  <si>
-    <t>11.05.202635</t>
-  </si>
-  <si>
-    <t>11.05.202636</t>
-  </si>
-  <si>
-    <t>11.05.202637</t>
-  </si>
-  <si>
-    <t>11.05.202638</t>
-  </si>
-  <si>
-    <t>11.05.202639</t>
-  </si>
-  <si>
-    <t>11.05.202640</t>
-  </si>
-  <si>
-    <t>11.05.202641</t>
-  </si>
-  <si>
-    <t>11.05.202642</t>
-  </si>
-  <si>
-    <t>11.05.202643</t>
-  </si>
-  <si>
-    <t>11.05.202644</t>
-  </si>
-  <si>
-    <t>11.05.202645</t>
-  </si>
-  <si>
-    <t>11.05.202646</t>
-  </si>
-  <si>
-    <t>11.05.202647</t>
-  </si>
-  <si>
-    <t>11.05.202648</t>
-  </si>
-  <si>
-    <t>11.05.202649</t>
-  </si>
-  <si>
-    <t>11.05.202650</t>
-  </si>
-  <si>
-    <t>11.05.202651</t>
-  </si>
-  <si>
-    <t>11.05.202652</t>
-  </si>
-  <si>
-    <t>11.05.202653</t>
-  </si>
-  <si>
-    <t>11.05.202654</t>
-  </si>
-  <si>
-    <t>11.05.202655</t>
-  </si>
-  <si>
-    <t>11.05.202656</t>
-  </si>
-  <si>
-    <t>11.05.202657</t>
-  </si>
-  <si>
-    <t>11.05.202658</t>
-  </si>
-  <si>
-    <t>11.05.202659</t>
-  </si>
-  <si>
-    <t>11.05.202660</t>
-  </si>
-  <si>
-    <t>11.05.202661</t>
-  </si>
-  <si>
-    <t>11.05.202662</t>
-  </si>
-  <si>
-    <t>11.05.202663</t>
-  </si>
-  <si>
-    <t>11.05.202664</t>
-  </si>
-  <si>
-    <t>11.05.202665</t>
-  </si>
-  <si>
-    <t>11.05.202666</t>
-  </si>
-  <si>
-    <t>11.05.202667</t>
-  </si>
-  <si>
-    <t>11.05.202668</t>
-  </si>
-  <si>
-    <t>11.05.202669</t>
-  </si>
-  <si>
-    <t>11.05.202670</t>
-  </si>
-  <si>
-    <t>11.05.202671</t>
-  </si>
-  <si>
-    <t>11.05.202672</t>
-  </si>
-  <si>
-    <t>11.05.202673</t>
-  </si>
-  <si>
-    <t>11.05.202674</t>
-  </si>
-  <si>
-    <t>11.05.202675</t>
-  </si>
-  <si>
-    <t>11.05.202676</t>
-  </si>
-  <si>
-    <t>11.05.202677</t>
-  </si>
-  <si>
-    <t>11.05.202678</t>
-  </si>
-  <si>
-    <t>11.05.202679</t>
-  </si>
-  <si>
-    <t>11.05.202680</t>
-  </si>
-  <si>
-    <t>11.05.202681</t>
-  </si>
-  <si>
-    <t>11.05.202682</t>
-  </si>
-  <si>
-    <t>11.05.202683</t>
-  </si>
-  <si>
-    <t>11.05.202684</t>
-  </si>
-  <si>
-    <t>11.05.202685</t>
-  </si>
-  <si>
-    <t>11.05.202686</t>
-  </si>
-  <si>
-    <t>11.05.202687</t>
-  </si>
-  <si>
-    <t>11.05.202688</t>
-  </si>
-  <si>
-    <t>11.05.202689</t>
-  </si>
-  <si>
-    <t>11.05.202690</t>
-  </si>
-  <si>
-    <t>11.05.202691</t>
-  </si>
-  <si>
-    <t>11.05.202692</t>
-  </si>
-  <si>
-    <t>11.05.202693</t>
-  </si>
-  <si>
-    <t>11.05.202694</t>
-  </si>
-  <si>
-    <t>11.05.202695</t>
-  </si>
-  <si>
-    <t>11.05.202696</t>
-  </si>
-  <si>
-    <t>12.05.20261</t>
-  </si>
-  <si>
-    <t>12.05.20262</t>
-  </si>
-  <si>
-    <t>12.05.20263</t>
-  </si>
-  <si>
-    <t>12.05.20264</t>
-  </si>
-  <si>
-    <t>12.05.20265</t>
-  </si>
-  <si>
-    <t>12.05.20266</t>
-  </si>
-  <si>
-    <t>12.05.20267</t>
-  </si>
-  <si>
-    <t>12.05.20268</t>
-  </si>
-  <si>
-    <t>12.05.20269</t>
-  </si>
-  <si>
-    <t>12.05.202610</t>
-  </si>
-  <si>
-    <t>12.05.202611</t>
-  </si>
-  <si>
-    <t>12.05.202612</t>
-  </si>
-  <si>
-    <t>12.05.202613</t>
-  </si>
-  <si>
-    <t>12.05.202614</t>
-  </si>
-  <si>
-    <t>12.05.202615</t>
-  </si>
-  <si>
-    <t>12.05.202616</t>
-  </si>
-  <si>
-    <t>12.05.202617</t>
-  </si>
-  <si>
-    <t>12.05.202618</t>
-  </si>
-  <si>
-    <t>12.05.202619</t>
-  </si>
-  <si>
-    <t>12.05.202620</t>
-  </si>
-  <si>
-    <t>12.05.202621</t>
-  </si>
-  <si>
-    <t>12.05.202622</t>
-  </si>
-  <si>
-    <t>12.05.202623</t>
-  </si>
-  <si>
-    <t>12.05.202624</t>
-  </si>
-  <si>
-    <t>12.05.202625</t>
-  </si>
-  <si>
-    <t>12.05.202626</t>
-  </si>
-  <si>
-    <t>12.05.202627</t>
-  </si>
-  <si>
-    <t>12.05.202628</t>
-  </si>
-  <si>
-    <t>12.05.202629</t>
-  </si>
-  <si>
-    <t>12.05.202630</t>
-  </si>
-  <si>
-    <t>12.05.202631</t>
-  </si>
-  <si>
-    <t>12.05.202632</t>
-  </si>
-  <si>
-    <t>12.05.202633</t>
-  </si>
-  <si>
-    <t>12.05.202634</t>
-  </si>
-  <si>
-    <t>12.05.202635</t>
-  </si>
-  <si>
-    <t>12.05.202636</t>
-  </si>
-  <si>
-    <t>12.05.202637</t>
-  </si>
-  <si>
-    <t>12.05.202638</t>
-  </si>
-  <si>
-    <t>12.05.202639</t>
-  </si>
-  <si>
-    <t>12.05.202640</t>
-  </si>
-  <si>
-    <t>12.05.202641</t>
-  </si>
-  <si>
-    <t>12.05.202642</t>
-  </si>
-  <si>
-    <t>12.05.202643</t>
-  </si>
-  <si>
-    <t>12.05.202644</t>
-  </si>
-  <si>
-    <t>12.05.202645</t>
-  </si>
-  <si>
-    <t>12.05.202646</t>
-  </si>
-  <si>
-    <t>12.05.202647</t>
-  </si>
-  <si>
-    <t>12.05.202648</t>
-  </si>
-  <si>
-    <t>12.05.202649</t>
-  </si>
-  <si>
-    <t>12.05.202650</t>
-  </si>
-  <si>
-    <t>12.05.202651</t>
-  </si>
-  <si>
-    <t>12.05.202652</t>
-  </si>
-  <si>
-    <t>12.05.202653</t>
-  </si>
-  <si>
-    <t>12.05.202654</t>
-  </si>
-  <si>
-    <t>12.05.202655</t>
-  </si>
-  <si>
-    <t>12.05.202656</t>
-  </si>
-  <si>
-    <t>12.05.202657</t>
-  </si>
-  <si>
-    <t>12.05.202658</t>
-  </si>
-  <si>
-    <t>12.05.202659</t>
-  </si>
-  <si>
-    <t>12.05.202660</t>
-  </si>
-  <si>
-    <t>12.05.202661</t>
-  </si>
-  <si>
-    <t>12.05.202662</t>
-  </si>
-  <si>
-    <t>12.05.202663</t>
-  </si>
-  <si>
-    <t>12.05.202664</t>
-  </si>
-  <si>
-    <t>12.05.202665</t>
-  </si>
-  <si>
-    <t>12.05.202666</t>
-  </si>
-  <si>
-    <t>12.05.202667</t>
-  </si>
-  <si>
-    <t>12.05.202668</t>
-  </si>
-  <si>
-    <t>12.05.202669</t>
-  </si>
-  <si>
-    <t>12.05.202670</t>
-  </si>
-  <si>
-    <t>12.05.202671</t>
-  </si>
-  <si>
-    <t>12.05.202672</t>
-  </si>
-  <si>
-    <t>12.05.202673</t>
-  </si>
-  <si>
-    <t>12.05.202674</t>
-  </si>
-  <si>
-    <t>12.05.202675</t>
-  </si>
-  <si>
-    <t>12.05.202676</t>
-  </si>
-  <si>
-    <t>12.05.202677</t>
-  </si>
-  <si>
-    <t>12.05.202678</t>
-  </si>
-  <si>
-    <t>12.05.202679</t>
-  </si>
-  <si>
-    <t>12.05.202680</t>
-  </si>
-  <si>
-    <t>12.05.202681</t>
-  </si>
-  <si>
-    <t>12.05.202682</t>
-  </si>
-  <si>
-    <t>12.05.202683</t>
-  </si>
-  <si>
-    <t>12.05.202684</t>
-  </si>
-  <si>
-    <t>12.05.202685</t>
-  </si>
-  <si>
-    <t>12.05.202686</t>
-  </si>
-  <si>
-    <t>12.05.202687</t>
-  </si>
-  <si>
-    <t>12.05.202688</t>
-  </si>
-  <si>
-    <t>12.05.202689</t>
-  </si>
-  <si>
-    <t>12.05.202690</t>
-  </si>
-  <si>
-    <t>12.05.202691</t>
-  </si>
-  <si>
-    <t>12.05.202692</t>
-  </si>
-  <si>
-    <t>12.05.202693</t>
-  </si>
-  <si>
-    <t>12.05.202694</t>
-  </si>
-  <si>
-    <t>12.05.202695</t>
-  </si>
-  <si>
-    <t>12.05.202696</t>
+    <t>13.05.20261</t>
+  </si>
+  <si>
+    <t>13.05.20262</t>
+  </si>
+  <si>
+    <t>13.05.20263</t>
+  </si>
+  <si>
+    <t>13.05.20264</t>
+  </si>
+  <si>
+    <t>13.05.20265</t>
+  </si>
+  <si>
+    <t>13.05.20266</t>
+  </si>
+  <si>
+    <t>13.05.20267</t>
+  </si>
+  <si>
+    <t>13.05.20268</t>
+  </si>
+  <si>
+    <t>13.05.20269</t>
+  </si>
+  <si>
+    <t>13.05.202610</t>
+  </si>
+  <si>
+    <t>13.05.202611</t>
+  </si>
+  <si>
+    <t>13.05.202612</t>
+  </si>
+  <si>
+    <t>13.05.202613</t>
+  </si>
+  <si>
+    <t>13.05.202614</t>
+  </si>
+  <si>
+    <t>13.05.202615</t>
+  </si>
+  <si>
+    <t>13.05.202616</t>
+  </si>
+  <si>
+    <t>13.05.202617</t>
+  </si>
+  <si>
+    <t>13.05.202618</t>
+  </si>
+  <si>
+    <t>13.05.202619</t>
+  </si>
+  <si>
+    <t>13.05.202620</t>
+  </si>
+  <si>
+    <t>13.05.202621</t>
+  </si>
+  <si>
+    <t>13.05.202622</t>
+  </si>
+  <si>
+    <t>13.05.202623</t>
+  </si>
+  <si>
+    <t>13.05.202624</t>
+  </si>
+  <si>
+    <t>13.05.202625</t>
+  </si>
+  <si>
+    <t>13.05.202626</t>
+  </si>
+  <si>
+    <t>13.05.202627</t>
+  </si>
+  <si>
+    <t>13.05.202628</t>
+  </si>
+  <si>
+    <t>13.05.202629</t>
+  </si>
+  <si>
+    <t>13.05.202630</t>
+  </si>
+  <si>
+    <t>13.05.202631</t>
+  </si>
+  <si>
+    <t>13.05.202632</t>
+  </si>
+  <si>
+    <t>13.05.202633</t>
+  </si>
+  <si>
+    <t>13.05.202634</t>
+  </si>
+  <si>
+    <t>13.05.202635</t>
+  </si>
+  <si>
+    <t>13.05.202636</t>
+  </si>
+  <si>
+    <t>13.05.202637</t>
+  </si>
+  <si>
+    <t>13.05.202638</t>
+  </si>
+  <si>
+    <t>13.05.202639</t>
+  </si>
+  <si>
+    <t>13.05.202640</t>
+  </si>
+  <si>
+    <t>13.05.202641</t>
+  </si>
+  <si>
+    <t>13.05.202642</t>
+  </si>
+  <si>
+    <t>13.05.202643</t>
+  </si>
+  <si>
+    <t>13.05.202644</t>
+  </si>
+  <si>
+    <t>13.05.202645</t>
+  </si>
+  <si>
+    <t>13.05.202646</t>
+  </si>
+  <si>
+    <t>13.05.202647</t>
+  </si>
+  <si>
+    <t>13.05.202648</t>
+  </si>
+  <si>
+    <t>13.05.202649</t>
+  </si>
+  <si>
+    <t>13.05.202650</t>
+  </si>
+  <si>
+    <t>13.05.202651</t>
+  </si>
+  <si>
+    <t>13.05.202652</t>
+  </si>
+  <si>
+    <t>13.05.202653</t>
+  </si>
+  <si>
+    <t>13.05.202654</t>
+  </si>
+  <si>
+    <t>13.05.202655</t>
+  </si>
+  <si>
+    <t>13.05.202656</t>
+  </si>
+  <si>
+    <t>13.05.202657</t>
+  </si>
+  <si>
+    <t>13.05.202658</t>
+  </si>
+  <si>
+    <t>13.05.202659</t>
+  </si>
+  <si>
+    <t>13.05.202660</t>
+  </si>
+  <si>
+    <t>13.05.202661</t>
+  </si>
+  <si>
+    <t>13.05.202662</t>
+  </si>
+  <si>
+    <t>13.05.202663</t>
+  </si>
+  <si>
+    <t>13.05.202664</t>
+  </si>
+  <si>
+    <t>13.05.202665</t>
+  </si>
+  <si>
+    <t>13.05.202666</t>
+  </si>
+  <si>
+    <t>13.05.202667</t>
+  </si>
+  <si>
+    <t>13.05.202668</t>
+  </si>
+  <si>
+    <t>13.05.202669</t>
+  </si>
+  <si>
+    <t>13.05.202670</t>
+  </si>
+  <si>
+    <t>13.05.202671</t>
+  </si>
+  <si>
+    <t>13.05.202672</t>
+  </si>
+  <si>
+    <t>13.05.202673</t>
+  </si>
+  <si>
+    <t>13.05.202674</t>
+  </si>
+  <si>
+    <t>13.05.202675</t>
+  </si>
+  <si>
+    <t>13.05.202676</t>
+  </si>
+  <si>
+    <t>13.05.202677</t>
+  </si>
+  <si>
+    <t>13.05.202678</t>
+  </si>
+  <si>
+    <t>13.05.202679</t>
+  </si>
+  <si>
+    <t>13.05.202680</t>
+  </si>
+  <si>
+    <t>13.05.202681</t>
+  </si>
+  <si>
+    <t>13.05.202682</t>
+  </si>
+  <si>
+    <t>13.05.202683</t>
+  </si>
+  <si>
+    <t>13.05.202684</t>
+  </si>
+  <si>
+    <t>13.05.202685</t>
+  </si>
+  <si>
+    <t>13.05.202686</t>
+  </si>
+  <si>
+    <t>13.05.202687</t>
+  </si>
+  <si>
+    <t>13.05.202688</t>
+  </si>
+  <si>
+    <t>13.05.202689</t>
+  </si>
+  <si>
+    <t>13.05.202690</t>
+  </si>
+  <si>
+    <t>13.05.202691</t>
+  </si>
+  <si>
+    <t>13.05.202692</t>
+  </si>
+  <si>
+    <t>13.05.202693</t>
+  </si>
+  <si>
+    <t>13.05.202694</t>
+  </si>
+  <si>
+    <t>13.05.202695</t>
+  </si>
+  <si>
+    <t>13.05.202696</t>
+  </si>
+  <si>
+    <t>14.05.20261</t>
+  </si>
+  <si>
+    <t>14.05.20262</t>
+  </si>
+  <si>
+    <t>14.05.20263</t>
+  </si>
+  <si>
+    <t>14.05.20264</t>
+  </si>
+  <si>
+    <t>14.05.20265</t>
+  </si>
+  <si>
+    <t>14.05.20266</t>
+  </si>
+  <si>
+    <t>14.05.20267</t>
+  </si>
+  <si>
+    <t>14.05.20268</t>
+  </si>
+  <si>
+    <t>14.05.20269</t>
+  </si>
+  <si>
+    <t>14.05.202610</t>
+  </si>
+  <si>
+    <t>14.05.202611</t>
+  </si>
+  <si>
+    <t>14.05.202612</t>
+  </si>
+  <si>
+    <t>14.05.202613</t>
+  </si>
+  <si>
+    <t>14.05.202614</t>
+  </si>
+  <si>
+    <t>14.05.202615</t>
+  </si>
+  <si>
+    <t>14.05.202616</t>
+  </si>
+  <si>
+    <t>14.05.202617</t>
+  </si>
+  <si>
+    <t>14.05.202618</t>
+  </si>
+  <si>
+    <t>14.05.202619</t>
+  </si>
+  <si>
+    <t>14.05.202620</t>
+  </si>
+  <si>
+    <t>14.05.202621</t>
+  </si>
+  <si>
+    <t>14.05.202622</t>
+  </si>
+  <si>
+    <t>14.05.202623</t>
+  </si>
+  <si>
+    <t>14.05.202624</t>
+  </si>
+  <si>
+    <t>14.05.202625</t>
+  </si>
+  <si>
+    <t>14.05.202626</t>
+  </si>
+  <si>
+    <t>14.05.202627</t>
+  </si>
+  <si>
+    <t>14.05.202628</t>
+  </si>
+  <si>
+    <t>14.05.202629</t>
+  </si>
+  <si>
+    <t>14.05.202630</t>
+  </si>
+  <si>
+    <t>14.05.202631</t>
+  </si>
+  <si>
+    <t>14.05.202632</t>
+  </si>
+  <si>
+    <t>14.05.202633</t>
+  </si>
+  <si>
+    <t>14.05.202634</t>
+  </si>
+  <si>
+    <t>14.05.202635</t>
+  </si>
+  <si>
+    <t>14.05.202636</t>
+  </si>
+  <si>
+    <t>14.05.202637</t>
+  </si>
+  <si>
+    <t>14.05.202638</t>
+  </si>
+  <si>
+    <t>14.05.202639</t>
+  </si>
+  <si>
+    <t>14.05.202640</t>
+  </si>
+  <si>
+    <t>14.05.202641</t>
+  </si>
+  <si>
+    <t>14.05.202642</t>
+  </si>
+  <si>
+    <t>14.05.202643</t>
+  </si>
+  <si>
+    <t>14.05.202644</t>
+  </si>
+  <si>
+    <t>14.05.202645</t>
+  </si>
+  <si>
+    <t>14.05.202646</t>
+  </si>
+  <si>
+    <t>14.05.202647</t>
+  </si>
+  <si>
+    <t>14.05.202648</t>
+  </si>
+  <si>
+    <t>14.05.202649</t>
+  </si>
+  <si>
+    <t>14.05.202650</t>
+  </si>
+  <si>
+    <t>14.05.202651</t>
+  </si>
+  <si>
+    <t>14.05.202652</t>
+  </si>
+  <si>
+    <t>14.05.202653</t>
+  </si>
+  <si>
+    <t>14.05.202654</t>
+  </si>
+  <si>
+    <t>14.05.202655</t>
+  </si>
+  <si>
+    <t>14.05.202656</t>
+  </si>
+  <si>
+    <t>14.05.202657</t>
+  </si>
+  <si>
+    <t>14.05.202658</t>
+  </si>
+  <si>
+    <t>14.05.202659</t>
+  </si>
+  <si>
+    <t>14.05.202660</t>
+  </si>
+  <si>
+    <t>14.05.202661</t>
+  </si>
+  <si>
+    <t>14.05.202662</t>
+  </si>
+  <si>
+    <t>14.05.202663</t>
+  </si>
+  <si>
+    <t>14.05.202664</t>
+  </si>
+  <si>
+    <t>14.05.202665</t>
+  </si>
+  <si>
+    <t>14.05.202666</t>
+  </si>
+  <si>
+    <t>14.05.202667</t>
+  </si>
+  <si>
+    <t>14.05.202668</t>
+  </si>
+  <si>
+    <t>14.05.202669</t>
+  </si>
+  <si>
+    <t>14.05.202670</t>
+  </si>
+  <si>
+    <t>14.05.202671</t>
+  </si>
+  <si>
+    <t>14.05.202672</t>
+  </si>
+  <si>
+    <t>14.05.202673</t>
+  </si>
+  <si>
+    <t>14.05.202674</t>
+  </si>
+  <si>
+    <t>14.05.202675</t>
+  </si>
+  <si>
+    <t>14.05.202676</t>
+  </si>
+  <si>
+    <t>14.05.202677</t>
+  </si>
+  <si>
+    <t>14.05.202678</t>
+  </si>
+  <si>
+    <t>14.05.202679</t>
+  </si>
+  <si>
+    <t>14.05.202680</t>
+  </si>
+  <si>
+    <t>14.05.202681</t>
+  </si>
+  <si>
+    <t>14.05.202682</t>
+  </si>
+  <si>
+    <t>14.05.202683</t>
+  </si>
+  <si>
+    <t>14.05.202684</t>
+  </si>
+  <si>
+    <t>14.05.202685</t>
+  </si>
+  <si>
+    <t>14.05.202686</t>
+  </si>
+  <si>
+    <t>14.05.202687</t>
+  </si>
+  <si>
+    <t>14.05.202688</t>
+  </si>
+  <si>
+    <t>14.05.202689</t>
+  </si>
+  <si>
+    <t>14.05.202690</t>
+  </si>
+  <si>
+    <t>14.05.202691</t>
+  </si>
+  <si>
+    <t>14.05.202692</t>
+  </si>
+  <si>
+    <t>14.05.202693</t>
+  </si>
+  <si>
+    <t>14.05.202694</t>
+  </si>
+  <si>
+    <t>14.05.202695</t>
+  </si>
+  <si>
+    <t>14.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
-        <v>-14.168</v>
+        <v>-17.176</v>
       </c>
       <c r="C6">
-        <v>600</v>
+        <v>889.7190000000001</v>
       </c>
       <c r="D6">
-        <v>600</v>
+        <v>889.7190000000001</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
-        <v>-8.077999999999999</v>
+        <v>-56.114</v>
       </c>
       <c r="C7">
-        <v>2500.833</v>
+        <v>819.1609999999999</v>
       </c>
       <c r="D7">
-        <v>2500.833</v>
+        <v>819.1609999999999</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
-        <v>-0.38</v>
+        <v>-43.899</v>
       </c>
       <c r="C8">
-        <v>270.979</v>
+        <v>826.25</v>
       </c>
       <c r="D8">
-        <v>270.979</v>
+        <v>826.25</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
-        <v>-14.341</v>
+        <v>-47.083</v>
       </c>
       <c r="C9">
-        <v>886.681</v>
+        <v>822.92</v>
       </c>
       <c r="D9">
-        <v>886.681</v>
+        <v>822.92</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
-        <v>-17.073</v>
+        <v>-22.763</v>
       </c>
       <c r="C10">
-        <v>891.8200000000001</v>
+        <v>829.4640000000001</v>
       </c>
       <c r="D10">
-        <v>891.8200000000001</v>
+        <v>829.4640000000001</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
-        <v>-46.73</v>
+        <v>-18.366</v>
       </c>
       <c r="C11">
-        <v>936.24</v>
+        <v>893.144</v>
       </c>
       <c r="D11">
-        <v>936.24</v>
+        <v>893.144</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
-        <v>-34.524</v>
+        <v>-21.44</v>
       </c>
       <c r="C12">
-        <v>884.273</v>
+        <v>856.872</v>
       </c>
       <c r="D12">
-        <v>884.273</v>
+        <v>856.872</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>-46.921</v>
+        <v>-14.233</v>
       </c>
       <c r="C13">
-        <v>889.89</v>
+        <v>837.8</v>
       </c>
       <c r="D13">
-        <v>889.89</v>
+        <v>837.8</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>-18.139</v>
+        <v>16.876</v>
       </c>
       <c r="C14">
-        <v>897.4</v>
+        <v>39.646</v>
       </c>
       <c r="D14">
-        <v>897.4</v>
+        <v>39.646</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>-38.346</v>
+        <v>18.715</v>
       </c>
       <c r="C15">
-        <v>950.441</v>
+        <v>-49.979</v>
       </c>
       <c r="D15">
-        <v>950.441</v>
+        <v>-49.979</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>-6.504</v>
+        <v>18.563</v>
       </c>
       <c r="C16">
-        <v>899.159</v>
+        <v>151.098</v>
       </c>
       <c r="D16">
-        <v>899.159</v>
+        <v>151.098</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>5.774</v>
+        <v>40.992</v>
       </c>
       <c r="C17">
-        <v>400</v>
+        <v>-122.914</v>
       </c>
       <c r="D17">
-        <v>400</v>
+        <v>-122.914</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>9.487</v>
+        <v>44.583</v>
       </c>
       <c r="C18">
-        <v>340.947</v>
+        <v>-320.405</v>
       </c>
       <c r="D18">
-        <v>340.947</v>
+        <v>-320.405</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>-3.326</v>
+        <v>19.059</v>
       </c>
       <c r="C19">
-        <v>899.295</v>
+        <v>8.914999999999999</v>
       </c>
       <c r="D19">
-        <v>899.295</v>
+        <v>8.914999999999999</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>-2.319</v>
+        <v>-8.997</v>
       </c>
       <c r="C20">
-        <v>898.38</v>
+        <v>994.549</v>
       </c>
       <c r="D20">
-        <v>898.38</v>
+        <v>994.549</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>29.408</v>
+        <v>24.933</v>
       </c>
       <c r="C21">
-        <v>314.432</v>
+        <v>255.156</v>
       </c>
       <c r="D21">
-        <v>314.432</v>
+        <v>255.156</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>79.20699999999999</v>
+        <v>45.217</v>
       </c>
       <c r="C22">
-        <v>259.73</v>
+        <v>233.974</v>
       </c>
       <c r="D22">
-        <v>259.73</v>
+        <v>233.974</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>58.444</v>
+        <v>61.591</v>
       </c>
       <c r="C23">
-        <v>283.661</v>
+        <v>-64.59099999999999</v>
       </c>
       <c r="D23">
-        <v>283.661</v>
+        <v>-64.59099999999999</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>36.431</v>
+        <v>62.627</v>
       </c>
       <c r="C24">
-        <v>-9.872999999999999</v>
+        <v>-122.213</v>
       </c>
       <c r="D24">
-        <v>-9.872999999999999</v>
+        <v>-122.213</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>50.171</v>
+        <v>70.879</v>
       </c>
       <c r="C25">
-        <v>-60.349</v>
+        <v>31.813</v>
       </c>
       <c r="D25">
-        <v>-60.349</v>
+        <v>31.813</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>77.51300000000001</v>
+        <v>55.22</v>
       </c>
       <c r="C26">
-        <v>-821.896</v>
+        <v>-313.382</v>
       </c>
       <c r="D26">
-        <v>-821.896</v>
+        <v>-313.382</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>105.659</v>
+        <v>46.738</v>
       </c>
       <c r="C27">
-        <v>-1279.248</v>
+        <v>4.982</v>
       </c>
       <c r="D27">
-        <v>-1279.248</v>
+        <v>4.982</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>84.858</v>
+        <v>33.457</v>
       </c>
       <c r="C28">
-        <v>-736.158</v>
+        <v>2.023</v>
       </c>
       <c r="D28">
-        <v>-736.158</v>
+        <v>2.023</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>127.552</v>
+        <v>21.317</v>
       </c>
       <c r="C29">
-        <v>19.42</v>
+        <v>1.1</v>
       </c>
       <c r="D29">
-        <v>19.42</v>
+        <v>1.1</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>112.201</v>
+        <v>12.567</v>
       </c>
       <c r="C30">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>86.818</v>
+        <v>23.454</v>
       </c>
       <c r="C31">
-        <v>-6.984</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>-6.984</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>120.677</v>
+        <v>39.635</v>
       </c>
       <c r="C32">
-        <v>18.573</v>
+        <v>1.413</v>
       </c>
       <c r="D32">
-        <v>18.573</v>
+        <v>1.413</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>79.68300000000001</v>
+        <v>40.533</v>
       </c>
       <c r="C33">
-        <v>-10.835</v>
+        <v>379.219</v>
       </c>
       <c r="D33">
-        <v>-10.835</v>
+        <v>379.219</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>87.498</v>
+        <v>82.13800000000001</v>
       </c>
       <c r="C34">
-        <v>-61.359</v>
+        <v>378.588</v>
       </c>
       <c r="D34">
-        <v>-61.359</v>
+        <v>378.588</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>88.902</v>
+        <v>71.736</v>
       </c>
       <c r="C35">
-        <v>-296.583</v>
+        <v>325.793</v>
       </c>
       <c r="D35">
-        <v>-296.583</v>
+        <v>325.793</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>110.341</v>
+        <v>53.16</v>
       </c>
       <c r="C36">
-        <v>-772.063</v>
+        <v>25.327</v>
       </c>
       <c r="D36">
-        <v>-772.063</v>
+        <v>25.327</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>110.856</v>
+        <v>46.718</v>
       </c>
       <c r="C37">
-        <v>-425.411</v>
+        <v>-142.248</v>
       </c>
       <c r="D37">
-        <v>-425.411</v>
+        <v>-142.248</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>92.789</v>
+        <v>70.529</v>
       </c>
       <c r="C38">
-        <v>1.967</v>
+        <v>-92.04300000000001</v>
       </c>
       <c r="D38">
-        <v>1.967</v>
+        <v>-92.04300000000001</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>145.429</v>
+        <v>45.639</v>
       </c>
       <c r="C39">
-        <v>2.294</v>
+        <v>-51.852</v>
       </c>
       <c r="D39">
-        <v>2.294</v>
+        <v>-51.852</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>140.161</v>
+        <v>28.711</v>
       </c>
       <c r="C40">
-        <v>-9.550000000000001</v>
+        <v>101.717</v>
       </c>
       <c r="D40">
-        <v>-9.550000000000001</v>
+        <v>101.717</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>66.036</v>
+        <v>-0.393</v>
       </c>
       <c r="C41">
-        <v>-1.19</v>
+        <v>777.741</v>
       </c>
       <c r="D41">
-        <v>-1.19</v>
+        <v>777.741</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>5.39</v>
+        <v>-39.91</v>
       </c>
       <c r="C42">
-        <v>1.382</v>
+        <v>675.03</v>
       </c>
       <c r="D42">
-        <v>1.382</v>
+        <v>675.03</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>43.794</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>1.092</v>
+        <v>696.2859999999999</v>
       </c>
       <c r="D43">
-        <v>1.092</v>
+        <v>696.2859999999999</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>-19.363</v>
+        <v>-66.98099999999999</v>
       </c>
       <c r="C44">
-        <v>700</v>
+        <v>864.763</v>
       </c>
       <c r="D44">
-        <v>700</v>
+        <v>864.763</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>26.403</v>
+        <v>-22.383</v>
       </c>
       <c r="C45">
-        <v>-49.97</v>
+        <v>792.532</v>
       </c>
       <c r="D45">
-        <v>-49.97</v>
+        <v>792.532</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>14.558</v>
+        <v>-79.35299999999999</v>
       </c>
       <c r="C46">
-        <v>-12.656</v>
+        <v>699.295</v>
       </c>
       <c r="D46">
-        <v>-12.656</v>
+        <v>699.295</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>41.945</v>
+        <v>2.562</v>
       </c>
       <c r="C47">
-        <v>-2.018</v>
+        <v>66.84</v>
       </c>
       <c r="D47">
-        <v>-2.018</v>
+        <v>66.84</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>55.558</v>
+        <v>-9.384</v>
       </c>
       <c r="C48">
-        <v>39.791</v>
+        <v>699</v>
       </c>
       <c r="D48">
-        <v>39.791</v>
+        <v>699</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>6.997</v>
+        <v>28.62</v>
       </c>
       <c r="C49">
-        <v>0.6</v>
+        <v>-2.307</v>
       </c>
       <c r="D49">
-        <v>0.6</v>
+        <v>-2.307</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>-39.435</v>
+        <v>64.681</v>
       </c>
       <c r="C50">
-        <v>771.495</v>
+        <v>-257.642</v>
       </c>
       <c r="D50">
-        <v>771.495</v>
+        <v>-257.642</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>-16.057</v>
+        <v>57.669</v>
       </c>
       <c r="C51">
-        <v>841.759</v>
+        <v>-184.632</v>
       </c>
       <c r="D51">
-        <v>841.759</v>
+        <v>-184.632</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>-4.555</v>
+        <v>56.157</v>
       </c>
       <c r="C52">
-        <v>700</v>
+        <v>-3227.642</v>
       </c>
       <c r="D52">
-        <v>700</v>
+        <v>-3227.642</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>42.623</v>
+        <v>3.392</v>
       </c>
       <c r="C53">
-        <v>-288.757</v>
+        <v>203.873</v>
       </c>
       <c r="D53">
-        <v>-288.757</v>
+        <v>203.873</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>-29.489</v>
+        <v>57.585</v>
       </c>
       <c r="C54">
-        <v>716.197</v>
+        <v>120.341</v>
       </c>
       <c r="D54">
-        <v>716.197</v>
+        <v>120.341</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>-50.073</v>
+        <v>90.524</v>
       </c>
       <c r="C55">
-        <v>816.669</v>
+        <v>-487.61</v>
       </c>
       <c r="D55">
-        <v>816.669</v>
+        <v>-487.61</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>18.373</v>
+        <v>62.901</v>
       </c>
       <c r="C56">
-        <v>-89.765</v>
+        <v>-4656.297</v>
       </c>
       <c r="D56">
-        <v>-89.765</v>
+        <v>-4656.297</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>57.757</v>
+        <v>31.345</v>
       </c>
       <c r="C57">
-        <v>-893.168</v>
+        <v>-176.515</v>
       </c>
       <c r="D57">
-        <v>-893.168</v>
+        <v>-176.515</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>69.015</v>
+        <v>27.681</v>
       </c>
       <c r="C58">
-        <v>-3442.658</v>
+        <v>-67.244</v>
       </c>
       <c r="D58">
-        <v>-3442.658</v>
+        <v>-67.244</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>80.52</v>
+        <v>4.206</v>
       </c>
       <c r="C59">
-        <v>-3219.49</v>
+        <v>283.474</v>
       </c>
       <c r="D59">
-        <v>-3219.49</v>
+        <v>283.474</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>41.556</v>
+        <v>-19.253</v>
       </c>
       <c r="C60">
-        <v>-71.377</v>
+        <v>699</v>
       </c>
       <c r="D60">
-        <v>-71.377</v>
+        <v>699</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>41.449</v>
+        <v>8.414</v>
       </c>
       <c r="C61">
-        <v>-1.125</v>
+        <v>82.964</v>
       </c>
       <c r="D61">
-        <v>-1.125</v>
+        <v>82.964</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>57.01</v>
+        <v>27.339</v>
       </c>
       <c r="C62">
-        <v>-20.927</v>
+        <v>0.763</v>
       </c>
       <c r="D62">
-        <v>-20.927</v>
+        <v>0.763</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>92.24299999999999</v>
+        <v>41.069</v>
       </c>
       <c r="C63">
-        <v>-7.109</v>
+        <v>-60.395</v>
       </c>
       <c r="D63">
-        <v>-7.109</v>
+        <v>-60.395</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>125.296</v>
+        <v>9.205</v>
       </c>
       <c r="C64">
-        <v>-97.05200000000001</v>
+        <v>-33.154</v>
       </c>
       <c r="D64">
-        <v>-97.05200000000001</v>
+        <v>-33.154</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>78.84099999999999</v>
+        <v>-19.422</v>
       </c>
       <c r="C65">
-        <v>-513.053</v>
+        <v>699</v>
       </c>
       <c r="D65">
-        <v>-513.053</v>
+        <v>699</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>61.731</v>
+        <v>-47.229</v>
       </c>
       <c r="C66">
-        <v>-3.514</v>
+        <v>894.862</v>
       </c>
       <c r="D66">
-        <v>-3.514</v>
+        <v>894.862</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>93.375</v>
+        <v>2.482</v>
       </c>
       <c r="C67">
-        <v>-25.985</v>
+        <v>258.488</v>
       </c>
       <c r="D67">
-        <v>-25.985</v>
+        <v>258.488</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>81.027</v>
+        <v>-10.693</v>
       </c>
       <c r="C68">
-        <v>1.65</v>
+        <v>912.102</v>
       </c>
       <c r="D68">
-        <v>1.65</v>
+        <v>912.102</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>27.03</v>
+        <v>-14.081</v>
       </c>
       <c r="C69">
-        <v>4.038</v>
+        <v>859.775</v>
       </c>
       <c r="D69">
-        <v>4.038</v>
+        <v>859.775</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>-21.747</v>
+        <v>-41.477</v>
       </c>
       <c r="C70">
-        <v>804.516</v>
+        <v>1257.189</v>
       </c>
       <c r="D70">
-        <v>804.516</v>
+        <v>1257.189</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>-29.609</v>
+        <v>-1.25</v>
       </c>
       <c r="C71">
-        <v>1909.084</v>
+        <v>981.794</v>
       </c>
       <c r="D71">
-        <v>1909.084</v>
+        <v>981.794</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>-36.645</v>
+        <v>6.84</v>
       </c>
       <c r="C72">
-        <v>1104.124</v>
+        <v>247.22</v>
       </c>
       <c r="D72">
-        <v>1104.124</v>
+        <v>247.22</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>-81.491</v>
+        <v>16.741</v>
       </c>
       <c r="C73">
-        <v>1157.284</v>
+        <v>401</v>
       </c>
       <c r="D73">
-        <v>1157.284</v>
+        <v>401</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>-3.795</v>
+        <v>11.272</v>
       </c>
       <c r="C74">
-        <v>1128.499</v>
+        <v>-104.99</v>
       </c>
       <c r="D74">
-        <v>1128.499</v>
+        <v>-104.99</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>-74.571</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="C75">
-        <v>1038.935</v>
+        <v>401</v>
       </c>
       <c r="D75">
-        <v>1038.935</v>
+        <v>401</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>-38.374</v>
+        <v>22.683</v>
       </c>
       <c r="C76">
-        <v>1146.026</v>
+        <v>256.153</v>
       </c>
       <c r="D76">
-        <v>1146.026</v>
+        <v>256.153</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>0.037</v>
+        <v>61.587</v>
       </c>
       <c r="C77">
-        <v>186.623</v>
+        <v>401</v>
       </c>
       <c r="D77">
-        <v>186.623</v>
+        <v>401</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>46.075</v>
+        <v>100.677</v>
       </c>
       <c r="C78">
-        <v>222.342</v>
+        <v>-1214.071</v>
       </c>
       <c r="D78">
-        <v>222.342</v>
+        <v>-1214.071</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>59.373</v>
+        <v>20.323</v>
       </c>
       <c r="C79">
-        <v>286.824</v>
+        <v>1.193</v>
       </c>
       <c r="D79">
-        <v>286.824</v>
+        <v>1.193</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>58.935</v>
+        <v>52.431</v>
       </c>
       <c r="C80">
-        <v>275.17</v>
+        <v>16.105</v>
       </c>
       <c r="D80">
-        <v>275.17</v>
+        <v>16.105</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>61.706</v>
+        <v>41.125</v>
       </c>
       <c r="C81">
-        <v>17.654</v>
+        <v>1.629</v>
       </c>
       <c r="D81">
-        <v>17.654</v>
+        <v>1.629</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>12.185</v>
+        <v>114.506</v>
       </c>
       <c r="C82">
-        <v>64.041</v>
+        <v>401</v>
       </c>
       <c r="D82">
-        <v>64.041</v>
+        <v>401</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>18.576</v>
+        <v>67.095</v>
       </c>
       <c r="C83">
-        <v>217.631</v>
+        <v>16.646</v>
       </c>
       <c r="D83">
-        <v>217.631</v>
+        <v>16.646</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>20.495</v>
+        <v>54.957</v>
       </c>
       <c r="C84">
-        <v>303.149</v>
+        <v>0.703</v>
       </c>
       <c r="D84">
-        <v>303.149</v>
+        <v>0.703</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>20.291</v>
+        <v>63.854</v>
       </c>
       <c r="C85">
-        <v>258.511</v>
+        <v>2.576</v>
       </c>
       <c r="D85">
-        <v>258.511</v>
+        <v>2.576</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>7.847</v>
+        <v>43.056</v>
       </c>
       <c r="C86">
-        <v>208.907</v>
+        <v>0.6</v>
       </c>
       <c r="D86">
-        <v>208.907</v>
+        <v>0.6</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
-        <v>10.225</v>
+        <v>24.295</v>
       </c>
       <c r="C87">
-        <v>255.679</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>255.679</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>58.774</v>
+        <v>29.89</v>
       </c>
       <c r="C88">
-        <v>210.098</v>
+        <v>7.216</v>
       </c>
       <c r="D88">
-        <v>210.098</v>
+        <v>7.216</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>68.07899999999999</v>
+        <v>-6.521</v>
       </c>
       <c r="C89">
-        <v>-178.056</v>
+        <v>2558.127</v>
       </c>
       <c r="D89">
-        <v>-178.056</v>
+        <v>2558.127</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>76.911</v>
+        <v>-3.519</v>
       </c>
       <c r="C90">
-        <v>-59.874</v>
+        <v>3855.765</v>
       </c>
       <c r="D90">
-        <v>-59.874</v>
+        <v>3855.765</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>27.274</v>
+        <v>-5.39</v>
       </c>
       <c r="C91">
-        <v>115.015</v>
+        <v>983.424</v>
       </c>
       <c r="D91">
-        <v>115.015</v>
+        <v>983.424</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
-        <v>13.165</v>
+        <v>0.031</v>
       </c>
       <c r="C92">
-        <v>111.03</v>
+        <v>256.355</v>
       </c>
       <c r="D92">
-        <v>111.03</v>
+        <v>256.355</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
-        <v>5.592</v>
+        <v>34.149</v>
       </c>
       <c r="C93">
-        <v>209.729</v>
+        <v>-63.495</v>
       </c>
       <c r="D93">
-        <v>209.729</v>
+        <v>-63.495</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
-        <v>48.15</v>
+        <v>68.223</v>
       </c>
       <c r="C94">
-        <v>228.831</v>
+        <v>-107.146</v>
       </c>
       <c r="D94">
-        <v>228.831</v>
+        <v>-107.146</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
-        <v>63.33</v>
+        <v>66.286</v>
       </c>
       <c r="C95">
-        <v>-246.371</v>
+        <v>-334.717</v>
       </c>
       <c r="D95">
-        <v>-246.371</v>
+        <v>-334.717</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
-        <v>50.686</v>
+        <v>42.012</v>
       </c>
       <c r="C96">
-        <v>10.338</v>
+        <v>-93.73999999999999</v>
       </c>
       <c r="D96">
-        <v>10.338</v>
+        <v>-93.73999999999999</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
-        <v>39.261</v>
+        <v>38.966</v>
       </c>
       <c r="C97">
-        <v>16.994</v>
+        <v>-18.137</v>
       </c>
       <c r="D97">
-        <v>16.994</v>
+        <v>-18.137</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
-        <v>22.91</v>
+        <v>-32.376</v>
       </c>
       <c r="C98">
-        <v>7.253</v>
+        <v>1272.699</v>
       </c>
       <c r="D98">
-        <v>7.253</v>
+        <v>1272.699</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B99">
-        <v>30.921</v>
+        <v>-3.246</v>
       </c>
       <c r="C99">
-        <v>1.1</v>
+        <v>900.638</v>
       </c>
       <c r="D99">
-        <v>1.1</v>
+        <v>900.638</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B100">
-        <v>37.232</v>
+        <v>-3.045</v>
       </c>
       <c r="C100">
-        <v>1.451</v>
+        <v>899.481</v>
       </c>
       <c r="D100">
-        <v>1.451</v>
+        <v>899.481</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B101">
-        <v>3.079</v>
+        <v>30.371</v>
       </c>
       <c r="C101">
-        <v>1.1</v>
+        <v>-17.118</v>
       </c>
       <c r="D101">
-        <v>1.1</v>
+        <v>-17.118</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B102">
-        <v>49.171</v>
+        <v>-1.987</v>
       </c>
       <c r="C102">
-        <v>3.209</v>
+        <v>899.005</v>
       </c>
       <c r="D102">
-        <v>3.209</v>
+        <v>899.005</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B103">
-        <v>57.152</v>
+        <v>15.306</v>
       </c>
       <c r="C103">
-        <v>26.288</v>
+        <v>112.628</v>
       </c>
       <c r="D103">
-        <v>26.288</v>
+        <v>112.628</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B104">
-        <v>83.49299999999999</v>
+        <v>29.617</v>
       </c>
       <c r="C104">
-        <v>32.937</v>
+        <v>197.84</v>
       </c>
       <c r="D104">
-        <v>32.937</v>
+        <v>197.84</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B105">
-        <v>52.954</v>
+        <v>15.889</v>
       </c>
       <c r="C105">
-        <v>-56.494</v>
+        <v>274.211</v>
       </c>
       <c r="D105">
-        <v>-56.494</v>
+        <v>274.211</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B106">
-        <v>85.873</v>
+        <v>33.406</v>
       </c>
       <c r="C106">
-        <v>37.527</v>
+        <v>369.307</v>
       </c>
       <c r="D106">
-        <v>37.527</v>
+        <v>369.307</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B107">
-        <v>41.985</v>
+        <v>48.96</v>
       </c>
       <c r="C107">
-        <v>58.64</v>
+        <v>287.949</v>
       </c>
       <c r="D107">
-        <v>58.64</v>
+        <v>287.949</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B108">
-        <v>28.262</v>
+        <v>46.346</v>
       </c>
       <c r="C108">
-        <v>-7.602</v>
+        <v>281.283</v>
       </c>
       <c r="D108">
-        <v>-7.602</v>
+        <v>281.283</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B109">
-        <v>18.471</v>
+        <v>-4.931</v>
       </c>
       <c r="C109">
-        <v>12.646</v>
+        <v>899.242</v>
       </c>
       <c r="D109">
-        <v>12.646</v>
+        <v>899.242</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B110">
-        <v>-9.81</v>
+        <v>-9.795</v>
       </c>
       <c r="C110">
-        <v>894.082</v>
+        <v>929.485</v>
       </c>
       <c r="D110">
-        <v>894.082</v>
+        <v>929.485</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B111">
-        <v>-59.708</v>
+        <v>-5.366</v>
       </c>
       <c r="C111">
-        <v>814.499</v>
+        <v>898.581</v>
       </c>
       <c r="D111">
-        <v>814.499</v>
+        <v>898.581</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B112">
-        <v>-65.226</v>
+        <v>7.066</v>
       </c>
       <c r="C112">
-        <v>918.426</v>
+        <v>896.364</v>
       </c>
       <c r="D112">
-        <v>918.426</v>
+        <v>896.364</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B113">
-        <v>-82.996</v>
+        <v>-6.392</v>
       </c>
       <c r="C113">
-        <v>866.374</v>
+        <v>899.342</v>
       </c>
       <c r="D113">
-        <v>866.374</v>
+        <v>899.342</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B114">
-        <v>-89.926</v>
+        <v>6.221</v>
       </c>
       <c r="C114">
-        <v>1463.553</v>
+        <v>400</v>
       </c>
       <c r="D114">
-        <v>1463.553</v>
+        <v>400</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B115">
-        <v>-102.381</v>
+        <v>13.032</v>
       </c>
       <c r="C115">
-        <v>3799.622</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>3799.622</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B116">
-        <v>-83.84399999999999</v>
+        <v>-0.443</v>
       </c>
       <c r="C116">
-        <v>1074.528</v>
+        <v>899.091</v>
       </c>
       <c r="D116">
-        <v>1074.528</v>
+        <v>899.091</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B117">
-        <v>-63.075</v>
+        <v>13.018</v>
       </c>
       <c r="C117">
-        <v>1087.546</v>
+        <v>366.5</v>
       </c>
       <c r="D117">
-        <v>1087.546</v>
+        <v>366.5</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>27.553</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B119">
-        <v>-40.118</v>
+        <v>30.43</v>
       </c>
       <c r="C119">
-        <v>1187.709</v>
+        <v>362.386</v>
       </c>
       <c r="D119">
-        <v>1187.709</v>
+        <v>362.386</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B120">
-        <v>-34.442</v>
+        <v>-3.535</v>
       </c>
       <c r="C120">
-        <v>1172.691</v>
+        <v>988.774</v>
       </c>
       <c r="D120">
-        <v>1172.691</v>
+        <v>988.774</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B121">
-        <v>-40.241</v>
+        <v>10.705</v>
       </c>
       <c r="C121">
-        <v>1177.233</v>
+        <v>386.406</v>
       </c>
       <c r="D121">
-        <v>1177.233</v>
+        <v>386.406</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B122">
-        <v>-16.118</v>
+        <v>-4.423</v>
       </c>
       <c r="C122">
-        <v>1508.113</v>
+        <v>990.285</v>
       </c>
       <c r="D122">
-        <v>1508.113</v>
+        <v>990.285</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B123">
-        <v>-60.464</v>
+        <v>-0.425</v>
       </c>
       <c r="C123">
-        <v>1189.467</v>
+        <v>996.627</v>
       </c>
       <c r="D123">
-        <v>1189.467</v>
+        <v>996.627</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B124">
-        <v>8.606</v>
+        <v>-27.548</v>
       </c>
       <c r="C124">
-        <v>-77.48</v>
+        <v>885.508</v>
       </c>
       <c r="D124">
-        <v>-77.48</v>
+        <v>885.508</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B125">
-        <v>33.602</v>
+        <v>-25.157</v>
       </c>
       <c r="C125">
-        <v>-54.995</v>
+        <v>1107.244</v>
       </c>
       <c r="D125">
-        <v>-54.995</v>
+        <v>1107.244</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B126">
-        <v>82.63500000000001</v>
+        <v>-43.164</v>
       </c>
       <c r="C126">
-        <v>60.365</v>
+        <v>2069.67</v>
       </c>
       <c r="D126">
-        <v>60.365</v>
+        <v>2069.67</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B127">
-        <v>71.577</v>
+        <v>-48.477</v>
       </c>
       <c r="C127">
-        <v>-399.22</v>
+        <v>1062.76</v>
       </c>
       <c r="D127">
-        <v>-399.22</v>
+        <v>1062.76</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B128">
-        <v>104.235</v>
+        <v>-12.263</v>
       </c>
       <c r="C128">
-        <v>-232.443</v>
+        <v>899.3200000000001</v>
       </c>
       <c r="D128">
-        <v>-232.443</v>
+        <v>899.3200000000001</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B129">
-        <v>28.477</v>
+        <v>3.689</v>
       </c>
       <c r="C129">
-        <v>-6.641</v>
+        <v>38.564</v>
       </c>
       <c r="D129">
-        <v>-6.641</v>
+        <v>38.564</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B130">
-        <v>-128.632</v>
+        <v>35.212</v>
       </c>
       <c r="C130">
-        <v>917.957</v>
+        <v>-128.732</v>
       </c>
       <c r="D130">
-        <v>917.957</v>
+        <v>-128.732</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B131">
-        <v>-139.276</v>
+        <v>114.375</v>
       </c>
       <c r="C131">
-        <v>5093.388</v>
+        <v>7.245</v>
       </c>
       <c r="D131">
-        <v>5093.388</v>
+        <v>7.245</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B132">
-        <v>-128.529</v>
+        <v>156.659</v>
       </c>
       <c r="C132">
-        <v>4634.56</v>
+        <v>283.599</v>
       </c>
       <c r="D132">
-        <v>4634.56</v>
+        <v>283.599</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B133">
-        <v>-149.961</v>
+        <v>58.728</v>
       </c>
       <c r="C133">
-        <v>3297.331</v>
+        <v>-4.945</v>
       </c>
       <c r="D133">
-        <v>3297.331</v>
+        <v>-4.945</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B134">
-        <v>-233.197</v>
+        <v>100.925</v>
       </c>
       <c r="C134">
-        <v>2831.181</v>
+        <v>-126.547</v>
       </c>
       <c r="D134">
-        <v>2831.181</v>
+        <v>-126.547</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B135">
-        <v>-214.142</v>
+        <v>75.526</v>
       </c>
       <c r="C135">
-        <v>957.452</v>
+        <v>-68.491</v>
       </c>
       <c r="D135">
-        <v>957.452</v>
+        <v>-68.491</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B136">
-        <v>-98.373</v>
+        <v>83.488</v>
       </c>
       <c r="C136">
-        <v>942.62</v>
+        <v>-305.518</v>
       </c>
       <c r="D136">
-        <v>942.62</v>
+        <v>-305.518</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B137">
-        <v>-40.696</v>
+        <v>57.545</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>-40.178</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>-40.178</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B138">
-        <v>120.943</v>
+        <v>-6.273</v>
       </c>
       <c r="C138">
-        <v>-1873.474</v>
+        <v>699</v>
       </c>
       <c r="D138">
-        <v>-1873.474</v>
+        <v>699</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B139">
-        <v>62.745</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>-518.845</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>-518.845</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.05.20261</t>
-  </si>
-  <si>
-    <t>13.05.20262</t>
-  </si>
-  <si>
-    <t>13.05.20263</t>
-  </si>
-  <si>
-    <t>13.05.20264</t>
-  </si>
-  <si>
-    <t>13.05.20265</t>
-  </si>
-  <si>
-    <t>13.05.20266</t>
-  </si>
-  <si>
-    <t>13.05.20267</t>
-  </si>
-  <si>
-    <t>13.05.20268</t>
-  </si>
-  <si>
-    <t>13.05.20269</t>
-  </si>
-  <si>
-    <t>13.05.202610</t>
-  </si>
-  <si>
-    <t>13.05.202611</t>
-  </si>
-  <si>
-    <t>13.05.202612</t>
-  </si>
-  <si>
-    <t>13.05.202613</t>
-  </si>
-  <si>
-    <t>13.05.202614</t>
-  </si>
-  <si>
-    <t>13.05.202615</t>
-  </si>
-  <si>
-    <t>13.05.202616</t>
-  </si>
-  <si>
-    <t>13.05.202617</t>
-  </si>
-  <si>
-    <t>13.05.202618</t>
-  </si>
-  <si>
-    <t>13.05.202619</t>
-  </si>
-  <si>
-    <t>13.05.202620</t>
-  </si>
-  <si>
-    <t>13.05.202621</t>
-  </si>
-  <si>
-    <t>13.05.202622</t>
-  </si>
-  <si>
-    <t>13.05.202623</t>
-  </si>
-  <si>
-    <t>13.05.202624</t>
-  </si>
-  <si>
-    <t>13.05.202625</t>
-  </si>
-  <si>
-    <t>13.05.202626</t>
-  </si>
-  <si>
-    <t>13.05.202627</t>
-  </si>
-  <si>
-    <t>13.05.202628</t>
-  </si>
-  <si>
-    <t>13.05.202629</t>
-  </si>
-  <si>
-    <t>13.05.202630</t>
-  </si>
-  <si>
-    <t>13.05.202631</t>
-  </si>
-  <si>
-    <t>13.05.202632</t>
-  </si>
-  <si>
-    <t>13.05.202633</t>
-  </si>
-  <si>
-    <t>13.05.202634</t>
-  </si>
-  <si>
-    <t>13.05.202635</t>
-  </si>
-  <si>
-    <t>13.05.202636</t>
-  </si>
-  <si>
-    <t>13.05.202637</t>
-  </si>
-  <si>
-    <t>13.05.202638</t>
-  </si>
-  <si>
-    <t>13.05.202639</t>
-  </si>
-  <si>
-    <t>13.05.202640</t>
-  </si>
-  <si>
-    <t>13.05.202641</t>
-  </si>
-  <si>
-    <t>13.05.202642</t>
-  </si>
-  <si>
-    <t>13.05.202643</t>
-  </si>
-  <si>
-    <t>13.05.202644</t>
-  </si>
-  <si>
-    <t>13.05.202645</t>
-  </si>
-  <si>
-    <t>13.05.202646</t>
-  </si>
-  <si>
-    <t>13.05.202647</t>
-  </si>
-  <si>
-    <t>13.05.202648</t>
-  </si>
-  <si>
-    <t>13.05.202649</t>
-  </si>
-  <si>
-    <t>13.05.202650</t>
-  </si>
-  <si>
-    <t>13.05.202651</t>
-  </si>
-  <si>
-    <t>13.05.202652</t>
-  </si>
-  <si>
-    <t>13.05.202653</t>
-  </si>
-  <si>
-    <t>13.05.202654</t>
-  </si>
-  <si>
-    <t>13.05.202655</t>
-  </si>
-  <si>
-    <t>13.05.202656</t>
-  </si>
-  <si>
-    <t>13.05.202657</t>
-  </si>
-  <si>
-    <t>13.05.202658</t>
-  </si>
-  <si>
-    <t>13.05.202659</t>
-  </si>
-  <si>
-    <t>13.05.202660</t>
-  </si>
-  <si>
-    <t>13.05.202661</t>
-  </si>
-  <si>
-    <t>13.05.202662</t>
-  </si>
-  <si>
-    <t>13.05.202663</t>
-  </si>
-  <si>
-    <t>13.05.202664</t>
-  </si>
-  <si>
-    <t>13.05.202665</t>
-  </si>
-  <si>
-    <t>13.05.202666</t>
-  </si>
-  <si>
-    <t>13.05.202667</t>
-  </si>
-  <si>
-    <t>13.05.202668</t>
-  </si>
-  <si>
-    <t>13.05.202669</t>
-  </si>
-  <si>
-    <t>13.05.202670</t>
-  </si>
-  <si>
-    <t>13.05.202671</t>
-  </si>
-  <si>
-    <t>13.05.202672</t>
-  </si>
-  <si>
-    <t>13.05.202673</t>
-  </si>
-  <si>
-    <t>13.05.202674</t>
-  </si>
-  <si>
-    <t>13.05.202675</t>
-  </si>
-  <si>
-    <t>13.05.202676</t>
-  </si>
-  <si>
-    <t>13.05.202677</t>
-  </si>
-  <si>
-    <t>13.05.202678</t>
-  </si>
-  <si>
-    <t>13.05.202679</t>
-  </si>
-  <si>
-    <t>13.05.202680</t>
-  </si>
-  <si>
-    <t>13.05.202681</t>
-  </si>
-  <si>
-    <t>13.05.202682</t>
-  </si>
-  <si>
-    <t>13.05.202683</t>
-  </si>
-  <si>
-    <t>13.05.202684</t>
-  </si>
-  <si>
-    <t>13.05.202685</t>
-  </si>
-  <si>
-    <t>13.05.202686</t>
-  </si>
-  <si>
-    <t>13.05.202687</t>
-  </si>
-  <si>
-    <t>13.05.202688</t>
-  </si>
-  <si>
-    <t>13.05.202689</t>
-  </si>
-  <si>
-    <t>13.05.202690</t>
-  </si>
-  <si>
-    <t>13.05.202691</t>
-  </si>
-  <si>
-    <t>13.05.202692</t>
-  </si>
-  <si>
-    <t>13.05.202693</t>
-  </si>
-  <si>
-    <t>13.05.202694</t>
-  </si>
-  <si>
-    <t>13.05.202695</t>
-  </si>
-  <si>
-    <t>13.05.202696</t>
-  </si>
-  <si>
     <t>14.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>14.05.202696</t>
+  </si>
+  <si>
+    <t>15.05.20261</t>
+  </si>
+  <si>
+    <t>15.05.20262</t>
+  </si>
+  <si>
+    <t>15.05.20263</t>
+  </si>
+  <si>
+    <t>15.05.20264</t>
+  </si>
+  <si>
+    <t>15.05.20265</t>
+  </si>
+  <si>
+    <t>15.05.20266</t>
+  </si>
+  <si>
+    <t>15.05.20267</t>
+  </si>
+  <si>
+    <t>15.05.20268</t>
+  </si>
+  <si>
+    <t>15.05.20269</t>
+  </si>
+  <si>
+    <t>15.05.202610</t>
+  </si>
+  <si>
+    <t>15.05.202611</t>
+  </si>
+  <si>
+    <t>15.05.202612</t>
+  </si>
+  <si>
+    <t>15.05.202613</t>
+  </si>
+  <si>
+    <t>15.05.202614</t>
+  </si>
+  <si>
+    <t>15.05.202615</t>
+  </si>
+  <si>
+    <t>15.05.202616</t>
+  </si>
+  <si>
+    <t>15.05.202617</t>
+  </si>
+  <si>
+    <t>15.05.202618</t>
+  </si>
+  <si>
+    <t>15.05.202619</t>
+  </si>
+  <si>
+    <t>15.05.202620</t>
+  </si>
+  <si>
+    <t>15.05.202621</t>
+  </si>
+  <si>
+    <t>15.05.202622</t>
+  </si>
+  <si>
+    <t>15.05.202623</t>
+  </si>
+  <si>
+    <t>15.05.202624</t>
+  </si>
+  <si>
+    <t>15.05.202625</t>
+  </si>
+  <si>
+    <t>15.05.202626</t>
+  </si>
+  <si>
+    <t>15.05.202627</t>
+  </si>
+  <si>
+    <t>15.05.202628</t>
+  </si>
+  <si>
+    <t>15.05.202629</t>
+  </si>
+  <si>
+    <t>15.05.202630</t>
+  </si>
+  <si>
+    <t>15.05.202631</t>
+  </si>
+  <si>
+    <t>15.05.202632</t>
+  </si>
+  <si>
+    <t>15.05.202633</t>
+  </si>
+  <si>
+    <t>15.05.202634</t>
+  </si>
+  <si>
+    <t>15.05.202635</t>
+  </si>
+  <si>
+    <t>15.05.202636</t>
+  </si>
+  <si>
+    <t>15.05.202637</t>
+  </si>
+  <si>
+    <t>15.05.202638</t>
+  </si>
+  <si>
+    <t>15.05.202639</t>
+  </si>
+  <si>
+    <t>15.05.202640</t>
+  </si>
+  <si>
+    <t>15.05.202641</t>
+  </si>
+  <si>
+    <t>15.05.202642</t>
+  </si>
+  <si>
+    <t>15.05.202643</t>
+  </si>
+  <si>
+    <t>15.05.202644</t>
+  </si>
+  <si>
+    <t>15.05.202645</t>
+  </si>
+  <si>
+    <t>15.05.202646</t>
+  </si>
+  <si>
+    <t>15.05.202647</t>
+  </si>
+  <si>
+    <t>15.05.202648</t>
+  </si>
+  <si>
+    <t>15.05.202649</t>
+  </si>
+  <si>
+    <t>15.05.202650</t>
+  </si>
+  <si>
+    <t>15.05.202651</t>
+  </si>
+  <si>
+    <t>15.05.202652</t>
+  </si>
+  <si>
+    <t>15.05.202653</t>
+  </si>
+  <si>
+    <t>15.05.202654</t>
+  </si>
+  <si>
+    <t>15.05.202655</t>
+  </si>
+  <si>
+    <t>15.05.202656</t>
+  </si>
+  <si>
+    <t>15.05.202657</t>
+  </si>
+  <si>
+    <t>15.05.202658</t>
+  </si>
+  <si>
+    <t>15.05.202659</t>
+  </si>
+  <si>
+    <t>15.05.202660</t>
+  </si>
+  <si>
+    <t>15.05.202661</t>
+  </si>
+  <si>
+    <t>15.05.202662</t>
+  </si>
+  <si>
+    <t>15.05.202663</t>
+  </si>
+  <si>
+    <t>15.05.202664</t>
+  </si>
+  <si>
+    <t>15.05.202665</t>
+  </si>
+  <si>
+    <t>15.05.202666</t>
+  </si>
+  <si>
+    <t>15.05.202667</t>
+  </si>
+  <si>
+    <t>15.05.202668</t>
+  </si>
+  <si>
+    <t>15.05.202669</t>
+  </si>
+  <si>
+    <t>15.05.202670</t>
+  </si>
+  <si>
+    <t>15.05.202671</t>
+  </si>
+  <si>
+    <t>15.05.202672</t>
+  </si>
+  <si>
+    <t>15.05.202673</t>
+  </si>
+  <si>
+    <t>15.05.202674</t>
+  </si>
+  <si>
+    <t>15.05.202675</t>
+  </si>
+  <si>
+    <t>15.05.202676</t>
+  </si>
+  <si>
+    <t>15.05.202677</t>
+  </si>
+  <si>
+    <t>15.05.202678</t>
+  </si>
+  <si>
+    <t>15.05.202679</t>
+  </si>
+  <si>
+    <t>15.05.202680</t>
+  </si>
+  <si>
+    <t>15.05.202681</t>
+  </si>
+  <si>
+    <t>15.05.202682</t>
+  </si>
+  <si>
+    <t>15.05.202683</t>
+  </si>
+  <si>
+    <t>15.05.202684</t>
+  </si>
+  <si>
+    <t>15.05.202685</t>
+  </si>
+  <si>
+    <t>15.05.202686</t>
+  </si>
+  <si>
+    <t>15.05.202687</t>
+  </si>
+  <si>
+    <t>15.05.202688</t>
+  </si>
+  <si>
+    <t>15.05.202689</t>
+  </si>
+  <si>
+    <t>15.05.202690</t>
+  </si>
+  <si>
+    <t>15.05.202691</t>
+  </si>
+  <si>
+    <t>15.05.202692</t>
+  </si>
+  <si>
+    <t>15.05.202693</t>
+  </si>
+  <si>
+    <t>15.05.202694</t>
+  </si>
+  <si>
+    <t>15.05.202695</t>
+  </si>
+  <si>
+    <t>15.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46155.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46155.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46155.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46155.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B6">
-        <v>-17.176</v>
+        <v>-1.987</v>
       </c>
       <c r="C6">
-        <v>889.7190000000001</v>
+        <v>899.005</v>
       </c>
       <c r="D6">
-        <v>889.7190000000001</v>
+        <v>899.005</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46155.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B7">
-        <v>-56.114</v>
+        <v>15.306</v>
       </c>
       <c r="C7">
-        <v>819.1609999999999</v>
+        <v>112.628</v>
       </c>
       <c r="D7">
-        <v>819.1609999999999</v>
+        <v>112.628</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46155.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B8">
-        <v>-43.899</v>
+        <v>29.617</v>
       </c>
       <c r="C8">
-        <v>826.25</v>
+        <v>197.84</v>
       </c>
       <c r="D8">
-        <v>826.25</v>
+        <v>197.84</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46155.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B9">
-        <v>-47.083</v>
+        <v>15.889</v>
       </c>
       <c r="C9">
-        <v>822.92</v>
+        <v>274.211</v>
       </c>
       <c r="D9">
-        <v>822.92</v>
+        <v>274.211</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46155.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B10">
-        <v>-22.763</v>
+        <v>33.406</v>
       </c>
       <c r="C10">
-        <v>829.4640000000001</v>
+        <v>369.307</v>
       </c>
       <c r="D10">
-        <v>829.4640000000001</v>
+        <v>369.307</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46155.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B11">
-        <v>-18.366</v>
+        <v>48.96</v>
       </c>
       <c r="C11">
-        <v>893.144</v>
+        <v>287.949</v>
       </c>
       <c r="D11">
-        <v>893.144</v>
+        <v>287.949</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46155.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B12">
-        <v>-21.44</v>
+        <v>46.346</v>
       </c>
       <c r="C12">
-        <v>856.872</v>
+        <v>281.283</v>
       </c>
       <c r="D12">
-        <v>856.872</v>
+        <v>281.283</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46155.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B13">
-        <v>-14.233</v>
+        <v>-4.931</v>
       </c>
       <c r="C13">
-        <v>837.8</v>
+        <v>899.242</v>
       </c>
       <c r="D13">
-        <v>837.8</v>
+        <v>899.242</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46155.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B14">
-        <v>16.876</v>
+        <v>-9.795</v>
       </c>
       <c r="C14">
-        <v>39.646</v>
+        <v>929.485</v>
       </c>
       <c r="D14">
-        <v>39.646</v>
+        <v>929.485</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46155.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B15">
-        <v>18.715</v>
+        <v>-5.366</v>
       </c>
       <c r="C15">
-        <v>-49.979</v>
+        <v>898.581</v>
       </c>
       <c r="D15">
-        <v>-49.979</v>
+        <v>898.581</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46155.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B16">
-        <v>18.563</v>
+        <v>7.066</v>
       </c>
       <c r="C16">
-        <v>151.098</v>
+        <v>896.364</v>
       </c>
       <c r="D16">
-        <v>151.098</v>
+        <v>896.364</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46155.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B17">
-        <v>40.992</v>
+        <v>-6.392</v>
       </c>
       <c r="C17">
-        <v>-122.914</v>
+        <v>899.342</v>
       </c>
       <c r="D17">
-        <v>-122.914</v>
+        <v>899.342</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46155.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B18">
-        <v>44.583</v>
+        <v>6.221</v>
       </c>
       <c r="C18">
-        <v>-320.405</v>
+        <v>400</v>
       </c>
       <c r="D18">
-        <v>-320.405</v>
+        <v>400</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46155.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B19">
-        <v>19.059</v>
+        <v>13.032</v>
       </c>
       <c r="C19">
-        <v>8.914999999999999</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>8.914999999999999</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46155.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B20">
-        <v>-8.997</v>
+        <v>-0.443</v>
       </c>
       <c r="C20">
-        <v>994.549</v>
+        <v>899.091</v>
       </c>
       <c r="D20">
-        <v>994.549</v>
+        <v>899.091</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46155.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B21">
-        <v>24.933</v>
+        <v>13.018</v>
       </c>
       <c r="C21">
-        <v>255.156</v>
+        <v>366.5</v>
       </c>
       <c r="D21">
-        <v>255.156</v>
+        <v>366.5</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46155.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B22">
-        <v>45.217</v>
+        <v>27.553</v>
       </c>
       <c r="C22">
-        <v>233.974</v>
+        <v>400</v>
       </c>
       <c r="D22">
-        <v>233.974</v>
+        <v>400</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46155.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B23">
-        <v>61.591</v>
+        <v>30.43</v>
       </c>
       <c r="C23">
-        <v>-64.59099999999999</v>
+        <v>362.386</v>
       </c>
       <c r="D23">
-        <v>-64.59099999999999</v>
+        <v>362.386</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46155.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B24">
-        <v>62.627</v>
+        <v>-3.535</v>
       </c>
       <c r="C24">
-        <v>-122.213</v>
+        <v>988.774</v>
       </c>
       <c r="D24">
-        <v>-122.213</v>
+        <v>988.774</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46155.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B25">
-        <v>70.879</v>
+        <v>10.705</v>
       </c>
       <c r="C25">
-        <v>31.813</v>
+        <v>386.406</v>
       </c>
       <c r="D25">
-        <v>31.813</v>
+        <v>386.406</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46155.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B26">
-        <v>55.22</v>
+        <v>-4.423</v>
       </c>
       <c r="C26">
-        <v>-313.382</v>
+        <v>990.285</v>
       </c>
       <c r="D26">
-        <v>-313.382</v>
+        <v>990.285</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46155.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B27">
-        <v>46.738</v>
+        <v>-0.425</v>
       </c>
       <c r="C27">
-        <v>4.982</v>
+        <v>996.627</v>
       </c>
       <c r="D27">
-        <v>4.982</v>
+        <v>996.627</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46155.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B28">
-        <v>33.457</v>
+        <v>-27.548</v>
       </c>
       <c r="C28">
-        <v>2.023</v>
+        <v>885.508</v>
       </c>
       <c r="D28">
-        <v>2.023</v>
+        <v>885.508</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46155.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B29">
-        <v>21.317</v>
+        <v>-25.157</v>
       </c>
       <c r="C29">
-        <v>1.1</v>
+        <v>1107.244</v>
       </c>
       <c r="D29">
-        <v>1.1</v>
+        <v>1107.244</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46155.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B30">
-        <v>12.567</v>
+        <v>-43.164</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2069.67</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>2069.67</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46155.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B31">
-        <v>23.454</v>
+        <v>-48.477</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1062.76</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1062.76</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46155.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B32">
-        <v>39.635</v>
+        <v>-12.263</v>
       </c>
       <c r="C32">
-        <v>1.413</v>
+        <v>899.3200000000001</v>
       </c>
       <c r="D32">
-        <v>1.413</v>
+        <v>899.3200000000001</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46155.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B33">
-        <v>40.533</v>
+        <v>3.689</v>
       </c>
       <c r="C33">
-        <v>379.219</v>
+        <v>38.564</v>
       </c>
       <c r="D33">
-        <v>379.219</v>
+        <v>38.564</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46155.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B34">
-        <v>82.13800000000001</v>
+        <v>35.212</v>
       </c>
       <c r="C34">
-        <v>378.588</v>
+        <v>-128.732</v>
       </c>
       <c r="D34">
-        <v>378.588</v>
+        <v>-128.732</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46155.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B35">
-        <v>71.736</v>
+        <v>114.375</v>
       </c>
       <c r="C35">
-        <v>325.793</v>
+        <v>7.245</v>
       </c>
       <c r="D35">
-        <v>325.793</v>
+        <v>7.245</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46155.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B36">
-        <v>53.16</v>
+        <v>156.659</v>
       </c>
       <c r="C36">
-        <v>25.327</v>
+        <v>283.599</v>
       </c>
       <c r="D36">
-        <v>25.327</v>
+        <v>283.599</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46155.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B37">
-        <v>46.718</v>
+        <v>58.728</v>
       </c>
       <c r="C37">
-        <v>-142.248</v>
+        <v>-4.945</v>
       </c>
       <c r="D37">
-        <v>-142.248</v>
+        <v>-4.945</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46155.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B38">
-        <v>70.529</v>
+        <v>100.925</v>
       </c>
       <c r="C38">
-        <v>-92.04300000000001</v>
+        <v>-126.547</v>
       </c>
       <c r="D38">
-        <v>-92.04300000000001</v>
+        <v>-126.547</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46155.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B39">
-        <v>45.639</v>
+        <v>75.526</v>
       </c>
       <c r="C39">
-        <v>-51.852</v>
+        <v>-68.491</v>
       </c>
       <c r="D39">
-        <v>-51.852</v>
+        <v>-68.491</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46155.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B40">
-        <v>28.711</v>
+        <v>83.488</v>
       </c>
       <c r="C40">
-        <v>101.717</v>
+        <v>-305.518</v>
       </c>
       <c r="D40">
-        <v>101.717</v>
+        <v>-305.518</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46155.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B41">
-        <v>-0.393</v>
+        <v>57.545</v>
       </c>
       <c r="C41">
-        <v>777.741</v>
+        <v>-40.178</v>
       </c>
       <c r="D41">
-        <v>777.741</v>
+        <v>-40.178</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46155.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B42">
-        <v>-39.91</v>
+        <v>-6.273</v>
       </c>
       <c r="C42">
-        <v>675.03</v>
+        <v>699</v>
       </c>
       <c r="D42">
-        <v>675.03</v>
+        <v>699</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46155.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>-13.069</v>
       </c>
       <c r="C43">
-        <v>696.2859999999999</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>696.2859999999999</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46155.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B44">
-        <v>-66.98099999999999</v>
+        <v>50.861</v>
       </c>
       <c r="C44">
-        <v>864.763</v>
+        <v>-242.905</v>
       </c>
       <c r="D44">
-        <v>864.763</v>
+        <v>-242.905</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46155.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B45">
-        <v>-22.383</v>
+        <v>67.486</v>
       </c>
       <c r="C45">
-        <v>792.532</v>
+        <v>-2027.875</v>
       </c>
       <c r="D45">
-        <v>792.532</v>
+        <v>-2027.875</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46155.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B46">
-        <v>-79.35299999999999</v>
+        <v>-1.484</v>
       </c>
       <c r="C46">
-        <v>699.295</v>
+        <v>602.994</v>
       </c>
       <c r="D46">
-        <v>699.295</v>
+        <v>602.994</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46155.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B47">
-        <v>2.562</v>
+        <v>7.283</v>
       </c>
       <c r="C47">
-        <v>66.84</v>
+        <v>4.667</v>
       </c>
       <c r="D47">
-        <v>66.84</v>
+        <v>4.667</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46155.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B48">
-        <v>-9.384</v>
+        <v>27.434</v>
       </c>
       <c r="C48">
-        <v>699</v>
+        <v>10.74</v>
       </c>
       <c r="D48">
-        <v>699</v>
+        <v>10.74</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46155.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B49">
-        <v>28.62</v>
+        <v>29.576</v>
       </c>
       <c r="C49">
-        <v>-2.307</v>
+        <v>34.383</v>
       </c>
       <c r="D49">
-        <v>-2.307</v>
+        <v>34.383</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46155.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B50">
-        <v>64.681</v>
+        <v>22.123</v>
       </c>
       <c r="C50">
-        <v>-257.642</v>
+        <v>-18.098</v>
       </c>
       <c r="D50">
-        <v>-257.642</v>
+        <v>-18.098</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46155.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B51">
-        <v>57.669</v>
+        <v>113.443</v>
       </c>
       <c r="C51">
-        <v>-184.632</v>
+        <v>-11.388</v>
       </c>
       <c r="D51">
-        <v>-184.632</v>
+        <v>-11.388</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46155.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B52">
-        <v>56.157</v>
+        <v>68.149</v>
       </c>
       <c r="C52">
-        <v>-3227.642</v>
+        <v>-3.707</v>
       </c>
       <c r="D52">
-        <v>-3227.642</v>
+        <v>-3.707</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46155.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B53">
-        <v>3.392</v>
+        <v>-5.259</v>
       </c>
       <c r="C53">
-        <v>203.873</v>
+        <v>507.679</v>
       </c>
       <c r="D53">
-        <v>203.873</v>
+        <v>507.679</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46155.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B54">
-        <v>57.585</v>
+        <v>8.191000000000001</v>
       </c>
       <c r="C54">
-        <v>120.341</v>
+        <v>3.168</v>
       </c>
       <c r="D54">
-        <v>120.341</v>
+        <v>3.168</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46155.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B55">
-        <v>90.524</v>
+        <v>-24.284</v>
       </c>
       <c r="C55">
-        <v>-487.61</v>
+        <v>656.317</v>
       </c>
       <c r="D55">
-        <v>-487.61</v>
+        <v>656.317</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46155.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B56">
-        <v>62.901</v>
+        <v>-52.076</v>
       </c>
       <c r="C56">
-        <v>-4656.297</v>
+        <v>734.8630000000001</v>
       </c>
       <c r="D56">
-        <v>-4656.297</v>
+        <v>734.8630000000001</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46155.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B57">
-        <v>31.345</v>
+        <v>11.302</v>
       </c>
       <c r="C57">
-        <v>-176.515</v>
+        <v>19.983</v>
       </c>
       <c r="D57">
-        <v>-176.515</v>
+        <v>19.983</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46155.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B58">
-        <v>27.681</v>
+        <v>4.946</v>
       </c>
       <c r="C58">
-        <v>-67.244</v>
+        <v>-84.92400000000001</v>
       </c>
       <c r="D58">
-        <v>-67.244</v>
+        <v>-84.92400000000001</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46155.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B59">
-        <v>4.206</v>
+        <v>-8.6</v>
       </c>
       <c r="C59">
-        <v>283.474</v>
+        <v>450</v>
       </c>
       <c r="D59">
-        <v>283.474</v>
+        <v>450</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46155.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B60">
-        <v>-19.253</v>
+        <v>11.973</v>
       </c>
       <c r="C60">
-        <v>699</v>
+        <v>249.215</v>
       </c>
       <c r="D60">
-        <v>699</v>
+        <v>249.215</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46155.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B61">
-        <v>8.414</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="C61">
-        <v>82.964</v>
+        <v>-99.071</v>
       </c>
       <c r="D61">
-        <v>82.964</v>
+        <v>-99.071</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46155.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B62">
-        <v>27.339</v>
+        <v>106.633</v>
       </c>
       <c r="C62">
-        <v>0.763</v>
+        <v>-2067.1</v>
       </c>
       <c r="D62">
-        <v>0.763</v>
+        <v>-2067.1</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46155.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B63">
-        <v>41.069</v>
+        <v>84.46899999999999</v>
       </c>
       <c r="C63">
-        <v>-60.395</v>
+        <v>-25.186</v>
       </c>
       <c r="D63">
-        <v>-60.395</v>
+        <v>-25.186</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46155.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B64">
-        <v>9.205</v>
+        <v>113.834</v>
       </c>
       <c r="C64">
-        <v>-33.154</v>
+        <v>-36.564</v>
       </c>
       <c r="D64">
-        <v>-33.154</v>
+        <v>-36.564</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46155.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B65">
-        <v>-19.422</v>
+        <v>132.007</v>
       </c>
       <c r="C65">
-        <v>699</v>
+        <v>-73.20099999999999</v>
       </c>
       <c r="D65">
-        <v>699</v>
+        <v>-73.20099999999999</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46155.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B66">
-        <v>-47.229</v>
+        <v>240.504</v>
       </c>
       <c r="C66">
-        <v>894.862</v>
+        <v>9.112</v>
       </c>
       <c r="D66">
-        <v>894.862</v>
+        <v>9.112</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46155.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B67">
-        <v>2.482</v>
+        <v>247.152</v>
       </c>
       <c r="C67">
-        <v>258.488</v>
+        <v>4.272</v>
       </c>
       <c r="D67">
-        <v>258.488</v>
+        <v>4.272</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46155.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B68">
-        <v>-10.693</v>
+        <v>213.449</v>
       </c>
       <c r="C68">
-        <v>912.102</v>
+        <v>-5.229</v>
       </c>
       <c r="D68">
-        <v>912.102</v>
+        <v>-5.229</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46155.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B69">
-        <v>-14.081</v>
+        <v>126.318</v>
       </c>
       <c r="C69">
-        <v>859.775</v>
+        <v>-37.145</v>
       </c>
       <c r="D69">
-        <v>859.775</v>
+        <v>-37.145</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46155.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B70">
-        <v>-41.477</v>
+        <v>114.523</v>
       </c>
       <c r="C70">
-        <v>1257.189</v>
+        <v>1.938</v>
       </c>
       <c r="D70">
-        <v>1257.189</v>
+        <v>1.938</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46155.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B71">
-        <v>-1.25</v>
+        <v>75.17</v>
       </c>
       <c r="C71">
-        <v>981.794</v>
+        <v>-2.421</v>
       </c>
       <c r="D71">
-        <v>981.794</v>
+        <v>-2.421</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46155.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B72">
-        <v>6.84</v>
+        <v>27.611</v>
       </c>
       <c r="C72">
-        <v>247.22</v>
+        <v>1.1</v>
       </c>
       <c r="D72">
-        <v>247.22</v>
+        <v>1.1</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46155.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B73">
-        <v>16.741</v>
+        <v>43.679</v>
       </c>
       <c r="C73">
-        <v>401</v>
+        <v>288.678</v>
       </c>
       <c r="D73">
-        <v>401</v>
+        <v>288.678</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46155.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B74">
-        <v>11.272</v>
+        <v>92.10299999999999</v>
       </c>
       <c r="C74">
-        <v>-104.99</v>
+        <v>155.593</v>
       </c>
       <c r="D74">
-        <v>-104.99</v>
+        <v>155.593</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46155.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B75">
-        <v>0.8120000000000001</v>
+        <v>23.003</v>
       </c>
       <c r="C75">
-        <v>401</v>
+        <v>258.651</v>
       </c>
       <c r="D75">
-        <v>401</v>
+        <v>258.651</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46155.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B76">
-        <v>22.683</v>
+        <v>0.247</v>
       </c>
       <c r="C76">
-        <v>256.153</v>
+        <v>927.87</v>
       </c>
       <c r="D76">
-        <v>256.153</v>
+        <v>927.87</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46155.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B77">
-        <v>61.587</v>
+        <v>-26.926</v>
       </c>
       <c r="C77">
-        <v>401</v>
+        <v>1769.907</v>
       </c>
       <c r="D77">
-        <v>401</v>
+        <v>1769.907</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46155.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B78">
-        <v>100.677</v>
+        <v>8.795</v>
       </c>
       <c r="C78">
-        <v>-1214.071</v>
+        <v>337.467</v>
       </c>
       <c r="D78">
-        <v>-1214.071</v>
+        <v>337.467</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46155.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B79">
-        <v>20.323</v>
+        <v>-8.301</v>
       </c>
       <c r="C79">
-        <v>1.193</v>
+        <v>1340.174</v>
       </c>
       <c r="D79">
-        <v>1.193</v>
+        <v>1340.174</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46155.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B80">
-        <v>52.431</v>
+        <v>-18.745</v>
       </c>
       <c r="C80">
-        <v>16.105</v>
+        <v>1538.636</v>
       </c>
       <c r="D80">
-        <v>16.105</v>
+        <v>1538.636</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46155.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B81">
-        <v>41.125</v>
+        <v>-43.293</v>
       </c>
       <c r="C81">
-        <v>1.629</v>
+        <v>3264.774</v>
       </c>
       <c r="D81">
-        <v>1.629</v>
+        <v>3264.774</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46155.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B82">
-        <v>114.506</v>
+        <v>-32.319</v>
       </c>
       <c r="C82">
-        <v>401</v>
+        <v>3166.859</v>
       </c>
       <c r="D82">
-        <v>401</v>
+        <v>3166.859</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46155.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B83">
-        <v>67.095</v>
+        <v>-39.243</v>
       </c>
       <c r="C83">
-        <v>16.646</v>
+        <v>2930.913</v>
       </c>
       <c r="D83">
-        <v>16.646</v>
+        <v>2930.913</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46155.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B84">
-        <v>54.957</v>
+        <v>-32.416</v>
       </c>
       <c r="C84">
-        <v>0.703</v>
+        <v>3446.732</v>
       </c>
       <c r="D84">
-        <v>0.703</v>
+        <v>3446.732</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46155.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B85">
-        <v>63.854</v>
+        <v>-64.25</v>
       </c>
       <c r="C85">
-        <v>2.576</v>
+        <v>6689.756</v>
       </c>
       <c r="D85">
-        <v>2.576</v>
+        <v>6689.756</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46155.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B86">
-        <v>43.056</v>
+        <v>-83.36</v>
       </c>
       <c r="C86">
-        <v>0.6</v>
+        <v>6892.27</v>
       </c>
       <c r="D86">
-        <v>0.6</v>
+        <v>6892.27</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46155.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B87">
-        <v>24.295</v>
+        <v>-125.368</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>6999</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>6999</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46155.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B88">
-        <v>29.89</v>
+        <v>1.014</v>
       </c>
       <c r="C88">
-        <v>7.216</v>
+        <v>354.213</v>
       </c>
       <c r="D88">
-        <v>7.216</v>
+        <v>354.213</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46155.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B89">
-        <v>-6.521</v>
+        <v>-34.612</v>
       </c>
       <c r="C89">
-        <v>2558.127</v>
+        <v>1641.73</v>
       </c>
       <c r="D89">
-        <v>2558.127</v>
+        <v>1641.73</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46155.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B90">
-        <v>-3.519</v>
+        <v>-24.278</v>
       </c>
       <c r="C90">
-        <v>3855.765</v>
+        <v>1258.839</v>
       </c>
       <c r="D90">
-        <v>3855.765</v>
+        <v>1258.839</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46155.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B91">
-        <v>-5.39</v>
+        <v>12.895</v>
       </c>
       <c r="C91">
-        <v>983.424</v>
+        <v>355.914</v>
       </c>
       <c r="D91">
-        <v>983.424</v>
+        <v>355.914</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46155.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B92">
-        <v>0.031</v>
+        <v>42.192</v>
       </c>
       <c r="C92">
-        <v>256.355</v>
+        <v>400</v>
       </c>
       <c r="D92">
-        <v>256.355</v>
+        <v>400</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46155.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B93">
-        <v>34.149</v>
+        <v>27.053</v>
       </c>
       <c r="C93">
-        <v>-63.495</v>
+        <v>384.27</v>
       </c>
       <c r="D93">
-        <v>-63.495</v>
+        <v>384.27</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46155.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B94">
-        <v>68.223</v>
+        <v>24.679</v>
       </c>
       <c r="C94">
-        <v>-107.146</v>
+        <v>339.935</v>
       </c>
       <c r="D94">
-        <v>-107.146</v>
+        <v>339.935</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46155.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B95">
-        <v>66.286</v>
+        <v>21.677</v>
       </c>
       <c r="C95">
-        <v>-334.717</v>
+        <v>262.764</v>
       </c>
       <c r="D95">
-        <v>-334.717</v>
+        <v>262.764</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46155.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B96">
-        <v>42.012</v>
+        <v>47.964</v>
       </c>
       <c r="C96">
-        <v>-93.73999999999999</v>
+        <v>263.453</v>
       </c>
       <c r="D96">
-        <v>-93.73999999999999</v>
+        <v>263.453</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46155.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B97">
-        <v>38.966</v>
+        <v>78.491</v>
       </c>
       <c r="C97">
-        <v>-18.137</v>
+        <v>323.67</v>
       </c>
       <c r="D97">
-        <v>-18.137</v>
+        <v>323.67</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B98">
-        <v>-32.376</v>
+        <v>34.239</v>
       </c>
       <c r="C98">
-        <v>1272.699</v>
+        <v>397.746</v>
       </c>
       <c r="D98">
-        <v>1272.699</v>
+        <v>397.746</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46156.01041666666</v>
+        <v>46157.01041666666</v>
       </c>
       <c r="B99">
-        <v>-3.246</v>
+        <v>33.557</v>
       </c>
       <c r="C99">
-        <v>900.638</v>
+        <v>282.4</v>
       </c>
       <c r="D99">
-        <v>900.638</v>
+        <v>282.4</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46156.02083333334</v>
+        <v>46157.02083333334</v>
       </c>
       <c r="B100">
-        <v>-3.045</v>
+        <v>48.052</v>
       </c>
       <c r="C100">
-        <v>899.481</v>
+        <v>217.076</v>
       </c>
       <c r="D100">
-        <v>899.481</v>
+        <v>217.076</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46156.03125</v>
+        <v>46157.03125</v>
       </c>
       <c r="B101">
-        <v>30.371</v>
+        <v>71.84</v>
       </c>
       <c r="C101">
-        <v>-17.118</v>
+        <v>76.732</v>
       </c>
       <c r="D101">
-        <v>-17.118</v>
+        <v>76.732</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46156.04166666666</v>
+        <v>46157.04166666666</v>
       </c>
       <c r="B102">
-        <v>-1.987</v>
+        <v>39.083</v>
       </c>
       <c r="C102">
-        <v>899.005</v>
+        <v>99.79600000000001</v>
       </c>
       <c r="D102">
-        <v>899.005</v>
+        <v>99.79600000000001</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46156.05208333334</v>
+        <v>46157.05208333334</v>
       </c>
       <c r="B103">
-        <v>15.306</v>
+        <v>2.228</v>
       </c>
       <c r="C103">
-        <v>112.628</v>
+        <v>400</v>
       </c>
       <c r="D103">
-        <v>112.628</v>
+        <v>400</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46156.0625</v>
+        <v>46157.0625</v>
       </c>
       <c r="B104">
-        <v>29.617</v>
+        <v>34</v>
       </c>
       <c r="C104">
-        <v>197.84</v>
+        <v>27.634</v>
       </c>
       <c r="D104">
-        <v>197.84</v>
+        <v>27.634</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46156.07291666666</v>
+        <v>46157.07291666666</v>
       </c>
       <c r="B105">
-        <v>15.889</v>
+        <v>-7.774</v>
       </c>
       <c r="C105">
-        <v>274.211</v>
+        <v>842.429</v>
       </c>
       <c r="D105">
-        <v>274.211</v>
+        <v>842.429</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46156.08333333334</v>
+        <v>46157.08333333334</v>
       </c>
       <c r="B106">
-        <v>33.406</v>
+        <v>-13.679</v>
       </c>
       <c r="C106">
-        <v>369.307</v>
+        <v>984.551</v>
       </c>
       <c r="D106">
-        <v>369.307</v>
+        <v>984.551</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46156.09375</v>
+        <v>46157.09375</v>
       </c>
       <c r="B107">
-        <v>48.96</v>
+        <v>-30.066</v>
       </c>
       <c r="C107">
-        <v>287.949</v>
+        <v>863.676</v>
       </c>
       <c r="D107">
-        <v>287.949</v>
+        <v>863.676</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46156.10416666666</v>
+        <v>46157.10416666666</v>
       </c>
       <c r="B108">
-        <v>46.346</v>
+        <v>-10.595</v>
       </c>
       <c r="C108">
-        <v>281.283</v>
+        <v>915.296</v>
       </c>
       <c r="D108">
-        <v>281.283</v>
+        <v>915.296</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46156.11458333334</v>
+        <v>46157.11458333334</v>
       </c>
       <c r="B109">
-        <v>-4.931</v>
+        <v>-11.588</v>
       </c>
       <c r="C109">
-        <v>899.242</v>
+        <v>898.568</v>
       </c>
       <c r="D109">
-        <v>899.242</v>
+        <v>898.568</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46156.125</v>
+        <v>46157.125</v>
       </c>
       <c r="B110">
-        <v>-9.795</v>
+        <v>14.166</v>
       </c>
       <c r="C110">
-        <v>929.485</v>
+        <v>400</v>
       </c>
       <c r="D110">
-        <v>929.485</v>
+        <v>400</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46156.13541666666</v>
+        <v>46157.13541666666</v>
       </c>
       <c r="B111">
-        <v>-5.366</v>
+        <v>19.427</v>
       </c>
       <c r="C111">
-        <v>898.581</v>
+        <v>271.875</v>
       </c>
       <c r="D111">
-        <v>898.581</v>
+        <v>271.875</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46156.14583333334</v>
+        <v>46157.14583333334</v>
       </c>
       <c r="B112">
-        <v>7.066</v>
+        <v>27.33</v>
       </c>
       <c r="C112">
-        <v>896.364</v>
+        <v>302.565</v>
       </c>
       <c r="D112">
-        <v>896.364</v>
+        <v>302.565</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46156.15625</v>
+        <v>46157.15625</v>
       </c>
       <c r="B113">
-        <v>-6.392</v>
+        <v>41.238</v>
       </c>
       <c r="C113">
-        <v>899.342</v>
+        <v>362.447</v>
       </c>
       <c r="D113">
-        <v>899.342</v>
+        <v>362.447</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46156.16666666666</v>
+        <v>46157.16666666666</v>
       </c>
       <c r="B114">
-        <v>6.221</v>
+        <v>93.105</v>
       </c>
       <c r="C114">
-        <v>400</v>
+        <v>188.356</v>
       </c>
       <c r="D114">
-        <v>400</v>
+        <v>188.356</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46156.17708333334</v>
+        <v>46157.17708333334</v>
       </c>
       <c r="B115">
-        <v>13.032</v>
+        <v>52.538</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>-226.857</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>-226.857</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46156.1875</v>
+        <v>46157.1875</v>
       </c>
       <c r="B116">
-        <v>-0.443</v>
+        <v>66.773</v>
       </c>
       <c r="C116">
-        <v>899.091</v>
+        <v>-273.32</v>
       </c>
       <c r="D116">
-        <v>899.091</v>
+        <v>-273.32</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46156.19791666666</v>
+        <v>46157.19791666666</v>
       </c>
       <c r="B117">
-        <v>13.018</v>
+        <v>29.059</v>
       </c>
       <c r="C117">
-        <v>366.5</v>
+        <v>186.898</v>
       </c>
       <c r="D117">
-        <v>366.5</v>
+        <v>186.898</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46156.20833333334</v>
+        <v>46157.20833333334</v>
       </c>
       <c r="B118">
-        <v>27.553</v>
+        <v>40.594</v>
       </c>
       <c r="C118">
-        <v>400</v>
+        <v>112.955</v>
       </c>
       <c r="D118">
-        <v>400</v>
+        <v>112.955</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46156.21875</v>
+        <v>46157.21875</v>
       </c>
       <c r="B119">
-        <v>30.43</v>
+        <v>34.717</v>
       </c>
       <c r="C119">
-        <v>362.386</v>
+        <v>266.01</v>
       </c>
       <c r="D119">
-        <v>362.386</v>
+        <v>266.01</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46156.22916666666</v>
+        <v>46157.22916666666</v>
       </c>
       <c r="B120">
-        <v>-3.535</v>
+        <v>10.113</v>
       </c>
       <c r="C120">
-        <v>988.774</v>
+        <v>260.652</v>
       </c>
       <c r="D120">
-        <v>988.774</v>
+        <v>260.652</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46156.23958333334</v>
+        <v>46157.23958333334</v>
       </c>
       <c r="B121">
-        <v>10.705</v>
+        <v>17.294</v>
       </c>
       <c r="C121">
-        <v>386.406</v>
+        <v>247.694</v>
       </c>
       <c r="D121">
-        <v>386.406</v>
+        <v>247.694</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46156.25</v>
+        <v>46157.25</v>
       </c>
       <c r="B122">
-        <v>-4.423</v>
+        <v>47.779</v>
       </c>
       <c r="C122">
-        <v>990.285</v>
+        <v>63.04</v>
       </c>
       <c r="D122">
-        <v>990.285</v>
+        <v>63.04</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46156.26041666666</v>
+        <v>46157.26041666666</v>
       </c>
       <c r="B123">
-        <v>-0.425</v>
+        <v>30.477</v>
       </c>
       <c r="C123">
-        <v>996.627</v>
+        <v>132.9</v>
       </c>
       <c r="D123">
-        <v>996.627</v>
+        <v>132.9</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46156.27083333334</v>
+        <v>46157.27083333334</v>
       </c>
       <c r="B124">
-        <v>-27.548</v>
+        <v>38.38</v>
       </c>
       <c r="C124">
-        <v>885.508</v>
+        <v>-13.768</v>
       </c>
       <c r="D124">
-        <v>885.508</v>
+        <v>-13.768</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46156.28125</v>
+        <v>46157.28125</v>
       </c>
       <c r="B125">
-        <v>-25.157</v>
+        <v>39.488</v>
       </c>
       <c r="C125">
-        <v>1107.244</v>
+        <v>-87.121</v>
       </c>
       <c r="D125">
-        <v>1107.244</v>
+        <v>-87.121</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46156.29166666666</v>
+        <v>46157.29166666666</v>
       </c>
       <c r="B126">
-        <v>-43.164</v>
+        <v>24.41</v>
       </c>
       <c r="C126">
-        <v>2069.67</v>
+        <v>178.347</v>
       </c>
       <c r="D126">
-        <v>2069.67</v>
+        <v>178.347</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46156.30208333334</v>
+        <v>46157.30208333334</v>
       </c>
       <c r="B127">
-        <v>-48.477</v>
+        <v>16.511</v>
       </c>
       <c r="C127">
-        <v>1062.76</v>
+        <v>9.385999999999999</v>
       </c>
       <c r="D127">
-        <v>1062.76</v>
+        <v>9.385999999999999</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46156.3125</v>
+        <v>46157.3125</v>
       </c>
       <c r="B128">
-        <v>-12.263</v>
+        <v>16.405</v>
       </c>
       <c r="C128">
-        <v>899.3200000000001</v>
+        <v>12.374</v>
       </c>
       <c r="D128">
-        <v>899.3200000000001</v>
+        <v>12.374</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46156.32291666666</v>
+        <v>46157.32291666666</v>
       </c>
       <c r="B129">
-        <v>3.689</v>
+        <v>26.347</v>
       </c>
       <c r="C129">
-        <v>38.564</v>
+        <v>-84.68000000000001</v>
       </c>
       <c r="D129">
-        <v>38.564</v>
+        <v>-84.68000000000001</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46156.33333333334</v>
+        <v>46157.33333333334</v>
       </c>
       <c r="B130">
-        <v>35.212</v>
+        <v>9.134</v>
       </c>
       <c r="C130">
-        <v>-128.732</v>
+        <v>173.403</v>
       </c>
       <c r="D130">
-        <v>-128.732</v>
+        <v>173.403</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46156.34375</v>
+        <v>46157.34375</v>
       </c>
       <c r="B131">
-        <v>114.375</v>
+        <v>-30.423</v>
       </c>
       <c r="C131">
-        <v>7.245</v>
+        <v>852.2</v>
       </c>
       <c r="D131">
-        <v>7.245</v>
+        <v>852.2</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46156.35416666666</v>
+        <v>46157.35416666666</v>
       </c>
       <c r="B132">
-        <v>156.659</v>
+        <v>-24.26</v>
       </c>
       <c r="C132">
-        <v>283.599</v>
+        <v>848.75</v>
       </c>
       <c r="D132">
-        <v>283.599</v>
+        <v>848.75</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46156.36458333334</v>
+        <v>46157.36458333334</v>
       </c>
       <c r="B133">
-        <v>58.728</v>
+        <v>-29.252</v>
       </c>
       <c r="C133">
-        <v>-4.945</v>
+        <v>847.143</v>
       </c>
       <c r="D133">
-        <v>-4.945</v>
+        <v>847.143</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46156.375</v>
+        <v>46157.375</v>
       </c>
       <c r="B134">
-        <v>100.925</v>
+        <v>-65.646</v>
       </c>
       <c r="C134">
-        <v>-126.547</v>
+        <v>898.773</v>
       </c>
       <c r="D134">
-        <v>-126.547</v>
+        <v>898.773</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46156.38541666666</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="B135">
-        <v>75.526</v>
+        <v>-77.47199999999999</v>
       </c>
       <c r="C135">
-        <v>-68.491</v>
+        <v>865.535</v>
       </c>
       <c r="D135">
-        <v>-68.491</v>
+        <v>865.535</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46156.39583333334</v>
+        <v>46157.39583333334</v>
       </c>
       <c r="B136">
-        <v>83.488</v>
+        <v>-33.456</v>
       </c>
       <c r="C136">
-        <v>-305.518</v>
+        <v>799.205</v>
       </c>
       <c r="D136">
-        <v>-305.518</v>
+        <v>799.205</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46156.40625</v>
+        <v>46157.40625</v>
       </c>
       <c r="B137">
-        <v>57.545</v>
+        <v>-21.656</v>
       </c>
       <c r="C137">
-        <v>-40.178</v>
+        <v>28.067</v>
       </c>
       <c r="D137">
-        <v>-40.178</v>
+        <v>28.067</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46156.41666666666</v>
+        <v>46157.41666666666</v>
       </c>
       <c r="B138">
-        <v>-6.273</v>
+        <v>-55.028</v>
       </c>
       <c r="C138">
-        <v>699</v>
+        <v>499</v>
       </c>
       <c r="D138">
-        <v>699</v>
+        <v>499</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46156.42708333334</v>
+        <v>46157.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>3.338</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>-16.965</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>-16.965</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46156.4375</v>
+        <v>46157.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>37.091</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>-33.655</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>-33.655</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46156.44791666666</v>
+        <v>46157.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46156.45833333334</v>
+        <v>46157.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46156.46875</v>
+        <v>46157.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46156.47916666666</v>
+        <v>46157.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46156.48958333334</v>
+        <v>46157.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46156.5</v>
+        <v>46157.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46156.51041666666</v>
+        <v>46157.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46156.52083333334</v>
+        <v>46157.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46156.53125</v>
+        <v>46157.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46156.54166666666</v>
+        <v>46157.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46156.55208333334</v>
+        <v>46157.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46156.5625</v>
+        <v>46157.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46156.57291666666</v>
+        <v>46157.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46156.58333333334</v>
+        <v>46157.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46156.59375</v>
+        <v>46157.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46156.60416666666</v>
+        <v>46157.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46156.61458333334</v>
+        <v>46157.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46156.625</v>
+        <v>46157.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46156.63541666666</v>
+        <v>46157.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46156.64583333334</v>
+        <v>46157.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46156.65625</v>
+        <v>46157.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46156.66666666666</v>
+        <v>46157.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46156.67708333334</v>
+        <v>46157.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46156.6875</v>
+        <v>46157.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46156.69791666666</v>
+        <v>46157.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46156.70833333334</v>
+        <v>46157.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46156.71875</v>
+        <v>46157.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46156.72916666666</v>
+        <v>46157.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46156.73958333334</v>
+        <v>46157.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46156.75</v>
+        <v>46157.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46156.76041666666</v>
+        <v>46157.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46156.77083333334</v>
+        <v>46157.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46156.78125</v>
+        <v>46157.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46156.79166666666</v>
+        <v>46157.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46156.80208333334</v>
+        <v>46157.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46156.8125</v>
+        <v>46157.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46156.82291666666</v>
+        <v>46157.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46156.83333333334</v>
+        <v>46157.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46156.84375</v>
+        <v>46157.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46156.85416666666</v>
+        <v>46157.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46156.86458333334</v>
+        <v>46157.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46156.875</v>
+        <v>46157.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46156.88541666666</v>
+        <v>46157.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46156.89583333334</v>
+        <v>46157.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46156.90625</v>
+        <v>46157.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46156.91666666666</v>
+        <v>46157.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46156.92708333334</v>
+        <v>46157.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46156.9375</v>
+        <v>46157.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46156.94791666666</v>
+        <v>46157.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46156.95833333334</v>
+        <v>46157.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46156.96875</v>
+        <v>46157.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46156.97916666666</v>
+        <v>46157.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46156.98958333334</v>
+        <v>46157.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>14.05.20261</t>
-  </si>
-  <si>
-    <t>14.05.20262</t>
-  </si>
-  <si>
-    <t>14.05.20263</t>
-  </si>
-  <si>
-    <t>14.05.20264</t>
-  </si>
-  <si>
-    <t>14.05.20265</t>
-  </si>
-  <si>
-    <t>14.05.20266</t>
-  </si>
-  <si>
-    <t>14.05.20267</t>
-  </si>
-  <si>
-    <t>14.05.20268</t>
-  </si>
-  <si>
-    <t>14.05.20269</t>
-  </si>
-  <si>
-    <t>14.05.202610</t>
-  </si>
-  <si>
-    <t>14.05.202611</t>
-  </si>
-  <si>
-    <t>14.05.202612</t>
-  </si>
-  <si>
-    <t>14.05.202613</t>
-  </si>
-  <si>
-    <t>14.05.202614</t>
-  </si>
-  <si>
-    <t>14.05.202615</t>
-  </si>
-  <si>
-    <t>14.05.202616</t>
-  </si>
-  <si>
-    <t>14.05.202617</t>
-  </si>
-  <si>
-    <t>14.05.202618</t>
-  </si>
-  <si>
-    <t>14.05.202619</t>
-  </si>
-  <si>
-    <t>14.05.202620</t>
-  </si>
-  <si>
-    <t>14.05.202621</t>
-  </si>
-  <si>
-    <t>14.05.202622</t>
-  </si>
-  <si>
-    <t>14.05.202623</t>
-  </si>
-  <si>
-    <t>14.05.202624</t>
-  </si>
-  <si>
-    <t>14.05.202625</t>
-  </si>
-  <si>
-    <t>14.05.202626</t>
-  </si>
-  <si>
-    <t>14.05.202627</t>
-  </si>
-  <si>
-    <t>14.05.202628</t>
-  </si>
-  <si>
-    <t>14.05.202629</t>
-  </si>
-  <si>
-    <t>14.05.202630</t>
-  </si>
-  <si>
-    <t>14.05.202631</t>
-  </si>
-  <si>
-    <t>14.05.202632</t>
-  </si>
-  <si>
-    <t>14.05.202633</t>
-  </si>
-  <si>
-    <t>14.05.202634</t>
-  </si>
-  <si>
-    <t>14.05.202635</t>
-  </si>
-  <si>
-    <t>14.05.202636</t>
-  </si>
-  <si>
-    <t>14.05.202637</t>
-  </si>
-  <si>
-    <t>14.05.202638</t>
-  </si>
-  <si>
-    <t>14.05.202639</t>
-  </si>
-  <si>
-    <t>14.05.202640</t>
-  </si>
-  <si>
-    <t>14.05.202641</t>
-  </si>
-  <si>
-    <t>14.05.202642</t>
-  </si>
-  <si>
-    <t>14.05.202643</t>
-  </si>
-  <si>
-    <t>14.05.202644</t>
-  </si>
-  <si>
-    <t>14.05.202645</t>
-  </si>
-  <si>
-    <t>14.05.202646</t>
-  </si>
-  <si>
-    <t>14.05.202647</t>
-  </si>
-  <si>
-    <t>14.05.202648</t>
-  </si>
-  <si>
-    <t>14.05.202649</t>
-  </si>
-  <si>
-    <t>14.05.202650</t>
-  </si>
-  <si>
-    <t>14.05.202651</t>
-  </si>
-  <si>
-    <t>14.05.202652</t>
-  </si>
-  <si>
-    <t>14.05.202653</t>
-  </si>
-  <si>
-    <t>14.05.202654</t>
-  </si>
-  <si>
-    <t>14.05.202655</t>
-  </si>
-  <si>
-    <t>14.05.202656</t>
-  </si>
-  <si>
-    <t>14.05.202657</t>
-  </si>
-  <si>
-    <t>14.05.202658</t>
-  </si>
-  <si>
-    <t>14.05.202659</t>
-  </si>
-  <si>
-    <t>14.05.202660</t>
-  </si>
-  <si>
-    <t>14.05.202661</t>
-  </si>
-  <si>
-    <t>14.05.202662</t>
-  </si>
-  <si>
-    <t>14.05.202663</t>
-  </si>
-  <si>
-    <t>14.05.202664</t>
-  </si>
-  <si>
-    <t>14.05.202665</t>
-  </si>
-  <si>
-    <t>14.05.202666</t>
-  </si>
-  <si>
-    <t>14.05.202667</t>
-  </si>
-  <si>
-    <t>14.05.202668</t>
-  </si>
-  <si>
-    <t>14.05.202669</t>
-  </si>
-  <si>
-    <t>14.05.202670</t>
-  </si>
-  <si>
-    <t>14.05.202671</t>
-  </si>
-  <si>
-    <t>14.05.202672</t>
-  </si>
-  <si>
-    <t>14.05.202673</t>
-  </si>
-  <si>
-    <t>14.05.202674</t>
-  </si>
-  <si>
-    <t>14.05.202675</t>
-  </si>
-  <si>
-    <t>14.05.202676</t>
-  </si>
-  <si>
-    <t>14.05.202677</t>
-  </si>
-  <si>
-    <t>14.05.202678</t>
-  </si>
-  <si>
-    <t>14.05.202679</t>
-  </si>
-  <si>
-    <t>14.05.202680</t>
-  </si>
-  <si>
-    <t>14.05.202681</t>
-  </si>
-  <si>
-    <t>14.05.202682</t>
-  </si>
-  <si>
-    <t>14.05.202683</t>
-  </si>
-  <si>
-    <t>14.05.202684</t>
-  </si>
-  <si>
-    <t>14.05.202685</t>
-  </si>
-  <si>
-    <t>14.05.202686</t>
-  </si>
-  <si>
-    <t>14.05.202687</t>
-  </si>
-  <si>
-    <t>14.05.202688</t>
-  </si>
-  <si>
-    <t>14.05.202689</t>
-  </si>
-  <si>
-    <t>14.05.202690</t>
-  </si>
-  <si>
-    <t>14.05.202691</t>
-  </si>
-  <si>
-    <t>14.05.202692</t>
-  </si>
-  <si>
-    <t>14.05.202693</t>
-  </si>
-  <si>
-    <t>14.05.202694</t>
-  </si>
-  <si>
-    <t>14.05.202695</t>
-  </si>
-  <si>
-    <t>14.05.202696</t>
-  </si>
-  <si>
-    <t>15.05.20261</t>
-  </si>
-  <si>
-    <t>15.05.20262</t>
-  </si>
-  <si>
-    <t>15.05.20263</t>
-  </si>
-  <si>
-    <t>15.05.20264</t>
-  </si>
-  <si>
-    <t>15.05.20265</t>
-  </si>
-  <si>
-    <t>15.05.20266</t>
-  </si>
-  <si>
-    <t>15.05.20267</t>
-  </si>
-  <si>
-    <t>15.05.20268</t>
-  </si>
-  <si>
-    <t>15.05.20269</t>
-  </si>
-  <si>
-    <t>15.05.202610</t>
-  </si>
-  <si>
-    <t>15.05.202611</t>
-  </si>
-  <si>
-    <t>15.05.202612</t>
-  </si>
-  <si>
-    <t>15.05.202613</t>
-  </si>
-  <si>
-    <t>15.05.202614</t>
-  </si>
-  <si>
-    <t>15.05.202615</t>
-  </si>
-  <si>
-    <t>15.05.202616</t>
-  </si>
-  <si>
-    <t>15.05.202617</t>
-  </si>
-  <si>
-    <t>15.05.202618</t>
-  </si>
-  <si>
-    <t>15.05.202619</t>
-  </si>
-  <si>
-    <t>15.05.202620</t>
-  </si>
-  <si>
-    <t>15.05.202621</t>
-  </si>
-  <si>
-    <t>15.05.202622</t>
-  </si>
-  <si>
-    <t>15.05.202623</t>
-  </si>
-  <si>
-    <t>15.05.202624</t>
-  </si>
-  <si>
-    <t>15.05.202625</t>
-  </si>
-  <si>
-    <t>15.05.202626</t>
-  </si>
-  <si>
-    <t>15.05.202627</t>
-  </si>
-  <si>
-    <t>15.05.202628</t>
-  </si>
-  <si>
-    <t>15.05.202629</t>
-  </si>
-  <si>
-    <t>15.05.202630</t>
-  </si>
-  <si>
-    <t>15.05.202631</t>
-  </si>
-  <si>
-    <t>15.05.202632</t>
-  </si>
-  <si>
-    <t>15.05.202633</t>
-  </si>
-  <si>
-    <t>15.05.202634</t>
-  </si>
-  <si>
-    <t>15.05.202635</t>
-  </si>
-  <si>
-    <t>15.05.202636</t>
-  </si>
-  <si>
-    <t>15.05.202637</t>
-  </si>
-  <si>
-    <t>15.05.202638</t>
-  </si>
-  <si>
-    <t>15.05.202639</t>
-  </si>
-  <si>
-    <t>15.05.202640</t>
-  </si>
-  <si>
-    <t>15.05.202641</t>
-  </si>
-  <si>
-    <t>15.05.202642</t>
-  </si>
-  <si>
-    <t>15.05.202643</t>
-  </si>
-  <si>
-    <t>15.05.202644</t>
-  </si>
-  <si>
-    <t>15.05.202645</t>
-  </si>
-  <si>
-    <t>15.05.202646</t>
-  </si>
-  <si>
-    <t>15.05.202647</t>
-  </si>
-  <si>
-    <t>15.05.202648</t>
-  </si>
-  <si>
-    <t>15.05.202649</t>
-  </si>
-  <si>
-    <t>15.05.202650</t>
-  </si>
-  <si>
-    <t>15.05.202651</t>
-  </si>
-  <si>
-    <t>15.05.202652</t>
-  </si>
-  <si>
-    <t>15.05.202653</t>
-  </si>
-  <si>
-    <t>15.05.202654</t>
-  </si>
-  <si>
-    <t>15.05.202655</t>
-  </si>
-  <si>
-    <t>15.05.202656</t>
-  </si>
-  <si>
-    <t>15.05.202657</t>
-  </si>
-  <si>
-    <t>15.05.202658</t>
-  </si>
-  <si>
-    <t>15.05.202659</t>
-  </si>
-  <si>
-    <t>15.05.202660</t>
-  </si>
-  <si>
-    <t>15.05.202661</t>
-  </si>
-  <si>
-    <t>15.05.202662</t>
-  </si>
-  <si>
-    <t>15.05.202663</t>
-  </si>
-  <si>
-    <t>15.05.202664</t>
-  </si>
-  <si>
-    <t>15.05.202665</t>
-  </si>
-  <si>
-    <t>15.05.202666</t>
-  </si>
-  <si>
-    <t>15.05.202667</t>
-  </si>
-  <si>
-    <t>15.05.202668</t>
-  </si>
-  <si>
-    <t>15.05.202669</t>
-  </si>
-  <si>
-    <t>15.05.202670</t>
-  </si>
-  <si>
-    <t>15.05.202671</t>
-  </si>
-  <si>
-    <t>15.05.202672</t>
-  </si>
-  <si>
-    <t>15.05.202673</t>
-  </si>
-  <si>
-    <t>15.05.202674</t>
-  </si>
-  <si>
-    <t>15.05.202675</t>
-  </si>
-  <si>
-    <t>15.05.202676</t>
-  </si>
-  <si>
-    <t>15.05.202677</t>
-  </si>
-  <si>
-    <t>15.05.202678</t>
-  </si>
-  <si>
-    <t>15.05.202679</t>
-  </si>
-  <si>
-    <t>15.05.202680</t>
-  </si>
-  <si>
-    <t>15.05.202681</t>
-  </si>
-  <si>
-    <t>15.05.202682</t>
-  </si>
-  <si>
-    <t>15.05.202683</t>
-  </si>
-  <si>
-    <t>15.05.202684</t>
-  </si>
-  <si>
-    <t>15.05.202685</t>
-  </si>
-  <si>
-    <t>15.05.202686</t>
-  </si>
-  <si>
-    <t>15.05.202687</t>
-  </si>
-  <si>
-    <t>15.05.202688</t>
-  </si>
-  <si>
-    <t>15.05.202689</t>
-  </si>
-  <si>
-    <t>15.05.202690</t>
-  </si>
-  <si>
-    <t>15.05.202691</t>
-  </si>
-  <si>
-    <t>15.05.202692</t>
-  </si>
-  <si>
-    <t>15.05.202693</t>
-  </si>
-  <si>
-    <t>15.05.202694</t>
-  </si>
-  <si>
-    <t>15.05.202695</t>
-  </si>
-  <si>
-    <t>15.05.202696</t>
+    <t>20.05.20261</t>
+  </si>
+  <si>
+    <t>20.05.20262</t>
+  </si>
+  <si>
+    <t>20.05.20263</t>
+  </si>
+  <si>
+    <t>20.05.20264</t>
+  </si>
+  <si>
+    <t>20.05.20265</t>
+  </si>
+  <si>
+    <t>20.05.20266</t>
+  </si>
+  <si>
+    <t>20.05.20267</t>
+  </si>
+  <si>
+    <t>20.05.20268</t>
+  </si>
+  <si>
+    <t>20.05.20269</t>
+  </si>
+  <si>
+    <t>20.05.202610</t>
+  </si>
+  <si>
+    <t>20.05.202611</t>
+  </si>
+  <si>
+    <t>20.05.202612</t>
+  </si>
+  <si>
+    <t>20.05.202613</t>
+  </si>
+  <si>
+    <t>20.05.202614</t>
+  </si>
+  <si>
+    <t>20.05.202615</t>
+  </si>
+  <si>
+    <t>20.05.202616</t>
+  </si>
+  <si>
+    <t>20.05.202617</t>
+  </si>
+  <si>
+    <t>20.05.202618</t>
+  </si>
+  <si>
+    <t>20.05.202619</t>
+  </si>
+  <si>
+    <t>20.05.202620</t>
+  </si>
+  <si>
+    <t>20.05.202621</t>
+  </si>
+  <si>
+    <t>20.05.202622</t>
+  </si>
+  <si>
+    <t>20.05.202623</t>
+  </si>
+  <si>
+    <t>20.05.202624</t>
+  </si>
+  <si>
+    <t>20.05.202625</t>
+  </si>
+  <si>
+    <t>20.05.202626</t>
+  </si>
+  <si>
+    <t>20.05.202627</t>
+  </si>
+  <si>
+    <t>20.05.202628</t>
+  </si>
+  <si>
+    <t>20.05.202629</t>
+  </si>
+  <si>
+    <t>20.05.202630</t>
+  </si>
+  <si>
+    <t>20.05.202631</t>
+  </si>
+  <si>
+    <t>20.05.202632</t>
+  </si>
+  <si>
+    <t>20.05.202633</t>
+  </si>
+  <si>
+    <t>20.05.202634</t>
+  </si>
+  <si>
+    <t>20.05.202635</t>
+  </si>
+  <si>
+    <t>20.05.202636</t>
+  </si>
+  <si>
+    <t>20.05.202637</t>
+  </si>
+  <si>
+    <t>20.05.202638</t>
+  </si>
+  <si>
+    <t>20.05.202639</t>
+  </si>
+  <si>
+    <t>20.05.202640</t>
+  </si>
+  <si>
+    <t>20.05.202641</t>
+  </si>
+  <si>
+    <t>20.05.202642</t>
+  </si>
+  <si>
+    <t>20.05.202643</t>
+  </si>
+  <si>
+    <t>20.05.202644</t>
+  </si>
+  <si>
+    <t>20.05.202645</t>
+  </si>
+  <si>
+    <t>20.05.202646</t>
+  </si>
+  <si>
+    <t>20.05.202647</t>
+  </si>
+  <si>
+    <t>20.05.202648</t>
+  </si>
+  <si>
+    <t>20.05.202649</t>
+  </si>
+  <si>
+    <t>20.05.202650</t>
+  </si>
+  <si>
+    <t>20.05.202651</t>
+  </si>
+  <si>
+    <t>20.05.202652</t>
+  </si>
+  <si>
+    <t>20.05.202653</t>
+  </si>
+  <si>
+    <t>20.05.202654</t>
+  </si>
+  <si>
+    <t>20.05.202655</t>
+  </si>
+  <si>
+    <t>20.05.202656</t>
+  </si>
+  <si>
+    <t>20.05.202657</t>
+  </si>
+  <si>
+    <t>20.05.202658</t>
+  </si>
+  <si>
+    <t>20.05.202659</t>
+  </si>
+  <si>
+    <t>20.05.202660</t>
+  </si>
+  <si>
+    <t>20.05.202661</t>
+  </si>
+  <si>
+    <t>20.05.202662</t>
+  </si>
+  <si>
+    <t>20.05.202663</t>
+  </si>
+  <si>
+    <t>20.05.202664</t>
+  </si>
+  <si>
+    <t>20.05.202665</t>
+  </si>
+  <si>
+    <t>20.05.202666</t>
+  </si>
+  <si>
+    <t>20.05.202667</t>
+  </si>
+  <si>
+    <t>20.05.202668</t>
+  </si>
+  <si>
+    <t>20.05.202669</t>
+  </si>
+  <si>
+    <t>20.05.202670</t>
+  </si>
+  <si>
+    <t>20.05.202671</t>
+  </si>
+  <si>
+    <t>20.05.202672</t>
+  </si>
+  <si>
+    <t>20.05.202673</t>
+  </si>
+  <si>
+    <t>20.05.202674</t>
+  </si>
+  <si>
+    <t>20.05.202675</t>
+  </si>
+  <si>
+    <t>20.05.202676</t>
+  </si>
+  <si>
+    <t>20.05.202677</t>
+  </si>
+  <si>
+    <t>20.05.202678</t>
+  </si>
+  <si>
+    <t>20.05.202679</t>
+  </si>
+  <si>
+    <t>20.05.202680</t>
+  </si>
+  <si>
+    <t>20.05.202681</t>
+  </si>
+  <si>
+    <t>20.05.202682</t>
+  </si>
+  <si>
+    <t>20.05.202683</t>
+  </si>
+  <si>
+    <t>20.05.202684</t>
+  </si>
+  <si>
+    <t>20.05.202685</t>
+  </si>
+  <si>
+    <t>20.05.202686</t>
+  </si>
+  <si>
+    <t>20.05.202687</t>
+  </si>
+  <si>
+    <t>20.05.202688</t>
+  </si>
+  <si>
+    <t>20.05.202689</t>
+  </si>
+  <si>
+    <t>20.05.202690</t>
+  </si>
+  <si>
+    <t>20.05.202691</t>
+  </si>
+  <si>
+    <t>20.05.202692</t>
+  </si>
+  <si>
+    <t>20.05.202693</t>
+  </si>
+  <si>
+    <t>20.05.202694</t>
+  </si>
+  <si>
+    <t>20.05.202695</t>
+  </si>
+  <si>
+    <t>20.05.202696</t>
+  </si>
+  <si>
+    <t>21.05.20261</t>
+  </si>
+  <si>
+    <t>21.05.20262</t>
+  </si>
+  <si>
+    <t>21.05.20263</t>
+  </si>
+  <si>
+    <t>21.05.20264</t>
+  </si>
+  <si>
+    <t>21.05.20265</t>
+  </si>
+  <si>
+    <t>21.05.20266</t>
+  </si>
+  <si>
+    <t>21.05.20267</t>
+  </si>
+  <si>
+    <t>21.05.20268</t>
+  </si>
+  <si>
+    <t>21.05.20269</t>
+  </si>
+  <si>
+    <t>21.05.202610</t>
+  </si>
+  <si>
+    <t>21.05.202611</t>
+  </si>
+  <si>
+    <t>21.05.202612</t>
+  </si>
+  <si>
+    <t>21.05.202613</t>
+  </si>
+  <si>
+    <t>21.05.202614</t>
+  </si>
+  <si>
+    <t>21.05.202615</t>
+  </si>
+  <si>
+    <t>21.05.202616</t>
+  </si>
+  <si>
+    <t>21.05.202617</t>
+  </si>
+  <si>
+    <t>21.05.202618</t>
+  </si>
+  <si>
+    <t>21.05.202619</t>
+  </si>
+  <si>
+    <t>21.05.202620</t>
+  </si>
+  <si>
+    <t>21.05.202621</t>
+  </si>
+  <si>
+    <t>21.05.202622</t>
+  </si>
+  <si>
+    <t>21.05.202623</t>
+  </si>
+  <si>
+    <t>21.05.202624</t>
+  </si>
+  <si>
+    <t>21.05.202625</t>
+  </si>
+  <si>
+    <t>21.05.202626</t>
+  </si>
+  <si>
+    <t>21.05.202627</t>
+  </si>
+  <si>
+    <t>21.05.202628</t>
+  </si>
+  <si>
+    <t>21.05.202629</t>
+  </si>
+  <si>
+    <t>21.05.202630</t>
+  </si>
+  <si>
+    <t>21.05.202631</t>
+  </si>
+  <si>
+    <t>21.05.202632</t>
+  </si>
+  <si>
+    <t>21.05.202633</t>
+  </si>
+  <si>
+    <t>21.05.202634</t>
+  </si>
+  <si>
+    <t>21.05.202635</t>
+  </si>
+  <si>
+    <t>21.05.202636</t>
+  </si>
+  <si>
+    <t>21.05.202637</t>
+  </si>
+  <si>
+    <t>21.05.202638</t>
+  </si>
+  <si>
+    <t>21.05.202639</t>
+  </si>
+  <si>
+    <t>21.05.202640</t>
+  </si>
+  <si>
+    <t>21.05.202641</t>
+  </si>
+  <si>
+    <t>21.05.202642</t>
+  </si>
+  <si>
+    <t>21.05.202643</t>
+  </si>
+  <si>
+    <t>21.05.202644</t>
+  </si>
+  <si>
+    <t>21.05.202645</t>
+  </si>
+  <si>
+    <t>21.05.202646</t>
+  </si>
+  <si>
+    <t>21.05.202647</t>
+  </si>
+  <si>
+    <t>21.05.202648</t>
+  </si>
+  <si>
+    <t>21.05.202649</t>
+  </si>
+  <si>
+    <t>21.05.202650</t>
+  </si>
+  <si>
+    <t>21.05.202651</t>
+  </si>
+  <si>
+    <t>21.05.202652</t>
+  </si>
+  <si>
+    <t>21.05.202653</t>
+  </si>
+  <si>
+    <t>21.05.202654</t>
+  </si>
+  <si>
+    <t>21.05.202655</t>
+  </si>
+  <si>
+    <t>21.05.202656</t>
+  </si>
+  <si>
+    <t>21.05.202657</t>
+  </si>
+  <si>
+    <t>21.05.202658</t>
+  </si>
+  <si>
+    <t>21.05.202659</t>
+  </si>
+  <si>
+    <t>21.05.202660</t>
+  </si>
+  <si>
+    <t>21.05.202661</t>
+  </si>
+  <si>
+    <t>21.05.202662</t>
+  </si>
+  <si>
+    <t>21.05.202663</t>
+  </si>
+  <si>
+    <t>21.05.202664</t>
+  </si>
+  <si>
+    <t>21.05.202665</t>
+  </si>
+  <si>
+    <t>21.05.202666</t>
+  </si>
+  <si>
+    <t>21.05.202667</t>
+  </si>
+  <si>
+    <t>21.05.202668</t>
+  </si>
+  <si>
+    <t>21.05.202669</t>
+  </si>
+  <si>
+    <t>21.05.202670</t>
+  </si>
+  <si>
+    <t>21.05.202671</t>
+  </si>
+  <si>
+    <t>21.05.202672</t>
+  </si>
+  <si>
+    <t>21.05.202673</t>
+  </si>
+  <si>
+    <t>21.05.202674</t>
+  </si>
+  <si>
+    <t>21.05.202675</t>
+  </si>
+  <si>
+    <t>21.05.202676</t>
+  </si>
+  <si>
+    <t>21.05.202677</t>
+  </si>
+  <si>
+    <t>21.05.202678</t>
+  </si>
+  <si>
+    <t>21.05.202679</t>
+  </si>
+  <si>
+    <t>21.05.202680</t>
+  </si>
+  <si>
+    <t>21.05.202681</t>
+  </si>
+  <si>
+    <t>21.05.202682</t>
+  </si>
+  <si>
+    <t>21.05.202683</t>
+  </si>
+  <si>
+    <t>21.05.202684</t>
+  </si>
+  <si>
+    <t>21.05.202685</t>
+  </si>
+  <si>
+    <t>21.05.202686</t>
+  </si>
+  <si>
+    <t>21.05.202687</t>
+  </si>
+  <si>
+    <t>21.05.202688</t>
+  </si>
+  <si>
+    <t>21.05.202689</t>
+  </si>
+  <si>
+    <t>21.05.202690</t>
+  </si>
+  <si>
+    <t>21.05.202691</t>
+  </si>
+  <si>
+    <t>21.05.202692</t>
+  </si>
+  <si>
+    <t>21.05.202693</t>
+  </si>
+  <si>
+    <t>21.05.202694</t>
+  </si>
+  <si>
+    <t>21.05.202695</t>
+  </si>
+  <si>
+    <t>21.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46156.01041666666</v>
+        <v>46162.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46156.02083333334</v>
+        <v>46162.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46156.03125</v>
+        <v>46162.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46156.04166666666</v>
+        <v>46162.04166666666</v>
       </c>
       <c r="B6">
-        <v>-1.987</v>
+        <v>-34.296</v>
       </c>
       <c r="C6">
-        <v>899.005</v>
+        <v>1467.586</v>
       </c>
       <c r="D6">
-        <v>899.005</v>
+        <v>1467.586</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46156.05208333334</v>
+        <v>46162.05208333334</v>
       </c>
       <c r="B7">
-        <v>15.306</v>
+        <v>-42.822</v>
       </c>
       <c r="C7">
-        <v>112.628</v>
+        <v>2127.7</v>
       </c>
       <c r="D7">
-        <v>112.628</v>
+        <v>2127.7</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46156.0625</v>
+        <v>46162.0625</v>
       </c>
       <c r="B8">
-        <v>29.617</v>
+        <v>-39.539</v>
       </c>
       <c r="C8">
-        <v>197.84</v>
+        <v>1427.006</v>
       </c>
       <c r="D8">
-        <v>197.84</v>
+        <v>1427.006</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46156.07291666666</v>
+        <v>46162.07291666666</v>
       </c>
       <c r="B9">
-        <v>15.889</v>
+        <v>-17.656</v>
       </c>
       <c r="C9">
-        <v>274.211</v>
+        <v>1227.368</v>
       </c>
       <c r="D9">
-        <v>274.211</v>
+        <v>1227.368</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46156.08333333334</v>
+        <v>46162.08333333334</v>
       </c>
       <c r="B10">
-        <v>33.406</v>
+        <v>-13.488</v>
       </c>
       <c r="C10">
-        <v>369.307</v>
+        <v>978.111</v>
       </c>
       <c r="D10">
-        <v>369.307</v>
+        <v>978.111</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46156.09375</v>
+        <v>46162.09375</v>
       </c>
       <c r="B11">
-        <v>48.96</v>
+        <v>-5.646</v>
       </c>
       <c r="C11">
-        <v>287.949</v>
+        <v>889.938</v>
       </c>
       <c r="D11">
-        <v>287.949</v>
+        <v>889.938</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46156.10416666666</v>
+        <v>46162.10416666666</v>
       </c>
       <c r="B12">
-        <v>46.346</v>
+        <v>11.284</v>
       </c>
       <c r="C12">
-        <v>281.283</v>
+        <v>334.94</v>
       </c>
       <c r="D12">
-        <v>281.283</v>
+        <v>334.94</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46156.11458333334</v>
+        <v>46162.11458333334</v>
       </c>
       <c r="B13">
-        <v>-4.931</v>
+        <v>46.916</v>
       </c>
       <c r="C13">
-        <v>899.242</v>
+        <v>362.713</v>
       </c>
       <c r="D13">
-        <v>899.242</v>
+        <v>362.713</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46156.125</v>
+        <v>46162.125</v>
       </c>
       <c r="B14">
-        <v>-9.795</v>
+        <v>49.243</v>
       </c>
       <c r="C14">
-        <v>929.485</v>
+        <v>270.173</v>
       </c>
       <c r="D14">
-        <v>929.485</v>
+        <v>270.173</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46156.13541666666</v>
+        <v>46162.13541666666</v>
       </c>
       <c r="B15">
-        <v>-5.366</v>
+        <v>64.97199999999999</v>
       </c>
       <c r="C15">
-        <v>898.581</v>
+        <v>-17.394</v>
       </c>
       <c r="D15">
-        <v>898.581</v>
+        <v>-17.394</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46156.14583333334</v>
+        <v>46162.14583333334</v>
       </c>
       <c r="B16">
-        <v>7.066</v>
+        <v>57.006</v>
       </c>
       <c r="C16">
-        <v>896.364</v>
+        <v>67.955</v>
       </c>
       <c r="D16">
-        <v>896.364</v>
+        <v>67.955</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46156.15625</v>
+        <v>46162.15625</v>
       </c>
       <c r="B17">
-        <v>-6.392</v>
+        <v>71.03400000000001</v>
       </c>
       <c r="C17">
-        <v>899.342</v>
+        <v>183.272</v>
       </c>
       <c r="D17">
-        <v>899.342</v>
+        <v>183.272</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46156.16666666666</v>
+        <v>46162.16666666666</v>
       </c>
       <c r="B18">
-        <v>6.221</v>
+        <v>42.949</v>
       </c>
       <c r="C18">
-        <v>400</v>
+        <v>280.814</v>
       </c>
       <c r="D18">
-        <v>400</v>
+        <v>280.814</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46156.17708333334</v>
+        <v>46162.17708333334</v>
       </c>
       <c r="B19">
-        <v>13.032</v>
+        <v>38.842</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46156.1875</v>
+        <v>46162.1875</v>
       </c>
       <c r="B20">
-        <v>-0.443</v>
+        <v>43.697</v>
       </c>
       <c r="C20">
-        <v>899.091</v>
+        <v>122.574</v>
       </c>
       <c r="D20">
-        <v>899.091</v>
+        <v>122.574</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46156.19791666666</v>
+        <v>46162.19791666666</v>
       </c>
       <c r="B21">
-        <v>13.018</v>
+        <v>56.445</v>
       </c>
       <c r="C21">
-        <v>366.5</v>
+        <v>-45.79</v>
       </c>
       <c r="D21">
-        <v>366.5</v>
+        <v>-45.79</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46156.20833333334</v>
+        <v>46162.20833333334</v>
       </c>
       <c r="B22">
-        <v>27.553</v>
+        <v>115.429</v>
       </c>
       <c r="C22">
-        <v>400</v>
+        <v>127.849</v>
       </c>
       <c r="D22">
-        <v>400</v>
+        <v>127.849</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46156.21875</v>
+        <v>46162.21875</v>
       </c>
       <c r="B23">
-        <v>30.43</v>
+        <v>103.766</v>
       </c>
       <c r="C23">
-        <v>362.386</v>
+        <v>350.743</v>
       </c>
       <c r="D23">
-        <v>362.386</v>
+        <v>350.743</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46156.22916666666</v>
+        <v>46162.22916666666</v>
       </c>
       <c r="B24">
-        <v>-3.535</v>
+        <v>113.255</v>
       </c>
       <c r="C24">
-        <v>988.774</v>
+        <v>335.858</v>
       </c>
       <c r="D24">
-        <v>988.774</v>
+        <v>335.858</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46156.23958333334</v>
+        <v>46162.23958333334</v>
       </c>
       <c r="B25">
-        <v>10.705</v>
+        <v>93.378</v>
       </c>
       <c r="C25">
-        <v>386.406</v>
+        <v>2.794</v>
       </c>
       <c r="D25">
-        <v>386.406</v>
+        <v>2.794</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46156.25</v>
+        <v>46162.25</v>
       </c>
       <c r="B26">
-        <v>-4.423</v>
+        <v>54.456</v>
       </c>
       <c r="C26">
-        <v>990.285</v>
+        <v>17.702</v>
       </c>
       <c r="D26">
-        <v>990.285</v>
+        <v>17.702</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46156.26041666666</v>
+        <v>46162.26041666666</v>
       </c>
       <c r="B27">
-        <v>-0.425</v>
+        <v>22.568</v>
       </c>
       <c r="C27">
-        <v>996.627</v>
+        <v>2.384</v>
       </c>
       <c r="D27">
-        <v>996.627</v>
+        <v>2.384</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46156.27083333334</v>
+        <v>46162.27083333334</v>
       </c>
       <c r="B28">
-        <v>-27.548</v>
+        <v>5.983</v>
       </c>
       <c r="C28">
-        <v>885.508</v>
+        <v>1.1</v>
       </c>
       <c r="D28">
-        <v>885.508</v>
+        <v>1.1</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46156.28125</v>
+        <v>46162.28125</v>
       </c>
       <c r="B29">
-        <v>-25.157</v>
+        <v>-30.78</v>
       </c>
       <c r="C29">
-        <v>1107.244</v>
+        <v>1028.036</v>
       </c>
       <c r="D29">
-        <v>1107.244</v>
+        <v>1028.036</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46156.29166666666</v>
+        <v>46162.29166666666</v>
       </c>
       <c r="B30">
-        <v>-43.164</v>
+        <v>-104.104</v>
       </c>
       <c r="C30">
-        <v>2069.67</v>
+        <v>3453.373</v>
       </c>
       <c r="D30">
-        <v>2069.67</v>
+        <v>3453.373</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46156.30208333334</v>
+        <v>46162.30208333334</v>
       </c>
       <c r="B31">
-        <v>-48.477</v>
+        <v>-124.267</v>
       </c>
       <c r="C31">
-        <v>1062.76</v>
+        <v>6722.079</v>
       </c>
       <c r="D31">
-        <v>1062.76</v>
+        <v>6722.079</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46156.3125</v>
+        <v>46162.3125</v>
       </c>
       <c r="B32">
-        <v>-12.263</v>
+        <v>-114.595</v>
       </c>
       <c r="C32">
-        <v>899.3200000000001</v>
+        <v>3930.32</v>
       </c>
       <c r="D32">
-        <v>899.3200000000001</v>
+        <v>3930.32</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46156.32291666666</v>
+        <v>46162.32291666666</v>
       </c>
       <c r="B33">
-        <v>3.689</v>
+        <v>-96.15900000000001</v>
       </c>
       <c r="C33">
-        <v>38.564</v>
+        <v>1109.86</v>
       </c>
       <c r="D33">
-        <v>38.564</v>
+        <v>1109.86</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46156.33333333334</v>
+        <v>46162.33333333334</v>
       </c>
       <c r="B34">
-        <v>35.212</v>
+        <v>-101.024</v>
       </c>
       <c r="C34">
-        <v>-128.732</v>
+        <v>3129.508</v>
       </c>
       <c r="D34">
-        <v>-128.732</v>
+        <v>3129.508</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46156.34375</v>
+        <v>46162.34375</v>
       </c>
       <c r="B35">
-        <v>114.375</v>
+        <v>-65.11499999999999</v>
       </c>
       <c r="C35">
-        <v>7.245</v>
+        <v>3185.071</v>
       </c>
       <c r="D35">
-        <v>7.245</v>
+        <v>3185.071</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46156.35416666666</v>
+        <v>46162.35416666666</v>
       </c>
       <c r="B36">
-        <v>156.659</v>
+        <v>-27.075</v>
       </c>
       <c r="C36">
-        <v>283.599</v>
+        <v>996.754</v>
       </c>
       <c r="D36">
-        <v>283.599</v>
+        <v>996.754</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46156.36458333334</v>
+        <v>46162.36458333334</v>
       </c>
       <c r="B37">
-        <v>58.728</v>
+        <v>-3.324</v>
       </c>
       <c r="C37">
-        <v>-4.945</v>
+        <v>996.816</v>
       </c>
       <c r="D37">
-        <v>-4.945</v>
+        <v>996.816</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46156.375</v>
+        <v>46162.375</v>
       </c>
       <c r="B38">
-        <v>100.925</v>
+        <v>-58.386</v>
       </c>
       <c r="C38">
-        <v>-126.547</v>
+        <v>847.836</v>
       </c>
       <c r="D38">
-        <v>-126.547</v>
+        <v>847.836</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46156.38541666666</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="B39">
-        <v>75.526</v>
+        <v>-31.749</v>
       </c>
       <c r="C39">
-        <v>-68.491</v>
+        <v>731.342</v>
       </c>
       <c r="D39">
-        <v>-68.491</v>
+        <v>731.342</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46156.39583333334</v>
+        <v>46162.39583333334</v>
       </c>
       <c r="B40">
-        <v>83.488</v>
+        <v>17.6</v>
       </c>
       <c r="C40">
-        <v>-305.518</v>
+        <v>-5.925</v>
       </c>
       <c r="D40">
-        <v>-305.518</v>
+        <v>-5.925</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46156.40625</v>
+        <v>46162.40625</v>
       </c>
       <c r="B41">
-        <v>57.545</v>
+        <v>5.156</v>
       </c>
       <c r="C41">
-        <v>-40.178</v>
+        <v>101.096</v>
       </c>
       <c r="D41">
-        <v>-40.178</v>
+        <v>101.096</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46156.41666666666</v>
+        <v>46162.41666666666</v>
       </c>
       <c r="B42">
-        <v>-6.273</v>
+        <v>58.851</v>
       </c>
       <c r="C42">
-        <v>699</v>
+        <v>82.589</v>
       </c>
       <c r="D42">
-        <v>699</v>
+        <v>82.589</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46156.42708333334</v>
+        <v>46162.42708333334</v>
       </c>
       <c r="B43">
-        <v>-13.069</v>
+        <v>54.228</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>141.879</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>141.879</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46156.4375</v>
+        <v>46162.4375</v>
       </c>
       <c r="B44">
-        <v>50.861</v>
+        <v>47.785</v>
       </c>
       <c r="C44">
-        <v>-242.905</v>
+        <v>17.922</v>
       </c>
       <c r="D44">
-        <v>-242.905</v>
+        <v>17.922</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46156.44791666666</v>
+        <v>46162.44791666666</v>
       </c>
       <c r="B45">
-        <v>67.486</v>
+        <v>22.001</v>
       </c>
       <c r="C45">
-        <v>-2027.875</v>
+        <v>-1.761</v>
       </c>
       <c r="D45">
-        <v>-2027.875</v>
+        <v>-1.761</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46156.45833333334</v>
+        <v>46162.45833333334</v>
       </c>
       <c r="B46">
-        <v>-1.484</v>
+        <v>-27.03</v>
       </c>
       <c r="C46">
-        <v>602.994</v>
+        <v>576.14</v>
       </c>
       <c r="D46">
-        <v>602.994</v>
+        <v>576.14</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46156.46875</v>
+        <v>46162.46875</v>
       </c>
       <c r="B47">
-        <v>7.283</v>
+        <v>-67.968</v>
       </c>
       <c r="C47">
-        <v>4.667</v>
+        <v>598.247</v>
       </c>
       <c r="D47">
-        <v>4.667</v>
+        <v>598.247</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46156.47916666666</v>
+        <v>46162.47916666666</v>
       </c>
       <c r="B48">
-        <v>27.434</v>
+        <v>-126.99</v>
       </c>
       <c r="C48">
-        <v>10.74</v>
+        <v>602.353</v>
       </c>
       <c r="D48">
-        <v>10.74</v>
+        <v>602.353</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46156.48958333334</v>
+        <v>46162.48958333334</v>
       </c>
       <c r="B49">
-        <v>29.576</v>
+        <v>-90.70399999999999</v>
       </c>
       <c r="C49">
-        <v>34.383</v>
+        <v>572.187</v>
       </c>
       <c r="D49">
-        <v>34.383</v>
+        <v>572.187</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46156.5</v>
+        <v>46162.5</v>
       </c>
       <c r="B50">
-        <v>22.123</v>
+        <v>-73.17100000000001</v>
       </c>
       <c r="C50">
-        <v>-18.098</v>
+        <v>772.615</v>
       </c>
       <c r="D50">
-        <v>-18.098</v>
+        <v>772.615</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46156.51041666666</v>
+        <v>46162.51041666666</v>
       </c>
       <c r="B51">
-        <v>113.443</v>
+        <v>-79.652</v>
       </c>
       <c r="C51">
-        <v>-11.388</v>
+        <v>642.875</v>
       </c>
       <c r="D51">
-        <v>-11.388</v>
+        <v>642.875</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46156.52083333334</v>
+        <v>46162.52083333334</v>
       </c>
       <c r="B52">
-        <v>68.149</v>
+        <v>-44.031</v>
       </c>
       <c r="C52">
-        <v>-3.707</v>
+        <v>592.534</v>
       </c>
       <c r="D52">
-        <v>-3.707</v>
+        <v>592.534</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46156.53125</v>
+        <v>46162.53125</v>
       </c>
       <c r="B53">
-        <v>-5.259</v>
+        <v>-51.703</v>
       </c>
       <c r="C53">
-        <v>507.679</v>
+        <v>592.566</v>
       </c>
       <c r="D53">
-        <v>507.679</v>
+        <v>592.566</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46156.54166666666</v>
+        <v>46162.54166666666</v>
       </c>
       <c r="B54">
-        <v>8.191000000000001</v>
+        <v>-81.56699999999999</v>
       </c>
       <c r="C54">
-        <v>3.168</v>
+        <v>1571.461</v>
       </c>
       <c r="D54">
-        <v>3.168</v>
+        <v>1571.461</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46156.55208333334</v>
+        <v>46162.55208333334</v>
       </c>
       <c r="B55">
-        <v>-24.284</v>
+        <v>-89.98</v>
       </c>
       <c r="C55">
-        <v>656.317</v>
+        <v>772.268</v>
       </c>
       <c r="D55">
-        <v>656.317</v>
+        <v>772.268</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46156.5625</v>
+        <v>46162.5625</v>
       </c>
       <c r="B56">
-        <v>-52.076</v>
+        <v>-57.439</v>
       </c>
       <c r="C56">
-        <v>734.8630000000001</v>
+        <v>665.097</v>
       </c>
       <c r="D56">
-        <v>734.8630000000001</v>
+        <v>665.097</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46156.57291666666</v>
+        <v>46162.57291666666</v>
       </c>
       <c r="B57">
-        <v>11.302</v>
+        <v>-24.31</v>
       </c>
       <c r="C57">
-        <v>19.983</v>
+        <v>609.9880000000001</v>
       </c>
       <c r="D57">
-        <v>19.983</v>
+        <v>609.9880000000001</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46156.58333333334</v>
+        <v>46162.58333333334</v>
       </c>
       <c r="B58">
-        <v>4.946</v>
+        <v>3.179</v>
       </c>
       <c r="C58">
-        <v>-84.92400000000001</v>
+        <v>299.512</v>
       </c>
       <c r="D58">
-        <v>-84.92400000000001</v>
+        <v>299.512</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46156.59375</v>
+        <v>46162.59375</v>
       </c>
       <c r="B59">
-        <v>-8.6</v>
+        <v>50.344</v>
       </c>
       <c r="C59">
-        <v>450</v>
+        <v>358.971</v>
       </c>
       <c r="D59">
-        <v>450</v>
+        <v>358.971</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46156.60416666666</v>
+        <v>46162.60416666666</v>
       </c>
       <c r="B60">
-        <v>11.973</v>
+        <v>102.336</v>
       </c>
       <c r="C60">
-        <v>249.215</v>
+        <v>281.115</v>
       </c>
       <c r="D60">
-        <v>249.215</v>
+        <v>281.115</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46156.61458333334</v>
+        <v>46162.61458333334</v>
       </c>
       <c r="B61">
-        <v>66.06999999999999</v>
+        <v>116.79</v>
       </c>
       <c r="C61">
-        <v>-99.071</v>
+        <v>-1702.49</v>
       </c>
       <c r="D61">
-        <v>-99.071</v>
+        <v>-1702.49</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46156.625</v>
+        <v>46162.625</v>
       </c>
       <c r="B62">
-        <v>106.633</v>
+        <v>81.482</v>
       </c>
       <c r="C62">
-        <v>-2067.1</v>
+        <v>135.037</v>
       </c>
       <c r="D62">
-        <v>-2067.1</v>
+        <v>135.037</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46156.63541666666</v>
+        <v>46162.63541666666</v>
       </c>
       <c r="B63">
-        <v>84.46899999999999</v>
+        <v>77.753</v>
       </c>
       <c r="C63">
-        <v>-25.186</v>
+        <v>305.027</v>
       </c>
       <c r="D63">
-        <v>-25.186</v>
+        <v>305.027</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46156.64583333334</v>
+        <v>46162.64583333334</v>
       </c>
       <c r="B64">
-        <v>113.834</v>
+        <v>107.415</v>
       </c>
       <c r="C64">
-        <v>-36.564</v>
+        <v>-57.301</v>
       </c>
       <c r="D64">
-        <v>-36.564</v>
+        <v>-57.301</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46156.65625</v>
+        <v>46162.65625</v>
       </c>
       <c r="B65">
-        <v>132.007</v>
+        <v>105.585</v>
       </c>
       <c r="C65">
-        <v>-73.20099999999999</v>
+        <v>6.005</v>
       </c>
       <c r="D65">
-        <v>-73.20099999999999</v>
+        <v>6.005</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46156.66666666666</v>
+        <v>46162.66666666666</v>
       </c>
       <c r="B66">
-        <v>240.504</v>
+        <v>19.017</v>
       </c>
       <c r="C66">
-        <v>9.112</v>
+        <v>-21.541</v>
       </c>
       <c r="D66">
-        <v>9.112</v>
+        <v>-21.541</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46156.67708333334</v>
+        <v>46162.67708333334</v>
       </c>
       <c r="B67">
-        <v>247.152</v>
+        <v>17.535</v>
       </c>
       <c r="C67">
-        <v>4.272</v>
+        <v>346.4</v>
       </c>
       <c r="D67">
-        <v>4.272</v>
+        <v>346.4</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46156.6875</v>
+        <v>46162.6875</v>
       </c>
       <c r="B68">
-        <v>213.449</v>
+        <v>94.364</v>
       </c>
       <c r="C68">
-        <v>-5.229</v>
+        <v>288.024</v>
       </c>
       <c r="D68">
-        <v>-5.229</v>
+        <v>288.024</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46156.69791666666</v>
+        <v>46162.69791666666</v>
       </c>
       <c r="B69">
-        <v>126.318</v>
+        <v>103.921</v>
       </c>
       <c r="C69">
-        <v>-37.145</v>
+        <v>273.446</v>
       </c>
       <c r="D69">
-        <v>-37.145</v>
+        <v>273.446</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46156.70833333334</v>
+        <v>46162.70833333334</v>
       </c>
       <c r="B70">
-        <v>114.523</v>
+        <v>127.021</v>
       </c>
       <c r="C70">
-        <v>1.938</v>
+        <v>-179.28</v>
       </c>
       <c r="D70">
-        <v>1.938</v>
+        <v>-179.28</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46156.71875</v>
+        <v>46162.71875</v>
       </c>
       <c r="B71">
-        <v>75.17</v>
+        <v>114.012</v>
       </c>
       <c r="C71">
-        <v>-2.421</v>
+        <v>0.885</v>
       </c>
       <c r="D71">
-        <v>-2.421</v>
+        <v>0.885</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46156.72916666666</v>
+        <v>46162.72916666666</v>
       </c>
       <c r="B72">
-        <v>27.611</v>
+        <v>112.283</v>
       </c>
       <c r="C72">
-        <v>1.1</v>
+        <v>-12.145</v>
       </c>
       <c r="D72">
-        <v>1.1</v>
+        <v>-12.145</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46156.73958333334</v>
+        <v>46162.73958333334</v>
       </c>
       <c r="B73">
-        <v>43.679</v>
+        <v>138.25</v>
       </c>
       <c r="C73">
-        <v>288.678</v>
+        <v>6.345</v>
       </c>
       <c r="D73">
-        <v>288.678</v>
+        <v>6.345</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46156.75</v>
+        <v>46162.75</v>
       </c>
       <c r="B74">
-        <v>92.10299999999999</v>
+        <v>125.693</v>
       </c>
       <c r="C74">
-        <v>155.593</v>
+        <v>10.459</v>
       </c>
       <c r="D74">
-        <v>155.593</v>
+        <v>10.459</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46156.76041666666</v>
+        <v>46162.76041666666</v>
       </c>
       <c r="B75">
-        <v>23.003</v>
+        <v>114.539</v>
       </c>
       <c r="C75">
-        <v>258.651</v>
+        <v>1.673</v>
       </c>
       <c r="D75">
-        <v>258.651</v>
+        <v>1.673</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46156.77083333334</v>
+        <v>46162.77083333334</v>
       </c>
       <c r="B76">
-        <v>0.247</v>
+        <v>32.627</v>
       </c>
       <c r="C76">
-        <v>927.87</v>
+        <v>0.6</v>
       </c>
       <c r="D76">
-        <v>927.87</v>
+        <v>0.6</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46156.78125</v>
+        <v>46162.78125</v>
       </c>
       <c r="B77">
-        <v>-26.926</v>
+        <v>35.937</v>
       </c>
       <c r="C77">
-        <v>1769.907</v>
+        <v>0.65</v>
       </c>
       <c r="D77">
-        <v>1769.907</v>
+        <v>0.65</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46156.79166666666</v>
+        <v>46162.79166666666</v>
       </c>
       <c r="B78">
-        <v>8.795</v>
+        <v>47.658</v>
       </c>
       <c r="C78">
-        <v>337.467</v>
+        <v>14.632</v>
       </c>
       <c r="D78">
-        <v>337.467</v>
+        <v>14.632</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46156.80208333334</v>
+        <v>46162.80208333334</v>
       </c>
       <c r="B79">
-        <v>-8.301</v>
+        <v>42.245</v>
       </c>
       <c r="C79">
-        <v>1340.174</v>
+        <v>3.816</v>
       </c>
       <c r="D79">
-        <v>1340.174</v>
+        <v>3.816</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46156.8125</v>
+        <v>46162.8125</v>
       </c>
       <c r="B80">
-        <v>-18.745</v>
+        <v>2.142</v>
       </c>
       <c r="C80">
-        <v>1538.636</v>
+        <v>263.498</v>
       </c>
       <c r="D80">
-        <v>1538.636</v>
+        <v>263.498</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46156.82291666666</v>
+        <v>46162.82291666666</v>
       </c>
       <c r="B81">
-        <v>-43.293</v>
+        <v>13.188</v>
       </c>
       <c r="C81">
-        <v>3264.774</v>
+        <v>288.704</v>
       </c>
       <c r="D81">
-        <v>3264.774</v>
+        <v>288.704</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46156.83333333334</v>
+        <v>46162.83333333334</v>
       </c>
       <c r="B82">
-        <v>-32.319</v>
+        <v>-34.097</v>
       </c>
       <c r="C82">
-        <v>3166.859</v>
+        <v>1460.639</v>
       </c>
       <c r="D82">
-        <v>3166.859</v>
+        <v>1460.639</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46156.84375</v>
+        <v>46162.84375</v>
       </c>
       <c r="B83">
-        <v>-39.243</v>
+        <v>-39.418</v>
       </c>
       <c r="C83">
-        <v>2930.913</v>
+        <v>1353.292</v>
       </c>
       <c r="D83">
-        <v>2930.913</v>
+        <v>1353.292</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46156.85416666666</v>
+        <v>46162.85416666666</v>
       </c>
       <c r="B84">
-        <v>-32.416</v>
+        <v>-44.261</v>
       </c>
       <c r="C84">
-        <v>3446.732</v>
+        <v>956.809</v>
       </c>
       <c r="D84">
-        <v>3446.732</v>
+        <v>956.809</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46156.86458333334</v>
+        <v>46162.86458333334</v>
       </c>
       <c r="B85">
-        <v>-64.25</v>
+        <v>0.463</v>
       </c>
       <c r="C85">
-        <v>6689.756</v>
+        <v>121.147</v>
       </c>
       <c r="D85">
-        <v>6689.756</v>
+        <v>121.147</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46156.875</v>
+        <v>46162.875</v>
       </c>
       <c r="B86">
-        <v>-83.36</v>
+        <v>-25.48</v>
       </c>
       <c r="C86">
-        <v>6892.27</v>
+        <v>1016.584</v>
       </c>
       <c r="D86">
-        <v>6892.27</v>
+        <v>1016.584</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46156.88541666666</v>
+        <v>46162.88541666666</v>
       </c>
       <c r="B87">
-        <v>-125.368</v>
+        <v>-8.191000000000001</v>
       </c>
       <c r="C87">
-        <v>6999</v>
+        <v>1096.38</v>
       </c>
       <c r="D87">
-        <v>6999</v>
+        <v>1096.38</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46156.89583333334</v>
+        <v>46162.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.014</v>
+        <v>2.81</v>
       </c>
       <c r="C88">
-        <v>354.213</v>
+        <v>266</v>
       </c>
       <c r="D88">
-        <v>354.213</v>
+        <v>266</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46156.90625</v>
+        <v>46162.90625</v>
       </c>
       <c r="B89">
-        <v>-34.612</v>
+        <v>40.442</v>
       </c>
       <c r="C89">
-        <v>1641.73</v>
+        <v>-1090.607</v>
       </c>
       <c r="D89">
-        <v>1641.73</v>
+        <v>-1090.607</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46156.91666666666</v>
+        <v>46162.91666666666</v>
       </c>
       <c r="B90">
-        <v>-24.278</v>
+        <v>22.499</v>
       </c>
       <c r="C90">
-        <v>1258.839</v>
+        <v>-317.049</v>
       </c>
       <c r="D90">
-        <v>1258.839</v>
+        <v>-317.049</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46156.92708333334</v>
+        <v>46162.92708333334</v>
       </c>
       <c r="B91">
-        <v>12.895</v>
+        <v>22.366</v>
       </c>
       <c r="C91">
-        <v>355.914</v>
+        <v>254.202</v>
       </c>
       <c r="D91">
-        <v>355.914</v>
+        <v>254.202</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46156.9375</v>
+        <v>46162.9375</v>
       </c>
       <c r="B92">
-        <v>42.192</v>
+        <v>13.728</v>
       </c>
       <c r="C92">
-        <v>400</v>
+        <v>179.479</v>
       </c>
       <c r="D92">
-        <v>400</v>
+        <v>179.479</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46156.94791666666</v>
+        <v>46162.94791666666</v>
       </c>
       <c r="B93">
-        <v>27.053</v>
+        <v>27.49</v>
       </c>
       <c r="C93">
-        <v>384.27</v>
+        <v>-57.571</v>
       </c>
       <c r="D93">
-        <v>384.27</v>
+        <v>-57.571</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46156.95833333334</v>
+        <v>46162.95833333334</v>
       </c>
       <c r="B94">
-        <v>24.679</v>
+        <v>31.925</v>
       </c>
       <c r="C94">
-        <v>339.935</v>
+        <v>153.453</v>
       </c>
       <c r="D94">
-        <v>339.935</v>
+        <v>153.453</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46156.96875</v>
+        <v>46162.96875</v>
       </c>
       <c r="B95">
-        <v>21.677</v>
+        <v>38.77</v>
       </c>
       <c r="C95">
-        <v>262.764</v>
+        <v>-18.118</v>
       </c>
       <c r="D95">
-        <v>262.764</v>
+        <v>-18.118</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46156.97916666666</v>
+        <v>46162.97916666666</v>
       </c>
       <c r="B96">
-        <v>47.964</v>
+        <v>25.327</v>
       </c>
       <c r="C96">
-        <v>263.453</v>
+        <v>106.975</v>
       </c>
       <c r="D96">
-        <v>263.453</v>
+        <v>106.975</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46156.98958333334</v>
+        <v>46162.98958333334</v>
       </c>
       <c r="B97">
-        <v>78.491</v>
+        <v>21.299</v>
       </c>
       <c r="C97">
-        <v>323.67</v>
+        <v>-36.204</v>
       </c>
       <c r="D97">
-        <v>323.67</v>
+        <v>-36.204</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B98">
-        <v>34.239</v>
+        <v>31.31</v>
       </c>
       <c r="C98">
-        <v>397.746</v>
+        <v>174.729</v>
       </c>
       <c r="D98">
-        <v>397.746</v>
+        <v>174.729</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B99">
-        <v>33.557</v>
+        <v>0.852</v>
       </c>
       <c r="C99">
-        <v>282.4</v>
+        <v>271.53</v>
       </c>
       <c r="D99">
-        <v>282.4</v>
+        <v>271.53</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B100">
-        <v>48.052</v>
+        <v>10.407</v>
       </c>
       <c r="C100">
-        <v>217.076</v>
+        <v>253.534</v>
       </c>
       <c r="D100">
-        <v>217.076</v>
+        <v>253.534</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B101">
-        <v>71.84</v>
+        <v>13.68</v>
       </c>
       <c r="C101">
-        <v>76.732</v>
+        <v>273.965</v>
       </c>
       <c r="D101">
-        <v>76.732</v>
+        <v>273.965</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B102">
-        <v>39.083</v>
+        <v>-7.336</v>
       </c>
       <c r="C102">
-        <v>99.79600000000001</v>
+        <v>949.943</v>
       </c>
       <c r="D102">
-        <v>99.79600000000001</v>
+        <v>949.943</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B103">
-        <v>2.228</v>
+        <v>3.595</v>
       </c>
       <c r="C103">
         <v>400</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B104">
-        <v>34</v>
+        <v>5.397</v>
       </c>
       <c r="C104">
-        <v>27.634</v>
+        <v>274.467</v>
       </c>
       <c r="D104">
-        <v>27.634</v>
+        <v>274.467</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B105">
-        <v>-7.774</v>
+        <v>21.265</v>
       </c>
       <c r="C105">
-        <v>842.429</v>
+        <v>207.668</v>
       </c>
       <c r="D105">
-        <v>842.429</v>
+        <v>207.668</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B106">
-        <v>-13.679</v>
+        <v>74.15600000000001</v>
       </c>
       <c r="C106">
-        <v>984.551</v>
+        <v>-677.771</v>
       </c>
       <c r="D106">
-        <v>984.551</v>
+        <v>-677.771</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B107">
-        <v>-30.066</v>
+        <v>18.611</v>
       </c>
       <c r="C107">
-        <v>863.676</v>
+        <v>-230.177</v>
       </c>
       <c r="D107">
-        <v>863.676</v>
+        <v>-230.177</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B108">
-        <v>-10.595</v>
+        <v>10.986</v>
       </c>
       <c r="C108">
-        <v>915.296</v>
+        <v>122.113</v>
       </c>
       <c r="D108">
-        <v>915.296</v>
+        <v>122.113</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B109">
-        <v>-11.588</v>
+        <v>10.63</v>
       </c>
       <c r="C109">
-        <v>898.568</v>
+        <v>164.987</v>
       </c>
       <c r="D109">
-        <v>898.568</v>
+        <v>164.987</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B110">
-        <v>14.166</v>
+        <v>31.922</v>
       </c>
       <c r="C110">
-        <v>400</v>
+        <v>256.163</v>
       </c>
       <c r="D110">
-        <v>400</v>
+        <v>256.163</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B111">
-        <v>19.427</v>
+        <v>15.413</v>
       </c>
       <c r="C111">
-        <v>271.875</v>
+        <v>97.91500000000001</v>
       </c>
       <c r="D111">
-        <v>271.875</v>
+        <v>97.91500000000001</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B112">
-        <v>27.33</v>
+        <v>16.558</v>
       </c>
       <c r="C112">
-        <v>302.565</v>
+        <v>52.185</v>
       </c>
       <c r="D112">
-        <v>302.565</v>
+        <v>52.185</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B113">
-        <v>41.238</v>
+        <v>26.543</v>
       </c>
       <c r="C113">
-        <v>362.447</v>
+        <v>102.069</v>
       </c>
       <c r="D113">
-        <v>362.447</v>
+        <v>102.069</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B114">
-        <v>93.105</v>
+        <v>48.332</v>
       </c>
       <c r="C114">
-        <v>188.356</v>
+        <v>258.136</v>
       </c>
       <c r="D114">
-        <v>188.356</v>
+        <v>258.136</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B115">
-        <v>52.538</v>
+        <v>12.537</v>
       </c>
       <c r="C115">
-        <v>-226.857</v>
+        <v>187.102</v>
       </c>
       <c r="D115">
-        <v>-226.857</v>
+        <v>187.102</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B116">
-        <v>66.773</v>
+        <v>37.009</v>
       </c>
       <c r="C116">
-        <v>-273.32</v>
+        <v>180.721</v>
       </c>
       <c r="D116">
-        <v>-273.32</v>
+        <v>180.721</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B117">
-        <v>29.059</v>
+        <v>41.747</v>
       </c>
       <c r="C117">
-        <v>186.898</v>
+        <v>70.494</v>
       </c>
       <c r="D117">
-        <v>186.898</v>
+        <v>70.494</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B118">
-        <v>40.594</v>
+        <v>46.538</v>
       </c>
       <c r="C118">
-        <v>112.955</v>
+        <v>131.914</v>
       </c>
       <c r="D118">
-        <v>112.955</v>
+        <v>131.914</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B119">
-        <v>34.717</v>
+        <v>21.219</v>
       </c>
       <c r="C119">
-        <v>266.01</v>
+        <v>261.944</v>
       </c>
       <c r="D119">
-        <v>266.01</v>
+        <v>261.944</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B120">
-        <v>10.113</v>
+        <v>-12.071</v>
       </c>
       <c r="C120">
-        <v>260.652</v>
+        <v>897.867</v>
       </c>
       <c r="D120">
-        <v>260.652</v>
+        <v>897.867</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B121">
-        <v>17.294</v>
+        <v>-35.771</v>
       </c>
       <c r="C121">
-        <v>247.694</v>
+        <v>998.724</v>
       </c>
       <c r="D121">
-        <v>247.694</v>
+        <v>998.724</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B122">
-        <v>47.779</v>
+        <v>-47.612</v>
       </c>
       <c r="C122">
-        <v>63.04</v>
+        <v>3992.366</v>
       </c>
       <c r="D122">
-        <v>63.04</v>
+        <v>3992.366</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B123">
-        <v>30.477</v>
+        <v>-38.998</v>
       </c>
       <c r="C123">
-        <v>132.9</v>
+        <v>2502.938</v>
       </c>
       <c r="D123">
-        <v>132.9</v>
+        <v>2502.938</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B124">
-        <v>38.38</v>
+        <v>-56.175</v>
       </c>
       <c r="C124">
-        <v>-13.768</v>
+        <v>1220.667</v>
       </c>
       <c r="D124">
-        <v>-13.768</v>
+        <v>1220.667</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B125">
-        <v>39.488</v>
+        <v>-46.927</v>
       </c>
       <c r="C125">
-        <v>-87.121</v>
+        <v>1137.69</v>
       </c>
       <c r="D125">
-        <v>-87.121</v>
+        <v>1137.69</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B126">
-        <v>24.41</v>
+        <v>-2.161</v>
       </c>
       <c r="C126">
-        <v>178.347</v>
+        <v>1053.15</v>
       </c>
       <c r="D126">
-        <v>178.347</v>
+        <v>1053.15</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B127">
-        <v>16.511</v>
+        <v>24.184</v>
       </c>
       <c r="C127">
-        <v>9.385999999999999</v>
+        <v>259.558</v>
       </c>
       <c r="D127">
-        <v>9.385999999999999</v>
+        <v>259.558</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B128">
-        <v>16.405</v>
+        <v>-8.269</v>
       </c>
       <c r="C128">
-        <v>12.374</v>
+        <v>899.152</v>
       </c>
       <c r="D128">
-        <v>12.374</v>
+        <v>899.152</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B129">
-        <v>26.347</v>
+        <v>-19.458</v>
       </c>
       <c r="C129">
-        <v>-84.68000000000001</v>
+        <v>1065.536</v>
       </c>
       <c r="D129">
-        <v>-84.68000000000001</v>
+        <v>1065.536</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B130">
-        <v>9.134</v>
+        <v>52.248</v>
       </c>
       <c r="C130">
-        <v>173.403</v>
+        <v>-14.549</v>
       </c>
       <c r="D130">
-        <v>173.403</v>
+        <v>-14.549</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B131">
-        <v>-30.423</v>
+        <v>-1.34</v>
       </c>
       <c r="C131">
-        <v>852.2</v>
+        <v>876.279</v>
       </c>
       <c r="D131">
-        <v>852.2</v>
+        <v>876.279</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B132">
-        <v>-24.26</v>
+        <v>-4.35</v>
       </c>
       <c r="C132">
-        <v>848.75</v>
+        <v>891.024</v>
       </c>
       <c r="D132">
-        <v>848.75</v>
+        <v>891.024</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B133">
-        <v>-29.252</v>
+        <v>-89.893</v>
       </c>
       <c r="C133">
-        <v>847.143</v>
+        <v>888.393</v>
       </c>
       <c r="D133">
-        <v>847.143</v>
+        <v>888.393</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B134">
-        <v>-65.646</v>
+        <v>-57.939</v>
       </c>
       <c r="C134">
-        <v>898.773</v>
+        <v>697.08</v>
       </c>
       <c r="D134">
-        <v>898.773</v>
+        <v>697.08</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B135">
-        <v>-77.47199999999999</v>
+        <v>-59.18</v>
       </c>
       <c r="C135">
-        <v>865.535</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>865.535</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B136">
-        <v>-33.456</v>
+        <v>-44.895</v>
       </c>
       <c r="C136">
-        <v>799.205</v>
+        <v>766.255</v>
       </c>
       <c r="D136">
-        <v>799.205</v>
+        <v>766.255</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B137">
-        <v>-21.656</v>
+        <v>-73.566</v>
       </c>
       <c r="C137">
-        <v>28.067</v>
+        <v>765.6660000000001</v>
       </c>
       <c r="D137">
-        <v>28.067</v>
+        <v>765.6660000000001</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B138">
-        <v>-55.028</v>
+        <v>-55.06</v>
       </c>
       <c r="C138">
-        <v>499</v>
+        <v>554.65</v>
       </c>
       <c r="D138">
-        <v>499</v>
+        <v>554.65</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B139">
-        <v>3.338</v>
+        <v>-33.074</v>
       </c>
       <c r="C139">
-        <v>-16.965</v>
+        <v>550.749</v>
       </c>
       <c r="D139">
-        <v>-16.965</v>
+        <v>550.749</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B140">
-        <v>37.091</v>
+        <v>-5.467</v>
       </c>
       <c r="C140">
-        <v>-33.655</v>
+        <v>550.65</v>
       </c>
       <c r="D140">
-        <v>-33.655</v>
+        <v>550.65</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>-11.176</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>552.6900000000001</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>552.6900000000001</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>107.787</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>-6147.741</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>-6147.741</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>26.042</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>34.084</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>324.677</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>324.677</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>17.038</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>16.744</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>16.744</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>29.288</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>-53.404</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>-53.404</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>39.191</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>73.535</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>73.535</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>-17.118</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>633.963</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>633.963</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.05.20261</t>
-  </si>
-  <si>
-    <t>20.05.20262</t>
-  </si>
-  <si>
-    <t>20.05.20263</t>
-  </si>
-  <si>
-    <t>20.05.20264</t>
-  </si>
-  <si>
-    <t>20.05.20265</t>
-  </si>
-  <si>
-    <t>20.05.20266</t>
-  </si>
-  <si>
-    <t>20.05.20267</t>
-  </si>
-  <si>
-    <t>20.05.20268</t>
-  </si>
-  <si>
-    <t>20.05.20269</t>
-  </si>
-  <si>
-    <t>20.05.202610</t>
-  </si>
-  <si>
-    <t>20.05.202611</t>
-  </si>
-  <si>
-    <t>20.05.202612</t>
-  </si>
-  <si>
-    <t>20.05.202613</t>
-  </si>
-  <si>
-    <t>20.05.202614</t>
-  </si>
-  <si>
-    <t>20.05.202615</t>
-  </si>
-  <si>
-    <t>20.05.202616</t>
-  </si>
-  <si>
-    <t>20.05.202617</t>
-  </si>
-  <si>
-    <t>20.05.202618</t>
-  </si>
-  <si>
-    <t>20.05.202619</t>
-  </si>
-  <si>
-    <t>20.05.202620</t>
-  </si>
-  <si>
-    <t>20.05.202621</t>
-  </si>
-  <si>
-    <t>20.05.202622</t>
-  </si>
-  <si>
-    <t>20.05.202623</t>
-  </si>
-  <si>
-    <t>20.05.202624</t>
-  </si>
-  <si>
-    <t>20.05.202625</t>
-  </si>
-  <si>
-    <t>20.05.202626</t>
-  </si>
-  <si>
-    <t>20.05.202627</t>
-  </si>
-  <si>
-    <t>20.05.202628</t>
-  </si>
-  <si>
-    <t>20.05.202629</t>
-  </si>
-  <si>
-    <t>20.05.202630</t>
-  </si>
-  <si>
-    <t>20.05.202631</t>
-  </si>
-  <si>
-    <t>20.05.202632</t>
-  </si>
-  <si>
-    <t>20.05.202633</t>
-  </si>
-  <si>
-    <t>20.05.202634</t>
-  </si>
-  <si>
-    <t>20.05.202635</t>
-  </si>
-  <si>
-    <t>20.05.202636</t>
-  </si>
-  <si>
-    <t>20.05.202637</t>
-  </si>
-  <si>
-    <t>20.05.202638</t>
-  </si>
-  <si>
-    <t>20.05.202639</t>
-  </si>
-  <si>
-    <t>20.05.202640</t>
-  </si>
-  <si>
-    <t>20.05.202641</t>
-  </si>
-  <si>
-    <t>20.05.202642</t>
-  </si>
-  <si>
-    <t>20.05.202643</t>
-  </si>
-  <si>
-    <t>20.05.202644</t>
-  </si>
-  <si>
-    <t>20.05.202645</t>
-  </si>
-  <si>
-    <t>20.05.202646</t>
-  </si>
-  <si>
-    <t>20.05.202647</t>
-  </si>
-  <si>
-    <t>20.05.202648</t>
-  </si>
-  <si>
-    <t>20.05.202649</t>
-  </si>
-  <si>
-    <t>20.05.202650</t>
-  </si>
-  <si>
-    <t>20.05.202651</t>
-  </si>
-  <si>
-    <t>20.05.202652</t>
-  </si>
-  <si>
-    <t>20.05.202653</t>
-  </si>
-  <si>
-    <t>20.05.202654</t>
-  </si>
-  <si>
-    <t>20.05.202655</t>
-  </si>
-  <si>
-    <t>20.05.202656</t>
-  </si>
-  <si>
-    <t>20.05.202657</t>
-  </si>
-  <si>
-    <t>20.05.202658</t>
-  </si>
-  <si>
-    <t>20.05.202659</t>
-  </si>
-  <si>
-    <t>20.05.202660</t>
-  </si>
-  <si>
-    <t>20.05.202661</t>
-  </si>
-  <si>
-    <t>20.05.202662</t>
-  </si>
-  <si>
-    <t>20.05.202663</t>
-  </si>
-  <si>
-    <t>20.05.202664</t>
-  </si>
-  <si>
-    <t>20.05.202665</t>
-  </si>
-  <si>
-    <t>20.05.202666</t>
-  </si>
-  <si>
-    <t>20.05.202667</t>
-  </si>
-  <si>
-    <t>20.05.202668</t>
-  </si>
-  <si>
-    <t>20.05.202669</t>
-  </si>
-  <si>
-    <t>20.05.202670</t>
-  </si>
-  <si>
-    <t>20.05.202671</t>
-  </si>
-  <si>
-    <t>20.05.202672</t>
-  </si>
-  <si>
-    <t>20.05.202673</t>
-  </si>
-  <si>
-    <t>20.05.202674</t>
-  </si>
-  <si>
-    <t>20.05.202675</t>
-  </si>
-  <si>
-    <t>20.05.202676</t>
-  </si>
-  <si>
-    <t>20.05.202677</t>
-  </si>
-  <si>
-    <t>20.05.202678</t>
-  </si>
-  <si>
-    <t>20.05.202679</t>
-  </si>
-  <si>
-    <t>20.05.202680</t>
-  </si>
-  <si>
-    <t>20.05.202681</t>
-  </si>
-  <si>
-    <t>20.05.202682</t>
-  </si>
-  <si>
-    <t>20.05.202683</t>
-  </si>
-  <si>
-    <t>20.05.202684</t>
-  </si>
-  <si>
-    <t>20.05.202685</t>
-  </si>
-  <si>
-    <t>20.05.202686</t>
-  </si>
-  <si>
-    <t>20.05.202687</t>
-  </si>
-  <si>
-    <t>20.05.202688</t>
-  </si>
-  <si>
-    <t>20.05.202689</t>
-  </si>
-  <si>
-    <t>20.05.202690</t>
-  </si>
-  <si>
-    <t>20.05.202691</t>
-  </si>
-  <si>
-    <t>20.05.202692</t>
-  </si>
-  <si>
-    <t>20.05.202693</t>
-  </si>
-  <si>
-    <t>20.05.202694</t>
-  </si>
-  <si>
-    <t>20.05.202695</t>
-  </si>
-  <si>
-    <t>20.05.202696</t>
-  </si>
-  <si>
     <t>21.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>21.05.202696</t>
+  </si>
+  <si>
+    <t>22.05.20261</t>
+  </si>
+  <si>
+    <t>22.05.20262</t>
+  </si>
+  <si>
+    <t>22.05.20263</t>
+  </si>
+  <si>
+    <t>22.05.20264</t>
+  </si>
+  <si>
+    <t>22.05.20265</t>
+  </si>
+  <si>
+    <t>22.05.20266</t>
+  </si>
+  <si>
+    <t>22.05.20267</t>
+  </si>
+  <si>
+    <t>22.05.20268</t>
+  </si>
+  <si>
+    <t>22.05.20269</t>
+  </si>
+  <si>
+    <t>22.05.202610</t>
+  </si>
+  <si>
+    <t>22.05.202611</t>
+  </si>
+  <si>
+    <t>22.05.202612</t>
+  </si>
+  <si>
+    <t>22.05.202613</t>
+  </si>
+  <si>
+    <t>22.05.202614</t>
+  </si>
+  <si>
+    <t>22.05.202615</t>
+  </si>
+  <si>
+    <t>22.05.202616</t>
+  </si>
+  <si>
+    <t>22.05.202617</t>
+  </si>
+  <si>
+    <t>22.05.202618</t>
+  </si>
+  <si>
+    <t>22.05.202619</t>
+  </si>
+  <si>
+    <t>22.05.202620</t>
+  </si>
+  <si>
+    <t>22.05.202621</t>
+  </si>
+  <si>
+    <t>22.05.202622</t>
+  </si>
+  <si>
+    <t>22.05.202623</t>
+  </si>
+  <si>
+    <t>22.05.202624</t>
+  </si>
+  <si>
+    <t>22.05.202625</t>
+  </si>
+  <si>
+    <t>22.05.202626</t>
+  </si>
+  <si>
+    <t>22.05.202627</t>
+  </si>
+  <si>
+    <t>22.05.202628</t>
+  </si>
+  <si>
+    <t>22.05.202629</t>
+  </si>
+  <si>
+    <t>22.05.202630</t>
+  </si>
+  <si>
+    <t>22.05.202631</t>
+  </si>
+  <si>
+    <t>22.05.202632</t>
+  </si>
+  <si>
+    <t>22.05.202633</t>
+  </si>
+  <si>
+    <t>22.05.202634</t>
+  </si>
+  <si>
+    <t>22.05.202635</t>
+  </si>
+  <si>
+    <t>22.05.202636</t>
+  </si>
+  <si>
+    <t>22.05.202637</t>
+  </si>
+  <si>
+    <t>22.05.202638</t>
+  </si>
+  <si>
+    <t>22.05.202639</t>
+  </si>
+  <si>
+    <t>22.05.202640</t>
+  </si>
+  <si>
+    <t>22.05.202641</t>
+  </si>
+  <si>
+    <t>22.05.202642</t>
+  </si>
+  <si>
+    <t>22.05.202643</t>
+  </si>
+  <si>
+    <t>22.05.202644</t>
+  </si>
+  <si>
+    <t>22.05.202645</t>
+  </si>
+  <si>
+    <t>22.05.202646</t>
+  </si>
+  <si>
+    <t>22.05.202647</t>
+  </si>
+  <si>
+    <t>22.05.202648</t>
+  </si>
+  <si>
+    <t>22.05.202649</t>
+  </si>
+  <si>
+    <t>22.05.202650</t>
+  </si>
+  <si>
+    <t>22.05.202651</t>
+  </si>
+  <si>
+    <t>22.05.202652</t>
+  </si>
+  <si>
+    <t>22.05.202653</t>
+  </si>
+  <si>
+    <t>22.05.202654</t>
+  </si>
+  <si>
+    <t>22.05.202655</t>
+  </si>
+  <si>
+    <t>22.05.202656</t>
+  </si>
+  <si>
+    <t>22.05.202657</t>
+  </si>
+  <si>
+    <t>22.05.202658</t>
+  </si>
+  <si>
+    <t>22.05.202659</t>
+  </si>
+  <si>
+    <t>22.05.202660</t>
+  </si>
+  <si>
+    <t>22.05.202661</t>
+  </si>
+  <si>
+    <t>22.05.202662</t>
+  </si>
+  <si>
+    <t>22.05.202663</t>
+  </si>
+  <si>
+    <t>22.05.202664</t>
+  </si>
+  <si>
+    <t>22.05.202665</t>
+  </si>
+  <si>
+    <t>22.05.202666</t>
+  </si>
+  <si>
+    <t>22.05.202667</t>
+  </si>
+  <si>
+    <t>22.05.202668</t>
+  </si>
+  <si>
+    <t>22.05.202669</t>
+  </si>
+  <si>
+    <t>22.05.202670</t>
+  </si>
+  <si>
+    <t>22.05.202671</t>
+  </si>
+  <si>
+    <t>22.05.202672</t>
+  </si>
+  <si>
+    <t>22.05.202673</t>
+  </si>
+  <si>
+    <t>22.05.202674</t>
+  </si>
+  <si>
+    <t>22.05.202675</t>
+  </si>
+  <si>
+    <t>22.05.202676</t>
+  </si>
+  <si>
+    <t>22.05.202677</t>
+  </si>
+  <si>
+    <t>22.05.202678</t>
+  </si>
+  <si>
+    <t>22.05.202679</t>
+  </si>
+  <si>
+    <t>22.05.202680</t>
+  </si>
+  <si>
+    <t>22.05.202681</t>
+  </si>
+  <si>
+    <t>22.05.202682</t>
+  </si>
+  <si>
+    <t>22.05.202683</t>
+  </si>
+  <si>
+    <t>22.05.202684</t>
+  </si>
+  <si>
+    <t>22.05.202685</t>
+  </si>
+  <si>
+    <t>22.05.202686</t>
+  </si>
+  <si>
+    <t>22.05.202687</t>
+  </si>
+  <si>
+    <t>22.05.202688</t>
+  </si>
+  <si>
+    <t>22.05.202689</t>
+  </si>
+  <si>
+    <t>22.05.202690</t>
+  </si>
+  <si>
+    <t>22.05.202691</t>
+  </si>
+  <si>
+    <t>22.05.202692</t>
+  </si>
+  <si>
+    <t>22.05.202693</t>
+  </si>
+  <si>
+    <t>22.05.202694</t>
+  </si>
+  <si>
+    <t>22.05.202695</t>
+  </si>
+  <si>
+    <t>22.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46162.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46162.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46162.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46162.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B6">
-        <v>-34.296</v>
+        <v>-7.336</v>
       </c>
       <c r="C6">
-        <v>1467.586</v>
+        <v>949.943</v>
       </c>
       <c r="D6">
-        <v>1467.586</v>
+        <v>949.943</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46162.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B7">
-        <v>-42.822</v>
+        <v>3.595</v>
       </c>
       <c r="C7">
-        <v>2127.7</v>
+        <v>400</v>
       </c>
       <c r="D7">
-        <v>2127.7</v>
+        <v>400</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46162.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B8">
-        <v>-39.539</v>
+        <v>5.397</v>
       </c>
       <c r="C8">
-        <v>1427.006</v>
+        <v>274.467</v>
       </c>
       <c r="D8">
-        <v>1427.006</v>
+        <v>274.467</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46162.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B9">
-        <v>-17.656</v>
+        <v>21.265</v>
       </c>
       <c r="C9">
-        <v>1227.368</v>
+        <v>207.668</v>
       </c>
       <c r="D9">
-        <v>1227.368</v>
+        <v>207.668</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46162.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B10">
-        <v>-13.488</v>
+        <v>74.15600000000001</v>
       </c>
       <c r="C10">
-        <v>978.111</v>
+        <v>-677.771</v>
       </c>
       <c r="D10">
-        <v>978.111</v>
+        <v>-677.771</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46162.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B11">
-        <v>-5.646</v>
+        <v>18.611</v>
       </c>
       <c r="C11">
-        <v>889.938</v>
+        <v>-230.177</v>
       </c>
       <c r="D11">
-        <v>889.938</v>
+        <v>-230.177</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46162.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B12">
-        <v>11.284</v>
+        <v>10.986</v>
       </c>
       <c r="C12">
-        <v>334.94</v>
+        <v>122.113</v>
       </c>
       <c r="D12">
-        <v>334.94</v>
+        <v>122.113</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46162.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B13">
-        <v>46.916</v>
+        <v>10.63</v>
       </c>
       <c r="C13">
-        <v>362.713</v>
+        <v>164.987</v>
       </c>
       <c r="D13">
-        <v>362.713</v>
+        <v>164.987</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46162.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B14">
-        <v>49.243</v>
+        <v>31.922</v>
       </c>
       <c r="C14">
-        <v>270.173</v>
+        <v>256.163</v>
       </c>
       <c r="D14">
-        <v>270.173</v>
+        <v>256.163</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46162.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B15">
-        <v>64.97199999999999</v>
+        <v>15.413</v>
       </c>
       <c r="C15">
-        <v>-17.394</v>
+        <v>97.91500000000001</v>
       </c>
       <c r="D15">
-        <v>-17.394</v>
+        <v>97.91500000000001</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46162.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B16">
-        <v>57.006</v>
+        <v>16.558</v>
       </c>
       <c r="C16">
-        <v>67.955</v>
+        <v>52.185</v>
       </c>
       <c r="D16">
-        <v>67.955</v>
+        <v>52.185</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46162.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B17">
-        <v>71.03400000000001</v>
+        <v>26.543</v>
       </c>
       <c r="C17">
-        <v>183.272</v>
+        <v>102.069</v>
       </c>
       <c r="D17">
-        <v>183.272</v>
+        <v>102.069</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46162.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B18">
-        <v>42.949</v>
+        <v>48.332</v>
       </c>
       <c r="C18">
-        <v>280.814</v>
+        <v>258.136</v>
       </c>
       <c r="D18">
-        <v>280.814</v>
+        <v>258.136</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46162.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B19">
-        <v>38.842</v>
+        <v>12.537</v>
       </c>
       <c r="C19">
-        <v>260</v>
+        <v>187.102</v>
       </c>
       <c r="D19">
-        <v>260</v>
+        <v>187.102</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46162.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B20">
-        <v>43.697</v>
+        <v>37.009</v>
       </c>
       <c r="C20">
-        <v>122.574</v>
+        <v>180.721</v>
       </c>
       <c r="D20">
-        <v>122.574</v>
+        <v>180.721</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46162.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B21">
-        <v>56.445</v>
+        <v>41.747</v>
       </c>
       <c r="C21">
-        <v>-45.79</v>
+        <v>70.494</v>
       </c>
       <c r="D21">
-        <v>-45.79</v>
+        <v>70.494</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46162.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B22">
-        <v>115.429</v>
+        <v>46.538</v>
       </c>
       <c r="C22">
-        <v>127.849</v>
+        <v>131.914</v>
       </c>
       <c r="D22">
-        <v>127.849</v>
+        <v>131.914</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46162.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B23">
-        <v>103.766</v>
+        <v>21.219</v>
       </c>
       <c r="C23">
-        <v>350.743</v>
+        <v>261.944</v>
       </c>
       <c r="D23">
-        <v>350.743</v>
+        <v>261.944</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46162.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B24">
-        <v>113.255</v>
+        <v>-12.071</v>
       </c>
       <c r="C24">
-        <v>335.858</v>
+        <v>897.867</v>
       </c>
       <c r="D24">
-        <v>335.858</v>
+        <v>897.867</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46162.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B25">
-        <v>93.378</v>
+        <v>-35.771</v>
       </c>
       <c r="C25">
-        <v>2.794</v>
+        <v>998.724</v>
       </c>
       <c r="D25">
-        <v>2.794</v>
+        <v>998.724</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46162.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B26">
-        <v>54.456</v>
+        <v>-47.612</v>
       </c>
       <c r="C26">
-        <v>17.702</v>
+        <v>3992.366</v>
       </c>
       <c r="D26">
-        <v>17.702</v>
+        <v>3992.366</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46162.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B27">
-        <v>22.568</v>
+        <v>-38.998</v>
       </c>
       <c r="C27">
-        <v>2.384</v>
+        <v>2502.938</v>
       </c>
       <c r="D27">
-        <v>2.384</v>
+        <v>2502.938</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46162.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B28">
-        <v>5.983</v>
+        <v>-56.175</v>
       </c>
       <c r="C28">
-        <v>1.1</v>
+        <v>1220.667</v>
       </c>
       <c r="D28">
-        <v>1.1</v>
+        <v>1220.667</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46162.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B29">
-        <v>-30.78</v>
+        <v>-46.927</v>
       </c>
       <c r="C29">
-        <v>1028.036</v>
+        <v>1137.69</v>
       </c>
       <c r="D29">
-        <v>1028.036</v>
+        <v>1137.69</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46162.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B30">
-        <v>-104.104</v>
+        <v>-2.161</v>
       </c>
       <c r="C30">
-        <v>3453.373</v>
+        <v>1053.15</v>
       </c>
       <c r="D30">
-        <v>3453.373</v>
+        <v>1053.15</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46162.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B31">
-        <v>-124.267</v>
+        <v>24.184</v>
       </c>
       <c r="C31">
-        <v>6722.079</v>
+        <v>259.558</v>
       </c>
       <c r="D31">
-        <v>6722.079</v>
+        <v>259.558</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46162.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B32">
-        <v>-114.595</v>
+        <v>-8.269</v>
       </c>
       <c r="C32">
-        <v>3930.32</v>
+        <v>899.152</v>
       </c>
       <c r="D32">
-        <v>3930.32</v>
+        <v>899.152</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46162.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B33">
-        <v>-96.15900000000001</v>
+        <v>-19.458</v>
       </c>
       <c r="C33">
-        <v>1109.86</v>
+        <v>1065.536</v>
       </c>
       <c r="D33">
-        <v>1109.86</v>
+        <v>1065.536</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46162.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B34">
-        <v>-101.024</v>
+        <v>52.248</v>
       </c>
       <c r="C34">
-        <v>3129.508</v>
+        <v>-14.549</v>
       </c>
       <c r="D34">
-        <v>3129.508</v>
+        <v>-14.549</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46162.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B35">
-        <v>-65.11499999999999</v>
+        <v>-1.34</v>
       </c>
       <c r="C35">
-        <v>3185.071</v>
+        <v>876.279</v>
       </c>
       <c r="D35">
-        <v>3185.071</v>
+        <v>876.279</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46162.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B36">
-        <v>-27.075</v>
+        <v>-4.35</v>
       </c>
       <c r="C36">
-        <v>996.754</v>
+        <v>891.024</v>
       </c>
       <c r="D36">
-        <v>996.754</v>
+        <v>891.024</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46162.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B37">
-        <v>-3.324</v>
+        <v>-89.893</v>
       </c>
       <c r="C37">
-        <v>996.816</v>
+        <v>888.393</v>
       </c>
       <c r="D37">
-        <v>996.816</v>
+        <v>888.393</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46162.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B38">
-        <v>-58.386</v>
+        <v>-57.939</v>
       </c>
       <c r="C38">
-        <v>847.836</v>
+        <v>697.08</v>
       </c>
       <c r="D38">
-        <v>847.836</v>
+        <v>697.08</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46162.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B39">
-        <v>-31.749</v>
+        <v>-59.18</v>
       </c>
       <c r="C39">
-        <v>731.342</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>731.342</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46162.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B40">
-        <v>17.6</v>
+        <v>-44.895</v>
       </c>
       <c r="C40">
-        <v>-5.925</v>
+        <v>766.255</v>
       </c>
       <c r="D40">
-        <v>-5.925</v>
+        <v>766.255</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46162.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B41">
-        <v>5.156</v>
+        <v>-73.566</v>
       </c>
       <c r="C41">
-        <v>101.096</v>
+        <v>765.6660000000001</v>
       </c>
       <c r="D41">
-        <v>101.096</v>
+        <v>765.6660000000001</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46162.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B42">
-        <v>58.851</v>
+        <v>-55.06</v>
       </c>
       <c r="C42">
-        <v>82.589</v>
+        <v>554.65</v>
       </c>
       <c r="D42">
-        <v>82.589</v>
+        <v>554.65</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46162.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B43">
-        <v>54.228</v>
+        <v>-33.074</v>
       </c>
       <c r="C43">
-        <v>141.879</v>
+        <v>550.749</v>
       </c>
       <c r="D43">
-        <v>141.879</v>
+        <v>550.749</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46162.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B44">
-        <v>47.785</v>
+        <v>-5.467</v>
       </c>
       <c r="C44">
-        <v>17.922</v>
+        <v>550.65</v>
       </c>
       <c r="D44">
-        <v>17.922</v>
+        <v>550.65</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46162.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B45">
-        <v>22.001</v>
+        <v>-11.176</v>
       </c>
       <c r="C45">
-        <v>-1.761</v>
+        <v>552.6900000000001</v>
       </c>
       <c r="D45">
-        <v>-1.761</v>
+        <v>552.6900000000001</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46162.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B46">
-        <v>-27.03</v>
+        <v>107.787</v>
       </c>
       <c r="C46">
-        <v>576.14</v>
+        <v>-6147.741</v>
       </c>
       <c r="D46">
-        <v>576.14</v>
+        <v>-6147.741</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46162.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B47">
-        <v>-67.968</v>
+        <v>26.042</v>
       </c>
       <c r="C47">
-        <v>598.247</v>
+        <v>293</v>
       </c>
       <c r="D47">
-        <v>598.247</v>
+        <v>293</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46162.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B48">
-        <v>-126.99</v>
+        <v>34.084</v>
       </c>
       <c r="C48">
-        <v>602.353</v>
+        <v>324.677</v>
       </c>
       <c r="D48">
-        <v>602.353</v>
+        <v>324.677</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46162.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B49">
-        <v>-90.70399999999999</v>
+        <v>17.038</v>
       </c>
       <c r="C49">
-        <v>572.187</v>
+        <v>16.744</v>
       </c>
       <c r="D49">
-        <v>572.187</v>
+        <v>16.744</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46162.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B50">
-        <v>-73.17100000000001</v>
+        <v>29.288</v>
       </c>
       <c r="C50">
-        <v>772.615</v>
+        <v>-53.404</v>
       </c>
       <c r="D50">
-        <v>772.615</v>
+        <v>-53.404</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46162.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B51">
-        <v>-79.652</v>
+        <v>39.191</v>
       </c>
       <c r="C51">
-        <v>642.875</v>
+        <v>73.535</v>
       </c>
       <c r="D51">
-        <v>642.875</v>
+        <v>73.535</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46162.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B52">
-        <v>-44.031</v>
+        <v>-17.118</v>
       </c>
       <c r="C52">
-        <v>592.534</v>
+        <v>633.963</v>
       </c>
       <c r="D52">
-        <v>592.534</v>
+        <v>633.963</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46162.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B53">
-        <v>-51.703</v>
+        <v>-68.461</v>
       </c>
       <c r="C53">
-        <v>592.566</v>
+        <v>786.564</v>
       </c>
       <c r="D53">
-        <v>592.566</v>
+        <v>786.564</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46162.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B54">
-        <v>-81.56699999999999</v>
+        <v>-57.855</v>
       </c>
       <c r="C54">
-        <v>1571.461</v>
+        <v>809.064</v>
       </c>
       <c r="D54">
-        <v>1571.461</v>
+        <v>809.064</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46162.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B55">
-        <v>-89.98</v>
+        <v>-105.274</v>
       </c>
       <c r="C55">
-        <v>772.268</v>
+        <v>1231.039</v>
       </c>
       <c r="D55">
-        <v>772.268</v>
+        <v>1231.039</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46162.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B56">
-        <v>-57.439</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>665.097</v>
+        <v>1308.511</v>
       </c>
       <c r="D56">
-        <v>665.097</v>
+        <v>1308.511</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46162.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B57">
-        <v>-24.31</v>
+        <v>-152.376</v>
       </c>
       <c r="C57">
-        <v>609.9880000000001</v>
+        <v>698.048</v>
       </c>
       <c r="D57">
-        <v>609.9880000000001</v>
+        <v>698.048</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46162.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B58">
-        <v>3.179</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>299.512</v>
+        <v>499.449</v>
       </c>
       <c r="D58">
-        <v>299.512</v>
+        <v>499.449</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46162.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B59">
-        <v>50.344</v>
+        <v>-2.242</v>
       </c>
       <c r="C59">
-        <v>358.971</v>
+        <v>499.44</v>
       </c>
       <c r="D59">
-        <v>358.971</v>
+        <v>499.44</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46162.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B60">
-        <v>102.336</v>
+        <v>56.874</v>
       </c>
       <c r="C60">
-        <v>281.115</v>
+        <v>-2535.806</v>
       </c>
       <c r="D60">
-        <v>281.115</v>
+        <v>-2535.806</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46162.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B61">
-        <v>116.79</v>
+        <v>114.999</v>
       </c>
       <c r="C61">
-        <v>-1702.49</v>
+        <v>-536.087</v>
       </c>
       <c r="D61">
-        <v>-1702.49</v>
+        <v>-536.087</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46162.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B62">
-        <v>81.482</v>
+        <v>160.77</v>
       </c>
       <c r="C62">
-        <v>135.037</v>
+        <v>89.86499999999999</v>
       </c>
       <c r="D62">
-        <v>135.037</v>
+        <v>89.86499999999999</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46162.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B63">
-        <v>77.753</v>
+        <v>118.001</v>
       </c>
       <c r="C63">
-        <v>305.027</v>
+        <v>-6482.078</v>
       </c>
       <c r="D63">
-        <v>305.027</v>
+        <v>-6482.078</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46162.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B64">
-        <v>107.415</v>
+        <v>132.862</v>
       </c>
       <c r="C64">
-        <v>-57.301</v>
+        <v>-3859.042</v>
       </c>
       <c r="D64">
-        <v>-57.301</v>
+        <v>-3859.042</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46162.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B65">
-        <v>105.585</v>
+        <v>53.908</v>
       </c>
       <c r="C65">
-        <v>6.005</v>
+        <v>-158.313</v>
       </c>
       <c r="D65">
-        <v>6.005</v>
+        <v>-158.313</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46162.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B66">
-        <v>19.017</v>
+        <v>-4.588</v>
       </c>
       <c r="C66">
-        <v>-21.541</v>
+        <v>699</v>
       </c>
       <c r="D66">
-        <v>-21.541</v>
+        <v>699</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46162.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B67">
-        <v>17.535</v>
+        <v>63.091</v>
       </c>
       <c r="C67">
-        <v>346.4</v>
+        <v>0.54</v>
       </c>
       <c r="D67">
-        <v>346.4</v>
+        <v>0.54</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46162.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B68">
-        <v>94.364</v>
+        <v>76.09399999999999</v>
       </c>
       <c r="C68">
-        <v>288.024</v>
+        <v>12.32</v>
       </c>
       <c r="D68">
-        <v>288.024</v>
+        <v>12.32</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46162.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B69">
-        <v>103.921</v>
+        <v>72.97199999999999</v>
       </c>
       <c r="C69">
-        <v>273.446</v>
+        <v>-1.226</v>
       </c>
       <c r="D69">
-        <v>273.446</v>
+        <v>-1.226</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46162.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B70">
-        <v>127.021</v>
+        <v>106.962</v>
       </c>
       <c r="C70">
-        <v>-179.28</v>
+        <v>5.372</v>
       </c>
       <c r="D70">
-        <v>-179.28</v>
+        <v>5.372</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46162.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B71">
-        <v>114.012</v>
+        <v>98.715</v>
       </c>
       <c r="C71">
-        <v>0.885</v>
+        <v>-18.056</v>
       </c>
       <c r="D71">
-        <v>0.885</v>
+        <v>-18.056</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46162.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B72">
-        <v>112.283</v>
+        <v>77.101</v>
       </c>
       <c r="C72">
-        <v>-12.145</v>
+        <v>-9.542</v>
       </c>
       <c r="D72">
-        <v>-12.145</v>
+        <v>-9.542</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46162.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B73">
-        <v>138.25</v>
+        <v>73.22199999999999</v>
       </c>
       <c r="C73">
-        <v>6.345</v>
+        <v>-5.247</v>
       </c>
       <c r="D73">
-        <v>6.345</v>
+        <v>-5.247</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46162.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B74">
-        <v>125.693</v>
+        <v>119.299</v>
       </c>
       <c r="C74">
-        <v>10.459</v>
+        <v>-3360.637</v>
       </c>
       <c r="D74">
-        <v>10.459</v>
+        <v>-3360.637</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46162.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B75">
-        <v>114.539</v>
+        <v>61.278</v>
       </c>
       <c r="C75">
-        <v>1.673</v>
+        <v>1.967</v>
       </c>
       <c r="D75">
-        <v>1.673</v>
+        <v>1.967</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46162.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B76">
-        <v>32.627</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="C76">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D76">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46162.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B77">
-        <v>35.937</v>
+        <v>66.628</v>
       </c>
       <c r="C77">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46162.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B78">
-        <v>47.658</v>
+        <v>70.312</v>
       </c>
       <c r="C78">
-        <v>14.632</v>
+        <v>7.807</v>
       </c>
       <c r="D78">
-        <v>14.632</v>
+        <v>7.807</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46162.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B79">
-        <v>42.245</v>
+        <v>67.709</v>
       </c>
       <c r="C79">
-        <v>3.816</v>
+        <v>21.448</v>
       </c>
       <c r="D79">
-        <v>3.816</v>
+        <v>21.448</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46162.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B80">
-        <v>2.142</v>
+        <v>74.137</v>
       </c>
       <c r="C80">
-        <v>263.498</v>
+        <v>3.516</v>
       </c>
       <c r="D80">
-        <v>263.498</v>
+        <v>3.516</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46162.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B81">
-        <v>13.188</v>
+        <v>87.098</v>
       </c>
       <c r="C81">
-        <v>288.704</v>
+        <v>2.634</v>
       </c>
       <c r="D81">
-        <v>288.704</v>
+        <v>2.634</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46162.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B82">
-        <v>-34.097</v>
+        <v>84.348</v>
       </c>
       <c r="C82">
-        <v>1460.639</v>
+        <v>2.269</v>
       </c>
       <c r="D82">
-        <v>1460.639</v>
+        <v>2.269</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46162.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B83">
-        <v>-39.418</v>
+        <v>95.735</v>
       </c>
       <c r="C83">
-        <v>1353.292</v>
+        <v>13.317</v>
       </c>
       <c r="D83">
-        <v>1353.292</v>
+        <v>13.317</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46162.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B84">
-        <v>-44.261</v>
+        <v>111.685</v>
       </c>
       <c r="C84">
-        <v>956.809</v>
+        <v>1.984</v>
       </c>
       <c r="D84">
-        <v>956.809</v>
+        <v>1.984</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46162.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B85">
-        <v>0.463</v>
+        <v>126.313</v>
       </c>
       <c r="C85">
-        <v>121.147</v>
+        <v>3.795</v>
       </c>
       <c r="D85">
-        <v>121.147</v>
+        <v>3.795</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46162.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B86">
-        <v>-25.48</v>
+        <v>26.285</v>
       </c>
       <c r="C86">
-        <v>1016.584</v>
+        <v>0.6</v>
       </c>
       <c r="D86">
-        <v>1016.584</v>
+        <v>0.6</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46162.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B87">
-        <v>-8.191000000000001</v>
+        <v>25.531</v>
       </c>
       <c r="C87">
-        <v>1096.38</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>1096.38</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46162.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B88">
-        <v>2.81</v>
+        <v>31.465</v>
       </c>
       <c r="C88">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46162.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B89">
-        <v>40.442</v>
+        <v>72.422</v>
       </c>
       <c r="C89">
-        <v>-1090.607</v>
+        <v>7.075</v>
       </c>
       <c r="D89">
-        <v>-1090.607</v>
+        <v>7.075</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46162.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B90">
-        <v>22.499</v>
+        <v>77.017</v>
       </c>
       <c r="C90">
-        <v>-317.049</v>
+        <v>275.359</v>
       </c>
       <c r="D90">
-        <v>-317.049</v>
+        <v>275.359</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46162.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B91">
-        <v>22.366</v>
+        <v>92.042</v>
       </c>
       <c r="C91">
-        <v>254.202</v>
+        <v>279.825</v>
       </c>
       <c r="D91">
-        <v>254.202</v>
+        <v>279.825</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46162.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B92">
-        <v>13.728</v>
+        <v>58.818</v>
       </c>
       <c r="C92">
-        <v>179.479</v>
+        <v>276.673</v>
       </c>
       <c r="D92">
-        <v>179.479</v>
+        <v>276.673</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46162.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B93">
-        <v>27.49</v>
+        <v>44.298</v>
       </c>
       <c r="C93">
-        <v>-57.571</v>
+        <v>270.531</v>
       </c>
       <c r="D93">
-        <v>-57.571</v>
+        <v>270.531</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46162.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B94">
-        <v>31.925</v>
+        <v>47.425</v>
       </c>
       <c r="C94">
-        <v>153.453</v>
+        <v>294.598</v>
       </c>
       <c r="D94">
-        <v>153.453</v>
+        <v>294.598</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46162.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B95">
-        <v>38.77</v>
+        <v>59.118</v>
       </c>
       <c r="C95">
-        <v>-18.118</v>
+        <v>33.073</v>
       </c>
       <c r="D95">
-        <v>-18.118</v>
+        <v>33.073</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46162.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B96">
-        <v>25.327</v>
+        <v>18.806</v>
       </c>
       <c r="C96">
-        <v>106.975</v>
+        <v>131.561</v>
       </c>
       <c r="D96">
-        <v>106.975</v>
+        <v>131.561</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46162.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B97">
-        <v>21.299</v>
+        <v>26.403</v>
       </c>
       <c r="C97">
-        <v>-36.204</v>
+        <v>-48.271</v>
       </c>
       <c r="D97">
-        <v>-36.204</v>
+        <v>-48.271</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B98">
-        <v>31.31</v>
+        <v>-4.361</v>
       </c>
       <c r="C98">
-        <v>174.729</v>
+        <v>1009.4</v>
       </c>
       <c r="D98">
-        <v>174.729</v>
+        <v>1009.4</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B99">
-        <v>0.852</v>
+        <v>-9.566000000000001</v>
       </c>
       <c r="C99">
-        <v>271.53</v>
+        <v>899.1559999999999</v>
       </c>
       <c r="D99">
-        <v>271.53</v>
+        <v>899.1559999999999</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B100">
-        <v>10.407</v>
+        <v>-14.996</v>
       </c>
       <c r="C100">
-        <v>253.534</v>
+        <v>897.428</v>
       </c>
       <c r="D100">
-        <v>253.534</v>
+        <v>897.428</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B101">
-        <v>13.68</v>
+        <v>-2.525</v>
       </c>
       <c r="C101">
-        <v>273.965</v>
+        <v>893.159</v>
       </c>
       <c r="D101">
-        <v>273.965</v>
+        <v>893.159</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B102">
-        <v>-7.336</v>
+        <v>3.927</v>
       </c>
       <c r="C102">
-        <v>949.943</v>
+        <v>273.5</v>
       </c>
       <c r="D102">
-        <v>949.943</v>
+        <v>273.5</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B103">
-        <v>3.595</v>
+        <v>-11.613</v>
       </c>
       <c r="C103">
-        <v>400</v>
+        <v>898.232</v>
       </c>
       <c r="D103">
-        <v>400</v>
+        <v>898.232</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B104">
-        <v>5.397</v>
+        <v>1.642</v>
       </c>
       <c r="C104">
-        <v>274.467</v>
+        <v>899</v>
       </c>
       <c r="D104">
-        <v>274.467</v>
+        <v>899</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B105">
-        <v>21.265</v>
+        <v>16.56</v>
       </c>
       <c r="C105">
-        <v>207.668</v>
+        <v>275.122</v>
       </c>
       <c r="D105">
-        <v>207.668</v>
+        <v>275.122</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B106">
-        <v>74.15600000000001</v>
+        <v>35.33</v>
       </c>
       <c r="C106">
-        <v>-677.771</v>
+        <v>298.795</v>
       </c>
       <c r="D106">
-        <v>-677.771</v>
+        <v>298.795</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B107">
-        <v>18.611</v>
+        <v>21.087</v>
       </c>
       <c r="C107">
-        <v>-230.177</v>
+        <v>271.878</v>
       </c>
       <c r="D107">
-        <v>-230.177</v>
+        <v>271.878</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B108">
-        <v>10.986</v>
+        <v>12.671</v>
       </c>
       <c r="C108">
-        <v>122.113</v>
+        <v>241.669</v>
       </c>
       <c r="D108">
-        <v>122.113</v>
+        <v>241.669</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B109">
-        <v>10.63</v>
+        <v>-4.25</v>
       </c>
       <c r="C109">
-        <v>164.987</v>
+        <v>898.824</v>
       </c>
       <c r="D109">
-        <v>164.987</v>
+        <v>898.824</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B110">
-        <v>31.922</v>
+        <v>27.282</v>
       </c>
       <c r="C110">
-        <v>256.163</v>
+        <v>-22.455</v>
       </c>
       <c r="D110">
-        <v>256.163</v>
+        <v>-22.455</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B111">
-        <v>15.413</v>
+        <v>16.57</v>
       </c>
       <c r="C111">
-        <v>97.91500000000001</v>
+        <v>41.962</v>
       </c>
       <c r="D111">
-        <v>97.91500000000001</v>
+        <v>41.962</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B112">
-        <v>16.558</v>
+        <v>-3.02</v>
       </c>
       <c r="C112">
-        <v>52.185</v>
+        <v>885.8</v>
       </c>
       <c r="D112">
-        <v>52.185</v>
+        <v>885.8</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B113">
-        <v>26.543</v>
+        <v>-10.328</v>
       </c>
       <c r="C113">
-        <v>102.069</v>
+        <v>876.446</v>
       </c>
       <c r="D113">
-        <v>102.069</v>
+        <v>876.446</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B114">
-        <v>48.332</v>
+        <v>9.244</v>
       </c>
       <c r="C114">
-        <v>258.136</v>
+        <v>257.601</v>
       </c>
       <c r="D114">
-        <v>258.136</v>
+        <v>257.601</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B115">
-        <v>12.537</v>
+        <v>-0.323</v>
       </c>
       <c r="C115">
-        <v>187.102</v>
+        <v>898.386</v>
       </c>
       <c r="D115">
-        <v>187.102</v>
+        <v>898.386</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B116">
-        <v>37.009</v>
+        <v>-10.957</v>
       </c>
       <c r="C116">
-        <v>180.721</v>
+        <v>898.42</v>
       </c>
       <c r="D116">
-        <v>180.721</v>
+        <v>898.42</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B117">
-        <v>41.747</v>
+        <v>-10.85</v>
       </c>
       <c r="C117">
-        <v>70.494</v>
+        <v>909.184</v>
       </c>
       <c r="D117">
-        <v>70.494</v>
+        <v>909.184</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B118">
-        <v>46.538</v>
+        <v>3.567</v>
       </c>
       <c r="C118">
-        <v>131.914</v>
+        <v>1032.723</v>
       </c>
       <c r="D118">
-        <v>131.914</v>
+        <v>1032.723</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B119">
-        <v>21.219</v>
+        <v>-6.647</v>
       </c>
       <c r="C119">
-        <v>261.944</v>
+        <v>925.575</v>
       </c>
       <c r="D119">
-        <v>261.944</v>
+        <v>925.575</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B120">
-        <v>-12.071</v>
+        <v>-34.273</v>
       </c>
       <c r="C120">
-        <v>897.867</v>
+        <v>924.845</v>
       </c>
       <c r="D120">
-        <v>897.867</v>
+        <v>924.845</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B121">
-        <v>-35.771</v>
+        <v>-34.033</v>
       </c>
       <c r="C121">
-        <v>998.724</v>
+        <v>925.224</v>
       </c>
       <c r="D121">
-        <v>998.724</v>
+        <v>925.224</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B122">
-        <v>-47.612</v>
+        <v>-0.108</v>
       </c>
       <c r="C122">
-        <v>3992.366</v>
+        <v>1079.135</v>
       </c>
       <c r="D122">
-        <v>3992.366</v>
+        <v>1079.135</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B123">
-        <v>-38.998</v>
+        <v>-26.345</v>
       </c>
       <c r="C123">
-        <v>2502.938</v>
+        <v>982.17</v>
       </c>
       <c r="D123">
-        <v>2502.938</v>
+        <v>982.17</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B124">
-        <v>-56.175</v>
+        <v>-24.328</v>
       </c>
       <c r="C124">
-        <v>1220.667</v>
+        <v>947.234</v>
       </c>
       <c r="D124">
-        <v>1220.667</v>
+        <v>947.234</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B125">
-        <v>-46.927</v>
+        <v>-45.203</v>
       </c>
       <c r="C125">
-        <v>1137.69</v>
+        <v>1859.176</v>
       </c>
       <c r="D125">
-        <v>1137.69</v>
+        <v>1859.176</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B126">
-        <v>-2.161</v>
+        <v>-46.009</v>
       </c>
       <c r="C126">
-        <v>1053.15</v>
+        <v>1163.461</v>
       </c>
       <c r="D126">
-        <v>1053.15</v>
+        <v>1163.461</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B127">
-        <v>24.184</v>
+        <v>-83.779</v>
       </c>
       <c r="C127">
-        <v>259.558</v>
+        <v>1985.174</v>
       </c>
       <c r="D127">
-        <v>259.558</v>
+        <v>1985.174</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B128">
-        <v>-8.269</v>
+        <v>-108.139</v>
       </c>
       <c r="C128">
-        <v>899.152</v>
+        <v>3149.064</v>
       </c>
       <c r="D128">
-        <v>899.152</v>
+        <v>3149.064</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B129">
-        <v>-19.458</v>
+        <v>-61.647</v>
       </c>
       <c r="C129">
-        <v>1065.536</v>
+        <v>1183.113</v>
       </c>
       <c r="D129">
-        <v>1065.536</v>
+        <v>1183.113</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B130">
-        <v>52.248</v>
+        <v>-35.381</v>
       </c>
       <c r="C130">
-        <v>-14.549</v>
+        <v>1099.616</v>
       </c>
       <c r="D130">
-        <v>-14.549</v>
+        <v>1099.616</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B131">
-        <v>-1.34</v>
+        <v>-41.944</v>
       </c>
       <c r="C131">
-        <v>876.279</v>
+        <v>1100.166</v>
       </c>
       <c r="D131">
-        <v>876.279</v>
+        <v>1100.166</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B132">
-        <v>-4.35</v>
+        <v>-94.14400000000001</v>
       </c>
       <c r="C132">
-        <v>891.024</v>
+        <v>1164.678</v>
       </c>
       <c r="D132">
-        <v>891.024</v>
+        <v>1164.678</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B133">
-        <v>-89.893</v>
+        <v>-57.253</v>
       </c>
       <c r="C133">
-        <v>888.393</v>
+        <v>1084.975</v>
       </c>
       <c r="D133">
-        <v>888.393</v>
+        <v>1084.975</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B134">
-        <v>-57.939</v>
+        <v>-73.89400000000001</v>
       </c>
       <c r="C134">
-        <v>697.08</v>
+        <v>911.2140000000001</v>
       </c>
       <c r="D134">
-        <v>697.08</v>
+        <v>911.2140000000001</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B135">
-        <v>-59.18</v>
+        <v>19.707</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>385.634</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>385.634</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B136">
-        <v>-44.895</v>
+        <v>21.381</v>
       </c>
       <c r="C136">
-        <v>766.255</v>
+        <v>401</v>
       </c>
       <c r="D136">
-        <v>766.255</v>
+        <v>401</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B137">
-        <v>-73.566</v>
+        <v>8.913</v>
       </c>
       <c r="C137">
-        <v>765.6660000000001</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>765.6660000000001</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B138">
-        <v>-55.06</v>
+        <v>-10.914</v>
       </c>
       <c r="C138">
-        <v>554.65</v>
+        <v>714.578</v>
       </c>
       <c r="D138">
-        <v>554.65</v>
+        <v>714.578</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B139">
-        <v>-33.074</v>
+        <v>2.711</v>
       </c>
       <c r="C139">
-        <v>550.749</v>
+        <v>401</v>
       </c>
       <c r="D139">
-        <v>550.749</v>
+        <v>401</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B140">
-        <v>-5.467</v>
+        <v>-54.363</v>
       </c>
       <c r="C140">
-        <v>550.65</v>
+        <v>755.428</v>
       </c>
       <c r="D140">
-        <v>550.65</v>
+        <v>755.428</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B141">
-        <v>-11.176</v>
+        <v>-35.596</v>
       </c>
       <c r="C141">
-        <v>552.6900000000001</v>
+        <v>1213.064</v>
       </c>
       <c r="D141">
-        <v>552.6900000000001</v>
+        <v>1213.064</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B142">
-        <v>107.787</v>
+        <v>3.801</v>
       </c>
       <c r="C142">
-        <v>-6147.741</v>
+        <v>31.143</v>
       </c>
       <c r="D142">
-        <v>-6147.741</v>
+        <v>31.143</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B143">
-        <v>26.042</v>
+        <v>7.867</v>
       </c>
       <c r="C143">
-        <v>293</v>
+        <v>75.93899999999999</v>
       </c>
       <c r="D143">
-        <v>293</v>
+        <v>75.93899999999999</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B144">
-        <v>34.084</v>
+        <v>36.201</v>
       </c>
       <c r="C144">
-        <v>324.677</v>
+        <v>-126.494</v>
       </c>
       <c r="D144">
-        <v>324.677</v>
+        <v>-126.494</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B145">
-        <v>17.038</v>
+        <v>34.484</v>
       </c>
       <c r="C145">
-        <v>16.744</v>
+        <v>-250.341</v>
       </c>
       <c r="D145">
-        <v>16.744</v>
+        <v>-250.341</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B146">
-        <v>29.288</v>
+        <v>12.325</v>
       </c>
       <c r="C146">
-        <v>-53.404</v>
+        <v>-189.078</v>
       </c>
       <c r="D146">
-        <v>-53.404</v>
+        <v>-189.078</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B147">
-        <v>39.191</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>73.535</v>
+        <v>0</v>
       </c>
       <c r="D147">
-        <v>73.535</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B148">
-        <v>-17.118</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>633.963</v>
+        <v>0</v>
       </c>
       <c r="D148">
-        <v>633.963</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.05.20261</t>
-  </si>
-  <si>
-    <t>21.05.20262</t>
-  </si>
-  <si>
-    <t>21.05.20263</t>
-  </si>
-  <si>
-    <t>21.05.20264</t>
-  </si>
-  <si>
-    <t>21.05.20265</t>
-  </si>
-  <si>
-    <t>21.05.20266</t>
-  </si>
-  <si>
-    <t>21.05.20267</t>
-  </si>
-  <si>
-    <t>21.05.20268</t>
-  </si>
-  <si>
-    <t>21.05.20269</t>
-  </si>
-  <si>
-    <t>21.05.202610</t>
-  </si>
-  <si>
-    <t>21.05.202611</t>
-  </si>
-  <si>
-    <t>21.05.202612</t>
-  </si>
-  <si>
-    <t>21.05.202613</t>
-  </si>
-  <si>
-    <t>21.05.202614</t>
-  </si>
-  <si>
-    <t>21.05.202615</t>
-  </si>
-  <si>
-    <t>21.05.202616</t>
-  </si>
-  <si>
-    <t>21.05.202617</t>
-  </si>
-  <si>
-    <t>21.05.202618</t>
-  </si>
-  <si>
-    <t>21.05.202619</t>
-  </si>
-  <si>
-    <t>21.05.202620</t>
-  </si>
-  <si>
-    <t>21.05.202621</t>
-  </si>
-  <si>
-    <t>21.05.202622</t>
-  </si>
-  <si>
-    <t>21.05.202623</t>
-  </si>
-  <si>
-    <t>21.05.202624</t>
-  </si>
-  <si>
-    <t>21.05.202625</t>
-  </si>
-  <si>
-    <t>21.05.202626</t>
-  </si>
-  <si>
-    <t>21.05.202627</t>
-  </si>
-  <si>
-    <t>21.05.202628</t>
-  </si>
-  <si>
-    <t>21.05.202629</t>
-  </si>
-  <si>
-    <t>21.05.202630</t>
-  </si>
-  <si>
-    <t>21.05.202631</t>
-  </si>
-  <si>
-    <t>21.05.202632</t>
-  </si>
-  <si>
-    <t>21.05.202633</t>
-  </si>
-  <si>
-    <t>21.05.202634</t>
-  </si>
-  <si>
-    <t>21.05.202635</t>
-  </si>
-  <si>
-    <t>21.05.202636</t>
-  </si>
-  <si>
-    <t>21.05.202637</t>
-  </si>
-  <si>
-    <t>21.05.202638</t>
-  </si>
-  <si>
-    <t>21.05.202639</t>
-  </si>
-  <si>
-    <t>21.05.202640</t>
-  </si>
-  <si>
-    <t>21.05.202641</t>
-  </si>
-  <si>
-    <t>21.05.202642</t>
-  </si>
-  <si>
-    <t>21.05.202643</t>
-  </si>
-  <si>
-    <t>21.05.202644</t>
-  </si>
-  <si>
-    <t>21.05.202645</t>
-  </si>
-  <si>
-    <t>21.05.202646</t>
-  </si>
-  <si>
-    <t>21.05.202647</t>
-  </si>
-  <si>
-    <t>21.05.202648</t>
-  </si>
-  <si>
-    <t>21.05.202649</t>
-  </si>
-  <si>
-    <t>21.05.202650</t>
-  </si>
-  <si>
-    <t>21.05.202651</t>
-  </si>
-  <si>
-    <t>21.05.202652</t>
-  </si>
-  <si>
-    <t>21.05.202653</t>
-  </si>
-  <si>
-    <t>21.05.202654</t>
-  </si>
-  <si>
-    <t>21.05.202655</t>
-  </si>
-  <si>
-    <t>21.05.202656</t>
-  </si>
-  <si>
-    <t>21.05.202657</t>
-  </si>
-  <si>
-    <t>21.05.202658</t>
-  </si>
-  <si>
-    <t>21.05.202659</t>
-  </si>
-  <si>
-    <t>21.05.202660</t>
-  </si>
-  <si>
-    <t>21.05.202661</t>
-  </si>
-  <si>
-    <t>21.05.202662</t>
-  </si>
-  <si>
-    <t>21.05.202663</t>
-  </si>
-  <si>
-    <t>21.05.202664</t>
-  </si>
-  <si>
-    <t>21.05.202665</t>
-  </si>
-  <si>
-    <t>21.05.202666</t>
-  </si>
-  <si>
-    <t>21.05.202667</t>
-  </si>
-  <si>
-    <t>21.05.202668</t>
-  </si>
-  <si>
-    <t>21.05.202669</t>
-  </si>
-  <si>
-    <t>21.05.202670</t>
-  </si>
-  <si>
-    <t>21.05.202671</t>
-  </si>
-  <si>
-    <t>21.05.202672</t>
-  </si>
-  <si>
-    <t>21.05.202673</t>
-  </si>
-  <si>
-    <t>21.05.202674</t>
-  </si>
-  <si>
-    <t>21.05.202675</t>
-  </si>
-  <si>
-    <t>21.05.202676</t>
-  </si>
-  <si>
-    <t>21.05.202677</t>
-  </si>
-  <si>
-    <t>21.05.202678</t>
-  </si>
-  <si>
-    <t>21.05.202679</t>
-  </si>
-  <si>
-    <t>21.05.202680</t>
-  </si>
-  <si>
-    <t>21.05.202681</t>
-  </si>
-  <si>
-    <t>21.05.202682</t>
-  </si>
-  <si>
-    <t>21.05.202683</t>
-  </si>
-  <si>
-    <t>21.05.202684</t>
-  </si>
-  <si>
-    <t>21.05.202685</t>
-  </si>
-  <si>
-    <t>21.05.202686</t>
-  </si>
-  <si>
-    <t>21.05.202687</t>
-  </si>
-  <si>
-    <t>21.05.202688</t>
-  </si>
-  <si>
-    <t>21.05.202689</t>
-  </si>
-  <si>
-    <t>21.05.202690</t>
-  </si>
-  <si>
-    <t>21.05.202691</t>
-  </si>
-  <si>
-    <t>21.05.202692</t>
-  </si>
-  <si>
-    <t>21.05.202693</t>
-  </si>
-  <si>
-    <t>21.05.202694</t>
-  </si>
-  <si>
-    <t>21.05.202695</t>
-  </si>
-  <si>
-    <t>21.05.202696</t>
-  </si>
-  <si>
     <t>22.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,870 @@
   </si>
   <si>
     <t>22.05.202696</t>
+  </si>
+  <si>
+    <t>23.05.20261</t>
+  </si>
+  <si>
+    <t>23.05.20262</t>
+  </si>
+  <si>
+    <t>23.05.20263</t>
+  </si>
+  <si>
+    <t>23.05.20264</t>
+  </si>
+  <si>
+    <t>23.05.20265</t>
+  </si>
+  <si>
+    <t>23.05.20266</t>
+  </si>
+  <si>
+    <t>23.05.20267</t>
+  </si>
+  <si>
+    <t>23.05.20268</t>
+  </si>
+  <si>
+    <t>23.05.20269</t>
+  </si>
+  <si>
+    <t>23.05.202610</t>
+  </si>
+  <si>
+    <t>23.05.202611</t>
+  </si>
+  <si>
+    <t>23.05.202612</t>
+  </si>
+  <si>
+    <t>23.05.202613</t>
+  </si>
+  <si>
+    <t>23.05.202614</t>
+  </si>
+  <si>
+    <t>23.05.202615</t>
+  </si>
+  <si>
+    <t>23.05.202616</t>
+  </si>
+  <si>
+    <t>23.05.202617</t>
+  </si>
+  <si>
+    <t>23.05.202618</t>
+  </si>
+  <si>
+    <t>23.05.202619</t>
+  </si>
+  <si>
+    <t>23.05.202620</t>
+  </si>
+  <si>
+    <t>23.05.202621</t>
+  </si>
+  <si>
+    <t>23.05.202622</t>
+  </si>
+  <si>
+    <t>23.05.202623</t>
+  </si>
+  <si>
+    <t>23.05.202624</t>
+  </si>
+  <si>
+    <t>23.05.202625</t>
+  </si>
+  <si>
+    <t>23.05.202626</t>
+  </si>
+  <si>
+    <t>23.05.202627</t>
+  </si>
+  <si>
+    <t>23.05.202628</t>
+  </si>
+  <si>
+    <t>23.05.202629</t>
+  </si>
+  <si>
+    <t>23.05.202630</t>
+  </si>
+  <si>
+    <t>23.05.202631</t>
+  </si>
+  <si>
+    <t>23.05.202632</t>
+  </si>
+  <si>
+    <t>23.05.202633</t>
+  </si>
+  <si>
+    <t>23.05.202634</t>
+  </si>
+  <si>
+    <t>23.05.202635</t>
+  </si>
+  <si>
+    <t>23.05.202636</t>
+  </si>
+  <si>
+    <t>23.05.202637</t>
+  </si>
+  <si>
+    <t>23.05.202638</t>
+  </si>
+  <si>
+    <t>23.05.202639</t>
+  </si>
+  <si>
+    <t>23.05.202640</t>
+  </si>
+  <si>
+    <t>23.05.202641</t>
+  </si>
+  <si>
+    <t>23.05.202642</t>
+  </si>
+  <si>
+    <t>23.05.202643</t>
+  </si>
+  <si>
+    <t>23.05.202644</t>
+  </si>
+  <si>
+    <t>23.05.202645</t>
+  </si>
+  <si>
+    <t>23.05.202646</t>
+  </si>
+  <si>
+    <t>23.05.202647</t>
+  </si>
+  <si>
+    <t>23.05.202648</t>
+  </si>
+  <si>
+    <t>23.05.202649</t>
+  </si>
+  <si>
+    <t>23.05.202650</t>
+  </si>
+  <si>
+    <t>23.05.202651</t>
+  </si>
+  <si>
+    <t>23.05.202652</t>
+  </si>
+  <si>
+    <t>23.05.202653</t>
+  </si>
+  <si>
+    <t>23.05.202654</t>
+  </si>
+  <si>
+    <t>23.05.202655</t>
+  </si>
+  <si>
+    <t>23.05.202656</t>
+  </si>
+  <si>
+    <t>23.05.202657</t>
+  </si>
+  <si>
+    <t>23.05.202658</t>
+  </si>
+  <si>
+    <t>23.05.202659</t>
+  </si>
+  <si>
+    <t>23.05.202660</t>
+  </si>
+  <si>
+    <t>23.05.202661</t>
+  </si>
+  <si>
+    <t>23.05.202662</t>
+  </si>
+  <si>
+    <t>23.05.202663</t>
+  </si>
+  <si>
+    <t>23.05.202664</t>
+  </si>
+  <si>
+    <t>23.05.202665</t>
+  </si>
+  <si>
+    <t>23.05.202666</t>
+  </si>
+  <si>
+    <t>23.05.202667</t>
+  </si>
+  <si>
+    <t>23.05.202668</t>
+  </si>
+  <si>
+    <t>23.05.202669</t>
+  </si>
+  <si>
+    <t>23.05.202670</t>
+  </si>
+  <si>
+    <t>23.05.202671</t>
+  </si>
+  <si>
+    <t>23.05.202672</t>
+  </si>
+  <si>
+    <t>23.05.202673</t>
+  </si>
+  <si>
+    <t>23.05.202674</t>
+  </si>
+  <si>
+    <t>23.05.202675</t>
+  </si>
+  <si>
+    <t>23.05.202676</t>
+  </si>
+  <si>
+    <t>23.05.202677</t>
+  </si>
+  <si>
+    <t>23.05.202678</t>
+  </si>
+  <si>
+    <t>23.05.202679</t>
+  </si>
+  <si>
+    <t>23.05.202680</t>
+  </si>
+  <si>
+    <t>23.05.202681</t>
+  </si>
+  <si>
+    <t>23.05.202682</t>
+  </si>
+  <si>
+    <t>23.05.202683</t>
+  </si>
+  <si>
+    <t>23.05.202684</t>
+  </si>
+  <si>
+    <t>23.05.202685</t>
+  </si>
+  <si>
+    <t>23.05.202686</t>
+  </si>
+  <si>
+    <t>23.05.202687</t>
+  </si>
+  <si>
+    <t>23.05.202688</t>
+  </si>
+  <si>
+    <t>23.05.202689</t>
+  </si>
+  <si>
+    <t>23.05.202690</t>
+  </si>
+  <si>
+    <t>23.05.202691</t>
+  </si>
+  <si>
+    <t>23.05.202692</t>
+  </si>
+  <si>
+    <t>23.05.202693</t>
+  </si>
+  <si>
+    <t>23.05.202694</t>
+  </si>
+  <si>
+    <t>23.05.202695</t>
+  </si>
+  <si>
+    <t>23.05.202696</t>
+  </si>
+  <si>
+    <t>24.05.20261</t>
+  </si>
+  <si>
+    <t>24.05.20262</t>
+  </si>
+  <si>
+    <t>24.05.20263</t>
+  </si>
+  <si>
+    <t>24.05.20264</t>
+  </si>
+  <si>
+    <t>24.05.20265</t>
+  </si>
+  <si>
+    <t>24.05.20266</t>
+  </si>
+  <si>
+    <t>24.05.20267</t>
+  </si>
+  <si>
+    <t>24.05.20268</t>
+  </si>
+  <si>
+    <t>24.05.20269</t>
+  </si>
+  <si>
+    <t>24.05.202610</t>
+  </si>
+  <si>
+    <t>24.05.202611</t>
+  </si>
+  <si>
+    <t>24.05.202612</t>
+  </si>
+  <si>
+    <t>24.05.202613</t>
+  </si>
+  <si>
+    <t>24.05.202614</t>
+  </si>
+  <si>
+    <t>24.05.202615</t>
+  </si>
+  <si>
+    <t>24.05.202616</t>
+  </si>
+  <si>
+    <t>24.05.202617</t>
+  </si>
+  <si>
+    <t>24.05.202618</t>
+  </si>
+  <si>
+    <t>24.05.202619</t>
+  </si>
+  <si>
+    <t>24.05.202620</t>
+  </si>
+  <si>
+    <t>24.05.202621</t>
+  </si>
+  <si>
+    <t>24.05.202622</t>
+  </si>
+  <si>
+    <t>24.05.202623</t>
+  </si>
+  <si>
+    <t>24.05.202624</t>
+  </si>
+  <si>
+    <t>24.05.202625</t>
+  </si>
+  <si>
+    <t>24.05.202626</t>
+  </si>
+  <si>
+    <t>24.05.202627</t>
+  </si>
+  <si>
+    <t>24.05.202628</t>
+  </si>
+  <si>
+    <t>24.05.202629</t>
+  </si>
+  <si>
+    <t>24.05.202630</t>
+  </si>
+  <si>
+    <t>24.05.202631</t>
+  </si>
+  <si>
+    <t>24.05.202632</t>
+  </si>
+  <si>
+    <t>24.05.202633</t>
+  </si>
+  <si>
+    <t>24.05.202634</t>
+  </si>
+  <si>
+    <t>24.05.202635</t>
+  </si>
+  <si>
+    <t>24.05.202636</t>
+  </si>
+  <si>
+    <t>24.05.202637</t>
+  </si>
+  <si>
+    <t>24.05.202638</t>
+  </si>
+  <si>
+    <t>24.05.202639</t>
+  </si>
+  <si>
+    <t>24.05.202640</t>
+  </si>
+  <si>
+    <t>24.05.202641</t>
+  </si>
+  <si>
+    <t>24.05.202642</t>
+  </si>
+  <si>
+    <t>24.05.202643</t>
+  </si>
+  <si>
+    <t>24.05.202644</t>
+  </si>
+  <si>
+    <t>24.05.202645</t>
+  </si>
+  <si>
+    <t>24.05.202646</t>
+  </si>
+  <si>
+    <t>24.05.202647</t>
+  </si>
+  <si>
+    <t>24.05.202648</t>
+  </si>
+  <si>
+    <t>24.05.202649</t>
+  </si>
+  <si>
+    <t>24.05.202650</t>
+  </si>
+  <si>
+    <t>24.05.202651</t>
+  </si>
+  <si>
+    <t>24.05.202652</t>
+  </si>
+  <si>
+    <t>24.05.202653</t>
+  </si>
+  <si>
+    <t>24.05.202654</t>
+  </si>
+  <si>
+    <t>24.05.202655</t>
+  </si>
+  <si>
+    <t>24.05.202656</t>
+  </si>
+  <si>
+    <t>24.05.202657</t>
+  </si>
+  <si>
+    <t>24.05.202658</t>
+  </si>
+  <si>
+    <t>24.05.202659</t>
+  </si>
+  <si>
+    <t>24.05.202660</t>
+  </si>
+  <si>
+    <t>24.05.202661</t>
+  </si>
+  <si>
+    <t>24.05.202662</t>
+  </si>
+  <si>
+    <t>24.05.202663</t>
+  </si>
+  <si>
+    <t>24.05.202664</t>
+  </si>
+  <si>
+    <t>24.05.202665</t>
+  </si>
+  <si>
+    <t>24.05.202666</t>
+  </si>
+  <si>
+    <t>24.05.202667</t>
+  </si>
+  <si>
+    <t>24.05.202668</t>
+  </si>
+  <si>
+    <t>24.05.202669</t>
+  </si>
+  <si>
+    <t>24.05.202670</t>
+  </si>
+  <si>
+    <t>24.05.202671</t>
+  </si>
+  <si>
+    <t>24.05.202672</t>
+  </si>
+  <si>
+    <t>24.05.202673</t>
+  </si>
+  <si>
+    <t>24.05.202674</t>
+  </si>
+  <si>
+    <t>24.05.202675</t>
+  </si>
+  <si>
+    <t>24.05.202676</t>
+  </si>
+  <si>
+    <t>24.05.202677</t>
+  </si>
+  <si>
+    <t>24.05.202678</t>
+  </si>
+  <si>
+    <t>24.05.202679</t>
+  </si>
+  <si>
+    <t>24.05.202680</t>
+  </si>
+  <si>
+    <t>24.05.202681</t>
+  </si>
+  <si>
+    <t>24.05.202682</t>
+  </si>
+  <si>
+    <t>24.05.202683</t>
+  </si>
+  <si>
+    <t>24.05.202684</t>
+  </si>
+  <si>
+    <t>24.05.202685</t>
+  </si>
+  <si>
+    <t>24.05.202686</t>
+  </si>
+  <si>
+    <t>24.05.202687</t>
+  </si>
+  <si>
+    <t>24.05.202688</t>
+  </si>
+  <si>
+    <t>24.05.202689</t>
+  </si>
+  <si>
+    <t>24.05.202690</t>
+  </si>
+  <si>
+    <t>24.05.202691</t>
+  </si>
+  <si>
+    <t>24.05.202692</t>
+  </si>
+  <si>
+    <t>24.05.202693</t>
+  </si>
+  <si>
+    <t>24.05.202694</t>
+  </si>
+  <si>
+    <t>24.05.202695</t>
+  </si>
+  <si>
+    <t>24.05.202696</t>
+  </si>
+  <si>
+    <t>25.05.20261</t>
+  </si>
+  <si>
+    <t>25.05.20262</t>
+  </si>
+  <si>
+    <t>25.05.20263</t>
+  </si>
+  <si>
+    <t>25.05.20264</t>
+  </si>
+  <si>
+    <t>25.05.20265</t>
+  </si>
+  <si>
+    <t>25.05.20266</t>
+  </si>
+  <si>
+    <t>25.05.20267</t>
+  </si>
+  <si>
+    <t>25.05.20268</t>
+  </si>
+  <si>
+    <t>25.05.20269</t>
+  </si>
+  <si>
+    <t>25.05.202610</t>
+  </si>
+  <si>
+    <t>25.05.202611</t>
+  </si>
+  <si>
+    <t>25.05.202612</t>
+  </si>
+  <si>
+    <t>25.05.202613</t>
+  </si>
+  <si>
+    <t>25.05.202614</t>
+  </si>
+  <si>
+    <t>25.05.202615</t>
+  </si>
+  <si>
+    <t>25.05.202616</t>
+  </si>
+  <si>
+    <t>25.05.202617</t>
+  </si>
+  <si>
+    <t>25.05.202618</t>
+  </si>
+  <si>
+    <t>25.05.202619</t>
+  </si>
+  <si>
+    <t>25.05.202620</t>
+  </si>
+  <si>
+    <t>25.05.202621</t>
+  </si>
+  <si>
+    <t>25.05.202622</t>
+  </si>
+  <si>
+    <t>25.05.202623</t>
+  </si>
+  <si>
+    <t>25.05.202624</t>
+  </si>
+  <si>
+    <t>25.05.202625</t>
+  </si>
+  <si>
+    <t>25.05.202626</t>
+  </si>
+  <si>
+    <t>25.05.202627</t>
+  </si>
+  <si>
+    <t>25.05.202628</t>
+  </si>
+  <si>
+    <t>25.05.202629</t>
+  </si>
+  <si>
+    <t>25.05.202630</t>
+  </si>
+  <si>
+    <t>25.05.202631</t>
+  </si>
+  <si>
+    <t>25.05.202632</t>
+  </si>
+  <si>
+    <t>25.05.202633</t>
+  </si>
+  <si>
+    <t>25.05.202634</t>
+  </si>
+  <si>
+    <t>25.05.202635</t>
+  </si>
+  <si>
+    <t>25.05.202636</t>
+  </si>
+  <si>
+    <t>25.05.202637</t>
+  </si>
+  <si>
+    <t>25.05.202638</t>
+  </si>
+  <si>
+    <t>25.05.202639</t>
+  </si>
+  <si>
+    <t>25.05.202640</t>
+  </si>
+  <si>
+    <t>25.05.202641</t>
+  </si>
+  <si>
+    <t>25.05.202642</t>
+  </si>
+  <si>
+    <t>25.05.202643</t>
+  </si>
+  <si>
+    <t>25.05.202644</t>
+  </si>
+  <si>
+    <t>25.05.202645</t>
+  </si>
+  <si>
+    <t>25.05.202646</t>
+  </si>
+  <si>
+    <t>25.05.202647</t>
+  </si>
+  <si>
+    <t>25.05.202648</t>
+  </si>
+  <si>
+    <t>25.05.202649</t>
+  </si>
+  <si>
+    <t>25.05.202650</t>
+  </si>
+  <si>
+    <t>25.05.202651</t>
+  </si>
+  <si>
+    <t>25.05.202652</t>
+  </si>
+  <si>
+    <t>25.05.202653</t>
+  </si>
+  <si>
+    <t>25.05.202654</t>
+  </si>
+  <si>
+    <t>25.05.202655</t>
+  </si>
+  <si>
+    <t>25.05.202656</t>
+  </si>
+  <si>
+    <t>25.05.202657</t>
+  </si>
+  <si>
+    <t>25.05.202658</t>
+  </si>
+  <si>
+    <t>25.05.202659</t>
+  </si>
+  <si>
+    <t>25.05.202660</t>
+  </si>
+  <si>
+    <t>25.05.202661</t>
+  </si>
+  <si>
+    <t>25.05.202662</t>
+  </si>
+  <si>
+    <t>25.05.202663</t>
+  </si>
+  <si>
+    <t>25.05.202664</t>
+  </si>
+  <si>
+    <t>25.05.202665</t>
+  </si>
+  <si>
+    <t>25.05.202666</t>
+  </si>
+  <si>
+    <t>25.05.202667</t>
+  </si>
+  <si>
+    <t>25.05.202668</t>
+  </si>
+  <si>
+    <t>25.05.202669</t>
+  </si>
+  <si>
+    <t>25.05.202670</t>
+  </si>
+  <si>
+    <t>25.05.202671</t>
+  </si>
+  <si>
+    <t>25.05.202672</t>
+  </si>
+  <si>
+    <t>25.05.202673</t>
+  </si>
+  <si>
+    <t>25.05.202674</t>
+  </si>
+  <si>
+    <t>25.05.202675</t>
+  </si>
+  <si>
+    <t>25.05.202676</t>
+  </si>
+  <si>
+    <t>25.05.202677</t>
+  </si>
+  <si>
+    <t>25.05.202678</t>
+  </si>
+  <si>
+    <t>25.05.202679</t>
+  </si>
+  <si>
+    <t>25.05.202680</t>
+  </si>
+  <si>
+    <t>25.05.202681</t>
+  </si>
+  <si>
+    <t>25.05.202682</t>
+  </si>
+  <si>
+    <t>25.05.202683</t>
+  </si>
+  <si>
+    <t>25.05.202684</t>
+  </si>
+  <si>
+    <t>25.05.202685</t>
+  </si>
+  <si>
+    <t>25.05.202686</t>
+  </si>
+  <si>
+    <t>25.05.202687</t>
+  </si>
+  <si>
+    <t>25.05.202688</t>
+  </si>
+  <si>
+    <t>25.05.202689</t>
+  </si>
+  <si>
+    <t>25.05.202690</t>
+  </si>
+  <si>
+    <t>25.05.202691</t>
+  </si>
+  <si>
+    <t>25.05.202692</t>
+  </si>
+  <si>
+    <t>25.05.202693</t>
+  </si>
+  <si>
+    <t>25.05.202694</t>
+  </si>
+  <si>
+    <t>25.05.202695</t>
+  </si>
+  <si>
+    <t>25.05.202696</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F385"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -994,7 +1570,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1590,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1610,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1630,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1650,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B6">
-        <v>-7.336</v>
+        <v>3.927</v>
       </c>
       <c r="C6">
-        <v>949.943</v>
+        <v>273.5</v>
       </c>
       <c r="D6">
-        <v>949.943</v>
+        <v>273.5</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1670,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B7">
-        <v>3.595</v>
+        <v>-11.613</v>
       </c>
       <c r="C7">
-        <v>400</v>
+        <v>898.232</v>
       </c>
       <c r="D7">
-        <v>400</v>
+        <v>898.232</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1690,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B8">
-        <v>5.397</v>
+        <v>1.642</v>
       </c>
       <c r="C8">
-        <v>274.467</v>
+        <v>899</v>
       </c>
       <c r="D8">
-        <v>274.467</v>
+        <v>899</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1710,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B9">
-        <v>21.265</v>
+        <v>16.56</v>
       </c>
       <c r="C9">
-        <v>207.668</v>
+        <v>275.122</v>
       </c>
       <c r="D9">
-        <v>207.668</v>
+        <v>275.122</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1730,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B10">
-        <v>74.15600000000001</v>
+        <v>35.33</v>
       </c>
       <c r="C10">
-        <v>-677.771</v>
+        <v>298.795</v>
       </c>
       <c r="D10">
-        <v>-677.771</v>
+        <v>298.795</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1750,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B11">
-        <v>18.611</v>
+        <v>21.087</v>
       </c>
       <c r="C11">
-        <v>-230.177</v>
+        <v>271.878</v>
       </c>
       <c r="D11">
-        <v>-230.177</v>
+        <v>271.878</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1770,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B12">
-        <v>10.986</v>
+        <v>12.671</v>
       </c>
       <c r="C12">
-        <v>122.113</v>
+        <v>241.669</v>
       </c>
       <c r="D12">
-        <v>122.113</v>
+        <v>241.669</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1790,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B13">
-        <v>10.63</v>
+        <v>-4.25</v>
       </c>
       <c r="C13">
-        <v>164.987</v>
+        <v>898.824</v>
       </c>
       <c r="D13">
-        <v>164.987</v>
+        <v>898.824</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1810,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B14">
-        <v>31.922</v>
+        <v>27.282</v>
       </c>
       <c r="C14">
-        <v>256.163</v>
+        <v>-22.455</v>
       </c>
       <c r="D14">
-        <v>256.163</v>
+        <v>-22.455</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1830,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B15">
-        <v>15.413</v>
+        <v>16.57</v>
       </c>
       <c r="C15">
-        <v>97.91500000000001</v>
+        <v>41.962</v>
       </c>
       <c r="D15">
-        <v>97.91500000000001</v>
+        <v>41.962</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1850,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B16">
-        <v>16.558</v>
+        <v>-3.02</v>
       </c>
       <c r="C16">
-        <v>52.185</v>
+        <v>885.8</v>
       </c>
       <c r="D16">
-        <v>52.185</v>
+        <v>885.8</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1870,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B17">
-        <v>26.543</v>
+        <v>-10.328</v>
       </c>
       <c r="C17">
-        <v>102.069</v>
+        <v>876.446</v>
       </c>
       <c r="D17">
-        <v>102.069</v>
+        <v>876.446</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1890,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B18">
-        <v>48.332</v>
+        <v>9.244</v>
       </c>
       <c r="C18">
-        <v>258.136</v>
+        <v>257.601</v>
       </c>
       <c r="D18">
-        <v>258.136</v>
+        <v>257.601</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1910,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B19">
-        <v>12.537</v>
+        <v>-0.323</v>
       </c>
       <c r="C19">
-        <v>187.102</v>
+        <v>898.386</v>
       </c>
       <c r="D19">
-        <v>187.102</v>
+        <v>898.386</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1930,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B20">
-        <v>37.009</v>
+        <v>-10.957</v>
       </c>
       <c r="C20">
-        <v>180.721</v>
+        <v>898.42</v>
       </c>
       <c r="D20">
-        <v>180.721</v>
+        <v>898.42</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1950,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B21">
-        <v>41.747</v>
+        <v>-10.85</v>
       </c>
       <c r="C21">
-        <v>70.494</v>
+        <v>909.184</v>
       </c>
       <c r="D21">
-        <v>70.494</v>
+        <v>909.184</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1970,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B22">
-        <v>46.538</v>
+        <v>3.567</v>
       </c>
       <c r="C22">
-        <v>131.914</v>
+        <v>1032.723</v>
       </c>
       <c r="D22">
-        <v>131.914</v>
+        <v>1032.723</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1990,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B23">
-        <v>21.219</v>
+        <v>-6.647</v>
       </c>
       <c r="C23">
-        <v>261.944</v>
+        <v>925.575</v>
       </c>
       <c r="D23">
-        <v>261.944</v>
+        <v>925.575</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +2010,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B24">
-        <v>-12.071</v>
+        <v>-34.273</v>
       </c>
       <c r="C24">
-        <v>897.867</v>
+        <v>924.845</v>
       </c>
       <c r="D24">
-        <v>897.867</v>
+        <v>924.845</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +2030,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B25">
-        <v>-35.771</v>
+        <v>-34.033</v>
       </c>
       <c r="C25">
-        <v>998.724</v>
+        <v>925.224</v>
       </c>
       <c r="D25">
-        <v>998.724</v>
+        <v>925.224</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +2050,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B26">
-        <v>-47.612</v>
+        <v>-0.108</v>
       </c>
       <c r="C26">
-        <v>3992.366</v>
+        <v>1079.135</v>
       </c>
       <c r="D26">
-        <v>3992.366</v>
+        <v>1079.135</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +2070,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B27">
-        <v>-38.998</v>
+        <v>-26.345</v>
       </c>
       <c r="C27">
-        <v>2502.938</v>
+        <v>982.17</v>
       </c>
       <c r="D27">
-        <v>2502.938</v>
+        <v>982.17</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +2090,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B28">
-        <v>-56.175</v>
+        <v>-24.328</v>
       </c>
       <c r="C28">
-        <v>1220.667</v>
+        <v>947.234</v>
       </c>
       <c r="D28">
-        <v>1220.667</v>
+        <v>947.234</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +2110,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B29">
-        <v>-46.927</v>
+        <v>-45.203</v>
       </c>
       <c r="C29">
-        <v>1137.69</v>
+        <v>1859.176</v>
       </c>
       <c r="D29">
-        <v>1137.69</v>
+        <v>1859.176</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +2130,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B30">
-        <v>-2.161</v>
+        <v>-46.009</v>
       </c>
       <c r="C30">
-        <v>1053.15</v>
+        <v>1163.461</v>
       </c>
       <c r="D30">
-        <v>1053.15</v>
+        <v>1163.461</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +2150,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B31">
-        <v>24.184</v>
+        <v>-83.779</v>
       </c>
       <c r="C31">
-        <v>259.558</v>
+        <v>1985.174</v>
       </c>
       <c r="D31">
-        <v>259.558</v>
+        <v>1985.174</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +2170,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B32">
-        <v>-8.269</v>
+        <v>-108.139</v>
       </c>
       <c r="C32">
-        <v>899.152</v>
+        <v>3149.064</v>
       </c>
       <c r="D32">
-        <v>899.152</v>
+        <v>3149.064</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +2190,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B33">
-        <v>-19.458</v>
+        <v>-61.647</v>
       </c>
       <c r="C33">
-        <v>1065.536</v>
+        <v>1183.113</v>
       </c>
       <c r="D33">
-        <v>1065.536</v>
+        <v>1183.113</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +2210,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B34">
-        <v>52.248</v>
+        <v>-35.381</v>
       </c>
       <c r="C34">
-        <v>-14.549</v>
+        <v>1099.616</v>
       </c>
       <c r="D34">
-        <v>-14.549</v>
+        <v>1099.616</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +2230,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B35">
-        <v>-1.34</v>
+        <v>-41.944</v>
       </c>
       <c r="C35">
-        <v>876.279</v>
+        <v>1100.166</v>
       </c>
       <c r="D35">
-        <v>876.279</v>
+        <v>1100.166</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +2250,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B36">
-        <v>-4.35</v>
+        <v>-94.14400000000001</v>
       </c>
       <c r="C36">
-        <v>891.024</v>
+        <v>1164.678</v>
       </c>
       <c r="D36">
-        <v>891.024</v>
+        <v>1164.678</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +2270,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B37">
-        <v>-89.893</v>
+        <v>-57.253</v>
       </c>
       <c r="C37">
-        <v>888.393</v>
+        <v>1084.975</v>
       </c>
       <c r="D37">
-        <v>888.393</v>
+        <v>1084.975</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +2290,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B38">
-        <v>-57.939</v>
+        <v>-73.89400000000001</v>
       </c>
       <c r="C38">
-        <v>697.08</v>
+        <v>911.2140000000001</v>
       </c>
       <c r="D38">
-        <v>697.08</v>
+        <v>911.2140000000001</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +2310,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B39">
-        <v>-59.18</v>
+        <v>19.707</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>385.634</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>385.634</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +2330,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B40">
-        <v>-44.895</v>
+        <v>21.381</v>
       </c>
       <c r="C40">
-        <v>766.255</v>
+        <v>401</v>
       </c>
       <c r="D40">
-        <v>766.255</v>
+        <v>401</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +2350,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B41">
-        <v>-73.566</v>
+        <v>8.913</v>
       </c>
       <c r="C41">
-        <v>765.6660000000001</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>765.6660000000001</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +2370,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B42">
-        <v>-55.06</v>
+        <v>-10.914</v>
       </c>
       <c r="C42">
-        <v>554.65</v>
+        <v>714.578</v>
       </c>
       <c r="D42">
-        <v>554.65</v>
+        <v>714.578</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +2390,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B43">
-        <v>-33.074</v>
+        <v>2.711</v>
       </c>
       <c r="C43">
-        <v>550.749</v>
+        <v>401</v>
       </c>
       <c r="D43">
-        <v>550.749</v>
+        <v>401</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +2410,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B44">
-        <v>-5.467</v>
+        <v>-54.363</v>
       </c>
       <c r="C44">
-        <v>550.65</v>
+        <v>755.428</v>
       </c>
       <c r="D44">
-        <v>550.65</v>
+        <v>755.428</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +2430,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B45">
-        <v>-11.176</v>
+        <v>-35.596</v>
       </c>
       <c r="C45">
-        <v>552.6900000000001</v>
+        <v>1213.064</v>
       </c>
       <c r="D45">
-        <v>552.6900000000001</v>
+        <v>1213.064</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +2450,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B46">
-        <v>107.787</v>
+        <v>3.801</v>
       </c>
       <c r="C46">
-        <v>-6147.741</v>
+        <v>31.143</v>
       </c>
       <c r="D46">
-        <v>-6147.741</v>
+        <v>31.143</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +2470,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B47">
-        <v>26.042</v>
+        <v>7.867</v>
       </c>
       <c r="C47">
-        <v>293</v>
+        <v>75.93899999999999</v>
       </c>
       <c r="D47">
-        <v>293</v>
+        <v>75.93899999999999</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +2490,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B48">
-        <v>34.084</v>
+        <v>36.201</v>
       </c>
       <c r="C48">
-        <v>324.677</v>
+        <v>-126.494</v>
       </c>
       <c r="D48">
-        <v>324.677</v>
+        <v>-126.494</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +2510,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B49">
-        <v>17.038</v>
+        <v>34.484</v>
       </c>
       <c r="C49">
-        <v>16.744</v>
+        <v>-250.341</v>
       </c>
       <c r="D49">
-        <v>16.744</v>
+        <v>-250.341</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +2530,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B50">
-        <v>29.288</v>
+        <v>12.325</v>
       </c>
       <c r="C50">
-        <v>-53.404</v>
+        <v>-189.078</v>
       </c>
       <c r="D50">
-        <v>-53.404</v>
+        <v>-189.078</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +2550,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B51">
-        <v>39.191</v>
+        <v>34.31</v>
       </c>
       <c r="C51">
-        <v>73.535</v>
+        <v>-100.625</v>
       </c>
       <c r="D51">
-        <v>73.535</v>
+        <v>-100.625</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +2570,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B52">
-        <v>-17.118</v>
+        <v>60.138</v>
       </c>
       <c r="C52">
-        <v>633.963</v>
+        <v>-183.237</v>
       </c>
       <c r="D52">
-        <v>633.963</v>
+        <v>-183.237</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2590,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B53">
-        <v>-68.461</v>
+        <v>88.688</v>
       </c>
       <c r="C53">
-        <v>786.564</v>
+        <v>-675.633</v>
       </c>
       <c r="D53">
-        <v>786.564</v>
+        <v>-675.633</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2610,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B54">
-        <v>-57.855</v>
+        <v>133.75</v>
       </c>
       <c r="C54">
-        <v>809.064</v>
+        <v>-347.828</v>
       </c>
       <c r="D54">
-        <v>809.064</v>
+        <v>-347.828</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2630,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B55">
-        <v>-105.274</v>
+        <v>133.076</v>
       </c>
       <c r="C55">
-        <v>1231.039</v>
+        <v>-808.202</v>
       </c>
       <c r="D55">
-        <v>1231.039</v>
+        <v>-808.202</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2650,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>117.315</v>
       </c>
       <c r="C56">
-        <v>1308.511</v>
+        <v>-920.08</v>
       </c>
       <c r="D56">
-        <v>1308.511</v>
+        <v>-920.08</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2670,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B57">
-        <v>-152.376</v>
+        <v>109.232</v>
       </c>
       <c r="C57">
-        <v>698.048</v>
+        <v>-1485.566</v>
       </c>
       <c r="D57">
-        <v>698.048</v>
+        <v>-1485.566</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2690,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>-8.053000000000001</v>
       </c>
       <c r="C58">
-        <v>499.449</v>
+        <v>630.471</v>
       </c>
       <c r="D58">
-        <v>499.449</v>
+        <v>630.471</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2710,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B59">
-        <v>-2.242</v>
+        <v>14.121</v>
       </c>
       <c r="C59">
-        <v>499.44</v>
+        <v>0.671</v>
       </c>
       <c r="D59">
-        <v>499.44</v>
+        <v>0.671</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2730,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B60">
-        <v>56.874</v>
+        <v>47.938</v>
       </c>
       <c r="C60">
-        <v>-2535.806</v>
+        <v>-109.555</v>
       </c>
       <c r="D60">
-        <v>-2535.806</v>
+        <v>-109.555</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2750,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B61">
-        <v>114.999</v>
+        <v>1.946</v>
       </c>
       <c r="C61">
-        <v>-536.087</v>
+        <v>-95.855</v>
       </c>
       <c r="D61">
-        <v>-536.087</v>
+        <v>-95.855</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2770,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B62">
-        <v>160.77</v>
+        <v>74.721</v>
       </c>
       <c r="C62">
-        <v>89.86499999999999</v>
+        <v>-3656.097</v>
       </c>
       <c r="D62">
-        <v>89.86499999999999</v>
+        <v>-3656.097</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2790,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B63">
-        <v>118.001</v>
+        <v>119.083</v>
       </c>
       <c r="C63">
-        <v>-6482.078</v>
+        <v>-6318.428</v>
       </c>
       <c r="D63">
-        <v>-6482.078</v>
+        <v>-6318.428</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2810,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B64">
-        <v>132.862</v>
+        <v>146.895</v>
       </c>
       <c r="C64">
-        <v>-3859.042</v>
+        <v>-6530.825</v>
       </c>
       <c r="D64">
-        <v>-3859.042</v>
+        <v>-6530.825</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2830,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B65">
-        <v>53.908</v>
+        <v>101.386</v>
       </c>
       <c r="C65">
-        <v>-158.313</v>
+        <v>-89.01900000000001</v>
       </c>
       <c r="D65">
-        <v>-158.313</v>
+        <v>-89.01900000000001</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2850,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B66">
-        <v>-4.588</v>
+        <v>49.958</v>
       </c>
       <c r="C66">
-        <v>699</v>
+        <v>12.539</v>
       </c>
       <c r="D66">
-        <v>699</v>
+        <v>12.539</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2870,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B67">
-        <v>63.091</v>
+        <v>62.326</v>
       </c>
       <c r="C67">
-        <v>0.54</v>
+        <v>3.019</v>
       </c>
       <c r="D67">
-        <v>0.54</v>
+        <v>3.019</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2890,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B68">
-        <v>76.09399999999999</v>
+        <v>85.065</v>
       </c>
       <c r="C68">
-        <v>12.32</v>
+        <v>1.44</v>
       </c>
       <c r="D68">
-        <v>12.32</v>
+        <v>1.44</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2910,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B69">
-        <v>72.97199999999999</v>
+        <v>34.695</v>
       </c>
       <c r="C69">
-        <v>-1.226</v>
+        <v>0.04</v>
       </c>
       <c r="D69">
-        <v>-1.226</v>
+        <v>0.04</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2930,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B70">
-        <v>106.962</v>
+        <v>53.706</v>
       </c>
       <c r="C70">
-        <v>5.372</v>
+        <v>-0.783</v>
       </c>
       <c r="D70">
-        <v>5.372</v>
+        <v>-0.783</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2950,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B71">
-        <v>98.715</v>
+        <v>24.037</v>
       </c>
       <c r="C71">
-        <v>-18.056</v>
+        <v>0.6</v>
       </c>
       <c r="D71">
-        <v>-18.056</v>
+        <v>0.6</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2970,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B72">
-        <v>77.101</v>
+        <v>6.854</v>
       </c>
       <c r="C72">
-        <v>-9.542</v>
+        <v>0.5</v>
       </c>
       <c r="D72">
-        <v>-9.542</v>
+        <v>0.5</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2990,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B73">
-        <v>73.22199999999999</v>
+        <v>43.532</v>
       </c>
       <c r="C73">
-        <v>-5.247</v>
+        <v>1.883</v>
       </c>
       <c r="D73">
-        <v>-5.247</v>
+        <v>1.883</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +3010,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B74">
-        <v>119.299</v>
+        <v>43.277</v>
       </c>
       <c r="C74">
-        <v>-3360.637</v>
+        <v>-4.591</v>
       </c>
       <c r="D74">
-        <v>-3360.637</v>
+        <v>-4.591</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +3030,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B75">
-        <v>61.278</v>
+        <v>9.048999999999999</v>
       </c>
       <c r="C75">
-        <v>1.967</v>
+        <v>1.1</v>
       </c>
       <c r="D75">
-        <v>1.967</v>
+        <v>1.1</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +3050,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B76">
-        <v>72.15000000000001</v>
+        <v>-15.03</v>
       </c>
       <c r="C76">
-        <v>0.5</v>
+        <v>2147.902</v>
       </c>
       <c r="D76">
-        <v>0.5</v>
+        <v>2147.902</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +3070,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B77">
-        <v>66.628</v>
+        <v>-42.14</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1848.462</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1848.462</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +3090,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B78">
-        <v>70.312</v>
+        <v>26.388</v>
       </c>
       <c r="C78">
-        <v>7.807</v>
+        <v>269.469</v>
       </c>
       <c r="D78">
-        <v>7.807</v>
+        <v>269.469</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +3110,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B79">
-        <v>67.709</v>
+        <v>0.098</v>
       </c>
       <c r="C79">
-        <v>21.448</v>
+        <v>292.321</v>
       </c>
       <c r="D79">
-        <v>21.448</v>
+        <v>292.321</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +3130,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B80">
-        <v>74.137</v>
+        <v>-39.411</v>
       </c>
       <c r="C80">
-        <v>3.516</v>
+        <v>3107.915</v>
       </c>
       <c r="D80">
-        <v>3.516</v>
+        <v>3107.915</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +3150,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B81">
-        <v>87.098</v>
+        <v>-44.149</v>
       </c>
       <c r="C81">
-        <v>2.634</v>
+        <v>3492.287</v>
       </c>
       <c r="D81">
-        <v>2.634</v>
+        <v>3492.287</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +3170,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B82">
-        <v>84.348</v>
+        <v>-59.108</v>
       </c>
       <c r="C82">
-        <v>2.269</v>
+        <v>2238.257</v>
       </c>
       <c r="D82">
-        <v>2.269</v>
+        <v>2238.257</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +3190,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B83">
-        <v>95.735</v>
+        <v>-28.736</v>
       </c>
       <c r="C83">
-        <v>13.317</v>
+        <v>1267.571</v>
       </c>
       <c r="D83">
-        <v>13.317</v>
+        <v>1267.571</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +3210,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B84">
-        <v>111.685</v>
+        <v>-50.912</v>
       </c>
       <c r="C84">
-        <v>1.984</v>
+        <v>918.134</v>
       </c>
       <c r="D84">
-        <v>1.984</v>
+        <v>918.134</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +3230,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B85">
-        <v>126.313</v>
+        <v>-5.569</v>
       </c>
       <c r="C85">
-        <v>3.795</v>
+        <v>941.6420000000001</v>
       </c>
       <c r="D85">
-        <v>3.795</v>
+        <v>941.6420000000001</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +3250,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B86">
-        <v>26.285</v>
+        <v>-60.337</v>
       </c>
       <c r="C86">
-        <v>0.6</v>
+        <v>1473.392</v>
       </c>
       <c r="D86">
-        <v>0.6</v>
+        <v>1473.392</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +3270,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B87">
-        <v>25.531</v>
+        <v>0.829</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +3290,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B88">
-        <v>31.465</v>
+        <v>40.799</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>259.548</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>259.548</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +3310,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B89">
-        <v>72.422</v>
+        <v>40.958</v>
       </c>
       <c r="C89">
-        <v>7.075</v>
+        <v>263.689</v>
       </c>
       <c r="D89">
-        <v>7.075</v>
+        <v>263.689</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +3330,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B90">
-        <v>77.017</v>
+        <v>9.071</v>
       </c>
       <c r="C90">
-        <v>275.359</v>
+        <v>400</v>
       </c>
       <c r="D90">
-        <v>275.359</v>
+        <v>400</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +3350,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B91">
-        <v>92.042</v>
+        <v>-5.796</v>
       </c>
       <c r="C91">
-        <v>279.825</v>
+        <v>1092.337</v>
       </c>
       <c r="D91">
-        <v>279.825</v>
+        <v>1092.337</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +3370,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B92">
-        <v>58.818</v>
+        <v>-32.541</v>
       </c>
       <c r="C92">
-        <v>276.673</v>
+        <v>1255.15</v>
       </c>
       <c r="D92">
-        <v>276.673</v>
+        <v>1255.15</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +3390,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B93">
-        <v>44.298</v>
+        <v>-25.173</v>
       </c>
       <c r="C93">
-        <v>270.531</v>
+        <v>868.182</v>
       </c>
       <c r="D93">
-        <v>270.531</v>
+        <v>868.182</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +3410,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B94">
-        <v>47.425</v>
+        <v>-44.621</v>
       </c>
       <c r="C94">
-        <v>294.598</v>
+        <v>1612.446</v>
       </c>
       <c r="D94">
-        <v>294.598</v>
+        <v>1612.446</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +3430,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B95">
-        <v>59.118</v>
+        <v>-29.406</v>
       </c>
       <c r="C95">
-        <v>33.073</v>
+        <v>1188.376</v>
       </c>
       <c r="D95">
-        <v>33.073</v>
+        <v>1188.376</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +3450,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B96">
-        <v>18.806</v>
+        <v>-33.312</v>
       </c>
       <c r="C96">
-        <v>131.561</v>
+        <v>1239.709</v>
       </c>
       <c r="D96">
-        <v>131.561</v>
+        <v>1239.709</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +3470,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B97">
-        <v>26.403</v>
+        <v>-23.974</v>
       </c>
       <c r="C97">
-        <v>-48.271</v>
+        <v>1016.065</v>
       </c>
       <c r="D97">
-        <v>-48.271</v>
+        <v>1016.065</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +3490,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B98">
-        <v>-4.361</v>
+        <v>-49.335</v>
       </c>
       <c r="C98">
-        <v>1009.4</v>
+        <v>3742.72</v>
       </c>
       <c r="D98">
-        <v>1009.4</v>
+        <v>3742.72</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +3510,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46164.01041666666</v>
+        <v>46165.01041666666</v>
       </c>
       <c r="B99">
-        <v>-9.566000000000001</v>
+        <v>-40.42</v>
       </c>
       <c r="C99">
-        <v>899.1559999999999</v>
+        <v>1313.452</v>
       </c>
       <c r="D99">
-        <v>899.1559999999999</v>
+        <v>1313.452</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +3530,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46164.02083333334</v>
+        <v>46165.02083333334</v>
       </c>
       <c r="B100">
-        <v>-14.996</v>
+        <v>-30.957</v>
       </c>
       <c r="C100">
-        <v>897.428</v>
+        <v>1139.28</v>
       </c>
       <c r="D100">
-        <v>897.428</v>
+        <v>1139.28</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +3550,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46164.03125</v>
+        <v>46165.03125</v>
       </c>
       <c r="B101">
-        <v>-2.525</v>
+        <v>-43.085</v>
       </c>
       <c r="C101">
-        <v>893.159</v>
+        <v>1155.404</v>
       </c>
       <c r="D101">
-        <v>893.159</v>
+        <v>1155.404</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +3570,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46164.04166666666</v>
+        <v>46165.04166666666</v>
       </c>
       <c r="B102">
-        <v>3.927</v>
+        <v>-41.354</v>
       </c>
       <c r="C102">
-        <v>273.5</v>
+        <v>1137.242</v>
       </c>
       <c r="D102">
-        <v>273.5</v>
+        <v>1137.242</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3590,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46164.05208333334</v>
+        <v>46165.05208333334</v>
       </c>
       <c r="B103">
-        <v>-11.613</v>
+        <v>-13.606</v>
       </c>
       <c r="C103">
-        <v>898.232</v>
+        <v>1125.224</v>
       </c>
       <c r="D103">
-        <v>898.232</v>
+        <v>1125.224</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3610,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46164.0625</v>
+        <v>46165.0625</v>
       </c>
       <c r="B104">
-        <v>1.642</v>
+        <v>13.755</v>
       </c>
       <c r="C104">
-        <v>899</v>
+        <v>220.45</v>
       </c>
       <c r="D104">
-        <v>899</v>
+        <v>220.45</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3630,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46164.07291666666</v>
+        <v>46165.07291666666</v>
       </c>
       <c r="B105">
-        <v>16.56</v>
+        <v>54.692</v>
       </c>
       <c r="C105">
-        <v>275.122</v>
+        <v>58.107</v>
       </c>
       <c r="D105">
-        <v>275.122</v>
+        <v>58.107</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3650,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46164.08333333334</v>
+        <v>46165.08333333334</v>
       </c>
       <c r="B106">
-        <v>35.33</v>
+        <v>39.956</v>
       </c>
       <c r="C106">
-        <v>298.795</v>
+        <v>239.298</v>
       </c>
       <c r="D106">
-        <v>298.795</v>
+        <v>239.298</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3670,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46164.09375</v>
+        <v>46165.09375</v>
       </c>
       <c r="B107">
-        <v>21.087</v>
+        <v>6.788</v>
       </c>
       <c r="C107">
-        <v>271.878</v>
+        <v>1133.53</v>
       </c>
       <c r="D107">
-        <v>271.878</v>
+        <v>1133.53</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3690,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46164.10416666666</v>
+        <v>46165.10416666666</v>
       </c>
       <c r="B108">
-        <v>12.671</v>
+        <v>11.753</v>
       </c>
       <c r="C108">
-        <v>241.669</v>
+        <v>-2345.473</v>
       </c>
       <c r="D108">
-        <v>241.669</v>
+        <v>-2345.473</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3710,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46164.11458333334</v>
+        <v>46165.11458333334</v>
       </c>
       <c r="B109">
-        <v>-4.25</v>
+        <v>-6.858</v>
       </c>
       <c r="C109">
-        <v>898.824</v>
+        <v>892.962</v>
       </c>
       <c r="D109">
-        <v>898.824</v>
+        <v>892.962</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3730,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46164.125</v>
+        <v>46165.125</v>
       </c>
       <c r="B110">
-        <v>27.282</v>
+        <v>14.232</v>
       </c>
       <c r="C110">
-        <v>-22.455</v>
+        <v>372.427</v>
       </c>
       <c r="D110">
-        <v>-22.455</v>
+        <v>372.427</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3750,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46164.13541666666</v>
+        <v>46165.13541666666</v>
       </c>
       <c r="B111">
-        <v>16.57</v>
+        <v>12.676</v>
       </c>
       <c r="C111">
-        <v>41.962</v>
+        <v>335.533</v>
       </c>
       <c r="D111">
-        <v>41.962</v>
+        <v>335.533</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3770,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46164.14583333334</v>
+        <v>46165.14583333334</v>
       </c>
       <c r="B112">
-        <v>-3.02</v>
+        <v>58.61</v>
       </c>
       <c r="C112">
-        <v>885.8</v>
+        <v>336.446</v>
       </c>
       <c r="D112">
-        <v>885.8</v>
+        <v>336.446</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3790,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46164.15625</v>
+        <v>46165.15625</v>
       </c>
       <c r="B113">
-        <v>-10.328</v>
+        <v>19.435</v>
       </c>
       <c r="C113">
-        <v>876.446</v>
+        <v>400</v>
       </c>
       <c r="D113">
-        <v>876.446</v>
+        <v>400</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3810,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46164.16666666666</v>
+        <v>46165.16666666666</v>
       </c>
       <c r="B114">
-        <v>9.244</v>
+        <v>-0.36</v>
       </c>
       <c r="C114">
-        <v>257.601</v>
+        <v>898.611</v>
       </c>
       <c r="D114">
-        <v>257.601</v>
+        <v>898.611</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3830,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46164.17708333334</v>
+        <v>46165.17708333334</v>
       </c>
       <c r="B115">
-        <v>-0.323</v>
+        <v>19.796</v>
       </c>
       <c r="C115">
-        <v>898.386</v>
+        <v>334.023</v>
       </c>
       <c r="D115">
-        <v>898.386</v>
+        <v>334.023</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3850,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46164.1875</v>
+        <v>46165.1875</v>
       </c>
       <c r="B116">
-        <v>-10.957</v>
+        <v>31.575</v>
       </c>
       <c r="C116">
-        <v>898.42</v>
+        <v>367.012</v>
       </c>
       <c r="D116">
-        <v>898.42</v>
+        <v>367.012</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3870,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46164.19791666666</v>
+        <v>46165.19791666666</v>
       </c>
       <c r="B117">
-        <v>-10.85</v>
+        <v>46.696</v>
       </c>
       <c r="C117">
-        <v>909.184</v>
+        <v>111.226</v>
       </c>
       <c r="D117">
-        <v>909.184</v>
+        <v>111.226</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3890,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46164.20833333334</v>
+        <v>46165.20833333334</v>
       </c>
       <c r="B118">
-        <v>3.567</v>
+        <v>57.685</v>
       </c>
       <c r="C118">
-        <v>1032.723</v>
+        <v>290.455</v>
       </c>
       <c r="D118">
-        <v>1032.723</v>
+        <v>290.455</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3910,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46164.21875</v>
+        <v>46165.21875</v>
       </c>
       <c r="B119">
-        <v>-6.647</v>
+        <v>53.072</v>
       </c>
       <c r="C119">
-        <v>925.575</v>
+        <v>233.003</v>
       </c>
       <c r="D119">
-        <v>925.575</v>
+        <v>233.003</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3930,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46164.22916666666</v>
+        <v>46165.22916666666</v>
       </c>
       <c r="B120">
-        <v>-34.273</v>
+        <v>87.348</v>
       </c>
       <c r="C120">
-        <v>924.845</v>
+        <v>89.72199999999999</v>
       </c>
       <c r="D120">
-        <v>924.845</v>
+        <v>89.72199999999999</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3950,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46164.23958333334</v>
+        <v>46165.23958333334</v>
       </c>
       <c r="B121">
-        <v>-34.033</v>
+        <v>82.04600000000001</v>
       </c>
       <c r="C121">
-        <v>925.224</v>
+        <v>-76.08499999999999</v>
       </c>
       <c r="D121">
-        <v>925.224</v>
+        <v>-76.08499999999999</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3970,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46164.25</v>
+        <v>46165.25</v>
       </c>
       <c r="B122">
-        <v>-0.108</v>
+        <v>47.462</v>
       </c>
       <c r="C122">
-        <v>1079.135</v>
+        <v>304.799</v>
       </c>
       <c r="D122">
-        <v>1079.135</v>
+        <v>304.799</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3990,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46164.26041666666</v>
+        <v>46165.26041666666</v>
       </c>
       <c r="B123">
-        <v>-26.345</v>
+        <v>7.357</v>
       </c>
       <c r="C123">
-        <v>982.17</v>
+        <v>400</v>
       </c>
       <c r="D123">
-        <v>982.17</v>
+        <v>400</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +4010,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46164.27083333334</v>
+        <v>46165.27083333334</v>
       </c>
       <c r="B124">
-        <v>-24.328</v>
+        <v>-29.795</v>
       </c>
       <c r="C124">
-        <v>947.234</v>
+        <v>1032.04</v>
       </c>
       <c r="D124">
-        <v>947.234</v>
+        <v>1032.04</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +4030,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46164.28125</v>
+        <v>46165.28125</v>
       </c>
       <c r="B125">
-        <v>-45.203</v>
+        <v>-45.195</v>
       </c>
       <c r="C125">
-        <v>1859.176</v>
+        <v>1109.043</v>
       </c>
       <c r="D125">
-        <v>1859.176</v>
+        <v>1109.043</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +4050,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46164.29166666666</v>
+        <v>46165.29166666666</v>
       </c>
       <c r="B126">
-        <v>-46.009</v>
+        <v>-0.911</v>
       </c>
       <c r="C126">
-        <v>1163.461</v>
+        <v>913.319</v>
       </c>
       <c r="D126">
-        <v>1163.461</v>
+        <v>913.319</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +4070,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46164.30208333334</v>
+        <v>46165.30208333334</v>
       </c>
       <c r="B127">
-        <v>-83.779</v>
+        <v>-94.63500000000001</v>
       </c>
       <c r="C127">
-        <v>1985.174</v>
+        <v>3617.361</v>
       </c>
       <c r="D127">
-        <v>1985.174</v>
+        <v>3617.361</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +4090,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46164.3125</v>
+        <v>46165.3125</v>
       </c>
       <c r="B128">
-        <v>-108.139</v>
+        <v>-89.505</v>
       </c>
       <c r="C128">
-        <v>3149.064</v>
+        <v>967.463</v>
       </c>
       <c r="D128">
-        <v>3149.064</v>
+        <v>967.463</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +4110,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46164.32291666666</v>
+        <v>46165.32291666666</v>
       </c>
       <c r="B129">
-        <v>-61.647</v>
+        <v>-73.408</v>
       </c>
       <c r="C129">
-        <v>1183.113</v>
+        <v>969.736</v>
       </c>
       <c r="D129">
-        <v>1183.113</v>
+        <v>969.736</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +4130,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46164.33333333334</v>
+        <v>46165.33333333334</v>
       </c>
       <c r="B130">
-        <v>-35.381</v>
+        <v>-106.129</v>
       </c>
       <c r="C130">
-        <v>1099.616</v>
+        <v>720.996</v>
       </c>
       <c r="D130">
-        <v>1099.616</v>
+        <v>720.996</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +4150,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46164.34375</v>
+        <v>46165.34375</v>
       </c>
       <c r="B131">
-        <v>-41.944</v>
+        <v>-69.758</v>
       </c>
       <c r="C131">
-        <v>1100.166</v>
+        <v>720.78</v>
       </c>
       <c r="D131">
-        <v>1100.166</v>
+        <v>720.78</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +4170,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46164.35416666666</v>
+        <v>46165.35416666666</v>
       </c>
       <c r="B132">
-        <v>-94.14400000000001</v>
+        <v>-106.577</v>
       </c>
       <c r="C132">
-        <v>1164.678</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>1164.678</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +4190,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46164.36458333334</v>
+        <v>46165.36458333334</v>
       </c>
       <c r="B133">
-        <v>-57.253</v>
+        <v>-120.794</v>
       </c>
       <c r="C133">
-        <v>1084.975</v>
+        <v>720.774</v>
       </c>
       <c r="D133">
-        <v>1084.975</v>
+        <v>720.774</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +4210,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46164.375</v>
+        <v>46165.375</v>
       </c>
       <c r="B134">
-        <v>-73.89400000000001</v>
+        <v>-117.224</v>
       </c>
       <c r="C134">
-        <v>911.2140000000001</v>
+        <v>542.8</v>
       </c>
       <c r="D134">
-        <v>911.2140000000001</v>
+        <v>542.8</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +4230,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46164.38541666666</v>
+        <v>46165.38541666666</v>
       </c>
       <c r="B135">
-        <v>19.707</v>
+        <v>-80.14700000000001</v>
       </c>
       <c r="C135">
-        <v>385.634</v>
+        <v>2197.915</v>
       </c>
       <c r="D135">
-        <v>385.634</v>
+        <v>2197.915</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +4250,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46164.39583333334</v>
+        <v>46165.39583333334</v>
       </c>
       <c r="B136">
-        <v>21.381</v>
+        <v>3.766</v>
       </c>
       <c r="C136">
-        <v>401</v>
+        <v>-1455.041</v>
       </c>
       <c r="D136">
-        <v>401</v>
+        <v>-1455.041</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +4270,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46164.40625</v>
+        <v>46165.40625</v>
       </c>
       <c r="B137">
-        <v>8.913</v>
+        <v>31.24</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>-6520.77</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>-6520.77</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +4290,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46164.41666666666</v>
+        <v>46165.41666666666</v>
       </c>
       <c r="B138">
-        <v>-10.914</v>
+        <v>39.826</v>
       </c>
       <c r="C138">
-        <v>714.578</v>
+        <v>-1739.895</v>
       </c>
       <c r="D138">
-        <v>714.578</v>
+        <v>-1739.895</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +4310,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46164.42708333334</v>
+        <v>46165.42708333334</v>
       </c>
       <c r="B139">
-        <v>2.711</v>
+        <v>21.769</v>
       </c>
       <c r="C139">
-        <v>401</v>
+        <v>101.866</v>
       </c>
       <c r="D139">
-        <v>401</v>
+        <v>101.866</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +4330,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46164.4375</v>
+        <v>46165.4375</v>
       </c>
       <c r="B140">
-        <v>-54.363</v>
+        <v>23.714</v>
       </c>
       <c r="C140">
-        <v>755.428</v>
+        <v>-494.246</v>
       </c>
       <c r="D140">
-        <v>755.428</v>
+        <v>-494.246</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +4350,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46164.44791666666</v>
+        <v>46165.44791666666</v>
       </c>
       <c r="B141">
-        <v>-35.596</v>
+        <v>37.309</v>
       </c>
       <c r="C141">
-        <v>1213.064</v>
+        <v>-1083.455</v>
       </c>
       <c r="D141">
-        <v>1213.064</v>
+        <v>-1083.455</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +4370,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46164.45833333334</v>
+        <v>46165.45833333334</v>
       </c>
       <c r="B142">
-        <v>3.801</v>
+        <v>-24.501</v>
       </c>
       <c r="C142">
-        <v>31.143</v>
+        <v>664.917</v>
       </c>
       <c r="D142">
-        <v>31.143</v>
+        <v>664.917</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +4390,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46164.46875</v>
+        <v>46165.46875</v>
       </c>
       <c r="B143">
-        <v>7.867</v>
+        <v>-24.791</v>
       </c>
       <c r="C143">
-        <v>75.93899999999999</v>
+        <v>787.37</v>
       </c>
       <c r="D143">
-        <v>75.93899999999999</v>
+        <v>787.37</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +4410,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46164.47916666666</v>
+        <v>46165.47916666666</v>
       </c>
       <c r="B144">
-        <v>36.201</v>
+        <v>37.424</v>
       </c>
       <c r="C144">
-        <v>-126.494</v>
+        <v>19.439</v>
       </c>
       <c r="D144">
-        <v>-126.494</v>
+        <v>19.439</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +4430,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46164.48958333334</v>
+        <v>46165.48958333334</v>
       </c>
       <c r="B145">
-        <v>34.484</v>
+        <v>24.399</v>
       </c>
       <c r="C145">
-        <v>-250.341</v>
+        <v>-55.243</v>
       </c>
       <c r="D145">
-        <v>-250.341</v>
+        <v>-55.243</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +4450,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46164.5</v>
+        <v>46165.5</v>
       </c>
       <c r="B146">
-        <v>12.325</v>
+        <v>-67.005</v>
       </c>
       <c r="C146">
-        <v>-189.078</v>
+        <v>449.763</v>
       </c>
       <c r="D146">
-        <v>-189.078</v>
+        <v>449.763</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +4470,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46164.51041666666</v>
+        <v>46165.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>-2.553</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>672.138</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>672.138</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +4490,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46164.52083333334</v>
+        <v>46165.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>57.907</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>-4691.839</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>-4691.839</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +4510,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46164.53125</v>
+        <v>46165.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>31.247</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>-4845.481</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>-4845.481</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,16 +4530,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46164.54166666666</v>
+        <v>46165.54166666666</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>-33.328</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>1227.553</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>1227.553</v>
       </c>
       <c r="E150">
         <v>53</v>
@@ -3974,16 +4550,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46164.55208333334</v>
+        <v>46165.55208333334</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>-2.995</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>871.4299999999999</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>871.4299999999999</v>
       </c>
       <c r="E151">
         <v>54</v>
@@ -3994,16 +4570,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46164.5625</v>
+        <v>46165.5625</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>26.09</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>-90.919</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>-90.919</v>
       </c>
       <c r="E152">
         <v>55</v>
@@ -4014,16 +4590,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46164.57291666666</v>
+        <v>46165.57291666666</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>16.667</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>-35.565</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>-35.565</v>
       </c>
       <c r="E153">
         <v>56</v>
@@ -4034,16 +4610,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46164.58333333334</v>
+        <v>46165.58333333334</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>72.056</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>-156.639</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>-156.639</v>
       </c>
       <c r="E154">
         <v>57</v>
@@ -4054,16 +4630,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46164.59375</v>
+        <v>46165.59375</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>64.30500000000001</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>-89.593</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>-89.593</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4074,16 +4650,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46164.60416666666</v>
+        <v>46165.60416666666</v>
       </c>
       <c r="B156">
-        <v>0</v>
+        <v>69.95</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>-47.115</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>-47.115</v>
       </c>
       <c r="E156">
         <v>59</v>
@@ -4094,16 +4670,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46164.61458333334</v>
+        <v>46165.61458333334</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>96.465</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>-1486.057</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>-1486.057</v>
       </c>
       <c r="E157">
         <v>60</v>
@@ -4114,16 +4690,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46164.625</v>
+        <v>46165.625</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>92.03700000000001</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>-6862.91</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>-6862.91</v>
       </c>
       <c r="E158">
         <v>61</v>
@@ -4134,16 +4710,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46164.63541666666</v>
+        <v>46165.63541666666</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>122.988</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>-6552.895</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>-6552.895</v>
       </c>
       <c r="E159">
         <v>62</v>
@@ -4154,16 +4730,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46164.64583333334</v>
+        <v>46165.64583333334</v>
       </c>
       <c r="B160">
-        <v>0</v>
+        <v>146.872</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>-1809.982</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>-1809.982</v>
       </c>
       <c r="E160">
         <v>63</v>
@@ -4174,16 +4750,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46164.65625</v>
+        <v>46165.65625</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>170.609</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>-44.388</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>-44.388</v>
       </c>
       <c r="E161">
         <v>64</v>
@@ -4194,16 +4770,16 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46164.66666666666</v>
+        <v>46165.66666666666</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>98.746</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>-7354.874</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>-7354.874</v>
       </c>
       <c r="E162">
         <v>65</v>
@@ -4214,16 +4790,16 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46164.67708333334</v>
+        <v>46165.67708333334</v>
       </c>
       <c r="B163">
-        <v>0</v>
+        <v>76.074</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>-4600.222</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>-4600.222</v>
       </c>
       <c r="E163">
         <v>66</v>
@@ -4234,16 +4810,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46164.6875</v>
+        <v>46165.6875</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>45.824</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>-115.729</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>-115.729</v>
       </c>
       <c r="E164">
         <v>67</v>
@@ -4254,16 +4830,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46164.69791666666</v>
+        <v>46165.69791666666</v>
       </c>
       <c r="B165">
-        <v>0</v>
+        <v>16.987</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>372.439</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>372.439</v>
       </c>
       <c r="E165">
         <v>68</v>
@@ -4274,16 +4850,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46164.70833333334</v>
+        <v>46165.70833333334</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>138.147</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>-3116.591</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>-3116.591</v>
       </c>
       <c r="E166">
         <v>69</v>
@@ -4294,16 +4870,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46164.71875</v>
+        <v>46165.71875</v>
       </c>
       <c r="B167">
-        <v>0</v>
+        <v>56.812</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>322.8</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>322.8</v>
       </c>
       <c r="E167">
         <v>70</v>
@@ -4314,16 +4890,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46164.72916666666</v>
+        <v>46165.72916666666</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>0.981</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E168">
         <v>71</v>
@@ -4334,10 +4910,10 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46164.73958333334</v>
+        <v>46165.73958333334</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>3.177</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -4354,16 +4930,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46164.75</v>
+        <v>46165.75</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>-5.375</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1274.558</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>1274.558</v>
       </c>
       <c r="E170">
         <v>73</v>
@@ -4374,16 +4950,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46164.76041666666</v>
+        <v>46165.76041666666</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>-38.856</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1750.419</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>1750.419</v>
       </c>
       <c r="E171">
         <v>74</v>
@@ -4394,16 +4970,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46164.77083333334</v>
+        <v>46165.77083333334</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>-39.263</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>2888.573</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>2888.573</v>
       </c>
       <c r="E172">
         <v>75</v>
@@ -4414,16 +4990,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46164.78125</v>
+        <v>46165.78125</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>-49.936</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>5999</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>5999</v>
       </c>
       <c r="E173">
         <v>76</v>
@@ -4434,16 +5010,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46164.79166666666</v>
+        <v>46165.79166666666</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>9.23</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>280.889</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>280.889</v>
       </c>
       <c r="E174">
         <v>77</v>
@@ -4454,16 +5030,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46164.80208333334</v>
+        <v>46165.80208333334</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>49.831</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>-54.629</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>-54.629</v>
       </c>
       <c r="E175">
         <v>78</v>
@@ -4474,16 +5050,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46164.8125</v>
+        <v>46165.8125</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>51.651</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>270.694</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>270.694</v>
       </c>
       <c r="E176">
         <v>79</v>
@@ -4494,16 +5070,16 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46164.82291666666</v>
+        <v>46165.82291666666</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>310.667</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>310.667</v>
       </c>
       <c r="E177">
         <v>80</v>
@@ -4514,16 +5090,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46164.83333333334</v>
+        <v>46165.83333333334</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>58.368</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>-63.726</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>-63.726</v>
       </c>
       <c r="E178">
         <v>81</v>
@@ -4534,16 +5110,16 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46164.84375</v>
+        <v>46165.84375</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>-6.721</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1446.439</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>1446.439</v>
       </c>
       <c r="E179">
         <v>82</v>
@@ -4554,16 +5130,16 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46164.85416666666</v>
+        <v>46165.85416666666</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>-28.084</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>1824.528</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>1824.528</v>
       </c>
       <c r="E180">
         <v>83</v>
@@ -4574,16 +5150,16 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46164.86458333334</v>
+        <v>46165.86458333334</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>-115.903</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>6729.538</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>6729.538</v>
       </c>
       <c r="E181">
         <v>84</v>
@@ -4594,16 +5170,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46164.875</v>
+        <v>46165.875</v>
       </c>
       <c r="B182">
-        <v>0</v>
+        <v>-229.994</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>6999</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>6999</v>
       </c>
       <c r="E182">
         <v>85</v>
@@ -4614,16 +5190,16 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46164.88541666666</v>
+        <v>46165.88541666666</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>-129.713</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>2787.204</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>2787.204</v>
       </c>
       <c r="E183">
         <v>86</v>
@@ -4634,16 +5210,16 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46164.89583333334</v>
+        <v>46165.89583333334</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>-120.196</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>1575.921</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>1575.921</v>
       </c>
       <c r="E184">
         <v>87</v>
@@ -4654,16 +5230,16 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46164.90625</v>
+        <v>46165.90625</v>
       </c>
       <c r="B185">
-        <v>0</v>
+        <v>-237.09</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>4053.344</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>4053.344</v>
       </c>
       <c r="E185">
         <v>88</v>
@@ -4674,16 +5250,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46164.91666666666</v>
+        <v>46165.91666666666</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>-233.615</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>3901.995</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>3901.995</v>
       </c>
       <c r="E186">
         <v>89</v>
@@ -4694,16 +5270,16 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46164.92708333334</v>
+        <v>46165.92708333334</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>-258.43</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>3599.338</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>3599.338</v>
       </c>
       <c r="E187">
         <v>90</v>
@@ -4714,16 +5290,16 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46164.9375</v>
+        <v>46165.9375</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>-263.539</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>4015.545</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>4015.545</v>
       </c>
       <c r="E188">
         <v>91</v>
@@ -4734,16 +5310,16 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46164.94791666666</v>
+        <v>46165.94791666666</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>-263.912</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>4094.182</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>4094.182</v>
       </c>
       <c r="E189">
         <v>92</v>
@@ -4754,16 +5330,16 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46164.95833333334</v>
+        <v>46165.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>-247.198</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>2609.838</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>2609.838</v>
       </c>
       <c r="E190">
         <v>93</v>
@@ -4774,16 +5350,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46164.96875</v>
+        <v>46165.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>-177.115</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>1232.994</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>1232.994</v>
       </c>
       <c r="E191">
         <v>94</v>
@@ -4794,16 +5370,16 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46164.97916666666</v>
+        <v>46165.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>-153.479</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>1233.06</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>1233.06</v>
       </c>
       <c r="E192">
         <v>95</v>
@@ -4814,10 +5390,10 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46164.98958333334</v>
+        <v>46165.98958333334</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>-76.017</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -4830,6 +5406,3846 @@
       </c>
       <c r="F193" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B194">
+        <v>31.438</v>
+      </c>
+      <c r="C194">
+        <v>-1867.914</v>
+      </c>
+      <c r="D194">
+        <v>-1867.914</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="2">
+        <v>46166.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>9.093</v>
+      </c>
+      <c r="C195">
+        <v>328.379</v>
+      </c>
+      <c r="D195">
+        <v>328.379</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" s="2">
+        <v>46166.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>12.728</v>
+      </c>
+      <c r="C196">
+        <v>-5.356</v>
+      </c>
+      <c r="D196">
+        <v>-5.356</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" s="2">
+        <v>46166.03125</v>
+      </c>
+      <c r="B197">
+        <v>26.38</v>
+      </c>
+      <c r="C197">
+        <v>32.665</v>
+      </c>
+      <c r="D197">
+        <v>32.665</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
+      <c r="F197" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2">
+        <v>46166.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>28.697</v>
+      </c>
+      <c r="C198">
+        <v>163.495</v>
+      </c>
+      <c r="D198">
+        <v>163.495</v>
+      </c>
+      <c r="E198">
+        <v>5</v>
+      </c>
+      <c r="F198" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="2">
+        <v>46166.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>38.997</v>
+      </c>
+      <c r="C199">
+        <v>67.642</v>
+      </c>
+      <c r="D199">
+        <v>67.642</v>
+      </c>
+      <c r="E199">
+        <v>6</v>
+      </c>
+      <c r="F199" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="2">
+        <v>46166.0625</v>
+      </c>
+      <c r="B200">
+        <v>29.312</v>
+      </c>
+      <c r="C200">
+        <v>29.154</v>
+      </c>
+      <c r="D200">
+        <v>29.154</v>
+      </c>
+      <c r="E200">
+        <v>7</v>
+      </c>
+      <c r="F200" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="2">
+        <v>46166.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>17.778</v>
+      </c>
+      <c r="C201">
+        <v>26.323</v>
+      </c>
+      <c r="D201">
+        <v>26.323</v>
+      </c>
+      <c r="E201">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="2">
+        <v>46166.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>-0.859</v>
+      </c>
+      <c r="C202">
+        <v>896.2430000000001</v>
+      </c>
+      <c r="D202">
+        <v>896.2430000000001</v>
+      </c>
+      <c r="E202">
+        <v>9</v>
+      </c>
+      <c r="F202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="2">
+        <v>46166.09375</v>
+      </c>
+      <c r="B203">
+        <v>11.346</v>
+      </c>
+      <c r="C203">
+        <v>8.031000000000001</v>
+      </c>
+      <c r="D203">
+        <v>8.031000000000001</v>
+      </c>
+      <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="2">
+        <v>46166.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>8.722</v>
+      </c>
+      <c r="C204">
+        <v>141.302</v>
+      </c>
+      <c r="D204">
+        <v>141.302</v>
+      </c>
+      <c r="E204">
+        <v>11</v>
+      </c>
+      <c r="F204" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="2">
+        <v>46166.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>3.606</v>
+      </c>
+      <c r="C205">
+        <v>252.757</v>
+      </c>
+      <c r="D205">
+        <v>252.757</v>
+      </c>
+      <c r="E205">
+        <v>12</v>
+      </c>
+      <c r="F205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2">
+        <v>46166.125</v>
+      </c>
+      <c r="B206">
+        <v>17.138</v>
+      </c>
+      <c r="C206">
+        <v>-95.679</v>
+      </c>
+      <c r="D206">
+        <v>-95.679</v>
+      </c>
+      <c r="E206">
+        <v>13</v>
+      </c>
+      <c r="F206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="2">
+        <v>46166.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>34.751</v>
+      </c>
+      <c r="C207">
+        <v>-405.731</v>
+      </c>
+      <c r="D207">
+        <v>-405.731</v>
+      </c>
+      <c r="E207">
+        <v>14</v>
+      </c>
+      <c r="F207" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="2">
+        <v>46166.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>28.492</v>
+      </c>
+      <c r="C208">
+        <v>-874.6</v>
+      </c>
+      <c r="D208">
+        <v>-874.6</v>
+      </c>
+      <c r="E208">
+        <v>15</v>
+      </c>
+      <c r="F208" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" s="2">
+        <v>46166.15625</v>
+      </c>
+      <c r="B209">
+        <v>24.611</v>
+      </c>
+      <c r="C209">
+        <v>-29.186</v>
+      </c>
+      <c r="D209">
+        <v>-29.186</v>
+      </c>
+      <c r="E209">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" s="2">
+        <v>46166.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>29.997</v>
+      </c>
+      <c r="C210">
+        <v>116.904</v>
+      </c>
+      <c r="D210">
+        <v>116.904</v>
+      </c>
+      <c r="E210">
+        <v>17</v>
+      </c>
+      <c r="F210" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2">
+        <v>46166.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>26.275</v>
+      </c>
+      <c r="C211">
+        <v>85.447</v>
+      </c>
+      <c r="D211">
+        <v>85.447</v>
+      </c>
+      <c r="E211">
+        <v>18</v>
+      </c>
+      <c r="F211" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="2">
+        <v>46166.1875</v>
+      </c>
+      <c r="B212">
+        <v>12.547</v>
+      </c>
+      <c r="C212">
+        <v>123.003</v>
+      </c>
+      <c r="D212">
+        <v>123.003</v>
+      </c>
+      <c r="E212">
+        <v>19</v>
+      </c>
+      <c r="F212" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="2">
+        <v>46166.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>5.776</v>
+      </c>
+      <c r="C213">
+        <v>258.608</v>
+      </c>
+      <c r="D213">
+        <v>258.608</v>
+      </c>
+      <c r="E213">
+        <v>20</v>
+      </c>
+      <c r="F213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="2">
+        <v>46166.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>-12.641</v>
+      </c>
+      <c r="C214">
+        <v>853.6900000000001</v>
+      </c>
+      <c r="D214">
+        <v>853.6900000000001</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="2">
+        <v>46166.21875</v>
+      </c>
+      <c r="B215">
+        <v>-17.088</v>
+      </c>
+      <c r="C215">
+        <v>829.899</v>
+      </c>
+      <c r="D215">
+        <v>829.899</v>
+      </c>
+      <c r="E215">
+        <v>22</v>
+      </c>
+      <c r="F215" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="2">
+        <v>46166.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>-3.992</v>
+      </c>
+      <c r="C216">
+        <v>816.5</v>
+      </c>
+      <c r="D216">
+        <v>816.5</v>
+      </c>
+      <c r="E216">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="2">
+        <v>46166.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>-3.945</v>
+      </c>
+      <c r="C217">
+        <v>800</v>
+      </c>
+      <c r="D217">
+        <v>800</v>
+      </c>
+      <c r="E217">
+        <v>24</v>
+      </c>
+      <c r="F217" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" s="2">
+        <v>46166.25</v>
+      </c>
+      <c r="B218">
+        <v>-47.169</v>
+      </c>
+      <c r="C218">
+        <v>851.097</v>
+      </c>
+      <c r="D218">
+        <v>851.097</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+      <c r="F218" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2">
+        <v>46166.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>-54.096</v>
+      </c>
+      <c r="C219">
+        <v>864.811</v>
+      </c>
+      <c r="D219">
+        <v>864.811</v>
+      </c>
+      <c r="E219">
+        <v>26</v>
+      </c>
+      <c r="F219" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="2">
+        <v>46166.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>-29.99</v>
+      </c>
+      <c r="C220">
+        <v>1023.811</v>
+      </c>
+      <c r="D220">
+        <v>1023.811</v>
+      </c>
+      <c r="E220">
+        <v>27</v>
+      </c>
+      <c r="F220" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="2">
+        <v>46166.28125</v>
+      </c>
+      <c r="B221">
+        <v>-31.868</v>
+      </c>
+      <c r="C221">
+        <v>843.26</v>
+      </c>
+      <c r="D221">
+        <v>843.26</v>
+      </c>
+      <c r="E221">
+        <v>28</v>
+      </c>
+      <c r="F221" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" s="2">
+        <v>46166.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>-126.906</v>
+      </c>
+      <c r="C222">
+        <v>896.516</v>
+      </c>
+      <c r="D222">
+        <v>896.516</v>
+      </c>
+      <c r="E222">
+        <v>29</v>
+      </c>
+      <c r="F222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" s="2">
+        <v>46166.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>-73.047</v>
+      </c>
+      <c r="C223">
+        <v>1249.496</v>
+      </c>
+      <c r="D223">
+        <v>1249.496</v>
+      </c>
+      <c r="E223">
+        <v>30</v>
+      </c>
+      <c r="F223" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2">
+        <v>46166.3125</v>
+      </c>
+      <c r="B224">
+        <v>-40.407</v>
+      </c>
+      <c r="C224">
+        <v>855.221</v>
+      </c>
+      <c r="D224">
+        <v>855.221</v>
+      </c>
+      <c r="E224">
+        <v>31</v>
+      </c>
+      <c r="F224" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="2">
+        <v>46166.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>-54.023</v>
+      </c>
+      <c r="C225">
+        <v>880.845</v>
+      </c>
+      <c r="D225">
+        <v>880.845</v>
+      </c>
+      <c r="E225">
+        <v>32</v>
+      </c>
+      <c r="F225" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="2">
+        <v>46166.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>-75.672</v>
+      </c>
+      <c r="C226">
+        <v>499.22</v>
+      </c>
+      <c r="D226">
+        <v>499.22</v>
+      </c>
+      <c r="E226">
+        <v>33</v>
+      </c>
+      <c r="F226" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="2">
+        <v>46166.34375</v>
+      </c>
+      <c r="B227">
+        <v>-34.009</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>34</v>
+      </c>
+      <c r="F227" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="2">
+        <v>46166.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>27.795</v>
+      </c>
+      <c r="C228">
+        <v>-277.588</v>
+      </c>
+      <c r="D228">
+        <v>-277.588</v>
+      </c>
+      <c r="E228">
+        <v>35</v>
+      </c>
+      <c r="F228" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="2">
+        <v>46166.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>35.122</v>
+      </c>
+      <c r="C229">
+        <v>-252.563</v>
+      </c>
+      <c r="D229">
+        <v>-252.563</v>
+      </c>
+      <c r="E229">
+        <v>36</v>
+      </c>
+      <c r="F229" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="2">
+        <v>46166.375</v>
+      </c>
+      <c r="B230">
+        <v>10.491</v>
+      </c>
+      <c r="C230">
+        <v>44.201</v>
+      </c>
+      <c r="D230">
+        <v>44.201</v>
+      </c>
+      <c r="E230">
+        <v>37</v>
+      </c>
+      <c r="F230" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" s="2">
+        <v>46166.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>45.958</v>
+      </c>
+      <c r="C231">
+        <v>-97.45699999999999</v>
+      </c>
+      <c r="D231">
+        <v>-97.45699999999999</v>
+      </c>
+      <c r="E231">
+        <v>38</v>
+      </c>
+      <c r="F231" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2">
+        <v>46166.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>42.761</v>
+      </c>
+      <c r="C232">
+        <v>-98.919</v>
+      </c>
+      <c r="D232">
+        <v>-98.919</v>
+      </c>
+      <c r="E232">
+        <v>39</v>
+      </c>
+      <c r="F232" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="2">
+        <v>46166.40625</v>
+      </c>
+      <c r="B233">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="C233">
+        <v>-114.752</v>
+      </c>
+      <c r="D233">
+        <v>-114.752</v>
+      </c>
+      <c r="E233">
+        <v>40</v>
+      </c>
+      <c r="F233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="2">
+        <v>46166.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>27.164</v>
+      </c>
+      <c r="C234">
+        <v>-124.189</v>
+      </c>
+      <c r="D234">
+        <v>-124.189</v>
+      </c>
+      <c r="E234">
+        <v>41</v>
+      </c>
+      <c r="F234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" s="2">
+        <v>46166.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>54.839</v>
+      </c>
+      <c r="C235">
+        <v>33.111</v>
+      </c>
+      <c r="D235">
+        <v>33.111</v>
+      </c>
+      <c r="E235">
+        <v>42</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" s="2">
+        <v>46166.4375</v>
+      </c>
+      <c r="B236">
+        <v>24.593</v>
+      </c>
+      <c r="C236">
+        <v>8.858000000000001</v>
+      </c>
+      <c r="D236">
+        <v>8.858000000000001</v>
+      </c>
+      <c r="E236">
+        <v>43</v>
+      </c>
+      <c r="F236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2">
+        <v>46166.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>-2.612</v>
+      </c>
+      <c r="C237">
+        <v>140.634</v>
+      </c>
+      <c r="D237">
+        <v>140.634</v>
+      </c>
+      <c r="E237">
+        <v>44</v>
+      </c>
+      <c r="F237" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="2">
+        <v>46166.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>5.9</v>
+      </c>
+      <c r="C238">
+        <v>210.482</v>
+      </c>
+      <c r="D238">
+        <v>210.482</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="2">
+        <v>46166.46875</v>
+      </c>
+      <c r="B239">
+        <v>0.848</v>
+      </c>
+      <c r="C239">
+        <v>481.891</v>
+      </c>
+      <c r="D239">
+        <v>481.891</v>
+      </c>
+      <c r="E239">
+        <v>46</v>
+      </c>
+      <c r="F239" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="2">
+        <v>46166.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>20.324</v>
+      </c>
+      <c r="C240">
+        <v>8.372999999999999</v>
+      </c>
+      <c r="D240">
+        <v>8.372999999999999</v>
+      </c>
+      <c r="E240">
+        <v>47</v>
+      </c>
+      <c r="F240" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="2">
+        <v>46166.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>91.93300000000001</v>
+      </c>
+      <c r="C241">
+        <v>-57.906</v>
+      </c>
+      <c r="D241">
+        <v>-57.906</v>
+      </c>
+      <c r="E241">
+        <v>48</v>
+      </c>
+      <c r="F241" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="2">
+        <v>46166.5</v>
+      </c>
+      <c r="B242">
+        <v>57.018</v>
+      </c>
+      <c r="C242">
+        <v>128.829</v>
+      </c>
+      <c r="D242">
+        <v>128.829</v>
+      </c>
+      <c r="E242">
+        <v>49</v>
+      </c>
+      <c r="F242" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="2">
+        <v>46166.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>75.51300000000001</v>
+      </c>
+      <c r="C243">
+        <v>61.871</v>
+      </c>
+      <c r="D243">
+        <v>61.871</v>
+      </c>
+      <c r="E243">
+        <v>50</v>
+      </c>
+      <c r="F243" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" s="2">
+        <v>46166.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>103.395</v>
+      </c>
+      <c r="C244">
+        <v>-5041.723</v>
+      </c>
+      <c r="D244">
+        <v>-5041.723</v>
+      </c>
+      <c r="E244">
+        <v>51</v>
+      </c>
+      <c r="F244" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2">
+        <v>46166.53125</v>
+      </c>
+      <c r="B245">
+        <v>127.011</v>
+      </c>
+      <c r="C245">
+        <v>-1450.45</v>
+      </c>
+      <c r="D245">
+        <v>-1450.45</v>
+      </c>
+      <c r="E245">
+        <v>52</v>
+      </c>
+      <c r="F245" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="2">
+        <v>46166.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>121.794</v>
+      </c>
+      <c r="C246">
+        <v>-939.2910000000001</v>
+      </c>
+      <c r="D246">
+        <v>-939.2910000000001</v>
+      </c>
+      <c r="E246">
+        <v>53</v>
+      </c>
+      <c r="F246" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="2">
+        <v>46166.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>88.04600000000001</v>
+      </c>
+      <c r="C247">
+        <v>-865.471</v>
+      </c>
+      <c r="D247">
+        <v>-865.471</v>
+      </c>
+      <c r="E247">
+        <v>54</v>
+      </c>
+      <c r="F247" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" s="2">
+        <v>46166.5625</v>
+      </c>
+      <c r="B248">
+        <v>65.307</v>
+      </c>
+      <c r="C248">
+        <v>-403.988</v>
+      </c>
+      <c r="D248">
+        <v>-403.988</v>
+      </c>
+      <c r="E248">
+        <v>55</v>
+      </c>
+      <c r="F248" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" s="2">
+        <v>46166.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>43.212</v>
+      </c>
+      <c r="C249">
+        <v>-614.451</v>
+      </c>
+      <c r="D249">
+        <v>-614.451</v>
+      </c>
+      <c r="E249">
+        <v>56</v>
+      </c>
+      <c r="F249" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2">
+        <v>46166.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>34.374</v>
+      </c>
+      <c r="C250">
+        <v>66.05200000000001</v>
+      </c>
+      <c r="D250">
+        <v>66.05200000000001</v>
+      </c>
+      <c r="E250">
+        <v>57</v>
+      </c>
+      <c r="F250" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="2">
+        <v>46166.59375</v>
+      </c>
+      <c r="B251">
+        <v>46.999</v>
+      </c>
+      <c r="C251">
+        <v>-1507.233</v>
+      </c>
+      <c r="D251">
+        <v>-1507.233</v>
+      </c>
+      <c r="E251">
+        <v>58</v>
+      </c>
+      <c r="F251" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="2">
+        <v>46166.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>42.571</v>
+      </c>
+      <c r="C252">
+        <v>-1627.906</v>
+      </c>
+      <c r="D252">
+        <v>-1627.906</v>
+      </c>
+      <c r="E252">
+        <v>59</v>
+      </c>
+      <c r="F252" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="2">
+        <v>46166.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>44.145</v>
+      </c>
+      <c r="C253">
+        <v>-191.753</v>
+      </c>
+      <c r="D253">
+        <v>-191.753</v>
+      </c>
+      <c r="E253">
+        <v>60</v>
+      </c>
+      <c r="F253" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="2">
+        <v>46166.625</v>
+      </c>
+      <c r="B254">
+        <v>52.148</v>
+      </c>
+      <c r="C254">
+        <v>-4086.57</v>
+      </c>
+      <c r="D254">
+        <v>-4086.57</v>
+      </c>
+      <c r="E254">
+        <v>61</v>
+      </c>
+      <c r="F254" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="2">
+        <v>46166.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>46.542</v>
+      </c>
+      <c r="C255">
+        <v>-1279.615</v>
+      </c>
+      <c r="D255">
+        <v>-1279.615</v>
+      </c>
+      <c r="E255">
+        <v>62</v>
+      </c>
+      <c r="F255" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="2">
+        <v>46166.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>31.476</v>
+      </c>
+      <c r="C256">
+        <v>-1986.471</v>
+      </c>
+      <c r="D256">
+        <v>-1986.471</v>
+      </c>
+      <c r="E256">
+        <v>63</v>
+      </c>
+      <c r="F256" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" s="2">
+        <v>46166.65625</v>
+      </c>
+      <c r="B257">
+        <v>29.783</v>
+      </c>
+      <c r="C257">
+        <v>-215.226</v>
+      </c>
+      <c r="D257">
+        <v>-215.226</v>
+      </c>
+      <c r="E257">
+        <v>64</v>
+      </c>
+      <c r="F257" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2">
+        <v>46166.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>10.842</v>
+      </c>
+      <c r="C258">
+        <v>-333.752</v>
+      </c>
+      <c r="D258">
+        <v>-333.752</v>
+      </c>
+      <c r="E258">
+        <v>65</v>
+      </c>
+      <c r="F258" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="2">
+        <v>46166.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>-13.068</v>
+      </c>
+      <c r="C259">
+        <v>450</v>
+      </c>
+      <c r="D259">
+        <v>450</v>
+      </c>
+      <c r="E259">
+        <v>66</v>
+      </c>
+      <c r="F259" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="2">
+        <v>46166.6875</v>
+      </c>
+      <c r="B260">
+        <v>4.027</v>
+      </c>
+      <c r="C260">
+        <v>380.563</v>
+      </c>
+      <c r="D260">
+        <v>380.563</v>
+      </c>
+      <c r="E260">
+        <v>67</v>
+      </c>
+      <c r="F260" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" s="2">
+        <v>46166.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>-10.254</v>
+      </c>
+      <c r="C261">
+        <v>513.576</v>
+      </c>
+      <c r="D261">
+        <v>513.576</v>
+      </c>
+      <c r="E261">
+        <v>68</v>
+      </c>
+      <c r="F261" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" s="2">
+        <v>46166.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>17.774</v>
+      </c>
+      <c r="C262">
+        <v>-267.919</v>
+      </c>
+      <c r="D262">
+        <v>-267.919</v>
+      </c>
+      <c r="E262">
+        <v>69</v>
+      </c>
+      <c r="F262" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" s="2">
+        <v>46166.71875</v>
+      </c>
+      <c r="B263">
+        <v>26.259</v>
+      </c>
+      <c r="C263">
+        <v>-3271.324</v>
+      </c>
+      <c r="D263">
+        <v>-3271.324</v>
+      </c>
+      <c r="E263">
+        <v>70</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" s="2">
+        <v>46166.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>-4.858</v>
+      </c>
+      <c r="C264">
+        <v>540.1900000000001</v>
+      </c>
+      <c r="D264">
+        <v>540.1900000000001</v>
+      </c>
+      <c r="E264">
+        <v>71</v>
+      </c>
+      <c r="F264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" s="2">
+        <v>46166.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>7.662</v>
+      </c>
+      <c r="C265">
+        <v>39.96</v>
+      </c>
+      <c r="D265">
+        <v>39.96</v>
+      </c>
+      <c r="E265">
+        <v>72</v>
+      </c>
+      <c r="F265" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" s="2">
+        <v>46166.75</v>
+      </c>
+      <c r="B266">
+        <v>20.629</v>
+      </c>
+      <c r="C266">
+        <v>-1590.243</v>
+      </c>
+      <c r="D266">
+        <v>-1590.243</v>
+      </c>
+      <c r="E266">
+        <v>73</v>
+      </c>
+      <c r="F266" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" s="2">
+        <v>46166.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>-4.461</v>
+      </c>
+      <c r="C267">
+        <v>1008.121</v>
+      </c>
+      <c r="D267">
+        <v>1008.121</v>
+      </c>
+      <c r="E267">
+        <v>74</v>
+      </c>
+      <c r="F267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" s="2">
+        <v>46166.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>-42.363</v>
+      </c>
+      <c r="C268">
+        <v>1816.142</v>
+      </c>
+      <c r="D268">
+        <v>1816.142</v>
+      </c>
+      <c r="E268">
+        <v>75</v>
+      </c>
+      <c r="F268" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" s="2">
+        <v>46166.78125</v>
+      </c>
+      <c r="B269">
+        <v>-80.392</v>
+      </c>
+      <c r="C269">
+        <v>3865.789</v>
+      </c>
+      <c r="D269">
+        <v>3865.789</v>
+      </c>
+      <c r="E269">
+        <v>76</v>
+      </c>
+      <c r="F269" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" s="2">
+        <v>46166.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>-44.465</v>
+      </c>
+      <c r="C270">
+        <v>2589.139</v>
+      </c>
+      <c r="D270">
+        <v>2589.139</v>
+      </c>
+      <c r="E270">
+        <v>77</v>
+      </c>
+      <c r="F270" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" s="2">
+        <v>46166.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>-50.361</v>
+      </c>
+      <c r="C271">
+        <v>1636.788</v>
+      </c>
+      <c r="D271">
+        <v>1636.788</v>
+      </c>
+      <c r="E271">
+        <v>78</v>
+      </c>
+      <c r="F271" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" s="2">
+        <v>46166.8125</v>
+      </c>
+      <c r="B272">
+        <v>-50.017</v>
+      </c>
+      <c r="C272">
+        <v>1645.627</v>
+      </c>
+      <c r="D272">
+        <v>1645.627</v>
+      </c>
+      <c r="E272">
+        <v>79</v>
+      </c>
+      <c r="F272" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" s="2">
+        <v>46166.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>-56.54</v>
+      </c>
+      <c r="C273">
+        <v>1428.602</v>
+      </c>
+      <c r="D273">
+        <v>1428.602</v>
+      </c>
+      <c r="E273">
+        <v>80</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" s="2">
+        <v>46166.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>-26.854</v>
+      </c>
+      <c r="C274">
+        <v>1167.531</v>
+      </c>
+      <c r="D274">
+        <v>1167.531</v>
+      </c>
+      <c r="E274">
+        <v>81</v>
+      </c>
+      <c r="F274" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" s="2">
+        <v>46166.84375</v>
+      </c>
+      <c r="B275">
+        <v>-20.106</v>
+      </c>
+      <c r="C275">
+        <v>1298.663</v>
+      </c>
+      <c r="D275">
+        <v>1298.663</v>
+      </c>
+      <c r="E275">
+        <v>82</v>
+      </c>
+      <c r="F275" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" s="2">
+        <v>46166.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>-29.98</v>
+      </c>
+      <c r="C276">
+        <v>1001.378</v>
+      </c>
+      <c r="D276">
+        <v>1001.378</v>
+      </c>
+      <c r="E276">
+        <v>83</v>
+      </c>
+      <c r="F276" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" s="2">
+        <v>46166.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>-39.177</v>
+      </c>
+      <c r="C277">
+        <v>1039.494</v>
+      </c>
+      <c r="D277">
+        <v>1039.494</v>
+      </c>
+      <c r="E277">
+        <v>84</v>
+      </c>
+      <c r="F277" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" s="2">
+        <v>46166.875</v>
+      </c>
+      <c r="B278">
+        <v>-68.023</v>
+      </c>
+      <c r="C278">
+        <v>1540.23</v>
+      </c>
+      <c r="D278">
+        <v>1540.23</v>
+      </c>
+      <c r="E278">
+        <v>85</v>
+      </c>
+      <c r="F278" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" s="2">
+        <v>46166.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>-67.05500000000001</v>
+      </c>
+      <c r="C279">
+        <v>1457.4</v>
+      </c>
+      <c r="D279">
+        <v>1457.4</v>
+      </c>
+      <c r="E279">
+        <v>86</v>
+      </c>
+      <c r="F279" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" s="2">
+        <v>46166.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>-12.824</v>
+      </c>
+      <c r="C280">
+        <v>1031.137</v>
+      </c>
+      <c r="D280">
+        <v>1031.137</v>
+      </c>
+      <c r="E280">
+        <v>87</v>
+      </c>
+      <c r="F280" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" s="2">
+        <v>46166.90625</v>
+      </c>
+      <c r="B281">
+        <v>-7.488</v>
+      </c>
+      <c r="C281">
+        <v>997.679</v>
+      </c>
+      <c r="D281">
+        <v>997.679</v>
+      </c>
+      <c r="E281">
+        <v>88</v>
+      </c>
+      <c r="F281" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" s="2">
+        <v>46166.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>-35.093</v>
+      </c>
+      <c r="C282">
+        <v>930.413</v>
+      </c>
+      <c r="D282">
+        <v>930.413</v>
+      </c>
+      <c r="E282">
+        <v>89</v>
+      </c>
+      <c r="F282" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" s="2">
+        <v>46166.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>-11.993</v>
+      </c>
+      <c r="C283">
+        <v>937.8869999999999</v>
+      </c>
+      <c r="D283">
+        <v>937.8869999999999</v>
+      </c>
+      <c r="E283">
+        <v>90</v>
+      </c>
+      <c r="F283" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" s="2">
+        <v>46166.9375</v>
+      </c>
+      <c r="B284">
+        <v>13.063</v>
+      </c>
+      <c r="C284">
+        <v>271.556</v>
+      </c>
+      <c r="D284">
+        <v>271.556</v>
+      </c>
+      <c r="E284">
+        <v>91</v>
+      </c>
+      <c r="F284" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" s="2">
+        <v>46166.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>20.122</v>
+      </c>
+      <c r="C285">
+        <v>171.262</v>
+      </c>
+      <c r="D285">
+        <v>171.262</v>
+      </c>
+      <c r="E285">
+        <v>92</v>
+      </c>
+      <c r="F285" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" s="2">
+        <v>46166.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>-12.818</v>
+      </c>
+      <c r="C286">
+        <v>1097.429</v>
+      </c>
+      <c r="D286">
+        <v>1097.429</v>
+      </c>
+      <c r="E286">
+        <v>93</v>
+      </c>
+      <c r="F286" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" s="2">
+        <v>46166.96875</v>
+      </c>
+      <c r="B287">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="C287">
+        <v>268.365</v>
+      </c>
+      <c r="D287">
+        <v>268.365</v>
+      </c>
+      <c r="E287">
+        <v>94</v>
+      </c>
+      <c r="F287" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" s="2">
+        <v>46166.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>-0.119</v>
+      </c>
+      <c r="C288">
+        <v>891.067</v>
+      </c>
+      <c r="D288">
+        <v>891.067</v>
+      </c>
+      <c r="E288">
+        <v>95</v>
+      </c>
+      <c r="F288" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" s="2">
+        <v>46166.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>-2.732</v>
+      </c>
+      <c r="C289">
+        <v>877.994</v>
+      </c>
+      <c r="D289">
+        <v>877.994</v>
+      </c>
+      <c r="E289">
+        <v>96</v>
+      </c>
+      <c r="F289" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B290">
+        <v>-40.623</v>
+      </c>
+      <c r="C290">
+        <v>1078.305</v>
+      </c>
+      <c r="D290">
+        <v>1078.305</v>
+      </c>
+      <c r="E290">
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" s="2">
+        <v>46167.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>-32.765</v>
+      </c>
+      <c r="C291">
+        <v>1139.549</v>
+      </c>
+      <c r="D291">
+        <v>1139.549</v>
+      </c>
+      <c r="E291">
+        <v>2</v>
+      </c>
+      <c r="F291" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" s="2">
+        <v>46167.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>-26.8</v>
+      </c>
+      <c r="C292">
+        <v>1117.816</v>
+      </c>
+      <c r="D292">
+        <v>1117.816</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
+      <c r="F292" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" s="2">
+        <v>46167.03125</v>
+      </c>
+      <c r="B293">
+        <v>-30.717</v>
+      </c>
+      <c r="C293">
+        <v>901.538</v>
+      </c>
+      <c r="D293">
+        <v>901.538</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
+      <c r="F293" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" s="2">
+        <v>46167.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>-33.871</v>
+      </c>
+      <c r="C294">
+        <v>1448.086</v>
+      </c>
+      <c r="D294">
+        <v>1448.086</v>
+      </c>
+      <c r="E294">
+        <v>5</v>
+      </c>
+      <c r="F294" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" s="2">
+        <v>46167.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>-24.831</v>
+      </c>
+      <c r="C295">
+        <v>1243.303</v>
+      </c>
+      <c r="D295">
+        <v>1243.303</v>
+      </c>
+      <c r="E295">
+        <v>6</v>
+      </c>
+      <c r="F295" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" s="2">
+        <v>46167.0625</v>
+      </c>
+      <c r="B296">
+        <v>-25.505</v>
+      </c>
+      <c r="C296">
+        <v>1332.922</v>
+      </c>
+      <c r="D296">
+        <v>1332.922</v>
+      </c>
+      <c r="E296">
+        <v>7</v>
+      </c>
+      <c r="F296" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" s="2">
+        <v>46167.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>-24.27</v>
+      </c>
+      <c r="C297">
+        <v>1170.089</v>
+      </c>
+      <c r="D297">
+        <v>1170.089</v>
+      </c>
+      <c r="E297">
+        <v>8</v>
+      </c>
+      <c r="F297" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" s="2">
+        <v>46167.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>-7.174</v>
+      </c>
+      <c r="C298">
+        <v>989.48</v>
+      </c>
+      <c r="D298">
+        <v>989.48</v>
+      </c>
+      <c r="E298">
+        <v>9</v>
+      </c>
+      <c r="F298" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" s="2">
+        <v>46167.09375</v>
+      </c>
+      <c r="B299">
+        <v>10.012</v>
+      </c>
+      <c r="C299">
+        <v>400</v>
+      </c>
+      <c r="D299">
+        <v>400</v>
+      </c>
+      <c r="E299">
+        <v>10</v>
+      </c>
+      <c r="F299" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" s="2">
+        <v>46167.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>51.928</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>11</v>
+      </c>
+      <c r="F300" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" s="2">
+        <v>46167.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>99.71599999999999</v>
+      </c>
+      <c r="C301">
+        <v>374.693</v>
+      </c>
+      <c r="D301">
+        <v>374.693</v>
+      </c>
+      <c r="E301">
+        <v>12</v>
+      </c>
+      <c r="F301" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" s="2">
+        <v>46167.125</v>
+      </c>
+      <c r="B302">
+        <v>124.424</v>
+      </c>
+      <c r="C302">
+        <v>378.163</v>
+      </c>
+      <c r="D302">
+        <v>378.163</v>
+      </c>
+      <c r="E302">
+        <v>13</v>
+      </c>
+      <c r="F302" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" s="2">
+        <v>46167.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>86.88800000000001</v>
+      </c>
+      <c r="C303">
+        <v>14.444</v>
+      </c>
+      <c r="D303">
+        <v>14.444</v>
+      </c>
+      <c r="E303">
+        <v>14</v>
+      </c>
+      <c r="F303" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" s="2">
+        <v>46167.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>40.906</v>
+      </c>
+      <c r="C304">
+        <v>-8.315</v>
+      </c>
+      <c r="D304">
+        <v>-8.315</v>
+      </c>
+      <c r="E304">
+        <v>15</v>
+      </c>
+      <c r="F304" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" s="2">
+        <v>46167.15625</v>
+      </c>
+      <c r="B305">
+        <v>26.362</v>
+      </c>
+      <c r="C305">
+        <v>212.262</v>
+      </c>
+      <c r="D305">
+        <v>212.262</v>
+      </c>
+      <c r="E305">
+        <v>16</v>
+      </c>
+      <c r="F305" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" s="2">
+        <v>46167.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>-9.177</v>
+      </c>
+      <c r="C306">
+        <v>850.148</v>
+      </c>
+      <c r="D306">
+        <v>850.148</v>
+      </c>
+      <c r="E306">
+        <v>17</v>
+      </c>
+      <c r="F306" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" s="2">
+        <v>46167.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>-24.727</v>
+      </c>
+      <c r="C307">
+        <v>828.696</v>
+      </c>
+      <c r="D307">
+        <v>828.696</v>
+      </c>
+      <c r="E307">
+        <v>18</v>
+      </c>
+      <c r="F307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" s="2">
+        <v>46167.1875</v>
+      </c>
+      <c r="B308">
+        <v>-30.554</v>
+      </c>
+      <c r="C308">
+        <v>800</v>
+      </c>
+      <c r="D308">
+        <v>800</v>
+      </c>
+      <c r="E308">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" s="2">
+        <v>46167.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>-8.811999999999999</v>
+      </c>
+      <c r="C309">
+        <v>883.6</v>
+      </c>
+      <c r="D309">
+        <v>883.6</v>
+      </c>
+      <c r="E309">
+        <v>20</v>
+      </c>
+      <c r="F309" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" s="2">
+        <v>46167.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>56.484</v>
+      </c>
+      <c r="C310">
+        <v>60.301</v>
+      </c>
+      <c r="D310">
+        <v>60.301</v>
+      </c>
+      <c r="E310">
+        <v>21</v>
+      </c>
+      <c r="F310" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" s="2">
+        <v>46167.21875</v>
+      </c>
+      <c r="B311">
+        <v>64.895</v>
+      </c>
+      <c r="C311">
+        <v>-105.634</v>
+      </c>
+      <c r="D311">
+        <v>-105.634</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" s="2">
+        <v>46167.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>78.913</v>
+      </c>
+      <c r="C312">
+        <v>-124.998</v>
+      </c>
+      <c r="D312">
+        <v>-124.998</v>
+      </c>
+      <c r="E312">
+        <v>23</v>
+      </c>
+      <c r="F312" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" s="2">
+        <v>46167.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>70.238</v>
+      </c>
+      <c r="C313">
+        <v>-135.928</v>
+      </c>
+      <c r="D313">
+        <v>-135.928</v>
+      </c>
+      <c r="E313">
+        <v>24</v>
+      </c>
+      <c r="F313" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
+      <c r="A314" s="2">
+        <v>46167.25</v>
+      </c>
+      <c r="B314">
+        <v>102.269</v>
+      </c>
+      <c r="C314">
+        <v>81.172</v>
+      </c>
+      <c r="D314">
+        <v>81.172</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+      <c r="F314" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
+      <c r="A315" s="2">
+        <v>46167.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>114.222</v>
+      </c>
+      <c r="C315">
+        <v>349.495</v>
+      </c>
+      <c r="D315">
+        <v>349.495</v>
+      </c>
+      <c r="E315">
+        <v>26</v>
+      </c>
+      <c r="F315" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
+      <c r="A316" s="2">
+        <v>46167.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>72.26900000000001</v>
+      </c>
+      <c r="C316">
+        <v>-83.45999999999999</v>
+      </c>
+      <c r="D316">
+        <v>-83.45999999999999</v>
+      </c>
+      <c r="E316">
+        <v>27</v>
+      </c>
+      <c r="F316" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
+      <c r="A317" s="2">
+        <v>46167.28125</v>
+      </c>
+      <c r="B317">
+        <v>62.753</v>
+      </c>
+      <c r="C317">
+        <v>-1334.451</v>
+      </c>
+      <c r="D317">
+        <v>-1334.451</v>
+      </c>
+      <c r="E317">
+        <v>28</v>
+      </c>
+      <c r="F317" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
+      <c r="A318" s="2">
+        <v>46167.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>76.577</v>
+      </c>
+      <c r="C318">
+        <v>42.177</v>
+      </c>
+      <c r="D318">
+        <v>42.177</v>
+      </c>
+      <c r="E318">
+        <v>29</v>
+      </c>
+      <c r="F318" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
+      <c r="A319" s="2">
+        <v>46167.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>58.089</v>
+      </c>
+      <c r="C319">
+        <v>5.141</v>
+      </c>
+      <c r="D319">
+        <v>5.141</v>
+      </c>
+      <c r="E319">
+        <v>30</v>
+      </c>
+      <c r="F319" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
+      <c r="A320" s="2">
+        <v>46167.3125</v>
+      </c>
+      <c r="B320">
+        <v>31.081</v>
+      </c>
+      <c r="C320">
+        <v>0.978</v>
+      </c>
+      <c r="D320">
+        <v>0.978</v>
+      </c>
+      <c r="E320">
+        <v>31</v>
+      </c>
+      <c r="F320" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
+      <c r="A321" s="2">
+        <v>46167.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>75.95</v>
+      </c>
+      <c r="C321">
+        <v>-14.482</v>
+      </c>
+      <c r="D321">
+        <v>-14.482</v>
+      </c>
+      <c r="E321">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
+      <c r="A322" s="2">
+        <v>46167.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>17.313</v>
+      </c>
+      <c r="C322">
+        <v>-3.388</v>
+      </c>
+      <c r="D322">
+        <v>-3.388</v>
+      </c>
+      <c r="E322">
+        <v>33</v>
+      </c>
+      <c r="F322" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
+      <c r="A323" s="2">
+        <v>46167.34375</v>
+      </c>
+      <c r="B323">
+        <v>32.455</v>
+      </c>
+      <c r="C323">
+        <v>0.016</v>
+      </c>
+      <c r="D323">
+        <v>0.016</v>
+      </c>
+      <c r="E323">
+        <v>34</v>
+      </c>
+      <c r="F323" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
+      <c r="A324" s="2">
+        <v>46167.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>53.049</v>
+      </c>
+      <c r="C324">
+        <v>4.701</v>
+      </c>
+      <c r="D324">
+        <v>4.701</v>
+      </c>
+      <c r="E324">
+        <v>35</v>
+      </c>
+      <c r="F324" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
+      <c r="A325" s="2">
+        <v>46167.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>39.762</v>
+      </c>
+      <c r="C325">
+        <v>3.754</v>
+      </c>
+      <c r="D325">
+        <v>3.754</v>
+      </c>
+      <c r="E325">
+        <v>36</v>
+      </c>
+      <c r="F325" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
+      <c r="A326" s="2">
+        <v>46167.375</v>
+      </c>
+      <c r="B326">
+        <v>34.378</v>
+      </c>
+      <c r="C326">
+        <v>5.197</v>
+      </c>
+      <c r="D326">
+        <v>5.197</v>
+      </c>
+      <c r="E326">
+        <v>37</v>
+      </c>
+      <c r="F326" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
+      <c r="A327" s="2">
+        <v>46167.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>53.953</v>
+      </c>
+      <c r="C327">
+        <v>-2465.463</v>
+      </c>
+      <c r="D327">
+        <v>-2465.463</v>
+      </c>
+      <c r="E327">
+        <v>38</v>
+      </c>
+      <c r="F327" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
+      <c r="A328" s="2">
+        <v>46167.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>75.226</v>
+      </c>
+      <c r="C328">
+        <v>-1278.489</v>
+      </c>
+      <c r="D328">
+        <v>-1278.489</v>
+      </c>
+      <c r="E328">
+        <v>39</v>
+      </c>
+      <c r="F328" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
+      <c r="A329" s="2">
+        <v>46167.40625</v>
+      </c>
+      <c r="B329">
+        <v>13.141</v>
+      </c>
+      <c r="C329">
+        <v>3.684</v>
+      </c>
+      <c r="D329">
+        <v>3.684</v>
+      </c>
+      <c r="E329">
+        <v>40</v>
+      </c>
+      <c r="F329" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
+      <c r="A330" s="2">
+        <v>46167.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>38.865</v>
+      </c>
+      <c r="C330">
+        <v>12.404</v>
+      </c>
+      <c r="D330">
+        <v>12.404</v>
+      </c>
+      <c r="E330">
+        <v>41</v>
+      </c>
+      <c r="F330" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
+      <c r="A331" s="2">
+        <v>46167.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>85.66200000000001</v>
+      </c>
+      <c r="C331">
+        <v>10.813</v>
+      </c>
+      <c r="D331">
+        <v>10.813</v>
+      </c>
+      <c r="E331">
+        <v>42</v>
+      </c>
+      <c r="F331" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
+      <c r="A332" s="2">
+        <v>46167.4375</v>
+      </c>
+      <c r="B332">
+        <v>108.529</v>
+      </c>
+      <c r="C332">
+        <v>-410.068</v>
+      </c>
+      <c r="D332">
+        <v>-410.068</v>
+      </c>
+      <c r="E332">
+        <v>43</v>
+      </c>
+      <c r="F332" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
+      <c r="A333" s="2">
+        <v>46167.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>44</v>
+      </c>
+      <c r="F333" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
+      <c r="A334" s="2">
+        <v>46167.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>45</v>
+      </c>
+      <c r="F334" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
+      <c r="A335" s="2">
+        <v>46167.46875</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>46</v>
+      </c>
+      <c r="F335" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
+      <c r="A336" s="2">
+        <v>46167.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>47</v>
+      </c>
+      <c r="F336" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
+      <c r="A337" s="2">
+        <v>46167.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>48</v>
+      </c>
+      <c r="F337" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
+      <c r="A338" s="2">
+        <v>46167.5</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>49</v>
+      </c>
+      <c r="F338" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
+      <c r="A339" s="2">
+        <v>46167.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>50</v>
+      </c>
+      <c r="F339" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
+      <c r="A340" s="2">
+        <v>46167.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>51</v>
+      </c>
+      <c r="F340" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
+      <c r="A341" s="2">
+        <v>46167.53125</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>52</v>
+      </c>
+      <c r="F341" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
+      <c r="A342" s="2">
+        <v>46167.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>53</v>
+      </c>
+      <c r="F342" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
+      <c r="A343" s="2">
+        <v>46167.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>54</v>
+      </c>
+      <c r="F343" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
+      <c r="A344" s="2">
+        <v>46167.5625</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>55</v>
+      </c>
+      <c r="F344" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
+      <c r="A345" s="2">
+        <v>46167.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>56</v>
+      </c>
+      <c r="F345" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
+      <c r="A346" s="2">
+        <v>46167.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>57</v>
+      </c>
+      <c r="F346" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
+      <c r="A347" s="2">
+        <v>46167.59375</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>58</v>
+      </c>
+      <c r="F347" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
+      <c r="A348" s="2">
+        <v>46167.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>59</v>
+      </c>
+      <c r="F348" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
+      <c r="A349" s="2">
+        <v>46167.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>60</v>
+      </c>
+      <c r="F349" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
+      <c r="A350" s="2">
+        <v>46167.625</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>61</v>
+      </c>
+      <c r="F350" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
+      <c r="A351" s="2">
+        <v>46167.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>62</v>
+      </c>
+      <c r="F351" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" s="2">
+        <v>46167.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>63</v>
+      </c>
+      <c r="F352" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" s="2">
+        <v>46167.65625</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>64</v>
+      </c>
+      <c r="F353" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" s="2">
+        <v>46167.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>65</v>
+      </c>
+      <c r="F354" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
+      <c r="A355" s="2">
+        <v>46167.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>66</v>
+      </c>
+      <c r="F355" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
+      <c r="A356" s="2">
+        <v>46167.6875</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>67</v>
+      </c>
+      <c r="F356" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
+      <c r="A357" s="2">
+        <v>46167.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>68</v>
+      </c>
+      <c r="F357" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
+      <c r="A358" s="2">
+        <v>46167.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>69</v>
+      </c>
+      <c r="F358" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
+      <c r="A359" s="2">
+        <v>46167.71875</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>70</v>
+      </c>
+      <c r="F359" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
+      <c r="A360" s="2">
+        <v>46167.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>71</v>
+      </c>
+      <c r="F360" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
+      <c r="A361" s="2">
+        <v>46167.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>72</v>
+      </c>
+      <c r="F361" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
+      <c r="A362" s="2">
+        <v>46167.75</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>73</v>
+      </c>
+      <c r="F362" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
+      <c r="A363" s="2">
+        <v>46167.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>74</v>
+      </c>
+      <c r="F363" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
+      <c r="A364" s="2">
+        <v>46167.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>75</v>
+      </c>
+      <c r="F364" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
+      <c r="A365" s="2">
+        <v>46167.78125</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>76</v>
+      </c>
+      <c r="F365" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
+      <c r="A366" s="2">
+        <v>46167.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>77</v>
+      </c>
+      <c r="F366" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
+      <c r="A367" s="2">
+        <v>46167.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>78</v>
+      </c>
+      <c r="F367" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
+      <c r="A368" s="2">
+        <v>46167.8125</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>79</v>
+      </c>
+      <c r="F368" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
+      <c r="A369" s="2">
+        <v>46167.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>80</v>
+      </c>
+      <c r="F369" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
+      <c r="A370" s="2">
+        <v>46167.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>81</v>
+      </c>
+      <c r="F370" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
+      <c r="A371" s="2">
+        <v>46167.84375</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>82</v>
+      </c>
+      <c r="F371" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
+      <c r="A372" s="2">
+        <v>46167.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>83</v>
+      </c>
+      <c r="F372" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
+      <c r="A373" s="2">
+        <v>46167.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>84</v>
+      </c>
+      <c r="F373" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
+      <c r="A374" s="2">
+        <v>46167.875</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>85</v>
+      </c>
+      <c r="F374" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
+      <c r="A375" s="2">
+        <v>46167.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>86</v>
+      </c>
+      <c r="F375" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
+      <c r="A376" s="2">
+        <v>46167.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>87</v>
+      </c>
+      <c r="F376" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
+      <c r="A377" s="2">
+        <v>46167.90625</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>88</v>
+      </c>
+      <c r="F377" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
+      <c r="A378" s="2">
+        <v>46167.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>89</v>
+      </c>
+      <c r="F378" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
+      <c r="A379" s="2">
+        <v>46167.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>90</v>
+      </c>
+      <c r="F379" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
+      <c r="A380" s="2">
+        <v>46167.9375</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>91</v>
+      </c>
+      <c r="F380" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
+      <c r="A381" s="2">
+        <v>46167.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>92</v>
+      </c>
+      <c r="F381" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
+      <c r="A382" s="2">
+        <v>46167.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>93</v>
+      </c>
+      <c r="F382" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
+      <c r="A383" s="2">
+        <v>46167.96875</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>94</v>
+      </c>
+      <c r="F383" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
+      <c r="A384" s="2">
+        <v>46167.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>95</v>
+      </c>
+      <c r="F384" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
+      <c r="A385" s="2">
+        <v>46167.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>96</v>
+      </c>
+      <c r="F385" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.05.20261</t>
-  </si>
-  <si>
-    <t>25.05.20262</t>
-  </si>
-  <si>
-    <t>25.05.20263</t>
-  </si>
-  <si>
-    <t>25.05.20264</t>
-  </si>
-  <si>
-    <t>25.05.20265</t>
-  </si>
-  <si>
-    <t>25.05.20266</t>
-  </si>
-  <si>
-    <t>25.05.20267</t>
-  </si>
-  <si>
-    <t>25.05.20268</t>
-  </si>
-  <si>
-    <t>25.05.20269</t>
-  </si>
-  <si>
-    <t>25.05.202610</t>
-  </si>
-  <si>
-    <t>25.05.202611</t>
-  </si>
-  <si>
-    <t>25.05.202612</t>
-  </si>
-  <si>
-    <t>25.05.202613</t>
-  </si>
-  <si>
-    <t>25.05.202614</t>
-  </si>
-  <si>
-    <t>25.05.202615</t>
-  </si>
-  <si>
-    <t>25.05.202616</t>
-  </si>
-  <si>
-    <t>25.05.202617</t>
-  </si>
-  <si>
-    <t>25.05.202618</t>
-  </si>
-  <si>
-    <t>25.05.202619</t>
-  </si>
-  <si>
-    <t>25.05.202620</t>
-  </si>
-  <si>
-    <t>25.05.202621</t>
-  </si>
-  <si>
-    <t>25.05.202622</t>
-  </si>
-  <si>
-    <t>25.05.202623</t>
-  </si>
-  <si>
-    <t>25.05.202624</t>
-  </si>
-  <si>
-    <t>25.05.202625</t>
-  </si>
-  <si>
-    <t>25.05.202626</t>
-  </si>
-  <si>
-    <t>25.05.202627</t>
-  </si>
-  <si>
-    <t>25.05.202628</t>
-  </si>
-  <si>
-    <t>25.05.202629</t>
-  </si>
-  <si>
-    <t>25.05.202630</t>
-  </si>
-  <si>
-    <t>25.05.202631</t>
-  </si>
-  <si>
-    <t>25.05.202632</t>
-  </si>
-  <si>
-    <t>25.05.202633</t>
-  </si>
-  <si>
-    <t>25.05.202634</t>
-  </si>
-  <si>
-    <t>25.05.202635</t>
-  </si>
-  <si>
-    <t>25.05.202636</t>
-  </si>
-  <si>
-    <t>25.05.202637</t>
-  </si>
-  <si>
-    <t>25.05.202638</t>
-  </si>
-  <si>
-    <t>25.05.202639</t>
-  </si>
-  <si>
-    <t>25.05.202640</t>
-  </si>
-  <si>
-    <t>25.05.202641</t>
-  </si>
-  <si>
-    <t>25.05.202642</t>
-  </si>
-  <si>
-    <t>25.05.202643</t>
-  </si>
-  <si>
-    <t>25.05.202644</t>
-  </si>
-  <si>
-    <t>25.05.202645</t>
-  </si>
-  <si>
-    <t>25.05.202646</t>
-  </si>
-  <si>
-    <t>25.05.202647</t>
-  </si>
-  <si>
-    <t>25.05.202648</t>
-  </si>
-  <si>
-    <t>25.05.202649</t>
-  </si>
-  <si>
-    <t>25.05.202650</t>
-  </si>
-  <si>
-    <t>25.05.202651</t>
-  </si>
-  <si>
-    <t>25.05.202652</t>
-  </si>
-  <si>
-    <t>25.05.202653</t>
-  </si>
-  <si>
-    <t>25.05.202654</t>
-  </si>
-  <si>
-    <t>25.05.202655</t>
-  </si>
-  <si>
-    <t>25.05.202656</t>
-  </si>
-  <si>
-    <t>25.05.202657</t>
-  </si>
-  <si>
-    <t>25.05.202658</t>
-  </si>
-  <si>
-    <t>25.05.202659</t>
-  </si>
-  <si>
-    <t>25.05.202660</t>
-  </si>
-  <si>
-    <t>25.05.202661</t>
-  </si>
-  <si>
-    <t>25.05.202662</t>
-  </si>
-  <si>
-    <t>25.05.202663</t>
-  </si>
-  <si>
-    <t>25.05.202664</t>
-  </si>
-  <si>
-    <t>25.05.202665</t>
-  </si>
-  <si>
-    <t>25.05.202666</t>
-  </si>
-  <si>
-    <t>25.05.202667</t>
-  </si>
-  <si>
-    <t>25.05.202668</t>
-  </si>
-  <si>
-    <t>25.05.202669</t>
-  </si>
-  <si>
-    <t>25.05.202670</t>
-  </si>
-  <si>
-    <t>25.05.202671</t>
-  </si>
-  <si>
-    <t>25.05.202672</t>
-  </si>
-  <si>
-    <t>25.05.202673</t>
-  </si>
-  <si>
-    <t>25.05.202674</t>
-  </si>
-  <si>
-    <t>25.05.202675</t>
-  </si>
-  <si>
-    <t>25.05.202676</t>
-  </si>
-  <si>
-    <t>25.05.202677</t>
-  </si>
-  <si>
-    <t>25.05.202678</t>
-  </si>
-  <si>
-    <t>25.05.202679</t>
-  </si>
-  <si>
-    <t>25.05.202680</t>
-  </si>
-  <si>
-    <t>25.05.202681</t>
-  </si>
-  <si>
-    <t>25.05.202682</t>
-  </si>
-  <si>
-    <t>25.05.202683</t>
-  </si>
-  <si>
-    <t>25.05.202684</t>
-  </si>
-  <si>
-    <t>25.05.202685</t>
-  </si>
-  <si>
-    <t>25.05.202686</t>
-  </si>
-  <si>
-    <t>25.05.202687</t>
-  </si>
-  <si>
-    <t>25.05.202688</t>
-  </si>
-  <si>
-    <t>25.05.202689</t>
-  </si>
-  <si>
-    <t>25.05.202690</t>
-  </si>
-  <si>
-    <t>25.05.202691</t>
-  </si>
-  <si>
-    <t>25.05.202692</t>
-  </si>
-  <si>
-    <t>25.05.202693</t>
-  </si>
-  <si>
-    <t>25.05.202694</t>
-  </si>
-  <si>
-    <t>25.05.202695</t>
-  </si>
-  <si>
-    <t>25.05.202696</t>
-  </si>
-  <si>
     <t>26.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>26.05.202696</t>
+  </si>
+  <si>
+    <t>27.05.20261</t>
+  </si>
+  <si>
+    <t>27.05.20262</t>
+  </si>
+  <si>
+    <t>27.05.20263</t>
+  </si>
+  <si>
+    <t>27.05.20264</t>
+  </si>
+  <si>
+    <t>27.05.20265</t>
+  </si>
+  <si>
+    <t>27.05.20266</t>
+  </si>
+  <si>
+    <t>27.05.20267</t>
+  </si>
+  <si>
+    <t>27.05.20268</t>
+  </si>
+  <si>
+    <t>27.05.20269</t>
+  </si>
+  <si>
+    <t>27.05.202610</t>
+  </si>
+  <si>
+    <t>27.05.202611</t>
+  </si>
+  <si>
+    <t>27.05.202612</t>
+  </si>
+  <si>
+    <t>27.05.202613</t>
+  </si>
+  <si>
+    <t>27.05.202614</t>
+  </si>
+  <si>
+    <t>27.05.202615</t>
+  </si>
+  <si>
+    <t>27.05.202616</t>
+  </si>
+  <si>
+    <t>27.05.202617</t>
+  </si>
+  <si>
+    <t>27.05.202618</t>
+  </si>
+  <si>
+    <t>27.05.202619</t>
+  </si>
+  <si>
+    <t>27.05.202620</t>
+  </si>
+  <si>
+    <t>27.05.202621</t>
+  </si>
+  <si>
+    <t>27.05.202622</t>
+  </si>
+  <si>
+    <t>27.05.202623</t>
+  </si>
+  <si>
+    <t>27.05.202624</t>
+  </si>
+  <si>
+    <t>27.05.202625</t>
+  </si>
+  <si>
+    <t>27.05.202626</t>
+  </si>
+  <si>
+    <t>27.05.202627</t>
+  </si>
+  <si>
+    <t>27.05.202628</t>
+  </si>
+  <si>
+    <t>27.05.202629</t>
+  </si>
+  <si>
+    <t>27.05.202630</t>
+  </si>
+  <si>
+    <t>27.05.202631</t>
+  </si>
+  <si>
+    <t>27.05.202632</t>
+  </si>
+  <si>
+    <t>27.05.202633</t>
+  </si>
+  <si>
+    <t>27.05.202634</t>
+  </si>
+  <si>
+    <t>27.05.202635</t>
+  </si>
+  <si>
+    <t>27.05.202636</t>
+  </si>
+  <si>
+    <t>27.05.202637</t>
+  </si>
+  <si>
+    <t>27.05.202638</t>
+  </si>
+  <si>
+    <t>27.05.202639</t>
+  </si>
+  <si>
+    <t>27.05.202640</t>
+  </si>
+  <si>
+    <t>27.05.202641</t>
+  </si>
+  <si>
+    <t>27.05.202642</t>
+  </si>
+  <si>
+    <t>27.05.202643</t>
+  </si>
+  <si>
+    <t>27.05.202644</t>
+  </si>
+  <si>
+    <t>27.05.202645</t>
+  </si>
+  <si>
+    <t>27.05.202646</t>
+  </si>
+  <si>
+    <t>27.05.202647</t>
+  </si>
+  <si>
+    <t>27.05.202648</t>
+  </si>
+  <si>
+    <t>27.05.202649</t>
+  </si>
+  <si>
+    <t>27.05.202650</t>
+  </si>
+  <si>
+    <t>27.05.202651</t>
+  </si>
+  <si>
+    <t>27.05.202652</t>
+  </si>
+  <si>
+    <t>27.05.202653</t>
+  </si>
+  <si>
+    <t>27.05.202654</t>
+  </si>
+  <si>
+    <t>27.05.202655</t>
+  </si>
+  <si>
+    <t>27.05.202656</t>
+  </si>
+  <si>
+    <t>27.05.202657</t>
+  </si>
+  <si>
+    <t>27.05.202658</t>
+  </si>
+  <si>
+    <t>27.05.202659</t>
+  </si>
+  <si>
+    <t>27.05.202660</t>
+  </si>
+  <si>
+    <t>27.05.202661</t>
+  </si>
+  <si>
+    <t>27.05.202662</t>
+  </si>
+  <si>
+    <t>27.05.202663</t>
+  </si>
+  <si>
+    <t>27.05.202664</t>
+  </si>
+  <si>
+    <t>27.05.202665</t>
+  </si>
+  <si>
+    <t>27.05.202666</t>
+  </si>
+  <si>
+    <t>27.05.202667</t>
+  </si>
+  <si>
+    <t>27.05.202668</t>
+  </si>
+  <si>
+    <t>27.05.202669</t>
+  </si>
+  <si>
+    <t>27.05.202670</t>
+  </si>
+  <si>
+    <t>27.05.202671</t>
+  </si>
+  <si>
+    <t>27.05.202672</t>
+  </si>
+  <si>
+    <t>27.05.202673</t>
+  </si>
+  <si>
+    <t>27.05.202674</t>
+  </si>
+  <si>
+    <t>27.05.202675</t>
+  </si>
+  <si>
+    <t>27.05.202676</t>
+  </si>
+  <si>
+    <t>27.05.202677</t>
+  </si>
+  <si>
+    <t>27.05.202678</t>
+  </si>
+  <si>
+    <t>27.05.202679</t>
+  </si>
+  <si>
+    <t>27.05.202680</t>
+  </si>
+  <si>
+    <t>27.05.202681</t>
+  </si>
+  <si>
+    <t>27.05.202682</t>
+  </si>
+  <si>
+    <t>27.05.202683</t>
+  </si>
+  <si>
+    <t>27.05.202684</t>
+  </si>
+  <si>
+    <t>27.05.202685</t>
+  </si>
+  <si>
+    <t>27.05.202686</t>
+  </si>
+  <si>
+    <t>27.05.202687</t>
+  </si>
+  <si>
+    <t>27.05.202688</t>
+  </si>
+  <si>
+    <t>27.05.202689</t>
+  </si>
+  <si>
+    <t>27.05.202690</t>
+  </si>
+  <si>
+    <t>27.05.202691</t>
+  </si>
+  <si>
+    <t>27.05.202692</t>
+  </si>
+  <si>
+    <t>27.05.202693</t>
+  </si>
+  <si>
+    <t>27.05.202694</t>
+  </si>
+  <si>
+    <t>27.05.202695</t>
+  </si>
+  <si>
+    <t>27.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
-        <v>-33.871</v>
+        <v>38.844</v>
       </c>
       <c r="C6">
-        <v>1448.086</v>
+        <v>-111.659</v>
       </c>
       <c r="D6">
-        <v>1448.086</v>
+        <v>-111.659</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
-        <v>-24.831</v>
+        <v>57.277</v>
       </c>
       <c r="C7">
-        <v>1243.303</v>
+        <v>-260.411</v>
       </c>
       <c r="D7">
-        <v>1243.303</v>
+        <v>-260.411</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
-        <v>-25.505</v>
+        <v>69.351</v>
       </c>
       <c r="C8">
-        <v>1332.922</v>
+        <v>-123.282</v>
       </c>
       <c r="D8">
-        <v>1332.922</v>
+        <v>-123.282</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
-        <v>-24.27</v>
+        <v>78.907</v>
       </c>
       <c r="C9">
-        <v>1170.089</v>
+        <v>-1117.639</v>
       </c>
       <c r="D9">
-        <v>1170.089</v>
+        <v>-1117.639</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
-        <v>-7.174</v>
+        <v>80.619</v>
       </c>
       <c r="C10">
-        <v>989.48</v>
+        <v>-4145.639</v>
       </c>
       <c r="D10">
-        <v>989.48</v>
+        <v>-4145.639</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
-        <v>10.012</v>
+        <v>71.125</v>
       </c>
       <c r="C11">
-        <v>400</v>
+        <v>-7495.051</v>
       </c>
       <c r="D11">
-        <v>400</v>
+        <v>-7495.051</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
-        <v>51.928</v>
+        <v>65.625</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>-7155.632</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>-7155.632</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
-        <v>99.71599999999999</v>
+        <v>74.58199999999999</v>
       </c>
       <c r="C13">
-        <v>374.693</v>
+        <v>-1210.419</v>
       </c>
       <c r="D13">
-        <v>374.693</v>
+        <v>-1210.419</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
-        <v>124.424</v>
+        <v>78.73699999999999</v>
       </c>
       <c r="C14">
-        <v>378.163</v>
+        <v>-50.901</v>
       </c>
       <c r="D14">
-        <v>378.163</v>
+        <v>-50.901</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
-        <v>86.88800000000001</v>
+        <v>75.955</v>
       </c>
       <c r="C15">
-        <v>14.444</v>
+        <v>-288.502</v>
       </c>
       <c r="D15">
-        <v>14.444</v>
+        <v>-288.502</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
-        <v>40.906</v>
+        <v>86.432</v>
       </c>
       <c r="C16">
-        <v>-8.315</v>
+        <v>-54.534</v>
       </c>
       <c r="D16">
-        <v>-8.315</v>
+        <v>-54.534</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
-        <v>26.362</v>
+        <v>132.921</v>
       </c>
       <c r="C17">
-        <v>212.262</v>
+        <v>-1103.312</v>
       </c>
       <c r="D17">
-        <v>212.262</v>
+        <v>-1103.312</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
-        <v>-9.177</v>
+        <v>91.51600000000001</v>
       </c>
       <c r="C18">
-        <v>850.148</v>
+        <v>-2583.893</v>
       </c>
       <c r="D18">
-        <v>850.148</v>
+        <v>-2583.893</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
-        <v>-24.727</v>
+        <v>54.538</v>
       </c>
       <c r="C19">
-        <v>828.696</v>
+        <v>3.97</v>
       </c>
       <c r="D19">
-        <v>828.696</v>
+        <v>3.97</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
-        <v>-30.554</v>
+        <v>57.783</v>
       </c>
       <c r="C20">
-        <v>800</v>
+        <v>-100</v>
       </c>
       <c r="D20">
-        <v>800</v>
+        <v>-100</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
-        <v>-8.811999999999999</v>
+        <v>58.11</v>
       </c>
       <c r="C21">
-        <v>883.6</v>
+        <v>0.256</v>
       </c>
       <c r="D21">
-        <v>883.6</v>
+        <v>0.256</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
-        <v>56.484</v>
+        <v>41.206</v>
       </c>
       <c r="C22">
-        <v>60.301</v>
+        <v>7.494</v>
       </c>
       <c r="D22">
-        <v>60.301</v>
+        <v>7.494</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
-        <v>64.895</v>
+        <v>-2.859</v>
       </c>
       <c r="C23">
-        <v>-105.634</v>
+        <v>884.718</v>
       </c>
       <c r="D23">
-        <v>-105.634</v>
+        <v>884.718</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
-        <v>78.913</v>
+        <v>54.176</v>
       </c>
       <c r="C24">
-        <v>-124.998</v>
+        <v>50.272</v>
       </c>
       <c r="D24">
-        <v>-124.998</v>
+        <v>50.272</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
-        <v>70.238</v>
+        <v>75.71599999999999</v>
       </c>
       <c r="C25">
-        <v>-135.928</v>
+        <v>-1160.759</v>
       </c>
       <c r="D25">
-        <v>-135.928</v>
+        <v>-1160.759</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
-        <v>102.269</v>
+        <v>50.293</v>
       </c>
       <c r="C26">
-        <v>81.172</v>
+        <v>-126.581</v>
       </c>
       <c r="D26">
-        <v>81.172</v>
+        <v>-126.581</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
-        <v>114.222</v>
+        <v>12.05</v>
       </c>
       <c r="C27">
-        <v>349.495</v>
+        <v>1.551</v>
       </c>
       <c r="D27">
-        <v>349.495</v>
+        <v>1.551</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
-        <v>72.26900000000001</v>
+        <v>2.123</v>
       </c>
       <c r="C28">
-        <v>-83.45999999999999</v>
+        <v>1.562</v>
       </c>
       <c r="D28">
-        <v>-83.45999999999999</v>
+        <v>1.562</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
-        <v>62.753</v>
+        <v>-23.774</v>
       </c>
       <c r="C29">
-        <v>-1334.451</v>
+        <v>859.173</v>
       </c>
       <c r="D29">
-        <v>-1334.451</v>
+        <v>859.173</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
-        <v>76.577</v>
+        <v>-21.283</v>
       </c>
       <c r="C30">
-        <v>42.177</v>
+        <v>890.458</v>
       </c>
       <c r="D30">
-        <v>42.177</v>
+        <v>890.458</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
-        <v>58.089</v>
+        <v>-60.119</v>
       </c>
       <c r="C31">
-        <v>5.141</v>
+        <v>1130.191</v>
       </c>
       <c r="D31">
-        <v>5.141</v>
+        <v>1130.191</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
-        <v>31.081</v>
+        <v>-70.705</v>
       </c>
       <c r="C32">
-        <v>0.978</v>
+        <v>4741.074</v>
       </c>
       <c r="D32">
-        <v>0.978</v>
+        <v>4741.074</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
-        <v>75.95</v>
+        <v>-65.901</v>
       </c>
       <c r="C33">
-        <v>-14.482</v>
+        <v>2425.999</v>
       </c>
       <c r="D33">
-        <v>-14.482</v>
+        <v>2425.999</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
-        <v>17.313</v>
+        <v>-71.43300000000001</v>
       </c>
       <c r="C34">
-        <v>-3.388</v>
+        <v>1028.586</v>
       </c>
       <c r="D34">
-        <v>-3.388</v>
+        <v>1028.586</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
-        <v>32.455</v>
+        <v>-36.133</v>
       </c>
       <c r="C35">
-        <v>0.016</v>
+        <v>1044.07</v>
       </c>
       <c r="D35">
-        <v>0.016</v>
+        <v>1044.07</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
-        <v>53.049</v>
+        <v>-38.062</v>
       </c>
       <c r="C36">
-        <v>4.701</v>
+        <v>1043.442</v>
       </c>
       <c r="D36">
-        <v>4.701</v>
+        <v>1043.442</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
-        <v>39.762</v>
+        <v>-35.632</v>
       </c>
       <c r="C37">
-        <v>3.754</v>
+        <v>1044.07</v>
       </c>
       <c r="D37">
-        <v>3.754</v>
+        <v>1044.07</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
-        <v>34.378</v>
+        <v>-55.316</v>
       </c>
       <c r="C38">
-        <v>5.197</v>
+        <v>715.449</v>
       </c>
       <c r="D38">
-        <v>5.197</v>
+        <v>715.449</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
-        <v>53.953</v>
+        <v>-32.127</v>
       </c>
       <c r="C39">
-        <v>-2465.463</v>
+        <v>712.979</v>
       </c>
       <c r="D39">
-        <v>-2465.463</v>
+        <v>712.979</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
-        <v>75.226</v>
+        <v>-13.767</v>
       </c>
       <c r="C40">
-        <v>-1278.489</v>
+        <v>707.923</v>
       </c>
       <c r="D40">
-        <v>-1278.489</v>
+        <v>707.923</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
-        <v>13.141</v>
+        <v>28.607</v>
       </c>
       <c r="C41">
-        <v>3.684</v>
+        <v>-54.144</v>
       </c>
       <c r="D41">
-        <v>3.684</v>
+        <v>-54.144</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
-        <v>38.865</v>
+        <v>47.427</v>
       </c>
       <c r="C42">
-        <v>12.404</v>
+        <v>-71.11799999999999</v>
       </c>
       <c r="D42">
-        <v>12.404</v>
+        <v>-71.11799999999999</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
-        <v>85.66200000000001</v>
+        <v>14.54</v>
       </c>
       <c r="C43">
-        <v>10.813</v>
+        <v>-7.551</v>
       </c>
       <c r="D43">
-        <v>10.813</v>
+        <v>-7.551</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
-        <v>108.529</v>
+        <v>55.577</v>
       </c>
       <c r="C44">
-        <v>-410.068</v>
+        <v>48.077</v>
       </c>
       <c r="D44">
-        <v>-410.068</v>
+        <v>48.077</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
-        <v>97.884</v>
+        <v>59.629</v>
       </c>
       <c r="C45">
-        <v>-574.852</v>
+        <v>-2251.176</v>
       </c>
       <c r="D45">
-        <v>-574.852</v>
+        <v>-2251.176</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
-        <v>16.949</v>
+        <v>47.167</v>
       </c>
       <c r="C46">
-        <v>-99.19799999999999</v>
+        <v>-1202.297</v>
       </c>
       <c r="D46">
-        <v>-99.19799999999999</v>
+        <v>-1202.297</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
-        <v>24.044</v>
+        <v>52.6</v>
       </c>
       <c r="C47">
-        <v>-108</v>
+        <v>-87.43300000000001</v>
       </c>
       <c r="D47">
-        <v>-108</v>
+        <v>-87.43300000000001</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
-        <v>15.061</v>
+        <v>67.069</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>-1693.846</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>-1693.846</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
-        <v>2.248</v>
+        <v>28.705</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>-109.117</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>-109.117</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
-        <v>-54.381</v>
+        <v>30.855</v>
       </c>
       <c r="C50">
-        <v>5460.902</v>
+        <v>242.144</v>
       </c>
       <c r="D50">
-        <v>5460.902</v>
+        <v>242.144</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
-        <v>-52.404</v>
+        <v>50.189</v>
       </c>
       <c r="C51">
-        <v>5409.967</v>
+        <v>-161.76</v>
       </c>
       <c r="D51">
-        <v>5409.967</v>
+        <v>-161.76</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
-        <v>-45.238</v>
+        <v>40.747</v>
       </c>
       <c r="C52">
-        <v>501.539</v>
+        <v>-52.054</v>
       </c>
       <c r="D52">
-        <v>501.539</v>
+        <v>-52.054</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
-        <v>-34.07</v>
+        <v>59.968</v>
       </c>
       <c r="C53">
-        <v>501.033</v>
+        <v>-846.576</v>
       </c>
       <c r="D53">
-        <v>501.033</v>
+        <v>-846.576</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
-        <v>-69.598</v>
+        <v>35.413</v>
       </c>
       <c r="C54">
-        <v>555.938</v>
+        <v>-529.067</v>
       </c>
       <c r="D54">
-        <v>555.938</v>
+        <v>-529.067</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
-        <v>-91.578</v>
+        <v>30.167</v>
       </c>
       <c r="C55">
-        <v>449.201</v>
+        <v>-12.656</v>
       </c>
       <c r="D55">
-        <v>449.201</v>
+        <v>-12.656</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
-        <v>-6.684</v>
+        <v>-9.234</v>
       </c>
       <c r="C56">
-        <v>448.86</v>
+        <v>489.455</v>
       </c>
       <c r="D56">
-        <v>448.86</v>
+        <v>489.455</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
-        <v>8.696999999999999</v>
+        <v>14.419</v>
       </c>
       <c r="C57">
-        <v>61.76</v>
+        <v>124.022</v>
       </c>
       <c r="D57">
-        <v>61.76</v>
+        <v>124.022</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
-        <v>13.856</v>
+        <v>49.964</v>
       </c>
       <c r="C58">
-        <v>66.81699999999999</v>
+        <v>61.758</v>
       </c>
       <c r="D58">
-        <v>66.81699999999999</v>
+        <v>61.758</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
-        <v>57.812</v>
+        <v>19.888</v>
       </c>
       <c r="C59">
-        <v>136.067</v>
+        <v>381.878</v>
       </c>
       <c r="D59">
-        <v>136.067</v>
+        <v>381.878</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
-        <v>64.755</v>
+        <v>15.134</v>
       </c>
       <c r="C60">
-        <v>31.577</v>
+        <v>397.135</v>
       </c>
       <c r="D60">
-        <v>31.577</v>
+        <v>397.135</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
-        <v>-20.171</v>
+        <v>47.44</v>
       </c>
       <c r="C61">
-        <v>479.491</v>
+        <v>388.02</v>
       </c>
       <c r="D61">
-        <v>479.491</v>
+        <v>388.02</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
-        <v>-114.047</v>
+        <v>45.965</v>
       </c>
       <c r="C62">
-        <v>647.265</v>
+        <v>-154.627</v>
       </c>
       <c r="D62">
-        <v>647.265</v>
+        <v>-154.627</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
-        <v>-51.678</v>
+        <v>-8.573</v>
       </c>
       <c r="C63">
-        <v>666.17</v>
+        <v>818.009</v>
       </c>
       <c r="D63">
-        <v>666.17</v>
+        <v>818.009</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
-        <v>-24.959</v>
+        <v>13.276</v>
       </c>
       <c r="C64">
-        <v>529.11</v>
+        <v>400</v>
       </c>
       <c r="D64">
-        <v>529.11</v>
+        <v>400</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
-        <v>-28.203</v>
+        <v>-2.599</v>
       </c>
       <c r="C65">
-        <v>534.5410000000001</v>
+        <v>790.567</v>
       </c>
       <c r="D65">
-        <v>534.5410000000001</v>
+        <v>790.567</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
-        <v>-82.587</v>
+        <v>10.221</v>
       </c>
       <c r="C66">
-        <v>1427.703</v>
+        <v>23.874</v>
       </c>
       <c r="D66">
-        <v>1427.703</v>
+        <v>23.874</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
-        <v>-74.916</v>
+        <v>52.148</v>
       </c>
       <c r="C67">
-        <v>817.723</v>
+        <v>277.234</v>
       </c>
       <c r="D67">
-        <v>817.723</v>
+        <v>277.234</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
-        <v>-21.206</v>
+        <v>8.109</v>
       </c>
       <c r="C68">
-        <v>832.511</v>
+        <v>400</v>
       </c>
       <c r="D68">
-        <v>832.511</v>
+        <v>400</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
-        <v>-23.807</v>
+        <v>16.448</v>
       </c>
       <c r="C69">
-        <v>833.84</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>833.84</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
-        <v>60.712</v>
+        <v>62.181</v>
       </c>
       <c r="C70">
-        <v>163.842</v>
+        <v>359.431</v>
       </c>
       <c r="D70">
-        <v>163.842</v>
+        <v>359.431</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
-        <v>34.39</v>
+        <v>76.77200000000001</v>
       </c>
       <c r="C71">
-        <v>168.982</v>
+        <v>386.6</v>
       </c>
       <c r="D71">
-        <v>168.982</v>
+        <v>386.6</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
-        <v>93.67400000000001</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="C72">
-        <v>180.482</v>
+        <v>400</v>
       </c>
       <c r="D72">
-        <v>180.482</v>
+        <v>400</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
-        <v>139.823</v>
+        <v>67.045</v>
       </c>
       <c r="C73">
-        <v>313.347</v>
+        <v>305.53</v>
       </c>
       <c r="D73">
-        <v>313.347</v>
+        <v>305.53</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
-        <v>253.342</v>
+        <v>173.807</v>
       </c>
       <c r="C74">
-        <v>-1192.646</v>
+        <v>129.275</v>
       </c>
       <c r="D74">
-        <v>-1192.646</v>
+        <v>129.275</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
-        <v>126.98</v>
+        <v>114.728</v>
       </c>
       <c r="C75">
-        <v>-11.216</v>
+        <v>-3406.708</v>
       </c>
       <c r="D75">
-        <v>-11.216</v>
+        <v>-3406.708</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
-        <v>86.303</v>
+        <v>84.676</v>
       </c>
       <c r="C76">
-        <v>5.853</v>
+        <v>362.12</v>
       </c>
       <c r="D76">
-        <v>5.853</v>
+        <v>362.12</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
-        <v>39.935</v>
+        <v>53.681</v>
       </c>
       <c r="C77">
-        <v>0.4</v>
+        <v>400</v>
       </c>
       <c r="D77">
-        <v>0.4</v>
+        <v>400</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
-        <v>34.84</v>
+        <v>37.751</v>
       </c>
       <c r="C78">
-        <v>0.6</v>
+        <v>322.517</v>
       </c>
       <c r="D78">
-        <v>0.6</v>
+        <v>322.517</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
-        <v>-14.014</v>
+        <v>94.55800000000001</v>
       </c>
       <c r="C79">
-        <v>6334.692</v>
+        <v>341.04</v>
       </c>
       <c r="D79">
-        <v>6334.692</v>
+        <v>341.04</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
-        <v>-16.913</v>
+        <v>78.816</v>
       </c>
       <c r="C80">
-        <v>3496.59</v>
+        <v>332.531</v>
       </c>
       <c r="D80">
-        <v>3496.59</v>
+        <v>332.531</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
-        <v>11.4</v>
+        <v>129.071</v>
       </c>
       <c r="C81">
-        <v>400</v>
+        <v>326.431</v>
       </c>
       <c r="D81">
-        <v>400</v>
+        <v>326.431</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
-        <v>-9.827999999999999</v>
+        <v>109.043</v>
       </c>
       <c r="C82">
-        <v>1423.558</v>
+        <v>326.679</v>
       </c>
       <c r="D82">
-        <v>1423.558</v>
+        <v>326.679</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
-        <v>-12.446</v>
+        <v>72.625</v>
       </c>
       <c r="C83">
-        <v>1463.907</v>
+        <v>400</v>
       </c>
       <c r="D83">
-        <v>1463.907</v>
+        <v>400</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
-        <v>-26.322</v>
+        <v>35.983</v>
       </c>
       <c r="C84">
-        <v>1709.77</v>
+        <v>358.125</v>
       </c>
       <c r="D84">
-        <v>1709.77</v>
+        <v>358.125</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
-        <v>-12.947</v>
+        <v>3.518</v>
       </c>
       <c r="C85">
-        <v>1354.739</v>
+        <v>338.154</v>
       </c>
       <c r="D85">
-        <v>1354.739</v>
+        <v>338.154</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
-        <v>-45.486</v>
+        <v>-31.274</v>
       </c>
       <c r="C86">
-        <v>5354.615</v>
+        <v>2867.661</v>
       </c>
       <c r="D86">
-        <v>5354.615</v>
+        <v>2867.661</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
-        <v>-28.743</v>
+        <v>-51.458</v>
       </c>
       <c r="C87">
-        <v>2740.522</v>
+        <v>5965.245</v>
       </c>
       <c r="D87">
-        <v>2740.522</v>
+        <v>5965.245</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
-        <v>-42.908</v>
+        <v>-87.119</v>
       </c>
       <c r="C88">
-        <v>4140.383</v>
+        <v>6784.287</v>
       </c>
       <c r="D88">
-        <v>4140.383</v>
+        <v>6784.287</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
-        <v>-40.312</v>
+        <v>-19.142</v>
       </c>
       <c r="C89">
-        <v>1834.608</v>
+        <v>2071.499</v>
       </c>
       <c r="D89">
-        <v>1834.608</v>
+        <v>2071.499</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
-        <v>-26.683</v>
+        <v>0.762</v>
       </c>
       <c r="C90">
-        <v>1342.086</v>
+        <v>93.515</v>
       </c>
       <c r="D90">
-        <v>1342.086</v>
+        <v>93.515</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
-        <v>-14.656</v>
+        <v>-37.721</v>
       </c>
       <c r="C91">
-        <v>1225.28</v>
+        <v>1403.55</v>
       </c>
       <c r="D91">
-        <v>1225.28</v>
+        <v>1403.55</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
-        <v>-10.436</v>
+        <v>-31.838</v>
       </c>
       <c r="C92">
-        <v>1166.096</v>
+        <v>1340.074</v>
       </c>
       <c r="D92">
-        <v>1166.096</v>
+        <v>1340.074</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
-        <v>30.288</v>
+        <v>-21.266</v>
       </c>
       <c r="C93">
-        <v>264.86</v>
+        <v>1150.009</v>
       </c>
       <c r="D93">
-        <v>264.86</v>
+        <v>1150.009</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.462</v>
+        <v>-15.279</v>
       </c>
       <c r="C94">
-        <v>224.814</v>
+        <v>1088.714</v>
       </c>
       <c r="D94">
-        <v>224.814</v>
+        <v>1088.714</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
-        <v>8.127000000000001</v>
+        <v>-4.325</v>
       </c>
       <c r="C95">
-        <v>88.157</v>
+        <v>897.684</v>
       </c>
       <c r="D95">
-        <v>88.157</v>
+        <v>897.684</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
-        <v>51.832</v>
+        <v>-10.863</v>
       </c>
       <c r="C96">
-        <v>-7.258</v>
+        <v>899.605</v>
       </c>
       <c r="D96">
-        <v>-7.258</v>
+        <v>899.605</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B97">
-        <v>52.218</v>
+        <v>3.691</v>
       </c>
       <c r="C97">
-        <v>-167.375</v>
+        <v>69.05200000000001</v>
       </c>
       <c r="D97">
-        <v>-167.375</v>
+        <v>69.05200000000001</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B98">
-        <v>21.345</v>
+        <v>38.446</v>
       </c>
       <c r="C98">
-        <v>114.027</v>
+        <v>184.721</v>
       </c>
       <c r="D98">
-        <v>114.027</v>
+        <v>184.721</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B99">
-        <v>48.619</v>
+        <v>49.336</v>
       </c>
       <c r="C99">
-        <v>-141.827</v>
+        <v>334.83</v>
       </c>
       <c r="D99">
-        <v>-141.827</v>
+        <v>334.83</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B100">
-        <v>39.388</v>
+        <v>47.12</v>
       </c>
       <c r="C100">
-        <v>-114.955</v>
+        <v>362.797</v>
       </c>
       <c r="D100">
-        <v>-114.955</v>
+        <v>362.797</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B101">
-        <v>32.852</v>
+        <v>13.031</v>
       </c>
       <c r="C101">
-        <v>-526.409</v>
+        <v>400</v>
       </c>
       <c r="D101">
-        <v>-526.409</v>
+        <v>400</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B102">
-        <v>38.844</v>
+        <v>12.075</v>
       </c>
       <c r="C102">
-        <v>-111.659</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>-111.659</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B103">
-        <v>57.277</v>
+        <v>-5.87</v>
       </c>
       <c r="C103">
-        <v>-260.411</v>
+        <v>899.306</v>
       </c>
       <c r="D103">
-        <v>-260.411</v>
+        <v>899.306</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B104">
-        <v>69.351</v>
+        <v>-16.545</v>
       </c>
       <c r="C104">
-        <v>-123.282</v>
+        <v>899.846</v>
       </c>
       <c r="D104">
-        <v>-123.282</v>
+        <v>899.846</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B105">
-        <v>78.907</v>
+        <v>-11.066</v>
       </c>
       <c r="C105">
-        <v>-1117.639</v>
+        <v>898.688</v>
       </c>
       <c r="D105">
-        <v>-1117.639</v>
+        <v>898.688</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B106">
-        <v>80.619</v>
+        <v>-12.106</v>
       </c>
       <c r="C106">
-        <v>-4145.639</v>
+        <v>894.3339999999999</v>
       </c>
       <c r="D106">
-        <v>-4145.639</v>
+        <v>894.3339999999999</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B107">
-        <v>71.125</v>
+        <v>-10.068</v>
       </c>
       <c r="C107">
-        <v>-7495.051</v>
+        <v>885.827</v>
       </c>
       <c r="D107">
-        <v>-7495.051</v>
+        <v>885.827</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B108">
-        <v>65.625</v>
+        <v>-3.179</v>
       </c>
       <c r="C108">
-        <v>-7155.632</v>
+        <v>890.564</v>
       </c>
       <c r="D108">
-        <v>-7155.632</v>
+        <v>890.564</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B109">
-        <v>74.58199999999999</v>
+        <v>-4.992</v>
       </c>
       <c r="C109">
-        <v>-1210.419</v>
+        <v>898.273</v>
       </c>
       <c r="D109">
-        <v>-1210.419</v>
+        <v>898.273</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B110">
-        <v>78.73699999999999</v>
+        <v>-3.175</v>
       </c>
       <c r="C110">
-        <v>-50.901</v>
+        <v>898.127</v>
       </c>
       <c r="D110">
-        <v>-50.901</v>
+        <v>898.127</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B111">
-        <v>75.955</v>
+        <v>-13.868</v>
       </c>
       <c r="C111">
-        <v>-288.502</v>
+        <v>915.122</v>
       </c>
       <c r="D111">
-        <v>-288.502</v>
+        <v>915.122</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B112">
-        <v>86.432</v>
+        <v>-32.38</v>
       </c>
       <c r="C112">
-        <v>-54.534</v>
+        <v>944.3150000000001</v>
       </c>
       <c r="D112">
-        <v>-54.534</v>
+        <v>944.3150000000001</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B113">
-        <v>132.921</v>
+        <v>-19.105</v>
       </c>
       <c r="C113">
-        <v>-1103.312</v>
+        <v>902.775</v>
       </c>
       <c r="D113">
-        <v>-1103.312</v>
+        <v>902.775</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B114">
-        <v>91.51600000000001</v>
+        <v>16.872</v>
       </c>
       <c r="C114">
-        <v>-2583.893</v>
+        <v>386</v>
       </c>
       <c r="D114">
-        <v>-2583.893</v>
+        <v>386</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B115">
-        <v>54.538</v>
+        <v>1.933</v>
       </c>
       <c r="C115">
-        <v>3.97</v>
+        <v>400</v>
       </c>
       <c r="D115">
-        <v>3.97</v>
+        <v>400</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B116">
-        <v>57.783</v>
+        <v>-13.022</v>
       </c>
       <c r="C116">
-        <v>-100</v>
+        <v>903.1</v>
       </c>
       <c r="D116">
-        <v>-100</v>
+        <v>903.1</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B117">
-        <v>58.11</v>
+        <v>-9.525</v>
       </c>
       <c r="C117">
-        <v>0.256</v>
+        <v>899.699</v>
       </c>
       <c r="D117">
-        <v>0.256</v>
+        <v>899.699</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B118">
-        <v>41.206</v>
+        <v>31.698</v>
       </c>
       <c r="C118">
-        <v>7.494</v>
+        <v>294.093</v>
       </c>
       <c r="D118">
-        <v>7.494</v>
+        <v>294.093</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B119">
-        <v>-2.859</v>
+        <v>2.039</v>
       </c>
       <c r="C119">
-        <v>884.718</v>
+        <v>397.667</v>
       </c>
       <c r="D119">
-        <v>884.718</v>
+        <v>397.667</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B120">
-        <v>54.176</v>
+        <v>-22.304</v>
       </c>
       <c r="C120">
-        <v>50.272</v>
+        <v>935.633</v>
       </c>
       <c r="D120">
-        <v>50.272</v>
+        <v>935.633</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B121">
-        <v>75.71599999999999</v>
+        <v>-28.969</v>
       </c>
       <c r="C121">
-        <v>-1160.759</v>
+        <v>954.976</v>
       </c>
       <c r="D121">
-        <v>-1160.759</v>
+        <v>954.976</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B122">
-        <v>50.293</v>
+        <v>-6.713</v>
       </c>
       <c r="C122">
-        <v>-126.581</v>
+        <v>899.518</v>
       </c>
       <c r="D122">
-        <v>-126.581</v>
+        <v>899.518</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B123">
-        <v>12.05</v>
+        <v>-12.036</v>
       </c>
       <c r="C123">
-        <v>1.551</v>
+        <v>914.524</v>
       </c>
       <c r="D123">
-        <v>1.551</v>
+        <v>914.524</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B124">
-        <v>2.123</v>
+        <v>-34.017</v>
       </c>
       <c r="C124">
-        <v>1.562</v>
+        <v>899.867</v>
       </c>
       <c r="D124">
-        <v>1.562</v>
+        <v>899.867</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B125">
-        <v>-23.774</v>
+        <v>21.456</v>
       </c>
       <c r="C125">
-        <v>859.173</v>
+        <v>278.241</v>
       </c>
       <c r="D125">
-        <v>859.173</v>
+        <v>278.241</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B126">
-        <v>-21.283</v>
+        <v>0.254</v>
       </c>
       <c r="C126">
-        <v>890.458</v>
+        <v>314.88</v>
       </c>
       <c r="D126">
-        <v>890.458</v>
+        <v>314.88</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B127">
-        <v>-60.119</v>
+        <v>-2.409</v>
       </c>
       <c r="C127">
-        <v>1130.191</v>
+        <v>897.823</v>
       </c>
       <c r="D127">
-        <v>1130.191</v>
+        <v>897.823</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B128">
-        <v>-70.705</v>
+        <v>16.375</v>
       </c>
       <c r="C128">
-        <v>4741.074</v>
+        <v>48.726</v>
       </c>
       <c r="D128">
-        <v>4741.074</v>
+        <v>48.726</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B129">
-        <v>-65.901</v>
+        <v>24.01</v>
       </c>
       <c r="C129">
-        <v>2425.999</v>
+        <v>-14.382</v>
       </c>
       <c r="D129">
-        <v>2425.999</v>
+        <v>-14.382</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B130">
-        <v>-71.43300000000001</v>
+        <v>11.606</v>
       </c>
       <c r="C130">
-        <v>1028.586</v>
+        <v>45.895</v>
       </c>
       <c r="D130">
-        <v>1028.586</v>
+        <v>45.895</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B131">
-        <v>-36.133</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>1044.07</v>
+        <v>869.794</v>
       </c>
       <c r="D131">
-        <v>1044.07</v>
+        <v>869.794</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B132">
-        <v>-38.062</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>1043.442</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>1043.442</v>
+        <v>0</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B133">
-        <v>-35.632</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>1044.07</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>1044.07</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>26.05.20261</t>
-  </si>
-  <si>
-    <t>26.05.20262</t>
-  </si>
-  <si>
-    <t>26.05.20263</t>
-  </si>
-  <si>
-    <t>26.05.20264</t>
-  </si>
-  <si>
-    <t>26.05.20265</t>
-  </si>
-  <si>
-    <t>26.05.20266</t>
-  </si>
-  <si>
-    <t>26.05.20267</t>
-  </si>
-  <si>
-    <t>26.05.20268</t>
-  </si>
-  <si>
-    <t>26.05.20269</t>
-  </si>
-  <si>
-    <t>26.05.202610</t>
-  </si>
-  <si>
-    <t>26.05.202611</t>
-  </si>
-  <si>
-    <t>26.05.202612</t>
-  </si>
-  <si>
-    <t>26.05.202613</t>
-  </si>
-  <si>
-    <t>26.05.202614</t>
-  </si>
-  <si>
-    <t>26.05.202615</t>
-  </si>
-  <si>
-    <t>26.05.202616</t>
-  </si>
-  <si>
-    <t>26.05.202617</t>
-  </si>
-  <si>
-    <t>26.05.202618</t>
-  </si>
-  <si>
-    <t>26.05.202619</t>
-  </si>
-  <si>
-    <t>26.05.202620</t>
-  </si>
-  <si>
-    <t>26.05.202621</t>
-  </si>
-  <si>
-    <t>26.05.202622</t>
-  </si>
-  <si>
-    <t>26.05.202623</t>
-  </si>
-  <si>
-    <t>26.05.202624</t>
-  </si>
-  <si>
-    <t>26.05.202625</t>
-  </si>
-  <si>
-    <t>26.05.202626</t>
-  </si>
-  <si>
-    <t>26.05.202627</t>
-  </si>
-  <si>
-    <t>26.05.202628</t>
-  </si>
-  <si>
-    <t>26.05.202629</t>
-  </si>
-  <si>
-    <t>26.05.202630</t>
-  </si>
-  <si>
-    <t>26.05.202631</t>
-  </si>
-  <si>
-    <t>26.05.202632</t>
-  </si>
-  <si>
-    <t>26.05.202633</t>
-  </si>
-  <si>
-    <t>26.05.202634</t>
-  </si>
-  <si>
-    <t>26.05.202635</t>
-  </si>
-  <si>
-    <t>26.05.202636</t>
-  </si>
-  <si>
-    <t>26.05.202637</t>
-  </si>
-  <si>
-    <t>26.05.202638</t>
-  </si>
-  <si>
-    <t>26.05.202639</t>
-  </si>
-  <si>
-    <t>26.05.202640</t>
-  </si>
-  <si>
-    <t>26.05.202641</t>
-  </si>
-  <si>
-    <t>26.05.202642</t>
-  </si>
-  <si>
-    <t>26.05.202643</t>
-  </si>
-  <si>
-    <t>26.05.202644</t>
-  </si>
-  <si>
-    <t>26.05.202645</t>
-  </si>
-  <si>
-    <t>26.05.202646</t>
-  </si>
-  <si>
-    <t>26.05.202647</t>
-  </si>
-  <si>
-    <t>26.05.202648</t>
-  </si>
-  <si>
-    <t>26.05.202649</t>
-  </si>
-  <si>
-    <t>26.05.202650</t>
-  </si>
-  <si>
-    <t>26.05.202651</t>
-  </si>
-  <si>
-    <t>26.05.202652</t>
-  </si>
-  <si>
-    <t>26.05.202653</t>
-  </si>
-  <si>
-    <t>26.05.202654</t>
-  </si>
-  <si>
-    <t>26.05.202655</t>
-  </si>
-  <si>
-    <t>26.05.202656</t>
-  </si>
-  <si>
-    <t>26.05.202657</t>
-  </si>
-  <si>
-    <t>26.05.202658</t>
-  </si>
-  <si>
-    <t>26.05.202659</t>
-  </si>
-  <si>
-    <t>26.05.202660</t>
-  </si>
-  <si>
-    <t>26.05.202661</t>
-  </si>
-  <si>
-    <t>26.05.202662</t>
-  </si>
-  <si>
-    <t>26.05.202663</t>
-  </si>
-  <si>
-    <t>26.05.202664</t>
-  </si>
-  <si>
-    <t>26.05.202665</t>
-  </si>
-  <si>
-    <t>26.05.202666</t>
-  </si>
-  <si>
-    <t>26.05.202667</t>
-  </si>
-  <si>
-    <t>26.05.202668</t>
-  </si>
-  <si>
-    <t>26.05.202669</t>
-  </si>
-  <si>
-    <t>26.05.202670</t>
-  </si>
-  <si>
-    <t>26.05.202671</t>
-  </si>
-  <si>
-    <t>26.05.202672</t>
-  </si>
-  <si>
-    <t>26.05.202673</t>
-  </si>
-  <si>
-    <t>26.05.202674</t>
-  </si>
-  <si>
-    <t>26.05.202675</t>
-  </si>
-  <si>
-    <t>26.05.202676</t>
-  </si>
-  <si>
-    <t>26.05.202677</t>
-  </si>
-  <si>
-    <t>26.05.202678</t>
-  </si>
-  <si>
-    <t>26.05.202679</t>
-  </si>
-  <si>
-    <t>26.05.202680</t>
-  </si>
-  <si>
-    <t>26.05.202681</t>
-  </si>
-  <si>
-    <t>26.05.202682</t>
-  </si>
-  <si>
-    <t>26.05.202683</t>
-  </si>
-  <si>
-    <t>26.05.202684</t>
-  </si>
-  <si>
-    <t>26.05.202685</t>
-  </si>
-  <si>
-    <t>26.05.202686</t>
-  </si>
-  <si>
-    <t>26.05.202687</t>
-  </si>
-  <si>
-    <t>26.05.202688</t>
-  </si>
-  <si>
-    <t>26.05.202689</t>
-  </si>
-  <si>
-    <t>26.05.202690</t>
-  </si>
-  <si>
-    <t>26.05.202691</t>
-  </si>
-  <si>
-    <t>26.05.202692</t>
-  </si>
-  <si>
-    <t>26.05.202693</t>
-  </si>
-  <si>
-    <t>26.05.202694</t>
-  </si>
-  <si>
-    <t>26.05.202695</t>
-  </si>
-  <si>
-    <t>26.05.202696</t>
-  </si>
-  <si>
     <t>27.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>27.05.202696</t>
+  </si>
+  <si>
+    <t>28.05.20261</t>
+  </si>
+  <si>
+    <t>28.05.20262</t>
+  </si>
+  <si>
+    <t>28.05.20263</t>
+  </si>
+  <si>
+    <t>28.05.20264</t>
+  </si>
+  <si>
+    <t>28.05.20265</t>
+  </si>
+  <si>
+    <t>28.05.20266</t>
+  </si>
+  <si>
+    <t>28.05.20267</t>
+  </si>
+  <si>
+    <t>28.05.20268</t>
+  </si>
+  <si>
+    <t>28.05.20269</t>
+  </si>
+  <si>
+    <t>28.05.202610</t>
+  </si>
+  <si>
+    <t>28.05.202611</t>
+  </si>
+  <si>
+    <t>28.05.202612</t>
+  </si>
+  <si>
+    <t>28.05.202613</t>
+  </si>
+  <si>
+    <t>28.05.202614</t>
+  </si>
+  <si>
+    <t>28.05.202615</t>
+  </si>
+  <si>
+    <t>28.05.202616</t>
+  </si>
+  <si>
+    <t>28.05.202617</t>
+  </si>
+  <si>
+    <t>28.05.202618</t>
+  </si>
+  <si>
+    <t>28.05.202619</t>
+  </si>
+  <si>
+    <t>28.05.202620</t>
+  </si>
+  <si>
+    <t>28.05.202621</t>
+  </si>
+  <si>
+    <t>28.05.202622</t>
+  </si>
+  <si>
+    <t>28.05.202623</t>
+  </si>
+  <si>
+    <t>28.05.202624</t>
+  </si>
+  <si>
+    <t>28.05.202625</t>
+  </si>
+  <si>
+    <t>28.05.202626</t>
+  </si>
+  <si>
+    <t>28.05.202627</t>
+  </si>
+  <si>
+    <t>28.05.202628</t>
+  </si>
+  <si>
+    <t>28.05.202629</t>
+  </si>
+  <si>
+    <t>28.05.202630</t>
+  </si>
+  <si>
+    <t>28.05.202631</t>
+  </si>
+  <si>
+    <t>28.05.202632</t>
+  </si>
+  <si>
+    <t>28.05.202633</t>
+  </si>
+  <si>
+    <t>28.05.202634</t>
+  </si>
+  <si>
+    <t>28.05.202635</t>
+  </si>
+  <si>
+    <t>28.05.202636</t>
+  </si>
+  <si>
+    <t>28.05.202637</t>
+  </si>
+  <si>
+    <t>28.05.202638</t>
+  </si>
+  <si>
+    <t>28.05.202639</t>
+  </si>
+  <si>
+    <t>28.05.202640</t>
+  </si>
+  <si>
+    <t>28.05.202641</t>
+  </si>
+  <si>
+    <t>28.05.202642</t>
+  </si>
+  <si>
+    <t>28.05.202643</t>
+  </si>
+  <si>
+    <t>28.05.202644</t>
+  </si>
+  <si>
+    <t>28.05.202645</t>
+  </si>
+  <si>
+    <t>28.05.202646</t>
+  </si>
+  <si>
+    <t>28.05.202647</t>
+  </si>
+  <si>
+    <t>28.05.202648</t>
+  </si>
+  <si>
+    <t>28.05.202649</t>
+  </si>
+  <si>
+    <t>28.05.202650</t>
+  </si>
+  <si>
+    <t>28.05.202651</t>
+  </si>
+  <si>
+    <t>28.05.202652</t>
+  </si>
+  <si>
+    <t>28.05.202653</t>
+  </si>
+  <si>
+    <t>28.05.202654</t>
+  </si>
+  <si>
+    <t>28.05.202655</t>
+  </si>
+  <si>
+    <t>28.05.202656</t>
+  </si>
+  <si>
+    <t>28.05.202657</t>
+  </si>
+  <si>
+    <t>28.05.202658</t>
+  </si>
+  <si>
+    <t>28.05.202659</t>
+  </si>
+  <si>
+    <t>28.05.202660</t>
+  </si>
+  <si>
+    <t>28.05.202661</t>
+  </si>
+  <si>
+    <t>28.05.202662</t>
+  </si>
+  <si>
+    <t>28.05.202663</t>
+  </si>
+  <si>
+    <t>28.05.202664</t>
+  </si>
+  <si>
+    <t>28.05.202665</t>
+  </si>
+  <si>
+    <t>28.05.202666</t>
+  </si>
+  <si>
+    <t>28.05.202667</t>
+  </si>
+  <si>
+    <t>28.05.202668</t>
+  </si>
+  <si>
+    <t>28.05.202669</t>
+  </si>
+  <si>
+    <t>28.05.202670</t>
+  </si>
+  <si>
+    <t>28.05.202671</t>
+  </si>
+  <si>
+    <t>28.05.202672</t>
+  </si>
+  <si>
+    <t>28.05.202673</t>
+  </si>
+  <si>
+    <t>28.05.202674</t>
+  </si>
+  <si>
+    <t>28.05.202675</t>
+  </si>
+  <si>
+    <t>28.05.202676</t>
+  </si>
+  <si>
+    <t>28.05.202677</t>
+  </si>
+  <si>
+    <t>28.05.202678</t>
+  </si>
+  <si>
+    <t>28.05.202679</t>
+  </si>
+  <si>
+    <t>28.05.202680</t>
+  </si>
+  <si>
+    <t>28.05.202681</t>
+  </si>
+  <si>
+    <t>28.05.202682</t>
+  </si>
+  <si>
+    <t>28.05.202683</t>
+  </si>
+  <si>
+    <t>28.05.202684</t>
+  </si>
+  <si>
+    <t>28.05.202685</t>
+  </si>
+  <si>
+    <t>28.05.202686</t>
+  </si>
+  <si>
+    <t>28.05.202687</t>
+  </si>
+  <si>
+    <t>28.05.202688</t>
+  </si>
+  <si>
+    <t>28.05.202689</t>
+  </si>
+  <si>
+    <t>28.05.202690</t>
+  </si>
+  <si>
+    <t>28.05.202691</t>
+  </si>
+  <si>
+    <t>28.05.202692</t>
+  </si>
+  <si>
+    <t>28.05.202693</t>
+  </si>
+  <si>
+    <t>28.05.202694</t>
+  </si>
+  <si>
+    <t>28.05.202695</t>
+  </si>
+  <si>
+    <t>28.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
-        <v>38.844</v>
+        <v>12.075</v>
       </c>
       <c r="C6">
-        <v>-111.659</v>
+        <v>400</v>
       </c>
       <c r="D6">
-        <v>-111.659</v>
+        <v>400</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
-        <v>57.277</v>
+        <v>-5.87</v>
       </c>
       <c r="C7">
-        <v>-260.411</v>
+        <v>899.306</v>
       </c>
       <c r="D7">
-        <v>-260.411</v>
+        <v>899.306</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
-        <v>69.351</v>
+        <v>-16.545</v>
       </c>
       <c r="C8">
-        <v>-123.282</v>
+        <v>899.846</v>
       </c>
       <c r="D8">
-        <v>-123.282</v>
+        <v>899.846</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
-        <v>78.907</v>
+        <v>-11.066</v>
       </c>
       <c r="C9">
-        <v>-1117.639</v>
+        <v>898.688</v>
       </c>
       <c r="D9">
-        <v>-1117.639</v>
+        <v>898.688</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
-        <v>80.619</v>
+        <v>-12.106</v>
       </c>
       <c r="C10">
-        <v>-4145.639</v>
+        <v>894.3339999999999</v>
       </c>
       <c r="D10">
-        <v>-4145.639</v>
+        <v>894.3339999999999</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
-        <v>71.125</v>
+        <v>-10.068</v>
       </c>
       <c r="C11">
-        <v>-7495.051</v>
+        <v>885.827</v>
       </c>
       <c r="D11">
-        <v>-7495.051</v>
+        <v>885.827</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
-        <v>65.625</v>
+        <v>-3.179</v>
       </c>
       <c r="C12">
-        <v>-7155.632</v>
+        <v>890.564</v>
       </c>
       <c r="D12">
-        <v>-7155.632</v>
+        <v>890.564</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
-        <v>74.58199999999999</v>
+        <v>-4.992</v>
       </c>
       <c r="C13">
-        <v>-1210.419</v>
+        <v>898.273</v>
       </c>
       <c r="D13">
-        <v>-1210.419</v>
+        <v>898.273</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
-        <v>78.73699999999999</v>
+        <v>-3.175</v>
       </c>
       <c r="C14">
-        <v>-50.901</v>
+        <v>898.127</v>
       </c>
       <c r="D14">
-        <v>-50.901</v>
+        <v>898.127</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
-        <v>75.955</v>
+        <v>-13.868</v>
       </c>
       <c r="C15">
-        <v>-288.502</v>
+        <v>915.122</v>
       </c>
       <c r="D15">
-        <v>-288.502</v>
+        <v>915.122</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
-        <v>86.432</v>
+        <v>-32.38</v>
       </c>
       <c r="C16">
-        <v>-54.534</v>
+        <v>944.3150000000001</v>
       </c>
       <c r="D16">
-        <v>-54.534</v>
+        <v>944.3150000000001</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
-        <v>132.921</v>
+        <v>-19.105</v>
       </c>
       <c r="C17">
-        <v>-1103.312</v>
+        <v>902.775</v>
       </c>
       <c r="D17">
-        <v>-1103.312</v>
+        <v>902.775</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
-        <v>91.51600000000001</v>
+        <v>16.872</v>
       </c>
       <c r="C18">
-        <v>-2583.893</v>
+        <v>386</v>
       </c>
       <c r="D18">
-        <v>-2583.893</v>
+        <v>386</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
-        <v>54.538</v>
+        <v>1.933</v>
       </c>
       <c r="C19">
-        <v>3.97</v>
+        <v>400</v>
       </c>
       <c r="D19">
-        <v>3.97</v>
+        <v>400</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
-        <v>57.783</v>
+        <v>-13.022</v>
       </c>
       <c r="C20">
-        <v>-100</v>
+        <v>903.1</v>
       </c>
       <c r="D20">
-        <v>-100</v>
+        <v>903.1</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>58.11</v>
+        <v>-9.525</v>
       </c>
       <c r="C21">
-        <v>0.256</v>
+        <v>899.699</v>
       </c>
       <c r="D21">
-        <v>0.256</v>
+        <v>899.699</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
-        <v>41.206</v>
+        <v>31.698</v>
       </c>
       <c r="C22">
-        <v>7.494</v>
+        <v>294.093</v>
       </c>
       <c r="D22">
-        <v>7.494</v>
+        <v>294.093</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>-2.859</v>
+        <v>2.039</v>
       </c>
       <c r="C23">
-        <v>884.718</v>
+        <v>397.667</v>
       </c>
       <c r="D23">
-        <v>884.718</v>
+        <v>397.667</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
-        <v>54.176</v>
+        <v>-22.304</v>
       </c>
       <c r="C24">
-        <v>50.272</v>
+        <v>935.633</v>
       </c>
       <c r="D24">
-        <v>50.272</v>
+        <v>935.633</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>75.71599999999999</v>
+        <v>-28.969</v>
       </c>
       <c r="C25">
-        <v>-1160.759</v>
+        <v>954.976</v>
       </c>
       <c r="D25">
-        <v>-1160.759</v>
+        <v>954.976</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>50.293</v>
+        <v>-6.713</v>
       </c>
       <c r="C26">
-        <v>-126.581</v>
+        <v>899.518</v>
       </c>
       <c r="D26">
-        <v>-126.581</v>
+        <v>899.518</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>12.05</v>
+        <v>-12.036</v>
       </c>
       <c r="C27">
-        <v>1.551</v>
+        <v>914.524</v>
       </c>
       <c r="D27">
-        <v>1.551</v>
+        <v>914.524</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>2.123</v>
+        <v>-34.017</v>
       </c>
       <c r="C28">
-        <v>1.562</v>
+        <v>899.867</v>
       </c>
       <c r="D28">
-        <v>1.562</v>
+        <v>899.867</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>-23.774</v>
+        <v>21.456</v>
       </c>
       <c r="C29">
-        <v>859.173</v>
+        <v>278.241</v>
       </c>
       <c r="D29">
-        <v>859.173</v>
+        <v>278.241</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>-21.283</v>
+        <v>0.254</v>
       </c>
       <c r="C30">
-        <v>890.458</v>
+        <v>314.88</v>
       </c>
       <c r="D30">
-        <v>890.458</v>
+        <v>314.88</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>-60.119</v>
+        <v>-2.409</v>
       </c>
       <c r="C31">
-        <v>1130.191</v>
+        <v>897.823</v>
       </c>
       <c r="D31">
-        <v>1130.191</v>
+        <v>897.823</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>-70.705</v>
+        <v>16.375</v>
       </c>
       <c r="C32">
-        <v>4741.074</v>
+        <v>48.726</v>
       </c>
       <c r="D32">
-        <v>4741.074</v>
+        <v>48.726</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>-65.901</v>
+        <v>24.01</v>
       </c>
       <c r="C33">
-        <v>2425.999</v>
+        <v>-14.382</v>
       </c>
       <c r="D33">
-        <v>2425.999</v>
+        <v>-14.382</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>-71.43300000000001</v>
+        <v>11.606</v>
       </c>
       <c r="C34">
-        <v>1028.586</v>
+        <v>45.895</v>
       </c>
       <c r="D34">
-        <v>1028.586</v>
+        <v>45.895</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>-36.133</v>
+        <v>-22.54</v>
       </c>
       <c r="C35">
-        <v>1044.07</v>
+        <v>869.794</v>
       </c>
       <c r="D35">
-        <v>1044.07</v>
+        <v>869.794</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>-38.062</v>
+        <v>1.772</v>
       </c>
       <c r="C36">
-        <v>1043.442</v>
+        <v>113.065</v>
       </c>
       <c r="D36">
-        <v>1043.442</v>
+        <v>113.065</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>-35.632</v>
+        <v>-14.458</v>
       </c>
       <c r="C37">
-        <v>1044.07</v>
+        <v>751.8440000000001</v>
       </c>
       <c r="D37">
-        <v>1044.07</v>
+        <v>751.8440000000001</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>-55.316</v>
+        <v>-38.269</v>
       </c>
       <c r="C38">
-        <v>715.449</v>
+        <v>797.655</v>
       </c>
       <c r="D38">
-        <v>715.449</v>
+        <v>797.655</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>-32.127</v>
+        <v>-45.228</v>
       </c>
       <c r="C39">
-        <v>712.979</v>
+        <v>1016.232</v>
       </c>
       <c r="D39">
-        <v>712.979</v>
+        <v>1016.232</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>-13.767</v>
+        <v>-20.675</v>
       </c>
       <c r="C40">
-        <v>707.923</v>
+        <v>801.324</v>
       </c>
       <c r="D40">
-        <v>707.923</v>
+        <v>801.324</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>28.607</v>
+        <v>-16.327</v>
       </c>
       <c r="C41">
-        <v>-54.144</v>
+        <v>713.4400000000001</v>
       </c>
       <c r="D41">
-        <v>-54.144</v>
+        <v>713.4400000000001</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>47.427</v>
+        <v>-55.946</v>
       </c>
       <c r="C42">
-        <v>-71.11799999999999</v>
+        <v>1900.074</v>
       </c>
       <c r="D42">
-        <v>-71.11799999999999</v>
+        <v>1900.074</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>14.54</v>
+        <v>-61.877</v>
       </c>
       <c r="C43">
-        <v>-7.551</v>
+        <v>798.088</v>
       </c>
       <c r="D43">
-        <v>-7.551</v>
+        <v>798.088</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>55.577</v>
+        <v>-22.693</v>
       </c>
       <c r="C44">
-        <v>48.077</v>
+        <v>479.02</v>
       </c>
       <c r="D44">
-        <v>48.077</v>
+        <v>479.02</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
-        <v>59.629</v>
+        <v>7.154</v>
       </c>
       <c r="C45">
-        <v>-2251.176</v>
+        <v>87.07599999999999</v>
       </c>
       <c r="D45">
-        <v>-2251.176</v>
+        <v>87.07599999999999</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
-        <v>47.167</v>
+        <v>-14.115</v>
       </c>
       <c r="C46">
-        <v>-1202.297</v>
+        <v>466.18</v>
       </c>
       <c r="D46">
-        <v>-1202.297</v>
+        <v>466.18</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
-        <v>52.6</v>
+        <v>18.998</v>
       </c>
       <c r="C47">
-        <v>-87.43300000000001</v>
+        <v>-46.848</v>
       </c>
       <c r="D47">
-        <v>-87.43300000000001</v>
+        <v>-46.848</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>67.069</v>
+        <v>-13.409</v>
       </c>
       <c r="C48">
-        <v>-1693.846</v>
+        <v>551.691</v>
       </c>
       <c r="D48">
-        <v>-1693.846</v>
+        <v>551.691</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>28.705</v>
+        <v>-13.101</v>
       </c>
       <c r="C49">
-        <v>-109.117</v>
+        <v>808.6559999999999</v>
       </c>
       <c r="D49">
-        <v>-109.117</v>
+        <v>808.6559999999999</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>30.855</v>
+        <v>45.667</v>
       </c>
       <c r="C50">
-        <v>242.144</v>
+        <v>-121.341</v>
       </c>
       <c r="D50">
-        <v>242.144</v>
+        <v>-121.341</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
-        <v>50.189</v>
+        <v>47.343</v>
       </c>
       <c r="C51">
-        <v>-161.76</v>
+        <v>-151.694</v>
       </c>
       <c r="D51">
-        <v>-161.76</v>
+        <v>-151.694</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>40.747</v>
+        <v>20.847</v>
       </c>
       <c r="C52">
-        <v>-52.054</v>
+        <v>104.843</v>
       </c>
       <c r="D52">
-        <v>-52.054</v>
+        <v>104.843</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
-        <v>59.968</v>
+        <v>52.854</v>
       </c>
       <c r="C53">
-        <v>-846.576</v>
+        <v>167.583</v>
       </c>
       <c r="D53">
-        <v>-846.576</v>
+        <v>167.583</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>35.413</v>
+        <v>5.911</v>
       </c>
       <c r="C54">
-        <v>-529.067</v>
+        <v>206.722</v>
       </c>
       <c r="D54">
-        <v>-529.067</v>
+        <v>206.722</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>30.167</v>
+        <v>-1.35</v>
       </c>
       <c r="C55">
-        <v>-12.656</v>
+        <v>448.525</v>
       </c>
       <c r="D55">
-        <v>-12.656</v>
+        <v>448.525</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>-9.234</v>
+        <v>-22.836</v>
       </c>
       <c r="C56">
-        <v>489.455</v>
+        <v>473.044</v>
       </c>
       <c r="D56">
-        <v>489.455</v>
+        <v>473.044</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>14.419</v>
+        <v>7.488</v>
       </c>
       <c r="C57">
-        <v>124.022</v>
+        <v>-49</v>
       </c>
       <c r="D57">
-        <v>124.022</v>
+        <v>-49</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>49.964</v>
+        <v>-1.364</v>
       </c>
       <c r="C58">
-        <v>61.758</v>
+        <v>621.876</v>
       </c>
       <c r="D58">
-        <v>61.758</v>
+        <v>621.876</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>19.888</v>
+        <v>-0.248</v>
       </c>
       <c r="C59">
-        <v>381.878</v>
+        <v>450.793</v>
       </c>
       <c r="D59">
-        <v>381.878</v>
+        <v>450.793</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>15.134</v>
+        <v>-10.246</v>
       </c>
       <c r="C60">
-        <v>397.135</v>
+        <v>715.404</v>
       </c>
       <c r="D60">
-        <v>397.135</v>
+        <v>715.404</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>47.44</v>
+        <v>-29.816</v>
       </c>
       <c r="C61">
-        <v>388.02</v>
+        <v>662.4450000000001</v>
       </c>
       <c r="D61">
-        <v>388.02</v>
+        <v>662.4450000000001</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>45.965</v>
+        <v>72.374</v>
       </c>
       <c r="C62">
-        <v>-154.627</v>
+        <v>-66.74299999999999</v>
       </c>
       <c r="D62">
-        <v>-154.627</v>
+        <v>-66.74299999999999</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>-8.573</v>
+        <v>54.701</v>
       </c>
       <c r="C63">
-        <v>818.009</v>
+        <v>-68.342</v>
       </c>
       <c r="D63">
-        <v>818.009</v>
+        <v>-68.342</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>13.276</v>
+        <v>47.697</v>
       </c>
       <c r="C64">
-        <v>400</v>
+        <v>-78.45099999999999</v>
       </c>
       <c r="D64">
-        <v>400</v>
+        <v>-78.45099999999999</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>-2.599</v>
+        <v>36.573</v>
       </c>
       <c r="C65">
-        <v>790.567</v>
+        <v>-68.56699999999999</v>
       </c>
       <c r="D65">
-        <v>790.567</v>
+        <v>-68.56699999999999</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>10.221</v>
+        <v>128.616</v>
       </c>
       <c r="C66">
-        <v>23.874</v>
+        <v>-1353.037</v>
       </c>
       <c r="D66">
-        <v>23.874</v>
+        <v>-1353.037</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>52.148</v>
+        <v>110.142</v>
       </c>
       <c r="C67">
-        <v>277.234</v>
+        <v>-99.15600000000001</v>
       </c>
       <c r="D67">
-        <v>277.234</v>
+        <v>-99.15600000000001</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>8.109</v>
+        <v>31.499</v>
       </c>
       <c r="C68">
-        <v>400</v>
+        <v>-81.096</v>
       </c>
       <c r="D68">
-        <v>400</v>
+        <v>-81.096</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>16.448</v>
+        <v>6.802</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>-106</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>-106</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>62.181</v>
+        <v>77.788</v>
       </c>
       <c r="C70">
-        <v>359.431</v>
+        <v>400</v>
       </c>
       <c r="D70">
-        <v>359.431</v>
+        <v>400</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>76.77200000000001</v>
+        <v>-9.612</v>
       </c>
       <c r="C71">
-        <v>386.6</v>
+        <v>1133.659</v>
       </c>
       <c r="D71">
-        <v>386.6</v>
+        <v>1133.659</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>73.01000000000001</v>
+        <v>-28.507</v>
       </c>
       <c r="C72">
-        <v>400</v>
+        <v>3073.582</v>
       </c>
       <c r="D72">
-        <v>400</v>
+        <v>3073.582</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>67.045</v>
+        <v>-66.172</v>
       </c>
       <c r="C73">
-        <v>305.53</v>
+        <v>6455.336</v>
       </c>
       <c r="D73">
-        <v>305.53</v>
+        <v>6455.336</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>173.807</v>
+        <v>-41.991</v>
       </c>
       <c r="C74">
-        <v>129.275</v>
+        <v>1427.532</v>
       </c>
       <c r="D74">
-        <v>129.275</v>
+        <v>1427.532</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>114.728</v>
+        <v>-63.673</v>
       </c>
       <c r="C75">
-        <v>-3406.708</v>
+        <v>1360.693</v>
       </c>
       <c r="D75">
-        <v>-3406.708</v>
+        <v>1360.693</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>84.676</v>
+        <v>-29.271</v>
       </c>
       <c r="C76">
-        <v>362.12</v>
+        <v>1284.864</v>
       </c>
       <c r="D76">
-        <v>362.12</v>
+        <v>1284.864</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>53.681</v>
+        <v>-32.629</v>
       </c>
       <c r="C77">
-        <v>400</v>
+        <v>1287.297</v>
       </c>
       <c r="D77">
-        <v>400</v>
+        <v>1287.297</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>37.751</v>
+        <v>60.11</v>
       </c>
       <c r="C78">
-        <v>322.517</v>
+        <v>-0.022</v>
       </c>
       <c r="D78">
-        <v>322.517</v>
+        <v>-0.022</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>94.55800000000001</v>
+        <v>39.546</v>
       </c>
       <c r="C79">
-        <v>341.04</v>
+        <v>80.235</v>
       </c>
       <c r="D79">
-        <v>341.04</v>
+        <v>80.235</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>78.816</v>
+        <v>41.74</v>
       </c>
       <c r="C80">
-        <v>332.531</v>
+        <v>280.164</v>
       </c>
       <c r="D80">
-        <v>332.531</v>
+        <v>280.164</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>129.071</v>
+        <v>20.163</v>
       </c>
       <c r="C81">
-        <v>326.431</v>
+        <v>316.503</v>
       </c>
       <c r="D81">
-        <v>326.431</v>
+        <v>316.503</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>109.043</v>
+        <v>48.001</v>
       </c>
       <c r="C82">
-        <v>326.679</v>
+        <v>277.893</v>
       </c>
       <c r="D82">
-        <v>326.679</v>
+        <v>277.893</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
-        <v>72.625</v>
+        <v>45.606</v>
       </c>
       <c r="C83">
-        <v>400</v>
+        <v>312.031</v>
       </c>
       <c r="D83">
-        <v>400</v>
+        <v>312.031</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
-        <v>35.983</v>
+        <v>33.917</v>
       </c>
       <c r="C84">
-        <v>358.125</v>
+        <v>302.378</v>
       </c>
       <c r="D84">
-        <v>358.125</v>
+        <v>302.378</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
-        <v>3.518</v>
+        <v>15.888</v>
       </c>
       <c r="C85">
-        <v>338.154</v>
+        <v>346.876</v>
       </c>
       <c r="D85">
-        <v>338.154</v>
+        <v>346.876</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
-        <v>-31.274</v>
+        <v>-29.132</v>
       </c>
       <c r="C86">
-        <v>2867.661</v>
+        <v>891.9829999999999</v>
       </c>
       <c r="D86">
-        <v>2867.661</v>
+        <v>891.9829999999999</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
-        <v>-51.458</v>
+        <v>-15.003</v>
       </c>
       <c r="C87">
-        <v>5965.245</v>
+        <v>942.014</v>
       </c>
       <c r="D87">
-        <v>5965.245</v>
+        <v>942.014</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
-        <v>-87.119</v>
+        <v>5.984</v>
       </c>
       <c r="C88">
-        <v>6784.287</v>
+        <v>1590.033</v>
       </c>
       <c r="D88">
-        <v>6784.287</v>
+        <v>1590.033</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
-        <v>-19.142</v>
+        <v>42.648</v>
       </c>
       <c r="C89">
-        <v>2071.499</v>
+        <v>-109.875</v>
       </c>
       <c r="D89">
-        <v>2071.499</v>
+        <v>-109.875</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.762</v>
+        <v>32.615</v>
       </c>
       <c r="C90">
-        <v>93.515</v>
+        <v>-78.14</v>
       </c>
       <c r="D90">
-        <v>93.515</v>
+        <v>-78.14</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
-        <v>-37.721</v>
+        <v>81.566</v>
       </c>
       <c r="C91">
-        <v>1403.55</v>
+        <v>-38.51</v>
       </c>
       <c r="D91">
-        <v>1403.55</v>
+        <v>-38.51</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
-        <v>-31.838</v>
+        <v>63.908</v>
       </c>
       <c r="C92">
-        <v>1340.074</v>
+        <v>-61.003</v>
       </c>
       <c r="D92">
-        <v>1340.074</v>
+        <v>-61.003</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
-        <v>-21.266</v>
+        <v>42.843</v>
       </c>
       <c r="C93">
-        <v>1150.009</v>
+        <v>2.42</v>
       </c>
       <c r="D93">
-        <v>1150.009</v>
+        <v>2.42</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
-        <v>-15.279</v>
+        <v>6.839</v>
       </c>
       <c r="C94">
-        <v>1088.714</v>
+        <v>3.015</v>
       </c>
       <c r="D94">
-        <v>1088.714</v>
+        <v>3.015</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
-        <v>-4.325</v>
+        <v>10.372</v>
       </c>
       <c r="C95">
-        <v>897.684</v>
+        <v>1.1</v>
       </c>
       <c r="D95">
-        <v>897.684</v>
+        <v>1.1</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
-        <v>-10.863</v>
+        <v>21.584</v>
       </c>
       <c r="C96">
-        <v>899.605</v>
+        <v>59.526</v>
       </c>
       <c r="D96">
-        <v>899.605</v>
+        <v>59.526</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
-        <v>3.691</v>
+        <v>12.601</v>
       </c>
       <c r="C97">
-        <v>69.05200000000001</v>
+        <v>251.346</v>
       </c>
       <c r="D97">
-        <v>69.05200000000001</v>
+        <v>251.346</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
-        <v>38.446</v>
+        <v>-29.084</v>
       </c>
       <c r="C98">
-        <v>184.721</v>
+        <v>898.413</v>
       </c>
       <c r="D98">
-        <v>184.721</v>
+        <v>898.413</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B99">
-        <v>49.336</v>
+        <v>-45.037</v>
       </c>
       <c r="C99">
-        <v>334.83</v>
+        <v>963.794</v>
       </c>
       <c r="D99">
-        <v>334.83</v>
+        <v>963.794</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B100">
-        <v>47.12</v>
+        <v>-102.821</v>
       </c>
       <c r="C100">
-        <v>362.797</v>
+        <v>1153.459</v>
       </c>
       <c r="D100">
-        <v>362.797</v>
+        <v>1153.459</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B101">
-        <v>13.031</v>
+        <v>-154.703</v>
       </c>
       <c r="C101">
-        <v>400</v>
+        <v>4759.836</v>
       </c>
       <c r="D101">
-        <v>400</v>
+        <v>4759.836</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B102">
-        <v>12.075</v>
+        <v>-132.906</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>4217.673</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>4217.673</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B103">
-        <v>-5.87</v>
+        <v>-273.372</v>
       </c>
       <c r="C103">
-        <v>899.306</v>
+        <v>1333.741</v>
       </c>
       <c r="D103">
-        <v>899.306</v>
+        <v>1333.741</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B104">
-        <v>-16.545</v>
+        <v>-277.269</v>
       </c>
       <c r="C104">
-        <v>899.846</v>
+        <v>1199.893</v>
       </c>
       <c r="D104">
-        <v>899.846</v>
+        <v>1199.893</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B105">
-        <v>-11.066</v>
+        <v>-208.726</v>
       </c>
       <c r="C105">
-        <v>898.688</v>
+        <v>2717.063</v>
       </c>
       <c r="D105">
-        <v>898.688</v>
+        <v>2717.063</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B106">
-        <v>-12.106</v>
+        <v>-166.824</v>
       </c>
       <c r="C106">
-        <v>894.3339999999999</v>
+        <v>1444.1</v>
       </c>
       <c r="D106">
-        <v>894.3339999999999</v>
+        <v>1444.1</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B107">
-        <v>-10.068</v>
+        <v>-212.234</v>
       </c>
       <c r="C107">
-        <v>885.827</v>
+        <v>2949.416</v>
       </c>
       <c r="D107">
-        <v>885.827</v>
+        <v>2949.416</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B108">
-        <v>-3.179</v>
+        <v>-272.455</v>
       </c>
       <c r="C108">
-        <v>890.564</v>
+        <v>4108.203</v>
       </c>
       <c r="D108">
-        <v>890.564</v>
+        <v>4108.203</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B109">
-        <v>-4.992</v>
+        <v>-286.514</v>
       </c>
       <c r="C109">
-        <v>898.273</v>
+        <v>3708.3</v>
       </c>
       <c r="D109">
-        <v>898.273</v>
+        <v>3708.3</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B110">
-        <v>-3.175</v>
+        <v>-224.058</v>
       </c>
       <c r="C110">
-        <v>898.127</v>
+        <v>1137.119</v>
       </c>
       <c r="D110">
-        <v>898.127</v>
+        <v>1137.119</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B111">
-        <v>-13.868</v>
+        <v>-209.493</v>
       </c>
       <c r="C111">
-        <v>915.122</v>
+        <v>1139.637</v>
       </c>
       <c r="D111">
-        <v>915.122</v>
+        <v>1139.637</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B112">
-        <v>-32.38</v>
+        <v>-157.946</v>
       </c>
       <c r="C112">
-        <v>944.3150000000001</v>
+        <v>1139.778</v>
       </c>
       <c r="D112">
-        <v>944.3150000000001</v>
+        <v>1139.778</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B113">
-        <v>-19.105</v>
+        <v>-135.481</v>
       </c>
       <c r="C113">
-        <v>902.775</v>
+        <v>1140.03</v>
       </c>
       <c r="D113">
-        <v>902.775</v>
+        <v>1140.03</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B114">
-        <v>16.872</v>
+        <v>-84.506</v>
       </c>
       <c r="C114">
-        <v>386</v>
+        <v>1147.47</v>
       </c>
       <c r="D114">
-        <v>386</v>
+        <v>1147.47</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.933</v>
+        <v>-45.016</v>
       </c>
       <c r="C115">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B116">
-        <v>-13.022</v>
+        <v>-17.338</v>
       </c>
       <c r="C116">
-        <v>903.1</v>
+        <v>1145.47</v>
       </c>
       <c r="D116">
-        <v>903.1</v>
+        <v>1145.47</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B117">
-        <v>-9.525</v>
+        <v>-40.205</v>
       </c>
       <c r="C117">
-        <v>899.699</v>
+        <v>1137.782</v>
       </c>
       <c r="D117">
-        <v>899.699</v>
+        <v>1137.782</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B118">
-        <v>31.698</v>
+        <v>-13.43</v>
       </c>
       <c r="C118">
-        <v>294.093</v>
+        <v>1163.404</v>
       </c>
       <c r="D118">
-        <v>294.093</v>
+        <v>1163.404</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B119">
-        <v>2.039</v>
+        <v>-33.311</v>
       </c>
       <c r="C119">
-        <v>397.667</v>
+        <v>1124.001</v>
       </c>
       <c r="D119">
-        <v>397.667</v>
+        <v>1124.001</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B120">
-        <v>-22.304</v>
+        <v>-75.09699999999999</v>
       </c>
       <c r="C120">
-        <v>935.633</v>
+        <v>1970.561</v>
       </c>
       <c r="D120">
-        <v>935.633</v>
+        <v>1970.561</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B121">
-        <v>-28.969</v>
+        <v>-78.467</v>
       </c>
       <c r="C121">
-        <v>954.976</v>
+        <v>1336.642</v>
       </c>
       <c r="D121">
-        <v>954.976</v>
+        <v>1336.642</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B122">
-        <v>-6.713</v>
+        <v>-91.221</v>
       </c>
       <c r="C122">
-        <v>899.518</v>
+        <v>3643.478</v>
       </c>
       <c r="D122">
-        <v>899.518</v>
+        <v>3643.478</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B123">
-        <v>-12.036</v>
+        <v>-116.62</v>
       </c>
       <c r="C123">
-        <v>914.524</v>
+        <v>2024.169</v>
       </c>
       <c r="D123">
-        <v>914.524</v>
+        <v>2024.169</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B124">
-        <v>-34.017</v>
+        <v>-8.458</v>
       </c>
       <c r="C124">
-        <v>899.867</v>
+        <v>1235.883</v>
       </c>
       <c r="D124">
-        <v>899.867</v>
+        <v>1235.883</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B125">
-        <v>21.456</v>
+        <v>-0.274</v>
       </c>
       <c r="C125">
-        <v>278.241</v>
+        <v>1235.39</v>
       </c>
       <c r="D125">
-        <v>278.241</v>
+        <v>1235.39</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B126">
-        <v>0.254</v>
+        <v>86.423</v>
       </c>
       <c r="C126">
-        <v>314.88</v>
+        <v>322.907</v>
       </c>
       <c r="D126">
-        <v>314.88</v>
+        <v>322.907</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B127">
-        <v>-2.409</v>
+        <v>72.20399999999999</v>
       </c>
       <c r="C127">
-        <v>897.823</v>
+        <v>-6116.777</v>
       </c>
       <c r="D127">
-        <v>897.823</v>
+        <v>-6116.777</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B128">
-        <v>16.375</v>
+        <v>64.042</v>
       </c>
       <c r="C128">
-        <v>48.726</v>
+        <v>-1691.008</v>
       </c>
       <c r="D128">
-        <v>48.726</v>
+        <v>-1691.008</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B129">
-        <v>24.01</v>
+        <v>40.418</v>
       </c>
       <c r="C129">
-        <v>-14.382</v>
+        <v>-41.292</v>
       </c>
       <c r="D129">
-        <v>-14.382</v>
+        <v>-41.292</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B130">
-        <v>11.606</v>
+        <v>47.405</v>
       </c>
       <c r="C130">
-        <v>45.895</v>
+        <v>-791.837</v>
       </c>
       <c r="D130">
-        <v>45.895</v>
+        <v>-791.837</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>32.762</v>
       </c>
       <c r="C131">
-        <v>869.794</v>
+        <v>-78.086</v>
       </c>
       <c r="D131">
-        <v>869.794</v>
+        <v>-78.086</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>24.516</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>19.752</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>19.752</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,294 +34,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>27.05.20261</t>
-  </si>
-  <si>
-    <t>27.05.20262</t>
-  </si>
-  <si>
-    <t>27.05.20263</t>
-  </si>
-  <si>
-    <t>27.05.20264</t>
-  </si>
-  <si>
-    <t>27.05.20265</t>
-  </si>
-  <si>
-    <t>27.05.20266</t>
-  </si>
-  <si>
-    <t>27.05.20267</t>
-  </si>
-  <si>
-    <t>27.05.20268</t>
-  </si>
-  <si>
-    <t>27.05.20269</t>
-  </si>
-  <si>
-    <t>27.05.202610</t>
-  </si>
-  <si>
-    <t>27.05.202611</t>
-  </si>
-  <si>
-    <t>27.05.202612</t>
-  </si>
-  <si>
-    <t>27.05.202613</t>
-  </si>
-  <si>
-    <t>27.05.202614</t>
-  </si>
-  <si>
-    <t>27.05.202615</t>
-  </si>
-  <si>
-    <t>27.05.202616</t>
-  </si>
-  <si>
-    <t>27.05.202617</t>
-  </si>
-  <si>
-    <t>27.05.202618</t>
-  </si>
-  <si>
-    <t>27.05.202619</t>
-  </si>
-  <si>
-    <t>27.05.202620</t>
-  </si>
-  <si>
-    <t>27.05.202621</t>
-  </si>
-  <si>
-    <t>27.05.202622</t>
-  </si>
-  <si>
-    <t>27.05.202623</t>
-  </si>
-  <si>
-    <t>27.05.202624</t>
-  </si>
-  <si>
-    <t>27.05.202625</t>
-  </si>
-  <si>
-    <t>27.05.202626</t>
-  </si>
-  <si>
-    <t>27.05.202627</t>
-  </si>
-  <si>
-    <t>27.05.202628</t>
-  </si>
-  <si>
-    <t>27.05.202629</t>
-  </si>
-  <si>
-    <t>27.05.202630</t>
-  </si>
-  <si>
-    <t>27.05.202631</t>
-  </si>
-  <si>
-    <t>27.05.202632</t>
-  </si>
-  <si>
-    <t>27.05.202633</t>
-  </si>
-  <si>
-    <t>27.05.202634</t>
-  </si>
-  <si>
-    <t>27.05.202635</t>
-  </si>
-  <si>
-    <t>27.05.202636</t>
-  </si>
-  <si>
-    <t>27.05.202637</t>
-  </si>
-  <si>
-    <t>27.05.202638</t>
-  </si>
-  <si>
-    <t>27.05.202639</t>
-  </si>
-  <si>
-    <t>27.05.202640</t>
-  </si>
-  <si>
-    <t>27.05.202641</t>
-  </si>
-  <si>
-    <t>27.05.202642</t>
-  </si>
-  <si>
-    <t>27.05.202643</t>
-  </si>
-  <si>
-    <t>27.05.202644</t>
-  </si>
-  <si>
-    <t>27.05.202645</t>
-  </si>
-  <si>
-    <t>27.05.202646</t>
-  </si>
-  <si>
-    <t>27.05.202647</t>
-  </si>
-  <si>
-    <t>27.05.202648</t>
-  </si>
-  <si>
-    <t>27.05.202649</t>
-  </si>
-  <si>
-    <t>27.05.202650</t>
-  </si>
-  <si>
-    <t>27.05.202651</t>
-  </si>
-  <si>
-    <t>27.05.202652</t>
-  </si>
-  <si>
-    <t>27.05.202653</t>
-  </si>
-  <si>
-    <t>27.05.202654</t>
-  </si>
-  <si>
-    <t>27.05.202655</t>
-  </si>
-  <si>
-    <t>27.05.202656</t>
-  </si>
-  <si>
-    <t>27.05.202657</t>
-  </si>
-  <si>
-    <t>27.05.202658</t>
-  </si>
-  <si>
-    <t>27.05.202659</t>
-  </si>
-  <si>
-    <t>27.05.202660</t>
-  </si>
-  <si>
-    <t>27.05.202661</t>
-  </si>
-  <si>
-    <t>27.05.202662</t>
-  </si>
-  <si>
-    <t>27.05.202663</t>
-  </si>
-  <si>
-    <t>27.05.202664</t>
-  </si>
-  <si>
-    <t>27.05.202665</t>
-  </si>
-  <si>
-    <t>27.05.202666</t>
-  </si>
-  <si>
-    <t>27.05.202667</t>
-  </si>
-  <si>
-    <t>27.05.202668</t>
-  </si>
-  <si>
-    <t>27.05.202669</t>
-  </si>
-  <si>
-    <t>27.05.202670</t>
-  </si>
-  <si>
-    <t>27.05.202671</t>
-  </si>
-  <si>
-    <t>27.05.202672</t>
-  </si>
-  <si>
-    <t>27.05.202673</t>
-  </si>
-  <si>
-    <t>27.05.202674</t>
-  </si>
-  <si>
-    <t>27.05.202675</t>
-  </si>
-  <si>
-    <t>27.05.202676</t>
-  </si>
-  <si>
-    <t>27.05.202677</t>
-  </si>
-  <si>
-    <t>27.05.202678</t>
-  </si>
-  <si>
-    <t>27.05.202679</t>
-  </si>
-  <si>
-    <t>27.05.202680</t>
-  </si>
-  <si>
-    <t>27.05.202681</t>
-  </si>
-  <si>
-    <t>27.05.202682</t>
-  </si>
-  <si>
-    <t>27.05.202683</t>
-  </si>
-  <si>
-    <t>27.05.202684</t>
-  </si>
-  <si>
-    <t>27.05.202685</t>
-  </si>
-  <si>
-    <t>27.05.202686</t>
-  </si>
-  <si>
-    <t>27.05.202687</t>
-  </si>
-  <si>
-    <t>27.05.202688</t>
-  </si>
-  <si>
-    <t>27.05.202689</t>
-  </si>
-  <si>
-    <t>27.05.202690</t>
-  </si>
-  <si>
-    <t>27.05.202691</t>
-  </si>
-  <si>
-    <t>27.05.202692</t>
-  </si>
-  <si>
-    <t>27.05.202693</t>
-  </si>
-  <si>
-    <t>27.05.202694</t>
-  </si>
-  <si>
-    <t>27.05.202695</t>
-  </si>
-  <si>
-    <t>27.05.202696</t>
-  </si>
-  <si>
     <t>28.05.20261</t>
   </si>
   <si>
@@ -608,6 +320,294 @@
   </si>
   <si>
     <t>28.05.202696</t>
+  </si>
+  <si>
+    <t>29.05.20261</t>
+  </si>
+  <si>
+    <t>29.05.20262</t>
+  </si>
+  <si>
+    <t>29.05.20263</t>
+  </si>
+  <si>
+    <t>29.05.20264</t>
+  </si>
+  <si>
+    <t>29.05.20265</t>
+  </si>
+  <si>
+    <t>29.05.20266</t>
+  </si>
+  <si>
+    <t>29.05.20267</t>
+  </si>
+  <si>
+    <t>29.05.20268</t>
+  </si>
+  <si>
+    <t>29.05.20269</t>
+  </si>
+  <si>
+    <t>29.05.202610</t>
+  </si>
+  <si>
+    <t>29.05.202611</t>
+  </si>
+  <si>
+    <t>29.05.202612</t>
+  </si>
+  <si>
+    <t>29.05.202613</t>
+  </si>
+  <si>
+    <t>29.05.202614</t>
+  </si>
+  <si>
+    <t>29.05.202615</t>
+  </si>
+  <si>
+    <t>29.05.202616</t>
+  </si>
+  <si>
+    <t>29.05.202617</t>
+  </si>
+  <si>
+    <t>29.05.202618</t>
+  </si>
+  <si>
+    <t>29.05.202619</t>
+  </si>
+  <si>
+    <t>29.05.202620</t>
+  </si>
+  <si>
+    <t>29.05.202621</t>
+  </si>
+  <si>
+    <t>29.05.202622</t>
+  </si>
+  <si>
+    <t>29.05.202623</t>
+  </si>
+  <si>
+    <t>29.05.202624</t>
+  </si>
+  <si>
+    <t>29.05.202625</t>
+  </si>
+  <si>
+    <t>29.05.202626</t>
+  </si>
+  <si>
+    <t>29.05.202627</t>
+  </si>
+  <si>
+    <t>29.05.202628</t>
+  </si>
+  <si>
+    <t>29.05.202629</t>
+  </si>
+  <si>
+    <t>29.05.202630</t>
+  </si>
+  <si>
+    <t>29.05.202631</t>
+  </si>
+  <si>
+    <t>29.05.202632</t>
+  </si>
+  <si>
+    <t>29.05.202633</t>
+  </si>
+  <si>
+    <t>29.05.202634</t>
+  </si>
+  <si>
+    <t>29.05.202635</t>
+  </si>
+  <si>
+    <t>29.05.202636</t>
+  </si>
+  <si>
+    <t>29.05.202637</t>
+  </si>
+  <si>
+    <t>29.05.202638</t>
+  </si>
+  <si>
+    <t>29.05.202639</t>
+  </si>
+  <si>
+    <t>29.05.202640</t>
+  </si>
+  <si>
+    <t>29.05.202641</t>
+  </si>
+  <si>
+    <t>29.05.202642</t>
+  </si>
+  <si>
+    <t>29.05.202643</t>
+  </si>
+  <si>
+    <t>29.05.202644</t>
+  </si>
+  <si>
+    <t>29.05.202645</t>
+  </si>
+  <si>
+    <t>29.05.202646</t>
+  </si>
+  <si>
+    <t>29.05.202647</t>
+  </si>
+  <si>
+    <t>29.05.202648</t>
+  </si>
+  <si>
+    <t>29.05.202649</t>
+  </si>
+  <si>
+    <t>29.05.202650</t>
+  </si>
+  <si>
+    <t>29.05.202651</t>
+  </si>
+  <si>
+    <t>29.05.202652</t>
+  </si>
+  <si>
+    <t>29.05.202653</t>
+  </si>
+  <si>
+    <t>29.05.202654</t>
+  </si>
+  <si>
+    <t>29.05.202655</t>
+  </si>
+  <si>
+    <t>29.05.202656</t>
+  </si>
+  <si>
+    <t>29.05.202657</t>
+  </si>
+  <si>
+    <t>29.05.202658</t>
+  </si>
+  <si>
+    <t>29.05.202659</t>
+  </si>
+  <si>
+    <t>29.05.202660</t>
+  </si>
+  <si>
+    <t>29.05.202661</t>
+  </si>
+  <si>
+    <t>29.05.202662</t>
+  </si>
+  <si>
+    <t>29.05.202663</t>
+  </si>
+  <si>
+    <t>29.05.202664</t>
+  </si>
+  <si>
+    <t>29.05.202665</t>
+  </si>
+  <si>
+    <t>29.05.202666</t>
+  </si>
+  <si>
+    <t>29.05.202667</t>
+  </si>
+  <si>
+    <t>29.05.202668</t>
+  </si>
+  <si>
+    <t>29.05.202669</t>
+  </si>
+  <si>
+    <t>29.05.202670</t>
+  </si>
+  <si>
+    <t>29.05.202671</t>
+  </si>
+  <si>
+    <t>29.05.202672</t>
+  </si>
+  <si>
+    <t>29.05.202673</t>
+  </si>
+  <si>
+    <t>29.05.202674</t>
+  </si>
+  <si>
+    <t>29.05.202675</t>
+  </si>
+  <si>
+    <t>29.05.202676</t>
+  </si>
+  <si>
+    <t>29.05.202677</t>
+  </si>
+  <si>
+    <t>29.05.202678</t>
+  </si>
+  <si>
+    <t>29.05.202679</t>
+  </si>
+  <si>
+    <t>29.05.202680</t>
+  </si>
+  <si>
+    <t>29.05.202681</t>
+  </si>
+  <si>
+    <t>29.05.202682</t>
+  </si>
+  <si>
+    <t>29.05.202683</t>
+  </si>
+  <si>
+    <t>29.05.202684</t>
+  </si>
+  <si>
+    <t>29.05.202685</t>
+  </si>
+  <si>
+    <t>29.05.202686</t>
+  </si>
+  <si>
+    <t>29.05.202687</t>
+  </si>
+  <si>
+    <t>29.05.202688</t>
+  </si>
+  <si>
+    <t>29.05.202689</t>
+  </si>
+  <si>
+    <t>29.05.202690</t>
+  </si>
+  <si>
+    <t>29.05.202691</t>
+  </si>
+  <si>
+    <t>29.05.202692</t>
+  </si>
+  <si>
+    <t>29.05.202693</t>
+  </si>
+  <si>
+    <t>29.05.202694</t>
+  </si>
+  <si>
+    <t>29.05.202695</t>
+  </si>
+  <si>
+    <t>29.05.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
-        <v>12.075</v>
+        <v>-132.906</v>
       </c>
       <c r="C6">
-        <v>400</v>
+        <v>4217.673</v>
       </c>
       <c r="D6">
-        <v>400</v>
+        <v>4217.673</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
-        <v>-5.87</v>
+        <v>-273.372</v>
       </c>
       <c r="C7">
-        <v>899.306</v>
+        <v>1333.741</v>
       </c>
       <c r="D7">
-        <v>899.306</v>
+        <v>1333.741</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
-        <v>-16.545</v>
+        <v>-277.269</v>
       </c>
       <c r="C8">
-        <v>899.846</v>
+        <v>1199.893</v>
       </c>
       <c r="D8">
-        <v>899.846</v>
+        <v>1199.893</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
-        <v>-11.066</v>
+        <v>-208.726</v>
       </c>
       <c r="C9">
-        <v>898.688</v>
+        <v>2717.063</v>
       </c>
       <c r="D9">
-        <v>898.688</v>
+        <v>2717.063</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
-        <v>-12.106</v>
+        <v>-166.824</v>
       </c>
       <c r="C10">
-        <v>894.3339999999999</v>
+        <v>1444.1</v>
       </c>
       <c r="D10">
-        <v>894.3339999999999</v>
+        <v>1444.1</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
-        <v>-10.068</v>
+        <v>-212.234</v>
       </c>
       <c r="C11">
-        <v>885.827</v>
+        <v>2949.416</v>
       </c>
       <c r="D11">
-        <v>885.827</v>
+        <v>2949.416</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
-        <v>-3.179</v>
+        <v>-272.455</v>
       </c>
       <c r="C12">
-        <v>890.564</v>
+        <v>4108.203</v>
       </c>
       <c r="D12">
-        <v>890.564</v>
+        <v>4108.203</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
-        <v>-4.992</v>
+        <v>-286.514</v>
       </c>
       <c r="C13">
-        <v>898.273</v>
+        <v>3708.3</v>
       </c>
       <c r="D13">
-        <v>898.273</v>
+        <v>3708.3</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
-        <v>-3.175</v>
+        <v>-224.058</v>
       </c>
       <c r="C14">
-        <v>898.127</v>
+        <v>1137.119</v>
       </c>
       <c r="D14">
-        <v>898.127</v>
+        <v>1137.119</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
-        <v>-13.868</v>
+        <v>-209.493</v>
       </c>
       <c r="C15">
-        <v>915.122</v>
+        <v>1139.637</v>
       </c>
       <c r="D15">
-        <v>915.122</v>
+        <v>1139.637</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
-        <v>-32.38</v>
+        <v>-157.946</v>
       </c>
       <c r="C16">
-        <v>944.3150000000001</v>
+        <v>1139.778</v>
       </c>
       <c r="D16">
-        <v>944.3150000000001</v>
+        <v>1139.778</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
-        <v>-19.105</v>
+        <v>-135.481</v>
       </c>
       <c r="C17">
-        <v>902.775</v>
+        <v>1140.03</v>
       </c>
       <c r="D17">
-        <v>902.775</v>
+        <v>1140.03</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
-        <v>16.872</v>
+        <v>-84.506</v>
       </c>
       <c r="C18">
-        <v>386</v>
+        <v>1147.47</v>
       </c>
       <c r="D18">
-        <v>386</v>
+        <v>1147.47</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.933</v>
+        <v>-45.016</v>
       </c>
       <c r="C19">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
-        <v>-13.022</v>
+        <v>-17.338</v>
       </c>
       <c r="C20">
-        <v>903.1</v>
+        <v>1145.47</v>
       </c>
       <c r="D20">
-        <v>903.1</v>
+        <v>1145.47</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
-        <v>-9.525</v>
+        <v>-40.205</v>
       </c>
       <c r="C21">
-        <v>899.699</v>
+        <v>1137.782</v>
       </c>
       <c r="D21">
-        <v>899.699</v>
+        <v>1137.782</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>31.698</v>
+        <v>-13.43</v>
       </c>
       <c r="C22">
-        <v>294.093</v>
+        <v>1163.404</v>
       </c>
       <c r="D22">
-        <v>294.093</v>
+        <v>1163.404</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>2.039</v>
+        <v>-33.311</v>
       </c>
       <c r="C23">
-        <v>397.667</v>
+        <v>1124.001</v>
       </c>
       <c r="D23">
-        <v>397.667</v>
+        <v>1124.001</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>-22.304</v>
+        <v>-75.09699999999999</v>
       </c>
       <c r="C24">
-        <v>935.633</v>
+        <v>1970.561</v>
       </c>
       <c r="D24">
-        <v>935.633</v>
+        <v>1970.561</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>-28.969</v>
+        <v>-78.467</v>
       </c>
       <c r="C25">
-        <v>954.976</v>
+        <v>1336.642</v>
       </c>
       <c r="D25">
-        <v>954.976</v>
+        <v>1336.642</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>-6.713</v>
+        <v>-91.221</v>
       </c>
       <c r="C26">
-        <v>899.518</v>
+        <v>3643.478</v>
       </c>
       <c r="D26">
-        <v>899.518</v>
+        <v>3643.478</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>-12.036</v>
+        <v>-116.62</v>
       </c>
       <c r="C27">
-        <v>914.524</v>
+        <v>2024.169</v>
       </c>
       <c r="D27">
-        <v>914.524</v>
+        <v>2024.169</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>-34.017</v>
+        <v>-8.458</v>
       </c>
       <c r="C28">
-        <v>899.867</v>
+        <v>1235.883</v>
       </c>
       <c r="D28">
-        <v>899.867</v>
+        <v>1235.883</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>21.456</v>
+        <v>-0.274</v>
       </c>
       <c r="C29">
-        <v>278.241</v>
+        <v>1235.39</v>
       </c>
       <c r="D29">
-        <v>278.241</v>
+        <v>1235.39</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>0.254</v>
+        <v>86.423</v>
       </c>
       <c r="C30">
-        <v>314.88</v>
+        <v>322.907</v>
       </c>
       <c r="D30">
-        <v>314.88</v>
+        <v>322.907</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>-2.409</v>
+        <v>72.20399999999999</v>
       </c>
       <c r="C31">
-        <v>897.823</v>
+        <v>-6116.777</v>
       </c>
       <c r="D31">
-        <v>897.823</v>
+        <v>-6116.777</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
-        <v>16.375</v>
+        <v>64.042</v>
       </c>
       <c r="C32">
-        <v>48.726</v>
+        <v>-1691.008</v>
       </c>
       <c r="D32">
-        <v>48.726</v>
+        <v>-1691.008</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
-        <v>24.01</v>
+        <v>40.418</v>
       </c>
       <c r="C33">
-        <v>-14.382</v>
+        <v>-41.292</v>
       </c>
       <c r="D33">
-        <v>-14.382</v>
+        <v>-41.292</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>11.606</v>
+        <v>47.405</v>
       </c>
       <c r="C34">
-        <v>45.895</v>
+        <v>-791.837</v>
       </c>
       <c r="D34">
-        <v>45.895</v>
+        <v>-791.837</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>-22.54</v>
+        <v>32.762</v>
       </c>
       <c r="C35">
-        <v>869.794</v>
+        <v>-78.086</v>
       </c>
       <c r="D35">
-        <v>869.794</v>
+        <v>-78.086</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>1.772</v>
+        <v>24.516</v>
       </c>
       <c r="C36">
-        <v>113.065</v>
+        <v>19.752</v>
       </c>
       <c r="D36">
-        <v>113.065</v>
+        <v>19.752</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>-14.458</v>
+        <v>-8.893000000000001</v>
       </c>
       <c r="C37">
-        <v>751.8440000000001</v>
+        <v>1031.723</v>
       </c>
       <c r="D37">
-        <v>751.8440000000001</v>
+        <v>1031.723</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>-38.269</v>
+        <v>-33.088</v>
       </c>
       <c r="C38">
-        <v>797.655</v>
+        <v>1036.477</v>
       </c>
       <c r="D38">
-        <v>797.655</v>
+        <v>1036.477</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>-45.228</v>
+        <v>-13.701</v>
       </c>
       <c r="C39">
-        <v>1016.232</v>
+        <v>666.019</v>
       </c>
       <c r="D39">
-        <v>1016.232</v>
+        <v>666.019</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>-20.675</v>
+        <v>-19.024</v>
       </c>
       <c r="C40">
-        <v>801.324</v>
+        <v>449</v>
       </c>
       <c r="D40">
-        <v>801.324</v>
+        <v>449</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>-16.327</v>
+        <v>17.028</v>
       </c>
       <c r="C41">
-        <v>713.4400000000001</v>
+        <v>-1664.511</v>
       </c>
       <c r="D41">
-        <v>713.4400000000001</v>
+        <v>-1664.511</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>-55.946</v>
+        <v>24.113</v>
       </c>
       <c r="C42">
-        <v>1900.074</v>
+        <v>-331.645</v>
       </c>
       <c r="D42">
-        <v>1900.074</v>
+        <v>-331.645</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>-61.877</v>
+        <v>-12.344</v>
       </c>
       <c r="C43">
-        <v>798.088</v>
+        <v>449</v>
       </c>
       <c r="D43">
-        <v>798.088</v>
+        <v>449</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>-22.693</v>
+        <v>-13.088</v>
       </c>
       <c r="C44">
-        <v>479.02</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>479.02</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>7.154</v>
+        <v>2.237</v>
       </c>
       <c r="C45">
-        <v>87.07599999999999</v>
+        <v>85.916</v>
       </c>
       <c r="D45">
-        <v>87.07599999999999</v>
+        <v>85.916</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
-        <v>-14.115</v>
+        <v>31.46</v>
       </c>
       <c r="C46">
-        <v>466.18</v>
+        <v>-716.322</v>
       </c>
       <c r="D46">
-        <v>466.18</v>
+        <v>-716.322</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
-        <v>18.998</v>
+        <v>22.849</v>
       </c>
       <c r="C47">
-        <v>-46.848</v>
+        <v>-35.277</v>
       </c>
       <c r="D47">
-        <v>-46.848</v>
+        <v>-35.277</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>-13.409</v>
+        <v>11.069</v>
       </c>
       <c r="C48">
-        <v>551.691</v>
+        <v>-92.324</v>
       </c>
       <c r="D48">
-        <v>551.691</v>
+        <v>-92.324</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>-13.101</v>
+        <v>35.353</v>
       </c>
       <c r="C49">
-        <v>808.6559999999999</v>
+        <v>3.32</v>
       </c>
       <c r="D49">
-        <v>808.6559999999999</v>
+        <v>3.32</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>45.667</v>
+        <v>31.378</v>
       </c>
       <c r="C50">
-        <v>-121.341</v>
+        <v>-119.314</v>
       </c>
       <c r="D50">
-        <v>-121.341</v>
+        <v>-119.314</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
-        <v>47.343</v>
+        <v>40.863</v>
       </c>
       <c r="C51">
-        <v>-151.694</v>
+        <v>-36.823</v>
       </c>
       <c r="D51">
-        <v>-151.694</v>
+        <v>-36.823</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>20.847</v>
+        <v>51.159</v>
       </c>
       <c r="C52">
-        <v>104.843</v>
+        <v>345.742</v>
       </c>
       <c r="D52">
-        <v>104.843</v>
+        <v>345.742</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>52.854</v>
+        <v>44.831</v>
       </c>
       <c r="C53">
-        <v>167.583</v>
+        <v>340.29</v>
       </c>
       <c r="D53">
-        <v>167.583</v>
+        <v>340.29</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>5.911</v>
+        <v>42.521</v>
       </c>
       <c r="C54">
-        <v>206.722</v>
+        <v>53.905</v>
       </c>
       <c r="D54">
-        <v>206.722</v>
+        <v>53.905</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>-1.35</v>
+        <v>9.69</v>
       </c>
       <c r="C55">
-        <v>448.525</v>
+        <v>297.89</v>
       </c>
       <c r="D55">
-        <v>448.525</v>
+        <v>297.89</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>-22.836</v>
+        <v>-27.177</v>
       </c>
       <c r="C56">
-        <v>473.044</v>
+        <v>1692.751</v>
       </c>
       <c r="D56">
-        <v>473.044</v>
+        <v>1692.751</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>7.488</v>
+        <v>-47.143</v>
       </c>
       <c r="C57">
-        <v>-49</v>
+        <v>1604.053</v>
       </c>
       <c r="D57">
-        <v>-49</v>
+        <v>1604.053</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>-1.364</v>
+        <v>-88.60599999999999</v>
       </c>
       <c r="C58">
-        <v>621.876</v>
+        <v>744.753</v>
       </c>
       <c r="D58">
-        <v>621.876</v>
+        <v>744.753</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>-0.248</v>
+        <v>-84.152</v>
       </c>
       <c r="C59">
-        <v>450.793</v>
+        <v>804.8579999999999</v>
       </c>
       <c r="D59">
-        <v>450.793</v>
+        <v>804.8579999999999</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>-10.246</v>
+        <v>-79.26300000000001</v>
       </c>
       <c r="C60">
-        <v>715.404</v>
+        <v>857.658</v>
       </c>
       <c r="D60">
-        <v>715.404</v>
+        <v>857.658</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>-29.816</v>
+        <v>-35.58</v>
       </c>
       <c r="C61">
-        <v>662.4450000000001</v>
+        <v>823.558</v>
       </c>
       <c r="D61">
-        <v>662.4450000000001</v>
+        <v>823.558</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>72.374</v>
+        <v>-9.679</v>
       </c>
       <c r="C62">
-        <v>-66.74299999999999</v>
+        <v>672.711</v>
       </c>
       <c r="D62">
-        <v>-66.74299999999999</v>
+        <v>672.711</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>54.701</v>
+        <v>-31.803</v>
       </c>
       <c r="C63">
-        <v>-68.342</v>
+        <v>782.712</v>
       </c>
       <c r="D63">
-        <v>-68.342</v>
+        <v>782.712</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>47.697</v>
+        <v>-57.256</v>
       </c>
       <c r="C64">
-        <v>-78.45099999999999</v>
+        <v>1140.472</v>
       </c>
       <c r="D64">
-        <v>-78.45099999999999</v>
+        <v>1140.472</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>36.573</v>
+        <v>-89.73</v>
       </c>
       <c r="C65">
-        <v>-68.56699999999999</v>
+        <v>887.778</v>
       </c>
       <c r="D65">
-        <v>-68.56699999999999</v>
+        <v>887.778</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>128.616</v>
+        <v>-43.236</v>
       </c>
       <c r="C66">
-        <v>-1353.037</v>
+        <v>814.4450000000001</v>
       </c>
       <c r="D66">
-        <v>-1353.037</v>
+        <v>814.4450000000001</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>110.142</v>
+        <v>-101.946</v>
       </c>
       <c r="C67">
-        <v>-99.15600000000001</v>
+        <v>6483.944</v>
       </c>
       <c r="D67">
-        <v>-99.15600000000001</v>
+        <v>6483.944</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>31.499</v>
+        <v>-54.394</v>
       </c>
       <c r="C68">
-        <v>-81.096</v>
+        <v>1667.088</v>
       </c>
       <c r="D68">
-        <v>-81.096</v>
+        <v>1667.088</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>6.802</v>
+        <v>-28.496</v>
       </c>
       <c r="C69">
-        <v>-106</v>
+        <v>670.437</v>
       </c>
       <c r="D69">
-        <v>-106</v>
+        <v>670.437</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>77.788</v>
+        <v>45.455</v>
       </c>
       <c r="C70">
-        <v>400</v>
+        <v>-3275.024</v>
       </c>
       <c r="D70">
-        <v>400</v>
+        <v>-3275.024</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
-        <v>-9.612</v>
+        <v>79.59</v>
       </c>
       <c r="C71">
-        <v>1133.659</v>
+        <v>401</v>
       </c>
       <c r="D71">
-        <v>1133.659</v>
+        <v>401</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>-28.507</v>
+        <v>106.569</v>
       </c>
       <c r="C72">
-        <v>3073.582</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>3073.582</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>-66.172</v>
+        <v>52.506</v>
       </c>
       <c r="C73">
-        <v>6455.336</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>6455.336</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>-41.991</v>
+        <v>15.954</v>
       </c>
       <c r="C74">
-        <v>1427.532</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>1427.532</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>-63.673</v>
+        <v>32.846</v>
       </c>
       <c r="C75">
-        <v>1360.693</v>
+        <v>251.888</v>
       </c>
       <c r="D75">
-        <v>1360.693</v>
+        <v>251.888</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>-29.271</v>
+        <v>50.64</v>
       </c>
       <c r="C76">
-        <v>1284.864</v>
+        <v>400.954</v>
       </c>
       <c r="D76">
-        <v>1284.864</v>
+        <v>400.954</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>-32.629</v>
+        <v>41.445</v>
       </c>
       <c r="C77">
-        <v>1287.297</v>
+        <v>401</v>
       </c>
       <c r="D77">
-        <v>1287.297</v>
+        <v>401</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>60.11</v>
+        <v>68.73</v>
       </c>
       <c r="C78">
-        <v>-0.022</v>
+        <v>263.857</v>
       </c>
       <c r="D78">
-        <v>-0.022</v>
+        <v>263.857</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>39.546</v>
+        <v>96.101</v>
       </c>
       <c r="C79">
-        <v>80.235</v>
+        <v>286.595</v>
       </c>
       <c r="D79">
-        <v>80.235</v>
+        <v>286.595</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>41.74</v>
+        <v>83.65600000000001</v>
       </c>
       <c r="C80">
-        <v>280.164</v>
+        <v>1.514</v>
       </c>
       <c r="D80">
-        <v>280.164</v>
+        <v>1.514</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>20.163</v>
+        <v>20.546</v>
       </c>
       <c r="C81">
-        <v>316.503</v>
+        <v>0.875</v>
       </c>
       <c r="D81">
-        <v>316.503</v>
+        <v>0.875</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
-        <v>48.001</v>
+        <v>-20.991</v>
       </c>
       <c r="C82">
-        <v>277.893</v>
+        <v>4882.908</v>
       </c>
       <c r="D82">
-        <v>277.893</v>
+        <v>4882.908</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
-        <v>45.606</v>
+        <v>4.342</v>
       </c>
       <c r="C83">
-        <v>312.031</v>
+        <v>1.1</v>
       </c>
       <c r="D83">
-        <v>312.031</v>
+        <v>1.1</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
-        <v>33.917</v>
+        <v>42.665</v>
       </c>
       <c r="C84">
-        <v>302.378</v>
+        <v>338.11</v>
       </c>
       <c r="D84">
-        <v>302.378</v>
+        <v>338.11</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
-        <v>15.888</v>
+        <v>73.889</v>
       </c>
       <c r="C85">
-        <v>346.876</v>
+        <v>25.379</v>
       </c>
       <c r="D85">
-        <v>346.876</v>
+        <v>25.379</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
-        <v>-29.132</v>
+        <v>72.23699999999999</v>
       </c>
       <c r="C86">
-        <v>891.9829999999999</v>
+        <v>-1016.639</v>
       </c>
       <c r="D86">
-        <v>891.9829999999999</v>
+        <v>-1016.639</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
-        <v>-15.003</v>
+        <v>71.93600000000001</v>
       </c>
       <c r="C87">
-        <v>942.014</v>
+        <v>-685.484</v>
       </c>
       <c r="D87">
-        <v>942.014</v>
+        <v>-685.484</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
-        <v>5.984</v>
+        <v>78.90300000000001</v>
       </c>
       <c r="C88">
-        <v>1590.033</v>
+        <v>-4.326</v>
       </c>
       <c r="D88">
-        <v>1590.033</v>
+        <v>-4.326</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
-        <v>42.648</v>
+        <v>27.51</v>
       </c>
       <c r="C89">
-        <v>-109.875</v>
+        <v>4.975</v>
       </c>
       <c r="D89">
-        <v>-109.875</v>
+        <v>4.975</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
-        <v>32.615</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="C90">
-        <v>-78.14</v>
+        <v>2591.037</v>
       </c>
       <c r="D90">
-        <v>-78.14</v>
+        <v>2591.037</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
-        <v>81.566</v>
+        <v>-5.937</v>
       </c>
       <c r="C91">
-        <v>-38.51</v>
+        <v>1370.409</v>
       </c>
       <c r="D91">
-        <v>-38.51</v>
+        <v>1370.409</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
-        <v>63.908</v>
+        <v>53.102</v>
       </c>
       <c r="C92">
-        <v>-61.003</v>
+        <v>-152.355</v>
       </c>
       <c r="D92">
-        <v>-61.003</v>
+        <v>-152.355</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
-        <v>42.843</v>
+        <v>29.892</v>
       </c>
       <c r="C93">
-        <v>2.42</v>
+        <v>55.727</v>
       </c>
       <c r="D93">
-        <v>2.42</v>
+        <v>55.727</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
-        <v>6.839</v>
+        <v>-24.451</v>
       </c>
       <c r="C94">
-        <v>3.015</v>
+        <v>1503.047</v>
       </c>
       <c r="D94">
-        <v>3.015</v>
+        <v>1503.047</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
-        <v>10.372</v>
+        <v>-45.045</v>
       </c>
       <c r="C95">
-        <v>1.1</v>
+        <v>887.244</v>
       </c>
       <c r="D95">
-        <v>1.1</v>
+        <v>887.244</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
-        <v>21.584</v>
+        <v>-73.175</v>
       </c>
       <c r="C96">
-        <v>59.526</v>
+        <v>1141.26</v>
       </c>
       <c r="D96">
-        <v>59.526</v>
+        <v>1141.26</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
-        <v>12.601</v>
+        <v>-72.298</v>
       </c>
       <c r="C97">
-        <v>251.346</v>
+        <v>2823.466</v>
       </c>
       <c r="D97">
-        <v>251.346</v>
+        <v>2823.466</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
-        <v>-29.084</v>
+        <v>-81.79600000000001</v>
       </c>
       <c r="C98">
-        <v>898.413</v>
+        <v>2164.96</v>
       </c>
       <c r="D98">
-        <v>898.413</v>
+        <v>2164.96</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B99">
-        <v>-45.037</v>
+        <v>-82.575</v>
       </c>
       <c r="C99">
-        <v>963.794</v>
+        <v>3897.566</v>
       </c>
       <c r="D99">
-        <v>963.794</v>
+        <v>3897.566</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B100">
-        <v>-102.821</v>
+        <v>-75.21299999999999</v>
       </c>
       <c r="C100">
-        <v>1153.459</v>
+        <v>4607.727</v>
       </c>
       <c r="D100">
-        <v>1153.459</v>
+        <v>4607.727</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B101">
-        <v>-154.703</v>
+        <v>-83.783</v>
       </c>
       <c r="C101">
-        <v>4759.836</v>
+        <v>5152.538</v>
       </c>
       <c r="D101">
-        <v>4759.836</v>
+        <v>5152.538</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B102">
-        <v>-132.906</v>
+        <v>-50.004</v>
       </c>
       <c r="C102">
-        <v>4217.673</v>
+        <v>1070.603</v>
       </c>
       <c r="D102">
-        <v>4217.673</v>
+        <v>1070.603</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B103">
-        <v>-273.372</v>
+        <v>-18.489</v>
       </c>
       <c r="C103">
-        <v>1333.741</v>
+        <v>1112.761</v>
       </c>
       <c r="D103">
-        <v>1333.741</v>
+        <v>1112.761</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B104">
-        <v>-277.269</v>
+        <v>-19.692</v>
       </c>
       <c r="C104">
-        <v>1199.893</v>
+        <v>1149.61</v>
       </c>
       <c r="D104">
-        <v>1199.893</v>
+        <v>1149.61</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B105">
-        <v>-208.726</v>
+        <v>28.656</v>
       </c>
       <c r="C105">
-        <v>2717.063</v>
+        <v>-573.818</v>
       </c>
       <c r="D105">
-        <v>2717.063</v>
+        <v>-573.818</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B106">
-        <v>-166.824</v>
+        <v>20.57</v>
       </c>
       <c r="C106">
-        <v>1444.1</v>
+        <v>-858.136</v>
       </c>
       <c r="D106">
-        <v>1444.1</v>
+        <v>-858.136</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B107">
-        <v>-212.234</v>
+        <v>69.426</v>
       </c>
       <c r="C107">
-        <v>2949.416</v>
+        <v>24.017</v>
       </c>
       <c r="D107">
-        <v>2949.416</v>
+        <v>24.017</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B108">
-        <v>-272.455</v>
+        <v>93.258</v>
       </c>
       <c r="C108">
-        <v>4108.203</v>
+        <v>21.504</v>
       </c>
       <c r="D108">
-        <v>4108.203</v>
+        <v>21.504</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B109">
-        <v>-286.514</v>
+        <v>110.865</v>
       </c>
       <c r="C109">
-        <v>3708.3</v>
+        <v>240.886</v>
       </c>
       <c r="D109">
-        <v>3708.3</v>
+        <v>240.886</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B110">
-        <v>-224.058</v>
+        <v>106.02</v>
       </c>
       <c r="C110">
-        <v>1137.119</v>
+        <v>167.422</v>
       </c>
       <c r="D110">
-        <v>1137.119</v>
+        <v>167.422</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B111">
-        <v>-209.493</v>
+        <v>64.093</v>
       </c>
       <c r="C111">
-        <v>1139.637</v>
+        <v>-23.361</v>
       </c>
       <c r="D111">
-        <v>1139.637</v>
+        <v>-23.361</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B112">
-        <v>-157.946</v>
+        <v>33.848</v>
       </c>
       <c r="C112">
-        <v>1139.778</v>
+        <v>-107.267</v>
       </c>
       <c r="D112">
-        <v>1139.778</v>
+        <v>-107.267</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B113">
-        <v>-135.481</v>
+        <v>25.883</v>
       </c>
       <c r="C113">
-        <v>1140.03</v>
+        <v>139.938</v>
       </c>
       <c r="D113">
-        <v>1140.03</v>
+        <v>139.938</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B114">
-        <v>-84.506</v>
+        <v>-7.739</v>
       </c>
       <c r="C114">
-        <v>1147.47</v>
+        <v>811.647</v>
       </c>
       <c r="D114">
-        <v>1147.47</v>
+        <v>811.647</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B115">
-        <v>-45.016</v>
+        <v>-4.488</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>806.3869999999999</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>806.3869999999999</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B116">
-        <v>-17.338</v>
+        <v>27.296</v>
       </c>
       <c r="C116">
-        <v>1145.47</v>
+        <v>173.364</v>
       </c>
       <c r="D116">
-        <v>1145.47</v>
+        <v>173.364</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B117">
-        <v>-40.205</v>
+        <v>25.381</v>
       </c>
       <c r="C117">
-        <v>1137.782</v>
+        <v>95.742</v>
       </c>
       <c r="D117">
-        <v>1137.782</v>
+        <v>95.742</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B118">
-        <v>-13.43</v>
+        <v>24.743</v>
       </c>
       <c r="C118">
-        <v>1163.404</v>
+        <v>259.094</v>
       </c>
       <c r="D118">
-        <v>1163.404</v>
+        <v>259.094</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B119">
-        <v>-33.311</v>
+        <v>10.337</v>
       </c>
       <c r="C119">
-        <v>1124.001</v>
+        <v>300.88</v>
       </c>
       <c r="D119">
-        <v>1124.001</v>
+        <v>300.88</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B120">
-        <v>-75.09699999999999</v>
+        <v>37.391</v>
       </c>
       <c r="C120">
-        <v>1970.561</v>
+        <v>311.088</v>
       </c>
       <c r="D120">
-        <v>1970.561</v>
+        <v>311.088</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B121">
-        <v>-78.467</v>
+        <v>39.824</v>
       </c>
       <c r="C121">
-        <v>1336.642</v>
+        <v>265.401</v>
       </c>
       <c r="D121">
-        <v>1336.642</v>
+        <v>265.401</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B122">
-        <v>-91.221</v>
+        <v>37.696</v>
       </c>
       <c r="C122">
-        <v>3643.478</v>
+        <v>-3.23</v>
       </c>
       <c r="D122">
-        <v>3643.478</v>
+        <v>-3.23</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B123">
-        <v>-116.62</v>
+        <v>25.477</v>
       </c>
       <c r="C123">
-        <v>2024.169</v>
+        <v>355.301</v>
       </c>
       <c r="D123">
-        <v>2024.169</v>
+        <v>355.301</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B124">
-        <v>-8.458</v>
+        <v>23.821</v>
       </c>
       <c r="C124">
-        <v>1235.883</v>
+        <v>273.595</v>
       </c>
       <c r="D124">
-        <v>1235.883</v>
+        <v>273.595</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B125">
-        <v>-0.274</v>
+        <v>34.26</v>
       </c>
       <c r="C125">
-        <v>1235.39</v>
+        <v>0.413</v>
       </c>
       <c r="D125">
-        <v>1235.39</v>
+        <v>0.413</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B126">
-        <v>86.423</v>
+        <v>-24.691</v>
       </c>
       <c r="C126">
-        <v>322.907</v>
+        <v>899</v>
       </c>
       <c r="D126">
-        <v>322.907</v>
+        <v>899</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B127">
-        <v>72.20399999999999</v>
+        <v>6.719</v>
       </c>
       <c r="C127">
-        <v>-6116.777</v>
+        <v>195.35</v>
       </c>
       <c r="D127">
-        <v>-6116.777</v>
+        <v>195.35</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B128">
-        <v>64.042</v>
+        <v>49.763</v>
       </c>
       <c r="C128">
-        <v>-1691.008</v>
+        <v>70.98099999999999</v>
       </c>
       <c r="D128">
-        <v>-1691.008</v>
+        <v>70.98099999999999</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B129">
-        <v>40.418</v>
+        <v>50.643</v>
       </c>
       <c r="C129">
-        <v>-41.292</v>
+        <v>-67.205</v>
       </c>
       <c r="D129">
-        <v>-41.292</v>
+        <v>-67.205</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B130">
-        <v>47.405</v>
+        <v>56.014</v>
       </c>
       <c r="C130">
-        <v>-791.837</v>
+        <v>195.986</v>
       </c>
       <c r="D130">
-        <v>-791.837</v>
+        <v>195.986</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B131">
-        <v>32.762</v>
+        <v>62.355</v>
       </c>
       <c r="C131">
-        <v>-78.086</v>
+        <v>-109.164</v>
       </c>
       <c r="D131">
-        <v>-78.086</v>
+        <v>-109.164</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B132">
-        <v>24.516</v>
+        <v>63.739</v>
       </c>
       <c r="C132">
-        <v>19.752</v>
+        <v>-70.23699999999999</v>
       </c>
       <c r="D132">
-        <v>19.752</v>
+        <v>-70.23699999999999</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3754,7 +3754,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3834,7 +3834,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -34,580 +34,580 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.06.20261</t>
-  </si>
-  <si>
-    <t>03.06.20262</t>
-  </si>
-  <si>
-    <t>03.06.20263</t>
-  </si>
-  <si>
-    <t>03.06.20264</t>
-  </si>
-  <si>
-    <t>03.06.20265</t>
-  </si>
-  <si>
-    <t>03.06.20266</t>
-  </si>
-  <si>
-    <t>03.06.20267</t>
-  </si>
-  <si>
-    <t>03.06.20268</t>
-  </si>
-  <si>
-    <t>03.06.20269</t>
-  </si>
-  <si>
-    <t>03.06.202610</t>
-  </si>
-  <si>
-    <t>03.06.202611</t>
-  </si>
-  <si>
-    <t>03.06.202612</t>
-  </si>
-  <si>
-    <t>03.06.202613</t>
-  </si>
-  <si>
-    <t>03.06.202614</t>
-  </si>
-  <si>
-    <t>03.06.202615</t>
-  </si>
-  <si>
-    <t>03.06.202616</t>
-  </si>
-  <si>
-    <t>03.06.202617</t>
-  </si>
-  <si>
-    <t>03.06.202618</t>
-  </si>
-  <si>
-    <t>03.06.202619</t>
-  </si>
-  <si>
-    <t>03.06.202620</t>
-  </si>
-  <si>
-    <t>03.06.202621</t>
-  </si>
-  <si>
-    <t>03.06.202622</t>
-  </si>
-  <si>
-    <t>03.06.202623</t>
-  </si>
-  <si>
-    <t>03.06.202624</t>
-  </si>
-  <si>
-    <t>03.06.202625</t>
-  </si>
-  <si>
-    <t>03.06.202626</t>
-  </si>
-  <si>
-    <t>03.06.202627</t>
-  </si>
-  <si>
-    <t>03.06.202628</t>
-  </si>
-  <si>
-    <t>03.06.202629</t>
-  </si>
-  <si>
-    <t>03.06.202630</t>
-  </si>
-  <si>
-    <t>03.06.202631</t>
-  </si>
-  <si>
-    <t>03.06.202632</t>
-  </si>
-  <si>
-    <t>03.06.202633</t>
-  </si>
-  <si>
-    <t>03.06.202634</t>
-  </si>
-  <si>
-    <t>03.06.202635</t>
-  </si>
-  <si>
-    <t>03.06.202636</t>
-  </si>
-  <si>
-    <t>03.06.202637</t>
-  </si>
-  <si>
-    <t>03.06.202638</t>
-  </si>
-  <si>
-    <t>03.06.202639</t>
-  </si>
-  <si>
-    <t>03.06.202640</t>
-  </si>
-  <si>
-    <t>03.06.202641</t>
-  </si>
-  <si>
-    <t>03.06.202642</t>
-  </si>
-  <si>
-    <t>03.06.202643</t>
-  </si>
-  <si>
-    <t>03.06.202644</t>
-  </si>
-  <si>
-    <t>03.06.202645</t>
-  </si>
-  <si>
-    <t>03.06.202646</t>
-  </si>
-  <si>
-    <t>03.06.202647</t>
-  </si>
-  <si>
-    <t>03.06.202648</t>
-  </si>
-  <si>
-    <t>03.06.202649</t>
-  </si>
-  <si>
-    <t>03.06.202650</t>
-  </si>
-  <si>
-    <t>03.06.202651</t>
-  </si>
-  <si>
-    <t>03.06.202652</t>
-  </si>
-  <si>
-    <t>03.06.202653</t>
-  </si>
-  <si>
-    <t>03.06.202654</t>
-  </si>
-  <si>
-    <t>03.06.202655</t>
-  </si>
-  <si>
-    <t>03.06.202656</t>
-  </si>
-  <si>
-    <t>03.06.202657</t>
-  </si>
-  <si>
-    <t>03.06.202658</t>
-  </si>
-  <si>
-    <t>03.06.202659</t>
-  </si>
-  <si>
-    <t>03.06.202660</t>
-  </si>
-  <si>
-    <t>03.06.202661</t>
-  </si>
-  <si>
-    <t>03.06.202662</t>
-  </si>
-  <si>
-    <t>03.06.202663</t>
-  </si>
-  <si>
-    <t>03.06.202664</t>
-  </si>
-  <si>
-    <t>03.06.202665</t>
-  </si>
-  <si>
-    <t>03.06.202666</t>
-  </si>
-  <si>
-    <t>03.06.202667</t>
-  </si>
-  <si>
-    <t>03.06.202668</t>
-  </si>
-  <si>
-    <t>03.06.202669</t>
-  </si>
-  <si>
-    <t>03.06.202670</t>
-  </si>
-  <si>
-    <t>03.06.202671</t>
-  </si>
-  <si>
-    <t>03.06.202672</t>
-  </si>
-  <si>
-    <t>03.06.202673</t>
-  </si>
-  <si>
-    <t>03.06.202674</t>
-  </si>
-  <si>
-    <t>03.06.202675</t>
-  </si>
-  <si>
-    <t>03.06.202676</t>
-  </si>
-  <si>
-    <t>03.06.202677</t>
-  </si>
-  <si>
-    <t>03.06.202678</t>
-  </si>
-  <si>
-    <t>03.06.202679</t>
-  </si>
-  <si>
-    <t>03.06.202680</t>
-  </si>
-  <si>
-    <t>03.06.202681</t>
-  </si>
-  <si>
-    <t>03.06.202682</t>
-  </si>
-  <si>
-    <t>03.06.202683</t>
-  </si>
-  <si>
-    <t>03.06.202684</t>
-  </si>
-  <si>
-    <t>03.06.202685</t>
-  </si>
-  <si>
-    <t>03.06.202686</t>
-  </si>
-  <si>
-    <t>03.06.202687</t>
-  </si>
-  <si>
-    <t>03.06.202688</t>
-  </si>
-  <si>
-    <t>03.06.202689</t>
-  </si>
-  <si>
-    <t>03.06.202690</t>
-  </si>
-  <si>
-    <t>03.06.202691</t>
-  </si>
-  <si>
-    <t>03.06.202692</t>
-  </si>
-  <si>
-    <t>03.06.202693</t>
-  </si>
-  <si>
-    <t>03.06.202694</t>
-  </si>
-  <si>
-    <t>03.06.202695</t>
-  </si>
-  <si>
-    <t>03.06.202696</t>
-  </si>
-  <si>
-    <t>04.06.20261</t>
-  </si>
-  <si>
-    <t>04.06.20262</t>
-  </si>
-  <si>
-    <t>04.06.20263</t>
-  </si>
-  <si>
-    <t>04.06.20264</t>
-  </si>
-  <si>
-    <t>04.06.20265</t>
-  </si>
-  <si>
-    <t>04.06.20266</t>
-  </si>
-  <si>
-    <t>04.06.20267</t>
-  </si>
-  <si>
-    <t>04.06.20268</t>
-  </si>
-  <si>
-    <t>04.06.20269</t>
-  </si>
-  <si>
-    <t>04.06.202610</t>
-  </si>
-  <si>
-    <t>04.06.202611</t>
-  </si>
-  <si>
-    <t>04.06.202612</t>
-  </si>
-  <si>
-    <t>04.06.202613</t>
-  </si>
-  <si>
-    <t>04.06.202614</t>
-  </si>
-  <si>
-    <t>04.06.202615</t>
-  </si>
-  <si>
-    <t>04.06.202616</t>
-  </si>
-  <si>
-    <t>04.06.202617</t>
-  </si>
-  <si>
-    <t>04.06.202618</t>
-  </si>
-  <si>
-    <t>04.06.202619</t>
-  </si>
-  <si>
-    <t>04.06.202620</t>
-  </si>
-  <si>
-    <t>04.06.202621</t>
-  </si>
-  <si>
-    <t>04.06.202622</t>
-  </si>
-  <si>
-    <t>04.06.202623</t>
-  </si>
-  <si>
-    <t>04.06.202624</t>
-  </si>
-  <si>
-    <t>04.06.202625</t>
-  </si>
-  <si>
-    <t>04.06.202626</t>
-  </si>
-  <si>
-    <t>04.06.202627</t>
-  </si>
-  <si>
-    <t>04.06.202628</t>
-  </si>
-  <si>
-    <t>04.06.202629</t>
-  </si>
-  <si>
-    <t>04.06.202630</t>
-  </si>
-  <si>
-    <t>04.06.202631</t>
-  </si>
-  <si>
-    <t>04.06.202632</t>
-  </si>
-  <si>
-    <t>04.06.202633</t>
-  </si>
-  <si>
-    <t>04.06.202634</t>
-  </si>
-  <si>
-    <t>04.06.202635</t>
-  </si>
-  <si>
-    <t>04.06.202636</t>
-  </si>
-  <si>
-    <t>04.06.202637</t>
-  </si>
-  <si>
-    <t>04.06.202638</t>
-  </si>
-  <si>
-    <t>04.06.202639</t>
-  </si>
-  <si>
-    <t>04.06.202640</t>
-  </si>
-  <si>
-    <t>04.06.202641</t>
-  </si>
-  <si>
-    <t>04.06.202642</t>
-  </si>
-  <si>
-    <t>04.06.202643</t>
-  </si>
-  <si>
-    <t>04.06.202644</t>
-  </si>
-  <si>
-    <t>04.06.202645</t>
-  </si>
-  <si>
-    <t>04.06.202646</t>
-  </si>
-  <si>
-    <t>04.06.202647</t>
-  </si>
-  <si>
-    <t>04.06.202648</t>
-  </si>
-  <si>
-    <t>04.06.202649</t>
-  </si>
-  <si>
-    <t>04.06.202650</t>
-  </si>
-  <si>
-    <t>04.06.202651</t>
-  </si>
-  <si>
-    <t>04.06.202652</t>
-  </si>
-  <si>
-    <t>04.06.202653</t>
-  </si>
-  <si>
-    <t>04.06.202654</t>
-  </si>
-  <si>
-    <t>04.06.202655</t>
-  </si>
-  <si>
-    <t>04.06.202656</t>
-  </si>
-  <si>
-    <t>04.06.202657</t>
-  </si>
-  <si>
-    <t>04.06.202658</t>
-  </si>
-  <si>
-    <t>04.06.202659</t>
-  </si>
-  <si>
-    <t>04.06.202660</t>
-  </si>
-  <si>
-    <t>04.06.202661</t>
-  </si>
-  <si>
-    <t>04.06.202662</t>
-  </si>
-  <si>
-    <t>04.06.202663</t>
-  </si>
-  <si>
-    <t>04.06.202664</t>
-  </si>
-  <si>
-    <t>04.06.202665</t>
-  </si>
-  <si>
-    <t>04.06.202666</t>
-  </si>
-  <si>
-    <t>04.06.202667</t>
-  </si>
-  <si>
-    <t>04.06.202668</t>
-  </si>
-  <si>
-    <t>04.06.202669</t>
-  </si>
-  <si>
-    <t>04.06.202670</t>
-  </si>
-  <si>
-    <t>04.06.202671</t>
-  </si>
-  <si>
-    <t>04.06.202672</t>
-  </si>
-  <si>
-    <t>04.06.202673</t>
-  </si>
-  <si>
-    <t>04.06.202674</t>
-  </si>
-  <si>
-    <t>04.06.202675</t>
-  </si>
-  <si>
-    <t>04.06.202676</t>
-  </si>
-  <si>
-    <t>04.06.202677</t>
-  </si>
-  <si>
-    <t>04.06.202678</t>
-  </si>
-  <si>
-    <t>04.06.202679</t>
-  </si>
-  <si>
-    <t>04.06.202680</t>
-  </si>
-  <si>
-    <t>04.06.202681</t>
-  </si>
-  <si>
-    <t>04.06.202682</t>
-  </si>
-  <si>
-    <t>04.06.202683</t>
-  </si>
-  <si>
-    <t>04.06.202684</t>
-  </si>
-  <si>
-    <t>04.06.202685</t>
-  </si>
-  <si>
-    <t>04.06.202686</t>
-  </si>
-  <si>
-    <t>04.06.202687</t>
-  </si>
-  <si>
-    <t>04.06.202688</t>
-  </si>
-  <si>
-    <t>04.06.202689</t>
-  </si>
-  <si>
-    <t>04.06.202690</t>
-  </si>
-  <si>
-    <t>04.06.202691</t>
-  </si>
-  <si>
-    <t>04.06.202692</t>
-  </si>
-  <si>
-    <t>04.06.202693</t>
-  </si>
-  <si>
-    <t>04.06.202694</t>
-  </si>
-  <si>
-    <t>04.06.202695</t>
-  </si>
-  <si>
-    <t>04.06.202696</t>
+    <t>11.06.20261</t>
+  </si>
+  <si>
+    <t>11.06.20262</t>
+  </si>
+  <si>
+    <t>11.06.20263</t>
+  </si>
+  <si>
+    <t>11.06.20264</t>
+  </si>
+  <si>
+    <t>11.06.20265</t>
+  </si>
+  <si>
+    <t>11.06.20266</t>
+  </si>
+  <si>
+    <t>11.06.20267</t>
+  </si>
+  <si>
+    <t>11.06.20268</t>
+  </si>
+  <si>
+    <t>11.06.20269</t>
+  </si>
+  <si>
+    <t>11.06.202610</t>
+  </si>
+  <si>
+    <t>11.06.202611</t>
+  </si>
+  <si>
+    <t>11.06.202612</t>
+  </si>
+  <si>
+    <t>11.06.202613</t>
+  </si>
+  <si>
+    <t>11.06.202614</t>
+  </si>
+  <si>
+    <t>11.06.202615</t>
+  </si>
+  <si>
+    <t>11.06.202616</t>
+  </si>
+  <si>
+    <t>11.06.202617</t>
+  </si>
+  <si>
+    <t>11.06.202618</t>
+  </si>
+  <si>
+    <t>11.06.202619</t>
+  </si>
+  <si>
+    <t>11.06.202620</t>
+  </si>
+  <si>
+    <t>11.06.202621</t>
+  </si>
+  <si>
+    <t>11.06.202622</t>
+  </si>
+  <si>
+    <t>11.06.202623</t>
+  </si>
+  <si>
+    <t>11.06.202624</t>
+  </si>
+  <si>
+    <t>11.06.202625</t>
+  </si>
+  <si>
+    <t>11.06.202626</t>
+  </si>
+  <si>
+    <t>11.06.202627</t>
+  </si>
+  <si>
+    <t>11.06.202628</t>
+  </si>
+  <si>
+    <t>11.06.202629</t>
+  </si>
+  <si>
+    <t>11.06.202630</t>
+  </si>
+  <si>
+    <t>11.06.202631</t>
+  </si>
+  <si>
+    <t>11.06.202632</t>
+  </si>
+  <si>
+    <t>11.06.202633</t>
+  </si>
+  <si>
+    <t>11.06.202634</t>
+  </si>
+  <si>
+    <t>11.06.202635</t>
+  </si>
+  <si>
+    <t>11.06.202636</t>
+  </si>
+  <si>
+    <t>11.06.202637</t>
+  </si>
+  <si>
+    <t>11.06.202638</t>
+  </si>
+  <si>
+    <t>11.06.202639</t>
+  </si>
+  <si>
+    <t>11.06.202640</t>
+  </si>
+  <si>
+    <t>11.06.202641</t>
+  </si>
+  <si>
+    <t>11.06.202642</t>
+  </si>
+  <si>
+    <t>11.06.202643</t>
+  </si>
+  <si>
+    <t>11.06.202644</t>
+  </si>
+  <si>
+    <t>11.06.202645</t>
+  </si>
+  <si>
+    <t>11.06.202646</t>
+  </si>
+  <si>
+    <t>11.06.202647</t>
+  </si>
+  <si>
+    <t>11.06.202648</t>
+  </si>
+  <si>
+    <t>11.06.202649</t>
+  </si>
+  <si>
+    <t>11.06.202650</t>
+  </si>
+  <si>
+    <t>11.06.202651</t>
+  </si>
+  <si>
+    <t>11.06.202652</t>
+  </si>
+  <si>
+    <t>11.06.202653</t>
+  </si>
+  <si>
+    <t>11.06.202654</t>
+  </si>
+  <si>
+    <t>11.06.202655</t>
+  </si>
+  <si>
+    <t>11.06.202656</t>
+  </si>
+  <si>
+    <t>11.06.202657</t>
+  </si>
+  <si>
+    <t>11.06.202658</t>
+  </si>
+  <si>
+    <t>11.06.202659</t>
+  </si>
+  <si>
+    <t>11.06.202660</t>
+  </si>
+  <si>
+    <t>11.06.202661</t>
+  </si>
+  <si>
+    <t>11.06.202662</t>
+  </si>
+  <si>
+    <t>11.06.202663</t>
+  </si>
+  <si>
+    <t>11.06.202664</t>
+  </si>
+  <si>
+    <t>11.06.202665</t>
+  </si>
+  <si>
+    <t>11.06.202666</t>
+  </si>
+  <si>
+    <t>11.06.202667</t>
+  </si>
+  <si>
+    <t>11.06.202668</t>
+  </si>
+  <si>
+    <t>11.06.202669</t>
+  </si>
+  <si>
+    <t>11.06.202670</t>
+  </si>
+  <si>
+    <t>11.06.202671</t>
+  </si>
+  <si>
+    <t>11.06.202672</t>
+  </si>
+  <si>
+    <t>11.06.202673</t>
+  </si>
+  <si>
+    <t>11.06.202674</t>
+  </si>
+  <si>
+    <t>11.06.202675</t>
+  </si>
+  <si>
+    <t>11.06.202676</t>
+  </si>
+  <si>
+    <t>11.06.202677</t>
+  </si>
+  <si>
+    <t>11.06.202678</t>
+  </si>
+  <si>
+    <t>11.06.202679</t>
+  </si>
+  <si>
+    <t>11.06.202680</t>
+  </si>
+  <si>
+    <t>11.06.202681</t>
+  </si>
+  <si>
+    <t>11.06.202682</t>
+  </si>
+  <si>
+    <t>11.06.202683</t>
+  </si>
+  <si>
+    <t>11.06.202684</t>
+  </si>
+  <si>
+    <t>11.06.202685</t>
+  </si>
+  <si>
+    <t>11.06.202686</t>
+  </si>
+  <si>
+    <t>11.06.202687</t>
+  </si>
+  <si>
+    <t>11.06.202688</t>
+  </si>
+  <si>
+    <t>11.06.202689</t>
+  </si>
+  <si>
+    <t>11.06.202690</t>
+  </si>
+  <si>
+    <t>11.06.202691</t>
+  </si>
+  <si>
+    <t>11.06.202692</t>
+  </si>
+  <si>
+    <t>11.06.202693</t>
+  </si>
+  <si>
+    <t>11.06.202694</t>
+  </si>
+  <si>
+    <t>11.06.202695</t>
+  </si>
+  <si>
+    <t>11.06.202696</t>
+  </si>
+  <si>
+    <t>12.06.20261</t>
+  </si>
+  <si>
+    <t>12.06.20262</t>
+  </si>
+  <si>
+    <t>12.06.20263</t>
+  </si>
+  <si>
+    <t>12.06.20264</t>
+  </si>
+  <si>
+    <t>12.06.20265</t>
+  </si>
+  <si>
+    <t>12.06.20266</t>
+  </si>
+  <si>
+    <t>12.06.20267</t>
+  </si>
+  <si>
+    <t>12.06.20268</t>
+  </si>
+  <si>
+    <t>12.06.20269</t>
+  </si>
+  <si>
+    <t>12.06.202610</t>
+  </si>
+  <si>
+    <t>12.06.202611</t>
+  </si>
+  <si>
+    <t>12.06.202612</t>
+  </si>
+  <si>
+    <t>12.06.202613</t>
+  </si>
+  <si>
+    <t>12.06.202614</t>
+  </si>
+  <si>
+    <t>12.06.202615</t>
+  </si>
+  <si>
+    <t>12.06.202616</t>
+  </si>
+  <si>
+    <t>12.06.202617</t>
+  </si>
+  <si>
+    <t>12.06.202618</t>
+  </si>
+  <si>
+    <t>12.06.202619</t>
+  </si>
+  <si>
+    <t>12.06.202620</t>
+  </si>
+  <si>
+    <t>12.06.202621</t>
+  </si>
+  <si>
+    <t>12.06.202622</t>
+  </si>
+  <si>
+    <t>12.06.202623</t>
+  </si>
+  <si>
+    <t>12.06.202624</t>
+  </si>
+  <si>
+    <t>12.06.202625</t>
+  </si>
+  <si>
+    <t>12.06.202626</t>
+  </si>
+  <si>
+    <t>12.06.202627</t>
+  </si>
+  <si>
+    <t>12.06.202628</t>
+  </si>
+  <si>
+    <t>12.06.202629</t>
+  </si>
+  <si>
+    <t>12.06.202630</t>
+  </si>
+  <si>
+    <t>12.06.202631</t>
+  </si>
+  <si>
+    <t>12.06.202632</t>
+  </si>
+  <si>
+    <t>12.06.202633</t>
+  </si>
+  <si>
+    <t>12.06.202634</t>
+  </si>
+  <si>
+    <t>12.06.202635</t>
+  </si>
+  <si>
+    <t>12.06.202636</t>
+  </si>
+  <si>
+    <t>12.06.202637</t>
+  </si>
+  <si>
+    <t>12.06.202638</t>
+  </si>
+  <si>
+    <t>12.06.202639</t>
+  </si>
+  <si>
+    <t>12.06.202640</t>
+  </si>
+  <si>
+    <t>12.06.202641</t>
+  </si>
+  <si>
+    <t>12.06.202642</t>
+  </si>
+  <si>
+    <t>12.06.202643</t>
+  </si>
+  <si>
+    <t>12.06.202644</t>
+  </si>
+  <si>
+    <t>12.06.202645</t>
+  </si>
+  <si>
+    <t>12.06.202646</t>
+  </si>
+  <si>
+    <t>12.06.202647</t>
+  </si>
+  <si>
+    <t>12.06.202648</t>
+  </si>
+  <si>
+    <t>12.06.202649</t>
+  </si>
+  <si>
+    <t>12.06.202650</t>
+  </si>
+  <si>
+    <t>12.06.202651</t>
+  </si>
+  <si>
+    <t>12.06.202652</t>
+  </si>
+  <si>
+    <t>12.06.202653</t>
+  </si>
+  <si>
+    <t>12.06.202654</t>
+  </si>
+  <si>
+    <t>12.06.202655</t>
+  </si>
+  <si>
+    <t>12.06.202656</t>
+  </si>
+  <si>
+    <t>12.06.202657</t>
+  </si>
+  <si>
+    <t>12.06.202658</t>
+  </si>
+  <si>
+    <t>12.06.202659</t>
+  </si>
+  <si>
+    <t>12.06.202660</t>
+  </si>
+  <si>
+    <t>12.06.202661</t>
+  </si>
+  <si>
+    <t>12.06.202662</t>
+  </si>
+  <si>
+    <t>12.06.202663</t>
+  </si>
+  <si>
+    <t>12.06.202664</t>
+  </si>
+  <si>
+    <t>12.06.202665</t>
+  </si>
+  <si>
+    <t>12.06.202666</t>
+  </si>
+  <si>
+    <t>12.06.202667</t>
+  </si>
+  <si>
+    <t>12.06.202668</t>
+  </si>
+  <si>
+    <t>12.06.202669</t>
+  </si>
+  <si>
+    <t>12.06.202670</t>
+  </si>
+  <si>
+    <t>12.06.202671</t>
+  </si>
+  <si>
+    <t>12.06.202672</t>
+  </si>
+  <si>
+    <t>12.06.202673</t>
+  </si>
+  <si>
+    <t>12.06.202674</t>
+  </si>
+  <si>
+    <t>12.06.202675</t>
+  </si>
+  <si>
+    <t>12.06.202676</t>
+  </si>
+  <si>
+    <t>12.06.202677</t>
+  </si>
+  <si>
+    <t>12.06.202678</t>
+  </si>
+  <si>
+    <t>12.06.202679</t>
+  </si>
+  <si>
+    <t>12.06.202680</t>
+  </si>
+  <si>
+    <t>12.06.202681</t>
+  </si>
+  <si>
+    <t>12.06.202682</t>
+  </si>
+  <si>
+    <t>12.06.202683</t>
+  </si>
+  <si>
+    <t>12.06.202684</t>
+  </si>
+  <si>
+    <t>12.06.202685</t>
+  </si>
+  <si>
+    <t>12.06.202686</t>
+  </si>
+  <si>
+    <t>12.06.202687</t>
+  </si>
+  <si>
+    <t>12.06.202688</t>
+  </si>
+  <si>
+    <t>12.06.202689</t>
+  </si>
+  <si>
+    <t>12.06.202690</t>
+  </si>
+  <si>
+    <t>12.06.202691</t>
+  </si>
+  <si>
+    <t>12.06.202692</t>
+  </si>
+  <si>
+    <t>12.06.202693</t>
+  </si>
+  <si>
+    <t>12.06.202694</t>
+  </si>
+  <si>
+    <t>12.06.202695</t>
+  </si>
+  <si>
+    <t>12.06.202696</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46176.01041666666</v>
+        <v>46184.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46176.02083333334</v>
+        <v>46184.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46176.03125</v>
+        <v>46184.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46176.04166666666</v>
+        <v>46184.04166666666</v>
       </c>
       <c r="B6">
-        <v>-67.154</v>
+        <v>-8.977</v>
       </c>
       <c r="C6">
-        <v>1774.669</v>
+        <v>998.741</v>
       </c>
       <c r="D6">
-        <v>1774.669</v>
+        <v>998.741</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46176.05208333334</v>
+        <v>46184.05208333334</v>
       </c>
       <c r="B7">
-        <v>-44.813</v>
+        <v>-34.28</v>
       </c>
       <c r="C7">
-        <v>1295.96</v>
+        <v>907.271</v>
       </c>
       <c r="D7">
-        <v>1295.96</v>
+        <v>907.271</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46176.0625</v>
+        <v>46184.0625</v>
       </c>
       <c r="B8">
-        <v>-38.27</v>
+        <v>-18.698</v>
       </c>
       <c r="C8">
-        <v>1052.077</v>
+        <v>880.121</v>
       </c>
       <c r="D8">
-        <v>1052.077</v>
+        <v>880.121</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46176.07291666666</v>
+        <v>46184.07291666666</v>
       </c>
       <c r="B9">
-        <v>-53.772</v>
+        <v>-21.68</v>
       </c>
       <c r="C9">
-        <v>978.179</v>
+        <v>873.194</v>
       </c>
       <c r="D9">
-        <v>978.179</v>
+        <v>873.194</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46176.08333333334</v>
+        <v>46184.08333333334</v>
       </c>
       <c r="B10">
-        <v>-37.286</v>
+        <v>-39.951</v>
       </c>
       <c r="C10">
-        <v>1033.017</v>
+        <v>814.143</v>
       </c>
       <c r="D10">
-        <v>1033.017</v>
+        <v>814.143</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46176.09375</v>
+        <v>46184.09375</v>
       </c>
       <c r="B11">
-        <v>-33.735</v>
+        <v>0.358</v>
       </c>
       <c r="C11">
-        <v>1084.736</v>
+        <v>270.124</v>
       </c>
       <c r="D11">
-        <v>1084.736</v>
+        <v>270.124</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46176.10416666666</v>
+        <v>46184.10416666666</v>
       </c>
       <c r="B12">
-        <v>-20.822</v>
+        <v>-16.606</v>
       </c>
       <c r="C12">
-        <v>975.9589999999999</v>
+        <v>853.804</v>
       </c>
       <c r="D12">
-        <v>975.9589999999999</v>
+        <v>853.804</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46176.11458333334</v>
+        <v>46184.11458333334</v>
       </c>
       <c r="B13">
-        <v>-28.19</v>
+        <v>-32.678</v>
       </c>
       <c r="C13">
-        <v>899.702</v>
+        <v>869.696</v>
       </c>
       <c r="D13">
-        <v>899.702</v>
+        <v>869.696</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46176.125</v>
+        <v>46184.125</v>
       </c>
       <c r="B14">
-        <v>-14.665</v>
+        <v>1.199</v>
       </c>
       <c r="C14">
-        <v>974.619</v>
+        <v>274.759</v>
       </c>
       <c r="D14">
-        <v>974.619</v>
+        <v>274.759</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46176.13541666666</v>
+        <v>46184.13541666666</v>
       </c>
       <c r="B15">
-        <v>-28.324</v>
+        <v>-2.145</v>
       </c>
       <c r="C15">
-        <v>1082.035</v>
+        <v>898.453</v>
       </c>
       <c r="D15">
-        <v>1082.035</v>
+        <v>898.453</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46176.14583333334</v>
+        <v>46184.14583333334</v>
       </c>
       <c r="B16">
-        <v>-8.904</v>
+        <v>-21.956</v>
       </c>
       <c r="C16">
-        <v>989.466</v>
+        <v>898.0890000000001</v>
       </c>
       <c r="D16">
-        <v>989.466</v>
+        <v>898.0890000000001</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46176.15625</v>
+        <v>46184.15625</v>
       </c>
       <c r="B17">
-        <v>35.625</v>
+        <v>-48.768</v>
       </c>
       <c r="C17">
-        <v>210.629</v>
+        <v>867.833</v>
       </c>
       <c r="D17">
-        <v>210.629</v>
+        <v>867.833</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46176.16666666666</v>
+        <v>46184.16666666666</v>
       </c>
       <c r="B18">
-        <v>16.675</v>
+        <v>-14.958</v>
       </c>
       <c r="C18">
-        <v>231.742</v>
+        <v>851.606</v>
       </c>
       <c r="D18">
-        <v>231.742</v>
+        <v>851.606</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46176.17708333334</v>
+        <v>46184.17708333334</v>
       </c>
       <c r="B19">
-        <v>29.682</v>
+        <v>7.638</v>
       </c>
       <c r="C19">
-        <v>271.525</v>
+        <v>260.301</v>
       </c>
       <c r="D19">
-        <v>271.525</v>
+        <v>260.301</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46176.1875</v>
+        <v>46184.1875</v>
       </c>
       <c r="B20">
-        <v>11.026</v>
+        <v>29.658</v>
       </c>
       <c r="C20">
-        <v>255.608</v>
+        <v>135.754</v>
       </c>
       <c r="D20">
-        <v>255.608</v>
+        <v>135.754</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46176.19791666666</v>
+        <v>46184.19791666666</v>
       </c>
       <c r="B21">
-        <v>34.158</v>
+        <v>1.797</v>
       </c>
       <c r="C21">
-        <v>256.555</v>
+        <v>266.801</v>
       </c>
       <c r="D21">
-        <v>256.555</v>
+        <v>266.801</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46176.20833333334</v>
+        <v>46184.20833333334</v>
       </c>
       <c r="B22">
-        <v>60.733</v>
+        <v>13.198</v>
       </c>
       <c r="C22">
-        <v>295.652</v>
+        <v>-19.091</v>
       </c>
       <c r="D22">
-        <v>295.652</v>
+        <v>-19.091</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46176.21875</v>
+        <v>46184.21875</v>
       </c>
       <c r="B23">
-        <v>67.529</v>
+        <v>-9.131</v>
       </c>
       <c r="C23">
-        <v>303.165</v>
+        <v>849.5</v>
       </c>
       <c r="D23">
-        <v>303.165</v>
+        <v>849.5</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46176.22916666666</v>
+        <v>46184.22916666666</v>
       </c>
       <c r="B24">
-        <v>73.786</v>
+        <v>6.225</v>
       </c>
       <c r="C24">
-        <v>286.807</v>
+        <v>253.894</v>
       </c>
       <c r="D24">
-        <v>286.807</v>
+        <v>253.894</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46176.23958333334</v>
+        <v>46184.23958333334</v>
       </c>
       <c r="B25">
-        <v>92.765</v>
+        <v>-10.156</v>
       </c>
       <c r="C25">
-        <v>275.225</v>
+        <v>882.7089999999999</v>
       </c>
       <c r="D25">
-        <v>275.225</v>
+        <v>882.7089999999999</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46176.25</v>
+        <v>46184.25</v>
       </c>
       <c r="B26">
-        <v>106.198</v>
+        <v>-10.357</v>
       </c>
       <c r="C26">
-        <v>-35.054</v>
+        <v>1005.79</v>
       </c>
       <c r="D26">
-        <v>-35.054</v>
+        <v>1005.79</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46176.26041666666</v>
+        <v>46184.26041666666</v>
       </c>
       <c r="B27">
-        <v>100.756</v>
+        <v>-19.248</v>
       </c>
       <c r="C27">
-        <v>324.41</v>
+        <v>1054.16</v>
       </c>
       <c r="D27">
-        <v>324.41</v>
+        <v>1054.16</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46176.27083333334</v>
+        <v>46184.27083333334</v>
       </c>
       <c r="B28">
-        <v>130.167</v>
+        <v>-49.469</v>
       </c>
       <c r="C28">
-        <v>336.784</v>
+        <v>943.2910000000001</v>
       </c>
       <c r="D28">
-        <v>336.784</v>
+        <v>943.2910000000001</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46176.28125</v>
+        <v>46184.28125</v>
       </c>
       <c r="B29">
-        <v>123.856</v>
+        <v>1.355</v>
       </c>
       <c r="C29">
-        <v>309.828</v>
+        <v>278.112</v>
       </c>
       <c r="D29">
-        <v>309.828</v>
+        <v>278.112</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46176.29166666666</v>
+        <v>46184.29166666666</v>
       </c>
       <c r="B30">
-        <v>80.892</v>
+        <v>-47.567</v>
       </c>
       <c r="C30">
-        <v>6.488</v>
+        <v>886.266</v>
       </c>
       <c r="D30">
-        <v>6.488</v>
+        <v>886.266</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46176.30208333334</v>
+        <v>46184.30208333334</v>
       </c>
       <c r="B31">
-        <v>82.02200000000001</v>
+        <v>-22.714</v>
       </c>
       <c r="C31">
-        <v>12.553</v>
+        <v>897.2089999999999</v>
       </c>
       <c r="D31">
-        <v>12.553</v>
+        <v>897.2089999999999</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46176.3125</v>
+        <v>46184.3125</v>
       </c>
       <c r="B32">
-        <v>87.901</v>
+        <v>-47.344</v>
       </c>
       <c r="C32">
-        <v>308.975</v>
+        <v>1245.405</v>
       </c>
       <c r="D32">
-        <v>308.975</v>
+        <v>1245.405</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46176.32291666666</v>
+        <v>46184.32291666666</v>
       </c>
       <c r="B33">
-        <v>136.378</v>
+        <v>-84.76600000000001</v>
       </c>
       <c r="C33">
-        <v>312.477</v>
+        <v>1045.756</v>
       </c>
       <c r="D33">
-        <v>312.477</v>
+        <v>1045.756</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46176.33333333334</v>
+        <v>46184.33333333334</v>
       </c>
       <c r="B34">
-        <v>109.459</v>
+        <v>-82.294</v>
       </c>
       <c r="C34">
-        <v>151.408</v>
+        <v>967.838</v>
       </c>
       <c r="D34">
-        <v>151.408</v>
+        <v>967.838</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46176.34375</v>
+        <v>46184.34375</v>
       </c>
       <c r="B35">
-        <v>105.711</v>
+        <v>-122.004</v>
       </c>
       <c r="C35">
-        <v>-1165.255</v>
+        <v>899.322</v>
       </c>
       <c r="D35">
-        <v>-1165.255</v>
+        <v>899.322</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46176.35416666666</v>
+        <v>46184.35416666666</v>
       </c>
       <c r="B36">
-        <v>75.22799999999999</v>
+        <v>-85.25700000000001</v>
       </c>
       <c r="C36">
-        <v>-1863.357</v>
+        <v>899.302</v>
       </c>
       <c r="D36">
-        <v>-1863.357</v>
+        <v>899.302</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46176.36458333334</v>
+        <v>46184.36458333334</v>
       </c>
       <c r="B37">
-        <v>76.265</v>
+        <v>-86.399</v>
       </c>
       <c r="C37">
-        <v>-226.443</v>
+        <v>899</v>
       </c>
       <c r="D37">
-        <v>-226.443</v>
+        <v>899</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46176.375</v>
+        <v>46184.375</v>
       </c>
       <c r="B38">
-        <v>76.79000000000001</v>
+        <v>-135.771</v>
       </c>
       <c r="C38">
-        <v>-12.688</v>
+        <v>703.421</v>
       </c>
       <c r="D38">
-        <v>-12.688</v>
+        <v>703.421</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46176.38541666666</v>
+        <v>46184.38541666666</v>
       </c>
       <c r="B39">
-        <v>88.633</v>
+        <v>-89.146</v>
       </c>
       <c r="C39">
-        <v>-81.053</v>
+        <v>699</v>
       </c>
       <c r="D39">
-        <v>-81.053</v>
+        <v>699</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46176.39583333334</v>
+        <v>46184.39583333334</v>
       </c>
       <c r="B40">
-        <v>80.941</v>
+        <v>-22.404</v>
       </c>
       <c r="C40">
-        <v>8.32</v>
+        <v>704.24</v>
       </c>
       <c r="D40">
-        <v>8.32</v>
+        <v>704.24</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46176.40625</v>
+        <v>46184.40625</v>
       </c>
       <c r="B41">
-        <v>65.038</v>
+        <v>16.127</v>
       </c>
       <c r="C41">
-        <v>0.328</v>
+        <v>-33.354</v>
       </c>
       <c r="D41">
-        <v>0.328</v>
+        <v>-33.354</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46176.41666666666</v>
+        <v>46184.41666666666</v>
       </c>
       <c r="B42">
-        <v>20.057</v>
+        <v>11.871</v>
       </c>
       <c r="C42">
-        <v>4.435</v>
+        <v>37.029</v>
       </c>
       <c r="D42">
-        <v>4.435</v>
+        <v>37.029</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46176.42708333334</v>
+        <v>46184.42708333334</v>
       </c>
       <c r="B43">
-        <v>52.397</v>
+        <v>-6</v>
       </c>
       <c r="C43">
-        <v>0.901</v>
+        <v>688.524</v>
       </c>
       <c r="D43">
-        <v>0.901</v>
+        <v>688.524</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46176.4375</v>
+        <v>46184.4375</v>
       </c>
       <c r="B44">
-        <v>63.301</v>
+        <v>41.063</v>
       </c>
       <c r="C44">
-        <v>0.772</v>
+        <v>258.661</v>
       </c>
       <c r="D44">
-        <v>0.772</v>
+        <v>258.661</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46176.44791666666</v>
+        <v>46184.44791666666</v>
       </c>
       <c r="B45">
-        <v>56.925</v>
+        <v>101.436</v>
       </c>
       <c r="C45">
-        <v>0.1</v>
+        <v>-133.199</v>
       </c>
       <c r="D45">
-        <v>0.1</v>
+        <v>-133.199</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46176.45833333334</v>
+        <v>46184.45833333334</v>
       </c>
       <c r="B46">
-        <v>11.821</v>
+        <v>88.571</v>
       </c>
       <c r="C46">
-        <v>0.2</v>
+        <v>-604.222</v>
       </c>
       <c r="D46">
-        <v>0.2</v>
+        <v>-604.222</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46176.46875</v>
+        <v>46184.46875</v>
       </c>
       <c r="B47">
-        <v>-15.749</v>
+        <v>56.381</v>
       </c>
       <c r="C47">
-        <v>793.917</v>
+        <v>-509.125</v>
       </c>
       <c r="D47">
-        <v>793.917</v>
+        <v>-509.125</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46176.47916666666</v>
+        <v>46184.47916666666</v>
       </c>
       <c r="B48">
-        <v>-14.263</v>
+        <v>31.774</v>
       </c>
       <c r="C48">
-        <v>408.921</v>
+        <v>113.136</v>
       </c>
       <c r="D48">
-        <v>408.921</v>
+        <v>113.136</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46176.48958333334</v>
+        <v>46184.48958333334</v>
       </c>
       <c r="B49">
-        <v>-46.755</v>
+        <v>40.934</v>
       </c>
       <c r="C49">
-        <v>412.981</v>
+        <v>-36.847</v>
       </c>
       <c r="D49">
-        <v>412.981</v>
+        <v>-36.847</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46176.5</v>
+        <v>46184.5</v>
       </c>
       <c r="B50">
-        <v>-28.786</v>
+        <v>7.026</v>
       </c>
       <c r="C50">
-        <v>576.414</v>
+        <v>91.694</v>
       </c>
       <c r="D50">
-        <v>576.414</v>
+        <v>91.694</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46176.51041666666</v>
+        <v>46184.51041666666</v>
       </c>
       <c r="B51">
-        <v>-38.794</v>
+        <v>39.83</v>
       </c>
       <c r="C51">
-        <v>586.159</v>
+        <v>44.118</v>
       </c>
       <c r="D51">
-        <v>586.159</v>
+        <v>44.118</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46176.52083333334</v>
+        <v>46184.52083333334</v>
       </c>
       <c r="B52">
-        <v>-13.33</v>
+        <v>69.81100000000001</v>
       </c>
       <c r="C52">
-        <v>558.513</v>
+        <v>-1706.231</v>
       </c>
       <c r="D52">
-        <v>558.513</v>
+        <v>-1706.231</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46176.53125</v>
+        <v>46184.53125</v>
       </c>
       <c r="B53">
-        <v>-2.584</v>
+        <v>55.383</v>
       </c>
       <c r="C53">
-        <v>680.8819999999999</v>
+        <v>-18.291</v>
       </c>
       <c r="D53">
-        <v>680.8819999999999</v>
+        <v>-18.291</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46176.54166666666</v>
+        <v>46184.54166666666</v>
       </c>
       <c r="B54">
-        <v>-22.274</v>
+        <v>5.611</v>
       </c>
       <c r="C54">
-        <v>653.256</v>
+        <v>13.618</v>
       </c>
       <c r="D54">
-        <v>653.256</v>
+        <v>13.618</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46176.55208333334</v>
+        <v>46184.55208333334</v>
       </c>
       <c r="B55">
-        <v>-55.631</v>
+        <v>17.71</v>
       </c>
       <c r="C55">
-        <v>719.553</v>
+        <v>17.491</v>
       </c>
       <c r="D55">
-        <v>719.553</v>
+        <v>17.491</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46176.5625</v>
+        <v>46184.5625</v>
       </c>
       <c r="B56">
-        <v>-56.167</v>
+        <v>28.573</v>
       </c>
       <c r="C56">
-        <v>1054.305</v>
+        <v>38.133</v>
       </c>
       <c r="D56">
-        <v>1054.305</v>
+        <v>38.133</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46176.57291666666</v>
+        <v>46184.57291666666</v>
       </c>
       <c r="B57">
-        <v>-58.259</v>
+        <v>38.936</v>
       </c>
       <c r="C57">
-        <v>839.17</v>
+        <v>-69.79600000000001</v>
       </c>
       <c r="D57">
-        <v>839.17</v>
+        <v>-69.79600000000001</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -2114,16 +2114,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2">
-        <v>46176.58333333334</v>
+        <v>46184.58333333334</v>
       </c>
       <c r="B58">
-        <v>-28.159</v>
+        <v>92.248</v>
       </c>
       <c r="C58">
-        <v>691.751</v>
+        <v>46.554</v>
       </c>
       <c r="D58">
-        <v>691.751</v>
+        <v>46.554</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2">
-        <v>46176.59375</v>
+        <v>46184.59375</v>
       </c>
       <c r="B59">
-        <v>-21.872</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>694.39</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>694.39</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -2154,16 +2154,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2">
-        <v>46176.60416666666</v>
+        <v>46184.60416666666</v>
       </c>
       <c r="B60">
-        <v>12.287</v>
+        <v>27.551</v>
       </c>
       <c r="C60">
-        <v>297.657</v>
+        <v>32.887</v>
       </c>
       <c r="D60">
-        <v>297.657</v>
+        <v>32.887</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -2174,16 +2174,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2">
-        <v>46176.61458333334</v>
+        <v>46184.61458333334</v>
       </c>
       <c r="B61">
-        <v>-4.558</v>
+        <v>2.352</v>
       </c>
       <c r="C61">
-        <v>399</v>
+        <v>154.199</v>
       </c>
       <c r="D61">
-        <v>399</v>
+        <v>154.199</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -2194,16 +2194,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2">
-        <v>46176.625</v>
+        <v>46184.625</v>
       </c>
       <c r="B62">
-        <v>66.867</v>
+        <v>33.659</v>
       </c>
       <c r="C62">
-        <v>-1594.171</v>
+        <v>-180.936</v>
       </c>
       <c r="D62">
-        <v>-1594.171</v>
+        <v>-180.936</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2">
-        <v>46176.63541666666</v>
+        <v>46184.63541666666</v>
       </c>
       <c r="B63">
-        <v>56.658</v>
+        <v>-68.967</v>
       </c>
       <c r="C63">
-        <v>-2757.014</v>
+        <v>763.225</v>
       </c>
       <c r="D63">
-        <v>-2757.014</v>
+        <v>763.225</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2">
-        <v>46176.64583333334</v>
+        <v>46184.64583333334</v>
       </c>
       <c r="B64">
-        <v>93.13800000000001</v>
+        <v>-131.953</v>
       </c>
       <c r="C64">
-        <v>-26.683</v>
+        <v>2897.348</v>
       </c>
       <c r="D64">
-        <v>-26.683</v>
+        <v>2897.348</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -2254,16 +2254,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2">
-        <v>46176.65625</v>
+        <v>46184.65625</v>
       </c>
       <c r="B65">
-        <v>102.332</v>
+        <v>-108.543</v>
       </c>
       <c r="C65">
-        <v>156.867</v>
+        <v>1176.36</v>
       </c>
       <c r="D65">
-        <v>156.867</v>
+        <v>1176.36</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -2274,16 +2274,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="2">
-        <v>46176.66666666666</v>
+        <v>46184.66666666666</v>
       </c>
       <c r="B66">
-        <v>57.445</v>
+        <v>-54.983</v>
       </c>
       <c r="C66">
-        <v>-105.262</v>
+        <v>870.769</v>
       </c>
       <c r="D66">
-        <v>-105.262</v>
+        <v>870.769</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2">
-        <v>46176.67708333334</v>
+        <v>46184.67708333334</v>
       </c>
       <c r="B67">
-        <v>118.694</v>
+        <v>-5.634</v>
       </c>
       <c r="C67">
-        <v>77.509</v>
+        <v>873</v>
       </c>
       <c r="D67">
-        <v>77.509</v>
+        <v>873</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2">
-        <v>46176.6875</v>
+        <v>46184.6875</v>
       </c>
       <c r="B68">
-        <v>84.97799999999999</v>
+        <v>61.926</v>
       </c>
       <c r="C68">
-        <v>177.557</v>
+        <v>268.601</v>
       </c>
       <c r="D68">
-        <v>177.557</v>
+        <v>268.601</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -2334,16 +2334,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2">
-        <v>46176.69791666666</v>
+        <v>46184.69791666666</v>
       </c>
       <c r="B69">
-        <v>51.579</v>
+        <v>31.759</v>
       </c>
       <c r="C69">
-        <v>-68.51300000000001</v>
+        <v>233.245</v>
       </c>
       <c r="D69">
-        <v>-68.51300000000001</v>
+        <v>233.245</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -2354,16 +2354,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2">
-        <v>46176.70833333334</v>
+        <v>46184.70833333334</v>
       </c>
       <c r="B70">
-        <v>48.6</v>
+        <v>-15.319</v>
       </c>
       <c r="C70">
-        <v>-790.261</v>
+        <v>899</v>
       </c>
       <c r="D70">
-        <v>-790.261</v>
+        <v>899</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -2374,16 +2374,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2">
-        <v>46176.71875</v>
+        <v>46184.71875</v>
       </c>
       <c r="B71">
-        <v>6.463</v>
+        <v>-4.756</v>
       </c>
       <c r="C71">
-        <v>38.959</v>
+        <v>920.331</v>
       </c>
       <c r="D71">
-        <v>38.959</v>
+        <v>920.331</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2">
-        <v>46176.72916666666</v>
+        <v>46184.72916666666</v>
       </c>
       <c r="B72">
-        <v>-25.633</v>
+        <v>-0.794</v>
       </c>
       <c r="C72">
-        <v>890.492</v>
+        <v>899</v>
       </c>
       <c r="D72">
-        <v>890.492</v>
+        <v>899</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -2414,16 +2414,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2">
-        <v>46176.73958333334</v>
+        <v>46184.73958333334</v>
       </c>
       <c r="B73">
-        <v>-84.411</v>
+        <v>-23.736</v>
       </c>
       <c r="C73">
-        <v>784.742</v>
+        <v>1172.213</v>
       </c>
       <c r="D73">
-        <v>784.742</v>
+        <v>1172.213</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2">
-        <v>46176.75</v>
+        <v>46184.75</v>
       </c>
       <c r="B74">
-        <v>-74.399</v>
+        <v>-102.556</v>
       </c>
       <c r="C74">
-        <v>1790.972</v>
+        <v>1554.175</v>
       </c>
       <c r="D74">
-        <v>1790.972</v>
+        <v>1554.175</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -2454,16 +2454,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2">
-        <v>46176.76041666666</v>
+        <v>46184.76041666666</v>
       </c>
       <c r="B75">
-        <v>-72.58799999999999</v>
+        <v>-140.035</v>
       </c>
       <c r="C75">
-        <v>1631.225</v>
+        <v>2908.794</v>
       </c>
       <c r="D75">
-        <v>1631.225</v>
+        <v>2908.794</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2">
-        <v>46176.77083333334</v>
+        <v>46184.77083333334</v>
       </c>
       <c r="B76">
-        <v>-73.19</v>
+        <v>-81.116</v>
       </c>
       <c r="C76">
-        <v>4546.428</v>
+        <v>1240.285</v>
       </c>
       <c r="D76">
-        <v>4546.428</v>
+        <v>1240.285</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2">
-        <v>46176.78125</v>
+        <v>46184.78125</v>
       </c>
       <c r="B77">
-        <v>-137.547</v>
+        <v>-62.311</v>
       </c>
       <c r="C77">
-        <v>2994.665</v>
+        <v>1166.478</v>
       </c>
       <c r="D77">
-        <v>2994.665</v>
+        <v>1166.478</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -2514,16 +2514,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2">
-        <v>46176.79166666666</v>
+        <v>46184.79166666666</v>
       </c>
       <c r="B78">
-        <v>13.769</v>
+        <v>-6.029</v>
       </c>
       <c r="C78">
-        <v>400</v>
+        <v>1291.01</v>
       </c>
       <c r="D78">
-        <v>400</v>
+        <v>1291.01</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -2534,16 +2534,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2">
-        <v>46176.80208333334</v>
+        <v>46184.80208333334</v>
       </c>
       <c r="B79">
-        <v>-1.201</v>
+        <v>26.801</v>
       </c>
       <c r="C79">
-        <v>1350.849</v>
+        <v>-236.096</v>
       </c>
       <c r="D79">
-        <v>1350.849</v>
+        <v>-236.096</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2">
-        <v>46176.8125</v>
+        <v>46184.8125</v>
       </c>
       <c r="B80">
-        <v>4.692</v>
+        <v>7.916</v>
       </c>
       <c r="C80">
-        <v>377.656</v>
+        <v>196.087</v>
       </c>
       <c r="D80">
-        <v>377.656</v>
+        <v>196.087</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -2574,16 +2574,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2">
-        <v>46176.82291666666</v>
+        <v>46184.82291666666</v>
       </c>
       <c r="B81">
-        <v>-9.153</v>
+        <v>11.321</v>
       </c>
       <c r="C81">
-        <v>1112.949</v>
+        <v>334.558</v>
       </c>
       <c r="D81">
-        <v>1112.949</v>
+        <v>334.558</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2">
-        <v>46176.83333333334</v>
+        <v>46184.83333333334</v>
       </c>
       <c r="B82">
-        <v>10.96</v>
+        <v>14.414</v>
       </c>
       <c r="C82">
-        <v>278.39</v>
+        <v>257.587</v>
       </c>
       <c r="D82">
-        <v>278.39</v>
+        <v>257.587</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -2614,16 +2614,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2">
-        <v>46176.84375</v>
+        <v>46184.84375</v>
       </c>
       <c r="B83">
-        <v>-33.081</v>
+        <v>51.347</v>
       </c>
       <c r="C83">
-        <v>894.903</v>
+        <v>270.152</v>
       </c>
       <c r="D83">
-        <v>894.903</v>
+        <v>270.152</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -2634,16 +2634,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2">
-        <v>46176.85416666666</v>
+        <v>46184.85416666666</v>
       </c>
       <c r="B84">
-        <v>-42.824</v>
+        <v>85.17400000000001</v>
       </c>
       <c r="C84">
-        <v>960.114</v>
+        <v>361.793</v>
       </c>
       <c r="D84">
-        <v>960.114</v>
+        <v>361.793</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -2654,16 +2654,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2">
-        <v>46176.86458333334</v>
+        <v>46184.86458333334</v>
       </c>
       <c r="B85">
-        <v>-23.048</v>
+        <v>69.54900000000001</v>
       </c>
       <c r="C85">
-        <v>1167.167</v>
+        <v>321.404</v>
       </c>
       <c r="D85">
-        <v>1167.167</v>
+        <v>321.404</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2">
-        <v>46176.875</v>
+        <v>46184.875</v>
       </c>
       <c r="B86">
-        <v>-61.715</v>
+        <v>37.866</v>
       </c>
       <c r="C86">
-        <v>1710.293</v>
+        <v>281.703</v>
       </c>
       <c r="D86">
-        <v>1710.293</v>
+        <v>281.703</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -2694,16 +2694,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2">
-        <v>46176.88541666666</v>
+        <v>46184.88541666666</v>
       </c>
       <c r="B87">
-        <v>-59.216</v>
+        <v>33.359</v>
       </c>
       <c r="C87">
-        <v>3183.49</v>
+        <v>347.307</v>
       </c>
       <c r="D87">
-        <v>3183.49</v>
+        <v>347.307</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -2714,16 +2714,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2">
-        <v>46176.89583333334</v>
+        <v>46184.89583333334</v>
       </c>
       <c r="B88">
-        <v>-63.961</v>
+        <v>25.248</v>
       </c>
       <c r="C88">
-        <v>5478.772</v>
+        <v>338.146</v>
       </c>
       <c r="D88">
-        <v>5478.772</v>
+        <v>338.146</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -2734,16 +2734,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2">
-        <v>46176.90625</v>
+        <v>46184.90625</v>
       </c>
       <c r="B89">
-        <v>-30.347</v>
+        <v>15.892</v>
       </c>
       <c r="C89">
-        <v>1249.975</v>
+        <v>-87.724</v>
       </c>
       <c r="D89">
-        <v>1249.975</v>
+        <v>-87.724</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="2">
-        <v>46176.91666666666</v>
+        <v>46184.91666666666</v>
       </c>
       <c r="B90">
-        <v>-33.016</v>
+        <v>-15.861</v>
       </c>
       <c r="C90">
-        <v>1158.593</v>
+        <v>898.925</v>
       </c>
       <c r="D90">
-        <v>1158.593</v>
+        <v>898.925</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2">
-        <v>46176.92708333334</v>
+        <v>46184.92708333334</v>
       </c>
       <c r="B91">
-        <v>-18.115</v>
+        <v>-32.303</v>
       </c>
       <c r="C91">
-        <v>1124.533</v>
+        <v>938.929</v>
       </c>
       <c r="D91">
-        <v>1124.533</v>
+        <v>938.929</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -2794,16 +2794,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2">
-        <v>46176.9375</v>
+        <v>46184.9375</v>
       </c>
       <c r="B92">
-        <v>-45.559</v>
+        <v>-32.439</v>
       </c>
       <c r="C92">
-        <v>1157.609</v>
+        <v>1022.155</v>
       </c>
       <c r="D92">
-        <v>1157.609</v>
+        <v>1022.155</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2">
-        <v>46176.94791666666</v>
+        <v>46184.94791666666</v>
       </c>
       <c r="B93">
-        <v>-20.685</v>
+        <v>-58.236</v>
       </c>
       <c r="C93">
-        <v>1119.752</v>
+        <v>896.811</v>
       </c>
       <c r="D93">
-        <v>1119.752</v>
+        <v>896.811</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -2834,16 +2834,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2">
-        <v>46176.95833333334</v>
+        <v>46184.95833333334</v>
       </c>
       <c r="B94">
-        <v>-33.524</v>
+        <v>-81.61</v>
       </c>
       <c r="C94">
-        <v>1110.102</v>
+        <v>898.2190000000001</v>
       </c>
       <c r="D94">
-        <v>1110.102</v>
+        <v>898.2190000000001</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -2854,16 +2854,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2">
-        <v>46176.96875</v>
+        <v>46184.96875</v>
       </c>
       <c r="B95">
-        <v>-5.373</v>
+        <v>-13.893</v>
       </c>
       <c r="C95">
-        <v>1156.22</v>
+        <v>899.011</v>
       </c>
       <c r="D95">
-        <v>1156.22</v>
+        <v>899.011</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2">
-        <v>46176.97916666666</v>
+        <v>46184.97916666666</v>
       </c>
       <c r="B96">
-        <v>-17.74</v>
+        <v>10.983</v>
       </c>
       <c r="C96">
-        <v>1155.509</v>
+        <v>254.785</v>
       </c>
       <c r="D96">
-        <v>1155.509</v>
+        <v>254.785</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -2894,16 +2894,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2">
-        <v>46176.98958333334</v>
+        <v>46184.98958333334</v>
       </c>
       <c r="B97">
-        <v>-13.01</v>
+        <v>-24.282</v>
       </c>
       <c r="C97">
-        <v>899.562</v>
+        <v>861.875</v>
       </c>
       <c r="D97">
-        <v>899.562</v>
+        <v>861.875</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -2914,16 +2914,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B98">
-        <v>15.292</v>
+        <v>-3.826</v>
       </c>
       <c r="C98">
-        <v>293.913</v>
+        <v>810.421</v>
       </c>
       <c r="D98">
-        <v>293.913</v>
+        <v>810.421</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -2934,16 +2934,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2">
-        <v>46177.01041666666</v>
+        <v>46185.01041666666</v>
       </c>
       <c r="B99">
-        <v>46.365</v>
+        <v>10.401</v>
       </c>
       <c r="C99">
-        <v>400</v>
+        <v>259.181</v>
       </c>
       <c r="D99">
-        <v>400</v>
+        <v>259.181</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -2954,16 +2954,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2">
-        <v>46177.02083333334</v>
+        <v>46185.02083333334</v>
       </c>
       <c r="B100">
-        <v>14.443</v>
+        <v>17.477</v>
       </c>
       <c r="C100">
-        <v>842.472</v>
+        <v>20.796</v>
       </c>
       <c r="D100">
-        <v>842.472</v>
+        <v>20.796</v>
       </c>
       <c r="E100">
         <v>3</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2">
-        <v>46177.03125</v>
+        <v>46185.03125</v>
       </c>
       <c r="B101">
-        <v>15.272</v>
+        <v>20.621</v>
       </c>
       <c r="C101">
-        <v>400</v>
+        <v>221.896</v>
       </c>
       <c r="D101">
-        <v>400</v>
+        <v>221.896</v>
       </c>
       <c r="E101">
         <v>4</v>
@@ -2994,16 +2994,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2">
-        <v>46177.04166666666</v>
+        <v>46185.04166666666</v>
       </c>
       <c r="B102">
-        <v>3.019</v>
+        <v>26.189</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>209.577</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>209.577</v>
       </c>
       <c r="E102">
         <v>5</v>
@@ -3014,16 +3014,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2">
-        <v>46177.05208333334</v>
+        <v>46185.05208333334</v>
       </c>
       <c r="B103">
-        <v>0.5679999999999999</v>
+        <v>13.595</v>
       </c>
       <c r="C103">
-        <v>319.367</v>
+        <v>255.385</v>
       </c>
       <c r="D103">
-        <v>319.367</v>
+        <v>255.385</v>
       </c>
       <c r="E103">
         <v>6</v>
@@ -3034,16 +3034,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2">
-        <v>46177.0625</v>
+        <v>46185.0625</v>
       </c>
       <c r="B104">
-        <v>18.973</v>
+        <v>7.407</v>
       </c>
       <c r="C104">
-        <v>346.247</v>
+        <v>259.01</v>
       </c>
       <c r="D104">
-        <v>346.247</v>
+        <v>259.01</v>
       </c>
       <c r="E104">
         <v>7</v>
@@ -3054,16 +3054,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2">
-        <v>46177.07291666666</v>
+        <v>46185.07291666666</v>
       </c>
       <c r="B105">
-        <v>28.768</v>
+        <v>10.398</v>
       </c>
       <c r="C105">
-        <v>330.692</v>
+        <v>135.378</v>
       </c>
       <c r="D105">
-        <v>330.692</v>
+        <v>135.378</v>
       </c>
       <c r="E105">
         <v>8</v>
@@ -3074,16 +3074,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2">
-        <v>46177.08333333334</v>
+        <v>46185.08333333334</v>
       </c>
       <c r="B106">
-        <v>38.963</v>
+        <v>11.039</v>
       </c>
       <c r="C106">
-        <v>265.671</v>
+        <v>166.887</v>
       </c>
       <c r="D106">
-        <v>265.671</v>
+        <v>166.887</v>
       </c>
       <c r="E106">
         <v>9</v>
@@ -3094,16 +3094,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2">
-        <v>46177.09375</v>
+        <v>46185.09375</v>
       </c>
       <c r="B107">
-        <v>38.54</v>
+        <v>19.454</v>
       </c>
       <c r="C107">
-        <v>110.74</v>
+        <v>105.015</v>
       </c>
       <c r="D107">
-        <v>110.74</v>
+        <v>105.015</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -3114,16 +3114,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2">
-        <v>46177.10416666666</v>
+        <v>46185.10416666666</v>
       </c>
       <c r="B108">
-        <v>58.984</v>
+        <v>23.749</v>
       </c>
       <c r="C108">
-        <v>172.003</v>
+        <v>170.55</v>
       </c>
       <c r="D108">
-        <v>172.003</v>
+        <v>170.55</v>
       </c>
       <c r="E108">
         <v>11</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2">
-        <v>46177.11458333334</v>
+        <v>46185.11458333334</v>
       </c>
       <c r="B109">
-        <v>48.128</v>
+        <v>6.474</v>
       </c>
       <c r="C109">
-        <v>22.981</v>
+        <v>264.681</v>
       </c>
       <c r="D109">
-        <v>22.981</v>
+        <v>264.681</v>
       </c>
       <c r="E109">
         <v>12</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2">
-        <v>46177.125</v>
+        <v>46185.125</v>
       </c>
       <c r="B110">
-        <v>59.736</v>
+        <v>21.254</v>
       </c>
       <c r="C110">
-        <v>254.431</v>
+        <v>191.734</v>
       </c>
       <c r="D110">
-        <v>254.431</v>
+        <v>191.734</v>
       </c>
       <c r="E110">
         <v>13</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2">
-        <v>46177.13541666666</v>
+        <v>46185.13541666666</v>
       </c>
       <c r="B111">
-        <v>45.405</v>
+        <v>35.588</v>
       </c>
       <c r="C111">
-        <v>281.373</v>
+        <v>165.827</v>
       </c>
       <c r="D111">
-        <v>281.373</v>
+        <v>165.827</v>
       </c>
       <c r="E111">
         <v>14</v>
@@ -3194,16 +3194,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2">
-        <v>46177.14583333334</v>
+        <v>46185.14583333334</v>
       </c>
       <c r="B112">
-        <v>9.384</v>
+        <v>44.584</v>
       </c>
       <c r="C112">
-        <v>112.274</v>
+        <v>251.479</v>
       </c>
       <c r="D112">
-        <v>112.274</v>
+        <v>251.479</v>
       </c>
       <c r="E112">
         <v>15</v>
@@ -3214,16 +3214,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2">
-        <v>46177.15625</v>
+        <v>46185.15625</v>
       </c>
       <c r="B113">
-        <v>24.978</v>
+        <v>54.082</v>
       </c>
       <c r="C113">
-        <v>-39.769</v>
+        <v>283.478</v>
       </c>
       <c r="D113">
-        <v>-39.769</v>
+        <v>283.478</v>
       </c>
       <c r="E113">
         <v>16</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2">
-        <v>46177.16666666666</v>
+        <v>46185.16666666666</v>
       </c>
       <c r="B114">
-        <v>20.435</v>
+        <v>33.791</v>
       </c>
       <c r="C114">
-        <v>118.125</v>
+        <v>315.081</v>
       </c>
       <c r="D114">
-        <v>118.125</v>
+        <v>315.081</v>
       </c>
       <c r="E114">
         <v>17</v>
@@ -3254,16 +3254,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2">
-        <v>46177.17708333334</v>
+        <v>46185.17708333334</v>
       </c>
       <c r="B115">
-        <v>29.451</v>
+        <v>53.218</v>
       </c>
       <c r="C115">
-        <v>324.04</v>
+        <v>264.024</v>
       </c>
       <c r="D115">
-        <v>324.04</v>
+        <v>264.024</v>
       </c>
       <c r="E115">
         <v>18</v>
@@ -3274,16 +3274,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2">
-        <v>46177.1875</v>
+        <v>46185.1875</v>
       </c>
       <c r="B116">
-        <v>25.801</v>
+        <v>40.818</v>
       </c>
       <c r="C116">
-        <v>269.556</v>
+        <v>290.44</v>
       </c>
       <c r="D116">
-        <v>269.556</v>
+        <v>290.44</v>
       </c>
       <c r="E116">
         <v>19</v>
@@ -3294,16 +3294,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2">
-        <v>46177.19791666666</v>
+        <v>46185.19791666666</v>
       </c>
       <c r="B117">
-        <v>31.291</v>
+        <v>7.217</v>
       </c>
       <c r="C117">
-        <v>260.123</v>
+        <v>344.887</v>
       </c>
       <c r="D117">
-        <v>260.123</v>
+        <v>344.887</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -3314,16 +3314,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="2">
-        <v>46177.20833333334</v>
+        <v>46185.20833333334</v>
       </c>
       <c r="B118">
-        <v>35.556</v>
+        <v>62.23</v>
       </c>
       <c r="C118">
-        <v>28.472</v>
+        <v>281.034</v>
       </c>
       <c r="D118">
-        <v>28.472</v>
+        <v>281.034</v>
       </c>
       <c r="E118">
         <v>21</v>
@@ -3334,16 +3334,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2">
-        <v>46177.21875</v>
+        <v>46185.21875</v>
       </c>
       <c r="B119">
-        <v>39.111</v>
+        <v>30.929</v>
       </c>
       <c r="C119">
-        <v>318.498</v>
+        <v>400</v>
       </c>
       <c r="D119">
-        <v>318.498</v>
+        <v>400</v>
       </c>
       <c r="E119">
         <v>22</v>
@@ -3354,16 +3354,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2">
-        <v>46177.22916666666</v>
+        <v>46185.22916666666</v>
       </c>
       <c r="B120">
-        <v>83.529</v>
+        <v>22.826</v>
       </c>
       <c r="C120">
-        <v>260.795</v>
+        <v>281.024</v>
       </c>
       <c r="D120">
-        <v>260.795</v>
+        <v>281.024</v>
       </c>
       <c r="E120">
         <v>23</v>
@@ -3374,16 +3374,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2">
-        <v>46177.23958333334</v>
+        <v>46185.23958333334</v>
       </c>
       <c r="B121">
-        <v>83.861</v>
+        <v>-5.584</v>
       </c>
       <c r="C121">
-        <v>335.451</v>
+        <v>916.794</v>
       </c>
       <c r="D121">
-        <v>335.451</v>
+        <v>916.794</v>
       </c>
       <c r="E121">
         <v>24</v>
@@ -3394,16 +3394,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2">
-        <v>46177.25</v>
+        <v>46185.25</v>
       </c>
       <c r="B122">
-        <v>102.235</v>
+        <v>-17.838</v>
       </c>
       <c r="C122">
-        <v>7.959</v>
+        <v>1064.933</v>
       </c>
       <c r="D122">
-        <v>7.959</v>
+        <v>1064.933</v>
       </c>
       <c r="E122">
         <v>25</v>
@@ -3414,16 +3414,16 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2">
-        <v>46177.26041666666</v>
+        <v>46185.26041666666</v>
       </c>
       <c r="B123">
-        <v>87.069</v>
+        <v>-27.022</v>
       </c>
       <c r="C123">
-        <v>1.239</v>
+        <v>947.657</v>
       </c>
       <c r="D123">
-        <v>1.239</v>
+        <v>947.657</v>
       </c>
       <c r="E123">
         <v>26</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2">
-        <v>46177.27083333334</v>
+        <v>46185.27083333334</v>
       </c>
       <c r="B124">
-        <v>46.433</v>
+        <v>-36.53</v>
       </c>
       <c r="C124">
-        <v>3.567</v>
+        <v>900</v>
       </c>
       <c r="D124">
-        <v>3.567</v>
+        <v>900</v>
       </c>
       <c r="E124">
         <v>27</v>
@@ -3454,16 +3454,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2">
-        <v>46177.28125</v>
+        <v>46185.28125</v>
       </c>
       <c r="B125">
-        <v>31.7</v>
+        <v>-8.769</v>
       </c>
       <c r="C125">
-        <v>3.238</v>
+        <v>893.739</v>
       </c>
       <c r="D125">
-        <v>3.238</v>
+        <v>893.739</v>
       </c>
       <c r="E125">
         <v>28</v>
@@ -3474,16 +3474,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2">
-        <v>46177.29166666666</v>
+        <v>46185.29166666666</v>
       </c>
       <c r="B126">
-        <v>77.607</v>
+        <v>53.796</v>
       </c>
       <c r="C126">
-        <v>12.386</v>
+        <v>266.779</v>
       </c>
       <c r="D126">
-        <v>12.386</v>
+        <v>266.779</v>
       </c>
       <c r="E126">
         <v>29</v>
@@ -3494,16 +3494,16 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2">
-        <v>46177.30208333334</v>
+        <v>46185.30208333334</v>
       </c>
       <c r="B127">
-        <v>71.83</v>
+        <v>30.919</v>
       </c>
       <c r="C127">
-        <v>0.882</v>
+        <v>283.816</v>
       </c>
       <c r="D127">
-        <v>0.882</v>
+        <v>283.816</v>
       </c>
       <c r="E127">
         <v>30</v>
@@ -3514,16 +3514,16 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2">
-        <v>46177.3125</v>
+        <v>46185.3125</v>
       </c>
       <c r="B128">
-        <v>30.846</v>
+        <v>62.293</v>
       </c>
       <c r="C128">
-        <v>0.5</v>
+        <v>261.155</v>
       </c>
       <c r="D128">
-        <v>0.5</v>
+        <v>261.155</v>
       </c>
       <c r="E128">
         <v>31</v>
@@ -3534,16 +3534,16 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2">
-        <v>46177.32291666666</v>
+        <v>46185.32291666666</v>
       </c>
       <c r="B129">
-        <v>4.406</v>
+        <v>32.089</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>261.91</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>261.91</v>
       </c>
       <c r="E129">
         <v>32</v>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2">
-        <v>46177.33333333334</v>
+        <v>46185.33333333334</v>
       </c>
       <c r="B130">
-        <v>-46.72</v>
+        <v>86.23</v>
       </c>
       <c r="C130">
-        <v>5134.019</v>
+        <v>-59.401</v>
       </c>
       <c r="D130">
-        <v>5134.019</v>
+        <v>-59.401</v>
       </c>
       <c r="E130">
         <v>33</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2">
-        <v>46177.34375</v>
+        <v>46185.34375</v>
       </c>
       <c r="B131">
-        <v>-128.98</v>
+        <v>53.017</v>
       </c>
       <c r="C131">
-        <v>2855.638</v>
+        <v>-85.435</v>
       </c>
       <c r="D131">
-        <v>2855.638</v>
+        <v>-85.435</v>
       </c>
       <c r="E131">
         <v>34</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2">
-        <v>46177.35416666666</v>
+        <v>46185.35416666666</v>
       </c>
       <c r="B132">
-        <v>-107.251</v>
+        <v>58.634</v>
       </c>
       <c r="C132">
-        <v>1542.938</v>
+        <v>-1479.557</v>
       </c>
       <c r="D132">
-        <v>1542.938</v>
+        <v>-1479.557</v>
       </c>
       <c r="E132">
         <v>35</v>
@@ -3614,16 +3614,16 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2">
-        <v>46177.36458333334</v>
+        <v>46185.36458333334</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>58.373</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>-96.413</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>-96.413</v>
       </c>
       <c r="E133">
         <v>36</v>
@@ -3634,16 +3634,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2">
-        <v>46177.375</v>
+        <v>46185.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>78.26300000000001</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>-248.244</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>-248.244</v>
       </c>
       <c r="E134">
         <v>37</v>
@@ -3654,16 +3654,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2">
-        <v>46177.38541666666</v>
+        <v>46185.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>59.125</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>-1696.094</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>-1696.094</v>
       </c>
       <c r="E135">
         <v>38</v>
@@ -3674,16 +3674,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2">
-        <v>46177.39583333334</v>
+        <v>46185.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>65.994</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>-257.297</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>-257.297</v>
       </c>
       <c r="E136">
         <v>39</v>
@@ -3694,16 +3694,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2">
-        <v>46177.40625</v>
+        <v>46185.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>54.709</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>42.297</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>42.297</v>
       </c>
       <c r="E137">
         <v>40</v>
@@ -3714,16 +3714,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2">
-        <v>46177.41666666666</v>
+        <v>46185.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>69.596</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>33.164</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>33.164</v>
       </c>
       <c r="E138">
         <v>41</v>
@@ -3734,16 +3734,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2">
-        <v>46177.42708333334</v>
+        <v>46185.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>75.304</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>20.803</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>20.803</v>
       </c>
       <c r="E139">
         <v>42</v>
@@ -3754,16 +3754,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2">
-        <v>46177.4375</v>
+        <v>46185.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>34.347</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>42.77</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>42.77</v>
       </c>
       <c r="E140">
         <v>43</v>
@@ -3774,16 +3774,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2">
-        <v>46177.44791666666</v>
+        <v>46185.44791666666</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>66.28700000000001</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>-77.723</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>-77.723</v>
       </c>
       <c r="E141">
         <v>44</v>
@@ -3794,16 +3794,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2">
-        <v>46177.45833333334</v>
+        <v>46185.45833333334</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>51.212</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>37.83</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>37.83</v>
       </c>
       <c r="E142">
         <v>45</v>
@@ -3814,16 +3814,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2">
-        <v>46177.46875</v>
+        <v>46185.46875</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>90.557</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>-41.093</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>-41.093</v>
       </c>
       <c r="E143">
         <v>46</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2">
-        <v>46177.47916666666</v>
+        <v>46185.47916666666</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>66.351</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>-148.227</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>-148.227</v>
       </c>
       <c r="E144">
         <v>47</v>
@@ -3854,16 +3854,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2">
-        <v>46177.48958333334</v>
+        <v>46185.48958333334</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>22.569</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>31.942</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>31.942</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3874,16 +3874,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2">
-        <v>46177.5</v>
+        <v>46185.5</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>14.151</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>16.437</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>16.437</v>
       </c>
       <c r="E146">
         <v>49</v>
@@ -3894,16 +3894,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="2">
-        <v>46177.51041666666</v>
+        <v>46185.51041666666</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>24.922</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>254.663</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>254.663</v>
       </c>
       <c r="E147">
         <v>50</v>
@@ -3914,16 +3914,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="2">
-        <v>46177.52083333334</v>
+        <v>46185.52083333334</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>33.643</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>266.944</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>266.944</v>
       </c>
       <c r="E148">
         <v>51</v>
@@ -3934,16 +3934,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2">
-        <v>46177.53125</v>
+        <v>46185.53125</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>24.711</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>311.441</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>311.441</v>
       </c>
       <c r="E149">
         <v>52</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2">
-        <v>46177.54166666666</v>
+        <v>46185.54166666666</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2">
-        <v>46177.55208333334</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2">
-        <v>46177.5625</v>
+        <v>46185.5625</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="2">
-        <v>46177.57291666666</v>
+        <v>46185.57291666666</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="2">
-        <v>46177.58333333334</v>
+        <v>46185.58333333334</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2">
-        <v>46177.59375</v>
+        <v>46185.59375</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="2">
-        <v>46177.60416666666</v>
+        <v>46185.60416666666</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="2">
-        <v>46177.61458333334</v>
+        <v>46185.61458333334</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="2">
-        <v>46177.625</v>
+        <v>46185.625</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2">
-        <v>46177.63541666666</v>
+        <v>46185.63541666666</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="2">
-        <v>46177.64583333334</v>
+        <v>46185.64583333334</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4174,7 +4174,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2">
-        <v>46177.65625</v>
+        <v>46185.65625</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="2">
-        <v>46177.66666666666</v>
+        <v>46185.66666666666</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2">
-        <v>46177.67708333334</v>
+        <v>46185.67708333334</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4234,7 +4234,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="2">
-        <v>46177.6875</v>
+        <v>46185.6875</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2">
-        <v>46177.69791666666</v>
+        <v>46185.69791666666</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="2">
-        <v>46177.70833333334</v>
+        <v>46185.70833333334</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2">
-        <v>46177.71875</v>
+        <v>46185.71875</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="2">
-        <v>46177.72916666666</v>
+        <v>46185.72916666666</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2">
-        <v>46177.73958333334</v>
+        <v>46185.73958333334</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="2">
-        <v>46177.75</v>
+        <v>46185.75</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4374,7 +4374,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="2">
-        <v>46177.76041666666</v>
+        <v>46185.76041666666</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="2">
-        <v>46177.77083333334</v>
+        <v>46185.77083333334</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="2">
-        <v>46177.78125</v>
+        <v>46185.78125</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="2">
-        <v>46177.79166666666</v>
+        <v>46185.79166666666</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="2">
-        <v>46177.80208333334</v>
+        <v>46185.80208333334</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="2">
-        <v>46177.8125</v>
+        <v>46185.8125</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="2">
-        <v>46177.82291666666</v>
+        <v>46185.82291666666</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="2">
-        <v>46177.83333333334</v>
+        <v>46185.83333333334</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2">
-        <v>46177.84375</v>
+        <v>46185.84375</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4554,7 +4554,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="2">
-        <v>46177.85416666666</v>
+        <v>46185.85416666666</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="2">
-        <v>46177.86458333334</v>
+        <v>46185.86458333334</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2">
-        <v>46177.875</v>
+        <v>46185.875</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2">
-        <v>46177.88541666666</v>
+        <v>46185.88541666666</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2">
-        <v>46177.89583333334</v>
+        <v>46185.89583333334</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4654,7 +4654,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2">
-        <v>46177.90625</v>
+        <v>46185.90625</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2">
-        <v>46177.91666666666</v>
+        <v>46185.91666666666</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2">
-        <v>46177.92708333334</v>
+        <v>46185.92708333334</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2">
-        <v>46177.9375</v>
+        <v>46185.9375</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2">
-        <v>46177.94791666666</v>
+        <v>46185.94791666666</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2">
-        <v>46177.95833333334</v>
+        <v>46185.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2">
-        <v>46177.96875</v>
+        <v>46185.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="2">
-        <v>46177.97916666666</v>
+        <v>46185.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2">
-        <v>46177.98958333334</v>
+        <v>46185.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Imbalance_Historical.xlsx
+++ b/data_fetching/Entsoe/Imbalance_Historical.xlsx
@@ -19,595 +19,595 @@
     <t>Timestamp</t>
   </si>
   <si>
+    <t>Excedent Price</t>
+  </si>
+  <si>
+    <t>Deficit Price</t>
+  </si>
+  <si>
     <t>Imbalance Volume</t>
   </si>
   <si>
-    <t>Excedent Price</t>
-  </si>
-  <si>
-    <t>Deficit Price</t>
-  </si>
-  <si>
     <t>Quarter</t>
   </si>
   <si>
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.06.20261</t>
-  </si>
-  <si>
-    <t>11.06.20262</t>
-  </si>
-  <si>
-    <t>11.06.20263</t>
-  </si>
-  <si>
-    <t>11.06.20264</t>
-  </si>
-  <si>
-    <t>11.06.20265</t>
-  </si>
-  <si>
-    <t>11.06.20266</t>
-  </si>
-  <si>
-    <t>11.06.20267</t>
-  </si>
-  <si>
-    <t>11.06.20268</t>
-  </si>
-  <si>
-    <t>11.06.20269</t>
-  </si>
-  <si>
-    <t>11.06.202610</t>
-  </si>
-  <si>
-    <t>11.06.202611</t>
-  </si>
-  <si>
-    <t>11.06.202612</t>
-  </si>
-  <si>
-    <t>11.06.202613</t>
-  </si>
-  <si>
-    <t>11.06.202614</t>
-  </si>
-  <si>
-    <t>11.06.202615</t>
-  </si>
-  <si>
-    <t>11.06.202616</t>
-  </si>
-  <si>
-    <t>11.06.202617</t>
-  </si>
-  <si>
-    <t>11.06.202618</t>
-  </si>
-  <si>
-    <t>11.06.202619</t>
-  </si>
-  <si>
-    <t>11.06.202620</t>
-  </si>
-  <si>
-    <t>11.06.202621</t>
-  </si>
-  <si>
-    <t>11.06.202622</t>
-  </si>
-  <si>
-    <t>11.06.202623</t>
-  </si>
-  <si>
-    <t>11.06.202624</t>
-  </si>
-  <si>
-    <t>11.06.202625</t>
-  </si>
-  <si>
-    <t>11.06.202626</t>
-  </si>
-  <si>
-    <t>11.06.202627</t>
-  </si>
-  <si>
-    <t>11.06.202628</t>
-  </si>
-  <si>
-    <t>11.06.202629</t>
-  </si>
-  <si>
-    <t>11.06.202630</t>
-  </si>
-  <si>
-    <t>11.06.202631</t>
-  </si>
-  <si>
-    <t>11.06.202632</t>
-  </si>
-  <si>
-    <t>11.06.202633</t>
-  </si>
-  <si>
-    <t>11.06.202634</t>
-  </si>
-  <si>
-    <t>11.06.202635</t>
-  </si>
-  <si>
-    <t>11.06.202636</t>
-  </si>
-  <si>
-    <t>11.06.202637</t>
-  </si>
-  <si>
-    <t>11.06.202638</t>
-  </si>
-  <si>
-    <t>11.06.202639</t>
-  </si>
-  <si>
-    <t>11.06.202640</t>
-  </si>
-  <si>
-    <t>11.06.202641</t>
-  </si>
-  <si>
-    <t>11.06.202642</t>
-  </si>
-  <si>
-    <t>11.06.202643</t>
-  </si>
-  <si>
-    <t>11.06.202644</t>
-  </si>
-  <si>
-    <t>11.06.202645</t>
-  </si>
-  <si>
-    <t>11.06.202646</t>
-  </si>
-  <si>
-    <t>11.06.202647</t>
-  </si>
-  <si>
-    <t>11.06.202648</t>
-  </si>
-  <si>
-    <t>11.06.202649</t>
-  </si>
-  <si>
-    <t>11.06.202650</t>
-  </si>
-  <si>
-    <t>11.06.202651</t>
-  </si>
-  <si>
-    <t>11.06.202652</t>
-  </si>
-  <si>
-    <t>11.06.202653</t>
-  </si>
-  <si>
-    <t>11.06.202654</t>
-  </si>
-  <si>
-    <t>11.06.202655</t>
-  </si>
-  <si>
-    <t>11.06.202656</t>
-  </si>
-  <si>
-    <t>11.06.202657</t>
-  </si>
-  <si>
-    <t>11.06.202658</t>
-  </si>
-  <si>
-    <t>11.06.202659</t>
-  </si>
-  <si>
-    <t>11.06.202660</t>
-  </si>
-  <si>
-    <t>11.06.202661</t>
-  </si>
-  <si>
-    <t>11.06.202662</t>
-  </si>
-  <si>
-    <t>11.06.202663</t>
-  </si>
-  <si>
-    <t>11.06.202664</t>
-  </si>
-  <si>
-    <t>11.06.202665</t>
-  </si>
-  <si>
-    <t>11.06.202666</t>
-  </si>
-  <si>
-    <t>11.06.202667</t>
-  </si>
-  <si>
-    <t>11.06.202668</t>
-  </si>
-  <si>
-    <t>11.06.202669</t>
-  </si>
-  <si>
-    <t>11.06.202670</t>
-  </si>
-  <si>
-    <t>11.06.202671</t>
-  </si>
-  <si>
-    <t>11.06.202672</t>
-  </si>
-  <si>
-    <t>11.06.202673</t>
-  </si>
-  <si>
-    <t>11.06.202674</t>
-  </si>
-  <si>
-    <t>11.06.202675</t>
-  </si>
-  <si>
-    <t>11.06.202676</t>
-  </si>
-  <si>
-    <t>11.06.202677</t>
-  </si>
-  <si>
-    <t>11.06.202678</t>
-  </si>
-  <si>
-    <t>11.06.202679</t>
-  </si>
-  <si>
-    <t>11.06.202680</t>
-  </si>
-  <si>
-    <t>11.06.202681</t>
-  </si>
-  <si>
-    <t>11.06.202682</t>
-  </si>
-  <si>
-    <t>11.06.202683</t>
-  </si>
-  <si>
-    <t>11.06.202684</t>
-  </si>
-  <si>
-    <t>11.06.202685</t>
-  </si>
-  <si>
-    <t>11.06.202686</t>
-  </si>
-  <si>
-    <t>11.06.202687</t>
-  </si>
-  <si>
-    <t>11.06.202688</t>
-  </si>
-  <si>
-    <t>11.06.202689</t>
-  </si>
-  <si>
-    <t>11.06.202690</t>
-  </si>
-  <si>
-    <t>11.06.202691</t>
-  </si>
-  <si>
-    <t>11.06.202692</t>
-  </si>
-  <si>
-    <t>11.06.202693</t>
-  </si>
-  <si>
-    <t>11.06.202694</t>
-  </si>
-  <si>
-    <t>11.06.202695</t>
-  </si>
-  <si>
-    <t>11.06.202696</t>
-  </si>
-  <si>
-    <t>12.06.20261</t>
-  </si>
-  <si>
-    <t>12.06.20262</t>
-  </si>
-  <si>
-    <t>12.06.20263</t>
-  </si>
-  <si>
-    <t>12.06.20264</t>
-  </si>
-  <si>
-    <t>12.06.20265</t>
-  </si>
-  <si>
-    <t>12.06.20266</t>
-  </si>
-  <si>
-    <t>12.06.20267</t>
-  </si>
-  <si>
-    <t>12.06.20268</t>
-  </si>
-  <si>
-    <t>12.06.20269</t>
-  </si>
-  <si>
-    <t>12.06.202610</t>
-  </si>
-  <si>
-    <t>12.06.202611</t>
-  </si>
-  <si>
-    <t>12.06.202612</t>
-  </si>
-  <si>
-    <t>12.06.202613</t>
-  </si>
-  <si>
-    <t>12.06.202614</t>
-  </si>
-  <si>
-    <t>12.06.202615</t>
-  </si>
-  <si>
-    <t>12.06.202616</t>
-  </si>
-  <si>
-    <t>12.06.202617</t>
-  </si>
-  <si>
-    <t>12.06.202618</t>
-  </si>
-  <si>
-    <t>12.06.202619</t>
-  </si>
-  <si>
-    <t>12.06.202620</t>
-  </si>
-  <si>
-    <t>12.06.202621</t>
-  </si>
-  <si>
-    <t>12.06.202622</t>
-  </si>
-  <si>
-    <t>12.06.202623</t>
-  </si>
-  <si>
-    <t>12.06.202624</t>
-  </si>
-  <si>
-    <t>12.06.202625</t>
-  </si>
-  <si>
-    <t>12.06.202626</t>
-  </si>
-  <si>
-    <t>12.06.202627</t>
-  </si>
-  <si>
-    <t>12.06.202628</t>
-  </si>
-  <si>
-    <t>12.06.202629</t>
-  </si>
-  <si>
-    <t>12.06.202630</t>
-  </si>
-  <si>
-    <t>12.06.202631</t>
-  </si>
-  <si>
-    <t>12.06.202632</t>
-  </si>
-  <si>
-    <t>12.06.202633</t>
-  </si>
-  <si>
-    <t>12.06.202634</t>
-  </si>
-  <si>
-    <t>12.06.202635</t>
-  </si>
-  <si>
-    <t>12.06.202636</t>
-  </si>
-  <si>
-    <t>12.06.202637</t>
-  </si>
-  <si>
-    <t>12.06.202638</t>
-  </si>
-  <si>
-    <t>12.06.202639</t>
-  </si>
-  <si>
-    <t>12.06.202640</t>
-  </si>
-  <si>
-    <t>12.06.202641</t>
-  </si>
-  <si>
-    <t>12.06.202642</t>
-  </si>
-  <si>
-    <t>12.06.202643</t>
-  </si>
-  <si>
-    <t>12.06.202644</t>
-  </si>
-  <si>
-    <t>12.06.202645</t>
-  </si>
-  <si>
-    <t>12.06.202646</t>
-  </si>
-  <si>
-    <t>12.06.202647</t>
-  </si>
-  <si>
-    <t>12.06.202648</t>
-  </si>
-  <si>
-    <t>12.06.202649</t>
-  </si>
-  <si>
-    <t>12.06.202650</t>
-  </si>
-  <si>
-    <t>12.06.202651</t>
-  </si>
-  <si>
-    <t>12.06.202652</t>
-  </si>
-  <si>
-    <t>12.06.202653</t>
-  </si>
-  <si>
-    <t>12.06.202654</t>
-  </si>
-  <si>
-    <t>12.06.202655</t>
-  </si>
-  <si>
-    <t>12.06.202656</t>
-  </si>
-  <si>
-    <t>12.06.202657</t>
-  </si>
-  <si>
-    <t>12.06.202658</t>
-  </si>
-  <si>
-    <t>12.06.202659</t>
-  </si>
-  <si>
-    <t>12.06.202660</t>
-  </si>
-  <si>
-    <t>12.06.202661</t>
-  </si>
-  <si>
-    <t>12.06.202662</t>
-  </si>
-  <si>
-    <t>12.06.202663</t>
-  </si>
-  <si>
-    <t>12.06.202664</t>
-  </si>
-  <si>
-    <t>12.06.202665</t>
-  </si>
-  <si>
-    <t>12.06.202666</t>
-  </si>
-  <si>
-    <t>12.06.202667</t>
-  </si>
-  <si>
-    <t>12.06.202668</t>
-  </si>
-  <si>
-    <t>12.06.202669</t>
-  </si>
-  <si>
-    <t>12.06.202670</t>
-  </si>
-  <si>
-    <t>12.06.202671</t>
-  </si>
-  <si>
-    <t>12.06.202672</t>
-  </si>
-  <si>
-    <t>12.06.202673</t>
-  </si>
-  <si>
-    <t>12.06.202674</t>
-  </si>
-  <si>
-    <t>12.06.202675</t>
-  </si>
-  <si>
-    <t>12.06.202676</t>
-  </si>
-  <si>
-    <t>12.06.202677</t>
-  </si>
-  <si>
-    <t>12.06.202678</t>
-  </si>
-  <si>
-    <t>12.06.202679</t>
-  </si>
-  <si>
-    <t>12.06.202680</t>
-  </si>
-  <si>
-    <t>12.06.202681</t>
-  </si>
-  <si>
-    <t>12.06.202682</t>
-  </si>
-  <si>
-    <t>12.06.202683</t>
-  </si>
-  <si>
-    <t>12.06.202684</t>
-  </si>
-  <si>
-    <t>12.06.202685</t>
-  </si>
-  <si>
-    <t>12.06.202686</t>
-  </si>
-  <si>
-    <t>12.06.202687</t>
-  </si>
-  <si>
-    <t>12.06.202688</t>
-  </si>
-  <si>
-    <t>12.06.202689</t>
-  </si>
-  <si>
-    <t>12.06.202690</t>
-  </si>
-  <si>
-    <t>12.06.202691</t>
-  </si>
-  <si>
-    <t>12.06.202692</t>
-  </si>
-  <si>
-    <t>12.06.202693</t>
-  </si>
-  <si>
-    <t>12.06.202694</t>
-  </si>
-  <si>
-    <t>12.06.202695</t>
-  </si>
-  <si>
-    <t>12.06.202696</t>
+    <t>09.07.20261</t>
+  </si>
+  <si>
+    <t>09.07.20262</t>
+  </si>
+  <si>
+    <t>09.07.20263</t>
+  </si>
+  <si>
+    <t>09.07.20264</t>
+  </si>
+  <si>
+    <t>09.07.20265</t>
+  </si>
+  <si>
+    <t>09.07.20266</t>
+  </si>
+  <si>
+    <t>09.07.20267</t>
+  </si>
+  <si>
+    <t>09.07.20268</t>
+  </si>
+  <si>
+    <t>09.07.20269</t>
+  </si>
+  <si>
+    <t>09.07.202610</t>
+  </si>
+  <si>
+    <t>09.07.202611</t>
+  </si>
+  <si>
+    <t>09.07.202612</t>
+  </si>
+  <si>
+    <t>09.07.202613</t>
+  </si>
+  <si>
+    <t>09.07.202614</t>
+  </si>
+  <si>
+    <t>09.07.202615</t>
+  </si>
+  <si>
+    <t>09.07.202616</t>
+  </si>
+  <si>
+    <t>09.07.202617</t>
+  </si>
+  <si>
+    <t>09.07.202618</t>
+  </si>
+  <si>
+    <t>09.07.202619</t>
+  </si>
+  <si>
+    <t>09.07.202620</t>
+  </si>
+  <si>
+    <t>09.07.202621</t>
+  </si>
+  <si>
+    <t>09.07.202622</t>
+  </si>
+  <si>
+    <t>09.07.202623</t>
+  </si>
+  <si>
+    <t>09.07.202624</t>
+  </si>
+  <si>
+    <t>09.07.202625</t>
+  </si>
+  <si>
+    <t>09.07.202626</t>
+  </si>
+  <si>
+    <t>09.07.202627</t>
+  </si>
+  <si>
+    <t>09.07.202628</t>
+  </si>
+  <si>
+    <t>09.07.202629</t>
+  </si>
+  <si>
+    <t>09.07.202630</t>
+  </si>
+  <si>
+    <t>09.07.202631</t>
+  </si>
+  <si>
+    <t>09.07.202632</t>
+  </si>
+  <si>
+    <t>09.07.202633</t>
+  </si>
+  <si>
+    <t>09.07.202634</t>
+  </si>
+  <si>
+    <t>09.07.202635</t>
+  </si>
+  <si>
+    <t>09.07.202636</t>
+  </si>
+  <si>
+    <t>09.07.202637</t>
+  </si>
+  <si>
+    <t>09.07.202638</t>
+  </si>
+  <si>
+    <t>09.07.202639</t>
+  </si>
+  <si>
+    <t>09.07.202640</t>
+  </si>
+  <si>
+    <t>09.07.202641</t>
+  </si>
+  <si>
+    <t>09.07.202642</t>
+  </si>
+  <si>
+    <t>09.07.202643</t>
+  </si>
+  <si>
+    <t>09.07.202644</t>
+  </si>
+  <si>
+    <t>09.07.202645</t>
+  </si>
+  <si>
+    <t>09.07.202646</t>
+  </si>
+  <si>
+    <t>09.07.202647</t>
+  </si>
+  <si>
+    <t>09.07.202648</t>
+  </si>
+  <si>
+    <t>09.07.202649</t>
+  </si>
+  <si>
+    <t>09.07.202650</t>
+  </si>
+  <si>
+    <t>09.07.202651</t>
+  </si>
+  <si>
+    <t>09.07.202652</t>
+  </si>
+  <si>
+    <t>09.07.202653</t>
+  </si>
+  <si>
+    <t>09.07.202654</t>
+  </si>
+  <si>
+    <t>09.07.202655</t>
+  </si>
+  <si>
+    <t>09.07.202656</t>
+  </si>
+  <si>
+    <t>09.07.202657</t>
+  </si>
+  <si>
+    <t>09.07.202658</t>
+  </si>
+  <si>
+    <t>09.07.202659</t>
+  </si>
+  <si>
+    <t>09.07.202660</t>
+  </si>
+  <si>
+    <t>09.07.202661</t>
+  </si>
+  <si>
+    <t>09.07.202662</t>
+  </si>
+  <si>
+    <t>09.07.202663</t>
+  </si>
+  <si>
+    <t>09.07.202664</t>
+  </si>
+  <si>
+    <t>09.07.202665</t>
+  </si>
+  <si>
+    <t>09.07.202666</t>
+  </si>
+  <si>
+    <t>09.07.202667</t>
+  </si>
+  <si>
+    <t>09.07.202668</t>
+  </si>
+  <si>
+    <t>09.07.202669</t>
+  </si>
+  <si>
+    <t>09.07.202670</t>
+  </si>
+  <si>
+    <t>09.07.202671</t>
+  </si>
+  <si>
+    <t>09.07.202672</t>
+  </si>
+  <si>
+    <t>09.07.202673</t>
+  </si>
+  <si>
+    <t>09.07.202674</t>
+  </si>
+  <si>
+    <t>09.07.202675</t>
+  </si>
+  <si>
+    <t>09.07.202676</t>
+  </si>
+  <si>
+    <t>09.07.202677</t>
+  </si>
+  <si>
+    <t>09.07.202678</t>
+  </si>
+  <si>
+    <t>09.07.202679</t>
+  </si>
+  <si>
+    <t>09.07.202680</t>
+  </si>
+  <si>
+    <t>09.07.202681</t>
+  </si>
+  <si>
+    <t>09.07.202682</t>
+  </si>
+  <si>
+    <t>09.07.202683</t>
+  </si>
+  <si>
+    <t>09.07.202684</t>
+  </si>
+  <si>
+    <t>09.07.202685</t>
+  </si>
+  <si>
+    <t>09.07.202686</t>
+  </si>
+  <si>
+    <t>09.07.202687</t>
+  </si>
+  <si>
+    <t>09.07.202688</t>
+  </si>
+  <si>
+    <t>09.07.202689</t>
+  </si>
+  <si>
+    <t>09.07.202690</t>
+  </si>
+  <si>
+    <t>09.07.202691</t>
+  </si>
+  <si>
+    <t>09.07.202692</t>
+  </si>
+  <si>
+    <t>09.07.202693</t>
+  </si>
+  <si>
+    <t>09.07.202694</t>
+  </si>
+  <si>
+    <t>09.07.202695</t>
+  </si>
+  <si>
+    <t>09.07.202696</t>
+  </si>
+  <si>
+    <t>10.07.20261</t>
+  </si>
+  <si>
+    <t>10.07.20262</t>
+  </si>
+  <si>
+    <t>10.07.20263</t>
+  </si>
+  <si>
+    <t>10.07.20264</t>
+  </si>
+  <si>
+    <t>10.07.20265</t>
+  </si>
+  <si>
+    <t>10.07.20266</t>
+  </si>
+  <si>
+    <t>10.07.20267</t>
+  </si>
+  <si>
+    <t>10.07.20268</t>
+  </si>
+  <si>
+    <t>10.07.20269</t>
+  </si>
+  <si>
+    <t>10.07.202610</t>
+  </si>
+  <si>
+    <t>10.07.202611</t>
+  </si>
+  <si>
+    <t>10.07.202612</t>
+  </si>
+  <si>
+    <t>10.07.202613</t>
+  </si>
+  <si>
+    <t>10.07.202614</t>
+  </si>
+  <si>
+    <t>10.07.202615</t>
+  </si>
+  <si>
+    <t>10.07.202616</t>
+  </si>
+  <si>
+    <t>10.07.202617</t>
+  </si>
+  <si>
+    <t>10.07.202618</t>
+  </si>
+  <si>
+    <t>10.07.202619</t>
+  </si>
+  <si>
+    <t>10.07.202620</t>
+  </si>
+  <si>
+    <t>10.07.202621</t>
+  </si>
+  <si>
+    <t>10.07.202622</t>
+  </si>
+  <si>
+    <t>10.07.202623</t>
+  </si>
+  <si>
+    <t>10.07.202624</t>
+  </si>
+  <si>
+    <t>10.07.202625</t>
+  </si>
+  <si>
+    <t>10.07.202626</t>
+  </si>
+  <si>
+    <t>10.07.202627</t>
+  </si>
+  <si>
+    <t>10.07.202628</t>
+  </si>
+  <si>
+    <t>10.07.202629</t>
+  </si>
+  <si>
+    <t>10.07.202630</t>
+  </si>
+  <si>
+    <t>10.07.202631</t>
+  </si>
+  <si>
+    <t>10.07.202632</t>
+  </si>
+  <si>
+    <t>10.07.202633</t>
+  </si>
+  <si>
+    <t>10.07.202634</t>
+  </si>
+  <si>
+    <t>10.07.202635</t>
+  </si>
+  <si>
+    <t>10.07.202636</t>
+  </si>
+  <si>
+    <t>10.07.202637</t>
+  </si>
+  <si>
+    <t>10.07.202638</t>
+  </si>
+  <si>
+    <t>10.07.202639</t>
+  </si>
+  <si>
+    <t>10.07.202640</t>
+  </si>
+  <si>
+    <t>10.07.202641</t>
+  </si>
+  <si>
+    <t>10.07.202642</t>
+  </si>
+  <si>
+    <t>10.07.202643</t>
+  </si>
+  <si>
+    <t>10.07.202644</t>
+  </si>
+  <si>
+    <t>10.07.202645</t>
+  </si>
+  <si>
+    <t>10.07.202646</t>
+  </si>
+  <si>
+    <t>10.07.202647</t>
+  </si>
+  <si>
+    <t>10.07.202648</t>
+  </si>
+  <si>
+    <t>10.07.202649</t>
+  </si>
+  <si>
+    <t>10.07.202650</t>
+  </si>
+  <si>
+    <t>10.07.202651</t>
+  </si>
+  <si>
+    <t>10.07.202652</t>
+  </si>
+  <si>
+    <t>10.07.202653</t>
+  </si>
+  <si>
+    <t>10.07.202654</t>
+  </si>
+  <si>
+    <t>10.07.202655</t>
+  </si>
+  <si>
+    <t>10.07.202656</t>
+  </si>
+  <si>
+    <t>10.07.202657</t>
+  </si>
+  <si>
+    <t>10.07.202658</t>
+  </si>
+  <si>
+    <t>10.07.202659</t>
+  </si>
+  <si>
+    <t>10.07.202660</t>
+  </si>
+  <si>
+    <t>10.07.202661</t>
+  </si>
+  <si>
+    <t>10.07.202662</t>
+  </si>
+  <si>
+    <t>10.07.202663</t>
+  </si>
+  <si>
+    <t>10.07.202664</t>
+  </si>
+  <si>
+    <t>10.07.202665</t>
+  </si>
+  <si>
+    <t>10.07.202666</t>
+  </si>
+  <si>
+    <t>10.07.202667</t>
+  </si>
+  <si>
+    <t>10.07.202668</t>
+  </si>
+  <si>
+    <t>10.07.202669</t>
+  </si>
+  <si>
+    <t>10.07.202670</t>
+  </si>
+  <si>
+    <t>10.07.202671</t>
+  </si>
+  <si>
+    <t>10.07.202672</t>
+  </si>
+  <si>
+    <t>10.07.202673</t>
+  </si>
+  <si>
+    <t>10.07.202674</t>
+  </si>
+  <si>
+    <t>10.07.202675</t>
+  </si>
+  <si>
+    <t>10.07.202676</t>
+  </si>
+  <si>
+    <t>10.07.202677</t>
+  </si>
+  <si>
+    <t>10.07.202678</t>
+  </si>
+  <si>
+    <t>10.07.202679</t>
+  </si>
+  <si>
+    <t>10.07.202680</t>
+  </si>
+  <si>
+    <t>10.07.202681</t>
+  </si>
+  <si>
+    <t>10.07.202682</t>
+  </si>
+  <si>
+    <t>10.07.202683</t>
+  </si>
+  <si>
+    <t>10.07.202684</t>
+  </si>
+  <si>
+    <t>10.07.202685</t>
+  </si>
+  <si>
+    <t>10.07.202686</t>
+  </si>
+  <si>
+    <t>10.07.202687</t>
+  </si>
+  <si>
+    <t>10.07.202688</t>
+  </si>
+  <si>
+    <t>10.07.202689</t>
+  </si>
+  <si>
+    <t>10.07.202690</t>
+  </si>
+  <si>
+    <t>10.07.202691</t>
+  </si>
+  <si>
+    <t>10.07.202692</t>
+  </si>
+  <si>
+    <t>10.07.202693</t>
+  </si>
+  <si>
+    <t>10.07.202694</t>
+  </si>
+  <si>
+    <t>10.07.202695</t>
+  </si>
+  <si>
+    <t>10.07.202696</t>
   </si>
 </sst>
 </file>
@@ -994,16 +994,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2">
-        <v>46184</v>
+        <v>46212</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>303.949</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>303.949</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>7.377</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1014,16 +1014,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2">
-        <v>46184.01041666666</v>
+        <v>46212.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>884.02</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>884.02</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-2.565</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2">
-        <v>46184.02083333334</v>
+        <v>46212.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>255.844</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>255.844</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>18.935</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2">
-        <v>46184.03125</v>
+        <v>46212.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>251.788</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>251.788</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>12.766</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2">
-        <v>46184.04166666666</v>
+        <v>46212.04166666666</v>
       </c>
       <c r="B6">
-        <v>-8.977</v>
+        <v>144.758</v>
       </c>
       <c r="C6">
-        <v>998.741</v>
+        <v>144.758</v>
       </c>
       <c r="D6">
-        <v>998.741</v>
+        <v>36.677</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1094,16 +1094,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2">
-        <v>46184.05208333334</v>
+        <v>46212.05208333334</v>
       </c>
       <c r="B7">
-        <v>-34.28</v>
+        <v>-3789.053</v>
       </c>
       <c r="C7">
-        <v>907.271</v>
+        <v>-3789.053</v>
       </c>
       <c r="D7">
-        <v>907.271</v>
+        <v>78.074</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1114,16 +1114,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2">
-        <v>46184.0625</v>
+        <v>46212.0625</v>
       </c>
       <c r="B8">
-        <v>-18.698</v>
+        <v>-667.223</v>
       </c>
       <c r="C8">
-        <v>880.121</v>
+        <v>-667.223</v>
       </c>
       <c r="D8">
-        <v>880.121</v>
+        <v>67.83499999999999</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1134,16 +1134,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2">
-        <v>46184.07291666666</v>
+        <v>46212.07291666666</v>
       </c>
       <c r="B9">
-        <v>-21.68</v>
+        <v>-12.047</v>
       </c>
       <c r="C9">
-        <v>873.194</v>
+        <v>-12.047</v>
       </c>
       <c r="D9">
-        <v>873.194</v>
+        <v>69.092</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1154,16 +1154,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2">
-        <v>46184.08333333334</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B10">
-        <v>-39.951</v>
+        <v>97.465</v>
       </c>
       <c r="C10">
-        <v>814.143</v>
+        <v>97.465</v>
       </c>
       <c r="D10">
-        <v>814.143</v>
+        <v>66.468</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2">
-        <v>46184.09375</v>
+        <v>46212.09375</v>
       </c>
       <c r="B11">
-        <v>0.358</v>
+        <v>152.033</v>
       </c>
       <c r="C11">
-        <v>270.124</v>
+        <v>152.033</v>
       </c>
       <c r="D11">
-        <v>270.124</v>
+        <v>65.56399999999999</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1194,16 +1194,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="2">
-        <v>46184.10416666666</v>
+        <v>46212.10416666666</v>
       </c>
       <c r="B12">
-        <v>-16.606</v>
+        <v>42.612</v>
       </c>
       <c r="C12">
-        <v>853.804</v>
+        <v>42.612</v>
       </c>
       <c r="D12">
-        <v>853.804</v>
+        <v>80.343</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2">
-        <v>46184.11458333334</v>
+        <v>46212.11458333334</v>
       </c>
       <c r="B13">
-        <v>-32.678</v>
+        <v>-227.73</v>
       </c>
       <c r="C13">
-        <v>869.696</v>
+        <v>-227.73</v>
       </c>
       <c r="D13">
-        <v>869.696</v>
+        <v>78.78100000000001</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2">
-        <v>46184.125</v>
+        <v>46212.125</v>
       </c>
       <c r="B14">
-        <v>1.199</v>
+        <v>-18.31</v>
       </c>
       <c r="C14">
-        <v>274.759</v>
+        <v>-18.31</v>
       </c>
       <c r="D14">
-        <v>274.759</v>
+        <v>70.557</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -1254,16 +1254,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="2">
-        <v>46184.13541666666</v>
+        <v>46212.13541666666</v>
       </c>
       <c r="B15">
-        <v>-2.145</v>
+        <v>45.259</v>
       </c>
       <c r="C15">
-        <v>898.453</v>
+        <v>45.259</v>
       </c>
       <c r="D15">
-        <v>898.453</v>
+        <v>78.587</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -1274,16 +1274,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2">
-        <v>46184.14583333334</v>
+        <v>46212.14583333334</v>
       </c>
       <c r="B16">
-        <v>-21.956</v>
+        <v>26.844</v>
       </c>
       <c r="C16">
-        <v>898.0890000000001</v>
+        <v>26.844</v>
       </c>
       <c r="D16">
-        <v>898.0890000000001</v>
+        <v>53.855</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2">
-        <v>46184.15625</v>
+        <v>46212.15625</v>
       </c>
       <c r="B17">
-        <v>-48.768</v>
+        <v>2.883</v>
       </c>
       <c r="C17">
-        <v>867.833</v>
+        <v>2.883</v>
       </c>
       <c r="D17">
-        <v>867.833</v>
+        <v>55.29</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -1314,16 +1314,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2">
-        <v>46184.16666666666</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B18">
-        <v>-14.958</v>
+        <v>130.245</v>
       </c>
       <c r="C18">
-        <v>851.606</v>
+        <v>130.245</v>
       </c>
       <c r="D18">
-        <v>851.606</v>
+        <v>83.2</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2">
-        <v>46184.17708333334</v>
+        <v>46212.17708333334</v>
       </c>
       <c r="B19">
-        <v>7.638</v>
+        <v>98.88</v>
       </c>
       <c r="C19">
-        <v>260.301</v>
+        <v>98.88</v>
       </c>
       <c r="D19">
-        <v>260.301</v>
+        <v>92.31</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -1354,16 +1354,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2">
-        <v>46184.1875</v>
+        <v>46212.1875</v>
       </c>
       <c r="B20">
-        <v>29.658</v>
+        <v>12.589</v>
       </c>
       <c r="C20">
-        <v>135.754</v>
+        <v>12.589</v>
       </c>
       <c r="D20">
-        <v>135.754</v>
+        <v>62.582</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -1374,16 +1374,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2">
-        <v>46184.19791666666</v>
+        <v>46212.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.797</v>
+        <v>122.387</v>
       </c>
       <c r="C21">
-        <v>266.801</v>
+        <v>122.387</v>
       </c>
       <c r="D21">
-        <v>266.801</v>
+        <v>18.759</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2">
-        <v>46184.20833333334</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B22">
-        <v>13.198</v>
+        <v>151.796</v>
       </c>
       <c r="C22">
-        <v>-19.091</v>
+        <v>151.796</v>
       </c>
       <c r="D22">
-        <v>-19.091</v>
+        <v>36.063</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -1414,16 +1414,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2">
-        <v>46184.21875</v>
+        <v>46212.21875</v>
       </c>
       <c r="B23">
-        <v>-9.131</v>
+        <v>939.795</v>
       </c>
       <c r="C23">
-        <v>849.5</v>
+        <v>939.795</v>
       </c>
       <c r="D23">
-        <v>849.5</v>
+        <v>-4.138</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -1434,16 +1434,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2">
-        <v>46184.22916666666</v>
+        <v>46212.22916666666</v>
       </c>
       <c r="B24">
-        <v>6.225</v>
+        <v>159.651</v>
       </c>
       <c r="C24">
-        <v>253.894</v>
+        <v>159.651</v>
       </c>
       <c r="D24">
-        <v>253.894</v>
+        <v>22.226</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -1454,16 +1454,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2">
-        <v>46184.23958333334</v>
+        <v>46212.23958333334</v>
       </c>
       <c r="B25">
-        <v>-10.156</v>
+        <v>157.861</v>
       </c>
       <c r="C25">
-        <v>882.7089999999999</v>
+        <v>157.861</v>
       </c>
       <c r="D25">
-        <v>882.7089999999999</v>
+        <v>41.997</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -1474,16 +1474,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2">
-        <v>46184.25</v>
+        <v>46212.25</v>
       </c>
       <c r="B26">
-        <v>-10.357</v>
+        <v>151</v>
       </c>
       <c r="C26">
-        <v>1005.79</v>
+        <v>151</v>
       </c>
       <c r="D26">
-        <v>1005.79</v>
+        <v>0.495</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -1494,16 +1494,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2">
-        <v>46184.26041666666</v>
+        <v>46212.26041666666</v>
       </c>
       <c r="B27">
-        <v>-19.248</v>
+        <v>155.422</v>
       </c>
       <c r="C27">
-        <v>1054.16</v>
+        <v>155.422</v>
       </c>
       <c r="D27">
-        <v>1054.16</v>
+        <v>30.352</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -1514,16 +1514,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2">
-        <v>46184.27083333334</v>
+        <v>46212.27083333334</v>
       </c>
       <c r="B28">
-        <v>-49.469</v>
+        <v>37.434</v>
       </c>
       <c r="C28">
-        <v>943.2910000000001</v>
+        <v>37.434</v>
       </c>
       <c r="D28">
-        <v>943.2910000000001</v>
+        <v>15.059</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2">
-        <v>46184.28125</v>
+        <v>46212.28125</v>
       </c>
       <c r="B29">
-        <v>1.355</v>
+        <v>-119.618</v>
       </c>
       <c r="C29">
-        <v>278.112</v>
+        <v>-119.618</v>
       </c>
       <c r="D29">
-        <v>278.112</v>
+        <v>44.737</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -1554,16 +1554,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2">
-        <v>46184.29166666666</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B30">
-        <v>-47.567</v>
+        <v>203.568</v>
       </c>
       <c r="C30">
-        <v>886.266</v>
+        <v>203.568</v>
       </c>
       <c r="D30">
-        <v>886.266</v>
+        <v>21.511</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -1574,16 +1574,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2">
-        <v>46184.30208333334</v>
+        <v>46212.30208333334</v>
       </c>
       <c r="B31">
-        <v>-22.714</v>
+        <v>127.331</v>
       </c>
       <c r="C31">
-        <v>897.2089999999999</v>
+        <v>127.331</v>
       </c>
       <c r="D31">
-        <v>897.2089999999999</v>
+        <v>50.713</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -1594,16 +1594,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2">
-        <v>46184.3125</v>
+        <v>46212.3125</v>
       </c>
       <c r="B32">
-        <v>-47.344</v>
+        <v>161.279</v>
       </c>
       <c r="C32">
-        <v>1245.405</v>
+        <v>161.279</v>
       </c>
       <c r="D32">
-        <v>1245.405</v>
+        <v>31.043</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -1614,16 +1614,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2">
-        <v>46184.32291666666</v>
+        <v>46212.32291666666</v>
       </c>
       <c r="B33">
-        <v>-84.76600000000001</v>
+        <v>153.551</v>
       </c>
       <c r="C33">
-        <v>1045.756</v>
+        <v>153.551</v>
       </c>
       <c r="D33">
-        <v>1045.756</v>
+        <v>15.414</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2">
-        <v>46184.33333333334</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B34">
-        <v>-82.294</v>
+        <v>152.374</v>
       </c>
       <c r="C34">
-        <v>967.838</v>
+        <v>152.374</v>
       </c>
       <c r="D34">
-        <v>967.838</v>
+        <v>54.889</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2">
-        <v>46184.34375</v>
+        <v>46212.34375</v>
       </c>
       <c r="B35">
-        <v>-122.004</v>
+        <v>-53.654</v>
       </c>
       <c r="C35">
-        <v>899.322</v>
+        <v>-53.654</v>
       </c>
       <c r="D35">
-        <v>899.322</v>
+        <v>92.69199999999999</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -1674,16 +1674,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2">
-        <v>46184.35416666666</v>
+        <v>46212.35416666666</v>
       </c>
       <c r="B36">
-        <v>-85.25700000000001</v>
+        <v>117.073</v>
       </c>
       <c r="C36">
-        <v>899.302</v>
+        <v>117.073</v>
       </c>
       <c r="D36">
-        <v>899.302</v>
+        <v>107.153</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -1694,16 +1694,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2">
-        <v>46184.36458333334</v>
+        <v>46212.36458333334</v>
       </c>
       <c r="B37">
-        <v>-86.399</v>
+        <v>-665.203</v>
       </c>
       <c r="C37">
-        <v>899</v>
+        <v>-665.203</v>
       </c>
       <c r="D37">
-        <v>899</v>
+        <v>122.096</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2">
-        <v>46184.375</v>
+        <v>46212.375</v>
       </c>
       <c r="B38">
-        <v>-135.771</v>
+        <v>-592.404</v>
       </c>
       <c r="C38">
-        <v>703.421</v>
+        <v>-592.404</v>
       </c>
       <c r="D38">
-        <v>703.421</v>
+        <v>93.76900000000001</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -1734,16 +1734,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2">
-        <v>46184.38541666666</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="B39">
-        <v>-89.146</v>
+        <v>-278.064</v>
       </c>
       <c r="C39">
-        <v>699</v>
+        <v>-278.064</v>
       </c>
       <c r="D39">
-        <v>699</v>
+        <v>119.038</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -1754,16 +1754,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2">
-        <v>46184.39583333334</v>
+        <v>46212.39583333334</v>
       </c>
       <c r="B40">
-        <v>-22.404</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="C40">
-        <v>704.24</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="D40">
-        <v>704.24</v>
+        <v>136.009</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2">
-        <v>46184.40625</v>
+        <v>46212.40625</v>
       </c>
       <c r="B41">
-        <v>16.127</v>
+        <v>7.18</v>
       </c>
       <c r="C41">
-        <v>-33.354</v>
+        <v>7.18</v>
       </c>
       <c r="D41">
-        <v>-33.354</v>
+        <v>135.104</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2">
-        <v>46184.41666666666</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B42">
-        <v>11.871</v>
+        <v>-53.228</v>
       </c>
       <c r="C42">
-        <v>37.029</v>
+        <v>-53.228</v>
       </c>
       <c r="D42">
-        <v>37.029</v>
+        <v>23.947</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -1814,16 +1814,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2">
-        <v>46184.42708333334</v>
+        <v>46212.42708333334</v>
       </c>
       <c r="B43">
-        <v>-6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C43">
-        <v>688.524</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D43">
-        <v>688.524</v>
+        <v>7.82</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -1834,16 +1834,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2">
-        <v>46184.4375</v>
+        <v>46212.4375</v>
       </c>
       <c r="B44">
-        <v>41.063</v>
+        <v>52.028</v>
       </c>
       <c r="C44">
-        <v>258.661</v>
+        <v>52.028</v>
       </c>
       <c r="D44">
-        <v>258.661</v>
+        <v>4.594</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -1854,16 +1854,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2">
-        <v>46184.44791666666</v>
+        <v>46212.44791666666</v>
       </c>
       <c r="B45">
-        <v>101.436</v>
+        <v>52.299</v>
       </c>
       <c r="C45">
-        <v>-133.199</v>
+        <v>52.299</v>
       </c>
       <c r="D45">
-        <v>-133.199</v>
+        <v>7.159</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -1874,16 +1874,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2">
-        <v>46184.45833333334</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B46">
-        <v>88.571</v>
+        <v>151.873</v>
       </c>
       <c r="C46">
-        <v>-604.222</v>
+        <v>151.873</v>
       </c>
       <c r="D46">
-        <v>-604.222</v>
+        <v>38.493</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -1894,16 +1894,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2">
-        <v>46184.46875</v>
+        <v>46212.46875</v>
       </c>
       <c r="B47">
-        <v>56.381</v>
+        <v>151</v>
       </c>
       <c r="C47">
-        <v>-509.125</v>
+        <v>151</v>
       </c>
       <c r="D47">
-        <v>-509.125</v>
+        <v>4.105</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="2">
-        <v>46184.47916666666</v>
+        <v>46212.47916666666</v>
       </c>
       <c r="B48">
-        <v>31.774</v>
+        <v>839.889</v>
       </c>
       <c r="C48">
-        <v>113.136</v>
+        <v>839.889</v>
       </c>
       <c r="D48">
-        <v>113.136</v>
+        <v>-25.572</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2">
-        <v>46184.48958333334</v>
+        <v>46212.48958333334</v>
       </c>
       <c r="B49">
-        <v>40.934</v>
+        <v>1091.645</v>
       </c>
       <c r="C49">
-        <v>-36.847</v>
+        <v>1091.645</v>
       </c>
       <c r="D49">
-        <v>-36.847</v>
+        <v>-59.441</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1954,16 +1954,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2">
-        <v>46184.5</v>
+        <v>46212.5</v>
       </c>
       <c r="B50">
-        <v>7.026</v>
+        <v>699.883</v>
       </c>
       <c r="C50">
-        <v>91.694</v>
+        <v>699.883</v>
       </c>
       <c r="D50">
-        <v>91.694</v>
+        <v>-49.629</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -1974,16 +1974,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2">
-        <v>46184.51041666666</v>
+        <v>46212.51041666666</v>
       </c>
       <c r="B51">
-        <v>39.83</v>
+        <v>766.927</v>
       </c>
       <c r="C51">
-        <v>44.118</v>
+        <v>766.927</v>
       </c>
       <c r="D51">
-        <v>44.118</v>
+        <v>-79.753</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -1994,16 +1994,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2">
-        <v>46184.52083333334</v>
+        <v>46212.52083333334</v>
       </c>
       <c r="B52">
-        <v>69.81100000000001</v>
+        <v>800.4059999999999</v>
       </c>
       <c r="C52">
-        <v>-1706.231</v>
+        <v>800.4059999999999</v>
       </c>
       <c r="D52">
-        <v>-1706.231</v>
+        <v>-154.347</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="2">
-        <v>46184.53125</v>
+        <v>46212.53125</v>
       </c>
       <c r="B53">
-        <v>55.383</v>
+        <v>768.878</v>
       </c>
       <c r="C53">
-        <v>-18.291</v>
+        <v>768.878</v>
       </c>
       <c r="D53">
-        <v>-18.291</v>
+        <v>-55.573</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2">
-        <v>46184.54166666666</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B54">
-        <v>5.611</v>
+        <v>175.094</v>
       </c>
       <c r="C54">
-        <v>13.618</v>
+        <v>175.094</v>
       </c>
       <c r="D54">
-        <v>13.618</v>
+        <v>44.55</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -2054,16 +2054,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2">
-        <v>46184.55208333334</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="B55">
-        <v>17.71</v>
+        <v>263.732</v>
       </c>
       <c r="C55">
-        <v>17.491</v>
+        <v>263.732</v>
       </c>
       <c r="D55">
-        <v>17.491</v>
+        <v>48.098</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -2074,16 +2074,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2">
-        <v>46184.5625</v>
+        <v>46212.5625</v>
       </c>
       <c r="B56">
-        <v>28.573</v>
+        <v>500</v>
       </c>
       <c r="C56">
-        <v>38.133</v>
+        <v>500</v>
       </c>
       <c r="D56">
-        <v>38.133</v>
+        <v>-7.263</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -2094,16 +2094,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2">
-        <v>46184.57291666666</v>
+        <v>46212.57291666666</v>
       </c>
